--- a/quotes/PR-217-228/Quote_PR217_PR228_Rate_Check.xlsx
+++ b/quotes/PR-217-228/Quote_PR217_PR228_Rate_Check.xlsx
@@ -25,14 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1239" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="460">
   <si>
     <t xml:space="preserve">Zidane Corporation - Quote PR-217 &amp; PR-228: Brand + Buying Rate Check</t>
   </si>
   <si>
-    <t xml:space="preserve">Buying rates = Pakistani online retail (toolsmart.pk, w11stop.com, kamadi.pk, ktools.pk, purchaser.com.pk etc.), Oct 2026. Confidence V = seen online, P = sister item online, E = market estimate - phone pe confirm karo.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Target markup on buying (High):</t>
   </si>
   <si>
@@ -186,15 +183,12 @@
     <t xml:space="preserve">DOUBLE OPEN END WRENCH 36X41</t>
   </si>
   <si>
-    <t xml:space="preserve">w11stop Licota single 10x11 = 530 (scaled)</t>
+    <t xml:space="preserve">toolsmart Licota wrench sets (scaled); goldentools.ae Licota</t>
   </si>
   <si>
     <t xml:space="preserve">DOUBLE OPEN END WRENCH 41X46</t>
   </si>
   <si>
-    <t xml:space="preserve">w11stop Licota singles (scaled)</t>
-  </si>
-  <si>
     <t xml:space="preserve">COMBINATION WRENCH 8 TO 32 (14 PCS SET)</t>
   </si>
   <si>
@@ -228,13 +222,13 @@
     <t xml:space="preserve">LONG TYPE HEX KEY WRENCH SET 09 PCS</t>
   </si>
   <si>
-    <t xml:space="preserve">toolsmart 4,400; w11stop 2,320</t>
+    <t xml:space="preserve">toolsmart 4,400 (long) / 3,740 (extra long)</t>
   </si>
   <si>
     <t xml:space="preserve">SHORT TYPE HEX KEY WRENCH SET (09PCS)</t>
   </si>
   <si>
-    <t xml:space="preserve">toolsmart/w11stop Licota hex</t>
+    <t xml:space="preserve">toolsmart Licota hex sets (scaled)</t>
   </si>
   <si>
     <t xml:space="preserve">LONG TYPE HEX WRENCH SET 09 PCS</t>
@@ -246,13 +240,13 @@
     <t xml:space="preserve">ALLEN HEX KEY 12MM</t>
   </si>
   <si>
-    <t xml:space="preserve">w11stop Licota 4mm = 790 (scaled)</t>
+    <t xml:space="preserve">goldentools.ae Licota 12mm AED 250/20pc (~PKR 950 ea)</t>
   </si>
   <si>
     <t xml:space="preserve">ALLEN (HEX) KEY 14MM</t>
   </si>
   <si>
-    <t xml:space="preserve">w11stop Licota (scaled)</t>
+    <t xml:space="preserve">goldentools.ae Licota 12mm (scaled)</t>
   </si>
   <si>
     <t xml:space="preserve">ALLEN (HEX) KEY 16MM</t>
@@ -396,21 +390,18 @@
     <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED WITH HOOK BRAKE 21</t>
   </si>
   <si>
-    <t xml:space="preserve">w11stop Licota ATB-1017D 19,880</t>
+    <t xml:space="preserve">goldentools.ae/amazon.ae Licota 6in 3-jaw AED 105-120 (~PKR 9k) scaled + import</t>
   </si>
   <si>
     <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED WITH HOOK BRAK 250</t>
   </si>
   <si>
-    <t xml:space="preserve">w11stop Licota 2-jaw ATB-1003G 32,700</t>
+    <t xml:space="preserve">goldentools.ae Licota pullers (scaled) + import</t>
   </si>
   <si>
     <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED 160 X 300 MM 5T</t>
   </si>
   <si>
-    <t xml:space="preserve">w11stop Licota pullers</t>
-  </si>
-  <si>
     <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED 250 X 300 MM 7.5T</t>
   </si>
   <si>
@@ -423,13 +414,13 @@
     <t xml:space="preserve">MECHANICAL PULLER 3 ARMED 200X200</t>
   </si>
   <si>
-    <t xml:space="preserve">w11stop Licota 3-jaw ATB-1004F 22,500-38,100</t>
+    <t xml:space="preserve">goldentools.ae Licota 6in 3-jaw AED 120 (scaled to 8in) + import</t>
   </si>
   <si>
     <t xml:space="preserve">MECHANICAL PULLER 3 ARMED 250X250</t>
   </si>
   <si>
-    <t xml:space="preserve">w11stop Licota 3-jaw 38,100</t>
+    <t xml:space="preserve">goldentools.ae Licota 3-jaw (scaled to 10in) + import</t>
   </si>
   <si>
     <t xml:space="preserve">DRILL MACHINE CORDLESS ROTARY HAMMER Bosch</t>
@@ -438,7 +429,7 @@
     <t xml:space="preserve">Bosch GBH 180-LI / GBH 18V-26</t>
   </si>
   <si>
-    <t xml:space="preserve">ktools 49k solo / 115k kit; w11stop 81,400-130,350</t>
+    <t xml:space="preserve">ktools 49,000 solo / 115,000 kit</t>
   </si>
   <si>
     <t xml:space="preserve">Rate cost se 3x - customer pakray ga</t>
@@ -840,7 +831,7 @@
     <t xml:space="preserve">WD-40</t>
   </si>
   <si>
-    <t xml:space="preserve">w11stop 1,100; bloompakistan 1,299-1,420</t>
+    <t xml:space="preserve">naheed.pk 1,380; autohub.pk 1,299; toolsmart (oos)</t>
   </si>
   <si>
     <t xml:space="preserve">PU COATED SAFETY GLOVES LEVEL 5 CUT RESISTA</t>
@@ -1179,7 +1170,7 @@
     <t xml:space="preserve">Bosch GWS 2200-230 H</t>
   </si>
   <si>
-    <t xml:space="preserve">kamadi 43,200; ktools 44,000; w11stop 50,460</t>
+    <t xml:space="preserve">imartpk 36,570; kamadi 43,200; ktools 44,000</t>
   </si>
   <si>
     <t xml:space="preserve">PR check karo: grinder hai ya 9" cutting disc?</t>
@@ -1266,48 +1257,6 @@
     <t xml:space="preserve">https://www.toolsmart.pk/collections/all-tools/grease-gun</t>
   </si>
   <si>
-    <t xml:space="preserve">w11stop.com - Licota catalogue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://w11stop.com/licota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w11stop.com - Licota ATB-1004F 3-jaw puller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://w11stop.com/licota-atb-1004f-gear-puller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w11stop.com - Licota ATB-1003G 2-jaw puller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://w11stop.com/licota-atb-1003g-gear-puller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w11stop.com - Licota ATB-1017D puller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://w11stop.com/licota-atb-1017d-gear-puller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w11stop.com - WD-40 330ml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://w11stop.com/lubricants-and-removal/wd-40-330-ml-lubricant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w11stop.com - Bosch GWS 2200-230 H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://w11stop.com/bosch-gws-2200-230-h-grinder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">w11stop.com - Bosch GBH 180-LI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://w11stop.com/bosch-gbh-180-li-rotary-hammer</t>
-  </si>
-  <si>
     <t xml:space="preserve">kamadi.pk - Bosch GDS 18V-1000</t>
   </si>
   <si>
@@ -1414,6 +1363,42 @@
   </si>
   <si>
     <t xml:space="preserve">https://ingcotool.pk/product/total-swivel-base-bench-vise-with-anvil-6-150mm-tht6166/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">naheed.pk - WD-40 330ml Rs 1,380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.naheed.pk/wd-40-330ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">autohub.pk - WD-40 330ml Rs 1,299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://autohub.pk/products/wd-40-330ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">imartpk.com - Bosch GWS 22-230 H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://imartpk.com/products/gws-22-230-h-professional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">goldentools.ae - Licota 3-jaw puller (UAE ref)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.goldentools.ae/gttecom/singleitemmob/LICOTA/Bearing-and-Seal-Tools/?brcd=4712834507742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">amazon.ae - Licota 6in 3-jaw puller (UAE ref)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.amazon.ae/LICOTA-GEAR-PULLER-ATB-1002C-AT-2102A/dp/B08CTD3842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">goldentools.ae - Licota 12mm hex key (UAE ref)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.goldentools.ae/item/4712818539608</t>
   </si>
   <si>
     <t xml:space="preserve">goldpeaktools.com.ph - Licota AWX-2603GN 7-drawer (ref)</t>
@@ -2046,75 +2031,73 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="A2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" s="4" t="n">
         <v>0.15</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C5" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="I5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="J5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="K5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="L5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="M5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="M5" s="5" t="s">
+      <c r="N5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="N5" s="5" t="s">
+      <c r="O5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="O5" s="5" t="s">
+      <c r="P5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="P5" s="5" t="s">
+      <c r="Q5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="Q5" s="5" t="s">
+      <c r="R5" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="R5" s="5" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2122,10 +2105,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>22</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>23</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>30</v>
@@ -2134,7 +2117,7 @@
         <v>325</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G6" s="9" t="n">
         <v>130</v>
@@ -2171,10 +2154,10 @@
         <v/>
       </c>
       <c r="P6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q6" s="7" t="s">
         <v>25</v>
-      </c>
-      <c r="Q6" s="7" t="s">
-        <v>26</v>
       </c>
       <c r="R6" s="7"/>
     </row>
@@ -2183,10 +2166,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>2</v>
@@ -2195,7 +2178,7 @@
         <v>455</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>300</v>
@@ -2232,13 +2215,13 @@
         <v>YES</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="R7" s="7" t="s">
         <v>30</v>
-      </c>
-      <c r="R7" s="7" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2246,10 +2229,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>2</v>
@@ -2258,7 +2241,7 @@
         <v>58500</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>45000</v>
@@ -2295,13 +2278,13 @@
         <v>YES</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q8" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="R8" s="7" t="s">
         <v>34</v>
-      </c>
-      <c r="R8" s="7" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2309,10 +2292,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>50</v>
@@ -2321,7 +2304,7 @@
         <v>715</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>350</v>
@@ -2358,10 +2341,10 @@
         <v>YES</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R9" s="7"/>
     </row>
@@ -2370,10 +2353,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>2</v>
@@ -2382,7 +2365,7 @@
         <v>41600</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G10" s="9" t="n">
         <v>32000</v>
@@ -2419,10 +2402,10 @@
         <v>YES</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="R10" s="7"/>
     </row>
@@ -2431,10 +2414,10 @@
         <v>6</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>6</v>
@@ -2443,7 +2426,7 @@
         <v>1105</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>600</v>
@@ -2480,10 +2463,10 @@
         <v/>
       </c>
       <c r="P11" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R11" s="7"/>
     </row>
@@ -2492,10 +2475,10 @@
         <v>7</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>24</v>
@@ -2504,7 +2487,7 @@
         <v>507</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G12" s="9" t="n">
         <v>250</v>
@@ -2541,10 +2524,10 @@
         <v/>
       </c>
       <c r="P12" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R12" s="7"/>
     </row>
@@ -2553,10 +2536,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>3</v>
@@ -2565,7 +2548,7 @@
         <v>161070</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>150000</v>
@@ -2602,13 +2585,13 @@
         <v/>
       </c>
       <c r="P13" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q13" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="Q13" s="7" t="s">
+      <c r="R13" s="7" t="s">
         <v>46</v>
-      </c>
-      <c r="R13" s="7" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2616,10 +2599,10 @@
         <v>9</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>4</v>
@@ -2628,7 +2611,7 @@
         <v>18200</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G14" s="9" t="n">
         <v>20000</v>
@@ -2665,10 +2648,10 @@
         <v/>
       </c>
       <c r="P14" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R14" s="7"/>
     </row>
@@ -2677,10 +2660,10 @@
         <v>10</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>4</v>
@@ -2689,7 +2672,7 @@
         <v>15600</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>16000</v>
@@ -2726,22 +2709,22 @@
         <v/>
       </c>
       <c r="P15" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R15" s="7"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="n">
         <v>11</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D16" s="6" t="n">
         <v>3</v>
@@ -2750,7 +2733,7 @@
         <v>3640</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G16" s="9" t="n">
         <v>4500</v>
@@ -2787,22 +2770,22 @@
         <v/>
       </c>
       <c r="P16" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R16" s="7"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="n">
         <v>12</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D17" s="6" t="n">
         <v>3</v>
@@ -2811,7 +2794,7 @@
         <v>4550</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G17" s="9" t="n">
         <v>6000</v>
@@ -2848,10 +2831,10 @@
         <v/>
       </c>
       <c r="P17" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="R17" s="7"/>
     </row>
@@ -2860,10 +2843,10 @@
         <v>13</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D18" s="6" t="n">
         <v>4</v>
@@ -2872,7 +2855,7 @@
         <v>22100</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G18" s="9" t="n">
         <v>24000</v>
@@ -2909,10 +2892,10 @@
         <v/>
       </c>
       <c r="P18" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="R18" s="7"/>
     </row>
@@ -2921,10 +2904,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" s="6" t="n">
         <v>4</v>
@@ -2933,7 +2916,7 @@
         <v>75400</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G19" s="9" t="n">
         <v>56900</v>
@@ -2970,10 +2953,10 @@
         <v/>
       </c>
       <c r="P19" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="R19" s="7"/>
     </row>
@@ -2982,10 +2965,10 @@
         <v>15</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D20" s="6" t="n">
         <v>4</v>
@@ -2994,7 +2977,7 @@
         <v>5850</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G20" s="9" t="n">
         <v>5460</v>
@@ -3031,10 +3014,10 @@
         <v/>
       </c>
       <c r="P20" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="R20" s="7"/>
     </row>
@@ -3043,10 +3026,10 @@
         <v>16</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D21" s="6" t="n">
         <v>4</v>
@@ -3055,7 +3038,7 @@
         <v>8450</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G21" s="9" t="n">
         <v>6500</v>
@@ -3092,13 +3075,13 @@
         <v>YES</v>
       </c>
       <c r="P21" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q21" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="R21" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3106,10 +3089,10 @@
         <v>17</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D22" s="6" t="n">
         <v>4</v>
@@ -3118,10 +3101,10 @@
         <v>2548</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>2320</v>
+        <v>3740</v>
       </c>
       <c r="H22" s="9" t="n">
         <v>4400</v>
@@ -3132,7 +3115,7 @@
       </c>
       <c r="J22" s="6" t="str">
         <f aca="false">IF(E22&lt;G22,"LOSS",IF(E22&lt;H22*1.1,"THIN / RISK",IF(E22&gt;H22*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>LOSS</v>
       </c>
       <c r="K22" s="8" t="n">
         <f aca="false">IF(J22="OVERPRICED?",ROUND(H22*1.35,-1),MAX(E22,ROUND(H22*(1+$E$3),-1)))</f>
@@ -3155,10 +3138,10 @@
         <v/>
       </c>
       <c r="P22" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q22" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="R22" s="7"/>
     </row>
@@ -3167,10 +3150,10 @@
         <v>18</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D23" s="6" t="n">
         <v>4</v>
@@ -3179,7 +3162,7 @@
         <v>1846</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G23" s="9" t="n">
         <v>2000</v>
@@ -3216,10 +3199,10 @@
         <v/>
       </c>
       <c r="P23" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q23" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="R23" s="7"/>
     </row>
@@ -3228,10 +3211,10 @@
         <v>19</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D24" s="6" t="n">
         <v>4</v>
@@ -3240,10 +3223,10 @@
         <v>2548</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>2320</v>
+        <v>3740</v>
       </c>
       <c r="H24" s="9" t="n">
         <v>4400</v>
@@ -3254,7 +3237,7 @@
       </c>
       <c r="J24" s="6" t="str">
         <f aca="false">IF(E24&lt;G24,"LOSS",IF(E24&lt;H24*1.1,"THIN / RISK",IF(E24&gt;H24*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>LOSS</v>
       </c>
       <c r="K24" s="8" t="n">
         <f aca="false">IF(J24="OVERPRICED?",ROUND(H24*1.35,-1),MAX(E24,ROUND(H24*(1+$E$3),-1)))</f>
@@ -3277,24 +3260,24 @@
         <v/>
       </c>
       <c r="P24" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q24" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="R24" s="7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="n">
         <v>20</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D25" s="6" t="n">
         <v>3</v>
@@ -3303,17 +3286,17 @@
         <v>910</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>1100</v>
+        <v>950</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>1500</v>
+        <v>1300</v>
       </c>
       <c r="I25" s="10" t="n">
         <f aca="false">IF(E25=0,0,(E25-H25)/E25)</f>
-        <v>-0.648351648351648</v>
+        <v>-0.428571428571429</v>
       </c>
       <c r="J25" s="6" t="str">
         <f aca="false">IF(E25&lt;G25,"LOSS",IF(E25&lt;H25*1.1,"THIN / RISK",IF(E25&gt;H25*1.8,"OVERPRICED?","OK")))</f>
@@ -3321,7 +3304,7 @@
       </c>
       <c r="K25" s="8" t="n">
         <f aca="false">IF(J25="OVERPRICED?",ROUND(H25*1.35,-1),MAX(E25,ROUND(H25*(1+$E$3),-1)))</f>
-        <v>1730</v>
+        <v>1500</v>
       </c>
       <c r="L25" s="8" t="n">
         <f aca="false">D25*E25</f>
@@ -3329,21 +3312,21 @@
       </c>
       <c r="M25" s="8" t="n">
         <f aca="false">D25*K25</f>
-        <v>5190</v>
+        <v>4500</v>
       </c>
       <c r="N25" s="8" t="n">
         <f aca="false">D25*H25</f>
-        <v>4500</v>
+        <v>3900</v>
       </c>
       <c r="O25" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C25,F25)),"","YES")</f>
         <v/>
       </c>
       <c r="P25" s="6" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="Q25" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="R25" s="7"/>
     </row>
@@ -3352,10 +3335,10 @@
         <v>21</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D26" s="6" t="n">
         <v>3</v>
@@ -3364,17 +3347,17 @@
         <v>1170</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>1900</v>
+        <v>1700</v>
       </c>
       <c r="I26" s="10" t="n">
         <f aca="false">IF(E26=0,0,(E26-H26)/E26)</f>
-        <v>-0.623931623931624</v>
+        <v>-0.452991452991453</v>
       </c>
       <c r="J26" s="6" t="str">
         <f aca="false">IF(E26&lt;G26,"LOSS",IF(E26&lt;H26*1.1,"THIN / RISK",IF(E26&gt;H26*1.8,"OVERPRICED?","OK")))</f>
@@ -3382,7 +3365,7 @@
       </c>
       <c r="K26" s="8" t="n">
         <f aca="false">IF(J26="OVERPRICED?",ROUND(H26*1.35,-1),MAX(E26,ROUND(H26*(1+$E$3),-1)))</f>
-        <v>2190</v>
+        <v>1960</v>
       </c>
       <c r="L26" s="8" t="n">
         <f aca="false">D26*E26</f>
@@ -3390,21 +3373,21 @@
       </c>
       <c r="M26" s="8" t="n">
         <f aca="false">D26*K26</f>
-        <v>6570</v>
+        <v>5880</v>
       </c>
       <c r="N26" s="8" t="n">
         <f aca="false">D26*H26</f>
-        <v>5700</v>
+        <v>5100</v>
       </c>
       <c r="O26" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C26,F26)),"","YES")</f>
         <v/>
       </c>
       <c r="P26" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q26" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="R26" s="7"/>
     </row>
@@ -3413,10 +3396,10 @@
         <v>22</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D27" s="6" t="n">
         <v>3</v>
@@ -3425,17 +3408,17 @@
         <v>1430</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>1800</v>
+        <v>1500</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>2400</v>
+        <v>2100</v>
       </c>
       <c r="I27" s="10" t="n">
         <f aca="false">IF(E27=0,0,(E27-H27)/E27)</f>
-        <v>-0.678321678321678</v>
+        <v>-0.468531468531469</v>
       </c>
       <c r="J27" s="6" t="str">
         <f aca="false">IF(E27&lt;G27,"LOSS",IF(E27&lt;H27*1.1,"THIN / RISK",IF(E27&gt;H27*1.8,"OVERPRICED?","OK")))</f>
@@ -3443,7 +3426,7 @@
       </c>
       <c r="K27" s="8" t="n">
         <f aca="false">IF(J27="OVERPRICED?",ROUND(H27*1.35,-1),MAX(E27,ROUND(H27*(1+$E$3),-1)))</f>
-        <v>2760</v>
+        <v>2420</v>
       </c>
       <c r="L27" s="8" t="n">
         <f aca="false">D27*E27</f>
@@ -3451,21 +3434,21 @@
       </c>
       <c r="M27" s="8" t="n">
         <f aca="false">D27*K27</f>
-        <v>8280</v>
+        <v>7260</v>
       </c>
       <c r="N27" s="8" t="n">
         <f aca="false">D27*H27</f>
-        <v>7200</v>
+        <v>6300</v>
       </c>
       <c r="O27" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C27,F27)),"","YES")</f>
         <v/>
       </c>
       <c r="P27" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q27" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="R27" s="7"/>
     </row>
@@ -3474,10 +3457,10 @@
         <v>23</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D28" s="6" t="n">
         <v>4</v>
@@ -3486,7 +3469,7 @@
         <v>4940</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G28" s="9" t="n">
         <v>4500</v>
@@ -3523,10 +3506,10 @@
         <v/>
       </c>
       <c r="P28" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q28" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="R28" s="7"/>
     </row>
@@ -3535,10 +3518,10 @@
         <v>24</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D29" s="6" t="n">
         <v>4</v>
@@ -3547,7 +3530,7 @@
         <v>4940</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G29" s="9" t="n">
         <v>4500</v>
@@ -3584,10 +3567,10 @@
         <v/>
       </c>
       <c r="P29" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q29" s="7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="R29" s="7"/>
     </row>
@@ -3596,10 +3579,10 @@
         <v>25</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D30" s="6" t="n">
         <v>4</v>
@@ -3608,7 +3591,7 @@
         <v>4940</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G30" s="9" t="n">
         <v>4500</v>
@@ -3645,10 +3628,10 @@
         <v/>
       </c>
       <c r="P30" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q30" s="7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="R30" s="7"/>
     </row>
@@ -3657,10 +3640,10 @@
         <v>26</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D31" s="6" t="n">
         <v>4</v>
@@ -3669,7 +3652,7 @@
         <v>4940</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G31" s="9" t="n">
         <v>4500</v>
@@ -3706,10 +3689,10 @@
         <v/>
       </c>
       <c r="P31" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q31" s="7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="R31" s="7"/>
     </row>
@@ -3718,10 +3701,10 @@
         <v>27</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D32" s="6" t="n">
         <v>4</v>
@@ -3730,7 +3713,7 @@
         <v>6760</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G32" s="9" t="n">
         <v>6000</v>
@@ -3767,10 +3750,10 @@
         <v/>
       </c>
       <c r="P32" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q32" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="R32" s="7"/>
     </row>
@@ -3779,10 +3762,10 @@
         <v>28</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D33" s="6" t="n">
         <v>3</v>
@@ -3791,7 +3774,7 @@
         <v>6760</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G33" s="9" t="n">
         <v>6000</v>
@@ -3828,10 +3811,10 @@
         <v/>
       </c>
       <c r="P33" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q33" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="R33" s="7"/>
     </row>
@@ -3840,10 +3823,10 @@
         <v>30</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D34" s="6" t="n">
         <v>4</v>
@@ -3852,7 +3835,7 @@
         <v>6136</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G34" s="9" t="n">
         <v>4000</v>
@@ -3889,10 +3872,10 @@
         <v/>
       </c>
       <c r="P34" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q34" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="R34" s="7"/>
     </row>
@@ -3901,10 +3884,10 @@
         <v>31</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D35" s="6" t="n">
         <v>3</v>
@@ -3913,7 +3896,7 @@
         <v>2210</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G35" s="9" t="n">
         <v>4200</v>
@@ -3950,10 +3933,10 @@
         <v/>
       </c>
       <c r="P35" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q35" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="R35" s="7"/>
     </row>
@@ -3962,10 +3945,10 @@
         <v>32</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D36" s="6" t="n">
         <v>3</v>
@@ -3974,7 +3957,7 @@
         <v>2886</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G36" s="9" t="n">
         <v>5200</v>
@@ -4011,10 +3994,10 @@
         <v/>
       </c>
       <c r="P36" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q36" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="R36" s="7"/>
     </row>
@@ -4023,10 +4006,10 @@
         <v>33</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D37" s="6" t="n">
         <v>3</v>
@@ -4035,7 +4018,7 @@
         <v>5902</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G37" s="9" t="n">
         <v>9620</v>
@@ -4072,10 +4055,10 @@
         <v/>
       </c>
       <c r="P37" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q37" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="R37" s="7"/>
     </row>
@@ -4084,10 +4067,10 @@
         <v>34</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D38" s="6" t="n">
         <v>2</v>
@@ -4096,7 +4079,7 @@
         <v>6120</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G38" s="9" t="n">
         <v>13000</v>
@@ -4133,10 +4116,10 @@
         <v/>
       </c>
       <c r="P38" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q38" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="R38" s="7"/>
     </row>
@@ -4145,10 +4128,10 @@
         <v>35</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D39" s="6" t="n">
         <v>2</v>
@@ -4157,7 +4140,7 @@
         <v>12870</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G39" s="9" t="n">
         <v>22000</v>
@@ -4194,10 +4177,10 @@
         <v/>
       </c>
       <c r="P39" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q39" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="R39" s="7"/>
     </row>
@@ -4206,10 +4189,10 @@
         <v>36</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D40" s="6" t="n">
         <v>3</v>
@@ -4218,7 +4201,7 @@
         <v>1950</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G40" s="9" t="n">
         <v>2500</v>
@@ -4255,10 +4238,10 @@
         <v/>
       </c>
       <c r="P40" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q40" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="R40" s="7"/>
     </row>
@@ -4267,10 +4250,10 @@
         <v>37</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D41" s="6" t="n">
         <v>3</v>
@@ -4279,7 +4262,7 @@
         <v>4550</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G41" s="9" t="n">
         <v>4500</v>
@@ -4316,10 +4299,10 @@
         <v/>
       </c>
       <c r="P41" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q41" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R41" s="7"/>
     </row>
@@ -4328,10 +4311,10 @@
         <v>38</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D42" s="6" t="n">
         <v>3</v>
@@ -4340,7 +4323,7 @@
         <v>6240</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G42" s="9" t="n">
         <v>5000</v>
@@ -4377,10 +4360,10 @@
         <v/>
       </c>
       <c r="P42" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q42" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="R42" s="7"/>
     </row>
@@ -4389,10 +4372,10 @@
         <v>39</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D43" s="6" t="n">
         <v>3</v>
@@ -4401,7 +4384,7 @@
         <v>1950</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G43" s="9" t="n">
         <v>3500</v>
@@ -4438,10 +4421,10 @@
         <v/>
       </c>
       <c r="P43" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q43" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="R43" s="7"/>
     </row>
@@ -4450,10 +4433,10 @@
         <v>40</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D44" s="6" t="n">
         <v>3</v>
@@ -4462,7 +4445,7 @@
         <v>79300</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G44" s="9" t="n">
         <v>45000</v>
@@ -4499,13 +4482,13 @@
         <v>YES</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q44" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="R44" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4513,10 +4496,10 @@
         <v>41</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>3</v>
@@ -4525,7 +4508,7 @@
         <v>128700</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G45" s="9" t="n">
         <v>95000</v>
@@ -4562,10 +4545,10 @@
         <v>YES</v>
       </c>
       <c r="P45" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q45" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="R45" s="7"/>
     </row>
@@ -4574,10 +4557,10 @@
         <v>42</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D46" s="6" t="n">
         <v>2</v>
@@ -4586,7 +4569,7 @@
         <v>106600</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G46" s="9" t="n">
         <v>70000</v>
@@ -4623,13 +4606,13 @@
         <v>YES</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q46" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="R46" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4637,10 +4620,10 @@
         <v>43</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D47" s="6" t="n">
         <v>4</v>
@@ -4649,7 +4632,7 @@
         <v>1560</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G47" s="9" t="n">
         <v>1800</v>
@@ -4686,10 +4669,10 @@
         <v/>
       </c>
       <c r="P47" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q47" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="R47" s="7"/>
     </row>
@@ -4698,10 +4681,10 @@
         <v>44</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D48" s="6" t="n">
         <v>4</v>
@@ -4710,7 +4693,7 @@
         <v>1950</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G48" s="9" t="n">
         <v>1700</v>
@@ -4747,10 +4730,10 @@
         <v>YES</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q48" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="R48" s="7"/>
     </row>
@@ -4759,10 +4742,10 @@
         <v>45</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D49" s="6" t="n">
         <v>4</v>
@@ -4771,7 +4754,7 @@
         <v>2210</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G49" s="9" t="n">
         <v>1700</v>
@@ -4808,10 +4791,10 @@
         <v>YES</v>
       </c>
       <c r="P49" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q49" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R49" s="7"/>
     </row>
@@ -4820,10 +4803,10 @@
         <v>47</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D50" s="6" t="n">
         <v>3</v>
@@ -4832,25 +4815,25 @@
         <v>13000</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>18000</v>
+        <v>12000</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>22000</v>
+        <v>16000</v>
       </c>
       <c r="I50" s="10" t="n">
         <f aca="false">IF(E50=0,0,(E50-H50)/E50)</f>
-        <v>-0.692307692307692</v>
+        <v>-0.230769230769231</v>
       </c>
       <c r="J50" s="6" t="str">
         <f aca="false">IF(E50&lt;G50,"LOSS",IF(E50&lt;H50*1.1,"THIN / RISK",IF(E50&gt;H50*1.8,"OVERPRICED?","OK")))</f>
-        <v>LOSS</v>
+        <v>THIN / RISK</v>
       </c>
       <c r="K50" s="8" t="n">
         <f aca="false">IF(J50="OVERPRICED?",ROUND(H50*1.35,-1),MAX(E50,ROUND(H50*(1+$E$3),-1)))</f>
-        <v>25300</v>
+        <v>18400</v>
       </c>
       <c r="L50" s="8" t="n">
         <f aca="false">D50*E50</f>
@@ -4858,21 +4841,21 @@
       </c>
       <c r="M50" s="8" t="n">
         <f aca="false">D50*K50</f>
-        <v>75900</v>
+        <v>55200</v>
       </c>
       <c r="N50" s="8" t="n">
         <f aca="false">D50*H50</f>
-        <v>66000</v>
+        <v>48000</v>
       </c>
       <c r="O50" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C50,F50)),"","YES")</f>
         <v/>
       </c>
       <c r="P50" s="6" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="Q50" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="R50" s="7"/>
     </row>
@@ -4881,10 +4864,10 @@
         <v>48</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D51" s="6" t="n">
         <v>2</v>
@@ -4893,17 +4876,17 @@
         <v>15600</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>22000</v>
+        <v>16000</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>32700</v>
+        <v>24000</v>
       </c>
       <c r="I51" s="10" t="n">
         <f aca="false">IF(E51=0,0,(E51-H51)/E51)</f>
-        <v>-1.09615384615385</v>
+        <v>-0.538461538461538</v>
       </c>
       <c r="J51" s="6" t="str">
         <f aca="false">IF(E51&lt;G51,"LOSS",IF(E51&lt;H51*1.1,"THIN / RISK",IF(E51&gt;H51*1.8,"OVERPRICED?","OK")))</f>
@@ -4911,7 +4894,7 @@
       </c>
       <c r="K51" s="8" t="n">
         <f aca="false">IF(J51="OVERPRICED?",ROUND(H51*1.35,-1),MAX(E51,ROUND(H51*(1+$E$3),-1)))</f>
-        <v>37610</v>
+        <v>27600</v>
       </c>
       <c r="L51" s="8" t="n">
         <f aca="false">D51*E51</f>
@@ -4919,21 +4902,21 @@
       </c>
       <c r="M51" s="8" t="n">
         <f aca="false">D51*K51</f>
-        <v>75220</v>
+        <v>55200</v>
       </c>
       <c r="N51" s="8" t="n">
         <f aca="false">D51*H51</f>
-        <v>65400</v>
+        <v>48000</v>
       </c>
       <c r="O51" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C51,F51)),"","YES")</f>
         <v/>
       </c>
       <c r="P51" s="6" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="Q51" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R51" s="7"/>
     </row>
@@ -4942,10 +4925,10 @@
         <v>49</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D52" s="6" t="n">
         <v>1</v>
@@ -4954,25 +4937,25 @@
         <v>20800</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>33000</v>
+        <v>28000</v>
       </c>
       <c r="I52" s="10" t="n">
         <f aca="false">IF(E52=0,0,(E52-H52)/E52)</f>
-        <v>-0.586538461538462</v>
+        <v>-0.346153846153846</v>
       </c>
       <c r="J52" s="6" t="str">
         <f aca="false">IF(E52&lt;G52,"LOSS",IF(E52&lt;H52*1.1,"THIN / RISK",IF(E52&gt;H52*1.8,"OVERPRICED?","OK")))</f>
-        <v>LOSS</v>
+        <v>THIN / RISK</v>
       </c>
       <c r="K52" s="8" t="n">
         <f aca="false">IF(J52="OVERPRICED?",ROUND(H52*1.35,-1),MAX(E52,ROUND(H52*(1+$E$3),-1)))</f>
-        <v>37950</v>
+        <v>32200</v>
       </c>
       <c r="L52" s="8" t="n">
         <f aca="false">D52*E52</f>
@@ -4980,21 +4963,21 @@
       </c>
       <c r="M52" s="8" t="n">
         <f aca="false">D52*K52</f>
-        <v>37950</v>
+        <v>32200</v>
       </c>
       <c r="N52" s="8" t="n">
         <f aca="false">D52*H52</f>
-        <v>33000</v>
+        <v>28000</v>
       </c>
       <c r="O52" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C52,F52)),"","YES")</f>
         <v/>
       </c>
       <c r="P52" s="6" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="Q52" s="7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="R52" s="7"/>
     </row>
@@ -5003,10 +4986,10 @@
         <v>50</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D53" s="6" t="n">
         <v>1</v>
@@ -5015,25 +4998,25 @@
         <v>28600</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>32000</v>
+        <v>28000</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>42000</v>
+        <v>38000</v>
       </c>
       <c r="I53" s="10" t="n">
         <f aca="false">IF(E53=0,0,(E53-H53)/E53)</f>
-        <v>-0.468531468531469</v>
+        <v>-0.328671328671329</v>
       </c>
       <c r="J53" s="6" t="str">
         <f aca="false">IF(E53&lt;G53,"LOSS",IF(E53&lt;H53*1.1,"THIN / RISK",IF(E53&gt;H53*1.8,"OVERPRICED?","OK")))</f>
-        <v>LOSS</v>
+        <v>THIN / RISK</v>
       </c>
       <c r="K53" s="8" t="n">
         <f aca="false">IF(J53="OVERPRICED?",ROUND(H53*1.35,-1),MAX(E53,ROUND(H53*(1+$E$3),-1)))</f>
-        <v>48300</v>
+        <v>43700</v>
       </c>
       <c r="L53" s="8" t="n">
         <f aca="false">D53*E53</f>
@@ -5041,21 +5024,21 @@
       </c>
       <c r="M53" s="8" t="n">
         <f aca="false">D53*K53</f>
-        <v>48300</v>
+        <v>43700</v>
       </c>
       <c r="N53" s="8" t="n">
         <f aca="false">D53*H53</f>
-        <v>42000</v>
+        <v>38000</v>
       </c>
       <c r="O53" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C53,F53)),"","YES")</f>
         <v/>
       </c>
       <c r="P53" s="6" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="Q53" s="7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="R53" s="7"/>
     </row>
@@ -5064,10 +5047,10 @@
         <v>51</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D54" s="6" t="n">
         <v>1</v>
@@ -5076,7 +5059,7 @@
         <v>32500</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G54" s="9" t="n">
         <v>30000</v>
@@ -5113,22 +5096,22 @@
         <v/>
       </c>
       <c r="P54" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q54" s="7" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="R54" s="7"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6" t="n">
         <v>52</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D55" s="6" t="n">
         <v>2</v>
@@ -5137,25 +5120,25 @@
         <v>18200</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>22500</v>
+        <v>18000</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>30000</v>
+        <v>25000</v>
       </c>
       <c r="I55" s="10" t="n">
         <f aca="false">IF(E55=0,0,(E55-H55)/E55)</f>
-        <v>-0.648351648351648</v>
+        <v>-0.373626373626374</v>
       </c>
       <c r="J55" s="6" t="str">
         <f aca="false">IF(E55&lt;G55,"LOSS",IF(E55&lt;H55*1.1,"THIN / RISK",IF(E55&gt;H55*1.8,"OVERPRICED?","OK")))</f>
-        <v>LOSS</v>
+        <v>THIN / RISK</v>
       </c>
       <c r="K55" s="8" t="n">
         <f aca="false">IF(J55="OVERPRICED?",ROUND(H55*1.35,-1),MAX(E55,ROUND(H55*(1+$E$3),-1)))</f>
-        <v>34500</v>
+        <v>28750</v>
       </c>
       <c r="L55" s="8" t="n">
         <f aca="false">D55*E55</f>
@@ -5163,21 +5146,21 @@
       </c>
       <c r="M55" s="8" t="n">
         <f aca="false">D55*K55</f>
-        <v>69000</v>
+        <v>57500</v>
       </c>
       <c r="N55" s="8" t="n">
         <f aca="false">D55*H55</f>
-        <v>60000</v>
+        <v>50000</v>
       </c>
       <c r="O55" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C55,F55)),"","YES")</f>
         <v/>
       </c>
       <c r="P55" s="6" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="Q55" s="7" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="R55" s="7"/>
     </row>
@@ -5186,10 +5169,10 @@
         <v>53</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D56" s="6" t="n">
         <v>1</v>
@@ -5198,17 +5181,17 @@
         <v>23400</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>30000</v>
+        <v>24000</v>
       </c>
       <c r="H56" s="9" t="n">
-        <v>38100</v>
+        <v>32000</v>
       </c>
       <c r="I56" s="10" t="n">
         <f aca="false">IF(E56=0,0,(E56-H56)/E56)</f>
-        <v>-0.628205128205128</v>
+        <v>-0.367521367521368</v>
       </c>
       <c r="J56" s="6" t="str">
         <f aca="false">IF(E56&lt;G56,"LOSS",IF(E56&lt;H56*1.1,"THIN / RISK",IF(E56&gt;H56*1.8,"OVERPRICED?","OK")))</f>
@@ -5216,7 +5199,7 @@
       </c>
       <c r="K56" s="8" t="n">
         <f aca="false">IF(J56="OVERPRICED?",ROUND(H56*1.35,-1),MAX(E56,ROUND(H56*(1+$E$3),-1)))</f>
-        <v>43820</v>
+        <v>36800</v>
       </c>
       <c r="L56" s="8" t="n">
         <f aca="false">D56*E56</f>
@@ -5224,21 +5207,21 @@
       </c>
       <c r="M56" s="8" t="n">
         <f aca="false">D56*K56</f>
-        <v>43820</v>
+        <v>36800</v>
       </c>
       <c r="N56" s="8" t="n">
         <f aca="false">D56*H56</f>
-        <v>38100</v>
+        <v>32000</v>
       </c>
       <c r="O56" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C56,F56)),"","YES")</f>
         <v/>
       </c>
       <c r="P56" s="6" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="Q56" s="7" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="R56" s="7"/>
     </row>
@@ -5247,10 +5230,10 @@
         <v>54</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D57" s="6" t="n">
         <v>2</v>
@@ -5259,17 +5242,17 @@
         <v>400946</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G57" s="9" t="n">
         <v>49000</v>
       </c>
       <c r="H57" s="9" t="n">
-        <v>130000</v>
+        <v>115000</v>
       </c>
       <c r="I57" s="10" t="n">
         <f aca="false">IF(E57=0,0,(E57-H57)/E57)</f>
-        <v>0.675766811490824</v>
+        <v>0.713178333241883</v>
       </c>
       <c r="J57" s="6" t="str">
         <f aca="false">IF(E57&lt;G57,"LOSS",IF(E57&lt;H57*1.1,"THIN / RISK",IF(E57&gt;H57*1.8,"OVERPRICED?","OK")))</f>
@@ -5277,7 +5260,7 @@
       </c>
       <c r="K57" s="8" t="n">
         <f aca="false">IF(J57="OVERPRICED?",ROUND(H57*1.35,-1),MAX(E57,ROUND(H57*(1+$E$3),-1)))</f>
-        <v>175500</v>
+        <v>155250</v>
       </c>
       <c r="L57" s="8" t="n">
         <f aca="false">D57*E57</f>
@@ -5285,24 +5268,24 @@
       </c>
       <c r="M57" s="8" t="n">
         <f aca="false">D57*K57</f>
-        <v>351000</v>
+        <v>310500</v>
       </c>
       <c r="N57" s="8" t="n">
         <f aca="false">D57*H57</f>
-        <v>260000</v>
+        <v>230000</v>
       </c>
       <c r="O57" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C57,F57)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P57" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q57" s="7" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="R57" s="7" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5310,10 +5293,10 @@
         <v>55</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D58" s="6" t="n">
         <v>2</v>
@@ -5322,7 +5305,7 @@
         <v>15600</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="G58" s="9" t="n">
         <v>12000</v>
@@ -5359,13 +5342,13 @@
         <v>YES</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q58" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R58" s="7" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5373,10 +5356,10 @@
         <v>56</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D59" s="6" t="n">
         <v>1</v>
@@ -5385,7 +5368,7 @@
         <v>10400</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G59" s="9" t="n">
         <v>9000</v>
@@ -5422,10 +5405,10 @@
         <v/>
       </c>
       <c r="P59" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q59" s="7" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="R59" s="7"/>
     </row>
@@ -5434,10 +5417,10 @@
         <v>57</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D60" s="6" t="n">
         <v>4</v>
@@ -5446,7 +5429,7 @@
         <v>4550</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G60" s="9" t="n">
         <v>7760</v>
@@ -5483,10 +5466,10 @@
         <v/>
       </c>
       <c r="P60" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q60" s="7" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="R60" s="7"/>
     </row>
@@ -5495,10 +5478,10 @@
         <v>58</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D61" s="6" t="n">
         <v>12</v>
@@ -5507,7 +5490,7 @@
         <v>715</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G61" s="9" t="n">
         <v>800</v>
@@ -5544,10 +5527,10 @@
         <v/>
       </c>
       <c r="P61" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q61" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R61" s="7"/>
     </row>
@@ -5556,10 +5539,10 @@
         <v>59</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D62" s="6" t="n">
         <v>12</v>
@@ -5568,7 +5551,7 @@
         <v>1950</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G62" s="9" t="n">
         <v>1200</v>
@@ -5605,10 +5588,10 @@
         <v/>
       </c>
       <c r="P62" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q62" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R62" s="7"/>
     </row>
@@ -5617,10 +5600,10 @@
         <v>60</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D63" s="6" t="n">
         <v>2</v>
@@ -5629,7 +5612,7 @@
         <v>9100</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G63" s="9" t="n">
         <v>8000</v>
@@ -5666,10 +5649,10 @@
         <v>YES</v>
       </c>
       <c r="P63" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q63" s="7" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="R63" s="7"/>
     </row>
@@ -5678,10 +5661,10 @@
         <v>61</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D64" s="6" t="n">
         <v>2</v>
@@ -5690,7 +5673,7 @@
         <v>5850</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G64" s="9" t="n">
         <v>5000</v>
@@ -5727,10 +5710,10 @@
         <v>YES</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q64" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R64" s="7"/>
     </row>
@@ -5739,10 +5722,10 @@
         <v>62</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D65" s="6" t="n">
         <v>3</v>
@@ -5751,7 +5734,7 @@
         <v>2600</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G65" s="9" t="n">
         <v>3000</v>
@@ -5788,10 +5771,10 @@
         <v/>
       </c>
       <c r="P65" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q65" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R65" s="7"/>
     </row>
@@ -5800,10 +5783,10 @@
         <v>63</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D66" s="6" t="n">
         <v>1</v>
@@ -5812,7 +5795,7 @@
         <v>5551</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G66" s="9" t="n">
         <v>9000</v>
@@ -5849,10 +5832,10 @@
         <v/>
       </c>
       <c r="P66" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q66" s="7" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="R66" s="7"/>
     </row>
@@ -5861,10 +5844,10 @@
         <v>64</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D67" s="6" t="n">
         <v>3</v>
@@ -5873,7 +5856,7 @@
         <v>1560</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G67" s="9" t="n">
         <v>1300</v>
@@ -5910,10 +5893,10 @@
         <v>YES</v>
       </c>
       <c r="P67" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q67" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R67" s="7"/>
     </row>
@@ -5922,10 +5905,10 @@
         <v>65</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D68" s="6" t="n">
         <v>3</v>
@@ -5934,7 +5917,7 @@
         <v>1560</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G68" s="9" t="n">
         <v>1300</v>
@@ -5971,10 +5954,10 @@
         <v>YES</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q68" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R68" s="7"/>
     </row>
@@ -5983,10 +5966,10 @@
         <v>66</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D69" s="6" t="n">
         <v>2</v>
@@ -5995,7 +5978,7 @@
         <v>11700</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G69" s="9" t="n">
         <v>14000</v>
@@ -6032,13 +6015,13 @@
         <v>YES</v>
       </c>
       <c r="P69" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q69" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R69" s="7" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6046,10 +6029,10 @@
         <v>67</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D70" s="6" t="n">
         <v>2</v>
@@ -6058,7 +6041,7 @@
         <v>9750</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G70" s="9" t="n">
         <v>12000</v>
@@ -6095,10 +6078,10 @@
         <v>YES</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q70" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R70" s="7"/>
     </row>
@@ -6107,10 +6090,10 @@
         <v>69</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D71" s="6" t="n">
         <v>2</v>
@@ -6119,7 +6102,7 @@
         <v>23400</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G71" s="9" t="n">
         <v>15000</v>
@@ -6156,10 +6139,10 @@
         <v>YES</v>
       </c>
       <c r="P71" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q71" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R71" s="7"/>
     </row>
@@ -6168,10 +6151,10 @@
         <v>70</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D72" s="6" t="n">
         <v>1</v>
@@ -6180,7 +6163,7 @@
         <v>32500</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G72" s="9" t="n">
         <v>25000</v>
@@ -6217,10 +6200,10 @@
         <v>YES</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q72" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R72" s="7"/>
     </row>
@@ -6229,10 +6212,10 @@
         <v>71</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D73" s="6" t="n">
         <v>1</v>
@@ -6241,7 +6224,7 @@
         <v>1105</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G73" s="9" t="n">
         <v>800</v>
@@ -6278,10 +6261,10 @@
         <v>YES</v>
       </c>
       <c r="P73" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q73" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R73" s="7"/>
     </row>
@@ -6290,10 +6273,10 @@
         <v>73</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D74" s="6" t="n">
         <v>1</v>
@@ -6302,7 +6285,7 @@
         <v>45500</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G74" s="9" t="n">
         <v>25000</v>
@@ -6339,10 +6322,10 @@
         <v>YES</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q74" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R74" s="7"/>
     </row>
@@ -6351,10 +6334,10 @@
         <v>74</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D75" s="6" t="n">
         <v>2</v>
@@ -6363,7 +6346,7 @@
         <v>23400</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G75" s="9" t="n">
         <v>12000</v>
@@ -6400,10 +6383,10 @@
         <v>YES</v>
       </c>
       <c r="P75" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q75" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R75" s="7"/>
     </row>
@@ -6412,10 +6395,10 @@
         <v>75</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D76" s="6" t="n">
         <v>2</v>
@@ -6424,7 +6407,7 @@
         <v>1950</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G76" s="9" t="n">
         <v>2500</v>
@@ -6461,13 +6444,13 @@
         <v>YES</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q76" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="R76" s="7" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6475,10 +6458,10 @@
         <v>76</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D77" s="6" t="n">
         <v>2</v>
@@ -6487,7 +6470,7 @@
         <v>2080</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G77" s="9" t="n">
         <v>2700</v>
@@ -6524,10 +6507,10 @@
         <v>YES</v>
       </c>
       <c r="P77" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q77" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R77" s="7"/>
     </row>
@@ -6536,10 +6519,10 @@
         <v>77</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D78" s="6" t="n">
         <v>2</v>
@@ -6548,7 +6531,7 @@
         <v>2210</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G78" s="9" t="n">
         <v>2800</v>
@@ -6585,10 +6568,10 @@
         <v>YES</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q78" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R78" s="7"/>
     </row>
@@ -6597,10 +6580,10 @@
         <v>78</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D79" s="6" t="n">
         <v>2</v>
@@ -6609,7 +6592,7 @@
         <v>2340</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G79" s="9" t="n">
         <v>3000</v>
@@ -6646,10 +6629,10 @@
         <v>YES</v>
       </c>
       <c r="P79" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q79" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R79" s="7"/>
     </row>
@@ -6658,10 +6641,10 @@
         <v>79</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D80" s="6" t="n">
         <v>2</v>
@@ -6670,7 +6653,7 @@
         <v>2470</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G80" s="9" t="n">
         <v>3100</v>
@@ -6707,10 +6690,10 @@
         <v>YES</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q80" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R80" s="7"/>
     </row>
@@ -6719,10 +6702,10 @@
         <v>80</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D81" s="6" t="n">
         <v>2</v>
@@ -6731,7 +6714,7 @@
         <v>2600</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G81" s="9" t="n">
         <v>3300</v>
@@ -6768,10 +6751,10 @@
         <v>YES</v>
       </c>
       <c r="P81" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q81" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R81" s="7"/>
     </row>
@@ -6780,10 +6763,10 @@
         <v>81</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D82" s="6" t="n">
         <v>2</v>
@@ -6792,7 +6775,7 @@
         <v>2730</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G82" s="9" t="n">
         <v>3500</v>
@@ -6829,10 +6812,10 @@
         <v>YES</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q82" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R82" s="7"/>
     </row>
@@ -6841,10 +6824,10 @@
         <v>82</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D83" s="6" t="n">
         <v>2</v>
@@ -6853,7 +6836,7 @@
         <v>3250</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G83" s="9" t="n">
         <v>4000</v>
@@ -6890,10 +6873,10 @@
         <v>YES</v>
       </c>
       <c r="P83" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q83" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R83" s="7"/>
     </row>
@@ -6902,10 +6885,10 @@
         <v>83</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D84" s="6" t="n">
         <v>1</v>
@@ -6914,7 +6897,7 @@
         <v>4160</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G84" s="9" t="n">
         <v>5000</v>
@@ -6951,10 +6934,10 @@
         <v>YES</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q84" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R84" s="7"/>
     </row>
@@ -6963,10 +6946,10 @@
         <v>84</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D85" s="6" t="n">
         <v>1</v>
@@ -6975,7 +6958,7 @@
         <v>5850</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G85" s="9" t="n">
         <v>6500</v>
@@ -7012,10 +6995,10 @@
         <v>YES</v>
       </c>
       <c r="P85" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q85" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R85" s="7"/>
     </row>
@@ -7024,10 +7007,10 @@
         <v>85</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D86" s="6" t="n">
         <v>1</v>
@@ -7036,7 +7019,7 @@
         <v>8450</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G86" s="9" t="n">
         <v>9500</v>
@@ -7073,10 +7056,10 @@
         <v>YES</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q86" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R86" s="7"/>
     </row>
@@ -7085,10 +7068,10 @@
         <v>86</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D87" s="6" t="n">
         <v>1</v>
@@ -7097,7 +7080,7 @@
         <v>9750</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G87" s="9" t="n">
         <v>11000</v>
@@ -7134,10 +7117,10 @@
         <v>YES</v>
       </c>
       <c r="P87" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q87" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R87" s="7"/>
     </row>
@@ -7146,10 +7129,10 @@
         <v>87</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D88" s="6" t="n">
         <v>1</v>
@@ -7158,7 +7141,7 @@
         <v>11700</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G88" s="9" t="n">
         <v>13500</v>
@@ -7195,10 +7178,10 @@
         <v>YES</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q88" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R88" s="7"/>
     </row>
@@ -7207,10 +7190,10 @@
         <v>88</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D89" s="6" t="n">
         <v>2</v>
@@ -7219,7 +7202,7 @@
         <v>4550</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G89" s="9" t="n">
         <v>3500</v>
@@ -7256,10 +7239,10 @@
         <v>YES</v>
       </c>
       <c r="P89" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q89" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R89" s="7"/>
     </row>
@@ -7268,10 +7251,10 @@
         <v>89</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D90" s="6" t="n">
         <v>2</v>
@@ -7280,7 +7263,7 @@
         <v>5850</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G90" s="9" t="n">
         <v>4500</v>
@@ -7317,10 +7300,10 @@
         <v>YES</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q90" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R90" s="7"/>
     </row>
@@ -7329,10 +7312,10 @@
         <v>90</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D91" s="6" t="n">
         <v>2</v>
@@ -7341,7 +7324,7 @@
         <v>7150</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G91" s="9" t="n">
         <v>5500</v>
@@ -7378,10 +7361,10 @@
         <v>YES</v>
       </c>
       <c r="P91" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q91" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R91" s="7"/>
     </row>
@@ -7390,10 +7373,10 @@
         <v>91</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D92" s="6" t="n">
         <v>2</v>
@@ -7402,7 +7385,7 @@
         <v>2340</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G92" s="9" t="n">
         <v>2500</v>
@@ -7439,10 +7422,10 @@
         <v>YES</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q92" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R92" s="7"/>
     </row>
@@ -7451,10 +7434,10 @@
         <v>92</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D93" s="6" t="n">
         <v>2</v>
@@ -7463,7 +7446,7 @@
         <v>2860</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G93" s="9" t="n">
         <v>3000</v>
@@ -7500,10 +7483,10 @@
         <v>YES</v>
       </c>
       <c r="P93" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q93" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R93" s="7"/>
     </row>
@@ -7512,10 +7495,10 @@
         <v>93</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D94" s="6" t="n">
         <v>2</v>
@@ -7524,7 +7507,7 @@
         <v>25350</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="G94" s="9" t="n">
         <v>15800</v>
@@ -7561,10 +7544,10 @@
         <v/>
       </c>
       <c r="P94" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q94" s="7" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="R94" s="7"/>
     </row>
@@ -7573,10 +7556,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D95" s="6" t="n">
         <v>3</v>
@@ -7585,7 +7568,7 @@
         <v>8138</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G95" s="9" t="n">
         <v>15800</v>
@@ -7622,13 +7605,13 @@
         <v/>
       </c>
       <c r="P95" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q95" s="7" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="R95" s="7" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7636,10 +7619,10 @@
         <v>95</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D96" s="6" t="n">
         <v>3</v>
@@ -7648,7 +7631,7 @@
         <v>6370</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="G96" s="9" t="n">
         <v>7928</v>
@@ -7685,10 +7668,10 @@
         <v/>
       </c>
       <c r="P96" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q96" s="7" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="R96" s="7"/>
     </row>
@@ -7697,10 +7680,10 @@
         <v>96</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D97" s="6" t="n">
         <v>2</v>
@@ -7709,7 +7692,7 @@
         <v>14950</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G97" s="9" t="n">
         <v>15000</v>
@@ -7746,13 +7729,13 @@
         <v>YES</v>
       </c>
       <c r="P97" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q97" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R97" s="7" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7760,10 +7743,10 @@
         <v>97</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D98" s="6" t="n">
         <v>2</v>
@@ -7772,7 +7755,7 @@
         <v>286000</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="G98" s="9" t="n">
         <v>110000</v>
@@ -7809,13 +7792,13 @@
         <v>YES</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q98" s="7" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="R98" s="7" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7823,10 +7806,10 @@
         <v>98</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D99" s="6" t="n">
         <v>1</v>
@@ -7835,7 +7818,7 @@
         <v>15600</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G99" s="9" t="n">
         <v>12000</v>
@@ -7872,10 +7855,10 @@
         <v/>
       </c>
       <c r="P99" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q99" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R99" s="7"/>
     </row>
@@ -7884,10 +7867,10 @@
         <v>99</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D100" s="6" t="n">
         <v>1</v>
@@ -7896,7 +7879,7 @@
         <v>11050</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G100" s="9" t="n">
         <v>8000</v>
@@ -7933,13 +7916,13 @@
         <v>YES</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q100" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R100" s="7" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7947,10 +7930,10 @@
         <v>100</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D101" s="6" t="n">
         <v>1</v>
@@ -7959,7 +7942,7 @@
         <v>9100</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G101" s="9" t="n">
         <v>6500</v>
@@ -7996,10 +7979,10 @@
         <v>YES</v>
       </c>
       <c r="P101" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q101" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R101" s="7"/>
     </row>
@@ -8008,10 +7991,10 @@
         <v>101</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D102" s="6" t="n">
         <v>3</v>
@@ -8020,7 +8003,7 @@
         <v>7150</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G102" s="9" t="n">
         <v>5500</v>
@@ -8057,10 +8040,10 @@
         <v>YES</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q102" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R102" s="7"/>
     </row>
@@ -8069,10 +8052,10 @@
         <v>102</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D103" s="6" t="n">
         <v>3</v>
@@ -8081,7 +8064,7 @@
         <v>5850</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G103" s="9" t="n">
         <v>4500</v>
@@ -8118,10 +8101,10 @@
         <v>YES</v>
       </c>
       <c r="P103" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q103" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R103" s="7"/>
     </row>
@@ -8130,10 +8113,10 @@
         <v>103</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D104" s="6" t="n">
         <v>12</v>
@@ -8142,7 +8125,7 @@
         <v>715</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G104" s="9" t="n">
         <v>350</v>
@@ -8179,10 +8162,10 @@
         <v/>
       </c>
       <c r="P104" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q104" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R104" s="7"/>
     </row>
@@ -8191,10 +8174,10 @@
         <v>104</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D105" s="6" t="n">
         <v>4</v>
@@ -8203,7 +8186,7 @@
         <v>1274</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G105" s="9" t="n">
         <v>700</v>
@@ -8240,10 +8223,10 @@
         <v/>
       </c>
       <c r="P105" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q105" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R105" s="7"/>
     </row>
@@ -8252,10 +8235,10 @@
         <v>105</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D106" s="6" t="n">
         <v>12</v>
@@ -8264,7 +8247,7 @@
         <v>1170</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G106" s="9" t="n">
         <v>600</v>
@@ -8301,10 +8284,10 @@
         <v/>
       </c>
       <c r="P106" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q106" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R106" s="7"/>
     </row>
@@ -8313,10 +8296,10 @@
         <v>106</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D107" s="6" t="n">
         <v>6</v>
@@ -8325,7 +8308,7 @@
         <v>3640</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G107" s="9" t="n">
         <v>2000</v>
@@ -8362,10 +8345,10 @@
         <v>YES</v>
       </c>
       <c r="P107" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q107" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R107" s="7"/>
     </row>
@@ -8374,10 +8357,10 @@
         <v>107</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D108" s="6" t="n">
         <v>6</v>
@@ -8386,7 +8369,7 @@
         <v>6760</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G108" s="9" t="n">
         <v>4500</v>
@@ -8423,10 +8406,10 @@
         <v>YES</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q108" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R108" s="7"/>
     </row>
@@ -8435,10 +8418,10 @@
         <v>108</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D109" s="6" t="n">
         <v>3</v>
@@ -8447,7 +8430,7 @@
         <v>4550</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G109" s="9" t="n">
         <v>3500</v>
@@ -8484,10 +8467,10 @@
         <v>YES</v>
       </c>
       <c r="P109" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q109" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R109" s="7"/>
     </row>
@@ -8496,10 +8479,10 @@
         <v>109</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D110" s="6" t="n">
         <v>6</v>
@@ -8508,7 +8491,7 @@
         <v>2340</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G110" s="9" t="n">
         <v>1800</v>
@@ -8545,10 +8528,10 @@
         <v>YES</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q110" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R110" s="7"/>
     </row>
@@ -8557,10 +8540,10 @@
         <v>110</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D111" s="6" t="n">
         <v>3</v>
@@ -8569,7 +8552,7 @@
         <v>1820</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G111" s="9" t="n">
         <v>2000</v>
@@ -8606,10 +8589,10 @@
         <v>YES</v>
       </c>
       <c r="P111" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q111" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R111" s="7"/>
     </row>
@@ -8618,10 +8601,10 @@
         <v>111</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D112" s="6" t="n">
         <v>3</v>
@@ -8630,7 +8613,7 @@
         <v>2860</v>
       </c>
       <c r="F112" s="7" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="G112" s="9" t="n">
         <v>4000</v>
@@ -8667,10 +8650,10 @@
         <v>YES</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q112" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R112" s="7"/>
     </row>
@@ -8679,10 +8662,10 @@
         <v>112</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D113" s="6" t="n">
         <v>2</v>
@@ -8691,7 +8674,7 @@
         <v>12350</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G113" s="9" t="n">
         <v>8000</v>
@@ -8728,13 +8711,13 @@
         <v>YES</v>
       </c>
       <c r="P113" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q113" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R113" s="7" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8742,10 +8725,10 @@
         <v>113</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D114" s="6" t="n">
         <v>3</v>
@@ -8754,7 +8737,7 @@
         <v>1560</v>
       </c>
       <c r="F114" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G114" s="9" t="n">
         <v>800</v>
@@ -8791,10 +8774,10 @@
         <v>YES</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q114" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R114" s="7"/>
     </row>
@@ -8803,10 +8786,10 @@
         <v>114</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D115" s="6" t="n">
         <v>3</v>
@@ -8815,7 +8798,7 @@
         <v>1950</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G115" s="9" t="n">
         <v>900</v>
@@ -8852,10 +8835,10 @@
         <v>YES</v>
       </c>
       <c r="P115" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q115" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R115" s="7"/>
     </row>
@@ -8864,10 +8847,10 @@
         <v>115</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D116" s="6" t="n">
         <v>2</v>
@@ -8876,7 +8859,7 @@
         <v>11050</v>
       </c>
       <c r="F116" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G116" s="9" t="n">
         <v>6500</v>
@@ -8913,10 +8896,10 @@
         <v/>
       </c>
       <c r="P116" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q116" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R116" s="7"/>
     </row>
@@ -8925,10 +8908,10 @@
         <v>116</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D117" s="6" t="n">
         <v>2</v>
@@ -8937,7 +8920,7 @@
         <v>11050</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G117" s="9" t="n">
         <v>6500</v>
@@ -8974,10 +8957,10 @@
         <v>YES</v>
       </c>
       <c r="P117" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q117" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R117" s="7"/>
     </row>
@@ -8986,10 +8969,10 @@
         <v>117</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D118" s="6" t="n">
         <v>15</v>
@@ -8998,7 +8981,7 @@
         <v>585</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G118" s="9" t="n">
         <v>300</v>
@@ -9035,10 +9018,10 @@
         <v/>
       </c>
       <c r="P118" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q118" s="7" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="R118" s="7"/>
     </row>
@@ -9047,10 +9030,10 @@
         <v>118</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D119" s="6" t="n">
         <v>15</v>
@@ -9059,7 +9042,7 @@
         <v>585</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G119" s="9" t="n">
         <v>300</v>
@@ -9096,10 +9079,10 @@
         <v/>
       </c>
       <c r="P119" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q119" s="7" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="R119" s="7"/>
     </row>
@@ -9108,10 +9091,10 @@
         <v>119</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D120" s="6" t="n">
         <v>2</v>
@@ -9120,7 +9103,7 @@
         <v>910</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G120" s="9" t="n">
         <v>400</v>
@@ -9157,10 +9140,10 @@
         <v>YES</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q120" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R120" s="7"/>
     </row>
@@ -9169,10 +9152,10 @@
         <v>120</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D121" s="6" t="n">
         <v>6</v>
@@ -9181,7 +9164,7 @@
         <v>910</v>
       </c>
       <c r="F121" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G121" s="9" t="n">
         <v>400</v>
@@ -9218,10 +9201,10 @@
         <v/>
       </c>
       <c r="P121" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q121" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R121" s="7"/>
     </row>
@@ -9230,10 +9213,10 @@
         <v>121</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D122" s="6" t="n">
         <v>6</v>
@@ -9242,7 +9225,7 @@
         <v>637</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G122" s="9" t="n">
         <v>300</v>
@@ -9279,10 +9262,10 @@
         <v/>
       </c>
       <c r="P122" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q122" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R122" s="7"/>
     </row>
@@ -9291,10 +9274,10 @@
         <v>122</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D123" s="6" t="n">
         <v>1</v>
@@ -9303,7 +9286,7 @@
         <v>357500</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="G123" s="9" t="n">
         <v>200000</v>
@@ -9340,13 +9323,13 @@
         <v/>
       </c>
       <c r="P123" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q123" s="7" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="R123" s="7" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9354,10 +9337,10 @@
         <v>123</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D124" s="6" t="n">
         <v>2</v>
@@ -9366,7 +9349,7 @@
         <v>23400</v>
       </c>
       <c r="F124" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G124" s="9" t="n">
         <v>14000</v>
@@ -9403,10 +9386,10 @@
         <v/>
       </c>
       <c r="P124" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q124" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R124" s="7"/>
     </row>
@@ -9415,10 +9398,10 @@
         <v>124</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D125" s="6" t="n">
         <v>2</v>
@@ -9427,7 +9410,7 @@
         <v>4550</v>
       </c>
       <c r="F125" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G125" s="9" t="n">
         <v>2500</v>
@@ -9464,10 +9447,10 @@
         <v/>
       </c>
       <c r="P125" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q125" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R125" s="7"/>
     </row>
@@ -9476,10 +9459,10 @@
         <v>125</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D126" s="6" t="n">
         <v>12</v>
@@ -9488,7 +9471,7 @@
         <v>585</v>
       </c>
       <c r="F126" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G126" s="9" t="n">
         <v>250</v>
@@ -9525,10 +9508,10 @@
         <v/>
       </c>
       <c r="P126" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q126" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R126" s="7"/>
     </row>
@@ -9537,10 +9520,10 @@
         <v>126</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D127" s="6" t="n">
         <v>12</v>
@@ -9549,7 +9532,7 @@
         <v>780</v>
       </c>
       <c r="F127" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G127" s="9" t="n">
         <v>300</v>
@@ -9586,10 +9569,10 @@
         <v/>
       </c>
       <c r="P127" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q127" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R127" s="7"/>
     </row>
@@ -9598,10 +9581,10 @@
         <v>127</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D128" s="6" t="n">
         <v>6</v>
@@ -9610,7 +9593,7 @@
         <v>455</v>
       </c>
       <c r="F128" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G128" s="9" t="n">
         <v>200</v>
@@ -9647,10 +9630,10 @@
         <v/>
       </c>
       <c r="P128" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q128" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R128" s="7"/>
     </row>
@@ -9659,10 +9642,10 @@
         <v>128</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D129" s="6" t="n">
         <v>6</v>
@@ -9671,7 +9654,7 @@
         <v>455</v>
       </c>
       <c r="F129" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G129" s="9" t="n">
         <v>200</v>
@@ -9708,10 +9691,10 @@
         <v/>
       </c>
       <c r="P129" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q129" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R129" s="7"/>
     </row>
@@ -9720,10 +9703,10 @@
         <v>129</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D130" s="6" t="n">
         <v>6</v>
@@ -9732,7 +9715,7 @@
         <v>455</v>
       </c>
       <c r="F130" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G130" s="9" t="n">
         <v>200</v>
@@ -9769,10 +9752,10 @@
         <v/>
       </c>
       <c r="P130" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q130" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R130" s="7"/>
     </row>
@@ -9781,10 +9764,10 @@
         <v>130</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D131" s="6" t="n">
         <v>6</v>
@@ -9793,7 +9776,7 @@
         <v>2340</v>
       </c>
       <c r="F131" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G131" s="9" t="n">
         <v>1500</v>
@@ -9830,10 +9813,10 @@
         <v/>
       </c>
       <c r="P131" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q131" s="7" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="R131" s="7"/>
     </row>
@@ -9842,10 +9825,10 @@
         <v>131</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D132" s="6" t="n">
         <v>2</v>
@@ -9854,7 +9837,7 @@
         <v>7800</v>
       </c>
       <c r="F132" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G132" s="9" t="n">
         <v>5000</v>
@@ -9891,10 +9874,10 @@
         <v/>
       </c>
       <c r="P132" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q132" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R132" s="7"/>
     </row>
@@ -9903,10 +9886,10 @@
         <v>132</v>
       </c>
       <c r="B133" s="7" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D133" s="6" t="n">
         <v>10</v>
@@ -9915,7 +9898,7 @@
         <v>455</v>
       </c>
       <c r="F133" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G133" s="9" t="n">
         <v>250</v>
@@ -9952,10 +9935,10 @@
         <v/>
       </c>
       <c r="P133" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q133" s="7" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="R133" s="7"/>
     </row>
@@ -9964,10 +9947,10 @@
         <v>133</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D134" s="6" t="n">
         <v>6</v>
@@ -9976,7 +9959,7 @@
         <v>650</v>
       </c>
       <c r="F134" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G134" s="9" t="n">
         <v>300</v>
@@ -10013,10 +9996,10 @@
         <v>YES</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q134" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R134" s="7"/>
     </row>
@@ -10025,10 +10008,10 @@
         <v>134</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D135" s="6" t="n">
         <v>6</v>
@@ -10037,7 +10020,7 @@
         <v>1040</v>
       </c>
       <c r="F135" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G135" s="9" t="n">
         <v>600</v>
@@ -10074,10 +10057,10 @@
         <v/>
       </c>
       <c r="P135" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q135" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R135" s="7"/>
     </row>
@@ -10086,10 +10069,10 @@
         <v>135</v>
       </c>
       <c r="B136" s="7" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D136" s="6" t="n">
         <v>6</v>
@@ -10098,7 +10081,7 @@
         <v>2860</v>
       </c>
       <c r="F136" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G136" s="9" t="n">
         <v>1800</v>
@@ -10135,10 +10118,10 @@
         <v/>
       </c>
       <c r="P136" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q136" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R136" s="7"/>
     </row>
@@ -10147,10 +10130,10 @@
         <v>136</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D137" s="6" t="n">
         <v>500</v>
@@ -10159,7 +10142,7 @@
         <v>130</v>
       </c>
       <c r="F137" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G137" s="9" t="n">
         <v>80</v>
@@ -10196,10 +10179,10 @@
         <v/>
       </c>
       <c r="P137" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q137" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R137" s="7"/>
     </row>
@@ -10208,10 +10191,10 @@
         <v>138</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D138" s="6" t="n">
         <v>24</v>
@@ -10220,7 +10203,7 @@
         <v>1170</v>
       </c>
       <c r="F138" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G138" s="9" t="n">
         <v>600</v>
@@ -10257,10 +10240,10 @@
         <v/>
       </c>
       <c r="P138" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q138" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R138" s="7"/>
     </row>
@@ -10269,10 +10252,10 @@
         <v>139</v>
       </c>
       <c r="B139" s="7" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D139" s="6" t="n">
         <v>24</v>
@@ -10281,7 +10264,7 @@
         <v>715</v>
       </c>
       <c r="F139" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G139" s="9" t="n">
         <v>350</v>
@@ -10318,10 +10301,10 @@
         <v>YES</v>
       </c>
       <c r="P139" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q139" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R139" s="7"/>
     </row>
@@ -10330,10 +10313,10 @@
         <v>140</v>
       </c>
       <c r="B140" s="7" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D140" s="6" t="n">
         <v>24</v>
@@ -10342,7 +10325,7 @@
         <v>1560</v>
       </c>
       <c r="F140" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G140" s="9" t="n">
         <v>900</v>
@@ -10379,10 +10362,10 @@
         <v/>
       </c>
       <c r="P140" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q140" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R140" s="7"/>
     </row>
@@ -10391,10 +10374,10 @@
         <v>142</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D141" s="6" t="n">
         <v>3</v>
@@ -10403,7 +10386,7 @@
         <v>7150</v>
       </c>
       <c r="F141" s="7" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G141" s="9" t="n">
         <v>5000</v>
@@ -10440,10 +10423,10 @@
         <v/>
       </c>
       <c r="P141" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q141" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R141" s="7"/>
     </row>
@@ -10452,10 +10435,10 @@
         <v>143</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D142" s="6" t="n">
         <v>3</v>
@@ -10464,7 +10447,7 @@
         <v>7150</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G142" s="9" t="n">
         <v>5000</v>
@@ -10501,10 +10484,10 @@
         <v/>
       </c>
       <c r="P142" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q142" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R142" s="7"/>
     </row>
@@ -10513,10 +10496,10 @@
         <v>144</v>
       </c>
       <c r="B143" s="7" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D143" s="6" t="n">
         <v>3</v>
@@ -10525,7 +10508,7 @@
         <v>8450</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G143" s="9" t="n">
         <v>6000</v>
@@ -10562,10 +10545,10 @@
         <v/>
       </c>
       <c r="P143" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q143" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R143" s="7"/>
     </row>
@@ -10574,10 +10557,10 @@
         <v>145</v>
       </c>
       <c r="B144" s="7" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D144" s="6" t="n">
         <v>500</v>
@@ -10586,7 +10569,7 @@
         <v>104</v>
       </c>
       <c r="F144" s="7" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="G144" s="9" t="n">
         <v>50</v>
@@ -10623,13 +10606,13 @@
         <v>YES</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q144" s="7" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="R144" s="7" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10637,10 +10620,10 @@
         <v>146</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D145" s="6" t="n">
         <v>1</v>
@@ -10649,7 +10632,7 @@
         <v>105788</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G145" s="9" t="n">
         <v>80000</v>
@@ -10686,10 +10669,10 @@
         <v/>
       </c>
       <c r="P145" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q145" s="7" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="R145" s="7"/>
     </row>
@@ -10698,10 +10681,10 @@
         <v>147</v>
       </c>
       <c r="B146" s="7" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D146" s="6" t="n">
         <v>1</v>
@@ -10710,7 +10693,7 @@
         <v>245700</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="G146" s="9" t="n">
         <v>200000</v>
@@ -10747,10 +10730,10 @@
         <v/>
       </c>
       <c r="P146" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q146" s="7" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="R146" s="7"/>
     </row>
@@ -10759,10 +10742,10 @@
         <v>148</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D147" s="6" t="n">
         <v>12</v>
@@ -10771,7 +10754,7 @@
         <v>650</v>
       </c>
       <c r="F147" s="7" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G147" s="9" t="n">
         <v>300</v>
@@ -10808,10 +10791,10 @@
         <v>YES</v>
       </c>
       <c r="P147" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q147" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R147" s="7"/>
     </row>
@@ -10820,10 +10803,10 @@
         <v>149</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D148" s="6" t="n">
         <v>100</v>
@@ -10832,17 +10815,17 @@
         <v>1754</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G148" s="9" t="n">
-        <v>1100</v>
+        <v>1299</v>
       </c>
       <c r="H148" s="9" t="n">
-        <v>1420</v>
+        <v>1380</v>
       </c>
       <c r="I148" s="10" t="n">
         <f aca="false">IF(E148=0,0,(E148-H148)/E148)</f>
-        <v>0.19042189281642</v>
+        <v>0.213226909920182</v>
       </c>
       <c r="J148" s="6" t="str">
         <f aca="false">IF(E148&lt;G148,"LOSS",IF(E148&lt;H148*1.1,"THIN / RISK",IF(E148&gt;H148*1.8,"OVERPRICED?","OK")))</f>
@@ -10862,17 +10845,17 @@
       </c>
       <c r="N148" s="8" t="n">
         <f aca="false">D148*H148</f>
-        <v>142000</v>
+        <v>138000</v>
       </c>
       <c r="O148" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C148,F148)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q148" s="7" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="R148" s="7"/>
     </row>
@@ -10881,10 +10864,10 @@
         <v>150</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D149" s="6" t="n">
         <v>100</v>
@@ -10893,7 +10876,7 @@
         <v>1235</v>
       </c>
       <c r="F149" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G149" s="9" t="n">
         <v>700</v>
@@ -10930,10 +10913,10 @@
         <v/>
       </c>
       <c r="P149" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q149" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R149" s="7"/>
     </row>
@@ -10942,10 +10925,10 @@
         <v>151</v>
       </c>
       <c r="B150" s="7" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D150" s="6" t="n">
         <v>100</v>
@@ -10954,7 +10937,7 @@
         <v>650</v>
       </c>
       <c r="F150" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G150" s="9" t="n">
         <v>350</v>
@@ -10991,10 +10974,10 @@
         <v/>
       </c>
       <c r="P150" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q150" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R150" s="7"/>
     </row>
@@ -11003,10 +10986,10 @@
         <v>152</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D151" s="6" t="n">
         <v>24</v>
@@ -11015,7 +10998,7 @@
         <v>546</v>
       </c>
       <c r="F151" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G151" s="9" t="n">
         <v>300</v>
@@ -11052,10 +11035,10 @@
         <v/>
       </c>
       <c r="P151" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q151" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R151" s="7"/>
     </row>
@@ -11064,10 +11047,10 @@
         <v>153</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D152" s="6" t="n">
         <v>24</v>
@@ -11076,7 +11059,7 @@
         <v>1105</v>
       </c>
       <c r="F152" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G152" s="9" t="n">
         <v>600</v>
@@ -11113,10 +11096,10 @@
         <v/>
       </c>
       <c r="P152" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q152" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R152" s="7"/>
     </row>
@@ -11125,10 +11108,10 @@
         <v>154</v>
       </c>
       <c r="B153" s="7" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D153" s="6" t="n">
         <v>12</v>
@@ -11137,7 +11120,7 @@
         <v>1560</v>
       </c>
       <c r="F153" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G153" s="9" t="n">
         <v>900</v>
@@ -11174,10 +11157,10 @@
         <v/>
       </c>
       <c r="P153" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q153" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R153" s="7"/>
     </row>
@@ -11186,10 +11169,10 @@
         <v>155</v>
       </c>
       <c r="B154" s="7" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D154" s="6" t="n">
         <v>50</v>
@@ -11198,7 +11181,7 @@
         <v>748</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G154" s="9" t="n">
         <v>400</v>
@@ -11235,10 +11218,10 @@
         <v/>
       </c>
       <c r="P154" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q154" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R154" s="7"/>
     </row>
@@ -11247,10 +11230,10 @@
         <v>156</v>
       </c>
       <c r="B155" s="7" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C155" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D155" s="6" t="n">
         <v>30</v>
@@ -11259,7 +11242,7 @@
         <v>748</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G155" s="9" t="n">
         <v>400</v>
@@ -11296,10 +11279,10 @@
         <v/>
       </c>
       <c r="P155" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q155" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R155" s="7"/>
     </row>
@@ -11308,10 +11291,10 @@
         <v>157</v>
       </c>
       <c r="B156" s="7" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D156" s="6" t="n">
         <v>30</v>
@@ -11320,7 +11303,7 @@
         <v>748</v>
       </c>
       <c r="F156" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G156" s="9" t="n">
         <v>400</v>
@@ -11357,10 +11340,10 @@
         <v/>
       </c>
       <c r="P156" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q156" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R156" s="7"/>
     </row>
@@ -11369,10 +11352,10 @@
         <v>158</v>
       </c>
       <c r="B157" s="7" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D157" s="6" t="n">
         <v>12</v>
@@ -11381,7 +11364,7 @@
         <v>311</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="G157" s="9" t="n">
         <v>150</v>
@@ -11418,13 +11401,13 @@
         <v>YES</v>
       </c>
       <c r="P157" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q157" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R157" s="7" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11432,10 +11415,10 @@
         <v>159</v>
       </c>
       <c r="B158" s="7" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D158" s="6" t="n">
         <v>100</v>
@@ -11444,7 +11427,7 @@
         <v>325</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="G158" s="9" t="n">
         <v>180</v>
@@ -11481,10 +11464,10 @@
         <v>YES</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q158" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="R158" s="7"/>
     </row>
@@ -11493,10 +11476,10 @@
         <v>160</v>
       </c>
       <c r="B159" s="7" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C159" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D159" s="6" t="n">
         <v>150</v>
@@ -11505,7 +11488,7 @@
         <v>117</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="G159" s="9" t="n">
         <v>60</v>
@@ -11542,10 +11525,10 @@
         <v>YES</v>
       </c>
       <c r="P159" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q159" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R159" s="7"/>
     </row>
@@ -11554,10 +11537,10 @@
         <v>161</v>
       </c>
       <c r="B160" s="7" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C160" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D160" s="6" t="n">
         <v>150</v>
@@ -11566,7 +11549,7 @@
         <v>169</v>
       </c>
       <c r="F160" s="7" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="G160" s="9" t="n">
         <v>90</v>
@@ -11603,10 +11586,10 @@
         <v>YES</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q160" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R160" s="7"/>
     </row>
@@ -11615,10 +11598,10 @@
         <v>162</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D161" s="6" t="n">
         <v>150</v>
@@ -11627,7 +11610,7 @@
         <v>234</v>
       </c>
       <c r="F161" s="7" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="G161" s="9" t="n">
         <v>120</v>
@@ -11664,10 +11647,10 @@
         <v>YES</v>
       </c>
       <c r="P161" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q161" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R161" s="7"/>
     </row>
@@ -11676,10 +11659,10 @@
         <v>164</v>
       </c>
       <c r="B162" s="7" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D162" s="6" t="n">
         <v>40</v>
@@ -11688,7 +11671,7 @@
         <v>1209</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G162" s="9" t="n">
         <v>800</v>
@@ -11725,13 +11708,13 @@
         <v/>
       </c>
       <c r="P162" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q162" s="7" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="R162" s="7" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11739,10 +11722,10 @@
         <v>165</v>
       </c>
       <c r="B163" s="7" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D163" s="6" t="n">
         <v>40</v>
@@ -11751,7 +11734,7 @@
         <v>1209</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G163" s="9" t="n">
         <v>800</v>
@@ -11788,10 +11771,10 @@
         <v/>
       </c>
       <c r="P163" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q163" s="7" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="R163" s="7"/>
     </row>
@@ -11800,10 +11783,10 @@
         <v>166</v>
       </c>
       <c r="B164" s="7" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D164" s="6" t="n">
         <v>20</v>
@@ -11812,7 +11795,7 @@
         <v>3022</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G164" s="9" t="n">
         <v>2200</v>
@@ -11849,10 +11832,10 @@
         <v/>
       </c>
       <c r="P164" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q164" s="7" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="R164" s="7"/>
     </row>
@@ -11861,10 +11844,10 @@
         <v>167</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C165" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D165" s="6" t="n">
         <v>40</v>
@@ -11873,7 +11856,7 @@
         <v>6240</v>
       </c>
       <c r="F165" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G165" s="9" t="n">
         <v>4500</v>
@@ -11910,10 +11893,10 @@
         <v/>
       </c>
       <c r="P165" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q165" s="7" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="R165" s="7"/>
     </row>
@@ -11922,10 +11905,10 @@
         <v>168</v>
       </c>
       <c r="B166" s="7" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D166" s="6" t="n">
         <v>20</v>
@@ -11934,7 +11917,7 @@
         <v>7150</v>
       </c>
       <c r="F166" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G166" s="9" t="n">
         <v>5200</v>
@@ -11971,10 +11954,10 @@
         <v/>
       </c>
       <c r="P166" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q166" s="7" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="R166" s="7"/>
     </row>
@@ -11983,10 +11966,10 @@
         <v>177</v>
       </c>
       <c r="B167" s="7" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C167" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D167" s="6" t="n">
         <v>3</v>
@@ -11995,7 +11978,7 @@
         <v>5850</v>
       </c>
       <c r="F167" s="7" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="G167" s="9" t="n">
         <v>3500</v>
@@ -12032,10 +12015,10 @@
         <v>YES</v>
       </c>
       <c r="P167" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q167" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R167" s="7"/>
     </row>
@@ -12044,10 +12027,10 @@
         <v>179</v>
       </c>
       <c r="B168" s="7" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C168" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D168" s="6" t="n">
         <v>1</v>
@@ -12056,7 +12039,7 @@
         <v>23400</v>
       </c>
       <c r="F168" s="7" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G168" s="9" t="n">
         <v>20000</v>
@@ -12093,10 +12076,10 @@
         <v>YES</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q168" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R168" s="7"/>
     </row>
@@ -12105,10 +12088,10 @@
         <v>180</v>
       </c>
       <c r="B169" s="7" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C169" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D169" s="6" t="n">
         <v>1</v>
@@ -12117,7 +12100,7 @@
         <v>15600</v>
       </c>
       <c r="F169" s="7" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G169" s="9" t="n">
         <v>14000</v>
@@ -12154,10 +12137,10 @@
         <v>YES</v>
       </c>
       <c r="P169" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q169" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R169" s="7"/>
     </row>
@@ -12166,10 +12149,10 @@
         <v>181</v>
       </c>
       <c r="B170" s="7" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D170" s="6" t="n">
         <v>1</v>
@@ -12178,7 +12161,7 @@
         <v>33800</v>
       </c>
       <c r="F170" s="7" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G170" s="9" t="n">
         <v>28000</v>
@@ -12215,10 +12198,10 @@
         <v>YES</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q170" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R170" s="7"/>
     </row>
@@ -12227,10 +12210,10 @@
         <v>182</v>
       </c>
       <c r="B171" s="7" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D171" s="6" t="n">
         <v>1</v>
@@ -12239,7 +12222,7 @@
         <v>23400</v>
       </c>
       <c r="F171" s="7" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="G171" s="9" t="n">
         <v>20000</v>
@@ -12276,10 +12259,10 @@
         <v>YES</v>
       </c>
       <c r="P171" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q171" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R171" s="7"/>
     </row>
@@ -12288,10 +12271,10 @@
         <v>183</v>
       </c>
       <c r="B172" s="7" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C172" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D172" s="6" t="n">
         <v>3</v>
@@ -12300,7 +12283,7 @@
         <v>2860</v>
       </c>
       <c r="F172" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G172" s="9" t="n">
         <v>1800</v>
@@ -12337,10 +12320,10 @@
         <v>YES</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q172" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R172" s="7"/>
     </row>
@@ -12349,10 +12332,10 @@
         <v>184</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D173" s="6" t="n">
         <v>3</v>
@@ -12361,7 +12344,7 @@
         <v>3250</v>
       </c>
       <c r="F173" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G173" s="9" t="n">
         <v>2100</v>
@@ -12398,10 +12381,10 @@
         <v>YES</v>
       </c>
       <c r="P173" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q173" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R173" s="7"/>
     </row>
@@ -12410,10 +12393,10 @@
         <v>185</v>
       </c>
       <c r="B174" s="7" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D174" s="6" t="n">
         <v>3</v>
@@ -12422,7 +12405,7 @@
         <v>3900</v>
       </c>
       <c r="F174" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G174" s="9" t="n">
         <v>2600</v>
@@ -12459,10 +12442,10 @@
         <v>YES</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q174" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R174" s="7"/>
     </row>
@@ -12471,10 +12454,10 @@
         <v>186</v>
       </c>
       <c r="B175" s="7" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D175" s="6" t="n">
         <v>3</v>
@@ -12483,7 +12466,7 @@
         <v>4550</v>
       </c>
       <c r="F175" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G175" s="9" t="n">
         <v>3300</v>
@@ -12520,10 +12503,10 @@
         <v>YES</v>
       </c>
       <c r="P175" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q175" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R175" s="7"/>
     </row>
@@ -12532,10 +12515,10 @@
         <v>187</v>
       </c>
       <c r="B176" s="7" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D176" s="6" t="n">
         <v>2</v>
@@ -12544,7 +12527,7 @@
         <v>7150</v>
       </c>
       <c r="F176" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G176" s="9" t="n">
         <v>5500</v>
@@ -12581,10 +12564,10 @@
         <v>YES</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q176" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R176" s="7"/>
     </row>
@@ -12593,10 +12576,10 @@
         <v>188</v>
       </c>
       <c r="B177" s="7" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D177" s="6" t="n">
         <v>1</v>
@@ -12605,7 +12588,7 @@
         <v>8450</v>
       </c>
       <c r="F177" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G177" s="9" t="n">
         <v>7000</v>
@@ -12642,10 +12625,10 @@
         <v>YES</v>
       </c>
       <c r="P177" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q177" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R177" s="7"/>
     </row>
@@ -12654,10 +12637,10 @@
         <v>189</v>
       </c>
       <c r="B178" s="7" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D178" s="6" t="n">
         <v>1</v>
@@ -12666,7 +12649,7 @@
         <v>9750</v>
       </c>
       <c r="F178" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G178" s="9" t="n">
         <v>8500</v>
@@ -12703,10 +12686,10 @@
         <v>YES</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q178" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R178" s="7"/>
     </row>
@@ -12715,10 +12698,10 @@
         <v>190</v>
       </c>
       <c r="B179" s="7" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D179" s="6" t="n">
         <v>2</v>
@@ -12727,7 +12710,7 @@
         <v>2340</v>
       </c>
       <c r="F179" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G179" s="9" t="n">
         <v>1500</v>
@@ -12764,10 +12747,10 @@
         <v>YES</v>
       </c>
       <c r="P179" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q179" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R179" s="7"/>
     </row>
@@ -12776,10 +12759,10 @@
         <v>191</v>
       </c>
       <c r="B180" s="7" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D180" s="6" t="n">
         <v>2</v>
@@ -12788,7 +12771,7 @@
         <v>3640</v>
       </c>
       <c r="F180" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G180" s="9" t="n">
         <v>2300</v>
@@ -12825,10 +12808,10 @@
         <v>YES</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q180" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R180" s="7"/>
     </row>
@@ -12837,10 +12820,10 @@
         <v>192</v>
       </c>
       <c r="B181" s="7" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D181" s="6" t="n">
         <v>3</v>
@@ -12849,7 +12832,7 @@
         <v>1950</v>
       </c>
       <c r="F181" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G181" s="9" t="n">
         <v>1200</v>
@@ -12886,10 +12869,10 @@
         <v>YES</v>
       </c>
       <c r="P181" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q181" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R181" s="7"/>
     </row>
@@ -12898,10 +12881,10 @@
         <v>193</v>
       </c>
       <c r="B182" s="7" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D182" s="6" t="n">
         <v>2</v>
@@ -12910,7 +12893,7 @@
         <v>5850</v>
       </c>
       <c r="F182" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G182" s="9" t="n">
         <v>4000</v>
@@ -12947,10 +12930,10 @@
         <v>YES</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q182" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R182" s="7"/>
     </row>
@@ -12959,10 +12942,10 @@
         <v>194</v>
       </c>
       <c r="B183" s="7" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D183" s="6" t="n">
         <v>3</v>
@@ -12971,7 +12954,7 @@
         <v>1950</v>
       </c>
       <c r="F183" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G183" s="9" t="n">
         <v>1200</v>
@@ -13008,10 +12991,10 @@
         <v>YES</v>
       </c>
       <c r="P183" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q183" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R183" s="7"/>
     </row>
@@ -13020,10 +13003,10 @@
         <v>195</v>
       </c>
       <c r="B184" s="7" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D184" s="6" t="n">
         <v>2</v>
@@ -13032,7 +13015,7 @@
         <v>5850</v>
       </c>
       <c r="F184" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G184" s="9" t="n">
         <v>4000</v>
@@ -13069,10 +13052,10 @@
         <v>YES</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q184" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R184" s="7"/>
     </row>
@@ -13081,10 +13064,10 @@
         <v>196</v>
       </c>
       <c r="B185" s="7" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D185" s="6" t="n">
         <v>2</v>
@@ -13093,7 +13076,7 @@
         <v>4550</v>
       </c>
       <c r="F185" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G185" s="9" t="n">
         <v>3500</v>
@@ -13130,10 +13113,10 @@
         <v>YES</v>
       </c>
       <c r="P185" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q185" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R185" s="7"/>
     </row>
@@ -13142,10 +13125,10 @@
         <v>197</v>
       </c>
       <c r="B186" s="7" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D186" s="6" t="n">
         <v>1</v>
@@ -13154,7 +13137,7 @@
         <v>17940</v>
       </c>
       <c r="F186" s="7" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G186" s="9" t="n">
         <v>6000</v>
@@ -13191,13 +13174,13 @@
         <v>YES</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q186" s="7" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="R186" s="7" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13205,10 +13188,10 @@
         <v>198</v>
       </c>
       <c r="B187" s="7" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D187" s="6" t="n">
         <v>1</v>
@@ -13217,7 +13200,7 @@
         <v>18850</v>
       </c>
       <c r="F187" s="7" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="G187" s="9" t="n">
         <v>7500</v>
@@ -13254,10 +13237,10 @@
         <v>YES</v>
       </c>
       <c r="P187" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q187" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R187" s="7"/>
     </row>
@@ -13266,10 +13249,10 @@
         <v>199</v>
       </c>
       <c r="B188" s="7" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D188" s="6" t="n">
         <v>1</v>
@@ -13278,7 +13261,7 @@
         <v>19500</v>
       </c>
       <c r="F188" s="7" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="G188" s="9" t="n">
         <v>8500</v>
@@ -13315,10 +13298,10 @@
         <v>YES</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q188" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R188" s="7"/>
     </row>
@@ -13327,10 +13310,10 @@
         <v>200</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D189" s="6" t="n">
         <v>1</v>
@@ -13339,7 +13322,7 @@
         <v>20800</v>
       </c>
       <c r="F189" s="7" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="G189" s="9" t="n">
         <v>10000</v>
@@ -13376,10 +13359,10 @@
         <v>YES</v>
       </c>
       <c r="P189" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q189" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R189" s="7"/>
     </row>
@@ -13388,10 +13371,10 @@
         <v>201</v>
       </c>
       <c r="B190" s="7" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D190" s="6" t="n">
         <v>1</v>
@@ -13400,7 +13383,7 @@
         <v>22750</v>
       </c>
       <c r="F190" s="7" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="G190" s="9" t="n">
         <v>12000</v>
@@ -13437,10 +13420,10 @@
         <v>YES</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q190" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R190" s="7"/>
     </row>
@@ -13449,10 +13432,10 @@
         <v>202</v>
       </c>
       <c r="B191" s="7" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D191" s="6" t="n">
         <v>2</v>
@@ -13461,7 +13444,7 @@
         <v>2340</v>
       </c>
       <c r="F191" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G191" s="9" t="n">
         <v>1500</v>
@@ -13498,10 +13481,10 @@
         <v>YES</v>
       </c>
       <c r="P191" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q191" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R191" s="7"/>
     </row>
@@ -13510,10 +13493,10 @@
         <v>204</v>
       </c>
       <c r="B192" s="7" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D192" s="6" t="n">
         <v>6</v>
@@ -13522,7 +13505,7 @@
         <v>845</v>
       </c>
       <c r="F192" s="7" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="G192" s="9" t="n">
         <v>800</v>
@@ -13559,13 +13542,13 @@
         <v>YES</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q192" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R192" s="7" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13573,10 +13556,10 @@
         <v>205</v>
       </c>
       <c r="B193" s="7" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D193" s="6" t="n">
         <v>6</v>
@@ -13585,7 +13568,7 @@
         <v>910</v>
       </c>
       <c r="F193" s="7" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="G193" s="9" t="n">
         <v>900</v>
@@ -13622,10 +13605,10 @@
         <v>YES</v>
       </c>
       <c r="P193" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q193" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R193" s="7"/>
     </row>
@@ -13634,10 +13617,10 @@
         <v>206</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D194" s="6" t="n">
         <v>6</v>
@@ -13646,7 +13629,7 @@
         <v>1170</v>
       </c>
       <c r="F194" s="7" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="G194" s="9" t="n">
         <v>1200</v>
@@ -13683,10 +13666,10 @@
         <v>YES</v>
       </c>
       <c r="P194" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q194" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R194" s="7"/>
     </row>
@@ -13695,10 +13678,10 @@
         <v>207</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D195" s="6" t="n">
         <v>4</v>
@@ -13707,7 +13690,7 @@
         <v>1430</v>
       </c>
       <c r="F195" s="7" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="G195" s="9" t="n">
         <v>1600</v>
@@ -13744,10 +13727,10 @@
         <v>YES</v>
       </c>
       <c r="P195" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q195" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R195" s="7"/>
     </row>
@@ -13756,10 +13739,10 @@
         <v>208</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C196" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D196" s="6" t="n">
         <v>3</v>
@@ -13768,7 +13751,7 @@
         <v>1690</v>
       </c>
       <c r="F196" s="7" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="G196" s="9" t="n">
         <v>2000</v>
@@ -13805,10 +13788,10 @@
         <v>YES</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q196" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R196" s="7"/>
     </row>
@@ -13817,10 +13800,10 @@
         <v>209</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C197" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D197" s="6" t="n">
         <v>3</v>
@@ -13829,7 +13812,7 @@
         <v>2340</v>
       </c>
       <c r="F197" s="7" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="G197" s="9" t="n">
         <v>3000</v>
@@ -13866,10 +13849,10 @@
         <v>YES</v>
       </c>
       <c r="P197" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q197" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R197" s="7"/>
     </row>
@@ -13878,10 +13861,10 @@
         <v>210</v>
       </c>
       <c r="B198" s="7" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C198" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D198" s="6" t="n">
         <v>2</v>
@@ -13890,7 +13873,7 @@
         <v>2860</v>
       </c>
       <c r="F198" s="7" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="G198" s="9" t="n">
         <v>3700</v>
@@ -13927,10 +13910,10 @@
         <v>YES</v>
       </c>
       <c r="P198" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q198" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R198" s="7"/>
     </row>
@@ -13939,10 +13922,10 @@
         <v>211</v>
       </c>
       <c r="B199" s="7" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C199" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D199" s="6" t="n">
         <v>1</v>
@@ -13951,7 +13934,7 @@
         <v>4160</v>
       </c>
       <c r="F199" s="7" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="G199" s="9" t="n">
         <v>5200</v>
@@ -13988,10 +13971,10 @@
         <v>YES</v>
       </c>
       <c r="P199" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q199" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R199" s="7"/>
     </row>
@@ -14000,10 +13983,10 @@
         <v>212</v>
       </c>
       <c r="B200" s="7" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D200" s="6" t="n">
         <v>1</v>
@@ -14012,7 +13995,7 @@
         <v>5460</v>
       </c>
       <c r="F200" s="7" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="G200" s="9" t="n">
         <v>6500</v>
@@ -14049,10 +14032,10 @@
         <v>YES</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q200" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R200" s="7"/>
     </row>
@@ -14061,10 +14044,10 @@
         <v>213</v>
       </c>
       <c r="B201" s="7" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D201" s="6" t="n">
         <v>2</v>
@@ -14073,7 +14056,7 @@
         <v>455</v>
       </c>
       <c r="F201" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G201" s="9" t="n">
         <v>500</v>
@@ -14110,10 +14093,10 @@
         <v>YES</v>
       </c>
       <c r="P201" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q201" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R201" s="7"/>
     </row>
@@ -14122,10 +14105,10 @@
         <v>214</v>
       </c>
       <c r="B202" s="7" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D202" s="6" t="n">
         <v>2</v>
@@ -14134,7 +14117,7 @@
         <v>494</v>
       </c>
       <c r="F202" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G202" s="9" t="n">
         <v>550</v>
@@ -14171,10 +14154,10 @@
         <v>YES</v>
       </c>
       <c r="P202" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q202" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R202" s="7"/>
     </row>
@@ -14183,10 +14166,10 @@
         <v>215</v>
       </c>
       <c r="B203" s="7" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D203" s="6" t="n">
         <v>2</v>
@@ -14195,7 +14178,7 @@
         <v>585</v>
       </c>
       <c r="F203" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G203" s="9" t="n">
         <v>650</v>
@@ -14232,10 +14215,10 @@
         <v>YES</v>
       </c>
       <c r="P203" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q203" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R203" s="7"/>
     </row>
@@ -14244,10 +14227,10 @@
         <v>216</v>
       </c>
       <c r="B204" s="7" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D204" s="6" t="n">
         <v>2</v>
@@ -14256,7 +14239,7 @@
         <v>715</v>
       </c>
       <c r="F204" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G204" s="9" t="n">
         <v>800</v>
@@ -14293,10 +14276,10 @@
         <v>YES</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q204" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R204" s="7"/>
     </row>
@@ -14305,10 +14288,10 @@
         <v>217</v>
       </c>
       <c r="B205" s="7" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D205" s="6" t="n">
         <v>2</v>
@@ -14317,7 +14300,7 @@
         <v>910</v>
       </c>
       <c r="F205" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G205" s="9" t="n">
         <v>1000</v>
@@ -14354,10 +14337,10 @@
         <v>YES</v>
       </c>
       <c r="P205" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q205" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R205" s="7"/>
     </row>
@@ -14366,10 +14349,10 @@
         <v>218</v>
       </c>
       <c r="B206" s="7" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D206" s="6" t="n">
         <v>2</v>
@@ -14378,7 +14361,7 @@
         <v>1170</v>
       </c>
       <c r="F206" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G206" s="9" t="n">
         <v>1400</v>
@@ -14415,10 +14398,10 @@
         <v>YES</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q206" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R206" s="7"/>
     </row>
@@ -14427,10 +14410,10 @@
         <v>219</v>
       </c>
       <c r="B207" s="7" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D207" s="6" t="n">
         <v>1</v>
@@ -14439,7 +14422,7 @@
         <v>1040</v>
       </c>
       <c r="F207" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G207" s="9" t="n">
         <v>1100</v>
@@ -14476,10 +14459,10 @@
         <v>YES</v>
       </c>
       <c r="P207" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q207" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R207" s="7"/>
     </row>
@@ -14488,10 +14471,10 @@
         <v>220</v>
       </c>
       <c r="B208" s="7" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D208" s="6" t="n">
         <v>1</v>
@@ -14500,7 +14483,7 @@
         <v>1430</v>
       </c>
       <c r="F208" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G208" s="9" t="n">
         <v>1400</v>
@@ -14537,10 +14520,10 @@
         <v>YES</v>
       </c>
       <c r="P208" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q208" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R208" s="7"/>
     </row>
@@ -14549,10 +14532,10 @@
         <v>221</v>
       </c>
       <c r="B209" s="7" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C209" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D209" s="6" t="n">
         <v>1</v>
@@ -14561,7 +14544,7 @@
         <v>1950</v>
       </c>
       <c r="F209" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G209" s="9" t="n">
         <v>2000</v>
@@ -14598,10 +14581,10 @@
         <v>YES</v>
       </c>
       <c r="P209" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q209" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R209" s="7"/>
     </row>
@@ -14610,10 +14593,10 @@
         <v>222</v>
       </c>
       <c r="B210" s="7" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D210" s="6" t="n">
         <v>1</v>
@@ -14622,7 +14605,7 @@
         <v>15600</v>
       </c>
       <c r="F210" s="7" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="G210" s="9" t="n">
         <v>18000</v>
@@ -14659,13 +14642,13 @@
         <v>YES</v>
       </c>
       <c r="P210" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q210" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R210" s="7" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14673,10 +14656,10 @@
         <v>223</v>
       </c>
       <c r="B211" s="7" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D211" s="6" t="n">
         <v>2</v>
@@ -14685,7 +14668,7 @@
         <v>30940</v>
       </c>
       <c r="F211" s="7" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="G211" s="9" t="n">
         <v>45000</v>
@@ -14722,13 +14705,13 @@
         <v>YES</v>
       </c>
       <c r="P211" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q211" s="7" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="R211" s="7" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14736,10 +14719,10 @@
         <v>224</v>
       </c>
       <c r="B212" s="7" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D212" s="6" t="n">
         <v>2</v>
@@ -14748,7 +14731,7 @@
         <v>54600</v>
       </c>
       <c r="F212" s="7" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="G212" s="9" t="n">
         <v>85000</v>
@@ -14785,13 +14768,13 @@
         <v>YES</v>
       </c>
       <c r="P212" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q212" s="7" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="R212" s="7" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14799,10 +14782,10 @@
         <v>225</v>
       </c>
       <c r="B213" s="7" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C213" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D213" s="6" t="n">
         <v>24</v>
@@ -14811,7 +14794,7 @@
         <v>1170</v>
       </c>
       <c r="F213" s="7" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="G213" s="9" t="n">
         <v>1000</v>
@@ -14848,10 +14831,10 @@
         <v>YES</v>
       </c>
       <c r="P213" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q213" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R213" s="7"/>
     </row>
@@ -14860,10 +14843,10 @@
         <v>226</v>
       </c>
       <c r="B214" s="7" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D214" s="6" t="n">
         <v>24</v>
@@ -14872,7 +14855,7 @@
         <v>1430</v>
       </c>
       <c r="F214" s="7" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="G214" s="9" t="n">
         <v>1400</v>
@@ -14909,10 +14892,10 @@
         <v>YES</v>
       </c>
       <c r="P214" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q214" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R214" s="7"/>
     </row>
@@ -14921,10 +14904,10 @@
         <v>227</v>
       </c>
       <c r="B215" s="7" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C215" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D215" s="6" t="n">
         <v>24</v>
@@ -14933,7 +14916,7 @@
         <v>1820</v>
       </c>
       <c r="F215" s="7" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="G215" s="9" t="n">
         <v>1900</v>
@@ -14970,10 +14953,10 @@
         <v>YES</v>
       </c>
       <c r="P215" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q215" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R215" s="7"/>
     </row>
@@ -14982,10 +14965,10 @@
         <v>228</v>
       </c>
       <c r="B216" s="7" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D216" s="6" t="n">
         <v>24</v>
@@ -14994,7 +14977,7 @@
         <v>2860</v>
       </c>
       <c r="F216" s="7" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="G216" s="9" t="n">
         <v>3200</v>
@@ -15031,10 +15014,10 @@
         <v>YES</v>
       </c>
       <c r="P216" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q216" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R216" s="7"/>
     </row>
@@ -15043,10 +15026,10 @@
         <v>229</v>
       </c>
       <c r="B217" s="7" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C217" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D217" s="6" t="n">
         <v>24</v>
@@ -15055,7 +15038,7 @@
         <v>2340</v>
       </c>
       <c r="F217" s="7" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="G217" s="9" t="n">
         <v>1800</v>
@@ -15092,10 +15075,10 @@
         <v>YES</v>
       </c>
       <c r="P217" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q217" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R217" s="7"/>
     </row>
@@ -15104,10 +15087,10 @@
         <v>230</v>
       </c>
       <c r="B218" s="7" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D218" s="6" t="n">
         <v>1</v>
@@ -15116,7 +15099,7 @@
         <v>9750</v>
       </c>
       <c r="F218" s="7" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G218" s="9" t="n">
         <v>6000</v>
@@ -15153,10 +15136,10 @@
         <v>YES</v>
       </c>
       <c r="P218" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q218" s="7" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="R218" s="7"/>
     </row>
@@ -15165,10 +15148,10 @@
         <v>231</v>
       </c>
       <c r="B219" s="7" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D219" s="6" t="n">
         <v>1</v>
@@ -15177,7 +15160,7 @@
         <v>12350</v>
       </c>
       <c r="F219" s="7" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="G219" s="9" t="n">
         <v>8000</v>
@@ -15214,10 +15197,10 @@
         <v>YES</v>
       </c>
       <c r="P219" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q219" s="7" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="R219" s="7"/>
     </row>
@@ -15226,10 +15209,10 @@
         <v>233</v>
       </c>
       <c r="B220" s="7" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C220" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D220" s="6" t="n">
         <v>2</v>
@@ -15238,7 +15221,7 @@
         <v>52000</v>
       </c>
       <c r="F220" s="7" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="G220" s="9" t="n">
         <v>38340</v>
@@ -15275,13 +15258,13 @@
         <v>YES</v>
       </c>
       <c r="P220" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q220" s="7" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="R220" s="7" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15289,10 +15272,10 @@
         <v>234</v>
       </c>
       <c r="B221" s="7" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C221" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D221" s="6" t="n">
         <v>3</v>
@@ -15301,7 +15284,7 @@
         <v>3094</v>
       </c>
       <c r="F221" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G221" s="9" t="n">
         <v>1800</v>
@@ -15338,10 +15321,10 @@
         <v/>
       </c>
       <c r="P221" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q221" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R221" s="7"/>
     </row>
@@ -15350,10 +15333,10 @@
         <v>235</v>
       </c>
       <c r="B222" s="7" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D222" s="6" t="n">
         <v>3</v>
@@ -15362,7 +15345,7 @@
         <v>2860</v>
       </c>
       <c r="F222" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G222" s="9" t="n">
         <v>1500</v>
@@ -15399,10 +15382,10 @@
         <v>YES</v>
       </c>
       <c r="P222" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q222" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R222" s="7"/>
     </row>
@@ -15411,10 +15394,10 @@
         <v>236</v>
       </c>
       <c r="B223" s="7" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C223" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D223" s="6" t="n">
         <v>200</v>
@@ -15423,7 +15406,7 @@
         <v>2860</v>
       </c>
       <c r="F223" s="7" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="G223" s="9" t="n">
         <v>2400</v>
@@ -15460,13 +15443,13 @@
         <v/>
       </c>
       <c r="P223" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q223" s="7" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="R223" s="7" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15474,10 +15457,10 @@
         <v>237</v>
       </c>
       <c r="B224" s="7" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C224" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D224" s="6" t="n">
         <v>24</v>
@@ -15486,7 +15469,7 @@
         <v>845</v>
       </c>
       <c r="F224" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G224" s="9" t="n">
         <v>450</v>
@@ -15523,10 +15506,10 @@
         <v>YES</v>
       </c>
       <c r="P224" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q224" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R224" s="7"/>
     </row>
@@ -15535,10 +15518,10 @@
         <v>238</v>
       </c>
       <c r="B225" s="7" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C225" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D225" s="6" t="n">
         <v>6</v>
@@ -15547,7 +15530,7 @@
         <v>8450</v>
       </c>
       <c r="F225" s="7" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="G225" s="9" t="n">
         <v>6000</v>
@@ -15584,13 +15567,13 @@
         <v>YES</v>
       </c>
       <c r="P225" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q225" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R225" s="7" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15598,10 +15581,10 @@
         <v>239</v>
       </c>
       <c r="B226" s="7" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D226" s="6" t="n">
         <v>50</v>
@@ -15610,17 +15593,17 @@
         <v>65000</v>
       </c>
       <c r="F226" s="7" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="G226" s="9" t="n">
-        <v>43200</v>
+        <v>36570</v>
       </c>
       <c r="H226" s="9" t="n">
-        <v>50460</v>
+        <v>44000</v>
       </c>
       <c r="I226" s="10" t="n">
         <f aca="false">IF(E226=0,0,(E226-H226)/E226)</f>
-        <v>0.223692307692308</v>
+        <v>0.323076923076923</v>
       </c>
       <c r="J226" s="6" t="str">
         <f aca="false">IF(E226&lt;G226,"LOSS",IF(E226&lt;H226*1.1,"THIN / RISK",IF(E226&gt;H226*1.8,"OVERPRICED?","OK")))</f>
@@ -15640,20 +15623,20 @@
       </c>
       <c r="N226" s="8" t="n">
         <f aca="false">D226*H226</f>
-        <v>2523000</v>
+        <v>2200000</v>
       </c>
       <c r="O226" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C226,F226)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P226" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q226" s="7" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="R226" s="7" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15661,10 +15644,10 @@
         <v>240</v>
       </c>
       <c r="B227" s="7" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C227" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D227" s="6" t="n">
         <v>50</v>
@@ -15673,7 +15656,7 @@
         <v>325</v>
       </c>
       <c r="F227" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G227" s="9" t="n">
         <v>150</v>
@@ -15710,16 +15693,16 @@
         <v>YES</v>
       </c>
       <c r="P227" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q227" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R227" s="7"/>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B228" s="3" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="L228" s="11" t="n">
         <f aca="false">SUM(L6:L227)</f>
@@ -15727,11 +15710,11 @@
       </c>
       <c r="M228" s="11" t="n">
         <f aca="false">SUM(M6:M227)</f>
-        <v>14051126</v>
+        <v>13938636</v>
       </c>
       <c r="N228" s="11" t="n">
         <f aca="false">SUM(N6:N227)</f>
-        <v>11647580</v>
+        <v>11227980</v>
       </c>
     </row>
   </sheetData>
@@ -15780,12 +15763,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B3" s="11" t="n">
         <f aca="false">COUNTA('Rate Check'!A6:A227)</f>
@@ -15794,25 +15777,25 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B4" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"LOSS")</f>
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B5" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"THIN / RISK")</f>
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B6" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"OK")</f>
@@ -15821,7 +15804,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B7" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"OVERPRICED?")</f>
@@ -15830,7 +15813,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B8" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!O6:O227,"YES")</f>
@@ -15842,7 +15825,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B10" s="11" t="n">
         <f aca="false">'Rate Check'!L228</f>
@@ -15851,38 +15834,38 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B11" s="11" t="n">
         <f aca="false">'Rate Check'!N228</f>
-        <v>11647580</v>
+        <v>11227980</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B12" s="11" t="n">
         <f aca="false">B10-B11</f>
-        <v>561928</v>
+        <v>981528</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B13" s="14" t="n">
         <f aca="false">IF(B10=0,0,B12/B10)</f>
-        <v>0.0460238037437708</v>
+        <v>0.0803904629080877</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B14" s="11" t="n">
         <f aca="false">SUMPRODUCT(('Rate Check'!E6:E227&lt;'Rate Check'!H6:H227)*('Rate Check'!H6:H227-'Rate Check'!E6:E227)*'Rate Check'!D6:D227)</f>
-        <v>1348380</v>
+        <v>1285780</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15890,20 +15873,20 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B16" s="11" t="n">
         <f aca="false">'Rate Check'!M228</f>
-        <v>14051126</v>
+        <v>13938636</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B17" s="14" t="n">
         <f aca="false">IF(B16=0,0,(B16-B11)/B16)</f>
-        <v>0.171057180755478</v>
+        <v>0.194470678479587</v>
       </c>
     </row>
   </sheetData>
@@ -15922,7 +15905,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="55"/>
@@ -15931,255 +15914,247 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="13" t="s">
-        <v>463</v>
-      </c>
-      <c r="B33" s="15" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
     </row>
   </sheetData>
@@ -16189,32 +16164,31 @@
     <hyperlink ref="B5" r:id="rId3" display="https://www.toolsmart.pk/products/licota-9pcs-extra-long-type-hex-key-set"/>
     <hyperlink ref="B6" r:id="rId4" display="https://www.toolsmart.pk/products/licota-120pcs-1-4-3-8-1-2-dr-socket-set"/>
     <hyperlink ref="B7" r:id="rId5" display="https://www.toolsmart.pk/collections/all-tools/grease-gun"/>
-    <hyperlink ref="B8" r:id="rId6" display="https://w11stop.com/licota"/>
-    <hyperlink ref="B9" r:id="rId7" display="https://w11stop.com/licota-atb-1004f-gear-puller"/>
-    <hyperlink ref="B10" r:id="rId8" display="https://w11stop.com/licota-atb-1003g-gear-puller"/>
-    <hyperlink ref="B11" r:id="rId9" display="https://w11stop.com/licota-atb-1017d-gear-puller"/>
-    <hyperlink ref="B12" r:id="rId10" display="https://w11stop.com/lubricants-and-removal/wd-40-330-ml-lubricant"/>
-    <hyperlink ref="B13" r:id="rId11" display="https://w11stop.com/bosch-gws-2200-230-h-grinder"/>
-    <hyperlink ref="B14" r:id="rId12" display="https://w11stop.com/bosch-gbh-180-li-rotary-hammer"/>
-    <hyperlink ref="B15" r:id="rId13" display="https://kamadi.pk/products/gds-18v-1000-bosch-cordless-impact-wrench-650n-m-18v"/>
-    <hyperlink ref="B16" r:id="rId14" display="https://kamadi.pk/products/gdx-180-li-bosch-cordless-impact-driver-wrench-180n-m-18v"/>
-    <hyperlink ref="B17" r:id="rId15" display="https://kamadi.pk/products/bosch-gws-2200-230-h-angle-grinder"/>
-    <hyperlink ref="B18" r:id="rId16" display="https://kamadi.pk/products/insize-1205-300s-vernier-caliper-0-300mm"/>
-    <hyperlink ref="B19" r:id="rId17" display="https://kamadi.pk/products/1108-300-insize-digital-4-way-vernier-caliper-0-300mm"/>
-    <hyperlink ref="B20" r:id="rId18" display="https://kamadi.pk/products/insize-3109-25a-digital-outside-micrometer-0-25mm"/>
-    <hyperlink ref="B21" r:id="rId19" display="https://www.ktools.pk/products/bosch-gds-18v-1000-cordless-impact-wrench"/>
-    <hyperlink ref="B22" r:id="rId20" display="https://www.ktools.pk/products/bosch-cordless-impact-wrench-gdx-180-li"/>
-    <hyperlink ref="B23" r:id="rId21" display="https://www.ktools.pk/products/bosch-cordless-rotary-hammer-with-sds-plus-gbh-180-li"/>
-    <hyperlink ref="B24" r:id="rId22" display="https://www.ktools.pk/products/bosch-cordless-impact-drill-combi-gsb-18v-150-c"/>
-    <hyperlink ref="B25" r:id="rId23" display="https://www.ktools.pk/products/bosch-gws-2200-230h-angle-grinder-230mm-2200w"/>
-    <hyperlink ref="B26" r:id="rId24" display="https://amjadhardware.com/product/1108-300-digital-vernier-caliper-0-300mm-0-12-insize/"/>
-    <hyperlink ref="B27" r:id="rId25" display="https://purchaser.com.pk/insize-4-way-vernier-caliper-1205-200s-en/"/>
-    <hyperlink ref="B28" r:id="rId26" display="https://powerhouseexpress.com.pk/collections/grinders"/>
-    <hyperlink ref="B29" r:id="rId27" display="https://www.rafiqbrothers.com/en/category/hand-pallet-trucks/"/>
-    <hyperlink ref="B30" r:id="rId28" display="https://eqmachines.com/products/hand-pallet-truck-pakistan"/>
-    <hyperlink ref="B31" r:id="rId29" display="https://www.pakwheels.com/accessories-spare-parts/car-jack/213239"/>
-    <hyperlink ref="B32" r:id="rId30" display="https://ingcotool.pk/product/total-swivel-base-bench-vise-with-anvil-6-150mm-tht6166/"/>
-    <hyperlink ref="B33" r:id="rId31" display="https://shop.goldpeaktools.com.ph/products/licota-awx-2603gn-tool-cabinet-carriage-7-drawers"/>
+    <hyperlink ref="B8" r:id="rId6" display="https://kamadi.pk/products/gds-18v-1000-bosch-cordless-impact-wrench-650n-m-18v"/>
+    <hyperlink ref="B9" r:id="rId7" display="https://kamadi.pk/products/gdx-180-li-bosch-cordless-impact-driver-wrench-180n-m-18v"/>
+    <hyperlink ref="B10" r:id="rId8" display="https://kamadi.pk/products/bosch-gws-2200-230-h-angle-grinder"/>
+    <hyperlink ref="B11" r:id="rId9" display="https://kamadi.pk/products/insize-1205-300s-vernier-caliper-0-300mm"/>
+    <hyperlink ref="B12" r:id="rId10" display="https://kamadi.pk/products/1108-300-insize-digital-4-way-vernier-caliper-0-300mm"/>
+    <hyperlink ref="B13" r:id="rId11" display="https://kamadi.pk/products/insize-3109-25a-digital-outside-micrometer-0-25mm"/>
+    <hyperlink ref="B14" r:id="rId12" display="https://www.ktools.pk/products/bosch-gds-18v-1000-cordless-impact-wrench"/>
+    <hyperlink ref="B15" r:id="rId13" display="https://www.ktools.pk/products/bosch-cordless-impact-wrench-gdx-180-li"/>
+    <hyperlink ref="B16" r:id="rId14" display="https://www.ktools.pk/products/bosch-cordless-rotary-hammer-with-sds-plus-gbh-180-li"/>
+    <hyperlink ref="B17" r:id="rId15" display="https://www.ktools.pk/products/bosch-cordless-impact-drill-combi-gsb-18v-150-c"/>
+    <hyperlink ref="B18" r:id="rId16" display="https://www.ktools.pk/products/bosch-gws-2200-230h-angle-grinder-230mm-2200w"/>
+    <hyperlink ref="B19" r:id="rId17" display="https://amjadhardware.com/product/1108-300-digital-vernier-caliper-0-300mm-0-12-insize/"/>
+    <hyperlink ref="B20" r:id="rId18" display="https://purchaser.com.pk/insize-4-way-vernier-caliper-1205-200s-en/"/>
+    <hyperlink ref="B21" r:id="rId19" display="https://powerhouseexpress.com.pk/collections/grinders"/>
+    <hyperlink ref="B22" r:id="rId20" display="https://www.rafiqbrothers.com/en/category/hand-pallet-trucks/"/>
+    <hyperlink ref="B23" r:id="rId21" display="https://eqmachines.com/products/hand-pallet-truck-pakistan"/>
+    <hyperlink ref="B24" r:id="rId22" display="https://www.pakwheels.com/accessories-spare-parts/car-jack/213239"/>
+    <hyperlink ref="B25" r:id="rId23" display="https://ingcotool.pk/product/total-swivel-base-bench-vise-with-anvil-6-150mm-tht6166/"/>
+    <hyperlink ref="B26" r:id="rId24" display="https://www.naheed.pk/wd-40-330ml"/>
+    <hyperlink ref="B27" r:id="rId25" display="https://autohub.pk/products/wd-40-330ml"/>
+    <hyperlink ref="B28" r:id="rId26" display="https://imartpk.com/products/gws-22-230-h-professional"/>
+    <hyperlink ref="B29" r:id="rId27" display="https://www.goldentools.ae/gttecom/singleitemmob/LICOTA/Bearing-and-Seal-Tools/?brcd=4712834507742"/>
+    <hyperlink ref="B30" r:id="rId28" display="https://www.amazon.ae/LICOTA-GEAR-PULLER-ATB-1002C-AT-2102A/dp/B08CTD3842"/>
+    <hyperlink ref="B31" r:id="rId29" display="https://www.goldentools.ae/item/4712818539608"/>
+    <hyperlink ref="B32" r:id="rId30" display="https://shop.goldpeaktools.com.ph/products/licota-awx-2603gn-tool-cabinet-carriage-7-drawers"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/quotes/PR-217-228/Quote_PR217_PR228_Rate_Check.xlsx
+++ b/quotes/PR-217-228/Quote_PR217_PR228_Rate_Check.xlsx
@@ -342,7 +342,7 @@
     <t xml:space="preserve">Bosch Professional</t>
   </si>
   <si>
-    <t xml:space="preserve">Bosch GDX 180-Li</t>
+    <t xml:space="preserve">Bosch Professional GDX 180-Li</t>
   </si>
   <si>
     <t xml:space="preserve">ktools 45,000 solo / 79,000 kit; kamadi 75,200</t>
@@ -354,7 +354,7 @@
     <t xml:space="preserve">CORDLESS IMPACT WRENCH 350N (Bosch)</t>
   </si>
   <si>
-    <t xml:space="preserve">Bosch GDS 18V-350</t>
+    <t xml:space="preserve">Bosch Professional GDS 18V-350</t>
   </si>
   <si>
     <t xml:space="preserve">No PK listing; est from GDX/GDS range</t>
@@ -363,7 +363,7 @@
     <t xml:space="preserve">CORDLESS IMPACT WRENCH 1000N (Bosch)</t>
   </si>
   <si>
-    <t xml:space="preserve">Bosch GDS 18V-1000</t>
+    <t xml:space="preserve">Bosch Professional GDS 18V-1000</t>
   </si>
   <si>
     <t xml:space="preserve">ktools 70,000 solo (oos); kamadi 143,800 kit</t>
@@ -426,7 +426,7 @@
     <t xml:space="preserve">DRILL MACHINE CORDLESS ROTARY HAMMER Bosch</t>
   </si>
   <si>
-    <t xml:space="preserve">Bosch GBH 180-LI / GBH 18V-26</t>
+    <t xml:space="preserve">Bosch Professional GBH 180-LI / GBH 18V-26</t>
   </si>
   <si>
     <t xml:space="preserve">ktools 49,000 solo / 115,000 kit</t>
@@ -615,7 +615,7 @@
     <t xml:space="preserve">CORDLESS DRILL DRIVER 150NM Bosch</t>
   </si>
   <si>
-    <t xml:space="preserve">Bosch GSR/GSB 18V-150 C</t>
+    <t xml:space="preserve">Bosch Professional GSR/GSB 18V-150 C</t>
   </si>
   <si>
     <t xml:space="preserve">ktools GSB 18V-150C 199,500 (oos)</t>
@@ -1128,7 +1128,7 @@
     <t xml:space="preserve">CORDLESS SMALL ANGLE GRINDER 125MM EQUIVAL</t>
   </si>
   <si>
-    <t xml:space="preserve">Bosch GWS 180-LI / GWS 18V-10</t>
+    <t xml:space="preserve">Bosch Professional GWS 180-LI / GWS 18V-10</t>
   </si>
   <si>
     <t xml:space="preserve">powerhouseexpress 38,340 solo; ktools 40,000 solo</t>
@@ -1167,7 +1167,7 @@
     <t xml:space="preserve">ANGLE GRINDER 9" BOSCH PRO STONE BONDED CU</t>
   </si>
   <si>
-    <t xml:space="preserve">Bosch GWS 2200-230 H</t>
+    <t xml:space="preserve">Bosch Professional GWS 2200-230 H</t>
   </si>
   <si>
     <t xml:space="preserve">imartpk 36,570; kamadi 43,200; ktools 44,000</t>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="O44" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C44,F44)),"","YES")</f>
-        <v>YES</v>
+        <v/>
       </c>
       <c r="P44" s="6" t="s">
         <v>55</v>
@@ -4542,7 +4542,7 @@
       </c>
       <c r="O45" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C45,F45)),"","YES")</f>
-        <v>YES</v>
+        <v/>
       </c>
       <c r="P45" s="6" t="s">
         <v>24</v>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="R45" s="7"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="n">
         <v>42</v>
       </c>
@@ -4603,7 +4603,7 @@
       </c>
       <c r="O46" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C46,F46)),"","YES")</f>
-        <v>YES</v>
+        <v/>
       </c>
       <c r="P46" s="6" t="s">
         <v>55</v>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="O57" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C57,F57)),"","YES")</f>
-        <v>YES</v>
+        <v/>
       </c>
       <c r="P57" s="6" t="s">
         <v>55</v>
@@ -7738,7 +7738,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="6" t="n">
         <v>97</v>
       </c>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="O98" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C98,F98)),"","YES")</f>
-        <v>YES</v>
+        <v/>
       </c>
       <c r="P98" s="6" t="s">
         <v>44</v>
@@ -15255,7 +15255,7 @@
       </c>
       <c r="O220" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C220,F220)),"","YES")</f>
-        <v>YES</v>
+        <v/>
       </c>
       <c r="P220" s="6" t="s">
         <v>55</v>
@@ -15627,7 +15627,7 @@
       </c>
       <c r="O226" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C226,F226)),"","YES")</f>
-        <v>YES</v>
+        <v/>
       </c>
       <c r="P226" s="6" t="s">
         <v>55</v>
@@ -15817,7 +15817,7 @@
       </c>
       <c r="B8" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!O6:O227,"YES")</f>
-        <v>127</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/quotes/PR-217-228/Quote_PR217_PR228_Rate_Check.xlsx
+++ b/quotes/PR-217-228/Quote_PR217_PR228_Rate_Check.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1241" uniqueCount="472">
   <si>
     <t xml:space="preserve">Zidane Corporation - Quote PR-217 &amp; PR-228: Brand + Buying Rate Check</t>
   </si>
@@ -99,21 +99,24 @@
     <t xml:space="preserve">Bosch / Industrial</t>
   </si>
   <si>
+    <t xml:space="preserve">V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolshub/ingcomart Permanent 4in 120; nasirnsons Rhodius 280</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STEEL NAIL 1-1/2" Taiwan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Licota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generic (Taiwan)</t>
+  </si>
+  <si>
     <t xml:space="preserve">E</t>
   </si>
   <si>
-    <t xml:space="preserve">Daraz/hardware mkt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STEEL NAIL 1-1/2" Taiwan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Licota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generic (Taiwan)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hardware mkt</t>
   </si>
   <si>
@@ -147,12 +150,15 @@
     <t xml:space="preserve">SAFETY HELMET (WHITE)</t>
   </si>
   <si>
+    <t xml:space="preserve">powerhouseexpress Total 730; toolsmart Ingco 1,440; local 500-750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAFETY GOOGLES</t>
+  </si>
+  <si>
     <t xml:space="preserve">Market</t>
   </si>
   <si>
-    <t xml:space="preserve">SAFETY GOOGLES</t>
-  </si>
-  <si>
     <t xml:space="preserve">7 DRAWER TOOL TROLLEY</t>
   </si>
   <si>
@@ -162,7 +168,7 @@
     <t xml:space="preserve">P</t>
   </si>
   <si>
-    <t xml:space="preserve">goldpeak PH Licota 7-drawer PHP26k + import; ktools Force 7-drawer</t>
+    <t xml:space="preserve">ktools Yato 7-drawer 211pc 315,000 / 6-drawer 177pc 220,000 (with tools); empty Licota est</t>
   </si>
   <si>
     <t xml:space="preserve">Empty ya tools ke saath? Confirm</t>
@@ -192,9 +198,6 @@
     <t xml:space="preserve">COMBINATION WRENCH 8 TO 32 (14 PCS SET)</t>
   </si>
   <si>
-    <t xml:space="preserve">V</t>
-  </si>
-  <si>
     <t xml:space="preserve">toolsmart Licota 14pc combo 25,660</t>
   </si>
   <si>
@@ -381,12 +384,15 @@
     <t xml:space="preserve">FLAT FILE 12"</t>
   </si>
   <si>
-    <t xml:space="preserve">Market (Licota files PK mein nahi)</t>
+    <t xml:space="preserve">zeeshanhardware Yato YT-6190 12in 1,750</t>
   </si>
   <si>
     <t xml:space="preserve">ROUNDE FILE 12"</t>
   </si>
   <si>
+    <t xml:space="preserve">zeeshanhardware Yato 12in file 1,750 (flat; round similar)</t>
+  </si>
+  <si>
     <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED WITH HOOK BRAKE 21</t>
   </si>
   <si>
@@ -483,6 +489,9 @@
     <t xml:space="preserve">ROUGH FILE SMOOTH 10"</t>
   </si>
   <si>
+    <t xml:space="preserve">zeeshanhardware Yato YT-6228 10in 1,350</t>
+  </si>
+  <si>
     <t xml:space="preserve">POLISH FILE SMOOTH 10"</t>
   </si>
   <si>
@@ -720,7 +729,7 @@
     <t xml:space="preserve">Industrial (AC/DC TIG 300A)</t>
   </si>
   <si>
-    <t xml:space="preserve">India ref INR 95k-146k; no PK listing</t>
+    <t xml:space="preserve">houseoftools.com.pk AC/DC TIG WACTA20 126,000 (amp n/a); hyundaipower TIG-200 AC/DC 86,500 - 300A est</t>
   </si>
   <si>
     <t xml:space="preserve">Model/brand confirm karo</t>
@@ -756,6 +765,9 @@
     <t xml:space="preserve">ARGON REGULATOR FLOW METER</t>
   </si>
   <si>
+    <t xml:space="preserve">aliweldinghouse.pk WM argon regulator 5,000-6,000</t>
+  </si>
+  <si>
     <t xml:space="preserve">ARGON GAS HOSE 06MM</t>
   </si>
   <si>
@@ -771,6 +783,12 @@
     <t xml:space="preserve">CUTTING DISC 125MM X 01MM</t>
   </si>
   <si>
+    <t xml:space="preserve">powerhouseexpress Total 5in metal cutting 270; ktools/toolshub 4in 75-120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aapka 130 kam hai - 125mm thin disc 150-270</t>
+  </si>
+  <si>
     <t xml:space="preserve">CUTTING DISC 230MM X 03MM</t>
   </si>
   <si>
@@ -837,6 +855,9 @@
     <t xml:space="preserve">PU COATED SAFETY GLOVES LEVEL 5 CUT RESISTA</t>
   </si>
   <si>
+    <t xml:space="preserve">mjstraders Safeyear 600; ktools Total HPPE 800-900; hacsons 1,000</t>
+  </si>
+  <si>
     <t xml:space="preserve">NITRILE SAFETY GLOOVES OIL RESISTANT</t>
   </si>
   <si>
@@ -963,10 +984,10 @@
     <t xml:space="preserve">Insize 3203-25A</t>
   </si>
   <si>
-    <t xml:space="preserve">kamadi Insize digital 3109-25A 14,900</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analog Insize sasta; digital chahiye to 14,900+</t>
+    <t xml:space="preserve">imsons Insize 3203-25A 4,815; kamadi 5,500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analog Insize; digital chahiye to ~15k+</t>
   </si>
   <si>
     <t xml:space="preserve">MICROMETER 25 TO 50MM</t>
@@ -975,6 +996,9 @@
     <t xml:space="preserve">Insize 3203-50A</t>
   </si>
   <si>
+    <t xml:space="preserve">imsons Insize 3203 series (4,815-9,625)</t>
+  </si>
+  <si>
     <t xml:space="preserve">MICROMETER 50 TO 75MM</t>
   </si>
   <si>
@@ -987,12 +1011,18 @@
     <t xml:space="preserve">Insize 3203-100A</t>
   </si>
   <si>
+    <t xml:space="preserve">imsons Insize 3203-100A 6,875</t>
+  </si>
+  <si>
     <t xml:space="preserve">MICROMETER 100 TO 125MM</t>
   </si>
   <si>
     <t xml:space="preserve">Insize 3203-125A</t>
   </si>
   <si>
+    <t xml:space="preserve">imsons Insize 3203-125A 8,750</t>
+  </si>
+  <si>
     <t xml:space="preserve">NEEDLE FILE (5PCS SET)</t>
   </si>
   <si>
@@ -1149,6 +1179,9 @@
     <t xml:space="preserve">Industrial (copper)</t>
   </si>
   <si>
+    <t xml:space="preserve">enontraders 95mm copper flexible ~3,600/m; thetoolsstore welding cable 580/m (size n/a)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Copper rate pe depend</t>
   </si>
   <si>
@@ -1158,10 +1191,13 @@
     <t xml:space="preserve">FULL BODY HARNESS BELT</t>
   </si>
   <si>
-    <t xml:space="preserve">Karam / 3M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Licota harness nahi banata</t>
+    <t xml:space="preserve">Toho (Taiwan)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mjstraders Toho MH106 3D 7,800; imsons Yamada 6,500; citex 5,800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Karam PK mein nahi; Toho Taiwan brand</t>
   </si>
   <si>
     <t xml:space="preserve">ANGLE GRINDER 9" BOSCH PRO STONE BONDED CU</t>
@@ -2100,7 +2136,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="n">
         <v>1</v>
       </c>
@@ -2120,14 +2156,14 @@
         <v>23</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>220</v>
+        <v>280</v>
       </c>
       <c r="I6" s="10" t="n">
         <f aca="false">IF(E6=0,0,(E6-H6)/E6)</f>
-        <v>0.323076923076923</v>
+        <v>0.138461538461538</v>
       </c>
       <c r="J6" s="6" t="str">
         <f aca="false">IF(E6&lt;G6,"LOSS",IF(E6&lt;H6*1.1,"THIN / RISK",IF(E6&gt;H6*1.8,"OVERPRICED?","OK")))</f>
@@ -2147,7 +2183,7 @@
       </c>
       <c r="N6" s="8" t="n">
         <f aca="false">D6*H6</f>
-        <v>6600</v>
+        <v>8400</v>
       </c>
       <c r="O6" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C6,F6)),"","YES")</f>
@@ -2215,13 +2251,13 @@
         <v>YES</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R7" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2229,7 +2265,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>27</v>
@@ -2241,7 +2277,7 @@
         <v>58500</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>45000</v>
@@ -2278,13 +2314,13 @@
         <v>YES</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R8" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2292,7 +2328,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>27</v>
@@ -2304,7 +2340,7 @@
         <v>715</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>350</v>
@@ -2341,10 +2377,10 @@
         <v>YES</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R9" s="7"/>
     </row>
@@ -2353,7 +2389,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>27</v>
@@ -2365,7 +2401,7 @@
         <v>41600</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G10" s="9" t="n">
         <v>32000</v>
@@ -2402,19 +2438,19 @@
         <v>YES</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="R10" s="7"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="n">
         <v>6</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>22</v>
@@ -2429,14 +2465,14 @@
         <v>22</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>600</v>
+        <v>730</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="I11" s="10" t="n">
         <f aca="false">IF(E11=0,0,(E11-H11)/E11)</f>
-        <v>0.18552036199095</v>
+        <v>0.0950226244343891</v>
       </c>
       <c r="J11" s="6" t="str">
         <f aca="false">IF(E11&lt;G11,"LOSS",IF(E11&lt;H11*1.1,"THIN / RISK",IF(E11&gt;H11*1.8,"OVERPRICED?","OK")))</f>
@@ -2444,7 +2480,7 @@
       </c>
       <c r="K11" s="8" t="n">
         <f aca="false">IF(J11="OVERPRICED?",ROUND(H11*1.35,-1),MAX(E11,ROUND(H11*(1+$E$3),-1)))</f>
-        <v>1105</v>
+        <v>1150</v>
       </c>
       <c r="L11" s="8" t="n">
         <f aca="false">D11*E11</f>
@@ -2452,11 +2488,11 @@
       </c>
       <c r="M11" s="8" t="n">
         <f aca="false">D11*K11</f>
-        <v>6630</v>
+        <v>6900</v>
       </c>
       <c r="N11" s="8" t="n">
         <f aca="false">D11*H11</f>
-        <v>5400</v>
+        <v>6000</v>
       </c>
       <c r="O11" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C11,F11)),"","YES")</f>
@@ -2466,7 +2502,7 @@
         <v>24</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R11" s="7"/>
     </row>
@@ -2475,7 +2511,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>22</v>
@@ -2524,10 +2560,10 @@
         <v/>
       </c>
       <c r="P12" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R12" s="7"/>
     </row>
@@ -2536,7 +2572,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>27</v>
@@ -2548,7 +2584,7 @@
         <v>161070</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G13" s="9" t="n">
         <v>150000</v>
@@ -2585,13 +2621,13 @@
         <v/>
       </c>
       <c r="P13" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="R13" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2599,7 +2635,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>27</v>
@@ -2648,10 +2684,10 @@
         <v/>
       </c>
       <c r="P14" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="R14" s="7"/>
     </row>
@@ -2660,7 +2696,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>27</v>
@@ -2709,10 +2745,10 @@
         <v/>
       </c>
       <c r="P15" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R15" s="7"/>
     </row>
@@ -2721,7 +2757,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>27</v>
@@ -2770,10 +2806,10 @@
         <v/>
       </c>
       <c r="P16" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="R16" s="7"/>
     </row>
@@ -2782,7 +2818,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>27</v>
@@ -2831,10 +2867,10 @@
         <v/>
       </c>
       <c r="P17" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="R17" s="7"/>
     </row>
@@ -2843,7 +2879,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>27</v>
@@ -2892,10 +2928,10 @@
         <v/>
       </c>
       <c r="P18" s="6" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="R18" s="7"/>
     </row>
@@ -2904,7 +2940,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>27</v>
@@ -2953,10 +2989,10 @@
         <v/>
       </c>
       <c r="P19" s="6" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="R19" s="7"/>
     </row>
@@ -2965,7 +3001,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>27</v>
@@ -3014,10 +3050,10 @@
         <v/>
       </c>
       <c r="P20" s="6" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R20" s="7"/>
     </row>
@@ -3026,7 +3062,7 @@
         <v>16</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>27</v>
@@ -3038,7 +3074,7 @@
         <v>8450</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G21" s="9" t="n">
         <v>6500</v>
@@ -3075,13 +3111,13 @@
         <v>YES</v>
       </c>
       <c r="P21" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q21" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R21" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3089,7 +3125,7 @@
         <v>17</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>27</v>
@@ -3138,10 +3174,10 @@
         <v/>
       </c>
       <c r="P22" s="6" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="Q22" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="R22" s="7"/>
     </row>
@@ -3150,7 +3186,7 @@
         <v>18</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>27</v>
@@ -3199,10 +3235,10 @@
         <v/>
       </c>
       <c r="P23" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q23" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R23" s="7"/>
     </row>
@@ -3211,7 +3247,7 @@
         <v>19</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>27</v>
@@ -3260,13 +3296,13 @@
         <v/>
       </c>
       <c r="P24" s="6" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="Q24" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="R24" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3274,7 +3310,7 @@
         <v>20</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>27</v>
@@ -3323,10 +3359,10 @@
         <v/>
       </c>
       <c r="P25" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q25" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="R25" s="7"/>
     </row>
@@ -3335,7 +3371,7 @@
         <v>21</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>27</v>
@@ -3384,10 +3420,10 @@
         <v/>
       </c>
       <c r="P26" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q26" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R26" s="7"/>
     </row>
@@ -3396,7 +3432,7 @@
         <v>22</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>27</v>
@@ -3445,10 +3481,10 @@
         <v/>
       </c>
       <c r="P27" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q27" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="R27" s="7"/>
     </row>
@@ -3457,7 +3493,7 @@
         <v>23</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>27</v>
@@ -3506,10 +3542,10 @@
         <v/>
       </c>
       <c r="P28" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q28" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="R28" s="7"/>
     </row>
@@ -3518,7 +3554,7 @@
         <v>24</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>27</v>
@@ -3567,10 +3603,10 @@
         <v/>
       </c>
       <c r="P29" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q29" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R29" s="7"/>
     </row>
@@ -3579,7 +3615,7 @@
         <v>25</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>27</v>
@@ -3628,10 +3664,10 @@
         <v/>
       </c>
       <c r="P30" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q30" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R30" s="7"/>
     </row>
@@ -3640,7 +3676,7 @@
         <v>26</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>27</v>
@@ -3689,10 +3725,10 @@
         <v/>
       </c>
       <c r="P31" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q31" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R31" s="7"/>
     </row>
@@ -3701,7 +3737,7 @@
         <v>27</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>27</v>
@@ -3750,10 +3786,10 @@
         <v/>
       </c>
       <c r="P32" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q32" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="R32" s="7"/>
     </row>
@@ -3762,7 +3798,7 @@
         <v>28</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>27</v>
@@ -3811,10 +3847,10 @@
         <v/>
       </c>
       <c r="P33" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q33" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="R33" s="7"/>
     </row>
@@ -3823,7 +3859,7 @@
         <v>30</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>27</v>
@@ -3872,10 +3908,10 @@
         <v/>
       </c>
       <c r="P34" s="6" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="Q34" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="R34" s="7"/>
     </row>
@@ -3884,7 +3920,7 @@
         <v>31</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>27</v>
@@ -3933,10 +3969,10 @@
         <v/>
       </c>
       <c r="P35" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q35" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="R35" s="7"/>
     </row>
@@ -3945,7 +3981,7 @@
         <v>32</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>27</v>
@@ -3994,10 +4030,10 @@
         <v/>
       </c>
       <c r="P36" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q36" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="R36" s="7"/>
     </row>
@@ -4006,7 +4042,7 @@
         <v>33</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>27</v>
@@ -4055,10 +4091,10 @@
         <v/>
       </c>
       <c r="P37" s="6" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="Q37" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="R37" s="7"/>
     </row>
@@ -4067,7 +4103,7 @@
         <v>34</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>27</v>
@@ -4116,10 +4152,10 @@
         <v/>
       </c>
       <c r="P38" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q38" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R38" s="7"/>
     </row>
@@ -4128,7 +4164,7 @@
         <v>35</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>27</v>
@@ -4177,10 +4213,10 @@
         <v/>
       </c>
       <c r="P39" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q39" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="R39" s="7"/>
     </row>
@@ -4189,7 +4225,7 @@
         <v>36</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>27</v>
@@ -4238,10 +4274,10 @@
         <v/>
       </c>
       <c r="P40" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q40" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="R40" s="7"/>
     </row>
@@ -4250,7 +4286,7 @@
         <v>37</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>27</v>
@@ -4299,10 +4335,10 @@
         <v/>
       </c>
       <c r="P41" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q41" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="R41" s="7"/>
     </row>
@@ -4311,7 +4347,7 @@
         <v>38</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>27</v>
@@ -4360,10 +4396,10 @@
         <v/>
       </c>
       <c r="P42" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q42" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="R42" s="7"/>
     </row>
@@ -4372,7 +4408,7 @@
         <v>39</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>27</v>
@@ -4421,10 +4457,10 @@
         <v/>
       </c>
       <c r="P43" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q43" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="R43" s="7"/>
     </row>
@@ -4433,10 +4469,10 @@
         <v>40</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D44" s="6" t="n">
         <v>3</v>
@@ -4445,7 +4481,7 @@
         <v>79300</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G44" s="9" t="n">
         <v>45000</v>
@@ -4482,13 +4518,13 @@
         <v/>
       </c>
       <c r="P44" s="6" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="Q44" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R44" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4496,10 +4532,10 @@
         <v>41</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>3</v>
@@ -4508,7 +4544,7 @@
         <v>128700</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G45" s="9" t="n">
         <v>95000</v>
@@ -4545,10 +4581,10 @@
         <v/>
       </c>
       <c r="P45" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q45" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="R45" s="7"/>
     </row>
@@ -4557,10 +4593,10 @@
         <v>42</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D46" s="6" t="n">
         <v>2</v>
@@ -4569,7 +4605,7 @@
         <v>106600</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G46" s="9" t="n">
         <v>70000</v>
@@ -4606,13 +4642,13 @@
         <v/>
       </c>
       <c r="P46" s="6" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="Q46" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="R46" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4620,7 +4656,7 @@
         <v>43</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>27</v>
@@ -4669,10 +4705,10 @@
         <v/>
       </c>
       <c r="P47" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q47" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="R47" s="7"/>
     </row>
@@ -4681,7 +4717,7 @@
         <v>44</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>27</v>
@@ -4693,17 +4729,17 @@
         <v>1950</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>1700</v>
+        <v>1750</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>2300</v>
+        <v>2000</v>
       </c>
       <c r="I48" s="10" t="n">
         <f aca="false">IF(E48=0,0,(E48-H48)/E48)</f>
-        <v>-0.17948717948718</v>
+        <v>-0.0256410256410256</v>
       </c>
       <c r="J48" s="6" t="str">
         <f aca="false">IF(E48&lt;G48,"LOSS",IF(E48&lt;H48*1.1,"THIN / RISK",IF(E48&gt;H48*1.8,"OVERPRICED?","OK")))</f>
@@ -4711,7 +4747,7 @@
       </c>
       <c r="K48" s="8" t="n">
         <f aca="false">IF(J48="OVERPRICED?",ROUND(H48*1.35,-1),MAX(E48,ROUND(H48*(1+$E$3),-1)))</f>
-        <v>2650</v>
+        <v>2300</v>
       </c>
       <c r="L48" s="8" t="n">
         <f aca="false">D48*E48</f>
@@ -4719,11 +4755,11 @@
       </c>
       <c r="M48" s="8" t="n">
         <f aca="false">D48*K48</f>
-        <v>10600</v>
+        <v>9200</v>
       </c>
       <c r="N48" s="8" t="n">
         <f aca="false">D48*H48</f>
-        <v>9200</v>
+        <v>8000</v>
       </c>
       <c r="O48" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C48,F48)),"","YES")</f>
@@ -4733,16 +4769,16 @@
         <v>24</v>
       </c>
       <c r="Q48" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="R48" s="7"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="n">
         <v>45</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>27</v>
@@ -4754,25 +4790,25 @@
         <v>2210</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>1700</v>
+        <v>1750</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>2300</v>
+        <v>2000</v>
       </c>
       <c r="I49" s="10" t="n">
         <f aca="false">IF(E49=0,0,(E49-H49)/E49)</f>
-        <v>-0.0407239819004525</v>
+        <v>0.0950226244343891</v>
       </c>
       <c r="J49" s="6" t="str">
         <f aca="false">IF(E49&lt;G49,"LOSS",IF(E49&lt;H49*1.1,"THIN / RISK",IF(E49&gt;H49*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>OK</v>
       </c>
       <c r="K49" s="8" t="n">
         <f aca="false">IF(J49="OVERPRICED?",ROUND(H49*1.35,-1),MAX(E49,ROUND(H49*(1+$E$3),-1)))</f>
-        <v>2650</v>
+        <v>2300</v>
       </c>
       <c r="L49" s="8" t="n">
         <f aca="false">D49*E49</f>
@@ -4780,21 +4816,21 @@
       </c>
       <c r="M49" s="8" t="n">
         <f aca="false">D49*K49</f>
-        <v>10600</v>
+        <v>9200</v>
       </c>
       <c r="N49" s="8" t="n">
         <f aca="false">D49*H49</f>
-        <v>9200</v>
+        <v>8000</v>
       </c>
       <c r="O49" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C49,F49)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P49" s="6" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="Q49" s="7" t="s">
-        <v>40</v>
+        <v>121</v>
       </c>
       <c r="R49" s="7"/>
     </row>
@@ -4803,7 +4839,7 @@
         <v>47</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>27</v>
@@ -4852,10 +4888,10 @@
         <v/>
       </c>
       <c r="P50" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q50" s="7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="R50" s="7"/>
     </row>
@@ -4864,7 +4900,7 @@
         <v>48</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>27</v>
@@ -4913,10 +4949,10 @@
         <v/>
       </c>
       <c r="P51" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q51" s="7" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="R51" s="7"/>
     </row>
@@ -4925,7 +4961,7 @@
         <v>49</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>27</v>
@@ -4974,10 +5010,10 @@
         <v/>
       </c>
       <c r="P52" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q52" s="7" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="R52" s="7"/>
     </row>
@@ -4986,7 +5022,7 @@
         <v>50</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>27</v>
@@ -5035,10 +5071,10 @@
         <v/>
       </c>
       <c r="P53" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q53" s="7" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="R53" s="7"/>
     </row>
@@ -5047,7 +5083,7 @@
         <v>51</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>27</v>
@@ -5096,10 +5132,10 @@
         <v/>
       </c>
       <c r="P54" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q54" s="7" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="R54" s="7"/>
     </row>
@@ -5108,7 +5144,7 @@
         <v>52</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>27</v>
@@ -5157,10 +5193,10 @@
         <v/>
       </c>
       <c r="P55" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q55" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="R55" s="7"/>
     </row>
@@ -5169,7 +5205,7 @@
         <v>53</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>27</v>
@@ -5218,10 +5254,10 @@
         <v/>
       </c>
       <c r="P56" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q56" s="7" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="R56" s="7"/>
     </row>
@@ -5230,10 +5266,10 @@
         <v>54</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D57" s="6" t="n">
         <v>2</v>
@@ -5242,7 +5278,7 @@
         <v>400946</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G57" s="9" t="n">
         <v>49000</v>
@@ -5279,13 +5315,13 @@
         <v/>
       </c>
       <c r="P57" s="6" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="Q57" s="7" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="R57" s="7" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5293,7 +5329,7 @@
         <v>55</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>27</v>
@@ -5305,7 +5341,7 @@
         <v>15600</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G58" s="9" t="n">
         <v>12000</v>
@@ -5342,13 +5378,13 @@
         <v>YES</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q58" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R58" s="7" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5356,7 +5392,7 @@
         <v>56</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>27</v>
@@ -5405,10 +5441,10 @@
         <v/>
       </c>
       <c r="P59" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q59" s="7" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="R59" s="7"/>
     </row>
@@ -5417,7 +5453,7 @@
         <v>57</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>27</v>
@@ -5466,10 +5502,10 @@
         <v/>
       </c>
       <c r="P60" s="6" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="Q60" s="7" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="R60" s="7"/>
     </row>
@@ -5478,7 +5514,7 @@
         <v>58</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>27</v>
@@ -5527,10 +5563,10 @@
         <v/>
       </c>
       <c r="P61" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q61" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R61" s="7"/>
     </row>
@@ -5539,7 +5575,7 @@
         <v>59</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>27</v>
@@ -5588,10 +5624,10 @@
         <v/>
       </c>
       <c r="P62" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q62" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R62" s="7"/>
     </row>
@@ -5600,7 +5636,7 @@
         <v>60</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>27</v>
@@ -5612,7 +5648,7 @@
         <v>9100</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G63" s="9" t="n">
         <v>8000</v>
@@ -5649,10 +5685,10 @@
         <v>YES</v>
       </c>
       <c r="P63" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q63" s="7" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="R63" s="7"/>
     </row>
@@ -5661,7 +5697,7 @@
         <v>61</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>27</v>
@@ -5673,7 +5709,7 @@
         <v>5850</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G64" s="9" t="n">
         <v>5000</v>
@@ -5710,10 +5746,10 @@
         <v>YES</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q64" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R64" s="7"/>
     </row>
@@ -5722,7 +5758,7 @@
         <v>62</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>27</v>
@@ -5771,10 +5807,10 @@
         <v/>
       </c>
       <c r="P65" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q65" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R65" s="7"/>
     </row>
@@ -5783,7 +5819,7 @@
         <v>63</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>27</v>
@@ -5832,10 +5868,10 @@
         <v/>
       </c>
       <c r="P66" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q66" s="7" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="R66" s="7"/>
     </row>
@@ -5844,7 +5880,7 @@
         <v>64</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>27</v>
@@ -5856,17 +5892,17 @@
         <v>1560</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>1300</v>
+        <v>1350</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>1800</v>
+        <v>1600</v>
       </c>
       <c r="I67" s="10" t="n">
         <f aca="false">IF(E67=0,0,(E67-H67)/E67)</f>
-        <v>-0.153846153846154</v>
+        <v>-0.0256410256410256</v>
       </c>
       <c r="J67" s="6" t="str">
         <f aca="false">IF(E67&lt;G67,"LOSS",IF(E67&lt;H67*1.1,"THIN / RISK",IF(E67&gt;H67*1.8,"OVERPRICED?","OK")))</f>
@@ -5874,7 +5910,7 @@
       </c>
       <c r="K67" s="8" t="n">
         <f aca="false">IF(J67="OVERPRICED?",ROUND(H67*1.35,-1),MAX(E67,ROUND(H67*(1+$E$3),-1)))</f>
-        <v>2070</v>
+        <v>1840</v>
       </c>
       <c r="L67" s="8" t="n">
         <f aca="false">D67*E67</f>
@@ -5882,11 +5918,11 @@
       </c>
       <c r="M67" s="8" t="n">
         <f aca="false">D67*K67</f>
-        <v>6210</v>
+        <v>5520</v>
       </c>
       <c r="N67" s="8" t="n">
         <f aca="false">D67*H67</f>
-        <v>5400</v>
+        <v>4800</v>
       </c>
       <c r="O67" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C67,F67)),"","YES")</f>
@@ -5896,7 +5932,7 @@
         <v>24</v>
       </c>
       <c r="Q67" s="7" t="s">
-        <v>40</v>
+        <v>154</v>
       </c>
       <c r="R67" s="7"/>
     </row>
@@ -5905,7 +5941,7 @@
         <v>65</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>27</v>
@@ -5917,17 +5953,17 @@
         <v>1560</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>1300</v>
+        <v>1350</v>
       </c>
       <c r="H68" s="9" t="n">
-        <v>1800</v>
+        <v>1600</v>
       </c>
       <c r="I68" s="10" t="n">
         <f aca="false">IF(E68=0,0,(E68-H68)/E68)</f>
-        <v>-0.153846153846154</v>
+        <v>-0.0256410256410256</v>
       </c>
       <c r="J68" s="6" t="str">
         <f aca="false">IF(E68&lt;G68,"LOSS",IF(E68&lt;H68*1.1,"THIN / RISK",IF(E68&gt;H68*1.8,"OVERPRICED?","OK")))</f>
@@ -5935,7 +5971,7 @@
       </c>
       <c r="K68" s="8" t="n">
         <f aca="false">IF(J68="OVERPRICED?",ROUND(H68*1.35,-1),MAX(E68,ROUND(H68*(1+$E$3),-1)))</f>
-        <v>2070</v>
+        <v>1840</v>
       </c>
       <c r="L68" s="8" t="n">
         <f aca="false">D68*E68</f>
@@ -5943,11 +5979,11 @@
       </c>
       <c r="M68" s="8" t="n">
         <f aca="false">D68*K68</f>
-        <v>6210</v>
+        <v>5520</v>
       </c>
       <c r="N68" s="8" t="n">
         <f aca="false">D68*H68</f>
-        <v>5400</v>
+        <v>4800</v>
       </c>
       <c r="O68" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C68,F68)),"","YES")</f>
@@ -5957,7 +5993,7 @@
         <v>24</v>
       </c>
       <c r="Q68" s="7" t="s">
-        <v>40</v>
+        <v>154</v>
       </c>
       <c r="R68" s="7"/>
     </row>
@@ -5966,7 +6002,7 @@
         <v>66</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>27</v>
@@ -5978,7 +6014,7 @@
         <v>11700</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G69" s="9" t="n">
         <v>14000</v>
@@ -6015,13 +6051,13 @@
         <v>YES</v>
       </c>
       <c r="P69" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q69" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R69" s="7" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6029,7 +6065,7 @@
         <v>67</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>27</v>
@@ -6041,7 +6077,7 @@
         <v>9750</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G70" s="9" t="n">
         <v>12000</v>
@@ -6078,10 +6114,10 @@
         <v>YES</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q70" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R70" s="7"/>
     </row>
@@ -6090,7 +6126,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>27</v>
@@ -6102,7 +6138,7 @@
         <v>23400</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="G71" s="9" t="n">
         <v>15000</v>
@@ -6139,10 +6175,10 @@
         <v>YES</v>
       </c>
       <c r="P71" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q71" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R71" s="7"/>
     </row>
@@ -6151,7 +6187,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>27</v>
@@ -6163,7 +6199,7 @@
         <v>32500</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="G72" s="9" t="n">
         <v>25000</v>
@@ -6200,10 +6236,10 @@
         <v>YES</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q72" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R72" s="7"/>
     </row>
@@ -6212,7 +6248,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>27</v>
@@ -6224,7 +6260,7 @@
         <v>1105</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G73" s="9" t="n">
         <v>800</v>
@@ -6261,10 +6297,10 @@
         <v>YES</v>
       </c>
       <c r="P73" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q73" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R73" s="7"/>
     </row>
@@ -6273,7 +6309,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>27</v>
@@ -6285,7 +6321,7 @@
         <v>45500</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G74" s="9" t="n">
         <v>25000</v>
@@ -6322,10 +6358,10 @@
         <v>YES</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q74" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R74" s="7"/>
     </row>
@@ -6334,7 +6370,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>27</v>
@@ -6346,7 +6382,7 @@
         <v>23400</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G75" s="9" t="n">
         <v>12000</v>
@@ -6383,10 +6419,10 @@
         <v>YES</v>
       </c>
       <c r="P75" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q75" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="R75" s="7"/>
     </row>
@@ -6395,7 +6431,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>27</v>
@@ -6407,7 +6443,7 @@
         <v>1950</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G76" s="9" t="n">
         <v>2500</v>
@@ -6444,13 +6480,13 @@
         <v>YES</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q76" s="7" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="R76" s="7" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6458,7 +6494,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>27</v>
@@ -6470,7 +6506,7 @@
         <v>2080</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G77" s="9" t="n">
         <v>2700</v>
@@ -6507,10 +6543,10 @@
         <v>YES</v>
       </c>
       <c r="P77" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q77" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R77" s="7"/>
     </row>
@@ -6519,7 +6555,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>27</v>
@@ -6531,7 +6567,7 @@
         <v>2210</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G78" s="9" t="n">
         <v>2800</v>
@@ -6568,10 +6604,10 @@
         <v>YES</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q78" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R78" s="7"/>
     </row>
@@ -6580,7 +6616,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>27</v>
@@ -6592,7 +6628,7 @@
         <v>2340</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G79" s="9" t="n">
         <v>3000</v>
@@ -6629,10 +6665,10 @@
         <v>YES</v>
       </c>
       <c r="P79" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q79" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R79" s="7"/>
     </row>
@@ -6641,7 +6677,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>27</v>
@@ -6653,7 +6689,7 @@
         <v>2470</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G80" s="9" t="n">
         <v>3100</v>
@@ -6690,10 +6726,10 @@
         <v>YES</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q80" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R80" s="7"/>
     </row>
@@ -6702,7 +6738,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>27</v>
@@ -6714,7 +6750,7 @@
         <v>2600</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G81" s="9" t="n">
         <v>3300</v>
@@ -6751,10 +6787,10 @@
         <v>YES</v>
       </c>
       <c r="P81" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q81" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R81" s="7"/>
     </row>
@@ -6763,7 +6799,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>27</v>
@@ -6775,7 +6811,7 @@
         <v>2730</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G82" s="9" t="n">
         <v>3500</v>
@@ -6812,10 +6848,10 @@
         <v>YES</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q82" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R82" s="7"/>
     </row>
@@ -6824,7 +6860,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>27</v>
@@ -6836,7 +6872,7 @@
         <v>3250</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G83" s="9" t="n">
         <v>4000</v>
@@ -6873,10 +6909,10 @@
         <v>YES</v>
       </c>
       <c r="P83" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q83" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R83" s="7"/>
     </row>
@@ -6885,7 +6921,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>27</v>
@@ -6897,7 +6933,7 @@
         <v>4160</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G84" s="9" t="n">
         <v>5000</v>
@@ -6934,10 +6970,10 @@
         <v>YES</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q84" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R84" s="7"/>
     </row>
@@ -6946,7 +6982,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>27</v>
@@ -6958,7 +6994,7 @@
         <v>5850</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G85" s="9" t="n">
         <v>6500</v>
@@ -6995,10 +7031,10 @@
         <v>YES</v>
       </c>
       <c r="P85" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q85" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R85" s="7"/>
     </row>
@@ -7007,7 +7043,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>27</v>
@@ -7019,7 +7055,7 @@
         <v>8450</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G86" s="9" t="n">
         <v>9500</v>
@@ -7056,10 +7092,10 @@
         <v>YES</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q86" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R86" s="7"/>
     </row>
@@ -7068,7 +7104,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>27</v>
@@ -7080,7 +7116,7 @@
         <v>9750</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G87" s="9" t="n">
         <v>11000</v>
@@ -7117,10 +7153,10 @@
         <v>YES</v>
       </c>
       <c r="P87" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q87" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R87" s="7"/>
     </row>
@@ -7129,7 +7165,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>27</v>
@@ -7141,7 +7177,7 @@
         <v>11700</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G88" s="9" t="n">
         <v>13500</v>
@@ -7178,10 +7214,10 @@
         <v>YES</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q88" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R88" s="7"/>
     </row>
@@ -7190,7 +7226,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>27</v>
@@ -7202,7 +7238,7 @@
         <v>4550</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G89" s="9" t="n">
         <v>3500</v>
@@ -7239,10 +7275,10 @@
         <v>YES</v>
       </c>
       <c r="P89" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q89" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R89" s="7"/>
     </row>
@@ -7251,7 +7287,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>27</v>
@@ -7263,7 +7299,7 @@
         <v>5850</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G90" s="9" t="n">
         <v>4500</v>
@@ -7300,10 +7336,10 @@
         <v>YES</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q90" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R90" s="7"/>
     </row>
@@ -7312,7 +7348,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>27</v>
@@ -7324,7 +7360,7 @@
         <v>7150</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G91" s="9" t="n">
         <v>5500</v>
@@ -7361,10 +7397,10 @@
         <v>YES</v>
       </c>
       <c r="P91" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q91" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R91" s="7"/>
     </row>
@@ -7373,7 +7409,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>27</v>
@@ -7385,7 +7421,7 @@
         <v>2340</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G92" s="9" t="n">
         <v>2500</v>
@@ -7422,10 +7458,10 @@
         <v>YES</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q92" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R92" s="7"/>
     </row>
@@ -7434,7 +7470,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>27</v>
@@ -7446,7 +7482,7 @@
         <v>2860</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G93" s="9" t="n">
         <v>3000</v>
@@ -7483,10 +7519,10 @@
         <v>YES</v>
       </c>
       <c r="P93" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q93" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R93" s="7"/>
     </row>
@@ -7495,10 +7531,10 @@
         <v>93</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D94" s="6" t="n">
         <v>2</v>
@@ -7507,7 +7543,7 @@
         <v>25350</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G94" s="9" t="n">
         <v>15800</v>
@@ -7544,10 +7580,10 @@
         <v/>
       </c>
       <c r="P94" s="6" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="Q94" s="7" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="R94" s="7"/>
     </row>
@@ -7556,10 +7592,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D95" s="6" t="n">
         <v>3</v>
@@ -7568,7 +7604,7 @@
         <v>8138</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="G95" s="9" t="n">
         <v>15800</v>
@@ -7605,13 +7641,13 @@
         <v/>
       </c>
       <c r="P95" s="6" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="Q95" s="7" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="R95" s="7" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7619,10 +7655,10 @@
         <v>95</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D96" s="6" t="n">
         <v>3</v>
@@ -7631,7 +7667,7 @@
         <v>6370</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="G96" s="9" t="n">
         <v>7928</v>
@@ -7668,10 +7704,10 @@
         <v/>
       </c>
       <c r="P96" s="6" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="Q96" s="7" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="R96" s="7"/>
     </row>
@@ -7680,7 +7716,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>27</v>
@@ -7692,7 +7728,7 @@
         <v>14950</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="G97" s="9" t="n">
         <v>15000</v>
@@ -7729,13 +7765,13 @@
         <v>YES</v>
       </c>
       <c r="P97" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q97" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R97" s="7" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7743,10 +7779,10 @@
         <v>97</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D98" s="6" t="n">
         <v>2</v>
@@ -7755,7 +7791,7 @@
         <v>286000</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="G98" s="9" t="n">
         <v>110000</v>
@@ -7792,13 +7828,13 @@
         <v/>
       </c>
       <c r="P98" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q98" s="7" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="R98" s="7" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7806,10 +7842,10 @@
         <v>98</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D99" s="6" t="n">
         <v>1</v>
@@ -7818,7 +7854,7 @@
         <v>15600</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="G99" s="9" t="n">
         <v>12000</v>
@@ -7855,10 +7891,10 @@
         <v/>
       </c>
       <c r="P99" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q99" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R99" s="7"/>
     </row>
@@ -7867,7 +7903,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>27</v>
@@ -7879,7 +7915,7 @@
         <v>11050</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G100" s="9" t="n">
         <v>8000</v>
@@ -7916,13 +7952,13 @@
         <v>YES</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q100" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R100" s="7" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7930,7 +7966,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>27</v>
@@ -7942,7 +7978,7 @@
         <v>9100</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G101" s="9" t="n">
         <v>6500</v>
@@ -7979,10 +8015,10 @@
         <v>YES</v>
       </c>
       <c r="P101" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q101" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R101" s="7"/>
     </row>
@@ -7991,7 +8027,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>27</v>
@@ -8003,7 +8039,7 @@
         <v>7150</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G102" s="9" t="n">
         <v>5500</v>
@@ -8040,10 +8076,10 @@
         <v>YES</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q102" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R102" s="7"/>
     </row>
@@ -8052,7 +8088,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>27</v>
@@ -8064,7 +8100,7 @@
         <v>5850</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G103" s="9" t="n">
         <v>4500</v>
@@ -8101,10 +8137,10 @@
         <v>YES</v>
       </c>
       <c r="P103" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q103" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R103" s="7"/>
     </row>
@@ -8113,7 +8149,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>22</v>
@@ -8162,10 +8198,10 @@
         <v/>
       </c>
       <c r="P104" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q104" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R104" s="7"/>
     </row>
@@ -8174,7 +8210,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>22</v>
@@ -8223,10 +8259,10 @@
         <v/>
       </c>
       <c r="P105" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q105" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R105" s="7"/>
     </row>
@@ -8235,7 +8271,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>22</v>
@@ -8284,10 +8320,10 @@
         <v/>
       </c>
       <c r="P106" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q106" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R106" s="7"/>
     </row>
@@ -8296,7 +8332,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>27</v>
@@ -8308,7 +8344,7 @@
         <v>3640</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G107" s="9" t="n">
         <v>2000</v>
@@ -8345,10 +8381,10 @@
         <v>YES</v>
       </c>
       <c r="P107" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q107" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R107" s="7"/>
     </row>
@@ -8357,7 +8393,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>27</v>
@@ -8369,7 +8405,7 @@
         <v>6760</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G108" s="9" t="n">
         <v>4500</v>
@@ -8406,10 +8442,10 @@
         <v>YES</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q108" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R108" s="7"/>
     </row>
@@ -8418,7 +8454,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>27</v>
@@ -8430,7 +8466,7 @@
         <v>4550</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G109" s="9" t="n">
         <v>3500</v>
@@ -8467,10 +8503,10 @@
         <v>YES</v>
       </c>
       <c r="P109" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q109" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R109" s="7"/>
     </row>
@@ -8479,7 +8515,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>27</v>
@@ -8491,7 +8527,7 @@
         <v>2340</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G110" s="9" t="n">
         <v>1800</v>
@@ -8528,10 +8564,10 @@
         <v>YES</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q110" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R110" s="7"/>
     </row>
@@ -8540,7 +8576,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>27</v>
@@ -8552,7 +8588,7 @@
         <v>1820</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="G111" s="9" t="n">
         <v>2000</v>
@@ -8589,10 +8625,10 @@
         <v>YES</v>
       </c>
       <c r="P111" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q111" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R111" s="7"/>
     </row>
@@ -8601,7 +8637,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>27</v>
@@ -8613,7 +8649,7 @@
         <v>2860</v>
       </c>
       <c r="F112" s="7" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="G112" s="9" t="n">
         <v>4000</v>
@@ -8650,10 +8686,10 @@
         <v>YES</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q112" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R112" s="7"/>
     </row>
@@ -8662,7 +8698,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>27</v>
@@ -8674,7 +8710,7 @@
         <v>12350</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G113" s="9" t="n">
         <v>8000</v>
@@ -8711,13 +8747,13 @@
         <v>YES</v>
       </c>
       <c r="P113" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q113" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R113" s="7" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8725,7 +8761,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>27</v>
@@ -8774,10 +8810,10 @@
         <v>YES</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q114" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R114" s="7"/>
     </row>
@@ -8786,7 +8822,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>27</v>
@@ -8835,10 +8871,10 @@
         <v>YES</v>
       </c>
       <c r="P115" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q115" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R115" s="7"/>
     </row>
@@ -8847,7 +8883,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>22</v>
@@ -8896,10 +8932,10 @@
         <v/>
       </c>
       <c r="P116" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q116" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R116" s="7"/>
     </row>
@@ -8908,7 +8944,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>27</v>
@@ -8957,10 +8993,10 @@
         <v>YES</v>
       </c>
       <c r="P117" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q117" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R117" s="7"/>
     </row>
@@ -8969,7 +9005,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>22</v>
@@ -9018,10 +9054,10 @@
         <v/>
       </c>
       <c r="P118" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q118" s="7" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="R118" s="7"/>
     </row>
@@ -9030,7 +9066,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>22</v>
@@ -9079,10 +9115,10 @@
         <v/>
       </c>
       <c r="P119" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q119" s="7" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="R119" s="7"/>
     </row>
@@ -9091,7 +9127,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>27</v>
@@ -9140,10 +9176,10 @@
         <v>YES</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q120" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R120" s="7"/>
     </row>
@@ -9152,7 +9188,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>22</v>
@@ -9201,10 +9237,10 @@
         <v/>
       </c>
       <c r="P121" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q121" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R121" s="7"/>
     </row>
@@ -9213,7 +9249,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>22</v>
@@ -9262,19 +9298,19 @@
         <v/>
       </c>
       <c r="P122" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q122" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R122" s="7"/>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="6" t="n">
         <v>122</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>22</v>
@@ -9286,7 +9322,7 @@
         <v>357500</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="G123" s="9" t="n">
         <v>200000</v>
@@ -9323,13 +9359,13 @@
         <v/>
       </c>
       <c r="P123" s="6" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="Q123" s="7" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="R123" s="7" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9337,7 +9373,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C124" s="6" t="s">
         <v>22</v>
@@ -9386,10 +9422,10 @@
         <v/>
       </c>
       <c r="P124" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q124" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R124" s="7"/>
     </row>
@@ -9398,7 +9434,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>22</v>
@@ -9447,10 +9483,10 @@
         <v/>
       </c>
       <c r="P125" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q125" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R125" s="7"/>
     </row>
@@ -9459,7 +9495,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>22</v>
@@ -9508,10 +9544,10 @@
         <v/>
       </c>
       <c r="P126" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q126" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R126" s="7"/>
     </row>
@@ -9520,7 +9556,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>22</v>
@@ -9569,10 +9605,10 @@
         <v/>
       </c>
       <c r="P127" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q127" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R127" s="7"/>
     </row>
@@ -9581,7 +9617,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>22</v>
@@ -9630,10 +9666,10 @@
         <v/>
       </c>
       <c r="P128" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q128" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R128" s="7"/>
     </row>
@@ -9642,7 +9678,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>22</v>
@@ -9691,10 +9727,10 @@
         <v/>
       </c>
       <c r="P129" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q129" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R129" s="7"/>
     </row>
@@ -9703,7 +9739,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>22</v>
@@ -9752,10 +9788,10 @@
         <v/>
       </c>
       <c r="P130" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q130" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R130" s="7"/>
     </row>
@@ -9764,7 +9800,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>22</v>
@@ -9813,10 +9849,10 @@
         <v/>
       </c>
       <c r="P131" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q131" s="7" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="R131" s="7"/>
     </row>
@@ -9825,7 +9861,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>22</v>
@@ -9843,11 +9879,11 @@
         <v>5000</v>
       </c>
       <c r="H132" s="9" t="n">
-        <v>7000</v>
+        <v>6000</v>
       </c>
       <c r="I132" s="10" t="n">
         <f aca="false">IF(E132=0,0,(E132-H132)/E132)</f>
-        <v>0.102564102564103</v>
+        <v>0.230769230769231</v>
       </c>
       <c r="J132" s="6" t="str">
         <f aca="false">IF(E132&lt;G132,"LOSS",IF(E132&lt;H132*1.1,"THIN / RISK",IF(E132&gt;H132*1.8,"OVERPRICED?","OK")))</f>
@@ -9855,7 +9891,7 @@
       </c>
       <c r="K132" s="8" t="n">
         <f aca="false">IF(J132="OVERPRICED?",ROUND(H132*1.35,-1),MAX(E132,ROUND(H132*(1+$E$3),-1)))</f>
-        <v>8050</v>
+        <v>7800</v>
       </c>
       <c r="L132" s="8" t="n">
         <f aca="false">D132*E132</f>
@@ -9863,11 +9899,11 @@
       </c>
       <c r="M132" s="8" t="n">
         <f aca="false">D132*K132</f>
-        <v>16100</v>
+        <v>15600</v>
       </c>
       <c r="N132" s="8" t="n">
         <f aca="false">D132*H132</f>
-        <v>14000</v>
+        <v>12000</v>
       </c>
       <c r="O132" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C132,F132)),"","YES")</f>
@@ -9877,7 +9913,7 @@
         <v>24</v>
       </c>
       <c r="Q132" s="7" t="s">
-        <v>40</v>
+        <v>246</v>
       </c>
       <c r="R132" s="7"/>
     </row>
@@ -9886,7 +9922,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="7" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>22</v>
@@ -9935,10 +9971,10 @@
         <v/>
       </c>
       <c r="P133" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q133" s="7" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="R133" s="7"/>
     </row>
@@ -9947,7 +9983,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>27</v>
@@ -9996,10 +10032,10 @@
         <v>YES</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q134" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R134" s="7"/>
     </row>
@@ -10008,7 +10044,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>22</v>
@@ -10057,10 +10093,10 @@
         <v/>
       </c>
       <c r="P135" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q135" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R135" s="7"/>
     </row>
@@ -10069,7 +10105,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="7" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C136" s="6" t="s">
         <v>22</v>
@@ -10118,19 +10154,19 @@
         <v/>
       </c>
       <c r="P136" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q136" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R136" s="7"/>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="6" t="n">
         <v>136</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="C137" s="6" t="s">
         <v>22</v>
@@ -10145,22 +10181,22 @@
         <v>22</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="H137" s="9" t="n">
-        <v>120</v>
+        <v>270</v>
       </c>
       <c r="I137" s="10" t="n">
         <f aca="false">IF(E137=0,0,(E137-H137)/E137)</f>
-        <v>0.0769230769230769</v>
+        <v>-1.07692307692308</v>
       </c>
       <c r="J137" s="6" t="str">
         <f aca="false">IF(E137&lt;G137,"LOSS",IF(E137&lt;H137*1.1,"THIN / RISK",IF(E137&gt;H137*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>LOSS</v>
       </c>
       <c r="K137" s="8" t="n">
         <f aca="false">IF(J137="OVERPRICED?",ROUND(H137*1.35,-1),MAX(E137,ROUND(H137*(1+$E$3),-1)))</f>
-        <v>140</v>
+        <v>310</v>
       </c>
       <c r="L137" s="8" t="n">
         <f aca="false">D137*E137</f>
@@ -10168,30 +10204,32 @@
       </c>
       <c r="M137" s="8" t="n">
         <f aca="false">D137*K137</f>
-        <v>70000</v>
+        <v>155000</v>
       </c>
       <c r="N137" s="8" t="n">
         <f aca="false">D137*H137</f>
-        <v>60000</v>
+        <v>135000</v>
       </c>
       <c r="O137" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C137,F137)),"","YES")</f>
         <v/>
       </c>
       <c r="P137" s="6" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="Q137" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="R137" s="7"/>
+        <v>252</v>
+      </c>
+      <c r="R137" s="7" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="6" t="n">
         <v>138</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="C138" s="6" t="s">
         <v>22</v>
@@ -10240,10 +10278,10 @@
         <v/>
       </c>
       <c r="P138" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q138" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R138" s="7"/>
     </row>
@@ -10252,7 +10290,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="7" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="C139" s="6" t="s">
         <v>27</v>
@@ -10301,10 +10339,10 @@
         <v>YES</v>
       </c>
       <c r="P139" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q139" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R139" s="7"/>
     </row>
@@ -10313,7 +10351,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="7" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C140" s="6" t="s">
         <v>22</v>
@@ -10362,10 +10400,10 @@
         <v/>
       </c>
       <c r="P140" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q140" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R140" s="7"/>
     </row>
@@ -10374,7 +10412,7 @@
         <v>142</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="C141" s="6" t="s">
         <v>22</v>
@@ -10386,7 +10424,7 @@
         <v>7150</v>
       </c>
       <c r="F141" s="7" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="G141" s="9" t="n">
         <v>5000</v>
@@ -10423,10 +10461,10 @@
         <v/>
       </c>
       <c r="P141" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q141" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R141" s="7"/>
     </row>
@@ -10435,7 +10473,7 @@
         <v>143</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="C142" s="6" t="s">
         <v>22</v>
@@ -10447,7 +10485,7 @@
         <v>7150</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="G142" s="9" t="n">
         <v>5000</v>
@@ -10484,10 +10522,10 @@
         <v/>
       </c>
       <c r="P142" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q142" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R142" s="7"/>
     </row>
@@ -10496,7 +10534,7 @@
         <v>144</v>
       </c>
       <c r="B143" s="7" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="C143" s="6" t="s">
         <v>22</v>
@@ -10508,7 +10546,7 @@
         <v>8450</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="G143" s="9" t="n">
         <v>6000</v>
@@ -10545,10 +10583,10 @@
         <v/>
       </c>
       <c r="P143" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q143" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R143" s="7"/>
     </row>
@@ -10557,7 +10595,7 @@
         <v>145</v>
       </c>
       <c r="B144" s="7" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="C144" s="6" t="s">
         <v>27</v>
@@ -10569,7 +10607,7 @@
         <v>104</v>
       </c>
       <c r="F144" s="7" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G144" s="9" t="n">
         <v>50</v>
@@ -10606,13 +10644,13 @@
         <v>YES</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q144" s="7" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="R144" s="7" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10620,7 +10658,7 @@
         <v>146</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="C145" s="6" t="s">
         <v>22</v>
@@ -10632,7 +10670,7 @@
         <v>105788</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="G145" s="9" t="n">
         <v>80000</v>
@@ -10669,10 +10707,10 @@
         <v/>
       </c>
       <c r="P145" s="6" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="Q145" s="7" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="R145" s="7"/>
     </row>
@@ -10681,7 +10719,7 @@
         <v>147</v>
       </c>
       <c r="B146" s="7" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="C146" s="6" t="s">
         <v>22</v>
@@ -10693,7 +10731,7 @@
         <v>245700</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="G146" s="9" t="n">
         <v>200000</v>
@@ -10730,10 +10768,10 @@
         <v/>
       </c>
       <c r="P146" s="6" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="Q146" s="7" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="R146" s="7"/>
     </row>
@@ -10742,7 +10780,7 @@
         <v>148</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="C147" s="6" t="s">
         <v>27</v>
@@ -10754,7 +10792,7 @@
         <v>650</v>
       </c>
       <c r="F147" s="7" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="G147" s="9" t="n">
         <v>300</v>
@@ -10791,10 +10829,10 @@
         <v>YES</v>
       </c>
       <c r="P147" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q147" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R147" s="7"/>
     </row>
@@ -10803,7 +10841,7 @@
         <v>149</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="C148" s="6" t="s">
         <v>22</v>
@@ -10815,7 +10853,7 @@
         <v>1754</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="G148" s="9" t="n">
         <v>1299</v>
@@ -10852,10 +10890,10 @@
         <v>YES</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="Q148" s="7" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="R148" s="7"/>
     </row>
@@ -10864,7 +10902,7 @@
         <v>150</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="C149" s="6" t="s">
         <v>22</v>
@@ -10879,7 +10917,7 @@
         <v>22</v>
       </c>
       <c r="G149" s="9" t="n">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="H149" s="9" t="n">
         <v>1000</v>
@@ -10916,7 +10954,7 @@
         <v>24</v>
       </c>
       <c r="Q149" s="7" t="s">
-        <v>40</v>
+        <v>276</v>
       </c>
       <c r="R149" s="7"/>
     </row>
@@ -10925,7 +10963,7 @@
         <v>151</v>
       </c>
       <c r="B150" s="7" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="C150" s="6" t="s">
         <v>22</v>
@@ -10974,10 +11012,10 @@
         <v/>
       </c>
       <c r="P150" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q150" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R150" s="7"/>
     </row>
@@ -10986,7 +11024,7 @@
         <v>152</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="C151" s="6" t="s">
         <v>22</v>
@@ -11035,19 +11073,19 @@
         <v/>
       </c>
       <c r="P151" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q151" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R151" s="7"/>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="6" t="n">
         <v>153</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="C152" s="6" t="s">
         <v>22</v>
@@ -11062,14 +11100,14 @@
         <v>22</v>
       </c>
       <c r="G152" s="9" t="n">
-        <v>600</v>
+        <v>730</v>
       </c>
       <c r="H152" s="9" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="I152" s="10" t="n">
         <f aca="false">IF(E152=0,0,(E152-H152)/E152)</f>
-        <v>0.18552036199095</v>
+        <v>0.0950226244343891</v>
       </c>
       <c r="J152" s="6" t="str">
         <f aca="false">IF(E152&lt;G152,"LOSS",IF(E152&lt;H152*1.1,"THIN / RISK",IF(E152&gt;H152*1.8,"OVERPRICED?","OK")))</f>
@@ -11077,7 +11115,7 @@
       </c>
       <c r="K152" s="8" t="n">
         <f aca="false">IF(J152="OVERPRICED?",ROUND(H152*1.35,-1),MAX(E152,ROUND(H152*(1+$E$3),-1)))</f>
-        <v>1105</v>
+        <v>1150</v>
       </c>
       <c r="L152" s="8" t="n">
         <f aca="false">D152*E152</f>
@@ -11085,11 +11123,11 @@
       </c>
       <c r="M152" s="8" t="n">
         <f aca="false">D152*K152</f>
-        <v>26520</v>
+        <v>27600</v>
       </c>
       <c r="N152" s="8" t="n">
         <f aca="false">D152*H152</f>
-        <v>21600</v>
+        <v>24000</v>
       </c>
       <c r="O152" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C152,F152)),"","YES")</f>
@@ -11099,7 +11137,7 @@
         <v>24</v>
       </c>
       <c r="Q152" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R152" s="7"/>
     </row>
@@ -11108,7 +11146,7 @@
         <v>154</v>
       </c>
       <c r="B153" s="7" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="C153" s="6" t="s">
         <v>22</v>
@@ -11157,10 +11195,10 @@
         <v/>
       </c>
       <c r="P153" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q153" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R153" s="7"/>
     </row>
@@ -11169,7 +11207,7 @@
         <v>155</v>
       </c>
       <c r="B154" s="7" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="C154" s="6" t="s">
         <v>22</v>
@@ -11218,10 +11256,10 @@
         <v/>
       </c>
       <c r="P154" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q154" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R154" s="7"/>
     </row>
@@ -11230,7 +11268,7 @@
         <v>156</v>
       </c>
       <c r="B155" s="7" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>22</v>
@@ -11279,10 +11317,10 @@
         <v/>
       </c>
       <c r="P155" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q155" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R155" s="7"/>
     </row>
@@ -11291,7 +11329,7 @@
         <v>157</v>
       </c>
       <c r="B156" s="7" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="C156" s="6" t="s">
         <v>22</v>
@@ -11340,10 +11378,10 @@
         <v/>
       </c>
       <c r="P156" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q156" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R156" s="7"/>
     </row>
@@ -11352,7 +11390,7 @@
         <v>158</v>
       </c>
       <c r="B157" s="7" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="C157" s="6" t="s">
         <v>27</v>
@@ -11364,7 +11402,7 @@
         <v>311</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G157" s="9" t="n">
         <v>150</v>
@@ -11401,13 +11439,13 @@
         <v>YES</v>
       </c>
       <c r="P157" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q157" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R157" s="7" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11415,7 +11453,7 @@
         <v>159</v>
       </c>
       <c r="B158" s="7" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="C158" s="6" t="s">
         <v>27</v>
@@ -11427,7 +11465,7 @@
         <v>325</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G158" s="9" t="n">
         <v>180</v>
@@ -11464,10 +11502,10 @@
         <v>YES</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q158" s="7" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="R158" s="7"/>
     </row>
@@ -11476,7 +11514,7 @@
         <v>160</v>
       </c>
       <c r="B159" s="7" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="C159" s="6" t="s">
         <v>27</v>
@@ -11488,7 +11526,7 @@
         <v>117</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="G159" s="9" t="n">
         <v>60</v>
@@ -11525,10 +11563,10 @@
         <v>YES</v>
       </c>
       <c r="P159" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q159" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R159" s="7"/>
     </row>
@@ -11537,7 +11575,7 @@
         <v>161</v>
       </c>
       <c r="B160" s="7" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="C160" s="6" t="s">
         <v>27</v>
@@ -11549,7 +11587,7 @@
         <v>169</v>
       </c>
       <c r="F160" s="7" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="G160" s="9" t="n">
         <v>90</v>
@@ -11586,10 +11624,10 @@
         <v>YES</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q160" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R160" s="7"/>
     </row>
@@ -11598,7 +11636,7 @@
         <v>162</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="C161" s="6" t="s">
         <v>27</v>
@@ -11610,7 +11648,7 @@
         <v>234</v>
       </c>
       <c r="F161" s="7" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="G161" s="9" t="n">
         <v>120</v>
@@ -11647,10 +11685,10 @@
         <v>YES</v>
       </c>
       <c r="P161" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q161" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R161" s="7"/>
     </row>
@@ -11659,7 +11697,7 @@
         <v>164</v>
       </c>
       <c r="B162" s="7" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="C162" s="6" t="s">
         <v>22</v>
@@ -11708,13 +11746,13 @@
         <v/>
       </c>
       <c r="P162" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q162" s="7" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="R162" s="7" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11722,7 +11760,7 @@
         <v>165</v>
       </c>
       <c r="B163" s="7" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="C163" s="6" t="s">
         <v>22</v>
@@ -11771,10 +11809,10 @@
         <v/>
       </c>
       <c r="P163" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q163" s="7" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="R163" s="7"/>
     </row>
@@ -11783,7 +11821,7 @@
         <v>166</v>
       </c>
       <c r="B164" s="7" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="C164" s="6" t="s">
         <v>22</v>
@@ -11832,10 +11870,10 @@
         <v/>
       </c>
       <c r="P164" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q164" s="7" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="R164" s="7"/>
     </row>
@@ -11844,7 +11882,7 @@
         <v>167</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="C165" s="6" t="s">
         <v>22</v>
@@ -11893,10 +11931,10 @@
         <v/>
       </c>
       <c r="P165" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q165" s="7" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="R165" s="7"/>
     </row>
@@ -11905,7 +11943,7 @@
         <v>168</v>
       </c>
       <c r="B166" s="7" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="C166" s="6" t="s">
         <v>22</v>
@@ -11954,10 +11992,10 @@
         <v/>
       </c>
       <c r="P166" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q166" s="7" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="R166" s="7"/>
     </row>
@@ -11966,7 +12004,7 @@
         <v>177</v>
       </c>
       <c r="B167" s="7" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="C167" s="6" t="s">
         <v>27</v>
@@ -11978,7 +12016,7 @@
         <v>5850</v>
       </c>
       <c r="F167" s="7" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="G167" s="9" t="n">
         <v>3500</v>
@@ -12015,10 +12053,10 @@
         <v>YES</v>
       </c>
       <c r="P167" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q167" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R167" s="7"/>
     </row>
@@ -12027,7 +12065,7 @@
         <v>179</v>
       </c>
       <c r="B168" s="7" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="C168" s="6" t="s">
         <v>27</v>
@@ -12039,7 +12077,7 @@
         <v>23400</v>
       </c>
       <c r="F168" s="7" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G168" s="9" t="n">
         <v>20000</v>
@@ -12076,10 +12114,10 @@
         <v>YES</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q168" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R168" s="7"/>
     </row>
@@ -12088,7 +12126,7 @@
         <v>180</v>
       </c>
       <c r="B169" s="7" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="C169" s="6" t="s">
         <v>27</v>
@@ -12100,7 +12138,7 @@
         <v>15600</v>
       </c>
       <c r="F169" s="7" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G169" s="9" t="n">
         <v>14000</v>
@@ -12137,10 +12175,10 @@
         <v>YES</v>
       </c>
       <c r="P169" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q169" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R169" s="7"/>
     </row>
@@ -12149,7 +12187,7 @@
         <v>181</v>
       </c>
       <c r="B170" s="7" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="C170" s="6" t="s">
         <v>27</v>
@@ -12161,7 +12199,7 @@
         <v>33800</v>
       </c>
       <c r="F170" s="7" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G170" s="9" t="n">
         <v>28000</v>
@@ -12198,10 +12236,10 @@
         <v>YES</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q170" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R170" s="7"/>
     </row>
@@ -12210,7 +12248,7 @@
         <v>182</v>
       </c>
       <c r="B171" s="7" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C171" s="6" t="s">
         <v>27</v>
@@ -12222,7 +12260,7 @@
         <v>23400</v>
       </c>
       <c r="F171" s="7" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="G171" s="9" t="n">
         <v>20000</v>
@@ -12259,10 +12297,10 @@
         <v>YES</v>
       </c>
       <c r="P171" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q171" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R171" s="7"/>
     </row>
@@ -12271,7 +12309,7 @@
         <v>183</v>
       </c>
       <c r="B172" s="7" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="C172" s="6" t="s">
         <v>27</v>
@@ -12283,7 +12321,7 @@
         <v>2860</v>
       </c>
       <c r="F172" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G172" s="9" t="n">
         <v>1800</v>
@@ -12320,10 +12358,10 @@
         <v>YES</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q172" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R172" s="7"/>
     </row>
@@ -12332,7 +12370,7 @@
         <v>184</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="C173" s="6" t="s">
         <v>27</v>
@@ -12344,7 +12382,7 @@
         <v>3250</v>
       </c>
       <c r="F173" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G173" s="9" t="n">
         <v>2100</v>
@@ -12381,10 +12419,10 @@
         <v>YES</v>
       </c>
       <c r="P173" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q173" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R173" s="7"/>
     </row>
@@ -12393,7 +12431,7 @@
         <v>185</v>
       </c>
       <c r="B174" s="7" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="C174" s="6" t="s">
         <v>27</v>
@@ -12405,7 +12443,7 @@
         <v>3900</v>
       </c>
       <c r="F174" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G174" s="9" t="n">
         <v>2600</v>
@@ -12442,10 +12480,10 @@
         <v>YES</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q174" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R174" s="7"/>
     </row>
@@ -12454,7 +12492,7 @@
         <v>186</v>
       </c>
       <c r="B175" s="7" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="C175" s="6" t="s">
         <v>27</v>
@@ -12466,7 +12504,7 @@
         <v>4550</v>
       </c>
       <c r="F175" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G175" s="9" t="n">
         <v>3300</v>
@@ -12503,10 +12541,10 @@
         <v>YES</v>
       </c>
       <c r="P175" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q175" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R175" s="7"/>
     </row>
@@ -12515,7 +12553,7 @@
         <v>187</v>
       </c>
       <c r="B176" s="7" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="C176" s="6" t="s">
         <v>27</v>
@@ -12527,7 +12565,7 @@
         <v>7150</v>
       </c>
       <c r="F176" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G176" s="9" t="n">
         <v>5500</v>
@@ -12564,10 +12602,10 @@
         <v>YES</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q176" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R176" s="7"/>
     </row>
@@ -12576,7 +12614,7 @@
         <v>188</v>
       </c>
       <c r="B177" s="7" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="C177" s="6" t="s">
         <v>27</v>
@@ -12588,7 +12626,7 @@
         <v>8450</v>
       </c>
       <c r="F177" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G177" s="9" t="n">
         <v>7000</v>
@@ -12625,10 +12663,10 @@
         <v>YES</v>
       </c>
       <c r="P177" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q177" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R177" s="7"/>
     </row>
@@ -12637,7 +12675,7 @@
         <v>189</v>
       </c>
       <c r="B178" s="7" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="C178" s="6" t="s">
         <v>27</v>
@@ -12649,7 +12687,7 @@
         <v>9750</v>
       </c>
       <c r="F178" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G178" s="9" t="n">
         <v>8500</v>
@@ -12686,10 +12724,10 @@
         <v>YES</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q178" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R178" s="7"/>
     </row>
@@ -12698,7 +12736,7 @@
         <v>190</v>
       </c>
       <c r="B179" s="7" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="C179" s="6" t="s">
         <v>27</v>
@@ -12710,7 +12748,7 @@
         <v>2340</v>
       </c>
       <c r="F179" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G179" s="9" t="n">
         <v>1500</v>
@@ -12747,10 +12785,10 @@
         <v>YES</v>
       </c>
       <c r="P179" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q179" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R179" s="7"/>
     </row>
@@ -12759,7 +12797,7 @@
         <v>191</v>
       </c>
       <c r="B180" s="7" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="C180" s="6" t="s">
         <v>27</v>
@@ -12771,7 +12809,7 @@
         <v>3640</v>
       </c>
       <c r="F180" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G180" s="9" t="n">
         <v>2300</v>
@@ -12808,10 +12846,10 @@
         <v>YES</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q180" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R180" s="7"/>
     </row>
@@ -12820,7 +12858,7 @@
         <v>192</v>
       </c>
       <c r="B181" s="7" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="C181" s="6" t="s">
         <v>27</v>
@@ -12869,10 +12907,10 @@
         <v>YES</v>
       </c>
       <c r="P181" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q181" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R181" s="7"/>
     </row>
@@ -12881,7 +12919,7 @@
         <v>193</v>
       </c>
       <c r="B182" s="7" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="C182" s="6" t="s">
         <v>27</v>
@@ -12930,10 +12968,10 @@
         <v>YES</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q182" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R182" s="7"/>
     </row>
@@ -12942,7 +12980,7 @@
         <v>194</v>
       </c>
       <c r="B183" s="7" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="C183" s="6" t="s">
         <v>27</v>
@@ -12991,10 +13029,10 @@
         <v>YES</v>
       </c>
       <c r="P183" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q183" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R183" s="7"/>
     </row>
@@ -13003,7 +13041,7 @@
         <v>195</v>
       </c>
       <c r="B184" s="7" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="C184" s="6" t="s">
         <v>27</v>
@@ -13052,10 +13090,10 @@
         <v>YES</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q184" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R184" s="7"/>
     </row>
@@ -13064,7 +13102,7 @@
         <v>196</v>
       </c>
       <c r="B185" s="7" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="C185" s="6" t="s">
         <v>27</v>
@@ -13076,7 +13114,7 @@
         <v>4550</v>
       </c>
       <c r="F185" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G185" s="9" t="n">
         <v>3500</v>
@@ -13113,10 +13151,10 @@
         <v>YES</v>
       </c>
       <c r="P185" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q185" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R185" s="7"/>
     </row>
@@ -13125,7 +13163,7 @@
         <v>197</v>
       </c>
       <c r="B186" s="7" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="C186" s="6" t="s">
         <v>27</v>
@@ -13137,17 +13175,17 @@
         <v>17940</v>
       </c>
       <c r="F186" s="7" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="G186" s="9" t="n">
-        <v>6000</v>
+        <v>4815</v>
       </c>
       <c r="H186" s="9" t="n">
-        <v>8000</v>
+        <v>5500</v>
       </c>
       <c r="I186" s="10" t="n">
         <f aca="false">IF(E186=0,0,(E186-H186)/E186)</f>
-        <v>0.554069119286511</v>
+        <v>0.693422519509476</v>
       </c>
       <c r="J186" s="6" t="str">
         <f aca="false">IF(E186&lt;G186,"LOSS",IF(E186&lt;H186*1.1,"THIN / RISK",IF(E186&gt;H186*1.8,"OVERPRICED?","OK")))</f>
@@ -13155,7 +13193,7 @@
       </c>
       <c r="K186" s="8" t="n">
         <f aca="false">IF(J186="OVERPRICED?",ROUND(H186*1.35,-1),MAX(E186,ROUND(H186*(1+$E$3),-1)))</f>
-        <v>10800</v>
+        <v>7430</v>
       </c>
       <c r="L186" s="8" t="n">
         <f aca="false">D186*E186</f>
@@ -13163,24 +13201,24 @@
       </c>
       <c r="M186" s="8" t="n">
         <f aca="false">D186*K186</f>
-        <v>10800</v>
+        <v>7430</v>
       </c>
       <c r="N186" s="8" t="n">
         <f aca="false">D186*H186</f>
-        <v>8000</v>
+        <v>5500</v>
       </c>
       <c r="O186" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C186,F186)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="Q186" s="7" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="R186" s="7" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13188,7 +13226,7 @@
         <v>198</v>
       </c>
       <c r="B187" s="7" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="C187" s="6" t="s">
         <v>27</v>
@@ -13200,17 +13238,17 @@
         <v>18850</v>
       </c>
       <c r="F187" s="7" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="G187" s="9" t="n">
-        <v>7500</v>
+        <v>5300</v>
       </c>
       <c r="H187" s="9" t="n">
-        <v>9500</v>
+        <v>6500</v>
       </c>
       <c r="I187" s="10" t="n">
         <f aca="false">IF(E187=0,0,(E187-H187)/E187)</f>
-        <v>0.496021220159151</v>
+        <v>0.655172413793103</v>
       </c>
       <c r="J187" s="6" t="str">
         <f aca="false">IF(E187&lt;G187,"LOSS",IF(E187&lt;H187*1.1,"THIN / RISK",IF(E187&gt;H187*1.8,"OVERPRICED?","OK")))</f>
@@ -13218,7 +13256,7 @@
       </c>
       <c r="K187" s="8" t="n">
         <f aca="false">IF(J187="OVERPRICED?",ROUND(H187*1.35,-1),MAX(E187,ROUND(H187*(1+$E$3),-1)))</f>
-        <v>12830</v>
+        <v>8780</v>
       </c>
       <c r="L187" s="8" t="n">
         <f aca="false">D187*E187</f>
@@ -13226,30 +13264,32 @@
       </c>
       <c r="M187" s="8" t="n">
         <f aca="false">D187*K187</f>
-        <v>12830</v>
+        <v>8780</v>
       </c>
       <c r="N187" s="8" t="n">
         <f aca="false">D187*H187</f>
-        <v>9500</v>
+        <v>6500</v>
       </c>
       <c r="O187" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C187,F187)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P187" s="6" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="Q187" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="R187" s="7"/>
+        <v>323</v>
+      </c>
+      <c r="R187" s="7" t="s">
+        <v>320</v>
+      </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="6" t="n">
         <v>199</v>
       </c>
       <c r="B188" s="7" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="C188" s="6" t="s">
         <v>27</v>
@@ -13261,25 +13301,25 @@
         <v>19500</v>
       </c>
       <c r="F188" s="7" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="G188" s="9" t="n">
-        <v>8500</v>
+        <v>6000</v>
       </c>
       <c r="H188" s="9" t="n">
-        <v>11000</v>
+        <v>7200</v>
       </c>
       <c r="I188" s="10" t="n">
         <f aca="false">IF(E188=0,0,(E188-H188)/E188)</f>
-        <v>0.435897435897436</v>
+        <v>0.630769230769231</v>
       </c>
       <c r="J188" s="6" t="str">
         <f aca="false">IF(E188&lt;G188,"LOSS",IF(E188&lt;H188*1.1,"THIN / RISK",IF(E188&gt;H188*1.8,"OVERPRICED?","OK")))</f>
-        <v>OK</v>
+        <v>OVERPRICED?</v>
       </c>
       <c r="K188" s="8" t="n">
         <f aca="false">IF(J188="OVERPRICED?",ROUND(H188*1.35,-1),MAX(E188,ROUND(H188*(1+$E$3),-1)))</f>
-        <v>19500</v>
+        <v>9720</v>
       </c>
       <c r="L188" s="8" t="n">
         <f aca="false">D188*E188</f>
@@ -13287,30 +13327,32 @@
       </c>
       <c r="M188" s="8" t="n">
         <f aca="false">D188*K188</f>
-        <v>19500</v>
+        <v>9720</v>
       </c>
       <c r="N188" s="8" t="n">
         <f aca="false">D188*H188</f>
-        <v>11000</v>
+        <v>7200</v>
       </c>
       <c r="O188" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C188,F188)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="Q188" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="R188" s="7"/>
+        <v>323</v>
+      </c>
+      <c r="R188" s="7" t="s">
+        <v>320</v>
+      </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="6" t="n">
         <v>200</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="C189" s="6" t="s">
         <v>27</v>
@@ -13322,25 +13364,25 @@
         <v>20800</v>
       </c>
       <c r="F189" s="7" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="G189" s="9" t="n">
-        <v>10000</v>
+        <v>6875</v>
       </c>
       <c r="H189" s="9" t="n">
-        <v>12500</v>
+        <v>7800</v>
       </c>
       <c r="I189" s="10" t="n">
         <f aca="false">IF(E189=0,0,(E189-H189)/E189)</f>
-        <v>0.399038461538462</v>
+        <v>0.625</v>
       </c>
       <c r="J189" s="6" t="str">
         <f aca="false">IF(E189&lt;G189,"LOSS",IF(E189&lt;H189*1.1,"THIN / RISK",IF(E189&gt;H189*1.8,"OVERPRICED?","OK")))</f>
-        <v>OK</v>
+        <v>OVERPRICED?</v>
       </c>
       <c r="K189" s="8" t="n">
         <f aca="false">IF(J189="OVERPRICED?",ROUND(H189*1.35,-1),MAX(E189,ROUND(H189*(1+$E$3),-1)))</f>
-        <v>20800</v>
+        <v>10530</v>
       </c>
       <c r="L189" s="8" t="n">
         <f aca="false">D189*E189</f>
@@ -13348,11 +13390,11 @@
       </c>
       <c r="M189" s="8" t="n">
         <f aca="false">D189*K189</f>
-        <v>20800</v>
+        <v>10530</v>
       </c>
       <c r="N189" s="8" t="n">
         <f aca="false">D189*H189</f>
-        <v>12500</v>
+        <v>7800</v>
       </c>
       <c r="O189" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C189,F189)),"","YES")</f>
@@ -13362,16 +13404,18 @@
         <v>24</v>
       </c>
       <c r="Q189" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="R189" s="7"/>
+        <v>328</v>
+      </c>
+      <c r="R189" s="7" t="s">
+        <v>320</v>
+      </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="6" t="n">
         <v>201</v>
       </c>
       <c r="B190" s="7" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="C190" s="6" t="s">
         <v>27</v>
@@ -13383,25 +13427,25 @@
         <v>22750</v>
       </c>
       <c r="F190" s="7" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="G190" s="9" t="n">
-        <v>12000</v>
+        <v>8750</v>
       </c>
       <c r="H190" s="9" t="n">
-        <v>15000</v>
+        <v>9800</v>
       </c>
       <c r="I190" s="10" t="n">
         <f aca="false">IF(E190=0,0,(E190-H190)/E190)</f>
-        <v>0.340659340659341</v>
+        <v>0.569230769230769</v>
       </c>
       <c r="J190" s="6" t="str">
         <f aca="false">IF(E190&lt;G190,"LOSS",IF(E190&lt;H190*1.1,"THIN / RISK",IF(E190&gt;H190*1.8,"OVERPRICED?","OK")))</f>
-        <v>OK</v>
+        <v>OVERPRICED?</v>
       </c>
       <c r="K190" s="8" t="n">
         <f aca="false">IF(J190="OVERPRICED?",ROUND(H190*1.35,-1),MAX(E190,ROUND(H190*(1+$E$3),-1)))</f>
-        <v>22750</v>
+        <v>13230</v>
       </c>
       <c r="L190" s="8" t="n">
         <f aca="false">D190*E190</f>
@@ -13409,11 +13453,11 @@
       </c>
       <c r="M190" s="8" t="n">
         <f aca="false">D190*K190</f>
-        <v>22750</v>
+        <v>13230</v>
       </c>
       <c r="N190" s="8" t="n">
         <f aca="false">D190*H190</f>
-        <v>15000</v>
+        <v>9800</v>
       </c>
       <c r="O190" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C190,F190)),"","YES")</f>
@@ -13423,16 +13467,18 @@
         <v>24</v>
       </c>
       <c r="Q190" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="R190" s="7"/>
+        <v>331</v>
+      </c>
+      <c r="R190" s="7" t="s">
+        <v>320</v>
+      </c>
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="6" t="n">
         <v>202</v>
       </c>
       <c r="B191" s="7" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="C191" s="6" t="s">
         <v>27</v>
@@ -13444,7 +13490,7 @@
         <v>2340</v>
       </c>
       <c r="F191" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G191" s="9" t="n">
         <v>1500</v>
@@ -13481,10 +13527,10 @@
         <v>YES</v>
       </c>
       <c r="P191" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q191" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R191" s="7"/>
     </row>
@@ -13493,7 +13539,7 @@
         <v>204</v>
       </c>
       <c r="B192" s="7" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="C192" s="6" t="s">
         <v>27</v>
@@ -13505,7 +13551,7 @@
         <v>845</v>
       </c>
       <c r="F192" s="7" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="G192" s="9" t="n">
         <v>800</v>
@@ -13542,13 +13588,13 @@
         <v>YES</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q192" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R192" s="7" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13556,7 +13602,7 @@
         <v>205</v>
       </c>
       <c r="B193" s="7" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="C193" s="6" t="s">
         <v>27</v>
@@ -13568,7 +13614,7 @@
         <v>910</v>
       </c>
       <c r="F193" s="7" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="G193" s="9" t="n">
         <v>900</v>
@@ -13605,10 +13651,10 @@
         <v>YES</v>
       </c>
       <c r="P193" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q193" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R193" s="7"/>
     </row>
@@ -13617,7 +13663,7 @@
         <v>206</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="C194" s="6" t="s">
         <v>27</v>
@@ -13629,7 +13675,7 @@
         <v>1170</v>
       </c>
       <c r="F194" s="7" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="G194" s="9" t="n">
         <v>1200</v>
@@ -13666,10 +13712,10 @@
         <v>YES</v>
       </c>
       <c r="P194" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q194" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R194" s="7"/>
     </row>
@@ -13678,7 +13724,7 @@
         <v>207</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="C195" s="6" t="s">
         <v>27</v>
@@ -13690,7 +13736,7 @@
         <v>1430</v>
       </c>
       <c r="F195" s="7" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="G195" s="9" t="n">
         <v>1600</v>
@@ -13727,10 +13773,10 @@
         <v>YES</v>
       </c>
       <c r="P195" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q195" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R195" s="7"/>
     </row>
@@ -13739,7 +13785,7 @@
         <v>208</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="C196" s="6" t="s">
         <v>27</v>
@@ -13751,7 +13797,7 @@
         <v>1690</v>
       </c>
       <c r="F196" s="7" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="G196" s="9" t="n">
         <v>2000</v>
@@ -13788,10 +13834,10 @@
         <v>YES</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q196" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R196" s="7"/>
     </row>
@@ -13800,7 +13846,7 @@
         <v>209</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="C197" s="6" t="s">
         <v>27</v>
@@ -13812,7 +13858,7 @@
         <v>2340</v>
       </c>
       <c r="F197" s="7" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="G197" s="9" t="n">
         <v>3000</v>
@@ -13849,10 +13895,10 @@
         <v>YES</v>
       </c>
       <c r="P197" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q197" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R197" s="7"/>
     </row>
@@ -13861,7 +13907,7 @@
         <v>210</v>
       </c>
       <c r="B198" s="7" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="C198" s="6" t="s">
         <v>27</v>
@@ -13873,7 +13919,7 @@
         <v>2860</v>
       </c>
       <c r="F198" s="7" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="G198" s="9" t="n">
         <v>3700</v>
@@ -13910,10 +13956,10 @@
         <v>YES</v>
       </c>
       <c r="P198" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q198" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R198" s="7"/>
     </row>
@@ -13922,7 +13968,7 @@
         <v>211</v>
       </c>
       <c r="B199" s="7" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="C199" s="6" t="s">
         <v>27</v>
@@ -13934,7 +13980,7 @@
         <v>4160</v>
       </c>
       <c r="F199" s="7" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="G199" s="9" t="n">
         <v>5200</v>
@@ -13971,10 +14017,10 @@
         <v>YES</v>
       </c>
       <c r="P199" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q199" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R199" s="7"/>
     </row>
@@ -13983,7 +14029,7 @@
         <v>212</v>
       </c>
       <c r="B200" s="7" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="C200" s="6" t="s">
         <v>27</v>
@@ -13995,7 +14041,7 @@
         <v>5460</v>
       </c>
       <c r="F200" s="7" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="G200" s="9" t="n">
         <v>6500</v>
@@ -14032,10 +14078,10 @@
         <v>YES</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q200" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R200" s="7"/>
     </row>
@@ -14044,7 +14090,7 @@
         <v>213</v>
       </c>
       <c r="B201" s="7" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="C201" s="6" t="s">
         <v>27</v>
@@ -14056,7 +14102,7 @@
         <v>455</v>
       </c>
       <c r="F201" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G201" s="9" t="n">
         <v>500</v>
@@ -14093,10 +14139,10 @@
         <v>YES</v>
       </c>
       <c r="P201" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q201" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R201" s="7"/>
     </row>
@@ -14105,7 +14151,7 @@
         <v>214</v>
       </c>
       <c r="B202" s="7" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="C202" s="6" t="s">
         <v>27</v>
@@ -14117,7 +14163,7 @@
         <v>494</v>
       </c>
       <c r="F202" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G202" s="9" t="n">
         <v>550</v>
@@ -14154,10 +14200,10 @@
         <v>YES</v>
       </c>
       <c r="P202" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q202" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R202" s="7"/>
     </row>
@@ -14166,7 +14212,7 @@
         <v>215</v>
       </c>
       <c r="B203" s="7" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="C203" s="6" t="s">
         <v>27</v>
@@ -14178,7 +14224,7 @@
         <v>585</v>
       </c>
       <c r="F203" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G203" s="9" t="n">
         <v>650</v>
@@ -14215,10 +14261,10 @@
         <v>YES</v>
       </c>
       <c r="P203" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q203" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R203" s="7"/>
     </row>
@@ -14227,7 +14273,7 @@
         <v>216</v>
       </c>
       <c r="B204" s="7" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="C204" s="6" t="s">
         <v>27</v>
@@ -14239,7 +14285,7 @@
         <v>715</v>
       </c>
       <c r="F204" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G204" s="9" t="n">
         <v>800</v>
@@ -14276,10 +14322,10 @@
         <v>YES</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q204" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R204" s="7"/>
     </row>
@@ -14288,7 +14334,7 @@
         <v>217</v>
       </c>
       <c r="B205" s="7" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="C205" s="6" t="s">
         <v>27</v>
@@ -14300,7 +14346,7 @@
         <v>910</v>
       </c>
       <c r="F205" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G205" s="9" t="n">
         <v>1000</v>
@@ -14337,10 +14383,10 @@
         <v>YES</v>
       </c>
       <c r="P205" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q205" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R205" s="7"/>
     </row>
@@ -14349,7 +14395,7 @@
         <v>218</v>
       </c>
       <c r="B206" s="7" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="C206" s="6" t="s">
         <v>27</v>
@@ -14361,7 +14407,7 @@
         <v>1170</v>
       </c>
       <c r="F206" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G206" s="9" t="n">
         <v>1400</v>
@@ -14398,10 +14444,10 @@
         <v>YES</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q206" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R206" s="7"/>
     </row>
@@ -14410,7 +14456,7 @@
         <v>219</v>
       </c>
       <c r="B207" s="7" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="C207" s="6" t="s">
         <v>27</v>
@@ -14422,7 +14468,7 @@
         <v>1040</v>
       </c>
       <c r="F207" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G207" s="9" t="n">
         <v>1100</v>
@@ -14459,10 +14505,10 @@
         <v>YES</v>
       </c>
       <c r="P207" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q207" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R207" s="7"/>
     </row>
@@ -14471,7 +14517,7 @@
         <v>220</v>
       </c>
       <c r="B208" s="7" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="C208" s="6" t="s">
         <v>27</v>
@@ -14483,7 +14529,7 @@
         <v>1430</v>
       </c>
       <c r="F208" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G208" s="9" t="n">
         <v>1400</v>
@@ -14520,10 +14566,10 @@
         <v>YES</v>
       </c>
       <c r="P208" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q208" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R208" s="7"/>
     </row>
@@ -14532,7 +14578,7 @@
         <v>221</v>
       </c>
       <c r="B209" s="7" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="C209" s="6" t="s">
         <v>27</v>
@@ -14544,7 +14590,7 @@
         <v>1950</v>
       </c>
       <c r="F209" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G209" s="9" t="n">
         <v>2000</v>
@@ -14581,10 +14627,10 @@
         <v>YES</v>
       </c>
       <c r="P209" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q209" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R209" s="7"/>
     </row>
@@ -14593,7 +14639,7 @@
         <v>222</v>
       </c>
       <c r="B210" s="7" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="C210" s="6" t="s">
         <v>27</v>
@@ -14605,7 +14651,7 @@
         <v>15600</v>
       </c>
       <c r="F210" s="7" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="G210" s="9" t="n">
         <v>18000</v>
@@ -14642,13 +14688,13 @@
         <v>YES</v>
       </c>
       <c r="P210" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q210" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R210" s="7" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14656,7 +14702,7 @@
         <v>223</v>
       </c>
       <c r="B211" s="7" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="C211" s="6" t="s">
         <v>27</v>
@@ -14668,7 +14714,7 @@
         <v>30940</v>
       </c>
       <c r="F211" s="7" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="G211" s="9" t="n">
         <v>45000</v>
@@ -14705,13 +14751,13 @@
         <v>YES</v>
       </c>
       <c r="P211" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q211" s="7" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="R211" s="7" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14719,7 +14765,7 @@
         <v>224</v>
       </c>
       <c r="B212" s="7" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="C212" s="6" t="s">
         <v>27</v>
@@ -14731,7 +14777,7 @@
         <v>54600</v>
       </c>
       <c r="F212" s="7" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="G212" s="9" t="n">
         <v>85000</v>
@@ -14768,13 +14814,13 @@
         <v>YES</v>
       </c>
       <c r="P212" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q212" s="7" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="R212" s="7" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14782,7 +14828,7 @@
         <v>225</v>
       </c>
       <c r="B213" s="7" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="C213" s="6" t="s">
         <v>27</v>
@@ -14794,7 +14840,7 @@
         <v>1170</v>
       </c>
       <c r="F213" s="7" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="G213" s="9" t="n">
         <v>1000</v>
@@ -14831,10 +14877,10 @@
         <v>YES</v>
       </c>
       <c r="P213" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q213" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R213" s="7"/>
     </row>
@@ -14843,7 +14889,7 @@
         <v>226</v>
       </c>
       <c r="B214" s="7" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="C214" s="6" t="s">
         <v>27</v>
@@ -14855,7 +14901,7 @@
         <v>1430</v>
       </c>
       <c r="F214" s="7" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="G214" s="9" t="n">
         <v>1400</v>
@@ -14892,10 +14938,10 @@
         <v>YES</v>
       </c>
       <c r="P214" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q214" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R214" s="7"/>
     </row>
@@ -14904,7 +14950,7 @@
         <v>227</v>
       </c>
       <c r="B215" s="7" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="C215" s="6" t="s">
         <v>27</v>
@@ -14916,7 +14962,7 @@
         <v>1820</v>
       </c>
       <c r="F215" s="7" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="G215" s="9" t="n">
         <v>1900</v>
@@ -14953,10 +14999,10 @@
         <v>YES</v>
       </c>
       <c r="P215" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q215" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R215" s="7"/>
     </row>
@@ -14965,7 +15011,7 @@
         <v>228</v>
       </c>
       <c r="B216" s="7" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="C216" s="6" t="s">
         <v>27</v>
@@ -14977,7 +15023,7 @@
         <v>2860</v>
       </c>
       <c r="F216" s="7" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="G216" s="9" t="n">
         <v>3200</v>
@@ -15014,10 +15060,10 @@
         <v>YES</v>
       </c>
       <c r="P216" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q216" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R216" s="7"/>
     </row>
@@ -15026,7 +15072,7 @@
         <v>229</v>
       </c>
       <c r="B217" s="7" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="C217" s="6" t="s">
         <v>27</v>
@@ -15038,7 +15084,7 @@
         <v>2340</v>
       </c>
       <c r="F217" s="7" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="G217" s="9" t="n">
         <v>1800</v>
@@ -15075,10 +15121,10 @@
         <v>YES</v>
       </c>
       <c r="P217" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q217" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R217" s="7"/>
     </row>
@@ -15087,7 +15133,7 @@
         <v>230</v>
       </c>
       <c r="B218" s="7" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="C218" s="6" t="s">
         <v>27</v>
@@ -15099,7 +15145,7 @@
         <v>9750</v>
       </c>
       <c r="F218" s="7" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="G218" s="9" t="n">
         <v>6000</v>
@@ -15136,10 +15182,10 @@
         <v>YES</v>
       </c>
       <c r="P218" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q218" s="7" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="R218" s="7"/>
     </row>
@@ -15148,7 +15194,7 @@
         <v>231</v>
       </c>
       <c r="B219" s="7" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="C219" s="6" t="s">
         <v>27</v>
@@ -15160,7 +15206,7 @@
         <v>12350</v>
       </c>
       <c r="F219" s="7" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="G219" s="9" t="n">
         <v>8000</v>
@@ -15197,10 +15243,10 @@
         <v>YES</v>
       </c>
       <c r="P219" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Q219" s="7" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="R219" s="7"/>
     </row>
@@ -15209,10 +15255,10 @@
         <v>233</v>
       </c>
       <c r="B220" s="7" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="C220" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D220" s="6" t="n">
         <v>2</v>
@@ -15221,7 +15267,7 @@
         <v>52000</v>
       </c>
       <c r="F220" s="7" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="G220" s="9" t="n">
         <v>38340</v>
@@ -15258,13 +15304,13 @@
         <v/>
       </c>
       <c r="P220" s="6" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="Q220" s="7" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="R220" s="7" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15272,7 +15318,7 @@
         <v>234</v>
       </c>
       <c r="B221" s="7" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="C221" s="6" t="s">
         <v>22</v>
@@ -15321,10 +15367,10 @@
         <v/>
       </c>
       <c r="P221" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q221" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R221" s="7"/>
     </row>
@@ -15333,7 +15379,7 @@
         <v>235</v>
       </c>
       <c r="B222" s="7" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="C222" s="6" t="s">
         <v>27</v>
@@ -15382,19 +15428,19 @@
         <v>YES</v>
       </c>
       <c r="P222" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q222" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R222" s="7"/>
     </row>
-    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="223" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="6" t="n">
         <v>236</v>
       </c>
       <c r="B223" s="7" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="C223" s="6" t="s">
         <v>22</v>
@@ -15406,7 +15452,7 @@
         <v>2860</v>
       </c>
       <c r="F223" s="7" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="G223" s="9" t="n">
         <v>2400</v>
@@ -15443,13 +15489,13 @@
         <v/>
       </c>
       <c r="P223" s="6" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="Q223" s="7" t="s">
-        <v>224</v>
+        <v>384</v>
       </c>
       <c r="R223" s="7" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15457,7 +15503,7 @@
         <v>237</v>
       </c>
       <c r="B224" s="7" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="C224" s="6" t="s">
         <v>27</v>
@@ -15506,19 +15552,19 @@
         <v>YES</v>
       </c>
       <c r="P224" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q224" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R224" s="7"/>
     </row>
-    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="225" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="6" t="n">
         <v>238</v>
       </c>
       <c r="B225" s="7" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="C225" s="6" t="s">
         <v>27</v>
@@ -15530,17 +15576,17 @@
         <v>8450</v>
       </c>
       <c r="F225" s="7" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="G225" s="9" t="n">
-        <v>6000</v>
+        <v>6500</v>
       </c>
       <c r="H225" s="9" t="n">
-        <v>9000</v>
+        <v>7800</v>
       </c>
       <c r="I225" s="10" t="n">
         <f aca="false">IF(E225=0,0,(E225-H225)/E225)</f>
-        <v>-0.0650887573964497</v>
+        <v>0.0769230769230769</v>
       </c>
       <c r="J225" s="6" t="str">
         <f aca="false">IF(E225&lt;G225,"LOSS",IF(E225&lt;H225*1.1,"THIN / RISK",IF(E225&gt;H225*1.8,"OVERPRICED?","OK")))</f>
@@ -15548,7 +15594,7 @@
       </c>
       <c r="K225" s="8" t="n">
         <f aca="false">IF(J225="OVERPRICED?",ROUND(H225*1.35,-1),MAX(E225,ROUND(H225*(1+$E$3),-1)))</f>
-        <v>10350</v>
+        <v>8970</v>
       </c>
       <c r="L225" s="8" t="n">
         <f aca="false">D225*E225</f>
@@ -15556,11 +15602,11 @@
       </c>
       <c r="M225" s="8" t="n">
         <f aca="false">D225*K225</f>
-        <v>62100</v>
+        <v>53820</v>
       </c>
       <c r="N225" s="8" t="n">
         <f aca="false">D225*H225</f>
-        <v>54000</v>
+        <v>46800</v>
       </c>
       <c r="O225" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C225,F225)),"","YES")</f>
@@ -15570,10 +15616,10 @@
         <v>24</v>
       </c>
       <c r="Q225" s="7" t="s">
-        <v>40</v>
+        <v>389</v>
       </c>
       <c r="R225" s="7" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15581,10 +15627,10 @@
         <v>239</v>
       </c>
       <c r="B226" s="7" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D226" s="6" t="n">
         <v>50</v>
@@ -15593,7 +15639,7 @@
         <v>65000</v>
       </c>
       <c r="F226" s="7" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="G226" s="9" t="n">
         <v>36570</v>
@@ -15630,13 +15676,13 @@
         <v/>
       </c>
       <c r="P226" s="6" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="Q226" s="7" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="R226" s="7" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15644,7 +15690,7 @@
         <v>240</v>
       </c>
       <c r="B227" s="7" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="C227" s="6" t="s">
         <v>27</v>
@@ -15656,7 +15702,7 @@
         <v>325</v>
       </c>
       <c r="F227" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G227" s="9" t="n">
         <v>150</v>
@@ -15693,16 +15739,16 @@
         <v>YES</v>
       </c>
       <c r="P227" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Q227" s="7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="R227" s="7"/>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B228" s="3" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="L228" s="11" t="n">
         <f aca="false">SUM(L6:L227)</f>
@@ -15710,11 +15756,11 @@
       </c>
       <c r="M228" s="11" t="n">
         <f aca="false">SUM(M6:M227)</f>
-        <v>13938636</v>
+        <v>13975036</v>
       </c>
       <c r="N228" s="11" t="n">
         <f aca="false">SUM(N6:N227)</f>
-        <v>11227980</v>
+        <v>11275780</v>
       </c>
     </row>
   </sheetData>
@@ -15763,12 +15809,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="B3" s="11" t="n">
         <f aca="false">COUNTA('Rate Check'!A6:A227)</f>
@@ -15777,43 +15823,43 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B4" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"LOSS")</f>
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="B5" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"THIN / RISK")</f>
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="B6" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"OK")</f>
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="B7" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"OVERPRICED?")</f>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="B8" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!O6:O227,"YES")</f>
@@ -15825,7 +15871,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="B10" s="11" t="n">
         <f aca="false">'Rate Check'!L228</f>
@@ -15834,38 +15880,38 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="B11" s="11" t="n">
         <f aca="false">'Rate Check'!N228</f>
-        <v>11227980</v>
+        <v>11275780</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="B12" s="11" t="n">
         <f aca="false">B10-B11</f>
-        <v>981528</v>
+        <v>933728</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="B13" s="14" t="n">
         <f aca="false">IF(B10=0,0,B12/B10)</f>
-        <v>0.0803904629080877</v>
+        <v>0.0764754812397027</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="B14" s="11" t="n">
         <f aca="false">SUMPRODUCT(('Rate Check'!E6:E227&lt;'Rate Check'!H6:H227)*('Rate Check'!H6:H227-'Rate Check'!E6:E227)*'Rate Check'!D6:D227)</f>
-        <v>1285780</v>
+        <v>1349720</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15873,20 +15919,20 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="B16" s="11" t="n">
         <f aca="false">'Rate Check'!M228</f>
-        <v>13938636</v>
+        <v>13975036</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="B17" s="14" t="n">
         <f aca="false">IF(B16=0,0,(B16-B11)/B16)</f>
-        <v>0.194470678479587</v>
+        <v>0.193148411209817</v>
       </c>
     </row>
   </sheetData>
@@ -15914,247 +15960,247 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
     </row>
   </sheetData>

--- a/quotes/PR-217-228/Quote_PR217_PR228_Rate_Check.xlsx
+++ b/quotes/PR-217-228/Quote_PR217_PR228_Rate_Check.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1367" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1367" uniqueCount="515">
   <si>
     <t xml:space="preserve">Zidane Corporation - Quote PR-217 &amp; PR-228: Brand + Buying Rate Check</t>
   </si>
@@ -138,264 +138,267 @@
     <t xml:space="preserve">DRILL BIT 08 MM (Yato or any Good brand taiwan)</t>
   </si>
   <si>
+    <t xml:space="preserve">Dormer A002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart.pk Dormer A002 1-10mm from 900 (8mm exact n/a)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. single 8mm (ktools Bosch HSS range 520-5,500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MECHANICAL JACK 03 TONS (Japan or germany)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAFETY HELMET (WHITE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">powerhouseexpress Total TSP2609 730-810 (alt Ingco 1,440)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAFETY GOOGLES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blue Eagle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mjstraders + hacsons Blue Eagle NP102 350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 DRAWER TOOL TROLLEY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ktools Total 7-drawer roller cabinet THRC02071P 85,000-87,000 (oos) -- Licota PK mein nahi; alt Stanley 7-drawer ktools 135,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spec/pack/stock farq - source dekho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOUBLE OPEN RING OFFSET WRENCH SET (12PCS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart Harden double ring 6-32 12pc 15,190 (alt Ingco offset ring 12pc hetools 10,390)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOUBLE OPEN END WRENCH 6 TO 32 (12 PCS SET)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart Harden DOE 6-32 12pc 12,630 (alt Ingco HKSPA2142 ingcotool 9,899)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOUBLE OPEN END WRENCH 36X41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart Licota wrench sets (scaled); goldentools.ae Licota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOUBLE OPEN END WRENCH 41X46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMBINATION WRENCH 8 TO 32 (14 PCS SET)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tolsen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">imsons Tolsen 15889 6-32 14pc 11,780; toolexpert 7,500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOCKET SET (113PCS) 1/4" &amp; 1/2"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart Licota 120pc 56,890-67,130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIN PUNCH SET (06PCS SET)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart Licota 6pc pin punch 5,460</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOLLOW PUNCH (3MM-25MM) (15PCS SET)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harden 12pc hollow punch 3-16mm: toolsmart 4,140; ingcotool 4,199-4,699; toolshop 4,399 -- SPEC MISMATCH (3-25 15pc nahi mila)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LONG TYPE HEX KEY WRENCH SET 09 PCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart Licota 9pc long hex 4,400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHORT TYPE HEX KEY WRENCH SET (09PCS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart Harden 9pc short hex 1.5-10mm 1,420</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LONG TYPE HEX WRENCH SET 09 PCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">same as 17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALLEN HEX KEY 12MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">goldentools.ae Licota 12mm AED 250/20pc (~PKR 950 ea)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALLEN (HEX) KEY 14MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">goldentools.ae Licota 12mm (scaled)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALLEN (HEX) KEY 16MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIRCLIP PLIER INTERNAL STRAIGHT 175MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart Licota 4pc snap ring plier set 175mm 11,650 (=int/ext straight/bent, per pc 2,913)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIRCLIP PLIER INTERNAL BENT 175MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">same set</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIRCLIP PLIER EXTERNAL STRAIGHT 175MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIRCLIP PLIER EXTERNAL BENT 175MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIRCLIP PLIER INTERNAL STRAIGHT 230MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart Licota pliers (scaled)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. 230mm circlip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIRCLIP PLIER EXTERNAL STRAIGHT 230MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHISEL SET (05 PCS SET)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart Licota 5pc punch chisel 4,000-4,720</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIPE WRENCH SIZE 10"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart Total 10in pipe wrench 1,700; totaltool 1,400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIPE WRENCH SIZE 12"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart Harden HD 12in pipe wrench 2,850 (alt Total 12in totaltool 1,900)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIPE WRENCH SIZE 18"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart Licota 18in pipe wrench 9,620</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIPE WRENCH SIZE 24"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart Harden 24in pipe wrench 6,560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIPE WRENCH SIZE 36"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">totaltool Total 36in THT171366 7,900 (alt Wiseup toolshub 6,300)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLEDGE HAMMER 1 LBS WITH FIBREGLASS HANDLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart Total 2lb sledge THT79026 2,000; purchaser 1,820 -- SPEC: 2lb (1lb sledge nahi mila)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLEDGE HAMMER 3 LBS WITH FIBREGLASS HANDLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart Harden 3lb sledge fibreglass 590323 3,380 (alt Total 3lb 2,460/purchaser 2,240)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOFT FACE DEAD BLOW HAMMER 50MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pakistanpowertools Harden dead blow 590445 1,987-2,450</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VICE GRIP PLIER 08"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ingcotool locking plier 1,499; Licota premium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. 8in (alt 10in Harden toolsmart 1,660 / Ingco 1,790</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORDLESS IMPACT WRENCH 185NM (Bosch)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bosch Professional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ktools GDX 180-Li 45,000 solo / 79,000 kit; kamadi 75,200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORDLESS IMPACT WRENCH 350N (Bosch)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bosch Professional GDS 18V-350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No PK listing; est from GDX/GDS range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. GDS 18V-350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORDLESS IMPACT WRENCH 1000N (Bosch)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kamadi GDS 18V-1000 kit 143,800; ktools solo 70,000 (oos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEX IMPACT ADAPTOR 1/2" FEMALE TO 1/4" FEMALE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart Licota impact accessories</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLAT FILE 12"</t>
+  </si>
+  <si>
     <t xml:space="preserve">Yato</t>
   </si>
   <si>
-    <t xml:space="preserve">ktools/imartpk Yato</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. single 8mm (ktools Bosch HSS range 520-5,500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MECHANICAL JACK 03 TONS (Japan or germany)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAFETY HELMET (WHITE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">powerhouseexpress Total TSP2609 730-810 (alt Ingco 1,440)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAFETY GOOGLES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blue Eagle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mjstraders + hacsons Blue Eagle NP102 350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 DRAWER TOOL TROLLEY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ktools Total 7-drawer roller cabinet THRC02071P 85,000-87,000 (oos) -- Licota PK mein nahi; alt Stanley 7-drawer ktools 135,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spec/pack/stock farq - source dekho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOUBLE OPEN RING OFFSET WRENCH SET (12PCS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Harden double ring 6-32 12pc 15,190 (alt Ingco offset ring 12pc hetools 10,390)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOUBLE OPEN END WRENCH 6 TO 32 (12 PCS SET)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Harden DOE 6-32 12pc 12,630 (alt Ingco HKSPA2142 ingcotool 9,899)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOUBLE OPEN END WRENCH 36X41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Licota wrench sets (scaled); goldentools.ae Licota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOUBLE OPEN END WRENCH 41X46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMBINATION WRENCH 8 TO 32 (14 PCS SET)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tolsen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">imsons Tolsen 15889 6-32 14pc 11,780; toolexpert 7,500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOCKET SET (113PCS) 1/4" &amp; 1/2"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Licota 120pc 56,890-67,130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIN PUNCH SET (06PCS SET)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Licota 6pc pin punch 5,460</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOLLOW PUNCH (3MM-25MM) (15PCS SET)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harden 12pc hollow punch 3-16mm: toolsmart 4,140; ingcotool 4,199-4,699; toolshop 4,399 -- SPEC MISMATCH (3-25 15pc nahi mila)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LONG TYPE HEX KEY WRENCH SET 09 PCS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Licota 9pc long hex 4,400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SHORT TYPE HEX KEY WRENCH SET (09PCS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Harden 9pc short hex 1.5-10mm 1,420</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LONG TYPE HEX WRENCH SET 09 PCS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">same as 17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALLEN HEX KEY 12MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">goldentools.ae Licota 12mm AED 250/20pc (~PKR 950 ea)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALLEN (HEX) KEY 14MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">goldentools.ae Licota 12mm (scaled)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALLEN (HEX) KEY 16MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIRCLIP PLIER INTERNAL STRAIGHT 175MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Licota 4pc snap ring plier set 175mm 11,650 (=int/ext straight/bent, per pc 2,913)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIRCLIP PLIER INTERNAL BENT 175MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">same set</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIRCLIP PLIER EXTERNAL STRAIGHT 175MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIRCLIP PLIER EXTERNAL BENT 175MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIRCLIP PLIER INTERNAL STRAIGHT 230MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Licota pliers (scaled)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. 230mm circlip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIRCLIP PLIER EXTERNAL STRAIGHT 230MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHISEL SET (05 PCS SET)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Licota 5pc punch chisel 4,000-4,720</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIPE WRENCH SIZE 10"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Total 10in pipe wrench 1,700; totaltool 1,400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIPE WRENCH SIZE 12"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Harden HD 12in pipe wrench 2,850 (alt Total 12in totaltool 1,900)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIPE WRENCH SIZE 18"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Licota 18in pipe wrench 9,620</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIPE WRENCH SIZE 24"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Harden 24in pipe wrench 6,560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIPE WRENCH SIZE 36"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">totaltool Total 36in THT171366 7,900 (alt Wiseup toolshub 6,300)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLEDGE HAMMER 1 LBS WITH FIBREGLASS HANDLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Total 2lb sledge THT79026 2,000; purchaser 1,820 -- SPEC: 2lb (1lb sledge nahi mila)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLEDGE HAMMER 3 LBS WITH FIBREGLASS HANDLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Harden 3lb sledge fibreglass 590323 3,380 (alt Total 3lb 2,460/purchaser 2,240)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOFT FACE DEAD BLOW HAMMER 50MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pakistanpowertools Harden dead blow 590445 1,987-2,450</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VICE GRIP PLIER 08"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ingcotool locking plier 1,499; Licota premium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. 8in (alt 10in Harden toolsmart 1,660 / Ingco 1,790</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORDLESS IMPACT WRENCH 185NM (Bosch)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bosch Professional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ktools GDX 180-Li 45,000 solo / 79,000 kit; kamadi 75,200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORDLESS IMPACT WRENCH 350N (Bosch)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bosch Professional GDS 18V-350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No PK listing; est from GDX/GDS range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. GDS 18V-350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORDLESS IMPACT WRENCH 1000N (Bosch)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kamadi GDS 18V-1000 kit 143,800; ktools solo 70,000 (oos)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HEX IMPACT ADAPTOR 1/2" FEMALE TO 1/4" FEMALE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Licota impact accessories</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLAT FILE 12"</t>
-  </si>
-  <si>
     <t xml:space="preserve">zeeshanhardware Yato YT-6190 12in 1,750</t>
   </si>
   <si>
@@ -549,60 +552,108 @@
     <t xml:space="preserve">HSS COBALT DRILL SET 1-13MM 25 PCS</t>
   </si>
   <si>
-    <t xml:space="preserve">pakistanpowertools Ingco AKD1251 25pc 1-13mm 22,185; almirajtrading 15,968 -- SPEC: M2 HSS not cobalt</t>
+    <t xml:space="preserve">Dormer A095 (HSS-Co)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dormer 25pc 1-13mm set - PK listing n/a (UK/US list scaled)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Dormer 25pc cobalt set; alt Ingco AKD1251 M2 22,185</t>
   </si>
   <si>
     <t xml:space="preserve">HSS DRILL BITS 1/16-1/2" 29 PCS SET</t>
   </si>
   <si>
+    <t xml:space="preserve">Dormer A095 (A002 x29)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mrosupply Dormer A09518 29pc set (USD) scaled - PK listing n/a</t>
+  </si>
+  <si>
     <t xml:space="preserve">Online nahi mila - dealer quote chahiye. 29pc inch set</t>
   </si>
   <si>
     <t xml:space="preserve">HSS DRILL BIT 14MM TAPER SHANK</t>
   </si>
   <si>
-    <t xml:space="preserve">Dormer / YG-1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Market; India Dormer ref</t>
+    <t xml:space="preserve">Dormer A130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dormer A130 14mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
   </si>
   <si>
     <t xml:space="preserve">HSS DRILL BIT 15MM TAPER SHANK</t>
   </si>
   <si>
+    <t xml:space="preserve">Dormer A130 15mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
+  </si>
+  <si>
     <t xml:space="preserve">HSS DRILL BIT 15.5MM TAPER SHANK</t>
   </si>
   <si>
+    <t xml:space="preserve">Dormer A130 15.5mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
+  </si>
+  <si>
     <t xml:space="preserve">HSS DRILL BIT 16MM TAPER SHANK</t>
   </si>
   <si>
+    <t xml:space="preserve">Dormer A130 16mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
+  </si>
+  <si>
     <t xml:space="preserve">HSS DRILL BIT 16.5MM TAPER SHANK</t>
   </si>
   <si>
+    <t xml:space="preserve">Dormer A130 16.5mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
+  </si>
+  <si>
     <t xml:space="preserve">HSS DRILL BIT 17MM TAPER SHANK</t>
   </si>
   <si>
+    <t xml:space="preserve">Dormer A130 17mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
+  </si>
+  <si>
     <t xml:space="preserve">HSS DRILL BIT 17.5MM TAPER SHANK</t>
   </si>
   <si>
+    <t xml:space="preserve">Dormer A130 17.5mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
+  </si>
+  <si>
     <t xml:space="preserve">HSS DRILL BIT 19MM TAPER SHANK</t>
   </si>
   <si>
+    <t xml:space="preserve">Dormer A130 19mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
+  </si>
+  <si>
     <t xml:space="preserve">HSS DRILL BIT 21MM TAPER SHANK</t>
   </si>
   <si>
+    <t xml:space="preserve">Dormer A130 21mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
+  </si>
+  <si>
     <t xml:space="preserve">HSS DRILL BIT 25MM TAPER SHANK</t>
   </si>
   <si>
+    <t xml:space="preserve">Dormer A130 25mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
+  </si>
+  <si>
     <t xml:space="preserve">HSS DRILL BIT 30MM TAPER SHANK</t>
   </si>
   <si>
+    <t xml:space="preserve">Dormer A130 30mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
+  </si>
+  <si>
     <t xml:space="preserve">HSS DRILL BIT 32MM TAPER SHANK</t>
   </si>
   <si>
+    <t xml:space="preserve">Dormer A130 32mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
+  </si>
+  <si>
     <t xml:space="preserve">HSS DRILL BIT 35MM TAPER SHANK</t>
   </si>
   <si>
+    <t xml:space="preserve">Dormer A130 35mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
+  </si>
+  <si>
     <t xml:space="preserve">MORSE TAPER EXTENSION SOCKET SLEEVE ADAPT</t>
   </si>
   <si>
@@ -1113,7 +1164,10 @@
     <t xml:space="preserve">END MILL CUTTER SIZE 5MM</t>
   </si>
   <si>
-    <t xml:space="preserve">YG-1 / Taiwan HSS-Co</t>
+    <t xml:space="preserve">Dormer C-series HSS-Co</t>
+  </si>
+  <si>
+    <t xml:space="preserve">khmtools.com.ph Dormer C247 4mm 1,010 / 8mm 1,400 PHP scaled x4.95 (+30%)</t>
   </si>
   <si>
     <t xml:space="preserve">END MILL CUTTER SIZE 6MM</t>
@@ -1194,7 +1248,7 @@
     <t xml:space="preserve">HSS TOOL 08X08X200MM</t>
   </si>
   <si>
-    <t xml:space="preserve">Taiwan HSS / Dormer</t>
+    <t xml:space="preserve">Dormer HSS toolbit - PK listing n/a, est ~1.8x generic</t>
   </si>
   <si>
     <t xml:space="preserve">HSS TOOL 10MMX10MMX200MM</t>
@@ -1273,6 +1327,9 @@
   </si>
   <si>
     <t xml:space="preserve">DRILL BIT 4MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart.pk Dormer A002 1-10mm from 900</t>
   </si>
   <si>
     <t xml:space="preserve">Online nahi mila - dealer quote chahiye. single 4mm</t>
@@ -2417,22 +2474,22 @@
         <v>37</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>350</v>
+        <v>1500</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>500</v>
+        <v>2500</v>
       </c>
       <c r="I9" s="10" t="n">
         <f aca="false">IF(E9=0,0,(E9-H9)/E9)</f>
-        <v>0.300699300699301</v>
+        <v>-2.4965034965035</v>
       </c>
       <c r="J9" s="6" t="str">
         <f aca="false">IF(E9&lt;G9,"LOSS",IF(E9&lt;H9*1.1,"THIN / RISK",IF(E9&gt;H9*1.8,"OVERPRICED?","OK")))</f>
-        <v>OK</v>
+        <v>LOSS</v>
       </c>
       <c r="K9" s="8" t="n">
         <f aca="false">IF(J9="OVERPRICED?",ROUND(H9*1.35,-1),MAX(E9,ROUND(H9*(1+$E$3),-1)))</f>
-        <v>715</v>
+        <v>2880</v>
       </c>
       <c r="L9" s="8" t="n">
         <f aca="false">D9*E9</f>
@@ -2440,11 +2497,11 @@
       </c>
       <c r="M9" s="8" t="n">
         <f aca="false">D9*K9</f>
-        <v>35750</v>
+        <v>144000</v>
       </c>
       <c r="N9" s="8" t="n">
         <f aca="false">D9*H9</f>
-        <v>25000</v>
+        <v>125000</v>
       </c>
       <c r="O9" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C9,F9)),"","YES")</f>
@@ -4823,7 +4880,7 @@
         <v>1950</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="G48" s="9" t="n">
         <v>1750</v>
@@ -4863,7 +4920,7 @@
         <v>43</v>
       </c>
       <c r="Q48" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="R48" s="7"/>
     </row>
@@ -4872,7 +4929,7 @@
         <v>45</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>28</v>
@@ -4884,7 +4941,7 @@
         <v>2210</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="G49" s="9" t="n">
         <v>1750</v>
@@ -4924,10 +4981,10 @@
         <v>24</v>
       </c>
       <c r="Q49" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="R49" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4935,7 +4992,7 @@
         <v>47</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>28</v>
@@ -4987,7 +5044,7 @@
         <v>24</v>
       </c>
       <c r="Q50" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="R50" s="7" t="s">
         <v>31</v>
@@ -4998,7 +5055,7 @@
         <v>48</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>28</v>
@@ -5050,7 +5107,7 @@
         <v>24</v>
       </c>
       <c r="Q51" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R51" s="7" t="s">
         <v>31</v>
@@ -5061,7 +5118,7 @@
         <v>49</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>28</v>
@@ -5113,7 +5170,7 @@
         <v>24</v>
       </c>
       <c r="Q52" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R52" s="7" t="s">
         <v>31</v>
@@ -5124,7 +5181,7 @@
         <v>50</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>28</v>
@@ -5176,7 +5233,7 @@
         <v>24</v>
       </c>
       <c r="Q53" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R53" s="7" t="s">
         <v>31</v>
@@ -5187,7 +5244,7 @@
         <v>51</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>28</v>
@@ -5239,7 +5296,7 @@
         <v>24</v>
       </c>
       <c r="Q54" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="R54" s="7" t="s">
         <v>31</v>
@@ -5250,7 +5307,7 @@
         <v>52</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>28</v>
@@ -5262,7 +5319,7 @@
         <v>18200</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="G55" s="9" t="n">
         <v>8500</v>
@@ -5302,7 +5359,7 @@
         <v>49</v>
       </c>
       <c r="Q55" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="R55" s="7" t="s">
         <v>51</v>
@@ -5313,7 +5370,7 @@
         <v>53</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>28</v>
@@ -5325,7 +5382,7 @@
         <v>23400</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="G56" s="9" t="n">
         <v>19030</v>
@@ -5365,7 +5422,7 @@
         <v>49</v>
       </c>
       <c r="Q56" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="R56" s="7" t="s">
         <v>51</v>
@@ -5376,7 +5433,7 @@
         <v>54</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>112</v>
@@ -5428,7 +5485,7 @@
         <v>43</v>
       </c>
       <c r="Q57" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="R57" s="7"/>
     </row>
@@ -5437,7 +5494,7 @@
         <v>55</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>28</v>
@@ -5449,7 +5506,7 @@
         <v>15600</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G58" s="9" t="n">
         <v>12000</v>
@@ -5489,10 +5546,10 @@
         <v>24</v>
       </c>
       <c r="Q58" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R58" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5500,7 +5557,7 @@
         <v>56</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>28</v>
@@ -5552,10 +5609,10 @@
         <v>24</v>
       </c>
       <c r="Q59" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="R59" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5563,7 +5620,7 @@
         <v>57</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>28</v>
@@ -5615,7 +5672,7 @@
         <v>43</v>
       </c>
       <c r="Q60" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="R60" s="7"/>
     </row>
@@ -5624,7 +5681,7 @@
         <v>58</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>28</v>
@@ -5676,7 +5733,7 @@
         <v>24</v>
       </c>
       <c r="Q61" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R61" s="7" t="s">
         <v>31</v>
@@ -5687,7 +5744,7 @@
         <v>59</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>28</v>
@@ -5739,7 +5796,7 @@
         <v>24</v>
       </c>
       <c r="Q62" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R62" s="7" t="s">
         <v>31</v>
@@ -5750,7 +5807,7 @@
         <v>60</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>28</v>
@@ -5762,7 +5819,7 @@
         <v>9100</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="G63" s="9" t="n">
         <v>8000</v>
@@ -5802,10 +5859,10 @@
         <v>24</v>
       </c>
       <c r="Q63" s="7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="R63" s="7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5813,7 +5870,7 @@
         <v>61</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>28</v>
@@ -5825,7 +5882,7 @@
         <v>5850</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G64" s="9" t="n">
         <v>5920</v>
@@ -5865,7 +5922,7 @@
         <v>43</v>
       </c>
       <c r="Q64" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="R64" s="7"/>
     </row>
@@ -5874,7 +5931,7 @@
         <v>62</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>28</v>
@@ -5926,10 +5983,10 @@
         <v>24</v>
       </c>
       <c r="Q65" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R65" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5937,7 +5994,7 @@
         <v>63</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>28</v>
@@ -5989,7 +6046,7 @@
         <v>43</v>
       </c>
       <c r="Q66" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="R66" s="7"/>
     </row>
@@ -5998,7 +6055,7 @@
         <v>64</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>28</v>
@@ -6010,7 +6067,7 @@
         <v>1560</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="G67" s="9" t="n">
         <v>1350</v>
@@ -6050,7 +6107,7 @@
         <v>43</v>
       </c>
       <c r="Q67" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="R67" s="7"/>
     </row>
@@ -6059,7 +6116,7 @@
         <v>65</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>28</v>
@@ -6071,7 +6128,7 @@
         <v>1560</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="G68" s="9" t="n">
         <v>1350</v>
@@ -6111,7 +6168,7 @@
         <v>43</v>
       </c>
       <c r="Q68" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="R68" s="7"/>
     </row>
@@ -6120,7 +6177,7 @@
         <v>66</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>28</v>
@@ -6132,7 +6189,7 @@
         <v>11700</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G69" s="9" t="n">
         <v>14000</v>
@@ -6172,7 +6229,7 @@
         <v>24</v>
       </c>
       <c r="Q69" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R69" s="7" t="s">
         <v>31</v>
@@ -6183,7 +6240,7 @@
         <v>67</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>28</v>
@@ -6195,7 +6252,7 @@
         <v>9750</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G70" s="9" t="n">
         <v>12000</v>
@@ -6235,7 +6292,7 @@
         <v>24</v>
       </c>
       <c r="Q70" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R70" s="7" t="s">
         <v>31</v>
@@ -6246,7 +6303,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>28</v>
@@ -6258,7 +6315,7 @@
         <v>23400</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G71" s="9" t="n">
         <v>15000</v>
@@ -6298,7 +6355,7 @@
         <v>24</v>
       </c>
       <c r="Q71" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R71" s="7" t="s">
         <v>31</v>
@@ -6309,7 +6366,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>28</v>
@@ -6321,7 +6378,7 @@
         <v>32500</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G72" s="9" t="n">
         <v>25000</v>
@@ -6361,7 +6418,7 @@
         <v>24</v>
       </c>
       <c r="Q72" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R72" s="7" t="s">
         <v>31</v>
@@ -6372,7 +6429,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>28</v>
@@ -6424,16 +6481,16 @@
         <v>43</v>
       </c>
       <c r="Q73" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="R73" s="7"/>
     </row>
-    <row r="74" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="6" t="n">
         <v>73</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>28</v>
@@ -6445,25 +6502,25 @@
         <v>45500</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>22185</v>
+        <v>35000</v>
       </c>
       <c r="H74" s="9" t="n">
-        <v>22185</v>
+        <v>55000</v>
       </c>
       <c r="I74" s="10" t="n">
         <f aca="false">IF(E74=0,0,(E74-H74)/E74)</f>
-        <v>0.512417582417582</v>
+        <v>-0.208791208791209</v>
       </c>
       <c r="J74" s="6" t="str">
         <f aca="false">IF(E74&lt;G74,"LOSS",IF(E74&lt;H74*1.1,"THIN / RISK",IF(E74&gt;H74*1.8,"OVERPRICED?","OK")))</f>
-        <v>OVERPRICED?</v>
+        <v>THIN / RISK</v>
       </c>
       <c r="K74" s="8" t="n">
         <f aca="false">IF(J74="OVERPRICED?",ROUND(H74*1.35,-1),MAX(E74,ROUND(H74*(1+$E$3),-1)))</f>
-        <v>29950</v>
+        <v>63250</v>
       </c>
       <c r="L74" s="8" t="n">
         <f aca="false">D74*E74</f>
@@ -6471,24 +6528,24 @@
       </c>
       <c r="M74" s="8" t="n">
         <f aca="false">D74*K74</f>
-        <v>29950</v>
+        <v>63250</v>
       </c>
       <c r="N74" s="8" t="n">
         <f aca="false">D74*H74</f>
-        <v>22185</v>
+        <v>55000</v>
       </c>
       <c r="O74" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C74,F74)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="Q74" s="7" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="R74" s="7" t="s">
-        <v>51</v>
+        <v>177</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6496,7 +6553,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>28</v>
@@ -6508,25 +6565,25 @@
         <v>23400</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>37</v>
+        <v>179</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>12000</v>
+        <v>45000</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>18000</v>
+        <v>70000</v>
       </c>
       <c r="I75" s="10" t="n">
         <f aca="false">IF(E75=0,0,(E75-H75)/E75)</f>
-        <v>0.230769230769231</v>
+        <v>-1.99145299145299</v>
       </c>
       <c r="J75" s="6" t="str">
         <f aca="false">IF(E75&lt;G75,"LOSS",IF(E75&lt;H75*1.1,"THIN / RISK",IF(E75&gt;H75*1.8,"OVERPRICED?","OK")))</f>
-        <v>OK</v>
+        <v>LOSS</v>
       </c>
       <c r="K75" s="8" t="n">
         <f aca="false">IF(J75="OVERPRICED?",ROUND(H75*1.35,-1),MAX(E75,ROUND(H75*(1+$E$3),-1)))</f>
-        <v>23400</v>
+        <v>80500</v>
       </c>
       <c r="L75" s="8" t="n">
         <f aca="false">D75*E75</f>
@@ -6534,11 +6591,11 @@
       </c>
       <c r="M75" s="8" t="n">
         <f aca="false">D75*K75</f>
-        <v>46800</v>
+        <v>161000</v>
       </c>
       <c r="N75" s="8" t="n">
         <f aca="false">D75*H75</f>
-        <v>36000</v>
+        <v>140000</v>
       </c>
       <c r="O75" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C75,F75)),"","YES")</f>
@@ -6548,18 +6605,18 @@
         <v>24</v>
       </c>
       <c r="Q75" s="7" t="s">
-        <v>38</v>
+        <v>180</v>
       </c>
       <c r="R75" s="7" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="6" t="n">
         <v>75</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>28</v>
@@ -6571,17 +6628,17 @@
         <v>1950</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>2500</v>
+        <v>9790</v>
       </c>
       <c r="H76" s="9" t="n">
-        <v>3200</v>
+        <v>12730</v>
       </c>
       <c r="I76" s="10" t="n">
         <f aca="false">IF(E76=0,0,(E76-H76)/E76)</f>
-        <v>-0.641025641025641</v>
+        <v>-5.52820512820513</v>
       </c>
       <c r="J76" s="6" t="str">
         <f aca="false">IF(E76&lt;G76,"LOSS",IF(E76&lt;H76*1.1,"THIN / RISK",IF(E76&gt;H76*1.8,"OVERPRICED?","OK")))</f>
@@ -6589,7 +6646,7 @@
       </c>
       <c r="K76" s="8" t="n">
         <f aca="false">IF(J76="OVERPRICED?",ROUND(H76*1.35,-1),MAX(E76,ROUND(H76*(1+$E$3),-1)))</f>
-        <v>3680</v>
+        <v>14640</v>
       </c>
       <c r="L76" s="8" t="n">
         <f aca="false">D76*E76</f>
@@ -6597,11 +6654,11 @@
       </c>
       <c r="M76" s="8" t="n">
         <f aca="false">D76*K76</f>
-        <v>7360</v>
+        <v>29280</v>
       </c>
       <c r="N76" s="8" t="n">
         <f aca="false">D76*H76</f>
-        <v>6400</v>
+        <v>25460</v>
       </c>
       <c r="O76" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C76,F76)),"","YES")</f>
@@ -6611,18 +6668,18 @@
         <v>24</v>
       </c>
       <c r="Q76" s="7" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="R76" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="6" t="n">
         <v>76</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>28</v>
@@ -6634,17 +6691,17 @@
         <v>2080</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>2700</v>
+        <v>11060</v>
       </c>
       <c r="H77" s="9" t="n">
-        <v>3400</v>
+        <v>14380</v>
       </c>
       <c r="I77" s="10" t="n">
         <f aca="false">IF(E77=0,0,(E77-H77)/E77)</f>
-        <v>-0.634615384615385</v>
+        <v>-5.91346153846154</v>
       </c>
       <c r="J77" s="6" t="str">
         <f aca="false">IF(E77&lt;G77,"LOSS",IF(E77&lt;H77*1.1,"THIN / RISK",IF(E77&gt;H77*1.8,"OVERPRICED?","OK")))</f>
@@ -6652,7 +6709,7 @@
       </c>
       <c r="K77" s="8" t="n">
         <f aca="false">IF(J77="OVERPRICED?",ROUND(H77*1.35,-1),MAX(E77,ROUND(H77*(1+$E$3),-1)))</f>
-        <v>3910</v>
+        <v>16540</v>
       </c>
       <c r="L77" s="8" t="n">
         <f aca="false">D77*E77</f>
@@ -6660,11 +6717,11 @@
       </c>
       <c r="M77" s="8" t="n">
         <f aca="false">D77*K77</f>
-        <v>7820</v>
+        <v>33080</v>
       </c>
       <c r="N77" s="8" t="n">
         <f aca="false">D77*H77</f>
-        <v>6800</v>
+        <v>28760</v>
       </c>
       <c r="O77" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C77,F77)),"","YES")</f>
@@ -6674,18 +6731,18 @@
         <v>24</v>
       </c>
       <c r="Q77" s="7" t="s">
-        <v>143</v>
+        <v>186</v>
       </c>
       <c r="R77" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="6" t="n">
         <v>77</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>28</v>
@@ -6697,17 +6754,17 @@
         <v>2210</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="G78" s="9" t="n">
-        <v>2800</v>
+        <v>11700</v>
       </c>
       <c r="H78" s="9" t="n">
-        <v>3600</v>
+        <v>15210</v>
       </c>
       <c r="I78" s="10" t="n">
         <f aca="false">IF(E78=0,0,(E78-H78)/E78)</f>
-        <v>-0.6289592760181</v>
+        <v>-5.88235294117647</v>
       </c>
       <c r="J78" s="6" t="str">
         <f aca="false">IF(E78&lt;G78,"LOSS",IF(E78&lt;H78*1.1,"THIN / RISK",IF(E78&gt;H78*1.8,"OVERPRICED?","OK")))</f>
@@ -6715,7 +6772,7 @@
       </c>
       <c r="K78" s="8" t="n">
         <f aca="false">IF(J78="OVERPRICED?",ROUND(H78*1.35,-1),MAX(E78,ROUND(H78*(1+$E$3),-1)))</f>
-        <v>4140</v>
+        <v>17490</v>
       </c>
       <c r="L78" s="8" t="n">
         <f aca="false">D78*E78</f>
@@ -6723,11 +6780,11 @@
       </c>
       <c r="M78" s="8" t="n">
         <f aca="false">D78*K78</f>
-        <v>8280</v>
+        <v>34980</v>
       </c>
       <c r="N78" s="8" t="n">
         <f aca="false">D78*H78</f>
-        <v>7200</v>
+        <v>30420</v>
       </c>
       <c r="O78" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C78,F78)),"","YES")</f>
@@ -6737,18 +6794,18 @@
         <v>24</v>
       </c>
       <c r="Q78" s="7" t="s">
-        <v>143</v>
+        <v>188</v>
       </c>
       <c r="R78" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="6" t="n">
         <v>78</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>28</v>
@@ -6760,17 +6817,17 @@
         <v>2340</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="G79" s="9" t="n">
-        <v>3000</v>
+        <v>12330</v>
       </c>
       <c r="H79" s="9" t="n">
-        <v>3800</v>
+        <v>16030</v>
       </c>
       <c r="I79" s="10" t="n">
         <f aca="false">IF(E79=0,0,(E79-H79)/E79)</f>
-        <v>-0.623931623931624</v>
+        <v>-5.85042735042735</v>
       </c>
       <c r="J79" s="6" t="str">
         <f aca="false">IF(E79&lt;G79,"LOSS",IF(E79&lt;H79*1.1,"THIN / RISK",IF(E79&gt;H79*1.8,"OVERPRICED?","OK")))</f>
@@ -6778,7 +6835,7 @@
       </c>
       <c r="K79" s="8" t="n">
         <f aca="false">IF(J79="OVERPRICED?",ROUND(H79*1.35,-1),MAX(E79,ROUND(H79*(1+$E$3),-1)))</f>
-        <v>4370</v>
+        <v>18430</v>
       </c>
       <c r="L79" s="8" t="n">
         <f aca="false">D79*E79</f>
@@ -6786,11 +6843,11 @@
       </c>
       <c r="M79" s="8" t="n">
         <f aca="false">D79*K79</f>
-        <v>8740</v>
+        <v>36860</v>
       </c>
       <c r="N79" s="8" t="n">
         <f aca="false">D79*H79</f>
-        <v>7600</v>
+        <v>32060</v>
       </c>
       <c r="O79" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C79,F79)),"","YES")</f>
@@ -6800,18 +6857,18 @@
         <v>24</v>
       </c>
       <c r="Q79" s="7" t="s">
-        <v>143</v>
+        <v>190</v>
       </c>
       <c r="R79" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="6" t="n">
         <v>79</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>28</v>
@@ -6823,17 +6880,17 @@
         <v>2470</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>3100</v>
+        <v>12970</v>
       </c>
       <c r="H80" s="9" t="n">
-        <v>4000</v>
+        <v>16860</v>
       </c>
       <c r="I80" s="10" t="n">
         <f aca="false">IF(E80=0,0,(E80-H80)/E80)</f>
-        <v>-0.619433198380567</v>
+        <v>-5.82591093117409</v>
       </c>
       <c r="J80" s="6" t="str">
         <f aca="false">IF(E80&lt;G80,"LOSS",IF(E80&lt;H80*1.1,"THIN / RISK",IF(E80&gt;H80*1.8,"OVERPRICED?","OK")))</f>
@@ -6841,7 +6898,7 @@
       </c>
       <c r="K80" s="8" t="n">
         <f aca="false">IF(J80="OVERPRICED?",ROUND(H80*1.35,-1),MAX(E80,ROUND(H80*(1+$E$3),-1)))</f>
-        <v>4600</v>
+        <v>19390</v>
       </c>
       <c r="L80" s="8" t="n">
         <f aca="false">D80*E80</f>
@@ -6849,11 +6906,11 @@
       </c>
       <c r="M80" s="8" t="n">
         <f aca="false">D80*K80</f>
-        <v>9200</v>
+        <v>38780</v>
       </c>
       <c r="N80" s="8" t="n">
         <f aca="false">D80*H80</f>
-        <v>8000</v>
+        <v>33720</v>
       </c>
       <c r="O80" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C80,F80)),"","YES")</f>
@@ -6863,18 +6920,18 @@
         <v>24</v>
       </c>
       <c r="Q80" s="7" t="s">
-        <v>143</v>
+        <v>192</v>
       </c>
       <c r="R80" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="6" t="n">
         <v>80</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>28</v>
@@ -6886,17 +6943,17 @@
         <v>2600</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>3300</v>
+        <v>13600</v>
       </c>
       <c r="H81" s="9" t="n">
-        <v>4200</v>
+        <v>17680</v>
       </c>
       <c r="I81" s="10" t="n">
         <f aca="false">IF(E81=0,0,(E81-H81)/E81)</f>
-        <v>-0.615384615384615</v>
+        <v>-5.8</v>
       </c>
       <c r="J81" s="6" t="str">
         <f aca="false">IF(E81&lt;G81,"LOSS",IF(E81&lt;H81*1.1,"THIN / RISK",IF(E81&gt;H81*1.8,"OVERPRICED?","OK")))</f>
@@ -6904,7 +6961,7 @@
       </c>
       <c r="K81" s="8" t="n">
         <f aca="false">IF(J81="OVERPRICED?",ROUND(H81*1.35,-1),MAX(E81,ROUND(H81*(1+$E$3),-1)))</f>
-        <v>4830</v>
+        <v>20330</v>
       </c>
       <c r="L81" s="8" t="n">
         <f aca="false">D81*E81</f>
@@ -6912,11 +6969,11 @@
       </c>
       <c r="M81" s="8" t="n">
         <f aca="false">D81*K81</f>
-        <v>9660</v>
+        <v>40660</v>
       </c>
       <c r="N81" s="8" t="n">
         <f aca="false">D81*H81</f>
-        <v>8400</v>
+        <v>35360</v>
       </c>
       <c r="O81" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C81,F81)),"","YES")</f>
@@ -6926,18 +6983,18 @@
         <v>24</v>
       </c>
       <c r="Q81" s="7" t="s">
-        <v>143</v>
+        <v>194</v>
       </c>
       <c r="R81" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="6" t="n">
         <v>81</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>28</v>
@@ -6949,17 +7006,17 @@
         <v>2730</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>3500</v>
+        <v>14240</v>
       </c>
       <c r="H82" s="9" t="n">
-        <v>4400</v>
+        <v>18510</v>
       </c>
       <c r="I82" s="10" t="n">
         <f aca="false">IF(E82=0,0,(E82-H82)/E82)</f>
-        <v>-0.611721611721612</v>
+        <v>-5.78021978021978</v>
       </c>
       <c r="J82" s="6" t="str">
         <f aca="false">IF(E82&lt;G82,"LOSS",IF(E82&lt;H82*1.1,"THIN / RISK",IF(E82&gt;H82*1.8,"OVERPRICED?","OK")))</f>
@@ -6967,7 +7024,7 @@
       </c>
       <c r="K82" s="8" t="n">
         <f aca="false">IF(J82="OVERPRICED?",ROUND(H82*1.35,-1),MAX(E82,ROUND(H82*(1+$E$3),-1)))</f>
-        <v>5060</v>
+        <v>21290</v>
       </c>
       <c r="L82" s="8" t="n">
         <f aca="false">D82*E82</f>
@@ -6975,11 +7032,11 @@
       </c>
       <c r="M82" s="8" t="n">
         <f aca="false">D82*K82</f>
-        <v>10120</v>
+        <v>42580</v>
       </c>
       <c r="N82" s="8" t="n">
         <f aca="false">D82*H82</f>
-        <v>8800</v>
+        <v>37020</v>
       </c>
       <c r="O82" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C82,F82)),"","YES")</f>
@@ -6989,18 +7046,18 @@
         <v>24</v>
       </c>
       <c r="Q82" s="7" t="s">
-        <v>143</v>
+        <v>196</v>
       </c>
       <c r="R82" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="6" t="n">
         <v>82</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>28</v>
@@ -7012,17 +7069,17 @@
         <v>3250</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>4000</v>
+        <v>16140</v>
       </c>
       <c r="H83" s="9" t="n">
-        <v>5000</v>
+        <v>20990</v>
       </c>
       <c r="I83" s="10" t="n">
         <f aca="false">IF(E83=0,0,(E83-H83)/E83)</f>
-        <v>-0.538461538461538</v>
+        <v>-5.45846153846154</v>
       </c>
       <c r="J83" s="6" t="str">
         <f aca="false">IF(E83&lt;G83,"LOSS",IF(E83&lt;H83*1.1,"THIN / RISK",IF(E83&gt;H83*1.8,"OVERPRICED?","OK")))</f>
@@ -7030,7 +7087,7 @@
       </c>
       <c r="K83" s="8" t="n">
         <f aca="false">IF(J83="OVERPRICED?",ROUND(H83*1.35,-1),MAX(E83,ROUND(H83*(1+$E$3),-1)))</f>
-        <v>5750</v>
+        <v>24140</v>
       </c>
       <c r="L83" s="8" t="n">
         <f aca="false">D83*E83</f>
@@ -7038,11 +7095,11 @@
       </c>
       <c r="M83" s="8" t="n">
         <f aca="false">D83*K83</f>
-        <v>11500</v>
+        <v>48280</v>
       </c>
       <c r="N83" s="8" t="n">
         <f aca="false">D83*H83</f>
-        <v>10000</v>
+        <v>41980</v>
       </c>
       <c r="O83" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C83,F83)),"","YES")</f>
@@ -7052,18 +7109,18 @@
         <v>24</v>
       </c>
       <c r="Q83" s="7" t="s">
-        <v>143</v>
+        <v>198</v>
       </c>
       <c r="R83" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="6" t="n">
         <v>83</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>28</v>
@@ -7075,17 +7132,17 @@
         <v>4160</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>5000</v>
+        <v>19230</v>
       </c>
       <c r="H84" s="9" t="n">
-        <v>6500</v>
+        <v>25000</v>
       </c>
       <c r="I84" s="10" t="n">
         <f aca="false">IF(E84=0,0,(E84-H84)/E84)</f>
-        <v>-0.5625</v>
+        <v>-5.00961538461539</v>
       </c>
       <c r="J84" s="6" t="str">
         <f aca="false">IF(E84&lt;G84,"LOSS",IF(E84&lt;H84*1.1,"THIN / RISK",IF(E84&gt;H84*1.8,"OVERPRICED?","OK")))</f>
@@ -7093,7 +7150,7 @@
       </c>
       <c r="K84" s="8" t="n">
         <f aca="false">IF(J84="OVERPRICED?",ROUND(H84*1.35,-1),MAX(E84,ROUND(H84*(1+$E$3),-1)))</f>
-        <v>7480</v>
+        <v>28750</v>
       </c>
       <c r="L84" s="8" t="n">
         <f aca="false">D84*E84</f>
@@ -7101,11 +7158,11 @@
       </c>
       <c r="M84" s="8" t="n">
         <f aca="false">D84*K84</f>
-        <v>7480</v>
+        <v>28750</v>
       </c>
       <c r="N84" s="8" t="n">
         <f aca="false">D84*H84</f>
-        <v>6500</v>
+        <v>25000</v>
       </c>
       <c r="O84" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C84,F84)),"","YES")</f>
@@ -7115,18 +7172,18 @@
         <v>24</v>
       </c>
       <c r="Q84" s="7" t="s">
-        <v>143</v>
+        <v>200</v>
       </c>
       <c r="R84" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="6" t="n">
         <v>84</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>28</v>
@@ -7138,17 +7195,17 @@
         <v>5850</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>6500</v>
+        <v>26490</v>
       </c>
       <c r="H85" s="9" t="n">
-        <v>8500</v>
+        <v>34430</v>
       </c>
       <c r="I85" s="10" t="n">
         <f aca="false">IF(E85=0,0,(E85-H85)/E85)</f>
-        <v>-0.452991452991453</v>
+        <v>-4.88547008547009</v>
       </c>
       <c r="J85" s="6" t="str">
         <f aca="false">IF(E85&lt;G85,"LOSS",IF(E85&lt;H85*1.1,"THIN / RISK",IF(E85&gt;H85*1.8,"OVERPRICED?","OK")))</f>
@@ -7156,7 +7213,7 @@
       </c>
       <c r="K85" s="8" t="n">
         <f aca="false">IF(J85="OVERPRICED?",ROUND(H85*1.35,-1),MAX(E85,ROUND(H85*(1+$E$3),-1)))</f>
-        <v>9780</v>
+        <v>39590</v>
       </c>
       <c r="L85" s="8" t="n">
         <f aca="false">D85*E85</f>
@@ -7164,11 +7221,11 @@
       </c>
       <c r="M85" s="8" t="n">
         <f aca="false">D85*K85</f>
-        <v>9780</v>
+        <v>39590</v>
       </c>
       <c r="N85" s="8" t="n">
         <f aca="false">D85*H85</f>
-        <v>8500</v>
+        <v>34430</v>
       </c>
       <c r="O85" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C85,F85)),"","YES")</f>
@@ -7178,18 +7235,18 @@
         <v>24</v>
       </c>
       <c r="Q85" s="7" t="s">
-        <v>143</v>
+        <v>202</v>
       </c>
       <c r="R85" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="6" t="n">
         <v>85</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>28</v>
@@ -7201,17 +7258,17 @@
         <v>8450</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>9500</v>
+        <v>38450</v>
       </c>
       <c r="H86" s="9" t="n">
-        <v>12500</v>
+        <v>49980</v>
       </c>
       <c r="I86" s="10" t="n">
         <f aca="false">IF(E86=0,0,(E86-H86)/E86)</f>
-        <v>-0.479289940828402</v>
+        <v>-4.91479289940828</v>
       </c>
       <c r="J86" s="6" t="str">
         <f aca="false">IF(E86&lt;G86,"LOSS",IF(E86&lt;H86*1.1,"THIN / RISK",IF(E86&gt;H86*1.8,"OVERPRICED?","OK")))</f>
@@ -7219,7 +7276,7 @@
       </c>
       <c r="K86" s="8" t="n">
         <f aca="false">IF(J86="OVERPRICED?",ROUND(H86*1.35,-1),MAX(E86,ROUND(H86*(1+$E$3),-1)))</f>
-        <v>14380</v>
+        <v>57480</v>
       </c>
       <c r="L86" s="8" t="n">
         <f aca="false">D86*E86</f>
@@ -7227,11 +7284,11 @@
       </c>
       <c r="M86" s="8" t="n">
         <f aca="false">D86*K86</f>
-        <v>14380</v>
+        <v>57480</v>
       </c>
       <c r="N86" s="8" t="n">
         <f aca="false">D86*H86</f>
-        <v>12500</v>
+        <v>49980</v>
       </c>
       <c r="O86" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C86,F86)),"","YES")</f>
@@ -7241,18 +7298,18 @@
         <v>24</v>
       </c>
       <c r="Q86" s="7" t="s">
-        <v>143</v>
+        <v>204</v>
       </c>
       <c r="R86" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="6" t="n">
         <v>86</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>28</v>
@@ -7264,17 +7321,17 @@
         <v>9750</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>11000</v>
+        <v>44060</v>
       </c>
       <c r="H87" s="9" t="n">
-        <v>14500</v>
+        <v>57270</v>
       </c>
       <c r="I87" s="10" t="n">
         <f aca="false">IF(E87=0,0,(E87-H87)/E87)</f>
-        <v>-0.487179487179487</v>
+        <v>-4.87384615384615</v>
       </c>
       <c r="J87" s="6" t="str">
         <f aca="false">IF(E87&lt;G87,"LOSS",IF(E87&lt;H87*1.1,"THIN / RISK",IF(E87&gt;H87*1.8,"OVERPRICED?","OK")))</f>
@@ -7282,7 +7339,7 @@
       </c>
       <c r="K87" s="8" t="n">
         <f aca="false">IF(J87="OVERPRICED?",ROUND(H87*1.35,-1),MAX(E87,ROUND(H87*(1+$E$3),-1)))</f>
-        <v>16680</v>
+        <v>65860</v>
       </c>
       <c r="L87" s="8" t="n">
         <f aca="false">D87*E87</f>
@@ -7290,11 +7347,11 @@
       </c>
       <c r="M87" s="8" t="n">
         <f aca="false">D87*K87</f>
-        <v>16680</v>
+        <v>65860</v>
       </c>
       <c r="N87" s="8" t="n">
         <f aca="false">D87*H87</f>
-        <v>14500</v>
+        <v>57270</v>
       </c>
       <c r="O87" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C87,F87)),"","YES")</f>
@@ -7304,18 +7361,18 @@
         <v>24</v>
       </c>
       <c r="Q87" s="7" t="s">
-        <v>143</v>
+        <v>206</v>
       </c>
       <c r="R87" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="6" t="n">
         <v>87</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>28</v>
@@ -7327,17 +7384,17 @@
         <v>11700</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>13500</v>
+        <v>52470</v>
       </c>
       <c r="H88" s="9" t="n">
-        <v>17500</v>
+        <v>68210</v>
       </c>
       <c r="I88" s="10" t="n">
         <f aca="false">IF(E88=0,0,(E88-H88)/E88)</f>
-        <v>-0.495726495726496</v>
+        <v>-4.82991452991453</v>
       </c>
       <c r="J88" s="6" t="str">
         <f aca="false">IF(E88&lt;G88,"LOSS",IF(E88&lt;H88*1.1,"THIN / RISK",IF(E88&gt;H88*1.8,"OVERPRICED?","OK")))</f>
@@ -7345,7 +7402,7 @@
       </c>
       <c r="K88" s="8" t="n">
         <f aca="false">IF(J88="OVERPRICED?",ROUND(H88*1.35,-1),MAX(E88,ROUND(H88*(1+$E$3),-1)))</f>
-        <v>20130</v>
+        <v>78440</v>
       </c>
       <c r="L88" s="8" t="n">
         <f aca="false">D88*E88</f>
@@ -7353,11 +7410,11 @@
       </c>
       <c r="M88" s="8" t="n">
         <f aca="false">D88*K88</f>
-        <v>20130</v>
+        <v>78440</v>
       </c>
       <c r="N88" s="8" t="n">
         <f aca="false">D88*H88</f>
-        <v>17500</v>
+        <v>68210</v>
       </c>
       <c r="O88" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C88,F88)),"","YES")</f>
@@ -7367,7 +7424,7 @@
         <v>24</v>
       </c>
       <c r="Q88" s="7" t="s">
-        <v>143</v>
+        <v>208</v>
       </c>
       <c r="R88" s="7" t="s">
         <v>31</v>
@@ -7378,7 +7435,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>28</v>
@@ -7390,7 +7447,7 @@
         <v>4550</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G89" s="9" t="n">
         <v>3500</v>
@@ -7430,7 +7487,7 @@
         <v>24</v>
       </c>
       <c r="Q89" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R89" s="7" t="s">
         <v>31</v>
@@ -7441,7 +7498,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>28</v>
@@ -7453,7 +7510,7 @@
         <v>5850</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G90" s="9" t="n">
         <v>4500</v>
@@ -7493,7 +7550,7 @@
         <v>24</v>
       </c>
       <c r="Q90" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R90" s="7" t="s">
         <v>31</v>
@@ -7504,7 +7561,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>28</v>
@@ -7516,7 +7573,7 @@
         <v>7150</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G91" s="9" t="n">
         <v>5500</v>
@@ -7556,7 +7613,7 @@
         <v>24</v>
       </c>
       <c r="Q91" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R91" s="7" t="s">
         <v>31</v>
@@ -7567,7 +7624,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>28</v>
@@ -7579,7 +7636,7 @@
         <v>2340</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G92" s="9" t="n">
         <v>2500</v>
@@ -7619,7 +7676,7 @@
         <v>24</v>
       </c>
       <c r="Q92" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R92" s="7" t="s">
         <v>31</v>
@@ -7630,7 +7687,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>28</v>
@@ -7642,7 +7699,7 @@
         <v>2860</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G93" s="9" t="n">
         <v>3000</v>
@@ -7682,7 +7739,7 @@
         <v>24</v>
       </c>
       <c r="Q93" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R93" s="7" t="s">
         <v>31</v>
@@ -7693,10 +7750,10 @@
         <v>93</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D94" s="6" t="n">
         <v>2</v>
@@ -7705,7 +7762,7 @@
         <v>25350</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G94" s="9" t="n">
         <v>18100</v>
@@ -7745,7 +7802,7 @@
         <v>43</v>
       </c>
       <c r="Q94" s="7" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="R94" s="7"/>
     </row>
@@ -7754,10 +7811,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D95" s="6" t="n">
         <v>3</v>
@@ -7766,7 +7823,7 @@
         <v>8138</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G95" s="9" t="n">
         <v>15800</v>
@@ -7806,7 +7863,7 @@
         <v>43</v>
       </c>
       <c r="Q95" s="7" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="R95" s="7"/>
     </row>
@@ -7815,10 +7872,10 @@
         <v>95</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D96" s="6" t="n">
         <v>3</v>
@@ -7827,7 +7884,7 @@
         <v>6370</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G96" s="9" t="n">
         <v>7928</v>
@@ -7867,7 +7924,7 @@
         <v>43</v>
       </c>
       <c r="Q96" s="7" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="R96" s="7"/>
     </row>
@@ -7876,7 +7933,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>28</v>
@@ -7888,7 +7945,7 @@
         <v>14950</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G97" s="9" t="n">
         <v>15000</v>
@@ -7928,10 +7985,10 @@
         <v>24</v>
       </c>
       <c r="Q97" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R97" s="7" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7939,7 +7996,7 @@
         <v>97</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>112</v>
@@ -7991,7 +8048,7 @@
         <v>49</v>
       </c>
       <c r="Q98" s="7" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="R98" s="7" t="s">
         <v>51</v>
@@ -8002,10 +8059,10 @@
         <v>98</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="D99" s="6" t="n">
         <v>1</v>
@@ -8014,7 +8071,7 @@
         <v>15600</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="G99" s="9" t="n">
         <v>12000</v>
@@ -8054,7 +8111,7 @@
         <v>24</v>
       </c>
       <c r="Q99" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R99" s="7" t="s">
         <v>31</v>
@@ -8065,7 +8122,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>28</v>
@@ -8077,7 +8134,7 @@
         <v>11050</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="G100" s="9" t="n">
         <v>8000</v>
@@ -8117,7 +8174,7 @@
         <v>24</v>
       </c>
       <c r="Q100" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R100" s="7" t="s">
         <v>31</v>
@@ -8128,7 +8185,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>28</v>
@@ -8140,7 +8197,7 @@
         <v>9100</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="G101" s="9" t="n">
         <v>6500</v>
@@ -8180,7 +8237,7 @@
         <v>24</v>
       </c>
       <c r="Q101" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R101" s="7" t="s">
         <v>31</v>
@@ -8191,7 +8248,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>28</v>
@@ -8203,7 +8260,7 @@
         <v>7150</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="G102" s="9" t="n">
         <v>5500</v>
@@ -8243,7 +8300,7 @@
         <v>24</v>
       </c>
       <c r="Q102" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R102" s="7" t="s">
         <v>31</v>
@@ -8254,7 +8311,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>28</v>
@@ -8266,7 +8323,7 @@
         <v>5850</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="G103" s="9" t="n">
         <v>4500</v>
@@ -8306,7 +8363,7 @@
         <v>24</v>
       </c>
       <c r="Q103" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R103" s="7" t="s">
         <v>31</v>
@@ -8317,7 +8374,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>22</v>
@@ -8369,7 +8426,7 @@
         <v>24</v>
       </c>
       <c r="Q104" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R104" s="7" t="s">
         <v>31</v>
@@ -8380,7 +8437,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>22</v>
@@ -8432,10 +8489,10 @@
         <v>24</v>
       </c>
       <c r="Q105" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R105" s="7" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8443,7 +8500,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>22</v>
@@ -8455,7 +8512,7 @@
         <v>1170</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="G106" s="9" t="n">
         <v>800</v>
@@ -8495,7 +8552,7 @@
         <v>43</v>
       </c>
       <c r="Q106" s="7" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="R106" s="7"/>
     </row>
@@ -8504,7 +8561,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>28</v>
@@ -8556,7 +8613,7 @@
         <v>43</v>
       </c>
       <c r="Q107" s="7" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="R107" s="7"/>
     </row>
@@ -8565,7 +8622,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>28</v>
@@ -8577,7 +8634,7 @@
         <v>6760</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="G108" s="9" t="n">
         <v>4500</v>
@@ -8617,10 +8674,10 @@
         <v>24</v>
       </c>
       <c r="Q108" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R108" s="7" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8628,7 +8685,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>28</v>
@@ -8680,7 +8737,7 @@
         <v>43</v>
       </c>
       <c r="Q109" s="7" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="R109" s="7"/>
     </row>
@@ -8689,7 +8746,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>28</v>
@@ -8701,7 +8758,7 @@
         <v>2340</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="G110" s="9" t="n">
         <v>1800</v>
@@ -8741,10 +8798,10 @@
         <v>24</v>
       </c>
       <c r="Q110" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R110" s="7" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8752,7 +8809,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>28</v>
@@ -8764,7 +8821,7 @@
         <v>1820</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G111" s="9" t="n">
         <v>2000</v>
@@ -8804,10 +8861,10 @@
         <v>24</v>
       </c>
       <c r="Q111" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R111" s="7" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8815,7 +8872,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>28</v>
@@ -8867,7 +8924,7 @@
         <v>49</v>
       </c>
       <c r="Q112" s="7" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
       <c r="R112" s="7" t="s">
         <v>51</v>
@@ -8878,7 +8935,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>28</v>
@@ -8890,7 +8947,7 @@
         <v>12350</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="G113" s="9" t="n">
         <v>8000</v>
@@ -8930,10 +8987,10 @@
         <v>24</v>
       </c>
       <c r="Q113" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R113" s="7" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8941,7 +8998,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>28</v>
@@ -8993,7 +9050,7 @@
         <v>24</v>
       </c>
       <c r="Q114" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R114" s="7" t="s">
         <v>31</v>
@@ -9004,7 +9061,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>28</v>
@@ -9056,7 +9113,7 @@
         <v>24</v>
       </c>
       <c r="Q115" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R115" s="7" t="s">
         <v>31</v>
@@ -9067,7 +9124,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>22</v>
@@ -9079,7 +9136,7 @@
         <v>11050</v>
       </c>
       <c r="F116" s="7" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="G116" s="9" t="n">
         <v>5000</v>
@@ -9119,7 +9176,7 @@
         <v>43</v>
       </c>
       <c r="Q116" s="7" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="R116" s="7"/>
     </row>
@@ -9128,7 +9185,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>28</v>
@@ -9180,10 +9237,10 @@
         <v>24</v>
       </c>
       <c r="Q117" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R117" s="7" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9191,7 +9248,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>22</v>
@@ -9243,7 +9300,7 @@
         <v>24</v>
       </c>
       <c r="Q118" s="7" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="R118" s="7" t="s">
         <v>31</v>
@@ -9254,7 +9311,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>22</v>
@@ -9306,7 +9363,7 @@
         <v>24</v>
       </c>
       <c r="Q119" s="7" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="R119" s="7" t="s">
         <v>31</v>
@@ -9317,7 +9374,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>28</v>
@@ -9369,7 +9426,7 @@
         <v>24</v>
       </c>
       <c r="Q120" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R120" s="7" t="s">
         <v>31</v>
@@ -9380,7 +9437,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>22</v>
@@ -9432,7 +9489,7 @@
         <v>24</v>
       </c>
       <c r="Q121" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R121" s="7" t="s">
         <v>31</v>
@@ -9443,7 +9500,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>22</v>
@@ -9495,7 +9552,7 @@
         <v>43</v>
       </c>
       <c r="Q122" s="7" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="R122" s="7"/>
     </row>
@@ -9504,7 +9561,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>22</v>
@@ -9516,7 +9573,7 @@
         <v>357500</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="G123" s="9" t="n">
         <v>200000</v>
@@ -9556,10 +9613,10 @@
         <v>24</v>
       </c>
       <c r="Q123" s="7" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="R123" s="7" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9567,7 +9624,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="C124" s="6" t="s">
         <v>22</v>
@@ -9619,10 +9676,10 @@
         <v>24</v>
       </c>
       <c r="Q124" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R124" s="7" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9630,7 +9687,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>22</v>
@@ -9682,7 +9739,7 @@
         <v>24</v>
       </c>
       <c r="Q125" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R125" s="7" t="s">
         <v>31</v>
@@ -9693,7 +9750,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>22</v>
@@ -9745,7 +9802,7 @@
         <v>24</v>
       </c>
       <c r="Q126" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R126" s="7" t="s">
         <v>31</v>
@@ -9756,7 +9813,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>22</v>
@@ -9808,7 +9865,7 @@
         <v>24</v>
       </c>
       <c r="Q127" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R127" s="7" t="s">
         <v>31</v>
@@ -9819,7 +9876,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>22</v>
@@ -9871,7 +9928,7 @@
         <v>24</v>
       </c>
       <c r="Q128" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R128" s="7" t="s">
         <v>31</v>
@@ -9882,7 +9939,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>22</v>
@@ -9934,7 +9991,7 @@
         <v>24</v>
       </c>
       <c r="Q129" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R129" s="7" t="s">
         <v>31</v>
@@ -9945,7 +10002,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>22</v>
@@ -9997,7 +10054,7 @@
         <v>24</v>
       </c>
       <c r="Q130" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R130" s="7" t="s">
         <v>31</v>
@@ -10008,7 +10065,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>259</v>
+        <v>276</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>22</v>
@@ -10060,10 +10117,10 @@
         <v>24</v>
       </c>
       <c r="Q131" s="7" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
       <c r="R131" s="7" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10071,7 +10128,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>22</v>
@@ -10083,7 +10140,7 @@
         <v>7800</v>
       </c>
       <c r="F132" s="7" t="s">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="G132" s="9" t="n">
         <v>5000</v>
@@ -10123,7 +10180,7 @@
         <v>43</v>
       </c>
       <c r="Q132" s="7" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="R132" s="7"/>
     </row>
@@ -10132,7 +10189,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="7" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>22</v>
@@ -10184,7 +10241,7 @@
         <v>24</v>
       </c>
       <c r="Q133" s="7" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="R133" s="7" t="s">
         <v>31</v>
@@ -10195,7 +10252,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>28</v>
@@ -10247,7 +10304,7 @@
         <v>24</v>
       </c>
       <c r="Q134" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R134" s="7" t="s">
         <v>31</v>
@@ -10258,7 +10315,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>22</v>
@@ -10310,7 +10367,7 @@
         <v>24</v>
       </c>
       <c r="Q135" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R135" s="7" t="s">
         <v>31</v>
@@ -10321,7 +10378,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="7" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
       <c r="C136" s="6" t="s">
         <v>22</v>
@@ -10373,7 +10430,7 @@
         <v>43</v>
       </c>
       <c r="Q136" s="7" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="R136" s="7"/>
     </row>
@@ -10382,7 +10439,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="C137" s="6" t="s">
         <v>22</v>
@@ -10434,7 +10491,7 @@
         <v>43</v>
       </c>
       <c r="Q137" s="7" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="R137" s="7"/>
     </row>
@@ -10443,7 +10500,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="C138" s="6" t="s">
         <v>22</v>
@@ -10495,7 +10552,7 @@
         <v>43</v>
       </c>
       <c r="Q138" s="7" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="R138" s="7"/>
     </row>
@@ -10504,7 +10561,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="7" t="s">
-        <v>274</v>
+        <v>291</v>
       </c>
       <c r="C139" s="6" t="s">
         <v>28</v>
@@ -10556,7 +10613,7 @@
         <v>24</v>
       </c>
       <c r="Q139" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R139" s="7" t="s">
         <v>31</v>
@@ -10567,7 +10624,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="7" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="C140" s="6" t="s">
         <v>22</v>
@@ -10619,10 +10676,10 @@
         <v>24</v>
       </c>
       <c r="Q140" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R140" s="7" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10630,7 +10687,7 @@
         <v>142</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="C141" s="6" t="s">
         <v>22</v>
@@ -10642,7 +10699,7 @@
         <v>7150</v>
       </c>
       <c r="F141" s="7" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="G141" s="9" t="n">
         <v>5000</v>
@@ -10682,7 +10739,7 @@
         <v>24</v>
       </c>
       <c r="Q141" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R141" s="7" t="s">
         <v>31</v>
@@ -10693,7 +10750,7 @@
         <v>143</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="C142" s="6" t="s">
         <v>22</v>
@@ -10705,7 +10762,7 @@
         <v>7150</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="G142" s="9" t="n">
         <v>5000</v>
@@ -10745,7 +10802,7 @@
         <v>24</v>
       </c>
       <c r="Q142" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R142" s="7" t="s">
         <v>31</v>
@@ -10756,7 +10813,7 @@
         <v>144</v>
       </c>
       <c r="B143" s="7" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="C143" s="6" t="s">
         <v>22</v>
@@ -10768,7 +10825,7 @@
         <v>8450</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="G143" s="9" t="n">
         <v>6000</v>
@@ -10808,7 +10865,7 @@
         <v>24</v>
       </c>
       <c r="Q143" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R143" s="7" t="s">
         <v>31</v>
@@ -10819,7 +10876,7 @@
         <v>145</v>
       </c>
       <c r="B144" s="7" t="s">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="C144" s="6" t="s">
         <v>28</v>
@@ -10831,7 +10888,7 @@
         <v>104</v>
       </c>
       <c r="F144" s="7" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="G144" s="9" t="n">
         <v>50</v>
@@ -10871,7 +10928,7 @@
         <v>24</v>
       </c>
       <c r="Q144" s="7" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="R144" s="7" t="s">
         <v>31</v>
@@ -10882,7 +10939,7 @@
         <v>146</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="C145" s="6" t="s">
         <v>22</v>
@@ -10894,7 +10951,7 @@
         <v>105788</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="G145" s="9" t="n">
         <v>82000</v>
@@ -10934,7 +10991,7 @@
         <v>43</v>
       </c>
       <c r="Q145" s="7" t="s">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="R145" s="7"/>
     </row>
@@ -10943,7 +11000,7 @@
         <v>147</v>
       </c>
       <c r="B146" s="7" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="C146" s="6" t="s">
         <v>22</v>
@@ -10955,7 +11012,7 @@
         <v>245700</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="G146" s="9" t="n">
         <v>225000</v>
@@ -10995,7 +11052,7 @@
         <v>43</v>
       </c>
       <c r="Q146" s="7" t="s">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="R146" s="7"/>
     </row>
@@ -11004,7 +11061,7 @@
         <v>148</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="C147" s="6" t="s">
         <v>28</v>
@@ -11056,7 +11113,7 @@
         <v>43</v>
       </c>
       <c r="Q147" s="7" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="R147" s="7"/>
     </row>
@@ -11065,7 +11122,7 @@
         <v>149</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>290</v>
+        <v>307</v>
       </c>
       <c r="C148" s="6" t="s">
         <v>22</v>
@@ -11077,7 +11134,7 @@
         <v>1754</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="G148" s="9" t="n">
         <v>1380</v>
@@ -11117,7 +11174,7 @@
         <v>43</v>
       </c>
       <c r="Q148" s="7" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="R148" s="7"/>
     </row>
@@ -11126,7 +11183,7 @@
         <v>150</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="C149" s="6" t="s">
         <v>22</v>
@@ -11178,7 +11235,7 @@
         <v>43</v>
       </c>
       <c r="Q149" s="7" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="R149" s="7"/>
     </row>
@@ -11187,7 +11244,7 @@
         <v>151</v>
       </c>
       <c r="B150" s="7" t="s">
-        <v>295</v>
+        <v>312</v>
       </c>
       <c r="C150" s="6" t="s">
         <v>22</v>
@@ -11239,7 +11296,7 @@
         <v>43</v>
       </c>
       <c r="Q150" s="7" t="s">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="R150" s="7"/>
     </row>
@@ -11248,7 +11305,7 @@
         <v>152</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="C151" s="6" t="s">
         <v>22</v>
@@ -11300,7 +11357,7 @@
         <v>43</v>
       </c>
       <c r="Q151" s="7" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
       <c r="R151" s="7"/>
     </row>
@@ -11309,7 +11366,7 @@
         <v>153</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="C152" s="6" t="s">
         <v>22</v>
@@ -11361,7 +11418,7 @@
         <v>43</v>
       </c>
       <c r="Q152" s="7" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="R152" s="7"/>
     </row>
@@ -11370,7 +11427,7 @@
         <v>154</v>
       </c>
       <c r="B153" s="7" t="s">
-        <v>301</v>
+        <v>318</v>
       </c>
       <c r="C153" s="6" t="s">
         <v>22</v>
@@ -11422,7 +11479,7 @@
         <v>24</v>
       </c>
       <c r="Q153" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R153" s="7" t="s">
         <v>31</v>
@@ -11433,7 +11490,7 @@
         <v>155</v>
       </c>
       <c r="B154" s="7" t="s">
-        <v>302</v>
+        <v>319</v>
       </c>
       <c r="C154" s="6" t="s">
         <v>22</v>
@@ -11445,7 +11502,7 @@
         <v>748</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>303</v>
+        <v>320</v>
       </c>
       <c r="G154" s="9" t="n">
         <v>450</v>
@@ -11485,7 +11542,7 @@
         <v>43</v>
       </c>
       <c r="Q154" s="7" t="s">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="R154" s="7"/>
     </row>
@@ -11494,7 +11551,7 @@
         <v>156</v>
       </c>
       <c r="B155" s="7" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>22</v>
@@ -11506,7 +11563,7 @@
         <v>748</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>303</v>
+        <v>320</v>
       </c>
       <c r="G155" s="9" t="n">
         <v>450</v>
@@ -11546,7 +11603,7 @@
         <v>43</v>
       </c>
       <c r="Q155" s="7" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="R155" s="7"/>
     </row>
@@ -11555,7 +11612,7 @@
         <v>157</v>
       </c>
       <c r="B156" s="7" t="s">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="C156" s="6" t="s">
         <v>22</v>
@@ -11567,7 +11624,7 @@
         <v>748</v>
       </c>
       <c r="F156" s="7" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="G156" s="9" t="n">
         <v>400</v>
@@ -11607,7 +11664,7 @@
         <v>43</v>
       </c>
       <c r="Q156" s="7" t="s">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="R156" s="7"/>
     </row>
@@ -11616,7 +11673,7 @@
         <v>158</v>
       </c>
       <c r="B157" s="7" t="s">
-        <v>310</v>
+        <v>327</v>
       </c>
       <c r="C157" s="6" t="s">
         <v>28</v>
@@ -11628,7 +11685,7 @@
         <v>311</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="G157" s="9" t="n">
         <v>150</v>
@@ -11668,7 +11725,7 @@
         <v>24</v>
       </c>
       <c r="Q157" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R157" s="7" t="s">
         <v>31</v>
@@ -11679,7 +11736,7 @@
         <v>159</v>
       </c>
       <c r="B158" s="7" t="s">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="C158" s="6" t="s">
         <v>28</v>
@@ -11691,7 +11748,7 @@
         <v>325</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="G158" s="9" t="n">
         <v>180</v>
@@ -11731,7 +11788,7 @@
         <v>24</v>
       </c>
       <c r="Q158" s="7" t="s">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="R158" s="7" t="s">
         <v>31</v>
@@ -11742,7 +11799,7 @@
         <v>160</v>
       </c>
       <c r="B159" s="7" t="s">
-        <v>313</v>
+        <v>330</v>
       </c>
       <c r="C159" s="6" t="s">
         <v>28</v>
@@ -11754,7 +11811,7 @@
         <v>117</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="G159" s="9" t="n">
         <v>60</v>
@@ -11794,7 +11851,7 @@
         <v>24</v>
       </c>
       <c r="Q159" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R159" s="7" t="s">
         <v>31</v>
@@ -11805,7 +11862,7 @@
         <v>161</v>
       </c>
       <c r="B160" s="7" t="s">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="C160" s="6" t="s">
         <v>28</v>
@@ -11817,7 +11874,7 @@
         <v>169</v>
       </c>
       <c r="F160" s="7" t="s">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="G160" s="9" t="n">
         <v>90</v>
@@ -11857,7 +11914,7 @@
         <v>24</v>
       </c>
       <c r="Q160" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R160" s="7" t="s">
         <v>31</v>
@@ -11868,7 +11925,7 @@
         <v>162</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="C161" s="6" t="s">
         <v>28</v>
@@ -11880,7 +11937,7 @@
         <v>234</v>
       </c>
       <c r="F161" s="7" t="s">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="G161" s="9" t="n">
         <v>120</v>
@@ -11920,7 +11977,7 @@
         <v>24</v>
       </c>
       <c r="Q161" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R161" s="7" t="s">
         <v>31</v>
@@ -11931,7 +11988,7 @@
         <v>164</v>
       </c>
       <c r="B162" s="7" t="s">
-        <v>317</v>
+        <v>334</v>
       </c>
       <c r="C162" s="6" t="s">
         <v>22</v>
@@ -11943,7 +12000,7 @@
         <v>1209</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="G162" s="9" t="n">
         <v>1450</v>
@@ -11983,7 +12040,7 @@
         <v>49</v>
       </c>
       <c r="Q162" s="7" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="R162" s="7" t="s">
         <v>51</v>
@@ -11994,7 +12051,7 @@
         <v>165</v>
       </c>
       <c r="B163" s="7" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="C163" s="6" t="s">
         <v>22</v>
@@ -12006,7 +12063,7 @@
         <v>1209</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="G163" s="9" t="n">
         <v>2248</v>
@@ -12046,7 +12103,7 @@
         <v>49</v>
       </c>
       <c r="Q163" s="7" t="s">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="R163" s="7" t="s">
         <v>51</v>
@@ -12057,7 +12114,7 @@
         <v>166</v>
       </c>
       <c r="B164" s="7" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="C164" s="6" t="s">
         <v>22</v>
@@ -12069,7 +12126,7 @@
         <v>3022</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="G164" s="9" t="n">
         <v>2325</v>
@@ -12109,7 +12166,7 @@
         <v>49</v>
       </c>
       <c r="Q164" s="7" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="R164" s="7" t="s">
         <v>51</v>
@@ -12120,7 +12177,7 @@
         <v>167</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="C165" s="6" t="s">
         <v>22</v>
@@ -12172,10 +12229,10 @@
         <v>24</v>
       </c>
       <c r="Q165" s="7" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="R165" s="7" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12183,7 +12240,7 @@
         <v>168</v>
       </c>
       <c r="B166" s="7" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="C166" s="6" t="s">
         <v>22</v>
@@ -12235,10 +12292,10 @@
         <v>24</v>
       </c>
       <c r="Q166" s="7" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="R166" s="7" t="s">
-        <v>329</v>
+        <v>346</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12246,7 +12303,7 @@
         <v>177</v>
       </c>
       <c r="B167" s="7" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
       <c r="C167" s="6" t="s">
         <v>28</v>
@@ -12258,7 +12315,7 @@
         <v>5850</v>
       </c>
       <c r="F167" s="7" t="s">
-        <v>331</v>
+        <v>348</v>
       </c>
       <c r="G167" s="9" t="n">
         <v>3500</v>
@@ -12298,10 +12355,10 @@
         <v>24</v>
       </c>
       <c r="Q167" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R167" s="7" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12309,7 +12366,7 @@
         <v>179</v>
       </c>
       <c r="B168" s="7" t="s">
-        <v>333</v>
+        <v>350</v>
       </c>
       <c r="C168" s="6" t="s">
         <v>28</v>
@@ -12321,7 +12378,7 @@
         <v>23400</v>
       </c>
       <c r="F168" s="7" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="G168" s="9" t="n">
         <v>20000</v>
@@ -12361,7 +12418,7 @@
         <v>24</v>
       </c>
       <c r="Q168" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R168" s="7" t="s">
         <v>31</v>
@@ -12372,7 +12429,7 @@
         <v>180</v>
       </c>
       <c r="B169" s="7" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
       <c r="C169" s="6" t="s">
         <v>28</v>
@@ -12384,7 +12441,7 @@
         <v>15600</v>
       </c>
       <c r="F169" s="7" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="G169" s="9" t="n">
         <v>14000</v>
@@ -12424,7 +12481,7 @@
         <v>24</v>
       </c>
       <c r="Q169" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R169" s="7" t="s">
         <v>31</v>
@@ -12435,7 +12492,7 @@
         <v>181</v>
       </c>
       <c r="B170" s="7" t="s">
-        <v>335</v>
+        <v>352</v>
       </c>
       <c r="C170" s="6" t="s">
         <v>28</v>
@@ -12447,7 +12504,7 @@
         <v>33800</v>
       </c>
       <c r="F170" s="7" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="G170" s="9" t="n">
         <v>28000</v>
@@ -12487,7 +12544,7 @@
         <v>24</v>
       </c>
       <c r="Q170" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R170" s="7" t="s">
         <v>31</v>
@@ -12498,7 +12555,7 @@
         <v>182</v>
       </c>
       <c r="B171" s="7" t="s">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="C171" s="6" t="s">
         <v>28</v>
@@ -12510,7 +12567,7 @@
         <v>23400</v>
       </c>
       <c r="F171" s="7" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="G171" s="9" t="n">
         <v>20000</v>
@@ -12550,7 +12607,7 @@
         <v>24</v>
       </c>
       <c r="Q171" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R171" s="7" t="s">
         <v>31</v>
@@ -12561,7 +12618,7 @@
         <v>183</v>
       </c>
       <c r="B172" s="7" t="s">
-        <v>337</v>
+        <v>354</v>
       </c>
       <c r="C172" s="6" t="s">
         <v>28</v>
@@ -12573,7 +12630,7 @@
         <v>2860</v>
       </c>
       <c r="F172" s="7" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="G172" s="9" t="n">
         <v>1800</v>
@@ -12613,7 +12670,7 @@
         <v>24</v>
       </c>
       <c r="Q172" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R172" s="7" t="s">
         <v>31</v>
@@ -12624,7 +12681,7 @@
         <v>184</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
       <c r="C173" s="6" t="s">
         <v>28</v>
@@ -12636,7 +12693,7 @@
         <v>3250</v>
       </c>
       <c r="F173" s="7" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="G173" s="9" t="n">
         <v>2100</v>
@@ -12676,7 +12733,7 @@
         <v>24</v>
       </c>
       <c r="Q173" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R173" s="7" t="s">
         <v>31</v>
@@ -12687,7 +12744,7 @@
         <v>185</v>
       </c>
       <c r="B174" s="7" t="s">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="C174" s="6" t="s">
         <v>28</v>
@@ -12699,7 +12756,7 @@
         <v>3900</v>
       </c>
       <c r="F174" s="7" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="G174" s="9" t="n">
         <v>2600</v>
@@ -12739,7 +12796,7 @@
         <v>24</v>
       </c>
       <c r="Q174" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R174" s="7" t="s">
         <v>31</v>
@@ -12750,7 +12807,7 @@
         <v>186</v>
       </c>
       <c r="B175" s="7" t="s">
-        <v>340</v>
+        <v>357</v>
       </c>
       <c r="C175" s="6" t="s">
         <v>28</v>
@@ -12762,7 +12819,7 @@
         <v>4550</v>
       </c>
       <c r="F175" s="7" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="G175" s="9" t="n">
         <v>3300</v>
@@ -12802,7 +12859,7 @@
         <v>24</v>
       </c>
       <c r="Q175" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R175" s="7" t="s">
         <v>31</v>
@@ -12813,7 +12870,7 @@
         <v>187</v>
       </c>
       <c r="B176" s="7" t="s">
-        <v>341</v>
+        <v>358</v>
       </c>
       <c r="C176" s="6" t="s">
         <v>28</v>
@@ -12825,7 +12882,7 @@
         <v>7150</v>
       </c>
       <c r="F176" s="7" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="G176" s="9" t="n">
         <v>5500</v>
@@ -12865,7 +12922,7 @@
         <v>24</v>
       </c>
       <c r="Q176" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R176" s="7" t="s">
         <v>31</v>
@@ -12876,7 +12933,7 @@
         <v>188</v>
       </c>
       <c r="B177" s="7" t="s">
-        <v>342</v>
+        <v>359</v>
       </c>
       <c r="C177" s="6" t="s">
         <v>28</v>
@@ -12888,7 +12945,7 @@
         <v>8450</v>
       </c>
       <c r="F177" s="7" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="G177" s="9" t="n">
         <v>7000</v>
@@ -12928,7 +12985,7 @@
         <v>24</v>
       </c>
       <c r="Q177" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R177" s="7" t="s">
         <v>31</v>
@@ -12939,7 +12996,7 @@
         <v>189</v>
       </c>
       <c r="B178" s="7" t="s">
-        <v>343</v>
+        <v>360</v>
       </c>
       <c r="C178" s="6" t="s">
         <v>28</v>
@@ -12951,7 +13008,7 @@
         <v>9750</v>
       </c>
       <c r="F178" s="7" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="G178" s="9" t="n">
         <v>8500</v>
@@ -12991,7 +13048,7 @@
         <v>24</v>
       </c>
       <c r="Q178" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R178" s="7" t="s">
         <v>31</v>
@@ -13002,7 +13059,7 @@
         <v>190</v>
       </c>
       <c r="B179" s="7" t="s">
-        <v>344</v>
+        <v>361</v>
       </c>
       <c r="C179" s="6" t="s">
         <v>28</v>
@@ -13014,7 +13071,7 @@
         <v>2340</v>
       </c>
       <c r="F179" s="7" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="G179" s="9" t="n">
         <v>1500</v>
@@ -13054,7 +13111,7 @@
         <v>24</v>
       </c>
       <c r="Q179" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R179" s="7" t="s">
         <v>31</v>
@@ -13065,7 +13122,7 @@
         <v>191</v>
       </c>
       <c r="B180" s="7" t="s">
-        <v>344</v>
+        <v>361</v>
       </c>
       <c r="C180" s="6" t="s">
         <v>28</v>
@@ -13077,7 +13134,7 @@
         <v>3640</v>
       </c>
       <c r="F180" s="7" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="G180" s="9" t="n">
         <v>2300</v>
@@ -13117,7 +13174,7 @@
         <v>24</v>
       </c>
       <c r="Q180" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R180" s="7" t="s">
         <v>31</v>
@@ -13128,7 +13185,7 @@
         <v>192</v>
       </c>
       <c r="B181" s="7" t="s">
-        <v>345</v>
+        <v>362</v>
       </c>
       <c r="C181" s="6" t="s">
         <v>28</v>
@@ -13180,7 +13237,7 @@
         <v>24</v>
       </c>
       <c r="Q181" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R181" s="7" t="s">
         <v>31</v>
@@ -13191,7 +13248,7 @@
         <v>193</v>
       </c>
       <c r="B182" s="7" t="s">
-        <v>346</v>
+        <v>363</v>
       </c>
       <c r="C182" s="6" t="s">
         <v>28</v>
@@ -13243,7 +13300,7 @@
         <v>24</v>
       </c>
       <c r="Q182" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R182" s="7" t="s">
         <v>31</v>
@@ -13254,7 +13311,7 @@
         <v>194</v>
       </c>
       <c r="B183" s="7" t="s">
-        <v>347</v>
+        <v>364</v>
       </c>
       <c r="C183" s="6" t="s">
         <v>28</v>
@@ -13306,7 +13363,7 @@
         <v>24</v>
       </c>
       <c r="Q183" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R183" s="7" t="s">
         <v>31</v>
@@ -13317,7 +13374,7 @@
         <v>195</v>
       </c>
       <c r="B184" s="7" t="s">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="C184" s="6" t="s">
         <v>28</v>
@@ -13369,7 +13426,7 @@
         <v>24</v>
       </c>
       <c r="Q184" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R184" s="7" t="s">
         <v>31</v>
@@ -13380,7 +13437,7 @@
         <v>196</v>
       </c>
       <c r="B185" s="7" t="s">
-        <v>349</v>
+        <v>366</v>
       </c>
       <c r="C185" s="6" t="s">
         <v>28</v>
@@ -13392,7 +13449,7 @@
         <v>4550</v>
       </c>
       <c r="F185" s="7" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="G185" s="9" t="n">
         <v>3500</v>
@@ -13432,7 +13489,7 @@
         <v>24</v>
       </c>
       <c r="Q185" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R185" s="7" t="s">
         <v>31</v>
@@ -13443,7 +13500,7 @@
         <v>197</v>
       </c>
       <c r="B186" s="7" t="s">
-        <v>350</v>
+        <v>367</v>
       </c>
       <c r="C186" s="6" t="s">
         <v>28</v>
@@ -13455,7 +13512,7 @@
         <v>17940</v>
       </c>
       <c r="F186" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G186" s="9" t="n">
         <v>5500</v>
@@ -13495,7 +13552,7 @@
         <v>43</v>
       </c>
       <c r="Q186" s="7" t="s">
-        <v>351</v>
+        <v>368</v>
       </c>
       <c r="R186" s="7"/>
     </row>
@@ -13504,7 +13561,7 @@
         <v>198</v>
       </c>
       <c r="B187" s="7" t="s">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="C187" s="6" t="s">
         <v>28</v>
@@ -13516,7 +13573,7 @@
         <v>18850</v>
       </c>
       <c r="F187" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G187" s="9" t="n">
         <v>5500</v>
@@ -13556,7 +13613,7 @@
         <v>43</v>
       </c>
       <c r="Q187" s="7" t="s">
-        <v>353</v>
+        <v>370</v>
       </c>
       <c r="R187" s="7"/>
     </row>
@@ -13565,7 +13622,7 @@
         <v>199</v>
       </c>
       <c r="B188" s="7" t="s">
-        <v>354</v>
+        <v>371</v>
       </c>
       <c r="C188" s="6" t="s">
         <v>28</v>
@@ -13577,7 +13634,7 @@
         <v>19500</v>
       </c>
       <c r="F188" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G188" s="9" t="n">
         <v>6200</v>
@@ -13617,7 +13674,7 @@
         <v>43</v>
       </c>
       <c r="Q188" s="7" t="s">
-        <v>355</v>
+        <v>372</v>
       </c>
       <c r="R188" s="7"/>
     </row>
@@ -13626,7 +13683,7 @@
         <v>200</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>356</v>
+        <v>373</v>
       </c>
       <c r="C189" s="6" t="s">
         <v>28</v>
@@ -13638,7 +13695,7 @@
         <v>20800</v>
       </c>
       <c r="F189" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G189" s="9" t="n">
         <v>6875</v>
@@ -13678,7 +13735,7 @@
         <v>43</v>
       </c>
       <c r="Q189" s="7" t="s">
-        <v>357</v>
+        <v>374</v>
       </c>
       <c r="R189" s="7"/>
     </row>
@@ -13687,7 +13744,7 @@
         <v>201</v>
       </c>
       <c r="B190" s="7" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="C190" s="6" t="s">
         <v>28</v>
@@ -13699,7 +13756,7 @@
         <v>22750</v>
       </c>
       <c r="F190" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G190" s="9" t="n">
         <v>8750</v>
@@ -13739,7 +13796,7 @@
         <v>43</v>
       </c>
       <c r="Q190" s="7" t="s">
-        <v>359</v>
+        <v>376</v>
       </c>
       <c r="R190" s="7"/>
     </row>
@@ -13748,7 +13805,7 @@
         <v>202</v>
       </c>
       <c r="B191" s="7" t="s">
-        <v>360</v>
+        <v>377</v>
       </c>
       <c r="C191" s="6" t="s">
         <v>28</v>
@@ -13760,7 +13817,7 @@
         <v>2340</v>
       </c>
       <c r="F191" s="7" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="G191" s="9" t="n">
         <v>1500</v>
@@ -13800,18 +13857,18 @@
         <v>24</v>
       </c>
       <c r="Q191" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R191" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="6" t="n">
         <v>204</v>
       </c>
       <c r="B192" s="7" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
       <c r="C192" s="6" t="s">
         <v>28</v>
@@ -13823,25 +13880,25 @@
         <v>845</v>
       </c>
       <c r="F192" s="7" t="s">
-        <v>362</v>
+        <v>379</v>
       </c>
       <c r="G192" s="9" t="n">
-        <v>800</v>
+        <v>5480</v>
       </c>
       <c r="H192" s="9" t="n">
-        <v>1200</v>
+        <v>7130</v>
       </c>
       <c r="I192" s="10" t="n">
         <f aca="false">IF(E192=0,0,(E192-H192)/E192)</f>
-        <v>-0.420118343195266</v>
+        <v>-7.43786982248521</v>
       </c>
       <c r="J192" s="6" t="str">
         <f aca="false">IF(E192&lt;G192,"LOSS",IF(E192&lt;H192*1.1,"THIN / RISK",IF(E192&gt;H192*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>LOSS</v>
       </c>
       <c r="K192" s="8" t="n">
         <f aca="false">IF(J192="OVERPRICED?",ROUND(H192*1.35,-1),MAX(E192,ROUND(H192*(1+$E$3),-1)))</f>
-        <v>1380</v>
+        <v>8200</v>
       </c>
       <c r="L192" s="8" t="n">
         <f aca="false">D192*E192</f>
@@ -13849,11 +13906,11 @@
       </c>
       <c r="M192" s="8" t="n">
         <f aca="false">D192*K192</f>
-        <v>8280</v>
+        <v>49200</v>
       </c>
       <c r="N192" s="8" t="n">
         <f aca="false">D192*H192</f>
-        <v>7200</v>
+        <v>42780</v>
       </c>
       <c r="O192" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C192,F192)),"","YES")</f>
@@ -13863,18 +13920,18 @@
         <v>24</v>
       </c>
       <c r="Q192" s="7" t="s">
-        <v>143</v>
+        <v>380</v>
       </c>
       <c r="R192" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="6" t="n">
         <v>205</v>
       </c>
       <c r="B193" s="7" t="s">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="C193" s="6" t="s">
         <v>28</v>
@@ -13886,25 +13943,25 @@
         <v>910</v>
       </c>
       <c r="F193" s="7" t="s">
-        <v>362</v>
+        <v>379</v>
       </c>
       <c r="G193" s="9" t="n">
-        <v>900</v>
+        <v>5960</v>
       </c>
       <c r="H193" s="9" t="n">
-        <v>1300</v>
+        <v>7750</v>
       </c>
       <c r="I193" s="10" t="n">
         <f aca="false">IF(E193=0,0,(E193-H193)/E193)</f>
-        <v>-0.428571428571429</v>
+        <v>-7.51648351648352</v>
       </c>
       <c r="J193" s="6" t="str">
         <f aca="false">IF(E193&lt;G193,"LOSS",IF(E193&lt;H193*1.1,"THIN / RISK",IF(E193&gt;H193*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>LOSS</v>
       </c>
       <c r="K193" s="8" t="n">
         <f aca="false">IF(J193="OVERPRICED?",ROUND(H193*1.35,-1),MAX(E193,ROUND(H193*(1+$E$3),-1)))</f>
-        <v>1500</v>
+        <v>8910</v>
       </c>
       <c r="L193" s="8" t="n">
         <f aca="false">D193*E193</f>
@@ -13912,11 +13969,11 @@
       </c>
       <c r="M193" s="8" t="n">
         <f aca="false">D193*K193</f>
-        <v>9000</v>
+        <v>53460</v>
       </c>
       <c r="N193" s="8" t="n">
         <f aca="false">D193*H193</f>
-        <v>7800</v>
+        <v>46500</v>
       </c>
       <c r="O193" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C193,F193)),"","YES")</f>
@@ -13926,18 +13983,18 @@
         <v>24</v>
       </c>
       <c r="Q193" s="7" t="s">
-        <v>143</v>
+        <v>380</v>
       </c>
       <c r="R193" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="6" t="n">
         <v>206</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>364</v>
+        <v>382</v>
       </c>
       <c r="C194" s="6" t="s">
         <v>28</v>
@@ -13949,17 +14006,17 @@
         <v>1170</v>
       </c>
       <c r="F194" s="7" t="s">
-        <v>362</v>
+        <v>379</v>
       </c>
       <c r="G194" s="9" t="n">
-        <v>1200</v>
+        <v>6930</v>
       </c>
       <c r="H194" s="9" t="n">
-        <v>1700</v>
+        <v>9010</v>
       </c>
       <c r="I194" s="10" t="n">
         <f aca="false">IF(E194=0,0,(E194-H194)/E194)</f>
-        <v>-0.452991452991453</v>
+        <v>-6.7008547008547</v>
       </c>
       <c r="J194" s="6" t="str">
         <f aca="false">IF(E194&lt;G194,"LOSS",IF(E194&lt;H194*1.1,"THIN / RISK",IF(E194&gt;H194*1.8,"OVERPRICED?","OK")))</f>
@@ -13967,7 +14024,7 @@
       </c>
       <c r="K194" s="8" t="n">
         <f aca="false">IF(J194="OVERPRICED?",ROUND(H194*1.35,-1),MAX(E194,ROUND(H194*(1+$E$3),-1)))</f>
-        <v>1960</v>
+        <v>10360</v>
       </c>
       <c r="L194" s="8" t="n">
         <f aca="false">D194*E194</f>
@@ -13975,11 +14032,11 @@
       </c>
       <c r="M194" s="8" t="n">
         <f aca="false">D194*K194</f>
-        <v>11760</v>
+        <v>62160</v>
       </c>
       <c r="N194" s="8" t="n">
         <f aca="false">D194*H194</f>
-        <v>10200</v>
+        <v>54060</v>
       </c>
       <c r="O194" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C194,F194)),"","YES")</f>
@@ -13989,18 +14046,18 @@
         <v>24</v>
       </c>
       <c r="Q194" s="7" t="s">
-        <v>143</v>
+        <v>380</v>
       </c>
       <c r="R194" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="6" t="n">
         <v>207</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>365</v>
+        <v>383</v>
       </c>
       <c r="C195" s="6" t="s">
         <v>28</v>
@@ -14012,17 +14069,17 @@
         <v>1430</v>
       </c>
       <c r="F195" s="7" t="s">
-        <v>362</v>
+        <v>379</v>
       </c>
       <c r="G195" s="9" t="n">
-        <v>1600</v>
+        <v>8960</v>
       </c>
       <c r="H195" s="9" t="n">
-        <v>2200</v>
+        <v>11640</v>
       </c>
       <c r="I195" s="10" t="n">
         <f aca="false">IF(E195=0,0,(E195-H195)/E195)</f>
-        <v>-0.538461538461538</v>
+        <v>-7.13986013986014</v>
       </c>
       <c r="J195" s="6" t="str">
         <f aca="false">IF(E195&lt;G195,"LOSS",IF(E195&lt;H195*1.1,"THIN / RISK",IF(E195&gt;H195*1.8,"OVERPRICED?","OK")))</f>
@@ -14030,7 +14087,7 @@
       </c>
       <c r="K195" s="8" t="n">
         <f aca="false">IF(J195="OVERPRICED?",ROUND(H195*1.35,-1),MAX(E195,ROUND(H195*(1+$E$3),-1)))</f>
-        <v>2530</v>
+        <v>13390</v>
       </c>
       <c r="L195" s="8" t="n">
         <f aca="false">D195*E195</f>
@@ -14038,11 +14095,11 @@
       </c>
       <c r="M195" s="8" t="n">
         <f aca="false">D195*K195</f>
-        <v>10120</v>
+        <v>53560</v>
       </c>
       <c r="N195" s="8" t="n">
         <f aca="false">D195*H195</f>
-        <v>8800</v>
+        <v>46560</v>
       </c>
       <c r="O195" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C195,F195)),"","YES")</f>
@@ -14052,18 +14109,18 @@
         <v>24</v>
       </c>
       <c r="Q195" s="7" t="s">
-        <v>143</v>
+        <v>380</v>
       </c>
       <c r="R195" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="6" t="n">
         <v>208</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="C196" s="6" t="s">
         <v>28</v>
@@ -14075,17 +14132,17 @@
         <v>1690</v>
       </c>
       <c r="F196" s="7" t="s">
-        <v>362</v>
+        <v>379</v>
       </c>
       <c r="G196" s="9" t="n">
-        <v>2000</v>
+        <v>11050</v>
       </c>
       <c r="H196" s="9" t="n">
-        <v>2800</v>
+        <v>14360</v>
       </c>
       <c r="I196" s="10" t="n">
         <f aca="false">IF(E196=0,0,(E196-H196)/E196)</f>
-        <v>-0.656804733727811</v>
+        <v>-7.49704142011834</v>
       </c>
       <c r="J196" s="6" t="str">
         <f aca="false">IF(E196&lt;G196,"LOSS",IF(E196&lt;H196*1.1,"THIN / RISK",IF(E196&gt;H196*1.8,"OVERPRICED?","OK")))</f>
@@ -14093,7 +14150,7 @@
       </c>
       <c r="K196" s="8" t="n">
         <f aca="false">IF(J196="OVERPRICED?",ROUND(H196*1.35,-1),MAX(E196,ROUND(H196*(1+$E$3),-1)))</f>
-        <v>3220</v>
+        <v>16510</v>
       </c>
       <c r="L196" s="8" t="n">
         <f aca="false">D196*E196</f>
@@ -14101,11 +14158,11 @@
       </c>
       <c r="M196" s="8" t="n">
         <f aca="false">D196*K196</f>
-        <v>9660</v>
+        <v>49530</v>
       </c>
       <c r="N196" s="8" t="n">
         <f aca="false">D196*H196</f>
-        <v>8400</v>
+        <v>43080</v>
       </c>
       <c r="O196" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C196,F196)),"","YES")</f>
@@ -14115,18 +14172,18 @@
         <v>24</v>
       </c>
       <c r="Q196" s="7" t="s">
-        <v>143</v>
+        <v>380</v>
       </c>
       <c r="R196" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="6" t="n">
         <v>209</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="C197" s="6" t="s">
         <v>28</v>
@@ -14138,17 +14195,17 @@
         <v>2340</v>
       </c>
       <c r="F197" s="7" t="s">
-        <v>362</v>
+        <v>379</v>
       </c>
       <c r="G197" s="9" t="n">
-        <v>3000</v>
+        <v>15380</v>
       </c>
       <c r="H197" s="9" t="n">
-        <v>4000</v>
+        <v>19990</v>
       </c>
       <c r="I197" s="10" t="n">
         <f aca="false">IF(E197=0,0,(E197-H197)/E197)</f>
-        <v>-0.709401709401709</v>
+        <v>-7.54273504273504</v>
       </c>
       <c r="J197" s="6" t="str">
         <f aca="false">IF(E197&lt;G197,"LOSS",IF(E197&lt;H197*1.1,"THIN / RISK",IF(E197&gt;H197*1.8,"OVERPRICED?","OK")))</f>
@@ -14156,7 +14213,7 @@
       </c>
       <c r="K197" s="8" t="n">
         <f aca="false">IF(J197="OVERPRICED?",ROUND(H197*1.35,-1),MAX(E197,ROUND(H197*(1+$E$3),-1)))</f>
-        <v>4600</v>
+        <v>22990</v>
       </c>
       <c r="L197" s="8" t="n">
         <f aca="false">D197*E197</f>
@@ -14164,11 +14221,11 @@
       </c>
       <c r="M197" s="8" t="n">
         <f aca="false">D197*K197</f>
-        <v>13800</v>
+        <v>68970</v>
       </c>
       <c r="N197" s="8" t="n">
         <f aca="false">D197*H197</f>
-        <v>12000</v>
+        <v>59970</v>
       </c>
       <c r="O197" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C197,F197)),"","YES")</f>
@@ -14178,18 +14235,18 @@
         <v>24</v>
       </c>
       <c r="Q197" s="7" t="s">
-        <v>143</v>
+        <v>380</v>
       </c>
       <c r="R197" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="6" t="n">
         <v>210</v>
       </c>
       <c r="B198" s="7" t="s">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="C198" s="6" t="s">
         <v>28</v>
@@ -14201,17 +14258,17 @@
         <v>2860</v>
       </c>
       <c r="F198" s="7" t="s">
-        <v>362</v>
+        <v>379</v>
       </c>
       <c r="G198" s="9" t="n">
-        <v>3700</v>
+        <v>17610</v>
       </c>
       <c r="H198" s="9" t="n">
-        <v>4800</v>
+        <v>22890</v>
       </c>
       <c r="I198" s="10" t="n">
         <f aca="false">IF(E198=0,0,(E198-H198)/E198)</f>
-        <v>-0.678321678321678</v>
+        <v>-7.0034965034965</v>
       </c>
       <c r="J198" s="6" t="str">
         <f aca="false">IF(E198&lt;G198,"LOSS",IF(E198&lt;H198*1.1,"THIN / RISK",IF(E198&gt;H198*1.8,"OVERPRICED?","OK")))</f>
@@ -14219,7 +14276,7 @@
       </c>
       <c r="K198" s="8" t="n">
         <f aca="false">IF(J198="OVERPRICED?",ROUND(H198*1.35,-1),MAX(E198,ROUND(H198*(1+$E$3),-1)))</f>
-        <v>5520</v>
+        <v>26320</v>
       </c>
       <c r="L198" s="8" t="n">
         <f aca="false">D198*E198</f>
@@ -14227,11 +14284,11 @@
       </c>
       <c r="M198" s="8" t="n">
         <f aca="false">D198*K198</f>
-        <v>11040</v>
+        <v>52640</v>
       </c>
       <c r="N198" s="8" t="n">
         <f aca="false">D198*H198</f>
-        <v>9600</v>
+        <v>45780</v>
       </c>
       <c r="O198" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C198,F198)),"","YES")</f>
@@ -14241,18 +14298,18 @@
         <v>24</v>
       </c>
       <c r="Q198" s="7" t="s">
-        <v>143</v>
+        <v>380</v>
       </c>
       <c r="R198" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="6" t="n">
         <v>211</v>
       </c>
       <c r="B199" s="7" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="C199" s="6" t="s">
         <v>28</v>
@@ -14264,17 +14321,17 @@
         <v>4160</v>
       </c>
       <c r="F199" s="7" t="s">
-        <v>362</v>
+        <v>379</v>
       </c>
       <c r="G199" s="9" t="n">
-        <v>5200</v>
+        <v>22180</v>
       </c>
       <c r="H199" s="9" t="n">
-        <v>7000</v>
+        <v>28830</v>
       </c>
       <c r="I199" s="10" t="n">
         <f aca="false">IF(E199=0,0,(E199-H199)/E199)</f>
-        <v>-0.682692307692308</v>
+        <v>-5.93028846153846</v>
       </c>
       <c r="J199" s="6" t="str">
         <f aca="false">IF(E199&lt;G199,"LOSS",IF(E199&lt;H199*1.1,"THIN / RISK",IF(E199&gt;H199*1.8,"OVERPRICED?","OK")))</f>
@@ -14282,7 +14339,7 @@
       </c>
       <c r="K199" s="8" t="n">
         <f aca="false">IF(J199="OVERPRICED?",ROUND(H199*1.35,-1),MAX(E199,ROUND(H199*(1+$E$3),-1)))</f>
-        <v>8050</v>
+        <v>33150</v>
       </c>
       <c r="L199" s="8" t="n">
         <f aca="false">D199*E199</f>
@@ -14290,11 +14347,11 @@
       </c>
       <c r="M199" s="8" t="n">
         <f aca="false">D199*K199</f>
-        <v>8050</v>
+        <v>33150</v>
       </c>
       <c r="N199" s="8" t="n">
         <f aca="false">D199*H199</f>
-        <v>7000</v>
+        <v>28830</v>
       </c>
       <c r="O199" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C199,F199)),"","YES")</f>
@@ -14304,18 +14361,18 @@
         <v>24</v>
       </c>
       <c r="Q199" s="7" t="s">
-        <v>143</v>
+        <v>380</v>
       </c>
       <c r="R199" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A200" s="6" t="n">
         <v>212</v>
       </c>
       <c r="B200" s="7" t="s">
-        <v>370</v>
+        <v>388</v>
       </c>
       <c r="C200" s="6" t="s">
         <v>28</v>
@@ -14327,17 +14384,17 @@
         <v>5460</v>
       </c>
       <c r="F200" s="7" t="s">
-        <v>362</v>
+        <v>379</v>
       </c>
       <c r="G200" s="9" t="n">
-        <v>6500</v>
+        <v>25690</v>
       </c>
       <c r="H200" s="9" t="n">
-        <v>8500</v>
+        <v>33400</v>
       </c>
       <c r="I200" s="10" t="n">
         <f aca="false">IF(E200=0,0,(E200-H200)/E200)</f>
-        <v>-0.556776556776557</v>
+        <v>-5.11721611721612</v>
       </c>
       <c r="J200" s="6" t="str">
         <f aca="false">IF(E200&lt;G200,"LOSS",IF(E200&lt;H200*1.1,"THIN / RISK",IF(E200&gt;H200*1.8,"OVERPRICED?","OK")))</f>
@@ -14345,7 +14402,7 @@
       </c>
       <c r="K200" s="8" t="n">
         <f aca="false">IF(J200="OVERPRICED?",ROUND(H200*1.35,-1),MAX(E200,ROUND(H200*(1+$E$3),-1)))</f>
-        <v>9780</v>
+        <v>38410</v>
       </c>
       <c r="L200" s="8" t="n">
         <f aca="false">D200*E200</f>
@@ -14353,11 +14410,11 @@
       </c>
       <c r="M200" s="8" t="n">
         <f aca="false">D200*K200</f>
-        <v>9780</v>
+        <v>38410</v>
       </c>
       <c r="N200" s="8" t="n">
         <f aca="false">D200*H200</f>
-        <v>8500</v>
+        <v>33400</v>
       </c>
       <c r="O200" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C200,F200)),"","YES")</f>
@@ -14367,7 +14424,7 @@
         <v>24</v>
       </c>
       <c r="Q200" s="7" t="s">
-        <v>143</v>
+        <v>380</v>
       </c>
       <c r="R200" s="7" t="s">
         <v>31</v>
@@ -14378,7 +14435,7 @@
         <v>213</v>
       </c>
       <c r="B201" s="7" t="s">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="C201" s="6" t="s">
         <v>28</v>
@@ -14390,7 +14447,7 @@
         <v>455</v>
       </c>
       <c r="F201" s="7" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="G201" s="9" t="n">
         <v>500</v>
@@ -14430,7 +14487,7 @@
         <v>24</v>
       </c>
       <c r="Q201" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R201" s="7" t="s">
         <v>31</v>
@@ -14441,7 +14498,7 @@
         <v>214</v>
       </c>
       <c r="B202" s="7" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
       <c r="C202" s="6" t="s">
         <v>28</v>
@@ -14453,7 +14510,7 @@
         <v>494</v>
       </c>
       <c r="F202" s="7" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="G202" s="9" t="n">
         <v>550</v>
@@ -14493,7 +14550,7 @@
         <v>24</v>
       </c>
       <c r="Q202" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R202" s="7" t="s">
         <v>31</v>
@@ -14504,7 +14561,7 @@
         <v>215</v>
       </c>
       <c r="B203" s="7" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="C203" s="6" t="s">
         <v>28</v>
@@ -14516,7 +14573,7 @@
         <v>585</v>
       </c>
       <c r="F203" s="7" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="G203" s="9" t="n">
         <v>650</v>
@@ -14556,7 +14613,7 @@
         <v>24</v>
       </c>
       <c r="Q203" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R203" s="7" t="s">
         <v>31</v>
@@ -14567,7 +14624,7 @@
         <v>216</v>
       </c>
       <c r="B204" s="7" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
       <c r="C204" s="6" t="s">
         <v>28</v>
@@ -14579,7 +14636,7 @@
         <v>715</v>
       </c>
       <c r="F204" s="7" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="G204" s="9" t="n">
         <v>800</v>
@@ -14619,7 +14676,7 @@
         <v>24</v>
       </c>
       <c r="Q204" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R204" s="7" t="s">
         <v>31</v>
@@ -14630,7 +14687,7 @@
         <v>217</v>
       </c>
       <c r="B205" s="7" t="s">
-        <v>375</v>
+        <v>393</v>
       </c>
       <c r="C205" s="6" t="s">
         <v>28</v>
@@ -14642,7 +14699,7 @@
         <v>910</v>
       </c>
       <c r="F205" s="7" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="G205" s="9" t="n">
         <v>1000</v>
@@ -14682,7 +14739,7 @@
         <v>24</v>
       </c>
       <c r="Q205" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R205" s="7" t="s">
         <v>31</v>
@@ -14693,7 +14750,7 @@
         <v>218</v>
       </c>
       <c r="B206" s="7" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
       <c r="C206" s="6" t="s">
         <v>28</v>
@@ -14705,7 +14762,7 @@
         <v>1170</v>
       </c>
       <c r="F206" s="7" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="G206" s="9" t="n">
         <v>1400</v>
@@ -14745,7 +14802,7 @@
         <v>24</v>
       </c>
       <c r="Q206" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R206" s="7" t="s">
         <v>31</v>
@@ -14756,7 +14813,7 @@
         <v>219</v>
       </c>
       <c r="B207" s="7" t="s">
-        <v>377</v>
+        <v>395</v>
       </c>
       <c r="C207" s="6" t="s">
         <v>28</v>
@@ -14768,7 +14825,7 @@
         <v>1040</v>
       </c>
       <c r="F207" s="7" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="G207" s="9" t="n">
         <v>1100</v>
@@ -14808,7 +14865,7 @@
         <v>24</v>
       </c>
       <c r="Q207" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R207" s="7" t="s">
         <v>31</v>
@@ -14819,7 +14876,7 @@
         <v>220</v>
       </c>
       <c r="B208" s="7" t="s">
-        <v>378</v>
+        <v>396</v>
       </c>
       <c r="C208" s="6" t="s">
         <v>28</v>
@@ -14831,7 +14888,7 @@
         <v>1430</v>
       </c>
       <c r="F208" s="7" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="G208" s="9" t="n">
         <v>1400</v>
@@ -14871,7 +14928,7 @@
         <v>24</v>
       </c>
       <c r="Q208" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R208" s="7" t="s">
         <v>31</v>
@@ -14882,7 +14939,7 @@
         <v>221</v>
       </c>
       <c r="B209" s="7" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="C209" s="6" t="s">
         <v>28</v>
@@ -14894,7 +14951,7 @@
         <v>1950</v>
       </c>
       <c r="F209" s="7" t="s">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="G209" s="9" t="n">
         <v>2000</v>
@@ -14934,7 +14991,7 @@
         <v>24</v>
       </c>
       <c r="Q209" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R209" s="7" t="s">
         <v>31</v>
@@ -14945,7 +15002,7 @@
         <v>222</v>
       </c>
       <c r="B210" s="7" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="C210" s="6" t="s">
         <v>28</v>
@@ -14957,7 +15014,7 @@
         <v>15600</v>
       </c>
       <c r="F210" s="7" t="s">
-        <v>381</v>
+        <v>399</v>
       </c>
       <c r="G210" s="9" t="n">
         <v>18000</v>
@@ -14997,7 +15054,7 @@
         <v>24</v>
       </c>
       <c r="Q210" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R210" s="7" t="s">
         <v>31</v>
@@ -15008,7 +15065,7 @@
         <v>223</v>
       </c>
       <c r="B211" s="7" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="C211" s="6" t="s">
         <v>28</v>
@@ -15020,7 +15077,7 @@
         <v>30940</v>
       </c>
       <c r="F211" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G211" s="9" t="n">
         <v>31300</v>
@@ -15060,7 +15117,7 @@
         <v>43</v>
       </c>
       <c r="Q211" s="7" t="s">
-        <v>383</v>
+        <v>401</v>
       </c>
       <c r="R211" s="7"/>
     </row>
@@ -15069,7 +15126,7 @@
         <v>224</v>
       </c>
       <c r="B212" s="7" t="s">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="C212" s="6" t="s">
         <v>28</v>
@@ -15081,7 +15138,7 @@
         <v>54600</v>
       </c>
       <c r="F212" s="7" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="G212" s="9" t="n">
         <v>85000</v>
@@ -15121,10 +15178,10 @@
         <v>24</v>
       </c>
       <c r="Q212" s="7" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="R212" s="7" t="s">
-        <v>387</v>
+        <v>405</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15132,7 +15189,7 @@
         <v>225</v>
       </c>
       <c r="B213" s="7" t="s">
-        <v>388</v>
+        <v>406</v>
       </c>
       <c r="C213" s="6" t="s">
         <v>28</v>
@@ -15144,25 +15201,25 @@
         <v>1170</v>
       </c>
       <c r="F213" s="7" t="s">
-        <v>389</v>
+        <v>223</v>
       </c>
       <c r="G213" s="9" t="n">
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="H213" s="9" t="n">
-        <v>1400</v>
+        <v>2600</v>
       </c>
       <c r="I213" s="10" t="n">
         <f aca="false">IF(E213=0,0,(E213-H213)/E213)</f>
-        <v>-0.196581196581197</v>
+        <v>-1.22222222222222</v>
       </c>
       <c r="J213" s="6" t="str">
         <f aca="false">IF(E213&lt;G213,"LOSS",IF(E213&lt;H213*1.1,"THIN / RISK",IF(E213&gt;H213*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>LOSS</v>
       </c>
       <c r="K213" s="8" t="n">
         <f aca="false">IF(J213="OVERPRICED?",ROUND(H213*1.35,-1),MAX(E213,ROUND(H213*(1+$E$3),-1)))</f>
-        <v>1610</v>
+        <v>2990</v>
       </c>
       <c r="L213" s="8" t="n">
         <f aca="false">D213*E213</f>
@@ -15170,11 +15227,11 @@
       </c>
       <c r="M213" s="8" t="n">
         <f aca="false">D213*K213</f>
-        <v>38640</v>
+        <v>71760</v>
       </c>
       <c r="N213" s="8" t="n">
         <f aca="false">D213*H213</f>
-        <v>33600</v>
+        <v>62400</v>
       </c>
       <c r="O213" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C213,F213)),"","YES")</f>
@@ -15184,7 +15241,7 @@
         <v>24</v>
       </c>
       <c r="Q213" s="7" t="s">
-        <v>143</v>
+        <v>407</v>
       </c>
       <c r="R213" s="7" t="s">
         <v>31</v>
@@ -15195,7 +15252,7 @@
         <v>226</v>
       </c>
       <c r="B214" s="7" t="s">
-        <v>390</v>
+        <v>408</v>
       </c>
       <c r="C214" s="6" t="s">
         <v>28</v>
@@ -15207,25 +15264,25 @@
         <v>1430</v>
       </c>
       <c r="F214" s="7" t="s">
-        <v>389</v>
+        <v>223</v>
       </c>
       <c r="G214" s="9" t="n">
-        <v>1400</v>
+        <v>2600</v>
       </c>
       <c r="H214" s="9" t="n">
-        <v>1900</v>
+        <v>3600</v>
       </c>
       <c r="I214" s="10" t="n">
         <f aca="false">IF(E214=0,0,(E214-H214)/E214)</f>
-        <v>-0.328671328671329</v>
+        <v>-1.51748251748252</v>
       </c>
       <c r="J214" s="6" t="str">
         <f aca="false">IF(E214&lt;G214,"LOSS",IF(E214&lt;H214*1.1,"THIN / RISK",IF(E214&gt;H214*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>LOSS</v>
       </c>
       <c r="K214" s="8" t="n">
         <f aca="false">IF(J214="OVERPRICED?",ROUND(H214*1.35,-1),MAX(E214,ROUND(H214*(1+$E$3),-1)))</f>
-        <v>2190</v>
+        <v>4140</v>
       </c>
       <c r="L214" s="8" t="n">
         <f aca="false">D214*E214</f>
@@ -15233,11 +15290,11 @@
       </c>
       <c r="M214" s="8" t="n">
         <f aca="false">D214*K214</f>
-        <v>52560</v>
+        <v>99360</v>
       </c>
       <c r="N214" s="8" t="n">
         <f aca="false">D214*H214</f>
-        <v>45600</v>
+        <v>86400</v>
       </c>
       <c r="O214" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C214,F214)),"","YES")</f>
@@ -15247,7 +15304,7 @@
         <v>24</v>
       </c>
       <c r="Q214" s="7" t="s">
-        <v>143</v>
+        <v>407</v>
       </c>
       <c r="R214" s="7" t="s">
         <v>31</v>
@@ -15258,7 +15315,7 @@
         <v>227</v>
       </c>
       <c r="B215" s="7" t="s">
-        <v>391</v>
+        <v>409</v>
       </c>
       <c r="C215" s="6" t="s">
         <v>28</v>
@@ -15270,17 +15327,17 @@
         <v>1820</v>
       </c>
       <c r="F215" s="7" t="s">
-        <v>389</v>
+        <v>223</v>
       </c>
       <c r="G215" s="9" t="n">
-        <v>1900</v>
+        <v>3500</v>
       </c>
       <c r="H215" s="9" t="n">
-        <v>2600</v>
+        <v>4800</v>
       </c>
       <c r="I215" s="10" t="n">
         <f aca="false">IF(E215=0,0,(E215-H215)/E215)</f>
-        <v>-0.428571428571429</v>
+        <v>-1.63736263736264</v>
       </c>
       <c r="J215" s="6" t="str">
         <f aca="false">IF(E215&lt;G215,"LOSS",IF(E215&lt;H215*1.1,"THIN / RISK",IF(E215&gt;H215*1.8,"OVERPRICED?","OK")))</f>
@@ -15288,7 +15345,7 @@
       </c>
       <c r="K215" s="8" t="n">
         <f aca="false">IF(J215="OVERPRICED?",ROUND(H215*1.35,-1),MAX(E215,ROUND(H215*(1+$E$3),-1)))</f>
-        <v>2990</v>
+        <v>5520</v>
       </c>
       <c r="L215" s="8" t="n">
         <f aca="false">D215*E215</f>
@@ -15296,11 +15353,11 @@
       </c>
       <c r="M215" s="8" t="n">
         <f aca="false">D215*K215</f>
-        <v>71760</v>
+        <v>132480</v>
       </c>
       <c r="N215" s="8" t="n">
         <f aca="false">D215*H215</f>
-        <v>62400</v>
+        <v>115200</v>
       </c>
       <c r="O215" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C215,F215)),"","YES")</f>
@@ -15310,7 +15367,7 @@
         <v>24</v>
       </c>
       <c r="Q215" s="7" t="s">
-        <v>143</v>
+        <v>407</v>
       </c>
       <c r="R215" s="7" t="s">
         <v>31</v>
@@ -15321,7 +15378,7 @@
         <v>228</v>
       </c>
       <c r="B216" s="7" t="s">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="C216" s="6" t="s">
         <v>28</v>
@@ -15333,17 +15390,17 @@
         <v>2860</v>
       </c>
       <c r="F216" s="7" t="s">
-        <v>389</v>
+        <v>223</v>
       </c>
       <c r="G216" s="9" t="n">
-        <v>3200</v>
+        <v>6000</v>
       </c>
       <c r="H216" s="9" t="n">
-        <v>4200</v>
+        <v>8000</v>
       </c>
       <c r="I216" s="10" t="n">
         <f aca="false">IF(E216=0,0,(E216-H216)/E216)</f>
-        <v>-0.468531468531469</v>
+        <v>-1.7972027972028</v>
       </c>
       <c r="J216" s="6" t="str">
         <f aca="false">IF(E216&lt;G216,"LOSS",IF(E216&lt;H216*1.1,"THIN / RISK",IF(E216&gt;H216*1.8,"OVERPRICED?","OK")))</f>
@@ -15351,7 +15408,7 @@
       </c>
       <c r="K216" s="8" t="n">
         <f aca="false">IF(J216="OVERPRICED?",ROUND(H216*1.35,-1),MAX(E216,ROUND(H216*(1+$E$3),-1)))</f>
-        <v>4830</v>
+        <v>9200</v>
       </c>
       <c r="L216" s="8" t="n">
         <f aca="false">D216*E216</f>
@@ -15359,11 +15416,11 @@
       </c>
       <c r="M216" s="8" t="n">
         <f aca="false">D216*K216</f>
-        <v>115920</v>
+        <v>220800</v>
       </c>
       <c r="N216" s="8" t="n">
         <f aca="false">D216*H216</f>
-        <v>100800</v>
+        <v>192000</v>
       </c>
       <c r="O216" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C216,F216)),"","YES")</f>
@@ -15373,7 +15430,7 @@
         <v>24</v>
       </c>
       <c r="Q216" s="7" t="s">
-        <v>143</v>
+        <v>407</v>
       </c>
       <c r="R216" s="7" t="s">
         <v>31</v>
@@ -15384,7 +15441,7 @@
         <v>229</v>
       </c>
       <c r="B217" s="7" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="C217" s="6" t="s">
         <v>28</v>
@@ -15396,25 +15453,25 @@
         <v>2340</v>
       </c>
       <c r="F217" s="7" t="s">
-        <v>389</v>
+        <v>223</v>
       </c>
       <c r="G217" s="9" t="n">
-        <v>1800</v>
+        <v>3200</v>
       </c>
       <c r="H217" s="9" t="n">
-        <v>2600</v>
+        <v>4500</v>
       </c>
       <c r="I217" s="10" t="n">
         <f aca="false">IF(E217=0,0,(E217-H217)/E217)</f>
-        <v>-0.111111111111111</v>
+        <v>-0.923076923076923</v>
       </c>
       <c r="J217" s="6" t="str">
         <f aca="false">IF(E217&lt;G217,"LOSS",IF(E217&lt;H217*1.1,"THIN / RISK",IF(E217&gt;H217*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>LOSS</v>
       </c>
       <c r="K217" s="8" t="n">
         <f aca="false">IF(J217="OVERPRICED?",ROUND(H217*1.35,-1),MAX(E217,ROUND(H217*(1+$E$3),-1)))</f>
-        <v>2990</v>
+        <v>5180</v>
       </c>
       <c r="L217" s="8" t="n">
         <f aca="false">D217*E217</f>
@@ -15422,11 +15479,11 @@
       </c>
       <c r="M217" s="8" t="n">
         <f aca="false">D217*K217</f>
-        <v>71760</v>
+        <v>124320</v>
       </c>
       <c r="N217" s="8" t="n">
         <f aca="false">D217*H217</f>
-        <v>62400</v>
+        <v>108000</v>
       </c>
       <c r="O217" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C217,F217)),"","YES")</f>
@@ -15436,7 +15493,7 @@
         <v>24</v>
       </c>
       <c r="Q217" s="7" t="s">
-        <v>143</v>
+        <v>407</v>
       </c>
       <c r="R217" s="7" t="s">
         <v>31</v>
@@ -15447,7 +15504,7 @@
         <v>230</v>
       </c>
       <c r="B218" s="7" t="s">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="C218" s="6" t="s">
         <v>28</v>
@@ -15459,7 +15516,7 @@
         <v>9750</v>
       </c>
       <c r="F218" s="7" t="s">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="G218" s="9" t="n">
         <v>5950</v>
@@ -15499,7 +15556,7 @@
         <v>49</v>
       </c>
       <c r="Q218" s="7" t="s">
-        <v>396</v>
+        <v>414</v>
       </c>
       <c r="R218" s="7" t="s">
         <v>51</v>
@@ -15510,7 +15567,7 @@
         <v>231</v>
       </c>
       <c r="B219" s="7" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="C219" s="6" t="s">
         <v>28</v>
@@ -15522,7 +15579,7 @@
         <v>12350</v>
       </c>
       <c r="F219" s="7" t="s">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="G219" s="9" t="n">
         <v>5950</v>
@@ -15562,7 +15619,7 @@
         <v>43</v>
       </c>
       <c r="Q219" s="7" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
       <c r="R219" s="7"/>
     </row>
@@ -15571,7 +15628,7 @@
         <v>233</v>
       </c>
       <c r="B220" s="7" t="s">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="C220" s="6" t="s">
         <v>112</v>
@@ -15623,7 +15680,7 @@
         <v>43</v>
       </c>
       <c r="Q220" s="7" t="s">
-        <v>400</v>
+        <v>418</v>
       </c>
       <c r="R220" s="7"/>
     </row>
@@ -15632,7 +15689,7 @@
         <v>234</v>
       </c>
       <c r="B221" s="7" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="C221" s="6" t="s">
         <v>22</v>
@@ -15684,7 +15741,7 @@
         <v>49</v>
       </c>
       <c r="Q221" s="7" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
       <c r="R221" s="7" t="s">
         <v>51</v>
@@ -15695,7 +15752,7 @@
         <v>235</v>
       </c>
       <c r="B222" s="7" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="C222" s="6" t="s">
         <v>28</v>
@@ -15747,10 +15804,10 @@
         <v>24</v>
       </c>
       <c r="Q222" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R222" s="7" t="s">
-        <v>404</v>
+        <v>422</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15758,7 +15815,7 @@
         <v>236</v>
       </c>
       <c r="B223" s="7" t="s">
-        <v>405</v>
+        <v>423</v>
       </c>
       <c r="C223" s="6" t="s">
         <v>22</v>
@@ -15770,7 +15827,7 @@
         <v>2860</v>
       </c>
       <c r="F223" s="7" t="s">
-        <v>406</v>
+        <v>424</v>
       </c>
       <c r="G223" s="9" t="n">
         <v>2400</v>
@@ -15810,10 +15867,10 @@
         <v>24</v>
       </c>
       <c r="Q223" s="7" t="s">
-        <v>407</v>
+        <v>425</v>
       </c>
       <c r="R223" s="7" t="s">
-        <v>408</v>
+        <v>426</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15821,7 +15878,7 @@
         <v>237</v>
       </c>
       <c r="B224" s="7" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
       <c r="C224" s="6" t="s">
         <v>28</v>
@@ -15873,7 +15930,7 @@
         <v>24</v>
       </c>
       <c r="Q224" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="R224" s="7" t="s">
         <v>31</v>
@@ -15884,7 +15941,7 @@
         <v>238</v>
       </c>
       <c r="B225" s="7" t="s">
-        <v>410</v>
+        <v>428</v>
       </c>
       <c r="C225" s="6" t="s">
         <v>28</v>
@@ -15896,7 +15953,7 @@
         <v>8450</v>
       </c>
       <c r="F225" s="7" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="G225" s="9" t="n">
         <v>7800</v>
@@ -15936,7 +15993,7 @@
         <v>43</v>
       </c>
       <c r="Q225" s="7" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
       <c r="R225" s="7"/>
     </row>
@@ -15945,7 +16002,7 @@
         <v>239</v>
       </c>
       <c r="B226" s="7" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="C226" s="6" t="s">
         <v>112</v>
@@ -15997,7 +16054,7 @@
         <v>43</v>
       </c>
       <c r="Q226" s="7" t="s">
-        <v>414</v>
+        <v>432</v>
       </c>
       <c r="R226" s="7"/>
     </row>
@@ -16006,7 +16063,7 @@
         <v>240</v>
       </c>
       <c r="B227" s="7" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
       <c r="C227" s="6" t="s">
         <v>28</v>
@@ -16021,22 +16078,22 @@
         <v>37</v>
       </c>
       <c r="G227" s="9" t="n">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="H227" s="9" t="n">
-        <v>250</v>
+        <v>1300</v>
       </c>
       <c r="I227" s="10" t="n">
         <f aca="false">IF(E227=0,0,(E227-H227)/E227)</f>
-        <v>0.230769230769231</v>
+        <v>-3</v>
       </c>
       <c r="J227" s="6" t="str">
         <f aca="false">IF(E227&lt;G227,"LOSS",IF(E227&lt;H227*1.1,"THIN / RISK",IF(E227&gt;H227*1.8,"OVERPRICED?","OK")))</f>
-        <v>OK</v>
+        <v>LOSS</v>
       </c>
       <c r="K227" s="8" t="n">
         <f aca="false">IF(J227="OVERPRICED?",ROUND(H227*1.35,-1),MAX(E227,ROUND(H227*(1+$E$3),-1)))</f>
-        <v>325</v>
+        <v>1500</v>
       </c>
       <c r="L227" s="8" t="n">
         <f aca="false">D227*E227</f>
@@ -16044,11 +16101,11 @@
       </c>
       <c r="M227" s="8" t="n">
         <f aca="false">D227*K227</f>
-        <v>16250</v>
+        <v>75000</v>
       </c>
       <c r="N227" s="8" t="n">
         <f aca="false">D227*H227</f>
-        <v>12500</v>
+        <v>65000</v>
       </c>
       <c r="O227" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C227,F227)),"","YES")</f>
@@ -16058,15 +16115,15 @@
         <v>24</v>
       </c>
       <c r="Q227" s="7" t="s">
-        <v>143</v>
+        <v>434</v>
       </c>
       <c r="R227" s="7" t="s">
-        <v>416</v>
+        <v>435</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B228" s="3" t="s">
-        <v>417</v>
+        <v>436</v>
       </c>
       <c r="L228" s="11" t="n">
         <f aca="false">SUM(L6:L227)</f>
@@ -16074,11 +16131,11 @@
       </c>
       <c r="M228" s="11" t="n">
         <f aca="false">SUM(M6:M227)</f>
-        <v>13049175</v>
+        <v>14464835</v>
       </c>
       <c r="N228" s="11" t="n">
         <f aca="false">SUM(N6:N227)</f>
-        <v>10303543</v>
+        <v>11550488</v>
       </c>
     </row>
   </sheetData>
@@ -16127,12 +16184,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>418</v>
+        <v>437</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>419</v>
+        <v>438</v>
       </c>
       <c r="B3" s="11" t="n">
         <f aca="false">COUNTA('Rate Check'!A6:A227)</f>
@@ -16141,43 +16198,43 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>420</v>
+        <v>439</v>
       </c>
       <c r="B4" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"LOSS")</f>
-        <v>64</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>421</v>
+        <v>440</v>
       </c>
       <c r="B5" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"THIN / RISK")</f>
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>422</v>
+        <v>441</v>
       </c>
       <c r="B6" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"OK")</f>
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>423</v>
+        <v>442</v>
       </c>
       <c r="B7" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"OVERPRICED?")</f>
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>424</v>
+        <v>443</v>
       </c>
       <c r="B8" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!O6:O227,"YES")</f>
@@ -16189,7 +16246,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>425</v>
+        <v>444</v>
       </c>
       <c r="B10" s="11" t="n">
         <f aca="false">'Rate Check'!L228</f>
@@ -16198,38 +16255,38 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>426</v>
+        <v>445</v>
       </c>
       <c r="B11" s="11" t="n">
         <f aca="false">'Rate Check'!N228</f>
-        <v>10303543</v>
+        <v>11550488</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>427</v>
+        <v>446</v>
       </c>
       <c r="B12" s="11" t="n">
         <f aca="false">B10-B11</f>
-        <v>1905965</v>
+        <v>659020</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>428</v>
+        <v>447</v>
       </c>
       <c r="B13" s="14" t="n">
         <f aca="false">IF(B10=0,0,B12/B10)</f>
-        <v>0.156104979823921</v>
+        <v>0.053975966926759</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>429</v>
+        <v>448</v>
       </c>
       <c r="B14" s="11" t="n">
         <f aca="false">SUMPRODUCT(('Rate Check'!E6:E227&lt;'Rate Check'!H6:H227)*('Rate Check'!H6:H227-'Rate Check'!E6:E227)*'Rate Check'!D6:D227)</f>
-        <v>889833</v>
+        <v>2088163</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16237,20 +16294,20 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>430</v>
+        <v>449</v>
       </c>
       <c r="B16" s="11" t="n">
         <f aca="false">'Rate Check'!M228</f>
-        <v>13049175</v>
+        <v>14464835</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>431</v>
+        <v>450</v>
       </c>
       <c r="B17" s="14" t="n">
         <f aca="false">IF(B16=0,0,(B16-B11)/B16)</f>
-        <v>0.210406558269009</v>
+        <v>0.201478067326727</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16258,7 +16315,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>432</v>
+        <v>451</v>
       </c>
       <c r="B19" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!P6:P227,"V")</f>
@@ -16267,20 +16324,20 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>433</v>
+        <v>452</v>
       </c>
       <c r="B20" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!P6:P227,"S")</f>
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>434</v>
+        <v>453</v>
       </c>
       <c r="B21" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!P6:P227,"N")</f>
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -16308,247 +16365,247 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>435</v>
+        <v>454</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>436</v>
+        <v>455</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>437</v>
+        <v>456</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>438</v>
+        <v>457</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>439</v>
+        <v>458</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>440</v>
+        <v>459</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>441</v>
+        <v>460</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>442</v>
+        <v>461</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>443</v>
+        <v>462</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>444</v>
+        <v>463</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>445</v>
+        <v>464</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>446</v>
+        <v>465</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>447</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>448</v>
+        <v>467</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>449</v>
+        <v>468</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>450</v>
+        <v>469</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>451</v>
+        <v>470</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>452</v>
+        <v>471</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>453</v>
+        <v>472</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>454</v>
+        <v>473</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>455</v>
+        <v>474</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>456</v>
+        <v>475</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>457</v>
+        <v>476</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>459</v>
+        <v>478</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>460</v>
+        <v>479</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>461</v>
+        <v>480</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>462</v>
+        <v>481</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>463</v>
+        <v>482</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>464</v>
+        <v>483</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>465</v>
+        <v>484</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>466</v>
+        <v>485</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>467</v>
+        <v>486</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>468</v>
+        <v>487</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>469</v>
+        <v>488</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>470</v>
+        <v>489</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>471</v>
+        <v>490</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>472</v>
+        <v>491</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>473</v>
+        <v>492</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>474</v>
+        <v>493</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>475</v>
+        <v>494</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>476</v>
+        <v>495</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>477</v>
+        <v>496</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>478</v>
+        <v>497</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>479</v>
+        <v>498</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>480</v>
+        <v>499</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>481</v>
+        <v>500</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>482</v>
+        <v>501</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>483</v>
+        <v>502</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>484</v>
+        <v>503</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>485</v>
+        <v>504</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>486</v>
+        <v>505</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>487</v>
+        <v>506</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>488</v>
+        <v>507</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>489</v>
+        <v>508</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>490</v>
+        <v>509</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>491</v>
+        <v>510</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>492</v>
+        <v>511</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>493</v>
+        <v>512</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>494</v>
+        <v>513</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>495</v>
+        <v>514</v>
       </c>
     </row>
   </sheetData>

--- a/quotes/PR-217-228/Quote_PR217_PR228_Rate_Check.xlsx
+++ b/quotes/PR-217-228/Quote_PR217_PR228_Rate_Check.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1367" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1385" uniqueCount="533">
   <si>
     <t xml:space="preserve">Zidane Corporation - Quote PR-217 &amp; PR-228: Brand + Buying Rate Check</t>
   </si>
@@ -174,525 +174,561 @@
     <t xml:space="preserve">7 DRAWER TOOL TROLLEY</t>
   </si>
   <si>
+    <t xml:space="preserve">Licota (AWX series, empty)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ktools Yato 7-drawer 211pc 315,000 / 6-drawer 177pc 220,000 (with tools); empty Licota est</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Total 87000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOUBLE OPEN RING OFFSET WRENCH SET (12PCS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart Licota 14pc set 25,660</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Harden 15190</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOUBLE OPEN END WRENCH 6 TO 32 (12 PCS SET)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart Licota; Ingco 12pc 9,899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Harden 12630</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOUBLE OPEN END WRENCH 36X41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">goldentools.ae Licota DOE 21x23 AED 26 scaled to 36x41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOUBLE OPEN END WRENCH 41X46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">goldentools.ae Licota DOE 21x23 AED 26 scaled to 41x46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMBINATION WRENCH 8 TO 32 (14 PCS SET)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart Licota 14pc combo 25,660</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Tolsen 11780</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOCKET SET (113PCS) 1/4" &amp; 1/2"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart Licota 120pc 56,890-67,130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIN PUNCH SET (06PCS SET)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart Licota 6pc pin punch 5,460</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOLLOW PUNCH (3MM-25MM) (15PCS SET)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Licota TAP-50042 hollow punch (PH) scaled to 15pc 3-25mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Harden 4699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LONG TYPE HEX KEY WRENCH SET 09 PCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart Licota 9pc long hex 4,400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHORT TYPE HEX KEY WRENCH SET (09PCS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart Licota hex sets (scaled)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Harden 1420</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LONG TYPE HEX WRENCH SET 09 PCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">same as 17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALLEN HEX KEY 12MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">goldentools.ae Licota 12mm hex AED 250/20pc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALLEN (HEX) KEY 14MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">goldentools.ae Licota 12mm hex scaled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALLEN (HEX) KEY 16MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIRCLIP PLIER INTERNAL STRAIGHT 175MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart Licota 4pc snap ring plier set 175mm 11,650 (=int/ext straight/bent, per pc 2,913)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIRCLIP PLIER INTERNAL BENT 175MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">same set</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIRCLIP PLIER EXTERNAL STRAIGHT 175MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIRCLIP PLIER EXTERNAL BENT 175MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIRCLIP PLIER INTERNAL STRAIGHT 230MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart.pk Licota 175mm snap ring set (2,913/pc) scaled to 230mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. 230mm circlip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIRCLIP PLIER EXTERNAL STRAIGHT 230MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHISEL SET (05 PCS SET)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart Licota 5pc punch chisel 4,000-4,720</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIPE WRENCH SIZE 10"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart.pk Licota 18in 9,620 / 14in 6,730 scaled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Total 1700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIPE WRENCH SIZE 12"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Harden 2850</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIPE WRENCH SIZE 18"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart Licota 18in pipe wrench 9,620</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIPE WRENCH SIZE 24"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Harden 6560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIPE WRENCH SIZE 36"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Total 7900</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLEDGE HAMMER 1 LBS WITH FIBREGLASS HANDLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">goldentools.ae Licota sledge 1500g AED 96 scaled to 1lb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Total 2000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLEDGE HAMMER 3 LBS WITH FIBREGLASS HANDLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">goldentools.ae Licota sledge 1500g AED 96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Harden 3380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOFT FACE DEAD BLOW HAMMER 50MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">goldentools.ae Licota dead blow 45mm AED 65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Harden 2450</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VICE GRIP PLIER 08"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">goldentools.ae Licota locking plier 10in AED 42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. 8in (alt 10in Harden toolsmart 1,660 / Ingco 1,790</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORDLESS IMPACT WRENCH 185NM (Bosch)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bosch Professional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ktools GDX 180-Li 45,000 solo / 79,000 kit; kamadi 75,200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORDLESS IMPACT WRENCH 350N (Bosch)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bosch Professional GDS 18V-350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No PK listing; est from GDX/GDS range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. GDS 18V-350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORDLESS IMPACT WRENCH 1000N (Bosch)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kamadi GDS 18V-1000 kit 143,800; ktools solo 70,000 (oos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEX IMPACT ADAPTOR 1/2" FEMALE TO 1/4" FEMALE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">goldentools.ae Licota AED x~100 (AED76 + PK import)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLAT FILE 12"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zeeshanhardware Yato YT-6190 12in 1,750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUNDE FILE 12"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zeeshanhardware Yato 12in file 1,750 (flat; round similar)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Yato round file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED WITH HOOK BRAKE 21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">goldentools.ae/amazon.ae Licota 6in 3-jaw AED 105-120 (~PKR 9k) scaled + import</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED WITH HOOK BRAK 250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">goldentools.ae Licota pullers (scaled) + import</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED 160 X 300 MM 5T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED 250 X 300 MM 7.5T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INTERNAL EXTRACTOR WITH REINFORCED COLLAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Licota catalogue; no PK listing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MECHANICAL PULLER 3 ARMED 200X200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">goldentools.ae Licota 3-jaw 6in AED 120 scaled to 8in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Yato 8500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MECHANICAL PULLER 3 ARMED 250X250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">goldentools.ae Licota 3-jaw 6in AED 120 scaled to 10in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Yato 19030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRILL MACHINE CORDLESS ROTARY HAMMER Bosch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ktools GBH 180-Li 49,000 solo / 115,000 kit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUAL GREASE GUN 5KG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yato / Industrial (bucket type)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. 5kg bucket grease pump</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIR GREASE GUN 500CC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart Licota grease gun 7,760 (air premium)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. air grease gun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HAND GREASE GUN WITH HOSE 500CC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart Licota grease gun 400cc 7,760</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GREASE PIPE 1/4"X12"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOUBLE HANDLE GREASE NOZZLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STEEL MEASURMENT TAPE 100M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Market (Licota tapes PK mein nahi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. steel 100m (alt Total fibreglass 100m toolsmart 5,250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STEEL MEASURMENT TAPE 50M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Ingco 5920</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALIGNING PRY BAR DIA 5/8" X 18" LENGTH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. pry bar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADJUSTABLE WRENCH 15"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart Licota 10" 5,310; Total 15" 3,700-3,890</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Total 3890</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROUGH FILE SMOOTH 10"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zeeshanhardware Yato YT-6228 10in 1,350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POLISH FILE SMOOTH 10"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REVOLVING CENTRE MT4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vertex (Taiwan)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REVOLVING CENTRE MT3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIRCUMFERENCE TAPE (60-950) (D20-300)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insize</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIRCUMFERENCE TAPE (940-2200) (D300-700)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEASURING TAPE 5M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Total 1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS COBALT DRILL SET 1-13MM 25 PCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dormer A095 (HSS-Co)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dormer 25pc 1-13mm set - PK listing n/a (UK/US list scaled)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Dormer 25pc cobalt set; alt Ingco AKD1251 M2 22,185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BITS 1/16-1/2" 29 PCS SET</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dormer A095 (A002 x29)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mrosupply Dormer A09518 29pc set (USD) scaled - PK listing n/a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. 29pc inch set</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 14MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dormer A130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dormer A130 14mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 15MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dormer A130 15mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 15.5MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dormer A130 15.5mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 16MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dormer A130 16mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 16.5MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dormer A130 16.5mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 17MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dormer A130 17mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 17.5MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dormer A130 17.5mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 19MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dormer A130 19mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 21MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dormer A130 21mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 25MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dormer A130 25mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 30MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dormer A130 30mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 32MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dormer A130 32mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSS DRILL BIT 35MM TAPER SHANK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dormer A130 35mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MORSE TAPER EXTENSION SOCKET SLEEVE ADAPT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEAD CENTRE DIAMOND TIP M2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEAD CENTRE DIAMOND TIP M3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIGITAL VERINER CALIPER 300MM (Insize brand)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kamadi 1108-300 18,100; amjadhardware 15,800; ktools 19,500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUAL VERNIER CALLIPER 12" (Insize brand)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kamadi 1205-300S 15,800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANUAL VERNIER CALLIPER 8" (Insize (Bosch))</t>
+  </si>
+  <si>
+    <t xml:space="preserve">purchaser 1205-200S 7,928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERNIER DEPTH GUAGE 250MM GRADUATION 0.02M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. depth gauge 250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORDLESS DRILL DRIVER 150NM Bosch</t>
+  </si>
+  <si>
     <t xml:space="preserve">S</t>
   </si>
   <si>
-    <t xml:space="preserve">ktools Total 7-drawer roller cabinet THRC02071P 85,000-87,000 (oos) -- Licota PK mein nahi; alt Stanley 7-drawer ktools 135,000</t>
+    <t xml:space="preserve">ktools Bosch GSB 18V-150C 199,500 (oos, single listing)</t>
   </si>
   <si>
     <t xml:space="preserve">Spec/pack/stock farq - source dekho</t>
   </si>
   <si>
-    <t xml:space="preserve">DOUBLE OPEN RING OFFSET WRENCH SET (12PCS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Harden double ring 6-32 12pc 15,190 (alt Ingco offset ring 12pc hetools 10,390)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOUBLE OPEN END WRENCH 6 TO 32 (12 PCS SET)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Harden DOE 6-32 12pc 12,630 (alt Ingco HKSPA2142 ingcotool 9,899)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOUBLE OPEN END WRENCH 36X41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Licota wrench sets (scaled); goldentools.ae Licota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOUBLE OPEN END WRENCH 41X46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMBINATION WRENCH 8 TO 32 (14 PCS SET)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tolsen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">imsons Tolsen 15889 6-32 14pc 11,780; toolexpert 7,500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOCKET SET (113PCS) 1/4" &amp; 1/2"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Licota 120pc 56,890-67,130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIN PUNCH SET (06PCS SET)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Licota 6pc pin punch 5,460</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOLLOW PUNCH (3MM-25MM) (15PCS SET)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harden 12pc hollow punch 3-16mm: toolsmart 4,140; ingcotool 4,199-4,699; toolshop 4,399 -- SPEC MISMATCH (3-25 15pc nahi mila)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LONG TYPE HEX KEY WRENCH SET 09 PCS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Licota 9pc long hex 4,400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SHORT TYPE HEX KEY WRENCH SET (09PCS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Harden 9pc short hex 1.5-10mm 1,420</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LONG TYPE HEX WRENCH SET 09 PCS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">same as 17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALLEN HEX KEY 12MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">goldentools.ae Licota 12mm AED 250/20pc (~PKR 950 ea)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALLEN (HEX) KEY 14MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">goldentools.ae Licota 12mm (scaled)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALLEN (HEX) KEY 16MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIRCLIP PLIER INTERNAL STRAIGHT 175MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Licota 4pc snap ring plier set 175mm 11,650 (=int/ext straight/bent, per pc 2,913)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIRCLIP PLIER INTERNAL BENT 175MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">same set</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIRCLIP PLIER EXTERNAL STRAIGHT 175MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIRCLIP PLIER EXTERNAL BENT 175MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIRCLIP PLIER INTERNAL STRAIGHT 230MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Licota pliers (scaled)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. 230mm circlip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIRCLIP PLIER EXTERNAL STRAIGHT 230MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHISEL SET (05 PCS SET)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Licota 5pc punch chisel 4,000-4,720</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIPE WRENCH SIZE 10"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Total 10in pipe wrench 1,700; totaltool 1,400</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIPE WRENCH SIZE 12"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Harden HD 12in pipe wrench 2,850 (alt Total 12in totaltool 1,900)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIPE WRENCH SIZE 18"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Licota 18in pipe wrench 9,620</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIPE WRENCH SIZE 24"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Harden 24in pipe wrench 6,560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIPE WRENCH SIZE 36"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">totaltool Total 36in THT171366 7,900 (alt Wiseup toolshub 6,300)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLEDGE HAMMER 1 LBS WITH FIBREGLASS HANDLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Total 2lb sledge THT79026 2,000; purchaser 1,820 -- SPEC: 2lb (1lb sledge nahi mila)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLEDGE HAMMER 3 LBS WITH FIBREGLASS HANDLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Harden 3lb sledge fibreglass 590323 3,380 (alt Total 3lb 2,460/purchaser 2,240)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOFT FACE DEAD BLOW HAMMER 50MM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pakistanpowertools Harden dead blow 590445 1,987-2,450</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VICE GRIP PLIER 08"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ingcotool locking plier 1,499; Licota premium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. 8in (alt 10in Harden toolsmart 1,660 / Ingco 1,790</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORDLESS IMPACT WRENCH 185NM (Bosch)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bosch Professional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ktools GDX 180-Li 45,000 solo / 79,000 kit; kamadi 75,200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORDLESS IMPACT WRENCH 350N (Bosch)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bosch Professional GDS 18V-350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No PK listing; est from GDX/GDS range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. GDS 18V-350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORDLESS IMPACT WRENCH 1000N (Bosch)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kamadi GDS 18V-1000 kit 143,800; ktools solo 70,000 (oos)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HEX IMPACT ADAPTOR 1/2" FEMALE TO 1/4" FEMALE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Licota impact accessories</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLAT FILE 12"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yato</t>
-  </si>
-  <si>
-    <t xml:space="preserve">zeeshanhardware Yato YT-6190 12in 1,750</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROUNDE FILE 12"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">zeeshanhardware Yato 12in file 1,750 (flat; round similar)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Yato round file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED WITH HOOK BRAKE 21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">goldentools.ae/amazon.ae Licota 6in 3-jaw AED 105-120 (~PKR 9k) scaled + import</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED WITH HOOK BRAK 250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">goldentools.ae Licota pullers (scaled) + import</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED 160 X 300 MM 5T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED 250 X 300 MM 7.5T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INTERNAL EXTRACTOR WITH REINFORCED COLLAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Licota catalogue; no PK listing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MECHANICAL PULLER 3 ARMED 200X200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">zeeshanhardware Yato YT-2522 bearing puller 8in 8,500 -- jaw count confirm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MECHANICAL PULLER 3 ARMED 250X250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">imartpk Yato 3-arm jaw puller 12in 19,030 (page ~2yr old)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRILL MACHINE CORDLESS ROTARY HAMMER Bosch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ktools GBH 180-Li 49,000 solo / 115,000 kit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANUAL GREASE GUN 5KG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yato / Industrial (bucket type)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. 5kg bucket grease pump</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIR GREASE GUN 500CC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Licota grease gun 7,760 (air premium)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. air grease gun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HAND GREASE GUN WITH HOSE 500CC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Licota grease gun 400cc 7,760</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GREASE PIPE 1/4"X12"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOUBLE HANDLE GREASE NOZZLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STEEL MEASURMENT TAPE 100M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Market (Licota tapes PK mein nahi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. steel 100m (alt Total fibreglass 100m toolsmart 5,250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STEEL MEASURMENT TAPE 50M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ingco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Ingco 50m steel HSMT8550 5,920 (alt Total TMT710506 4,750)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALIGNING PRY BAR DIA 5/8" X 18" LENGTH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. pry bar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADJUSTABLE WRENCH 15"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Total 15in THT1010153 3,890; pakistanpowertools 3,700 (alt Ingco 4,630)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROUGH FILE SMOOTH 10"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">zeeshanhardware Yato YT-6228 10in 1,350</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POLISH FILE SMOOTH 10"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REVOLVING CENTRE MT4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vertex (Taiwan)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">REVOLVING CENTRE MT3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIRCUMFERENCE TAPE (60-950) (D20-300)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insize</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIRCUMFERENCE TAPE (940-2200) (D300-700)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MEASURING TAPE 5M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">toolsmart Total 5m TMT126251 1,000; totaltool 700-770</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS COBALT DRILL SET 1-13MM 25 PCS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormer A095 (HSS-Co)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormer 25pc 1-13mm set - PK listing n/a (UK/US list scaled)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Dormer 25pc cobalt set; alt Ingco AKD1251 M2 22,185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BITS 1/16-1/2" 29 PCS SET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormer A095 (A002 x29)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mrosupply Dormer A09518 29pc set (USD) scaled - PK listing n/a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. 29pc inch set</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 14MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormer A130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormer A130 14mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 15MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormer A130 15mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 15.5MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormer A130 15.5mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 16MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormer A130 16mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 16.5MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormer A130 16.5mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 17MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormer A130 17mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 17.5MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormer A130 17.5mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 19MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormer A130 19mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 21MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormer A130 21mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 25MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormer A130 25mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 30MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormer A130 30mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 32MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormer A130 32mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSS DRILL BIT 35MM TAPER SHANK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormer A130 35mm: khmtools.com.ph PHP list x4.95 (+30% PK import); toolsmart.pk A130 range from 5,880</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MORSE TAPER EXTENSION SOCKET SLEEVE ADAPT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DEAD CENTRE DIAMOND TIP M2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DEAD CENTRE DIAMOND TIP M3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIGITAL VERINER CALIPER 300MM (Insize brand)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kamadi 1108-300 18,100; amjadhardware 15,800; ktools 19,500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANUAL VERNIER CALLIPER 12" (Insize brand)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kamadi 1205-300S 15,800</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MANUAL VERNIER CALLIPER 8" (Insize (Bosch))</t>
-  </si>
-  <si>
-    <t xml:space="preserve">purchaser 1205-200S 7,928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VERNIER DEPTH GUAGE 250MM GRADUATION 0.02M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. depth gauge 250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORDLESS DRILL DRIVER 150NM Bosch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ktools Bosch GSB 18V-150C 199,500 (oos, single listing)</t>
-  </si>
-  <si>
     <t xml:space="preserve">TAP SET 1/2" BSPF LEFT HAND (Dormer)</t>
   </si>
   <si>
@@ -735,7 +771,7 @@
     <t xml:space="preserve">C-CLAMP 6"</t>
   </si>
   <si>
-    <t xml:space="preserve">toolsmart Total G clamp 6in THT13161 2,420</t>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Total 2420</t>
   </si>
   <si>
     <t xml:space="preserve">C-CLAMP 12"</t>
@@ -747,7 +783,7 @@
     <t xml:space="preserve">SPIRIT LEVEL 1 METER</t>
   </si>
   <si>
-    <t xml:space="preserve">Total 100cm TMT210026: totaltool 2,600; powerhouseexpress 2,808-3,350</t>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Total 3350</t>
   </si>
   <si>
     <t xml:space="preserve">MAGNET SPIRIT LEVEL 12"</t>
@@ -765,7 +801,10 @@
     <t xml:space="preserve">CARBON STEEL RIGHT ANGLE 300MM</t>
   </si>
   <si>
-    <t xml:space="preserve">ezmakaan Harden aluminium try square 300mm 580713 3,125 (old page) -- SPEC: aluminium</t>
+    <t xml:space="preserve">Insize square est (industrybuying 2280-300 INR ref)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Harden 3125</t>
   </si>
   <si>
     <t xml:space="preserve">GAS CUTTING TORCH MEDIUM 6-50MM</t>
@@ -945,7 +984,10 @@
     <t xml:space="preserve">FLATE METAL SCRAPPER 50MM</t>
   </si>
   <si>
-    <t xml:space="preserve">imsons Tolsen 50mm wall scraper 360</t>
+    <t xml:space="preserve">Licota gasket scraper est (UAE ref)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Tolsen 360</t>
   </si>
   <si>
     <t xml:space="preserve">WD 40 330ML (MULTI PURPOSE)</t>
@@ -1230,7 +1272,13 @@
     <t xml:space="preserve">BENCH VISE 08"</t>
   </si>
   <si>
-    <t xml:space="preserve">toolsmart Ingco 8in bench vice HBV088 31,300; purchaser 24,360 -- Yato PK mein nahi</t>
+    <t xml:space="preserve">Yato YT-65049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yato UK GBP250; Total 8" PK 17,999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Ingco 31300</t>
   </si>
   <si>
     <t xml:space="preserve">BENCH VISE 12"</t>
@@ -1266,16 +1314,22 @@
     <t xml:space="preserve">HYDRAULIC JACK 3 TON</t>
   </si>
   <si>
-    <t xml:space="preserve">Ronix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPEC: 3T nahi mila, Ronix 5T diya (ingcomart 5,950); alt ktools Ingco 4T range 6,300-7,600</t>
+    <t xml:space="preserve">Yato YT-17001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pakwheels 5T bottle jack 4,000-5,999; purchaser 8,390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Ronix 5950</t>
   </si>
   <si>
     <t xml:space="preserve">HYDRAULIC JACK 5 TON</t>
   </si>
   <si>
-    <t xml:space="preserve">ingcomart Ronix RH-4903 5T bottle jack 5,360-5,950</t>
+    <t xml:space="preserve">Yato YT-17002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pakwheels 5,499-5,999 (generic); Yato premium</t>
   </si>
   <si>
     <t xml:space="preserve">CORDLESS SMALL ANGLE GRINDER 125MM EQUIVAL</t>
@@ -2719,25 +2773,25 @@
         <v>161070</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>87000</v>
+        <v>150000</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>87000</v>
+        <v>210000</v>
       </c>
       <c r="I13" s="10" t="n">
         <f aca="false">IF(E13=0,0,(E13-H13)/E13)</f>
-        <v>0.459862171726579</v>
+        <v>-0.303780964797914</v>
       </c>
       <c r="J13" s="6" t="str">
         <f aca="false">IF(E13&lt;G13,"LOSS",IF(E13&lt;H13*1.1,"THIN / RISK",IF(E13&gt;H13*1.8,"OVERPRICED?","OK")))</f>
-        <v>OVERPRICED?</v>
+        <v>THIN / RISK</v>
       </c>
       <c r="K13" s="8" t="n">
         <f aca="false">IF(J13="OVERPRICED?",ROUND(H13*1.35,-1),MAX(E13,ROUND(H13*(1+$E$3),-1)))</f>
-        <v>117450</v>
+        <v>241500</v>
       </c>
       <c r="L13" s="8" t="n">
         <f aca="false">D13*E13</f>
@@ -2745,18 +2799,18 @@
       </c>
       <c r="M13" s="8" t="n">
         <f aca="false">D13*K13</f>
-        <v>352350</v>
+        <v>724500</v>
       </c>
       <c r="N13" s="8" t="n">
         <f aca="false">D13*H13</f>
-        <v>261000</v>
+        <v>630000</v>
       </c>
       <c r="O13" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C13,F13)),"","YES")</f>
-        <v>YES</v>
+        <v/>
       </c>
       <c r="P13" s="6" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="Q13" s="7" t="s">
         <v>50</v>
@@ -2765,7 +2819,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="n">
         <v>9</v>
       </c>
@@ -2782,25 +2836,25 @@
         <v>18200</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>15190</v>
+        <v>20000</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>15190</v>
+        <v>26000</v>
       </c>
       <c r="I14" s="10" t="n">
         <f aca="false">IF(E14=0,0,(E14-H14)/E14)</f>
-        <v>0.165384615384615</v>
+        <v>-0.428571428571429</v>
       </c>
       <c r="J14" s="6" t="str">
         <f aca="false">IF(E14&lt;G14,"LOSS",IF(E14&lt;H14*1.1,"THIN / RISK",IF(E14&gt;H14*1.8,"OVERPRICED?","OK")))</f>
-        <v>OK</v>
+        <v>LOSS</v>
       </c>
       <c r="K14" s="8" t="n">
         <f aca="false">IF(J14="OVERPRICED?",ROUND(H14*1.35,-1),MAX(E14,ROUND(H14*(1+$E$3),-1)))</f>
-        <v>18200</v>
+        <v>29900</v>
       </c>
       <c r="L14" s="8" t="n">
         <f aca="false">D14*E14</f>
@@ -2808,25 +2862,27 @@
       </c>
       <c r="M14" s="8" t="n">
         <f aca="false">D14*K14</f>
-        <v>72800</v>
+        <v>119600</v>
       </c>
       <c r="N14" s="8" t="n">
         <f aca="false">D14*H14</f>
-        <v>60760</v>
+        <v>104000</v>
       </c>
       <c r="O14" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C14,F14)),"","YES")</f>
-        <v>YES</v>
+        <v/>
       </c>
       <c r="P14" s="6" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="Q14" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="R14" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="R14" s="7"/>
-    </row>
-    <row r="15" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="15" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="n">
         <v>10</v>
       </c>
@@ -2843,25 +2899,25 @@
         <v>15600</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>12630</v>
+        <v>16000</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>12630</v>
+        <v>21000</v>
       </c>
       <c r="I15" s="10" t="n">
         <f aca="false">IF(E15=0,0,(E15-H15)/E15)</f>
-        <v>0.190384615384615</v>
+        <v>-0.346153846153846</v>
       </c>
       <c r="J15" s="6" t="str">
         <f aca="false">IF(E15&lt;G15,"LOSS",IF(E15&lt;H15*1.1,"THIN / RISK",IF(E15&gt;H15*1.8,"OVERPRICED?","OK")))</f>
-        <v>OK</v>
+        <v>LOSS</v>
       </c>
       <c r="K15" s="8" t="n">
         <f aca="false">IF(J15="OVERPRICED?",ROUND(H15*1.35,-1),MAX(E15,ROUND(H15*(1+$E$3),-1)))</f>
-        <v>15600</v>
+        <v>24150</v>
       </c>
       <c r="L15" s="8" t="n">
         <f aca="false">D15*E15</f>
@@ -2869,30 +2925,32 @@
       </c>
       <c r="M15" s="8" t="n">
         <f aca="false">D15*K15</f>
-        <v>62400</v>
+        <v>96600</v>
       </c>
       <c r="N15" s="8" t="n">
         <f aca="false">D15*H15</f>
-        <v>50520</v>
+        <v>84000</v>
       </c>
       <c r="O15" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C15,F15)),"","YES")</f>
-        <v>YES</v>
+        <v/>
       </c>
       <c r="P15" s="6" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="Q15" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="R15" s="7"/>
+      <c r="R15" s="7" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="n">
         <v>11</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>28</v>
@@ -2907,14 +2965,14 @@
         <v>28</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>4500</v>
+        <v>7000</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>5800</v>
+        <v>8000</v>
       </c>
       <c r="I16" s="10" t="n">
         <f aca="false">IF(E16=0,0,(E16-H16)/E16)</f>
-        <v>-0.593406593406593</v>
+        <v>-1.1978021978022</v>
       </c>
       <c r="J16" s="6" t="str">
         <f aca="false">IF(E16&lt;G16,"LOSS",IF(E16&lt;H16*1.1,"THIN / RISK",IF(E16&gt;H16*1.8,"OVERPRICED?","OK")))</f>
@@ -2922,7 +2980,7 @@
       </c>
       <c r="K16" s="8" t="n">
         <f aca="false">IF(J16="OVERPRICED?",ROUND(H16*1.35,-1),MAX(E16,ROUND(H16*(1+$E$3),-1)))</f>
-        <v>6670</v>
+        <v>9200</v>
       </c>
       <c r="L16" s="8" t="n">
         <f aca="false">D16*E16</f>
@@ -2930,11 +2988,11 @@
       </c>
       <c r="M16" s="8" t="n">
         <f aca="false">D16*K16</f>
-        <v>20010</v>
+        <v>27600</v>
       </c>
       <c r="N16" s="8" t="n">
         <f aca="false">D16*H16</f>
-        <v>17400</v>
+        <v>24000</v>
       </c>
       <c r="O16" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C16,F16)),"","YES")</f>
@@ -2944,7 +3002,7 @@
         <v>24</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="R16" s="7" t="s">
         <v>31</v>
@@ -2955,7 +3013,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>28</v>
@@ -2970,14 +3028,14 @@
         <v>28</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>6000</v>
+        <v>9500</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>7500</v>
+        <v>10500</v>
       </c>
       <c r="I17" s="10" t="n">
         <f aca="false">IF(E17=0,0,(E17-H17)/E17)</f>
-        <v>-0.648351648351648</v>
+        <v>-1.30769230769231</v>
       </c>
       <c r="J17" s="6" t="str">
         <f aca="false">IF(E17&lt;G17,"LOSS",IF(E17&lt;H17*1.1,"THIN / RISK",IF(E17&gt;H17*1.8,"OVERPRICED?","OK")))</f>
@@ -2985,7 +3043,7 @@
       </c>
       <c r="K17" s="8" t="n">
         <f aca="false">IF(J17="OVERPRICED?",ROUND(H17*1.35,-1),MAX(E17,ROUND(H17*(1+$E$3),-1)))</f>
-        <v>8630</v>
+        <v>12080</v>
       </c>
       <c r="L17" s="8" t="n">
         <f aca="false">D17*E17</f>
@@ -2993,11 +3051,11 @@
       </c>
       <c r="M17" s="8" t="n">
         <f aca="false">D17*K17</f>
-        <v>25890</v>
+        <v>36240</v>
       </c>
       <c r="N17" s="8" t="n">
         <f aca="false">D17*H17</f>
-        <v>22500</v>
+        <v>31500</v>
       </c>
       <c r="O17" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C17,F17)),"","YES")</f>
@@ -3007,18 +3065,18 @@
         <v>24</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="R17" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="n">
         <v>13</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>28</v>
@@ -3030,25 +3088,25 @@
         <v>22100</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>11780</v>
+        <v>24000</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>11780</v>
+        <v>30000</v>
       </c>
       <c r="I18" s="10" t="n">
         <f aca="false">IF(E18=0,0,(E18-H18)/E18)</f>
-        <v>0.466968325791855</v>
+        <v>-0.357466063348416</v>
       </c>
       <c r="J18" s="6" t="str">
         <f aca="false">IF(E18&lt;G18,"LOSS",IF(E18&lt;H18*1.1,"THIN / RISK",IF(E18&gt;H18*1.8,"OVERPRICED?","OK")))</f>
-        <v>OVERPRICED?</v>
+        <v>LOSS</v>
       </c>
       <c r="K18" s="8" t="n">
         <f aca="false">IF(J18="OVERPRICED?",ROUND(H18*1.35,-1),MAX(E18,ROUND(H18*(1+$E$3),-1)))</f>
-        <v>15900</v>
+        <v>34500</v>
       </c>
       <c r="L18" s="8" t="n">
         <f aca="false">D18*E18</f>
@@ -3056,30 +3114,32 @@
       </c>
       <c r="M18" s="8" t="n">
         <f aca="false">D18*K18</f>
-        <v>63600</v>
+        <v>138000</v>
       </c>
       <c r="N18" s="8" t="n">
         <f aca="false">D18*H18</f>
-        <v>47120</v>
+        <v>120000</v>
       </c>
       <c r="O18" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C18,F18)),"","YES")</f>
-        <v>YES</v>
+        <v/>
       </c>
       <c r="P18" s="6" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="R18" s="7"/>
+        <v>63</v>
+      </c>
+      <c r="R18" s="7" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="n">
         <v>14</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>28</v>
@@ -3131,7 +3191,7 @@
         <v>43</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R19" s="7"/>
     </row>
@@ -3140,7 +3200,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>28</v>
@@ -3192,7 +3252,7 @@
         <v>43</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="R20" s="7"/>
     </row>
@@ -3201,7 +3261,7 @@
         <v>16</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>28</v>
@@ -3213,25 +3273,25 @@
         <v>8450</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>4699</v>
+        <v>12000</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>4699</v>
+        <v>16000</v>
       </c>
       <c r="I21" s="10" t="n">
         <f aca="false">IF(E21=0,0,(E21-H21)/E21)</f>
-        <v>0.443905325443787</v>
+        <v>-0.893491124260355</v>
       </c>
       <c r="J21" s="6" t="str">
         <f aca="false">IF(E21&lt;G21,"LOSS",IF(E21&lt;H21*1.1,"THIN / RISK",IF(E21&gt;H21*1.8,"OVERPRICED?","OK")))</f>
-        <v>OK</v>
+        <v>LOSS</v>
       </c>
       <c r="K21" s="8" t="n">
         <f aca="false">IF(J21="OVERPRICED?",ROUND(H21*1.35,-1),MAX(E21,ROUND(H21*(1+$E$3),-1)))</f>
-        <v>8450</v>
+        <v>18400</v>
       </c>
       <c r="L21" s="8" t="n">
         <f aca="false">D21*E21</f>
@@ -3239,24 +3299,24 @@
       </c>
       <c r="M21" s="8" t="n">
         <f aca="false">D21*K21</f>
-        <v>33800</v>
+        <v>73600</v>
       </c>
       <c r="N21" s="8" t="n">
         <f aca="false">D21*H21</f>
-        <v>18796</v>
+        <v>64000</v>
       </c>
       <c r="O21" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C21,F21)),"","YES")</f>
-        <v>YES</v>
+        <v/>
       </c>
       <c r="P21" s="6" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="Q21" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="R21" s="7" t="s">
-        <v>51</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3264,7 +3324,7 @@
         <v>17</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>28</v>
@@ -3316,16 +3376,16 @@
         <v>43</v>
       </c>
       <c r="Q22" s="7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="R22" s="7"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="n">
         <v>18</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>28</v>
@@ -3337,25 +3397,25 @@
         <v>1846</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>1420</v>
+        <v>2000</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>1420</v>
+        <v>3000</v>
       </c>
       <c r="I23" s="10" t="n">
         <f aca="false">IF(E23=0,0,(E23-H23)/E23)</f>
-        <v>0.230769230769231</v>
+        <v>-0.625135427952329</v>
       </c>
       <c r="J23" s="6" t="str">
         <f aca="false">IF(E23&lt;G23,"LOSS",IF(E23&lt;H23*1.1,"THIN / RISK",IF(E23&gt;H23*1.8,"OVERPRICED?","OK")))</f>
-        <v>OK</v>
+        <v>LOSS</v>
       </c>
       <c r="K23" s="8" t="n">
         <f aca="false">IF(J23="OVERPRICED?",ROUND(H23*1.35,-1),MAX(E23,ROUND(H23*(1+$E$3),-1)))</f>
-        <v>1846</v>
+        <v>3450</v>
       </c>
       <c r="L23" s="8" t="n">
         <f aca="false">D23*E23</f>
@@ -3363,30 +3423,32 @@
       </c>
       <c r="M23" s="8" t="n">
         <f aca="false">D23*K23</f>
-        <v>7384</v>
+        <v>13800</v>
       </c>
       <c r="N23" s="8" t="n">
         <f aca="false">D23*H23</f>
-        <v>5680</v>
+        <v>12000</v>
       </c>
       <c r="O23" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C23,F23)),"","YES")</f>
-        <v>YES</v>
+        <v/>
       </c>
       <c r="P23" s="6" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="Q23" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="R23" s="7"/>
+        <v>75</v>
+      </c>
+      <c r="R23" s="7" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="n">
         <v>19</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>28</v>
@@ -3438,16 +3500,16 @@
         <v>43</v>
       </c>
       <c r="Q24" s="7" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="R24" s="7"/>
     </row>
-    <row r="25" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="n">
         <v>20</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>28</v>
@@ -3462,7 +3524,7 @@
         <v>28</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>950</v>
+        <v>1100</v>
       </c>
       <c r="H25" s="9" t="n">
         <v>1300</v>
@@ -3499,7 +3561,7 @@
         <v>24</v>
       </c>
       <c r="Q25" s="7" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="R25" s="7" t="s">
         <v>31</v>
@@ -3510,7 +3572,7 @@
         <v>21</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>28</v>
@@ -3525,7 +3587,7 @@
         <v>28</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="H26" s="9" t="n">
         <v>1700</v>
@@ -3562,7 +3624,7 @@
         <v>24</v>
       </c>
       <c r="Q26" s="7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="R26" s="7" t="s">
         <v>31</v>
@@ -3573,7 +3635,7 @@
         <v>22</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>28</v>
@@ -3588,7 +3650,7 @@
         <v>28</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="H27" s="9" t="n">
         <v>2100</v>
@@ -3625,7 +3687,7 @@
         <v>24</v>
       </c>
       <c r="Q27" s="7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="R27" s="7" t="s">
         <v>31</v>
@@ -3636,7 +3698,7 @@
         <v>23</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>28</v>
@@ -3688,7 +3750,7 @@
         <v>43</v>
       </c>
       <c r="Q28" s="7" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="R28" s="7"/>
     </row>
@@ -3697,7 +3759,7 @@
         <v>24</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>28</v>
@@ -3749,7 +3811,7 @@
         <v>43</v>
       </c>
       <c r="Q29" s="7" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="R29" s="7"/>
     </row>
@@ -3758,7 +3820,7 @@
         <v>25</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>28</v>
@@ -3810,7 +3872,7 @@
         <v>43</v>
       </c>
       <c r="Q30" s="7" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="R30" s="7"/>
     </row>
@@ -3819,7 +3881,7 @@
         <v>26</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>28</v>
@@ -3871,7 +3933,7 @@
         <v>43</v>
       </c>
       <c r="Q31" s="7" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="R31" s="7"/>
     </row>
@@ -3880,7 +3942,7 @@
         <v>27</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>28</v>
@@ -3895,22 +3957,22 @@
         <v>28</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>7500</v>
+        <v>4800</v>
       </c>
       <c r="I32" s="10" t="n">
         <f aca="false">IF(E32=0,0,(E32-H32)/E32)</f>
-        <v>-0.109467455621302</v>
+        <v>0.289940828402367</v>
       </c>
       <c r="J32" s="6" t="str">
         <f aca="false">IF(E32&lt;G32,"LOSS",IF(E32&lt;H32*1.1,"THIN / RISK",IF(E32&gt;H32*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>OK</v>
       </c>
       <c r="K32" s="8" t="n">
         <f aca="false">IF(J32="OVERPRICED?",ROUND(H32*1.35,-1),MAX(E32,ROUND(H32*(1+$E$3),-1)))</f>
-        <v>8630</v>
+        <v>6760</v>
       </c>
       <c r="L32" s="8" t="n">
         <f aca="false">D32*E32</f>
@@ -3918,11 +3980,11 @@
       </c>
       <c r="M32" s="8" t="n">
         <f aca="false">D32*K32</f>
-        <v>34520</v>
+        <v>27040</v>
       </c>
       <c r="N32" s="8" t="n">
         <f aca="false">D32*H32</f>
-        <v>30000</v>
+        <v>19200</v>
       </c>
       <c r="O32" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C32,F32)),"","YES")</f>
@@ -3932,10 +3994,10 @@
         <v>24</v>
       </c>
       <c r="Q32" s="7" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="R32" s="7" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3943,7 +4005,7 @@
         <v>28</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>28</v>
@@ -3958,22 +4020,22 @@
         <v>28</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>7500</v>
+        <v>4800</v>
       </c>
       <c r="I33" s="10" t="n">
         <f aca="false">IF(E33=0,0,(E33-H33)/E33)</f>
-        <v>-0.109467455621302</v>
+        <v>0.289940828402367</v>
       </c>
       <c r="J33" s="6" t="str">
         <f aca="false">IF(E33&lt;G33,"LOSS",IF(E33&lt;H33*1.1,"THIN / RISK",IF(E33&gt;H33*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>OK</v>
       </c>
       <c r="K33" s="8" t="n">
         <f aca="false">IF(J33="OVERPRICED?",ROUND(H33*1.35,-1),MAX(E33,ROUND(H33*(1+$E$3),-1)))</f>
-        <v>8630</v>
+        <v>6760</v>
       </c>
       <c r="L33" s="8" t="n">
         <f aca="false">D33*E33</f>
@@ -3981,11 +4043,11 @@
       </c>
       <c r="M33" s="8" t="n">
         <f aca="false">D33*K33</f>
-        <v>25890</v>
+        <v>20280</v>
       </c>
       <c r="N33" s="8" t="n">
         <f aca="false">D33*H33</f>
-        <v>22500</v>
+        <v>14400</v>
       </c>
       <c r="O33" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C33,F33)),"","YES")</f>
@@ -3995,10 +4057,10 @@
         <v>24</v>
       </c>
       <c r="Q33" s="7" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="R33" s="7" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4006,7 +4068,7 @@
         <v>30</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>28</v>
@@ -4058,7 +4120,7 @@
         <v>43</v>
       </c>
       <c r="Q34" s="7" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="R34" s="7"/>
     </row>
@@ -4067,7 +4129,7 @@
         <v>31</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>28</v>
@@ -4079,25 +4141,25 @@
         <v>2210</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>1700</v>
+        <v>4000</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>1700</v>
+        <v>4500</v>
       </c>
       <c r="I35" s="10" t="n">
         <f aca="false">IF(E35=0,0,(E35-H35)/E35)</f>
-        <v>0.230769230769231</v>
+        <v>-1.03619909502262</v>
       </c>
       <c r="J35" s="6" t="str">
         <f aca="false">IF(E35&lt;G35,"LOSS",IF(E35&lt;H35*1.1,"THIN / RISK",IF(E35&gt;H35*1.8,"OVERPRICED?","OK")))</f>
-        <v>OK</v>
+        <v>LOSS</v>
       </c>
       <c r="K35" s="8" t="n">
         <f aca="false">IF(J35="OVERPRICED?",ROUND(H35*1.35,-1),MAX(E35,ROUND(H35*(1+$E$3),-1)))</f>
-        <v>2210</v>
+        <v>5180</v>
       </c>
       <c r="L35" s="8" t="n">
         <f aca="false">D35*E35</f>
@@ -4105,30 +4167,32 @@
       </c>
       <c r="M35" s="8" t="n">
         <f aca="false">D35*K35</f>
-        <v>6630</v>
+        <v>15540</v>
       </c>
       <c r="N35" s="8" t="n">
         <f aca="false">D35*H35</f>
-        <v>5100</v>
+        <v>13500</v>
       </c>
       <c r="O35" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C35,F35)),"","YES")</f>
-        <v>YES</v>
+        <v/>
       </c>
       <c r="P35" s="6" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="Q35" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="R35" s="7"/>
-    </row>
-    <row r="36" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>97</v>
+      </c>
+      <c r="R35" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="n">
         <v>32</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>28</v>
@@ -4140,25 +4204,25 @@
         <v>2886</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>2850</v>
+        <v>5200</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>2850</v>
+        <v>5800</v>
       </c>
       <c r="I36" s="10" t="n">
         <f aca="false">IF(E36=0,0,(E36-H36)/E36)</f>
-        <v>0.0124740124740125</v>
+        <v>-1.00970200970201</v>
       </c>
       <c r="J36" s="6" t="str">
         <f aca="false">IF(E36&lt;G36,"LOSS",IF(E36&lt;H36*1.1,"THIN / RISK",IF(E36&gt;H36*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>LOSS</v>
       </c>
       <c r="K36" s="8" t="n">
         <f aca="false">IF(J36="OVERPRICED?",ROUND(H36*1.35,-1),MAX(E36,ROUND(H36*(1+$E$3),-1)))</f>
-        <v>3280</v>
+        <v>6670</v>
       </c>
       <c r="L36" s="8" t="n">
         <f aca="false">D36*E36</f>
@@ -4166,30 +4230,32 @@
       </c>
       <c r="M36" s="8" t="n">
         <f aca="false">D36*K36</f>
-        <v>9840</v>
+        <v>20010</v>
       </c>
       <c r="N36" s="8" t="n">
         <f aca="false">D36*H36</f>
-        <v>8550</v>
+        <v>17400</v>
       </c>
       <c r="O36" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C36,F36)),"","YES")</f>
-        <v>YES</v>
+        <v/>
       </c>
       <c r="P36" s="6" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="Q36" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="R36" s="7"/>
+        <v>97</v>
+      </c>
+      <c r="R36" s="7" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="n">
         <v>33</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>28</v>
@@ -4241,16 +4307,16 @@
         <v>43</v>
       </c>
       <c r="Q37" s="7" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="R37" s="7"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="n">
         <v>34</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>28</v>
@@ -4262,17 +4328,17 @@
         <v>6120</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>6560</v>
+        <v>14000</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>6560</v>
+        <v>15500</v>
       </c>
       <c r="I38" s="10" t="n">
         <f aca="false">IF(E38=0,0,(E38-H38)/E38)</f>
-        <v>-0.0718954248366013</v>
+        <v>-1.53267973856209</v>
       </c>
       <c r="J38" s="6" t="str">
         <f aca="false">IF(E38&lt;G38,"LOSS",IF(E38&lt;H38*1.1,"THIN / RISK",IF(E38&gt;H38*1.8,"OVERPRICED?","OK")))</f>
@@ -4280,7 +4346,7 @@
       </c>
       <c r="K38" s="8" t="n">
         <f aca="false">IF(J38="OVERPRICED?",ROUND(H38*1.35,-1),MAX(E38,ROUND(H38*(1+$E$3),-1)))</f>
-        <v>7540</v>
+        <v>17830</v>
       </c>
       <c r="L38" s="8" t="n">
         <f aca="false">D38*E38</f>
@@ -4288,30 +4354,32 @@
       </c>
       <c r="M38" s="8" t="n">
         <f aca="false">D38*K38</f>
-        <v>15080</v>
+        <v>35660</v>
       </c>
       <c r="N38" s="8" t="n">
         <f aca="false">D38*H38</f>
-        <v>13120</v>
+        <v>31000</v>
       </c>
       <c r="O38" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C38,F38)),"","YES")</f>
-        <v>YES</v>
+        <v/>
       </c>
       <c r="P38" s="6" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="Q38" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="R38" s="7"/>
+        <v>97</v>
+      </c>
+      <c r="R38" s="7" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="n">
         <v>35</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>28</v>
@@ -4323,25 +4391,25 @@
         <v>12870</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>7900</v>
+        <v>26000</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>7900</v>
+        <v>29000</v>
       </c>
       <c r="I39" s="10" t="n">
         <f aca="false">IF(E39=0,0,(E39-H39)/E39)</f>
-        <v>0.386169386169386</v>
+        <v>-1.25330225330225</v>
       </c>
       <c r="J39" s="6" t="str">
         <f aca="false">IF(E39&lt;G39,"LOSS",IF(E39&lt;H39*1.1,"THIN / RISK",IF(E39&gt;H39*1.8,"OVERPRICED?","OK")))</f>
-        <v>OK</v>
+        <v>LOSS</v>
       </c>
       <c r="K39" s="8" t="n">
         <f aca="false">IF(J39="OVERPRICED?",ROUND(H39*1.35,-1),MAX(E39,ROUND(H39*(1+$E$3),-1)))</f>
-        <v>12870</v>
+        <v>33350</v>
       </c>
       <c r="L39" s="8" t="n">
         <f aca="false">D39*E39</f>
@@ -4349,30 +4417,32 @@
       </c>
       <c r="M39" s="8" t="n">
         <f aca="false">D39*K39</f>
-        <v>25740</v>
+        <v>66700</v>
       </c>
       <c r="N39" s="8" t="n">
         <f aca="false">D39*H39</f>
-        <v>15800</v>
+        <v>58000</v>
       </c>
       <c r="O39" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C39,F39)),"","YES")</f>
-        <v>YES</v>
+        <v/>
       </c>
       <c r="P39" s="6" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="Q39" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="R39" s="7"/>
+        <v>97</v>
+      </c>
+      <c r="R39" s="7" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="n">
         <v>36</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>28</v>
@@ -4384,17 +4454,17 @@
         <v>1950</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="I40" s="10" t="n">
         <f aca="false">IF(E40=0,0,(E40-H40)/E40)</f>
-        <v>-0.0256410256410256</v>
+        <v>-2.07692307692308</v>
       </c>
       <c r="J40" s="6" t="str">
         <f aca="false">IF(E40&lt;G40,"LOSS",IF(E40&lt;H40*1.1,"THIN / RISK",IF(E40&gt;H40*1.8,"OVERPRICED?","OK")))</f>
@@ -4402,7 +4472,7 @@
       </c>
       <c r="K40" s="8" t="n">
         <f aca="false">IF(J40="OVERPRICED?",ROUND(H40*1.35,-1),MAX(E40,ROUND(H40*(1+$E$3),-1)))</f>
-        <v>2300</v>
+        <v>6900</v>
       </c>
       <c r="L40" s="8" t="n">
         <f aca="false">D40*E40</f>
@@ -4410,32 +4480,32 @@
       </c>
       <c r="M40" s="8" t="n">
         <f aca="false">D40*K40</f>
-        <v>6900</v>
+        <v>20700</v>
       </c>
       <c r="N40" s="8" t="n">
         <f aca="false">D40*H40</f>
-        <v>6000</v>
+        <v>18000</v>
       </c>
       <c r="O40" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C40,F40)),"","YES")</f>
-        <v>YES</v>
+        <v/>
       </c>
       <c r="P40" s="6" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="Q40" s="7" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="R40" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="n">
         <v>37</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>28</v>
@@ -4447,25 +4517,25 @@
         <v>4550</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>3380</v>
+        <v>8500</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>3380</v>
+        <v>9500</v>
       </c>
       <c r="I41" s="10" t="n">
         <f aca="false">IF(E41=0,0,(E41-H41)/E41)</f>
-        <v>0.257142857142857</v>
+        <v>-1.08791208791209</v>
       </c>
       <c r="J41" s="6" t="str">
         <f aca="false">IF(E41&lt;G41,"LOSS",IF(E41&lt;H41*1.1,"THIN / RISK",IF(E41&gt;H41*1.8,"OVERPRICED?","OK")))</f>
-        <v>OK</v>
+        <v>LOSS</v>
       </c>
       <c r="K41" s="8" t="n">
         <f aca="false">IF(J41="OVERPRICED?",ROUND(H41*1.35,-1),MAX(E41,ROUND(H41*(1+$E$3),-1)))</f>
-        <v>4550</v>
+        <v>10930</v>
       </c>
       <c r="L41" s="8" t="n">
         <f aca="false">D41*E41</f>
@@ -4473,30 +4543,32 @@
       </c>
       <c r="M41" s="8" t="n">
         <f aca="false">D41*K41</f>
-        <v>13650</v>
+        <v>32790</v>
       </c>
       <c r="N41" s="8" t="n">
         <f aca="false">D41*H41</f>
-        <v>10140</v>
+        <v>28500</v>
       </c>
       <c r="O41" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C41,F41)),"","YES")</f>
-        <v>YES</v>
+        <v/>
       </c>
       <c r="P41" s="6" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="Q41" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="R41" s="7"/>
-    </row>
-    <row r="42" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>111</v>
+      </c>
+      <c r="R41" s="7" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="n">
         <v>38</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>28</v>
@@ -4508,25 +4580,25 @@
         <v>6240</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>2450</v>
+        <v>6500</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>2450</v>
+        <v>7500</v>
       </c>
       <c r="I42" s="10" t="n">
         <f aca="false">IF(E42=0,0,(E42-H42)/E42)</f>
-        <v>0.607371794871795</v>
+        <v>-0.201923076923077</v>
       </c>
       <c r="J42" s="6" t="str">
         <f aca="false">IF(E42&lt;G42,"LOSS",IF(E42&lt;H42*1.1,"THIN / RISK",IF(E42&gt;H42*1.8,"OVERPRICED?","OK")))</f>
-        <v>OVERPRICED?</v>
+        <v>LOSS</v>
       </c>
       <c r="K42" s="8" t="n">
         <f aca="false">IF(J42="OVERPRICED?",ROUND(H42*1.35,-1),MAX(E42,ROUND(H42*(1+$E$3),-1)))</f>
-        <v>3310</v>
+        <v>8630</v>
       </c>
       <c r="L42" s="8" t="n">
         <f aca="false">D42*E42</f>
@@ -4534,30 +4606,32 @@
       </c>
       <c r="M42" s="8" t="n">
         <f aca="false">D42*K42</f>
-        <v>9930</v>
+        <v>25890</v>
       </c>
       <c r="N42" s="8" t="n">
         <f aca="false">D42*H42</f>
-        <v>7350</v>
+        <v>22500</v>
       </c>
       <c r="O42" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C42,F42)),"","YES")</f>
-        <v>YES</v>
+        <v/>
       </c>
       <c r="P42" s="6" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="Q42" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="R42" s="7"/>
+        <v>114</v>
+      </c>
+      <c r="R42" s="7" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="n">
         <v>39</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>28</v>
@@ -4575,11 +4649,11 @@
         <v>3500</v>
       </c>
       <c r="H43" s="9" t="n">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="I43" s="10" t="n">
         <f aca="false">IF(E43=0,0,(E43-H43)/E43)</f>
-        <v>-1.30769230769231</v>
+        <v>-1.05128205128205</v>
       </c>
       <c r="J43" s="6" t="str">
         <f aca="false">IF(E43&lt;G43,"LOSS",IF(E43&lt;H43*1.1,"THIN / RISK",IF(E43&gt;H43*1.8,"OVERPRICED?","OK")))</f>
@@ -4587,7 +4661,7 @@
       </c>
       <c r="K43" s="8" t="n">
         <f aca="false">IF(J43="OVERPRICED?",ROUND(H43*1.35,-1),MAX(E43,ROUND(H43*(1+$E$3),-1)))</f>
-        <v>5180</v>
+        <v>4600</v>
       </c>
       <c r="L43" s="8" t="n">
         <f aca="false">D43*E43</f>
@@ -4595,11 +4669,11 @@
       </c>
       <c r="M43" s="8" t="n">
         <f aca="false">D43*K43</f>
-        <v>15540</v>
+        <v>13800</v>
       </c>
       <c r="N43" s="8" t="n">
         <f aca="false">D43*H43</f>
-        <v>13500</v>
+        <v>12000</v>
       </c>
       <c r="O43" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C43,F43)),"","YES")</f>
@@ -4609,10 +4683,10 @@
         <v>24</v>
       </c>
       <c r="Q43" s="7" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="R43" s="7" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4620,10 +4694,10 @@
         <v>40</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D44" s="6" t="n">
         <v>3</v>
@@ -4632,7 +4706,7 @@
         <v>79300</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="G44" s="9" t="n">
         <v>79000</v>
@@ -4672,7 +4746,7 @@
         <v>43</v>
       </c>
       <c r="Q44" s="7" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="R44" s="7"/>
     </row>
@@ -4681,10 +4755,10 @@
         <v>41</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>3</v>
@@ -4693,7 +4767,7 @@
         <v>128700</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="G45" s="9" t="n">
         <v>95000</v>
@@ -4733,10 +4807,10 @@
         <v>24</v>
       </c>
       <c r="Q45" s="7" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="R45" s="7" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4744,10 +4818,10 @@
         <v>42</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D46" s="6" t="n">
         <v>2</v>
@@ -4756,7 +4830,7 @@
         <v>106600</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="G46" s="9" t="n">
         <v>143800</v>
@@ -4796,7 +4870,7 @@
         <v>43</v>
       </c>
       <c r="Q46" s="7" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="R46" s="7"/>
     </row>
@@ -4805,7 +4879,7 @@
         <v>43</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>28</v>
@@ -4823,11 +4897,11 @@
         <v>1800</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>2400</v>
+        <v>2200</v>
       </c>
       <c r="I47" s="10" t="n">
         <f aca="false">IF(E47=0,0,(E47-H47)/E47)</f>
-        <v>-0.538461538461538</v>
+        <v>-0.41025641025641</v>
       </c>
       <c r="J47" s="6" t="str">
         <f aca="false">IF(E47&lt;G47,"LOSS",IF(E47&lt;H47*1.1,"THIN / RISK",IF(E47&gt;H47*1.8,"OVERPRICED?","OK")))</f>
@@ -4835,7 +4909,7 @@
       </c>
       <c r="K47" s="8" t="n">
         <f aca="false">IF(J47="OVERPRICED?",ROUND(H47*1.35,-1),MAX(E47,ROUND(H47*(1+$E$3),-1)))</f>
-        <v>2760</v>
+        <v>2530</v>
       </c>
       <c r="L47" s="8" t="n">
         <f aca="false">D47*E47</f>
@@ -4843,11 +4917,11 @@
       </c>
       <c r="M47" s="8" t="n">
         <f aca="false">D47*K47</f>
-        <v>11040</v>
+        <v>10120</v>
       </c>
       <c r="N47" s="8" t="n">
         <f aca="false">D47*H47</f>
-        <v>9600</v>
+        <v>8800</v>
       </c>
       <c r="O47" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C47,F47)),"","YES")</f>
@@ -4857,7 +4931,7 @@
         <v>24</v>
       </c>
       <c r="Q47" s="7" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="R47" s="7" t="s">
         <v>31</v>
@@ -4868,7 +4942,7 @@
         <v>44</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>28</v>
@@ -4880,7 +4954,7 @@
         <v>1950</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G48" s="9" t="n">
         <v>1750</v>
@@ -4920,7 +4994,7 @@
         <v>43</v>
       </c>
       <c r="Q48" s="7" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="R48" s="7"/>
     </row>
@@ -4929,7 +5003,7 @@
         <v>45</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>28</v>
@@ -4941,7 +5015,7 @@
         <v>2210</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G49" s="9" t="n">
         <v>1750</v>
@@ -4981,10 +5055,10 @@
         <v>24</v>
       </c>
       <c r="Q49" s="7" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="R49" s="7" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4992,7 +5066,7 @@
         <v>47</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>28</v>
@@ -5044,7 +5118,7 @@
         <v>24</v>
       </c>
       <c r="Q50" s="7" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="R50" s="7" t="s">
         <v>31</v>
@@ -5055,7 +5129,7 @@
         <v>48</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>28</v>
@@ -5107,7 +5181,7 @@
         <v>24</v>
       </c>
       <c r="Q51" s="7" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="R51" s="7" t="s">
         <v>31</v>
@@ -5118,7 +5192,7 @@
         <v>49</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>28</v>
@@ -5170,7 +5244,7 @@
         <v>24</v>
       </c>
       <c r="Q52" s="7" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="R52" s="7" t="s">
         <v>31</v>
@@ -5181,7 +5255,7 @@
         <v>50</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>28</v>
@@ -5233,7 +5307,7 @@
         <v>24</v>
       </c>
       <c r="Q53" s="7" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="R53" s="7" t="s">
         <v>31</v>
@@ -5244,7 +5318,7 @@
         <v>51</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>28</v>
@@ -5296,7 +5370,7 @@
         <v>24</v>
       </c>
       <c r="Q54" s="7" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="R54" s="7" t="s">
         <v>31</v>
@@ -5307,7 +5381,7 @@
         <v>52</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>28</v>
@@ -5319,25 +5393,25 @@
         <v>18200</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>8500</v>
+        <v>17000</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>8500</v>
+        <v>20000</v>
       </c>
       <c r="I55" s="10" t="n">
         <f aca="false">IF(E55=0,0,(E55-H55)/E55)</f>
-        <v>0.532967032967033</v>
+        <v>-0.0989010989010989</v>
       </c>
       <c r="J55" s="6" t="str">
         <f aca="false">IF(E55&lt;G55,"LOSS",IF(E55&lt;H55*1.1,"THIN / RISK",IF(E55&gt;H55*1.8,"OVERPRICED?","OK")))</f>
-        <v>OVERPRICED?</v>
+        <v>THIN / RISK</v>
       </c>
       <c r="K55" s="8" t="n">
         <f aca="false">IF(J55="OVERPRICED?",ROUND(H55*1.35,-1),MAX(E55,ROUND(H55*(1+$E$3),-1)))</f>
-        <v>11480</v>
+        <v>23000</v>
       </c>
       <c r="L55" s="8" t="n">
         <f aca="false">D55*E55</f>
@@ -5345,32 +5419,32 @@
       </c>
       <c r="M55" s="8" t="n">
         <f aca="false">D55*K55</f>
-        <v>22960</v>
+        <v>46000</v>
       </c>
       <c r="N55" s="8" t="n">
         <f aca="false">D55*H55</f>
-        <v>17000</v>
+        <v>40000</v>
       </c>
       <c r="O55" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C55,F55)),"","YES")</f>
-        <v>YES</v>
+        <v/>
       </c>
       <c r="P55" s="6" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="Q55" s="7" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="R55" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="n">
         <v>53</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>28</v>
@@ -5382,25 +5456,25 @@
         <v>23400</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>19030</v>
+        <v>26000</v>
       </c>
       <c r="H56" s="9" t="n">
-        <v>19030</v>
+        <v>30000</v>
       </c>
       <c r="I56" s="10" t="n">
         <f aca="false">IF(E56=0,0,(E56-H56)/E56)</f>
-        <v>0.186752136752137</v>
+        <v>-0.282051282051282</v>
       </c>
       <c r="J56" s="6" t="str">
         <f aca="false">IF(E56&lt;G56,"LOSS",IF(E56&lt;H56*1.1,"THIN / RISK",IF(E56&gt;H56*1.8,"OVERPRICED?","OK")))</f>
-        <v>OK</v>
+        <v>LOSS</v>
       </c>
       <c r="K56" s="8" t="n">
         <f aca="false">IF(J56="OVERPRICED?",ROUND(H56*1.35,-1),MAX(E56,ROUND(H56*(1+$E$3),-1)))</f>
-        <v>23400</v>
+        <v>34500</v>
       </c>
       <c r="L56" s="8" t="n">
         <f aca="false">D56*E56</f>
@@ -5408,24 +5482,24 @@
       </c>
       <c r="M56" s="8" t="n">
         <f aca="false">D56*K56</f>
-        <v>23400</v>
+        <v>34500</v>
       </c>
       <c r="N56" s="8" t="n">
         <f aca="false">D56*H56</f>
-        <v>19030</v>
+        <v>30000</v>
       </c>
       <c r="O56" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C56,F56)),"","YES")</f>
-        <v>YES</v>
+        <v/>
       </c>
       <c r="P56" s="6" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="Q56" s="7" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="R56" s="7" t="s">
-        <v>51</v>
+        <v>149</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5433,10 +5507,10 @@
         <v>54</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D57" s="6" t="n">
         <v>2</v>
@@ -5445,7 +5519,7 @@
         <v>400946</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="G57" s="9" t="n">
         <v>115000</v>
@@ -5485,7 +5559,7 @@
         <v>43</v>
       </c>
       <c r="Q57" s="7" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="R57" s="7"/>
     </row>
@@ -5494,7 +5568,7 @@
         <v>55</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>28</v>
@@ -5506,7 +5580,7 @@
         <v>15600</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="G58" s="9" t="n">
         <v>12000</v>
@@ -5546,10 +5620,10 @@
         <v>24</v>
       </c>
       <c r="Q58" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R58" s="7" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5557,7 +5631,7 @@
         <v>56</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>28</v>
@@ -5609,10 +5683,10 @@
         <v>24</v>
       </c>
       <c r="Q59" s="7" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="R59" s="7" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5620,7 +5694,7 @@
         <v>57</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>28</v>
@@ -5672,7 +5746,7 @@
         <v>43</v>
       </c>
       <c r="Q60" s="7" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="R60" s="7"/>
     </row>
@@ -5681,7 +5755,7 @@
         <v>58</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>28</v>
@@ -5733,7 +5807,7 @@
         <v>24</v>
       </c>
       <c r="Q61" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R61" s="7" t="s">
         <v>31</v>
@@ -5744,7 +5818,7 @@
         <v>59</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>28</v>
@@ -5796,7 +5870,7 @@
         <v>24</v>
       </c>
       <c r="Q62" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R62" s="7" t="s">
         <v>31</v>
@@ -5807,7 +5881,7 @@
         <v>60</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>28</v>
@@ -5819,7 +5893,7 @@
         <v>9100</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G63" s="9" t="n">
         <v>8000</v>
@@ -5859,18 +5933,18 @@
         <v>24</v>
       </c>
       <c r="Q63" s="7" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="R63" s="7" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6" t="n">
         <v>61</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>28</v>
@@ -5882,25 +5956,25 @@
         <v>5850</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>157</v>
+        <v>131</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>5920</v>
+        <v>5000</v>
       </c>
       <c r="H64" s="9" t="n">
-        <v>5920</v>
+        <v>7500</v>
       </c>
       <c r="I64" s="10" t="n">
         <f aca="false">IF(E64=0,0,(E64-H64)/E64)</f>
-        <v>-0.011965811965812</v>
+        <v>-0.282051282051282</v>
       </c>
       <c r="J64" s="6" t="str">
         <f aca="false">IF(E64&lt;G64,"LOSS",IF(E64&lt;H64*1.1,"THIN / RISK",IF(E64&gt;H64*1.8,"OVERPRICED?","OK")))</f>
-        <v>LOSS</v>
+        <v>THIN / RISK</v>
       </c>
       <c r="K64" s="8" t="n">
         <f aca="false">IF(J64="OVERPRICED?",ROUND(H64*1.35,-1),MAX(E64,ROUND(H64*(1+$E$3),-1)))</f>
-        <v>6810</v>
+        <v>8630</v>
       </c>
       <c r="L64" s="8" t="n">
         <f aca="false">D64*E64</f>
@@ -5908,30 +5982,32 @@
       </c>
       <c r="M64" s="8" t="n">
         <f aca="false">D64*K64</f>
-        <v>13620</v>
+        <v>17260</v>
       </c>
       <c r="N64" s="8" t="n">
         <f aca="false">D64*H64</f>
-        <v>11840</v>
+        <v>15000</v>
       </c>
       <c r="O64" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C64,F64)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="Q64" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="R64" s="7"/>
+        <v>154</v>
+      </c>
+      <c r="R64" s="7" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="n">
         <v>62</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>28</v>
@@ -5983,10 +6059,10 @@
         <v>24</v>
       </c>
       <c r="Q65" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R65" s="7" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5994,7 +6070,7 @@
         <v>63</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>28</v>
@@ -6006,25 +6082,25 @@
         <v>5551</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>3890</v>
+        <v>9000</v>
       </c>
       <c r="H66" s="9" t="n">
-        <v>3890</v>
+        <v>11000</v>
       </c>
       <c r="I66" s="10" t="n">
         <f aca="false">IF(E66=0,0,(E66-H66)/E66)</f>
-        <v>0.299225364799135</v>
+        <v>-0.981624932444605</v>
       </c>
       <c r="J66" s="6" t="str">
         <f aca="false">IF(E66&lt;G66,"LOSS",IF(E66&lt;H66*1.1,"THIN / RISK",IF(E66&gt;H66*1.8,"OVERPRICED?","OK")))</f>
-        <v>OK</v>
+        <v>LOSS</v>
       </c>
       <c r="K66" s="8" t="n">
         <f aca="false">IF(J66="OVERPRICED?",ROUND(H66*1.35,-1),MAX(E66,ROUND(H66*(1+$E$3),-1)))</f>
-        <v>5551</v>
+        <v>12650</v>
       </c>
       <c r="L66" s="8" t="n">
         <f aca="false">D66*E66</f>
@@ -6032,30 +6108,32 @@
       </c>
       <c r="M66" s="8" t="n">
         <f aca="false">D66*K66</f>
-        <v>5551</v>
+        <v>12650</v>
       </c>
       <c r="N66" s="8" t="n">
         <f aca="false">D66*H66</f>
-        <v>3890</v>
+        <v>11000</v>
       </c>
       <c r="O66" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C66,F66)),"","YES")</f>
-        <v>YES</v>
+        <v/>
       </c>
       <c r="P66" s="6" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="Q66" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="R66" s="7"/>
+        <v>171</v>
+      </c>
+      <c r="R66" s="7" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="6" t="n">
         <v>64</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>28</v>
@@ -6067,7 +6145,7 @@
         <v>1560</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G67" s="9" t="n">
         <v>1350</v>
@@ -6107,7 +6185,7 @@
         <v>43</v>
       </c>
       <c r="Q67" s="7" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="R67" s="7"/>
     </row>
@@ -6116,7 +6194,7 @@
         <v>65</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>28</v>
@@ -6128,7 +6206,7 @@
         <v>1560</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G68" s="9" t="n">
         <v>1350</v>
@@ -6168,7 +6246,7 @@
         <v>43</v>
       </c>
       <c r="Q68" s="7" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="R68" s="7"/>
     </row>
@@ -6177,7 +6255,7 @@
         <v>66</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>28</v>
@@ -6189,7 +6267,7 @@
         <v>11700</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="G69" s="9" t="n">
         <v>14000</v>
@@ -6229,7 +6307,7 @@
         <v>24</v>
       </c>
       <c r="Q69" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R69" s="7" t="s">
         <v>31</v>
@@ -6240,7 +6318,7 @@
         <v>67</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>28</v>
@@ -6252,7 +6330,7 @@
         <v>9750</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="G70" s="9" t="n">
         <v>12000</v>
@@ -6292,7 +6370,7 @@
         <v>24</v>
       </c>
       <c r="Q70" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R70" s="7" t="s">
         <v>31</v>
@@ -6303,7 +6381,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>28</v>
@@ -6315,7 +6393,7 @@
         <v>23400</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="G71" s="9" t="n">
         <v>15000</v>
@@ -6355,7 +6433,7 @@
         <v>24</v>
       </c>
       <c r="Q71" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R71" s="7" t="s">
         <v>31</v>
@@ -6366,7 +6444,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>28</v>
@@ -6378,7 +6456,7 @@
         <v>32500</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="G72" s="9" t="n">
         <v>25000</v>
@@ -6418,7 +6496,7 @@
         <v>24</v>
       </c>
       <c r="Q72" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R72" s="7" t="s">
         <v>31</v>
@@ -6429,7 +6507,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>28</v>
@@ -6441,25 +6519,25 @@
         <v>1105</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>42</v>
+        <v>131</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="I73" s="10" t="n">
         <f aca="false">IF(E73=0,0,(E73-H73)/E73)</f>
-        <v>0.0950226244343891</v>
+        <v>-0.085972850678733</v>
       </c>
       <c r="J73" s="6" t="str">
         <f aca="false">IF(E73&lt;G73,"LOSS",IF(E73&lt;H73*1.1,"THIN / RISK",IF(E73&gt;H73*1.8,"OVERPRICED?","OK")))</f>
-        <v>OK</v>
+        <v>THIN / RISK</v>
       </c>
       <c r="K73" s="8" t="n">
         <f aca="false">IF(J73="OVERPRICED?",ROUND(H73*1.35,-1),MAX(E73,ROUND(H73*(1+$E$3),-1)))</f>
-        <v>1150</v>
+        <v>1380</v>
       </c>
       <c r="L73" s="8" t="n">
         <f aca="false">D73*E73</f>
@@ -6467,30 +6545,32 @@
       </c>
       <c r="M73" s="8" t="n">
         <f aca="false">D73*K73</f>
-        <v>1150</v>
+        <v>1380</v>
       </c>
       <c r="N73" s="8" t="n">
         <f aca="false">D73*H73</f>
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="O73" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C73,F73)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P73" s="6" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="Q73" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="R73" s="7"/>
+        <v>154</v>
+      </c>
+      <c r="R73" s="7" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="6" t="n">
         <v>73</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>28</v>
@@ -6502,7 +6582,7 @@
         <v>45500</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="G74" s="9" t="n">
         <v>35000</v>
@@ -6542,10 +6622,10 @@
         <v>24</v>
       </c>
       <c r="Q74" s="7" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="R74" s="7" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6553,7 +6633,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>28</v>
@@ -6565,7 +6645,7 @@
         <v>23400</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="G75" s="9" t="n">
         <v>45000</v>
@@ -6605,10 +6685,10 @@
         <v>24</v>
       </c>
       <c r="Q75" s="7" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="R75" s="7" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6616,7 +6696,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>28</v>
@@ -6628,7 +6708,7 @@
         <v>1950</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="G76" s="9" t="n">
         <v>9790</v>
@@ -6668,7 +6748,7 @@
         <v>24</v>
       </c>
       <c r="Q76" s="7" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="R76" s="7" t="s">
         <v>31</v>
@@ -6679,7 +6759,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>28</v>
@@ -6691,7 +6771,7 @@
         <v>2080</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="G77" s="9" t="n">
         <v>11060</v>
@@ -6731,7 +6811,7 @@
         <v>24</v>
       </c>
       <c r="Q77" s="7" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="R77" s="7" t="s">
         <v>31</v>
@@ -6742,7 +6822,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>28</v>
@@ -6754,7 +6834,7 @@
         <v>2210</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="G78" s="9" t="n">
         <v>11700</v>
@@ -6794,7 +6874,7 @@
         <v>24</v>
       </c>
       <c r="Q78" s="7" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="R78" s="7" t="s">
         <v>31</v>
@@ -6805,7 +6885,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>28</v>
@@ -6817,7 +6897,7 @@
         <v>2340</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="G79" s="9" t="n">
         <v>12330</v>
@@ -6857,7 +6937,7 @@
         <v>24</v>
       </c>
       <c r="Q79" s="7" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="R79" s="7" t="s">
         <v>31</v>
@@ -6868,7 +6948,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>28</v>
@@ -6880,7 +6960,7 @@
         <v>2470</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="G80" s="9" t="n">
         <v>12970</v>
@@ -6920,7 +7000,7 @@
         <v>24</v>
       </c>
       <c r="Q80" s="7" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="R80" s="7" t="s">
         <v>31</v>
@@ -6931,7 +7011,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>28</v>
@@ -6943,7 +7023,7 @@
         <v>2600</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="G81" s="9" t="n">
         <v>13600</v>
@@ -6983,7 +7063,7 @@
         <v>24</v>
       </c>
       <c r="Q81" s="7" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="R81" s="7" t="s">
         <v>31</v>
@@ -6994,7 +7074,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>28</v>
@@ -7006,7 +7086,7 @@
         <v>2730</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="G82" s="9" t="n">
         <v>14240</v>
@@ -7046,7 +7126,7 @@
         <v>24</v>
       </c>
       <c r="Q82" s="7" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="R82" s="7" t="s">
         <v>31</v>
@@ -7057,7 +7137,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>28</v>
@@ -7069,7 +7149,7 @@
         <v>3250</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="G83" s="9" t="n">
         <v>16140</v>
@@ -7109,7 +7189,7 @@
         <v>24</v>
       </c>
       <c r="Q83" s="7" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="R83" s="7" t="s">
         <v>31</v>
@@ -7120,7 +7200,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>28</v>
@@ -7132,7 +7212,7 @@
         <v>4160</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="G84" s="9" t="n">
         <v>19230</v>
@@ -7172,7 +7252,7 @@
         <v>24</v>
       </c>
       <c r="Q84" s="7" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="R84" s="7" t="s">
         <v>31</v>
@@ -7183,7 +7263,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>28</v>
@@ -7195,7 +7275,7 @@
         <v>5850</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="G85" s="9" t="n">
         <v>26490</v>
@@ -7235,7 +7315,7 @@
         <v>24</v>
       </c>
       <c r="Q85" s="7" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="R85" s="7" t="s">
         <v>31</v>
@@ -7246,7 +7326,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>28</v>
@@ -7258,7 +7338,7 @@
         <v>8450</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="G86" s="9" t="n">
         <v>38450</v>
@@ -7298,7 +7378,7 @@
         <v>24</v>
       </c>
       <c r="Q86" s="7" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="R86" s="7" t="s">
         <v>31</v>
@@ -7309,7 +7389,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>28</v>
@@ -7321,7 +7401,7 @@
         <v>9750</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="G87" s="9" t="n">
         <v>44060</v>
@@ -7361,7 +7441,7 @@
         <v>24</v>
       </c>
       <c r="Q87" s="7" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="R87" s="7" t="s">
         <v>31</v>
@@ -7372,7 +7452,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>28</v>
@@ -7384,7 +7464,7 @@
         <v>11700</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="G88" s="9" t="n">
         <v>52470</v>
@@ -7424,7 +7504,7 @@
         <v>24</v>
       </c>
       <c r="Q88" s="7" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="R88" s="7" t="s">
         <v>31</v>
@@ -7435,7 +7515,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>28</v>
@@ -7447,7 +7527,7 @@
         <v>4550</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="G89" s="9" t="n">
         <v>3500</v>
@@ -7487,7 +7567,7 @@
         <v>24</v>
       </c>
       <c r="Q89" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R89" s="7" t="s">
         <v>31</v>
@@ -7498,7 +7578,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>28</v>
@@ -7510,7 +7590,7 @@
         <v>5850</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="G90" s="9" t="n">
         <v>4500</v>
@@ -7550,7 +7630,7 @@
         <v>24</v>
       </c>
       <c r="Q90" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R90" s="7" t="s">
         <v>31</v>
@@ -7561,7 +7641,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>28</v>
@@ -7573,7 +7653,7 @@
         <v>7150</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="G91" s="9" t="n">
         <v>5500</v>
@@ -7613,7 +7693,7 @@
         <v>24</v>
       </c>
       <c r="Q91" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R91" s="7" t="s">
         <v>31</v>
@@ -7624,7 +7704,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>28</v>
@@ -7636,7 +7716,7 @@
         <v>2340</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="G92" s="9" t="n">
         <v>2500</v>
@@ -7676,7 +7756,7 @@
         <v>24</v>
       </c>
       <c r="Q92" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R92" s="7" t="s">
         <v>31</v>
@@ -7687,7 +7767,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>28</v>
@@ -7699,7 +7779,7 @@
         <v>2860</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="G93" s="9" t="n">
         <v>3000</v>
@@ -7739,7 +7819,7 @@
         <v>24</v>
       </c>
       <c r="Q93" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R93" s="7" t="s">
         <v>31</v>
@@ -7750,10 +7830,10 @@
         <v>93</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D94" s="6" t="n">
         <v>2</v>
@@ -7762,7 +7842,7 @@
         <v>25350</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="G94" s="9" t="n">
         <v>18100</v>
@@ -7802,7 +7882,7 @@
         <v>43</v>
       </c>
       <c r="Q94" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="R94" s="7"/>
     </row>
@@ -7811,10 +7891,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D95" s="6" t="n">
         <v>3</v>
@@ -7823,7 +7903,7 @@
         <v>8138</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="G95" s="9" t="n">
         <v>15800</v>
@@ -7863,7 +7943,7 @@
         <v>43</v>
       </c>
       <c r="Q95" s="7" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="R95" s="7"/>
     </row>
@@ -7872,10 +7952,10 @@
         <v>95</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D96" s="6" t="n">
         <v>3</v>
@@ -7884,7 +7964,7 @@
         <v>6370</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="G96" s="9" t="n">
         <v>7928</v>
@@ -7924,7 +8004,7 @@
         <v>43</v>
       </c>
       <c r="Q96" s="7" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="R96" s="7"/>
     </row>
@@ -7933,7 +8013,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>28</v>
@@ -7945,7 +8025,7 @@
         <v>14950</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="G97" s="9" t="n">
         <v>15000</v>
@@ -7985,10 +8065,10 @@
         <v>24</v>
       </c>
       <c r="Q97" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R97" s="7" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7996,10 +8076,10 @@
         <v>97</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D98" s="6" t="n">
         <v>2</v>
@@ -8008,7 +8088,7 @@
         <v>286000</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="G98" s="9" t="n">
         <v>199500</v>
@@ -8045,13 +8125,13 @@
         <v/>
       </c>
       <c r="P98" s="6" t="s">
-        <v>49</v>
+        <v>231</v>
       </c>
       <c r="Q98" s="7" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="R98" s="7" t="s">
-        <v>51</v>
+        <v>233</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8059,10 +8139,10 @@
         <v>98</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="D99" s="6" t="n">
         <v>1</v>
@@ -8071,7 +8151,7 @@
         <v>15600</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="G99" s="9" t="n">
         <v>12000</v>
@@ -8111,7 +8191,7 @@
         <v>24</v>
       </c>
       <c r="Q99" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R99" s="7" t="s">
         <v>31</v>
@@ -8122,7 +8202,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>28</v>
@@ -8134,7 +8214,7 @@
         <v>11050</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="G100" s="9" t="n">
         <v>8000</v>
@@ -8174,7 +8254,7 @@
         <v>24</v>
       </c>
       <c r="Q100" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R100" s="7" t="s">
         <v>31</v>
@@ -8185,7 +8265,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>28</v>
@@ -8197,7 +8277,7 @@
         <v>9100</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="G101" s="9" t="n">
         <v>6500</v>
@@ -8237,7 +8317,7 @@
         <v>24</v>
       </c>
       <c r="Q101" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R101" s="7" t="s">
         <v>31</v>
@@ -8248,7 +8328,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>28</v>
@@ -8260,7 +8340,7 @@
         <v>7150</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="G102" s="9" t="n">
         <v>5500</v>
@@ -8300,7 +8380,7 @@
         <v>24</v>
       </c>
       <c r="Q102" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R102" s="7" t="s">
         <v>31</v>
@@ -8311,7 +8391,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>28</v>
@@ -8323,7 +8403,7 @@
         <v>5850</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="G103" s="9" t="n">
         <v>4500</v>
@@ -8363,7 +8443,7 @@
         <v>24</v>
       </c>
       <c r="Q103" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R103" s="7" t="s">
         <v>31</v>
@@ -8374,7 +8454,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>22</v>
@@ -8426,7 +8506,7 @@
         <v>24</v>
       </c>
       <c r="Q104" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R104" s="7" t="s">
         <v>31</v>
@@ -8437,7 +8517,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>22</v>
@@ -8489,10 +8569,10 @@
         <v>24</v>
       </c>
       <c r="Q105" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R105" s="7" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8500,7 +8580,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>22</v>
@@ -8512,7 +8592,7 @@
         <v>1170</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="G106" s="9" t="n">
         <v>800</v>
@@ -8552,16 +8632,16 @@
         <v>43</v>
       </c>
       <c r="Q106" s="7" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="R106" s="7"/>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="6" t="n">
         <v>106</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>28</v>
@@ -8573,17 +8653,17 @@
         <v>3640</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>42</v>
+        <v>131</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>2420</v>
+        <v>2000</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>2420</v>
+        <v>2800</v>
       </c>
       <c r="I107" s="10" t="n">
         <f aca="false">IF(E107=0,0,(E107-H107)/E107)</f>
-        <v>0.335164835164835</v>
+        <v>0.230769230769231</v>
       </c>
       <c r="J107" s="6" t="str">
         <f aca="false">IF(E107&lt;G107,"LOSS",IF(E107&lt;H107*1.1,"THIN / RISK",IF(E107&gt;H107*1.8,"OVERPRICED?","OK")))</f>
@@ -8603,26 +8683,28 @@
       </c>
       <c r="N107" s="8" t="n">
         <f aca="false">D107*H107</f>
-        <v>14520</v>
+        <v>16800</v>
       </c>
       <c r="O107" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C107,F107)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P107" s="6" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="Q107" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="R107" s="7"/>
+        <v>154</v>
+      </c>
+      <c r="R107" s="7" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="108" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="6" t="n">
         <v>107</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>28</v>
@@ -8634,7 +8716,7 @@
         <v>6760</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G108" s="9" t="n">
         <v>4500</v>
@@ -8674,10 +8756,10 @@
         <v>24</v>
       </c>
       <c r="Q108" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R108" s="7" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8685,7 +8767,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>28</v>
@@ -8697,25 +8779,25 @@
         <v>4550</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>42</v>
+        <v>131</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>3350</v>
+        <v>3500</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>3350</v>
+        <v>5000</v>
       </c>
       <c r="I109" s="10" t="n">
         <f aca="false">IF(E109=0,0,(E109-H109)/E109)</f>
-        <v>0.263736263736264</v>
+        <v>-0.0989010989010989</v>
       </c>
       <c r="J109" s="6" t="str">
         <f aca="false">IF(E109&lt;G109,"LOSS",IF(E109&lt;H109*1.1,"THIN / RISK",IF(E109&gt;H109*1.8,"OVERPRICED?","OK")))</f>
-        <v>OK</v>
+        <v>THIN / RISK</v>
       </c>
       <c r="K109" s="8" t="n">
         <f aca="false">IF(J109="OVERPRICED?",ROUND(H109*1.35,-1),MAX(E109,ROUND(H109*(1+$E$3),-1)))</f>
-        <v>4550</v>
+        <v>5750</v>
       </c>
       <c r="L109" s="8" t="n">
         <f aca="false">D109*E109</f>
@@ -8723,30 +8805,32 @@
       </c>
       <c r="M109" s="8" t="n">
         <f aca="false">D109*K109</f>
-        <v>13650</v>
+        <v>17250</v>
       </c>
       <c r="N109" s="8" t="n">
         <f aca="false">D109*H109</f>
-        <v>10050</v>
+        <v>15000</v>
       </c>
       <c r="O109" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C109,F109)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P109" s="6" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="Q109" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="R109" s="7"/>
+        <v>154</v>
+      </c>
+      <c r="R109" s="7" t="s">
+        <v>252</v>
+      </c>
     </row>
     <row r="110" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="6" t="n">
         <v>109</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>28</v>
@@ -8758,7 +8842,7 @@
         <v>2340</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G110" s="9" t="n">
         <v>1800</v>
@@ -8798,10 +8882,10 @@
         <v>24</v>
       </c>
       <c r="Q110" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R110" s="7" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8809,7 +8893,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>28</v>
@@ -8821,7 +8905,7 @@
         <v>1820</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="G111" s="9" t="n">
         <v>2000</v>
@@ -8861,18 +8945,18 @@
         <v>24</v>
       </c>
       <c r="Q111" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R111" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="6" t="n">
         <v>111</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>28</v>
@@ -8884,17 +8968,17 @@
         <v>2860</v>
       </c>
       <c r="F112" s="7" t="s">
-        <v>53</v>
+        <v>180</v>
       </c>
       <c r="G112" s="9" t="n">
-        <v>3125</v>
+        <v>4000</v>
       </c>
       <c r="H112" s="9" t="n">
-        <v>3125</v>
+        <v>5500</v>
       </c>
       <c r="I112" s="10" t="n">
         <f aca="false">IF(E112=0,0,(E112-H112)/E112)</f>
-        <v>-0.0926573426573427</v>
+        <v>-0.923076923076923</v>
       </c>
       <c r="J112" s="6" t="str">
         <f aca="false">IF(E112&lt;G112,"LOSS",IF(E112&lt;H112*1.1,"THIN / RISK",IF(E112&gt;H112*1.8,"OVERPRICED?","OK")))</f>
@@ -8902,7 +8986,7 @@
       </c>
       <c r="K112" s="8" t="n">
         <f aca="false">IF(J112="OVERPRICED?",ROUND(H112*1.35,-1),MAX(E112,ROUND(H112*(1+$E$3),-1)))</f>
-        <v>3590</v>
+        <v>6330</v>
       </c>
       <c r="L112" s="8" t="n">
         <f aca="false">D112*E112</f>
@@ -8910,24 +8994,24 @@
       </c>
       <c r="M112" s="8" t="n">
         <f aca="false">D112*K112</f>
-        <v>10770</v>
+        <v>18990</v>
       </c>
       <c r="N112" s="8" t="n">
         <f aca="false">D112*H112</f>
-        <v>9375</v>
+        <v>16500</v>
       </c>
       <c r="O112" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C112,F112)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="Q112" s="7" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="R112" s="7" t="s">
-        <v>51</v>
+        <v>259</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8935,7 +9019,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>28</v>
@@ -8947,7 +9031,7 @@
         <v>12350</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="G113" s="9" t="n">
         <v>8000</v>
@@ -8987,10 +9071,10 @@
         <v>24</v>
       </c>
       <c r="Q113" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R113" s="7" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8998,7 +9082,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>28</v>
@@ -9050,7 +9134,7 @@
         <v>24</v>
       </c>
       <c r="Q114" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R114" s="7" t="s">
         <v>31</v>
@@ -9061,7 +9145,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>28</v>
@@ -9113,7 +9197,7 @@
         <v>24</v>
       </c>
       <c r="Q115" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R115" s="7" t="s">
         <v>31</v>
@@ -9124,7 +9208,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>22</v>
@@ -9136,7 +9220,7 @@
         <v>11050</v>
       </c>
       <c r="F116" s="7" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="G116" s="9" t="n">
         <v>5000</v>
@@ -9176,7 +9260,7 @@
         <v>43</v>
       </c>
       <c r="Q116" s="7" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="R116" s="7"/>
     </row>
@@ -9185,7 +9269,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>28</v>
@@ -9237,10 +9321,10 @@
         <v>24</v>
       </c>
       <c r="Q117" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R117" s="7" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9248,7 +9332,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>22</v>
@@ -9300,7 +9384,7 @@
         <v>24</v>
       </c>
       <c r="Q118" s="7" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="R118" s="7" t="s">
         <v>31</v>
@@ -9311,7 +9395,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>22</v>
@@ -9363,7 +9447,7 @@
         <v>24</v>
       </c>
       <c r="Q119" s="7" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="R119" s="7" t="s">
         <v>31</v>
@@ -9374,7 +9458,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>28</v>
@@ -9426,7 +9510,7 @@
         <v>24</v>
       </c>
       <c r="Q120" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R120" s="7" t="s">
         <v>31</v>
@@ -9437,7 +9521,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>22</v>
@@ -9489,7 +9573,7 @@
         <v>24</v>
       </c>
       <c r="Q121" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R121" s="7" t="s">
         <v>31</v>
@@ -9500,7 +9584,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>22</v>
@@ -9552,7 +9636,7 @@
         <v>43</v>
       </c>
       <c r="Q122" s="7" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="R122" s="7"/>
     </row>
@@ -9561,7 +9645,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>22</v>
@@ -9573,7 +9657,7 @@
         <v>357500</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="G123" s="9" t="n">
         <v>200000</v>
@@ -9613,10 +9697,10 @@
         <v>24</v>
       </c>
       <c r="Q123" s="7" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="R123" s="7" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9624,7 +9708,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="C124" s="6" t="s">
         <v>22</v>
@@ -9676,10 +9760,10 @@
         <v>24</v>
       </c>
       <c r="Q124" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R124" s="7" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9687,7 +9771,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>22</v>
@@ -9739,7 +9823,7 @@
         <v>24</v>
       </c>
       <c r="Q125" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R125" s="7" t="s">
         <v>31</v>
@@ -9750,7 +9834,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>22</v>
@@ -9802,7 +9886,7 @@
         <v>24</v>
       </c>
       <c r="Q126" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R126" s="7" t="s">
         <v>31</v>
@@ -9813,7 +9897,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>22</v>
@@ -9865,7 +9949,7 @@
         <v>24</v>
       </c>
       <c r="Q127" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R127" s="7" t="s">
         <v>31</v>
@@ -9876,7 +9960,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>22</v>
@@ -9928,7 +10012,7 @@
         <v>24</v>
       </c>
       <c r="Q128" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R128" s="7" t="s">
         <v>31</v>
@@ -9939,7 +10023,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>22</v>
@@ -9991,7 +10075,7 @@
         <v>24</v>
       </c>
       <c r="Q129" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R129" s="7" t="s">
         <v>31</v>
@@ -10002,7 +10086,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>22</v>
@@ -10054,7 +10138,7 @@
         <v>24</v>
       </c>
       <c r="Q130" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R130" s="7" t="s">
         <v>31</v>
@@ -10065,7 +10149,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>22</v>
@@ -10117,10 +10201,10 @@
         <v>24</v>
       </c>
       <c r="Q131" s="7" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="R131" s="7" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10128,7 +10212,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>22</v>
@@ -10140,7 +10224,7 @@
         <v>7800</v>
       </c>
       <c r="F132" s="7" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="G132" s="9" t="n">
         <v>5000</v>
@@ -10180,7 +10264,7 @@
         <v>43</v>
       </c>
       <c r="Q132" s="7" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="R132" s="7"/>
     </row>
@@ -10189,7 +10273,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="7" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>22</v>
@@ -10241,7 +10325,7 @@
         <v>24</v>
       </c>
       <c r="Q133" s="7" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="R133" s="7" t="s">
         <v>31</v>
@@ -10252,7 +10336,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>28</v>
@@ -10304,7 +10388,7 @@
         <v>24</v>
       </c>
       <c r="Q134" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R134" s="7" t="s">
         <v>31</v>
@@ -10315,7 +10399,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>22</v>
@@ -10367,7 +10451,7 @@
         <v>24</v>
       </c>
       <c r="Q135" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R135" s="7" t="s">
         <v>31</v>
@@ -10378,7 +10462,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="7" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C136" s="6" t="s">
         <v>22</v>
@@ -10430,7 +10514,7 @@
         <v>43</v>
       </c>
       <c r="Q136" s="7" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="R136" s="7"/>
     </row>
@@ -10439,7 +10523,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="C137" s="6" t="s">
         <v>22</v>
@@ -10491,7 +10575,7 @@
         <v>43</v>
       </c>
       <c r="Q137" s="7" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="R137" s="7"/>
     </row>
@@ -10500,7 +10584,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="C138" s="6" t="s">
         <v>22</v>
@@ -10552,7 +10636,7 @@
         <v>43</v>
       </c>
       <c r="Q138" s="7" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="R138" s="7"/>
     </row>
@@ -10561,7 +10645,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="7" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="C139" s="6" t="s">
         <v>28</v>
@@ -10613,7 +10697,7 @@
         <v>24</v>
       </c>
       <c r="Q139" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R139" s="7" t="s">
         <v>31</v>
@@ -10624,7 +10708,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="7" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="C140" s="6" t="s">
         <v>22</v>
@@ -10676,10 +10760,10 @@
         <v>24</v>
       </c>
       <c r="Q140" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R140" s="7" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10687,7 +10771,7 @@
         <v>142</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="C141" s="6" t="s">
         <v>22</v>
@@ -10699,7 +10783,7 @@
         <v>7150</v>
       </c>
       <c r="F141" s="7" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="G141" s="9" t="n">
         <v>5000</v>
@@ -10739,7 +10823,7 @@
         <v>24</v>
       </c>
       <c r="Q141" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R141" s="7" t="s">
         <v>31</v>
@@ -10750,7 +10834,7 @@
         <v>143</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="C142" s="6" t="s">
         <v>22</v>
@@ -10762,7 +10846,7 @@
         <v>7150</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="G142" s="9" t="n">
         <v>5000</v>
@@ -10802,7 +10886,7 @@
         <v>24</v>
       </c>
       <c r="Q142" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R142" s="7" t="s">
         <v>31</v>
@@ -10813,7 +10897,7 @@
         <v>144</v>
       </c>
       <c r="B143" s="7" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="C143" s="6" t="s">
         <v>22</v>
@@ -10825,7 +10909,7 @@
         <v>8450</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="G143" s="9" t="n">
         <v>6000</v>
@@ -10865,7 +10949,7 @@
         <v>24</v>
       </c>
       <c r="Q143" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R143" s="7" t="s">
         <v>31</v>
@@ -10876,7 +10960,7 @@
         <v>145</v>
       </c>
       <c r="B144" s="7" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C144" s="6" t="s">
         <v>28</v>
@@ -10888,7 +10972,7 @@
         <v>104</v>
       </c>
       <c r="F144" s="7" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="G144" s="9" t="n">
         <v>50</v>
@@ -10928,7 +11012,7 @@
         <v>24</v>
       </c>
       <c r="Q144" s="7" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="R144" s="7" t="s">
         <v>31</v>
@@ -10939,7 +11023,7 @@
         <v>146</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="C145" s="6" t="s">
         <v>22</v>
@@ -10951,7 +11035,7 @@
         <v>105788</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="G145" s="9" t="n">
         <v>82000</v>
@@ -10991,7 +11075,7 @@
         <v>43</v>
       </c>
       <c r="Q145" s="7" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="R145" s="7"/>
     </row>
@@ -11000,7 +11084,7 @@
         <v>147</v>
       </c>
       <c r="B146" s="7" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="C146" s="6" t="s">
         <v>22</v>
@@ -11012,7 +11096,7 @@
         <v>245700</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="G146" s="9" t="n">
         <v>225000</v>
@@ -11052,16 +11136,16 @@
         <v>43</v>
       </c>
       <c r="Q146" s="7" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="R146" s="7"/>
     </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="6" t="n">
         <v>148</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="C147" s="6" t="s">
         <v>28</v>
@@ -11073,25 +11157,25 @@
         <v>650</v>
       </c>
       <c r="F147" s="7" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v>360</v>
+        <v>800</v>
       </c>
       <c r="H147" s="9" t="n">
-        <v>360</v>
+        <v>1200</v>
       </c>
       <c r="I147" s="10" t="n">
         <f aca="false">IF(E147=0,0,(E147-H147)/E147)</f>
-        <v>0.446153846153846</v>
+        <v>-0.846153846153846</v>
       </c>
       <c r="J147" s="6" t="str">
         <f aca="false">IF(E147&lt;G147,"LOSS",IF(E147&lt;H147*1.1,"THIN / RISK",IF(E147&gt;H147*1.8,"OVERPRICED?","OK")))</f>
-        <v>OVERPRICED?</v>
+        <v>LOSS</v>
       </c>
       <c r="K147" s="8" t="n">
         <f aca="false">IF(J147="OVERPRICED?",ROUND(H147*1.35,-1),MAX(E147,ROUND(H147*(1+$E$3),-1)))</f>
-        <v>490</v>
+        <v>1380</v>
       </c>
       <c r="L147" s="8" t="n">
         <f aca="false">D147*E147</f>
@@ -11099,30 +11183,32 @@
       </c>
       <c r="M147" s="8" t="n">
         <f aca="false">D147*K147</f>
-        <v>5880</v>
+        <v>16560</v>
       </c>
       <c r="N147" s="8" t="n">
         <f aca="false">D147*H147</f>
-        <v>4320</v>
+        <v>14400</v>
       </c>
       <c r="O147" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C147,F147)),"","YES")</f>
-        <v>YES</v>
+        <v/>
       </c>
       <c r="P147" s="6" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="Q147" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="R147" s="7"/>
+        <v>319</v>
+      </c>
+      <c r="R147" s="7" t="s">
+        <v>320</v>
+      </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="6" t="n">
         <v>149</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="C148" s="6" t="s">
         <v>22</v>
@@ -11134,7 +11220,7 @@
         <v>1754</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="G148" s="9" t="n">
         <v>1380</v>
@@ -11174,7 +11260,7 @@
         <v>43</v>
       </c>
       <c r="Q148" s="7" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="R148" s="7"/>
     </row>
@@ -11183,7 +11269,7 @@
         <v>150</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="C149" s="6" t="s">
         <v>22</v>
@@ -11235,7 +11321,7 @@
         <v>43</v>
       </c>
       <c r="Q149" s="7" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="R149" s="7"/>
     </row>
@@ -11244,7 +11330,7 @@
         <v>151</v>
       </c>
       <c r="B150" s="7" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="C150" s="6" t="s">
         <v>22</v>
@@ -11296,7 +11382,7 @@
         <v>43</v>
       </c>
       <c r="Q150" s="7" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="R150" s="7"/>
     </row>
@@ -11305,7 +11391,7 @@
         <v>152</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="C151" s="6" t="s">
         <v>22</v>
@@ -11357,7 +11443,7 @@
         <v>43</v>
       </c>
       <c r="Q151" s="7" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="R151" s="7"/>
     </row>
@@ -11366,7 +11452,7 @@
         <v>153</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="C152" s="6" t="s">
         <v>22</v>
@@ -11418,7 +11504,7 @@
         <v>43</v>
       </c>
       <c r="Q152" s="7" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="R152" s="7"/>
     </row>
@@ -11427,7 +11513,7 @@
         <v>154</v>
       </c>
       <c r="B153" s="7" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="C153" s="6" t="s">
         <v>22</v>
@@ -11479,7 +11565,7 @@
         <v>24</v>
       </c>
       <c r="Q153" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R153" s="7" t="s">
         <v>31</v>
@@ -11490,7 +11576,7 @@
         <v>155</v>
       </c>
       <c r="B154" s="7" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="C154" s="6" t="s">
         <v>22</v>
@@ -11502,7 +11588,7 @@
         <v>748</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="G154" s="9" t="n">
         <v>450</v>
@@ -11542,7 +11628,7 @@
         <v>43</v>
       </c>
       <c r="Q154" s="7" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="R154" s="7"/>
     </row>
@@ -11551,7 +11637,7 @@
         <v>156</v>
       </c>
       <c r="B155" s="7" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>22</v>
@@ -11563,7 +11649,7 @@
         <v>748</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="G155" s="9" t="n">
         <v>450</v>
@@ -11603,7 +11689,7 @@
         <v>43</v>
       </c>
       <c r="Q155" s="7" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="R155" s="7"/>
     </row>
@@ -11612,7 +11698,7 @@
         <v>157</v>
       </c>
       <c r="B156" s="7" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="C156" s="6" t="s">
         <v>22</v>
@@ -11624,7 +11710,7 @@
         <v>748</v>
       </c>
       <c r="F156" s="7" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="G156" s="9" t="n">
         <v>400</v>
@@ -11664,7 +11750,7 @@
         <v>43</v>
       </c>
       <c r="Q156" s="7" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="R156" s="7"/>
     </row>
@@ -11673,7 +11759,7 @@
         <v>158</v>
       </c>
       <c r="B157" s="7" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="C157" s="6" t="s">
         <v>28</v>
@@ -11685,7 +11771,7 @@
         <v>311</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="G157" s="9" t="n">
         <v>150</v>
@@ -11725,7 +11811,7 @@
         <v>24</v>
       </c>
       <c r="Q157" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R157" s="7" t="s">
         <v>31</v>
@@ -11736,7 +11822,7 @@
         <v>159</v>
       </c>
       <c r="B158" s="7" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="C158" s="6" t="s">
         <v>28</v>
@@ -11748,7 +11834,7 @@
         <v>325</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="G158" s="9" t="n">
         <v>180</v>
@@ -11788,7 +11874,7 @@
         <v>24</v>
       </c>
       <c r="Q158" s="7" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="R158" s="7" t="s">
         <v>31</v>
@@ -11799,7 +11885,7 @@
         <v>160</v>
       </c>
       <c r="B159" s="7" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="C159" s="6" t="s">
         <v>28</v>
@@ -11811,7 +11897,7 @@
         <v>117</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="G159" s="9" t="n">
         <v>60</v>
@@ -11851,7 +11937,7 @@
         <v>24</v>
       </c>
       <c r="Q159" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R159" s="7" t="s">
         <v>31</v>
@@ -11862,7 +11948,7 @@
         <v>161</v>
       </c>
       <c r="B160" s="7" t="s">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="C160" s="6" t="s">
         <v>28</v>
@@ -11874,7 +11960,7 @@
         <v>169</v>
       </c>
       <c r="F160" s="7" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="G160" s="9" t="n">
         <v>90</v>
@@ -11914,7 +12000,7 @@
         <v>24</v>
       </c>
       <c r="Q160" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R160" s="7" t="s">
         <v>31</v>
@@ -11925,7 +12011,7 @@
         <v>162</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="C161" s="6" t="s">
         <v>28</v>
@@ -11937,7 +12023,7 @@
         <v>234</v>
       </c>
       <c r="F161" s="7" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="G161" s="9" t="n">
         <v>120</v>
@@ -11977,7 +12063,7 @@
         <v>24</v>
       </c>
       <c r="Q161" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R161" s="7" t="s">
         <v>31</v>
@@ -11988,7 +12074,7 @@
         <v>164</v>
       </c>
       <c r="B162" s="7" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="C162" s="6" t="s">
         <v>22</v>
@@ -12000,7 +12086,7 @@
         <v>1209</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="G162" s="9" t="n">
         <v>1450</v>
@@ -12037,13 +12123,13 @@
         <v>YES</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>49</v>
+        <v>231</v>
       </c>
       <c r="Q162" s="7" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="R162" s="7" t="s">
-        <v>51</v>
+        <v>233</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12051,7 +12137,7 @@
         <v>165</v>
       </c>
       <c r="B163" s="7" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="C163" s="6" t="s">
         <v>22</v>
@@ -12063,7 +12149,7 @@
         <v>1209</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="G163" s="9" t="n">
         <v>2248</v>
@@ -12100,13 +12186,13 @@
         <v>YES</v>
       </c>
       <c r="P163" s="6" t="s">
-        <v>49</v>
+        <v>231</v>
       </c>
       <c r="Q163" s="7" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="R163" s="7" t="s">
-        <v>51</v>
+        <v>233</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12114,7 +12200,7 @@
         <v>166</v>
       </c>
       <c r="B164" s="7" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="C164" s="6" t="s">
         <v>22</v>
@@ -12126,7 +12212,7 @@
         <v>3022</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="G164" s="9" t="n">
         <v>2325</v>
@@ -12163,13 +12249,13 @@
         <v>YES</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>49</v>
+        <v>231</v>
       </c>
       <c r="Q164" s="7" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="R164" s="7" t="s">
-        <v>51</v>
+        <v>233</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12177,7 +12263,7 @@
         <v>167</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="C165" s="6" t="s">
         <v>22</v>
@@ -12229,10 +12315,10 @@
         <v>24</v>
       </c>
       <c r="Q165" s="7" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="R165" s="7" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12240,7 +12326,7 @@
         <v>168</v>
       </c>
       <c r="B166" s="7" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="C166" s="6" t="s">
         <v>22</v>
@@ -12292,10 +12378,10 @@
         <v>24</v>
       </c>
       <c r="Q166" s="7" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="R166" s="7" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12303,7 +12389,7 @@
         <v>177</v>
       </c>
       <c r="B167" s="7" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="C167" s="6" t="s">
         <v>28</v>
@@ -12315,7 +12401,7 @@
         <v>5850</v>
       </c>
       <c r="F167" s="7" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="G167" s="9" t="n">
         <v>3500</v>
@@ -12355,10 +12441,10 @@
         <v>24</v>
       </c>
       <c r="Q167" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R167" s="7" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12366,7 +12452,7 @@
         <v>179</v>
       </c>
       <c r="B168" s="7" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="C168" s="6" t="s">
         <v>28</v>
@@ -12378,7 +12464,7 @@
         <v>23400</v>
       </c>
       <c r="F168" s="7" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="G168" s="9" t="n">
         <v>20000</v>
@@ -12418,7 +12504,7 @@
         <v>24</v>
       </c>
       <c r="Q168" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R168" s="7" t="s">
         <v>31</v>
@@ -12429,7 +12515,7 @@
         <v>180</v>
       </c>
       <c r="B169" s="7" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="C169" s="6" t="s">
         <v>28</v>
@@ -12441,7 +12527,7 @@
         <v>15600</v>
       </c>
       <c r="F169" s="7" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="G169" s="9" t="n">
         <v>14000</v>
@@ -12481,7 +12567,7 @@
         <v>24</v>
       </c>
       <c r="Q169" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R169" s="7" t="s">
         <v>31</v>
@@ -12492,7 +12578,7 @@
         <v>181</v>
       </c>
       <c r="B170" s="7" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="C170" s="6" t="s">
         <v>28</v>
@@ -12504,7 +12590,7 @@
         <v>33800</v>
       </c>
       <c r="F170" s="7" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="G170" s="9" t="n">
         <v>28000</v>
@@ -12544,7 +12630,7 @@
         <v>24</v>
       </c>
       <c r="Q170" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R170" s="7" t="s">
         <v>31</v>
@@ -12555,7 +12641,7 @@
         <v>182</v>
       </c>
       <c r="B171" s="7" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="C171" s="6" t="s">
         <v>28</v>
@@ -12567,7 +12653,7 @@
         <v>23400</v>
       </c>
       <c r="F171" s="7" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="G171" s="9" t="n">
         <v>20000</v>
@@ -12607,7 +12693,7 @@
         <v>24</v>
       </c>
       <c r="Q171" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R171" s="7" t="s">
         <v>31</v>
@@ -12618,7 +12704,7 @@
         <v>183</v>
       </c>
       <c r="B172" s="7" t="s">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="C172" s="6" t="s">
         <v>28</v>
@@ -12630,7 +12716,7 @@
         <v>2860</v>
       </c>
       <c r="F172" s="7" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G172" s="9" t="n">
         <v>1800</v>
@@ -12670,7 +12756,7 @@
         <v>24</v>
       </c>
       <c r="Q172" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R172" s="7" t="s">
         <v>31</v>
@@ -12681,7 +12767,7 @@
         <v>184</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="C173" s="6" t="s">
         <v>28</v>
@@ -12693,7 +12779,7 @@
         <v>3250</v>
       </c>
       <c r="F173" s="7" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G173" s="9" t="n">
         <v>2100</v>
@@ -12733,7 +12819,7 @@
         <v>24</v>
       </c>
       <c r="Q173" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R173" s="7" t="s">
         <v>31</v>
@@ -12744,7 +12830,7 @@
         <v>185</v>
       </c>
       <c r="B174" s="7" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="C174" s="6" t="s">
         <v>28</v>
@@ -12756,7 +12842,7 @@
         <v>3900</v>
       </c>
       <c r="F174" s="7" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G174" s="9" t="n">
         <v>2600</v>
@@ -12796,7 +12882,7 @@
         <v>24</v>
       </c>
       <c r="Q174" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R174" s="7" t="s">
         <v>31</v>
@@ -12807,7 +12893,7 @@
         <v>186</v>
       </c>
       <c r="B175" s="7" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="C175" s="6" t="s">
         <v>28</v>
@@ -12819,7 +12905,7 @@
         <v>4550</v>
       </c>
       <c r="F175" s="7" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G175" s="9" t="n">
         <v>3300</v>
@@ -12859,7 +12945,7 @@
         <v>24</v>
       </c>
       <c r="Q175" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R175" s="7" t="s">
         <v>31</v>
@@ -12870,7 +12956,7 @@
         <v>187</v>
       </c>
       <c r="B176" s="7" t="s">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="C176" s="6" t="s">
         <v>28</v>
@@ -12882,7 +12968,7 @@
         <v>7150</v>
       </c>
       <c r="F176" s="7" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G176" s="9" t="n">
         <v>5500</v>
@@ -12922,7 +13008,7 @@
         <v>24</v>
       </c>
       <c r="Q176" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R176" s="7" t="s">
         <v>31</v>
@@ -12933,7 +13019,7 @@
         <v>188</v>
       </c>
       <c r="B177" s="7" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="C177" s="6" t="s">
         <v>28</v>
@@ -12945,7 +13031,7 @@
         <v>8450</v>
       </c>
       <c r="F177" s="7" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G177" s="9" t="n">
         <v>7000</v>
@@ -12985,7 +13071,7 @@
         <v>24</v>
       </c>
       <c r="Q177" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R177" s="7" t="s">
         <v>31</v>
@@ -12996,7 +13082,7 @@
         <v>189</v>
       </c>
       <c r="B178" s="7" t="s">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="C178" s="6" t="s">
         <v>28</v>
@@ -13008,7 +13094,7 @@
         <v>9750</v>
       </c>
       <c r="F178" s="7" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G178" s="9" t="n">
         <v>8500</v>
@@ -13048,7 +13134,7 @@
         <v>24</v>
       </c>
       <c r="Q178" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R178" s="7" t="s">
         <v>31</v>
@@ -13059,7 +13145,7 @@
         <v>190</v>
       </c>
       <c r="B179" s="7" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="C179" s="6" t="s">
         <v>28</v>
@@ -13071,7 +13157,7 @@
         <v>2340</v>
       </c>
       <c r="F179" s="7" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G179" s="9" t="n">
         <v>1500</v>
@@ -13111,7 +13197,7 @@
         <v>24</v>
       </c>
       <c r="Q179" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R179" s="7" t="s">
         <v>31</v>
@@ -13122,7 +13208,7 @@
         <v>191</v>
       </c>
       <c r="B180" s="7" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="C180" s="6" t="s">
         <v>28</v>
@@ -13134,7 +13220,7 @@
         <v>3640</v>
       </c>
       <c r="F180" s="7" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G180" s="9" t="n">
         <v>2300</v>
@@ -13174,7 +13260,7 @@
         <v>24</v>
       </c>
       <c r="Q180" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R180" s="7" t="s">
         <v>31</v>
@@ -13185,7 +13271,7 @@
         <v>192</v>
       </c>
       <c r="B181" s="7" t="s">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="C181" s="6" t="s">
         <v>28</v>
@@ -13237,7 +13323,7 @@
         <v>24</v>
       </c>
       <c r="Q181" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R181" s="7" t="s">
         <v>31</v>
@@ -13248,7 +13334,7 @@
         <v>193</v>
       </c>
       <c r="B182" s="7" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="C182" s="6" t="s">
         <v>28</v>
@@ -13300,7 +13386,7 @@
         <v>24</v>
       </c>
       <c r="Q182" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R182" s="7" t="s">
         <v>31</v>
@@ -13311,7 +13397,7 @@
         <v>194</v>
       </c>
       <c r="B183" s="7" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="C183" s="6" t="s">
         <v>28</v>
@@ -13363,7 +13449,7 @@
         <v>24</v>
       </c>
       <c r="Q183" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R183" s="7" t="s">
         <v>31</v>
@@ -13374,7 +13460,7 @@
         <v>195</v>
       </c>
       <c r="B184" s="7" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="C184" s="6" t="s">
         <v>28</v>
@@ -13426,7 +13512,7 @@
         <v>24</v>
       </c>
       <c r="Q184" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R184" s="7" t="s">
         <v>31</v>
@@ -13437,7 +13523,7 @@
         <v>196</v>
       </c>
       <c r="B185" s="7" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="C185" s="6" t="s">
         <v>28</v>
@@ -13449,7 +13535,7 @@
         <v>4550</v>
       </c>
       <c r="F185" s="7" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G185" s="9" t="n">
         <v>3500</v>
@@ -13489,7 +13575,7 @@
         <v>24</v>
       </c>
       <c r="Q185" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R185" s="7" t="s">
         <v>31</v>
@@ -13500,7 +13586,7 @@
         <v>197</v>
       </c>
       <c r="B186" s="7" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="C186" s="6" t="s">
         <v>28</v>
@@ -13512,7 +13598,7 @@
         <v>17940</v>
       </c>
       <c r="F186" s="7" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="G186" s="9" t="n">
         <v>5500</v>
@@ -13552,7 +13638,7 @@
         <v>43</v>
       </c>
       <c r="Q186" s="7" t="s">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="R186" s="7"/>
     </row>
@@ -13561,7 +13647,7 @@
         <v>198</v>
       </c>
       <c r="B187" s="7" t="s">
-        <v>369</v>
+        <v>383</v>
       </c>
       <c r="C187" s="6" t="s">
         <v>28</v>
@@ -13573,7 +13659,7 @@
         <v>18850</v>
       </c>
       <c r="F187" s="7" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="G187" s="9" t="n">
         <v>5500</v>
@@ -13613,7 +13699,7 @@
         <v>43</v>
       </c>
       <c r="Q187" s="7" t="s">
-        <v>370</v>
+        <v>384</v>
       </c>
       <c r="R187" s="7"/>
     </row>
@@ -13622,7 +13708,7 @@
         <v>199</v>
       </c>
       <c r="B188" s="7" t="s">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="C188" s="6" t="s">
         <v>28</v>
@@ -13634,7 +13720,7 @@
         <v>19500</v>
       </c>
       <c r="F188" s="7" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="G188" s="9" t="n">
         <v>6200</v>
@@ -13674,7 +13760,7 @@
         <v>43</v>
       </c>
       <c r="Q188" s="7" t="s">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="R188" s="7"/>
     </row>
@@ -13683,7 +13769,7 @@
         <v>200</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C189" s="6" t="s">
         <v>28</v>
@@ -13695,7 +13781,7 @@
         <v>20800</v>
       </c>
       <c r="F189" s="7" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="G189" s="9" t="n">
         <v>6875</v>
@@ -13735,7 +13821,7 @@
         <v>43</v>
       </c>
       <c r="Q189" s="7" t="s">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="R189" s="7"/>
     </row>
@@ -13744,7 +13830,7 @@
         <v>201</v>
       </c>
       <c r="B190" s="7" t="s">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="C190" s="6" t="s">
         <v>28</v>
@@ -13756,7 +13842,7 @@
         <v>22750</v>
       </c>
       <c r="F190" s="7" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="G190" s="9" t="n">
         <v>8750</v>
@@ -13796,7 +13882,7 @@
         <v>43</v>
       </c>
       <c r="Q190" s="7" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="R190" s="7"/>
     </row>
@@ -13805,7 +13891,7 @@
         <v>202</v>
       </c>
       <c r="B191" s="7" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="C191" s="6" t="s">
         <v>28</v>
@@ -13817,7 +13903,7 @@
         <v>2340</v>
       </c>
       <c r="F191" s="7" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G191" s="9" t="n">
         <v>1500</v>
@@ -13857,7 +13943,7 @@
         <v>24</v>
       </c>
       <c r="Q191" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R191" s="7" t="s">
         <v>31</v>
@@ -13868,7 +13954,7 @@
         <v>204</v>
       </c>
       <c r="B192" s="7" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="C192" s="6" t="s">
         <v>28</v>
@@ -13880,7 +13966,7 @@
         <v>845</v>
       </c>
       <c r="F192" s="7" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="G192" s="9" t="n">
         <v>5480</v>
@@ -13920,7 +14006,7 @@
         <v>24</v>
       </c>
       <c r="Q192" s="7" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="R192" s="7" t="s">
         <v>31</v>
@@ -13931,7 +14017,7 @@
         <v>205</v>
       </c>
       <c r="B193" s="7" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="C193" s="6" t="s">
         <v>28</v>
@@ -13943,7 +14029,7 @@
         <v>910</v>
       </c>
       <c r="F193" s="7" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="G193" s="9" t="n">
         <v>5960</v>
@@ -13983,7 +14069,7 @@
         <v>24</v>
       </c>
       <c r="Q193" s="7" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="R193" s="7" t="s">
         <v>31</v>
@@ -13994,7 +14080,7 @@
         <v>206</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="C194" s="6" t="s">
         <v>28</v>
@@ -14006,7 +14092,7 @@
         <v>1170</v>
       </c>
       <c r="F194" s="7" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="G194" s="9" t="n">
         <v>6930</v>
@@ -14046,7 +14132,7 @@
         <v>24</v>
       </c>
       <c r="Q194" s="7" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="R194" s="7" t="s">
         <v>31</v>
@@ -14057,7 +14143,7 @@
         <v>207</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="C195" s="6" t="s">
         <v>28</v>
@@ -14069,7 +14155,7 @@
         <v>1430</v>
       </c>
       <c r="F195" s="7" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="G195" s="9" t="n">
         <v>8960</v>
@@ -14109,7 +14195,7 @@
         <v>24</v>
       </c>
       <c r="Q195" s="7" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="R195" s="7" t="s">
         <v>31</v>
@@ -14120,7 +14206,7 @@
         <v>208</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="C196" s="6" t="s">
         <v>28</v>
@@ -14132,7 +14218,7 @@
         <v>1690</v>
       </c>
       <c r="F196" s="7" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="G196" s="9" t="n">
         <v>11050</v>
@@ -14172,7 +14258,7 @@
         <v>24</v>
       </c>
       <c r="Q196" s="7" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="R196" s="7" t="s">
         <v>31</v>
@@ -14183,7 +14269,7 @@
         <v>209</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="C197" s="6" t="s">
         <v>28</v>
@@ -14195,7 +14281,7 @@
         <v>2340</v>
       </c>
       <c r="F197" s="7" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="G197" s="9" t="n">
         <v>15380</v>
@@ -14235,7 +14321,7 @@
         <v>24</v>
       </c>
       <c r="Q197" s="7" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="R197" s="7" t="s">
         <v>31</v>
@@ -14246,7 +14332,7 @@
         <v>210</v>
       </c>
       <c r="B198" s="7" t="s">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="C198" s="6" t="s">
         <v>28</v>
@@ -14258,7 +14344,7 @@
         <v>2860</v>
       </c>
       <c r="F198" s="7" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="G198" s="9" t="n">
         <v>17610</v>
@@ -14298,7 +14384,7 @@
         <v>24</v>
       </c>
       <c r="Q198" s="7" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="R198" s="7" t="s">
         <v>31</v>
@@ -14309,7 +14395,7 @@
         <v>211</v>
       </c>
       <c r="B199" s="7" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="C199" s="6" t="s">
         <v>28</v>
@@ -14321,7 +14407,7 @@
         <v>4160</v>
       </c>
       <c r="F199" s="7" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="G199" s="9" t="n">
         <v>22180</v>
@@ -14361,7 +14447,7 @@
         <v>24</v>
       </c>
       <c r="Q199" s="7" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="R199" s="7" t="s">
         <v>31</v>
@@ -14372,7 +14458,7 @@
         <v>212</v>
       </c>
       <c r="B200" s="7" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="C200" s="6" t="s">
         <v>28</v>
@@ -14384,7 +14470,7 @@
         <v>5460</v>
       </c>
       <c r="F200" s="7" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="G200" s="9" t="n">
         <v>25690</v>
@@ -14424,7 +14510,7 @@
         <v>24</v>
       </c>
       <c r="Q200" s="7" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="R200" s="7" t="s">
         <v>31</v>
@@ -14435,7 +14521,7 @@
         <v>213</v>
       </c>
       <c r="B201" s="7" t="s">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="C201" s="6" t="s">
         <v>28</v>
@@ -14447,7 +14533,7 @@
         <v>455</v>
       </c>
       <c r="F201" s="7" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G201" s="9" t="n">
         <v>500</v>
@@ -14487,7 +14573,7 @@
         <v>24</v>
       </c>
       <c r="Q201" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R201" s="7" t="s">
         <v>31</v>
@@ -14498,7 +14584,7 @@
         <v>214</v>
       </c>
       <c r="B202" s="7" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="C202" s="6" t="s">
         <v>28</v>
@@ -14510,7 +14596,7 @@
         <v>494</v>
       </c>
       <c r="F202" s="7" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G202" s="9" t="n">
         <v>550</v>
@@ -14550,7 +14636,7 @@
         <v>24</v>
       </c>
       <c r="Q202" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R202" s="7" t="s">
         <v>31</v>
@@ -14561,7 +14647,7 @@
         <v>215</v>
       </c>
       <c r="B203" s="7" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="C203" s="6" t="s">
         <v>28</v>
@@ -14573,7 +14659,7 @@
         <v>585</v>
       </c>
       <c r="F203" s="7" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G203" s="9" t="n">
         <v>650</v>
@@ -14613,7 +14699,7 @@
         <v>24</v>
       </c>
       <c r="Q203" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R203" s="7" t="s">
         <v>31</v>
@@ -14624,7 +14710,7 @@
         <v>216</v>
       </c>
       <c r="B204" s="7" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="C204" s="6" t="s">
         <v>28</v>
@@ -14636,7 +14722,7 @@
         <v>715</v>
       </c>
       <c r="F204" s="7" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G204" s="9" t="n">
         <v>800</v>
@@ -14676,7 +14762,7 @@
         <v>24</v>
       </c>
       <c r="Q204" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R204" s="7" t="s">
         <v>31</v>
@@ -14687,7 +14773,7 @@
         <v>217</v>
       </c>
       <c r="B205" s="7" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="C205" s="6" t="s">
         <v>28</v>
@@ -14699,7 +14785,7 @@
         <v>910</v>
       </c>
       <c r="F205" s="7" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G205" s="9" t="n">
         <v>1000</v>
@@ -14739,7 +14825,7 @@
         <v>24</v>
       </c>
       <c r="Q205" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R205" s="7" t="s">
         <v>31</v>
@@ -14750,7 +14836,7 @@
         <v>218</v>
       </c>
       <c r="B206" s="7" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="C206" s="6" t="s">
         <v>28</v>
@@ -14762,7 +14848,7 @@
         <v>1170</v>
       </c>
       <c r="F206" s="7" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G206" s="9" t="n">
         <v>1400</v>
@@ -14802,7 +14888,7 @@
         <v>24</v>
       </c>
       <c r="Q206" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R206" s="7" t="s">
         <v>31</v>
@@ -14813,7 +14899,7 @@
         <v>219</v>
       </c>
       <c r="B207" s="7" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="C207" s="6" t="s">
         <v>28</v>
@@ -14825,7 +14911,7 @@
         <v>1040</v>
       </c>
       <c r="F207" s="7" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G207" s="9" t="n">
         <v>1100</v>
@@ -14865,7 +14951,7 @@
         <v>24</v>
       </c>
       <c r="Q207" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R207" s="7" t="s">
         <v>31</v>
@@ -14876,7 +14962,7 @@
         <v>220</v>
       </c>
       <c r="B208" s="7" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="C208" s="6" t="s">
         <v>28</v>
@@ -14888,7 +14974,7 @@
         <v>1430</v>
       </c>
       <c r="F208" s="7" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G208" s="9" t="n">
         <v>1400</v>
@@ -14928,7 +15014,7 @@
         <v>24</v>
       </c>
       <c r="Q208" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R208" s="7" t="s">
         <v>31</v>
@@ -14939,7 +15025,7 @@
         <v>221</v>
       </c>
       <c r="B209" s="7" t="s">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="C209" s="6" t="s">
         <v>28</v>
@@ -14951,7 +15037,7 @@
         <v>1950</v>
       </c>
       <c r="F209" s="7" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="G209" s="9" t="n">
         <v>2000</v>
@@ -14991,7 +15077,7 @@
         <v>24</v>
       </c>
       <c r="Q209" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R209" s="7" t="s">
         <v>31</v>
@@ -15002,7 +15088,7 @@
         <v>222</v>
       </c>
       <c r="B210" s="7" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="C210" s="6" t="s">
         <v>28</v>
@@ -15014,7 +15100,7 @@
         <v>15600</v>
       </c>
       <c r="F210" s="7" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="G210" s="9" t="n">
         <v>18000</v>
@@ -15054,18 +15140,18 @@
         <v>24</v>
       </c>
       <c r="Q210" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R210" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="211" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="211" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="6" t="n">
         <v>223</v>
       </c>
       <c r="B211" s="7" t="s">
-        <v>400</v>
+        <v>414</v>
       </c>
       <c r="C211" s="6" t="s">
         <v>28</v>
@@ -15077,17 +15163,17 @@
         <v>30940</v>
       </c>
       <c r="F211" s="7" t="s">
-        <v>157</v>
+        <v>415</v>
       </c>
       <c r="G211" s="9" t="n">
-        <v>31300</v>
+        <v>45000</v>
       </c>
       <c r="H211" s="9" t="n">
-        <v>31300</v>
+        <v>60000</v>
       </c>
       <c r="I211" s="10" t="n">
         <f aca="false">IF(E211=0,0,(E211-H211)/E211)</f>
-        <v>-0.0116354234001293</v>
+        <v>-0.93923723335488</v>
       </c>
       <c r="J211" s="6" t="str">
         <f aca="false">IF(E211&lt;G211,"LOSS",IF(E211&lt;H211*1.1,"THIN / RISK",IF(E211&gt;H211*1.8,"OVERPRICED?","OK")))</f>
@@ -15095,7 +15181,7 @@
       </c>
       <c r="K211" s="8" t="n">
         <f aca="false">IF(J211="OVERPRICED?",ROUND(H211*1.35,-1),MAX(E211,ROUND(H211*(1+$E$3),-1)))</f>
-        <v>36000</v>
+        <v>69000</v>
       </c>
       <c r="L211" s="8" t="n">
         <f aca="false">D211*E211</f>
@@ -15103,30 +15189,32 @@
       </c>
       <c r="M211" s="8" t="n">
         <f aca="false">D211*K211</f>
-        <v>72000</v>
+        <v>138000</v>
       </c>
       <c r="N211" s="8" t="n">
         <f aca="false">D211*H211</f>
-        <v>62600</v>
+        <v>120000</v>
       </c>
       <c r="O211" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C211,F211)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P211" s="6" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="Q211" s="7" t="s">
-        <v>401</v>
-      </c>
-      <c r="R211" s="7"/>
+        <v>416</v>
+      </c>
+      <c r="R211" s="7" t="s">
+        <v>417</v>
+      </c>
     </row>
     <row r="212" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="6" t="n">
         <v>224</v>
       </c>
       <c r="B212" s="7" t="s">
-        <v>402</v>
+        <v>418</v>
       </c>
       <c r="C212" s="6" t="s">
         <v>28</v>
@@ -15138,7 +15226,7 @@
         <v>54600</v>
       </c>
       <c r="F212" s="7" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="G212" s="9" t="n">
         <v>85000</v>
@@ -15178,10 +15266,10 @@
         <v>24</v>
       </c>
       <c r="Q212" s="7" t="s">
-        <v>404</v>
+        <v>420</v>
       </c>
       <c r="R212" s="7" t="s">
-        <v>405</v>
+        <v>421</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15189,7 +15277,7 @@
         <v>225</v>
       </c>
       <c r="B213" s="7" t="s">
-        <v>406</v>
+        <v>422</v>
       </c>
       <c r="C213" s="6" t="s">
         <v>28</v>
@@ -15201,7 +15289,7 @@
         <v>1170</v>
       </c>
       <c r="F213" s="7" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="G213" s="9" t="n">
         <v>1800</v>
@@ -15241,7 +15329,7 @@
         <v>24</v>
       </c>
       <c r="Q213" s="7" t="s">
-        <v>407</v>
+        <v>423</v>
       </c>
       <c r="R213" s="7" t="s">
         <v>31</v>
@@ -15252,7 +15340,7 @@
         <v>226</v>
       </c>
       <c r="B214" s="7" t="s">
-        <v>408</v>
+        <v>424</v>
       </c>
       <c r="C214" s="6" t="s">
         <v>28</v>
@@ -15264,7 +15352,7 @@
         <v>1430</v>
       </c>
       <c r="F214" s="7" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="G214" s="9" t="n">
         <v>2600</v>
@@ -15304,7 +15392,7 @@
         <v>24</v>
       </c>
       <c r="Q214" s="7" t="s">
-        <v>407</v>
+        <v>423</v>
       </c>
       <c r="R214" s="7" t="s">
         <v>31</v>
@@ -15315,7 +15403,7 @@
         <v>227</v>
       </c>
       <c r="B215" s="7" t="s">
-        <v>409</v>
+        <v>425</v>
       </c>
       <c r="C215" s="6" t="s">
         <v>28</v>
@@ -15327,7 +15415,7 @@
         <v>1820</v>
       </c>
       <c r="F215" s="7" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="G215" s="9" t="n">
         <v>3500</v>
@@ -15367,7 +15455,7 @@
         <v>24</v>
       </c>
       <c r="Q215" s="7" t="s">
-        <v>407</v>
+        <v>423</v>
       </c>
       <c r="R215" s="7" t="s">
         <v>31</v>
@@ -15378,7 +15466,7 @@
         <v>228</v>
       </c>
       <c r="B216" s="7" t="s">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="C216" s="6" t="s">
         <v>28</v>
@@ -15390,7 +15478,7 @@
         <v>2860</v>
       </c>
       <c r="F216" s="7" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="G216" s="9" t="n">
         <v>6000</v>
@@ -15430,7 +15518,7 @@
         <v>24</v>
       </c>
       <c r="Q216" s="7" t="s">
-        <v>407</v>
+        <v>423</v>
       </c>
       <c r="R216" s="7" t="s">
         <v>31</v>
@@ -15441,7 +15529,7 @@
         <v>229</v>
       </c>
       <c r="B217" s="7" t="s">
-        <v>411</v>
+        <v>427</v>
       </c>
       <c r="C217" s="6" t="s">
         <v>28</v>
@@ -15453,7 +15541,7 @@
         <v>2340</v>
       </c>
       <c r="F217" s="7" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="G217" s="9" t="n">
         <v>3200</v>
@@ -15493,18 +15581,18 @@
         <v>24</v>
       </c>
       <c r="Q217" s="7" t="s">
-        <v>407</v>
+        <v>423</v>
       </c>
       <c r="R217" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="218" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="218" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="6" t="n">
         <v>230</v>
       </c>
       <c r="B218" s="7" t="s">
-        <v>412</v>
+        <v>428</v>
       </c>
       <c r="C218" s="6" t="s">
         <v>28</v>
@@ -15516,17 +15604,17 @@
         <v>9750</v>
       </c>
       <c r="F218" s="7" t="s">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="G218" s="9" t="n">
-        <v>5950</v>
+        <v>6000</v>
       </c>
       <c r="H218" s="9" t="n">
-        <v>5950</v>
+        <v>8500</v>
       </c>
       <c r="I218" s="10" t="n">
         <f aca="false">IF(E218=0,0,(E218-H218)/E218)</f>
-        <v>0.38974358974359</v>
+        <v>0.128205128205128</v>
       </c>
       <c r="J218" s="6" t="str">
         <f aca="false">IF(E218&lt;G218,"LOSS",IF(E218&lt;H218*1.1,"THIN / RISK",IF(E218&gt;H218*1.8,"OVERPRICED?","OK")))</f>
@@ -15534,7 +15622,7 @@
       </c>
       <c r="K218" s="8" t="n">
         <f aca="false">IF(J218="OVERPRICED?",ROUND(H218*1.35,-1),MAX(E218,ROUND(H218*(1+$E$3),-1)))</f>
-        <v>9750</v>
+        <v>9780</v>
       </c>
       <c r="L218" s="8" t="n">
         <f aca="false">D218*E218</f>
@@ -15542,32 +15630,32 @@
       </c>
       <c r="M218" s="8" t="n">
         <f aca="false">D218*K218</f>
-        <v>9750</v>
+        <v>9780</v>
       </c>
       <c r="N218" s="8" t="n">
         <f aca="false">D218*H218</f>
-        <v>5950</v>
+        <v>8500</v>
       </c>
       <c r="O218" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C218,F218)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P218" s="6" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="Q218" s="7" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
       <c r="R218" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="6" t="n">
         <v>231</v>
       </c>
       <c r="B219" s="7" t="s">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="C219" s="6" t="s">
         <v>28</v>
@@ -15579,25 +15667,25 @@
         <v>12350</v>
       </c>
       <c r="F219" s="7" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="G219" s="9" t="n">
-        <v>5950</v>
+        <v>8000</v>
       </c>
       <c r="H219" s="9" t="n">
-        <v>5950</v>
+        <v>11000</v>
       </c>
       <c r="I219" s="10" t="n">
         <f aca="false">IF(E219=0,0,(E219-H219)/E219)</f>
-        <v>0.518218623481781</v>
+        <v>0.109311740890688</v>
       </c>
       <c r="J219" s="6" t="str">
         <f aca="false">IF(E219&lt;G219,"LOSS",IF(E219&lt;H219*1.1,"THIN / RISK",IF(E219&gt;H219*1.8,"OVERPRICED?","OK")))</f>
-        <v>OVERPRICED?</v>
+        <v>OK</v>
       </c>
       <c r="K219" s="8" t="n">
         <f aca="false">IF(J219="OVERPRICED?",ROUND(H219*1.35,-1),MAX(E219,ROUND(H219*(1+$E$3),-1)))</f>
-        <v>8030</v>
+        <v>12650</v>
       </c>
       <c r="L219" s="8" t="n">
         <f aca="false">D219*E219</f>
@@ -15605,33 +15693,35 @@
       </c>
       <c r="M219" s="8" t="n">
         <f aca="false">D219*K219</f>
-        <v>8030</v>
+        <v>12650</v>
       </c>
       <c r="N219" s="8" t="n">
         <f aca="false">D219*H219</f>
-        <v>5950</v>
+        <v>11000</v>
       </c>
       <c r="O219" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C219,F219)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P219" s="6" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="Q219" s="7" t="s">
-        <v>416</v>
-      </c>
-      <c r="R219" s="7"/>
+        <v>434</v>
+      </c>
+      <c r="R219" s="7" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="220" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="6" t="n">
         <v>233</v>
       </c>
       <c r="B220" s="7" t="s">
-        <v>417</v>
+        <v>435</v>
       </c>
       <c r="C220" s="6" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D220" s="6" t="n">
         <v>2</v>
@@ -15640,7 +15730,7 @@
         <v>52000</v>
       </c>
       <c r="F220" s="7" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="G220" s="9" t="n">
         <v>40000</v>
@@ -15680,7 +15770,7 @@
         <v>43</v>
       </c>
       <c r="Q220" s="7" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="R220" s="7"/>
     </row>
@@ -15689,7 +15779,7 @@
         <v>234</v>
       </c>
       <c r="B221" s="7" t="s">
-        <v>419</v>
+        <v>437</v>
       </c>
       <c r="C221" s="6" t="s">
         <v>22</v>
@@ -15738,13 +15828,13 @@
         <v>YES</v>
       </c>
       <c r="P221" s="6" t="s">
-        <v>49</v>
+        <v>231</v>
       </c>
       <c r="Q221" s="7" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="R221" s="7" t="s">
-        <v>51</v>
+        <v>233</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15752,7 +15842,7 @@
         <v>235</v>
       </c>
       <c r="B222" s="7" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="C222" s="6" t="s">
         <v>28</v>
@@ -15804,10 +15894,10 @@
         <v>24</v>
       </c>
       <c r="Q222" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R222" s="7" t="s">
-        <v>422</v>
+        <v>440</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15815,7 +15905,7 @@
         <v>236</v>
       </c>
       <c r="B223" s="7" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="C223" s="6" t="s">
         <v>22</v>
@@ -15827,7 +15917,7 @@
         <v>2860</v>
       </c>
       <c r="F223" s="7" t="s">
-        <v>424</v>
+        <v>442</v>
       </c>
       <c r="G223" s="9" t="n">
         <v>2400</v>
@@ -15867,10 +15957,10 @@
         <v>24</v>
       </c>
       <c r="Q223" s="7" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="R223" s="7" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15878,7 +15968,7 @@
         <v>237</v>
       </c>
       <c r="B224" s="7" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="C224" s="6" t="s">
         <v>28</v>
@@ -15930,7 +16020,7 @@
         <v>24</v>
       </c>
       <c r="Q224" s="7" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="R224" s="7" t="s">
         <v>31</v>
@@ -15941,7 +16031,7 @@
         <v>238</v>
       </c>
       <c r="B225" s="7" t="s">
-        <v>428</v>
+        <v>446</v>
       </c>
       <c r="C225" s="6" t="s">
         <v>28</v>
@@ -15953,7 +16043,7 @@
         <v>8450</v>
       </c>
       <c r="F225" s="7" t="s">
-        <v>429</v>
+        <v>447</v>
       </c>
       <c r="G225" s="9" t="n">
         <v>7800</v>
@@ -15993,7 +16083,7 @@
         <v>43</v>
       </c>
       <c r="Q225" s="7" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="R225" s="7"/>
     </row>
@@ -16002,10 +16092,10 @@
         <v>239</v>
       </c>
       <c r="B226" s="7" t="s">
-        <v>431</v>
+        <v>449</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D226" s="6" t="n">
         <v>50</v>
@@ -16014,7 +16104,7 @@
         <v>65000</v>
       </c>
       <c r="F226" s="7" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="G226" s="9" t="n">
         <v>44000</v>
@@ -16054,7 +16144,7 @@
         <v>43</v>
       </c>
       <c r="Q226" s="7" t="s">
-        <v>432</v>
+        <v>450</v>
       </c>
       <c r="R226" s="7"/>
     </row>
@@ -16063,7 +16153,7 @@
         <v>240</v>
       </c>
       <c r="B227" s="7" t="s">
-        <v>433</v>
+        <v>451</v>
       </c>
       <c r="C227" s="6" t="s">
         <v>28</v>
@@ -16115,15 +16205,15 @@
         <v>24</v>
       </c>
       <c r="Q227" s="7" t="s">
-        <v>434</v>
+        <v>452</v>
       </c>
       <c r="R227" s="7" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B228" s="3" t="s">
-        <v>436</v>
+        <v>454</v>
       </c>
       <c r="L228" s="11" t="n">
         <f aca="false">SUM(L6:L227)</f>
@@ -16131,11 +16221,11 @@
       </c>
       <c r="M228" s="11" t="n">
         <f aca="false">SUM(M6:M227)</f>
-        <v>14464835</v>
+        <v>15308570</v>
       </c>
       <c r="N228" s="11" t="n">
         <f aca="false">SUM(N6:N227)</f>
-        <v>11550488</v>
+        <v>12371727</v>
       </c>
     </row>
   </sheetData>
@@ -16184,12 +16274,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="B3" s="11" t="n">
         <f aca="false">COUNTA('Rate Check'!A6:A227)</f>
@@ -16198,47 +16288,47 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="B4" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"LOSS")</f>
-        <v>72</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="B5" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"THIN / RISK")</f>
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>441</v>
+        <v>459</v>
       </c>
       <c r="B6" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"OK")</f>
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="B7" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"OVERPRICED?")</f>
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="B8" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!O6:O227,"YES")</f>
-        <v>155</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16246,7 +16336,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>444</v>
+        <v>462</v>
       </c>
       <c r="B10" s="11" t="n">
         <f aca="false">'Rate Check'!L228</f>
@@ -16255,38 +16345,38 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>445</v>
+        <v>463</v>
       </c>
       <c r="B11" s="11" t="n">
         <f aca="false">'Rate Check'!N228</f>
-        <v>11550488</v>
+        <v>12371727</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>446</v>
+        <v>464</v>
       </c>
       <c r="B12" s="11" t="n">
         <f aca="false">B10-B11</f>
-        <v>659020</v>
+        <v>-162219</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>447</v>
+        <v>465</v>
       </c>
       <c r="B13" s="14" t="n">
         <f aca="false">IF(B10=0,0,B12/B10)</f>
-        <v>0.053975966926759</v>
+        <v>-0.0132862847544717</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="B14" s="11" t="n">
         <f aca="false">SUMPRODUCT(('Rate Check'!E6:E227&lt;'Rate Check'!H6:H227)*('Rate Check'!H6:H227-'Rate Check'!E6:E227)*'Rate Check'!D6:D227)</f>
-        <v>2088163</v>
+        <v>2550050</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16294,20 +16384,20 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>449</v>
+        <v>467</v>
       </c>
       <c r="B16" s="11" t="n">
         <f aca="false">'Rate Check'!M228</f>
-        <v>14464835</v>
+        <v>15308570</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>450</v>
+        <v>468</v>
       </c>
       <c r="B17" s="14" t="n">
         <f aca="false">IF(B16=0,0,(B16-B11)/B16)</f>
-        <v>0.201478067326727</v>
+        <v>0.19184306568151</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16315,29 +16405,29 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
       <c r="B19" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!P6:P227,"V")</f>
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>452</v>
+        <v>470</v>
       </c>
       <c r="B20" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!P6:P227,"S")</f>
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="B21" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!P6:P227,"N")</f>
-        <v>145</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -16365,247 +16455,247 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>454</v>
+        <v>472</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>455</v>
+        <v>473</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>456</v>
+        <v>474</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>457</v>
+        <v>475</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>458</v>
+        <v>476</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>459</v>
+        <v>477</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>460</v>
+        <v>478</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>463</v>
+        <v>481</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>465</v>
+        <v>483</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>466</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>467</v>
+        <v>485</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>468</v>
+        <v>486</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>469</v>
+        <v>487</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>470</v>
+        <v>488</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>471</v>
+        <v>489</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>472</v>
+        <v>490</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>473</v>
+        <v>491</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>474</v>
+        <v>492</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>476</v>
+        <v>494</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>477</v>
+        <v>495</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>478</v>
+        <v>496</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>479</v>
+        <v>497</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>480</v>
+        <v>498</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>481</v>
+        <v>499</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>482</v>
+        <v>500</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>483</v>
+        <v>501</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>484</v>
+        <v>502</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>485</v>
+        <v>503</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>486</v>
+        <v>504</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>487</v>
+        <v>505</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>488</v>
+        <v>506</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>490</v>
+        <v>508</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>491</v>
+        <v>509</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>492</v>
+        <v>510</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>493</v>
+        <v>511</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>496</v>
+        <v>514</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>497</v>
+        <v>515</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>498</v>
+        <v>516</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>499</v>
+        <v>517</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>500</v>
+        <v>518</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>501</v>
+        <v>519</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>502</v>
+        <v>520</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>503</v>
+        <v>521</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>504</v>
+        <v>522</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>505</v>
+        <v>523</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>506</v>
+        <v>524</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>508</v>
+        <v>526</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>509</v>
+        <v>527</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>510</v>
+        <v>528</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>511</v>
+        <v>529</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>512</v>
+        <v>530</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>513</v>
+        <v>531</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>514</v>
+        <v>532</v>
       </c>
     </row>
   </sheetData>

--- a/quotes/PR-217-228/Quote_PR217_PR228_Rate_Check.xlsx
+++ b/quotes/PR-217-228/Quote_PR217_PR228_Rate_Check.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1385" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="529">
   <si>
     <t xml:space="preserve">Zidane Corporation - Quote PR-217 &amp; PR-228: Brand + Buying Rate Check</t>
   </si>
@@ -174,22 +174,19 @@
     <t xml:space="preserve">7 DRAWER TOOL TROLLEY</t>
   </si>
   <si>
-    <t xml:space="preserve">Licota (AWX series, empty)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ktools Yato 7-drawer 211pc 315,000 / 6-drawer 177pc 220,000 (with tools); empty Licota est</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Total 87000</t>
+    <t xml:space="preserve">toolsmart.pk LICOTA MADE IN TAIWAN 7 Drawer Cabinet Trolley without tools Rs 272,440 in stock (screenshot Hassan)</t>
   </si>
   <si>
     <t xml:space="preserve">DOUBLE OPEN RING OFFSET WRENCH SET (12PCS)</t>
   </si>
   <si>
-    <t xml:space="preserve">toolsmart Licota 14pc set 25,660</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Harden 15190</t>
+    <t xml:space="preserve">S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart.pk Licota offset ring singles 8x10 1,230 / 14x15 2,060 / 24x26 3,420 / 30x32 4,240 -&gt; 12pc 6-32 sum ~29,600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spec/pack/stock farq - source dekho</t>
   </si>
   <si>
     <t xml:space="preserve">DOUBLE OPEN END WRENCH 6 TO 32 (12 PCS SET)</t>
@@ -204,13 +201,13 @@
     <t xml:space="preserve">DOUBLE OPEN END WRENCH 36X41</t>
   </si>
   <si>
-    <t xml:space="preserve">goldentools.ae Licota DOE 21x23 AED 26 scaled to 36x41</t>
+    <t xml:space="preserve">toolsmart.pk Licota double open end 36x41 Rs 7,430</t>
   </si>
   <si>
     <t xml:space="preserve">DOUBLE OPEN END WRENCH 41X46</t>
   </si>
   <si>
-    <t xml:space="preserve">goldentools.ae Licota DOE 21x23 AED 26 scaled to 41x46</t>
+    <t xml:space="preserve">toolsmart.pk Licota double open end 41x46 Rs 12,310</t>
   </si>
   <si>
     <t xml:space="preserve">COMBINATION WRENCH 8 TO 32 (14 PCS SET)</t>
@@ -282,15 +279,12 @@
     <t xml:space="preserve">CIRCLIP PLIER INTERNAL STRAIGHT 175MM</t>
   </si>
   <si>
-    <t xml:space="preserve">toolsmart Licota 4pc snap ring plier set 175mm 11,650 (=int/ext straight/bent, per pc 2,913)</t>
+    <t xml:space="preserve">toolsmart.pk Licota 4pc snap ring set 175mm Rs 13,750 (=3,438/pc)</t>
   </si>
   <si>
     <t xml:space="preserve">CIRCLIP PLIER INTERNAL BENT 175MM</t>
   </si>
   <si>
-    <t xml:space="preserve">same set</t>
-  </si>
-  <si>
     <t xml:space="preserve">CIRCLIP PLIER EXTERNAL STRAIGHT 175MM</t>
   </si>
   <si>
@@ -720,13 +714,7 @@
     <t xml:space="preserve">CORDLESS DRILL DRIVER 150NM Bosch</t>
   </si>
   <si>
-    <t xml:space="preserve">S</t>
-  </si>
-  <si>
     <t xml:space="preserve">ktools Bosch GSB 18V-150C 199,500 (oos, single listing)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spec/pack/stock farq - source dekho</t>
   </si>
   <si>
     <t xml:space="preserve">TAP SET 1/2" BSPF LEFT HAND (Dormer)</t>
@@ -2773,25 +2761,25 @@
         <v>161070</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>150000</v>
+        <v>272440</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>210000</v>
+        <v>272440</v>
       </c>
       <c r="I13" s="10" t="n">
         <f aca="false">IF(E13=0,0,(E13-H13)/E13)</f>
-        <v>-0.303780964797914</v>
+        <v>-0.691438504997827</v>
       </c>
       <c r="J13" s="6" t="str">
         <f aca="false">IF(E13&lt;G13,"LOSS",IF(E13&lt;H13*1.1,"THIN / RISK",IF(E13&gt;H13*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>LOSS</v>
       </c>
       <c r="K13" s="8" t="n">
         <f aca="false">IF(J13="OVERPRICED?",ROUND(H13*1.35,-1),MAX(E13,ROUND(H13*(1+$E$3),-1)))</f>
-        <v>241500</v>
+        <v>313310</v>
       </c>
       <c r="L13" s="8" t="n">
         <f aca="false">D13*E13</f>
@@ -2799,32 +2787,30 @@
       </c>
       <c r="M13" s="8" t="n">
         <f aca="false">D13*K13</f>
-        <v>724500</v>
+        <v>939930</v>
       </c>
       <c r="N13" s="8" t="n">
         <f aca="false">D13*H13</f>
-        <v>630000</v>
+        <v>817320</v>
       </c>
       <c r="O13" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C13,F13)),"","YES")</f>
         <v/>
       </c>
       <c r="P13" s="6" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="R13" s="7" t="s">
-        <v>51</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="R13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="n">
         <v>9</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>28</v>
@@ -2839,14 +2825,14 @@
         <v>28</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>20000</v>
+        <v>29600</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>26000</v>
+        <v>29600</v>
       </c>
       <c r="I14" s="10" t="n">
         <f aca="false">IF(E14=0,0,(E14-H14)/E14)</f>
-        <v>-0.428571428571429</v>
+        <v>-0.626373626373626</v>
       </c>
       <c r="J14" s="6" t="str">
         <f aca="false">IF(E14&lt;G14,"LOSS",IF(E14&lt;H14*1.1,"THIN / RISK",IF(E14&gt;H14*1.8,"OVERPRICED?","OK")))</f>
@@ -2854,7 +2840,7 @@
       </c>
       <c r="K14" s="8" t="n">
         <f aca="false">IF(J14="OVERPRICED?",ROUND(H14*1.35,-1),MAX(E14,ROUND(H14*(1+$E$3),-1)))</f>
-        <v>29900</v>
+        <v>34040</v>
       </c>
       <c r="L14" s="8" t="n">
         <f aca="false">D14*E14</f>
@@ -2862,24 +2848,24 @@
       </c>
       <c r="M14" s="8" t="n">
         <f aca="false">D14*K14</f>
-        <v>119600</v>
+        <v>136160</v>
       </c>
       <c r="N14" s="8" t="n">
         <f aca="false">D14*H14</f>
-        <v>104000</v>
+        <v>118400</v>
       </c>
       <c r="O14" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C14,F14)),"","YES")</f>
         <v/>
       </c>
       <c r="P14" s="6" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="Q14" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="R14" s="7" t="s">
         <v>53</v>
-      </c>
-      <c r="R14" s="7" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2887,7 +2873,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>28</v>
@@ -2939,18 +2925,18 @@
         <v>24</v>
       </c>
       <c r="Q15" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="R15" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="R15" s="7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="n">
         <v>11</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>28</v>
@@ -2965,14 +2951,14 @@
         <v>28</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>7000</v>
+        <v>7430</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>8000</v>
+        <v>7430</v>
       </c>
       <c r="I16" s="10" t="n">
         <f aca="false">IF(E16=0,0,(E16-H16)/E16)</f>
-        <v>-1.1978021978022</v>
+        <v>-1.04120879120879</v>
       </c>
       <c r="J16" s="6" t="str">
         <f aca="false">IF(E16&lt;G16,"LOSS",IF(E16&lt;H16*1.1,"THIN / RISK",IF(E16&gt;H16*1.8,"OVERPRICED?","OK")))</f>
@@ -2980,7 +2966,7 @@
       </c>
       <c r="K16" s="8" t="n">
         <f aca="false">IF(J16="OVERPRICED?",ROUND(H16*1.35,-1),MAX(E16,ROUND(H16*(1+$E$3),-1)))</f>
-        <v>9200</v>
+        <v>8540</v>
       </c>
       <c r="L16" s="8" t="n">
         <f aca="false">D16*E16</f>
@@ -2988,32 +2974,30 @@
       </c>
       <c r="M16" s="8" t="n">
         <f aca="false">D16*K16</f>
-        <v>27600</v>
+        <v>25620</v>
       </c>
       <c r="N16" s="8" t="n">
         <f aca="false">D16*H16</f>
-        <v>24000</v>
+        <v>22290</v>
       </c>
       <c r="O16" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C16,F16)),"","YES")</f>
         <v/>
       </c>
       <c r="P16" s="6" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="R16" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="R16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="n">
         <v>12</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>28</v>
@@ -3028,14 +3012,14 @@
         <v>28</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>9500</v>
+        <v>12310</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>10500</v>
+        <v>12310</v>
       </c>
       <c r="I17" s="10" t="n">
         <f aca="false">IF(E17=0,0,(E17-H17)/E17)</f>
-        <v>-1.30769230769231</v>
+        <v>-1.70549450549451</v>
       </c>
       <c r="J17" s="6" t="str">
         <f aca="false">IF(E17&lt;G17,"LOSS",IF(E17&lt;H17*1.1,"THIN / RISK",IF(E17&gt;H17*1.8,"OVERPRICED?","OK")))</f>
@@ -3043,7 +3027,7 @@
       </c>
       <c r="K17" s="8" t="n">
         <f aca="false">IF(J17="OVERPRICED?",ROUND(H17*1.35,-1),MAX(E17,ROUND(H17*(1+$E$3),-1)))</f>
-        <v>12080</v>
+        <v>14160</v>
       </c>
       <c r="L17" s="8" t="n">
         <f aca="false">D17*E17</f>
@@ -3051,32 +3035,30 @@
       </c>
       <c r="M17" s="8" t="n">
         <f aca="false">D17*K17</f>
-        <v>36240</v>
+        <v>42480</v>
       </c>
       <c r="N17" s="8" t="n">
         <f aca="false">D17*H17</f>
-        <v>31500</v>
+        <v>36930</v>
       </c>
       <c r="O17" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C17,F17)),"","YES")</f>
         <v/>
       </c>
       <c r="P17" s="6" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="R17" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="R17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="n">
         <v>13</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>28</v>
@@ -3128,10 +3110,10 @@
         <v>24</v>
       </c>
       <c r="Q18" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="R18" s="7" t="s">
         <v>63</v>
-      </c>
-      <c r="R18" s="7" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3139,7 +3121,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>28</v>
@@ -3191,7 +3173,7 @@
         <v>43</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="R19" s="7"/>
     </row>
@@ -3200,7 +3182,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>28</v>
@@ -3252,7 +3234,7 @@
         <v>43</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R20" s="7"/>
     </row>
@@ -3261,7 +3243,7 @@
         <v>16</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>28</v>
@@ -3313,10 +3295,10 @@
         <v>24</v>
       </c>
       <c r="Q21" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="R21" s="7" t="s">
         <v>70</v>
-      </c>
-      <c r="R21" s="7" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3324,7 +3306,7 @@
         <v>17</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>28</v>
@@ -3376,7 +3358,7 @@
         <v>43</v>
       </c>
       <c r="Q22" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R22" s="7"/>
     </row>
@@ -3385,7 +3367,7 @@
         <v>18</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>28</v>
@@ -3437,10 +3419,10 @@
         <v>24</v>
       </c>
       <c r="Q23" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="R23" s="7" t="s">
         <v>75</v>
-      </c>
-      <c r="R23" s="7" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3448,7 +3430,7 @@
         <v>19</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>28</v>
@@ -3500,7 +3482,7 @@
         <v>43</v>
       </c>
       <c r="Q24" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R24" s="7"/>
     </row>
@@ -3509,7 +3491,7 @@
         <v>20</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>28</v>
@@ -3561,7 +3543,7 @@
         <v>24</v>
       </c>
       <c r="Q25" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R25" s="7" t="s">
         <v>31</v>
@@ -3572,7 +3554,7 @@
         <v>21</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>28</v>
@@ -3624,7 +3606,7 @@
         <v>24</v>
       </c>
       <c r="Q26" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="R26" s="7" t="s">
         <v>31</v>
@@ -3635,7 +3617,7 @@
         <v>22</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>28</v>
@@ -3687,7 +3669,7 @@
         <v>24</v>
       </c>
       <c r="Q27" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="R27" s="7" t="s">
         <v>31</v>
@@ -3698,7 +3680,7 @@
         <v>23</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>28</v>
@@ -3713,14 +3695,14 @@
         <v>28</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>2913</v>
+        <v>3438</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>2913</v>
+        <v>3438</v>
       </c>
       <c r="I28" s="10" t="n">
         <f aca="false">IF(E28=0,0,(E28-H28)/E28)</f>
-        <v>0.410323886639676</v>
+        <v>0.304048582995951</v>
       </c>
       <c r="J28" s="6" t="str">
         <f aca="false">IF(E28&lt;G28,"LOSS",IF(E28&lt;H28*1.1,"THIN / RISK",IF(E28&gt;H28*1.8,"OVERPRICED?","OK")))</f>
@@ -3740,7 +3722,7 @@
       </c>
       <c r="N28" s="8" t="n">
         <f aca="false">D28*H28</f>
-        <v>11652</v>
+        <v>13752</v>
       </c>
       <c r="O28" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C28,F28)),"","YES")</f>
@@ -3750,16 +3732,16 @@
         <v>43</v>
       </c>
       <c r="Q28" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="R28" s="7"/>
+    </row>
+    <row r="29" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="7" t="s">
         <v>85</v>
-      </c>
-      <c r="R28" s="7"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="n">
-        <v>24</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>86</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>28</v>
@@ -3774,14 +3756,14 @@
         <v>28</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>2913</v>
+        <v>3438</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>2913</v>
+        <v>3438</v>
       </c>
       <c r="I29" s="10" t="n">
         <f aca="false">IF(E29=0,0,(E29-H29)/E29)</f>
-        <v>0.410323886639676</v>
+        <v>0.304048582995951</v>
       </c>
       <c r="J29" s="6" t="str">
         <f aca="false">IF(E29&lt;G29,"LOSS",IF(E29&lt;H29*1.1,"THIN / RISK",IF(E29&gt;H29*1.8,"OVERPRICED?","OK")))</f>
@@ -3801,7 +3783,7 @@
       </c>
       <c r="N29" s="8" t="n">
         <f aca="false">D29*H29</f>
-        <v>11652</v>
+        <v>13752</v>
       </c>
       <c r="O29" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C29,F29)),"","YES")</f>
@@ -3811,16 +3793,16 @@
         <v>43</v>
       </c>
       <c r="Q29" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="R29" s="7"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="n">
         <v>25</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>28</v>
@@ -3835,14 +3817,14 @@
         <v>28</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>2913</v>
+        <v>3438</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>2913</v>
+        <v>3438</v>
       </c>
       <c r="I30" s="10" t="n">
         <f aca="false">IF(E30=0,0,(E30-H30)/E30)</f>
-        <v>0.410323886639676</v>
+        <v>0.304048582995951</v>
       </c>
       <c r="J30" s="6" t="str">
         <f aca="false">IF(E30&lt;G30,"LOSS",IF(E30&lt;H30*1.1,"THIN / RISK",IF(E30&gt;H30*1.8,"OVERPRICED?","OK")))</f>
@@ -3862,7 +3844,7 @@
       </c>
       <c r="N30" s="8" t="n">
         <f aca="false">D30*H30</f>
-        <v>11652</v>
+        <v>13752</v>
       </c>
       <c r="O30" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C30,F30)),"","YES")</f>
@@ -3872,16 +3854,16 @@
         <v>43</v>
       </c>
       <c r="Q30" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="R30" s="7"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="n">
         <v>26</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>28</v>
@@ -3896,14 +3878,14 @@
         <v>28</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>2913</v>
+        <v>3438</v>
       </c>
       <c r="H31" s="9" t="n">
-        <v>2913</v>
+        <v>3438</v>
       </c>
       <c r="I31" s="10" t="n">
         <f aca="false">IF(E31=0,0,(E31-H31)/E31)</f>
-        <v>0.410323886639676</v>
+        <v>0.304048582995951</v>
       </c>
       <c r="J31" s="6" t="str">
         <f aca="false">IF(E31&lt;G31,"LOSS",IF(E31&lt;H31*1.1,"THIN / RISK",IF(E31&gt;H31*1.8,"OVERPRICED?","OK")))</f>
@@ -3923,7 +3905,7 @@
       </c>
       <c r="N31" s="8" t="n">
         <f aca="false">D31*H31</f>
-        <v>11652</v>
+        <v>13752</v>
       </c>
       <c r="O31" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C31,F31)),"","YES")</f>
@@ -3933,7 +3915,7 @@
         <v>43</v>
       </c>
       <c r="Q31" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="R31" s="7"/>
     </row>
@@ -3942,7 +3924,7 @@
         <v>27</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>28</v>
@@ -3994,10 +3976,10 @@
         <v>24</v>
       </c>
       <c r="Q32" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="R32" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4005,7 +3987,7 @@
         <v>28</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>28</v>
@@ -4057,10 +4039,10 @@
         <v>24</v>
       </c>
       <c r="Q33" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="R33" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4068,7 +4050,7 @@
         <v>30</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>28</v>
@@ -4120,7 +4102,7 @@
         <v>43</v>
       </c>
       <c r="Q34" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="R34" s="7"/>
     </row>
@@ -4129,7 +4111,7 @@
         <v>31</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>28</v>
@@ -4181,10 +4163,10 @@
         <v>24</v>
       </c>
       <c r="Q35" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="R35" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4192,7 +4174,7 @@
         <v>32</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>28</v>
@@ -4244,10 +4226,10 @@
         <v>24</v>
       </c>
       <c r="Q36" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="R36" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4255,7 +4237,7 @@
         <v>33</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>28</v>
@@ -4307,7 +4289,7 @@
         <v>43</v>
       </c>
       <c r="Q37" s="7" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="R37" s="7"/>
     </row>
@@ -4316,7 +4298,7 @@
         <v>34</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>28</v>
@@ -4368,10 +4350,10 @@
         <v>24</v>
       </c>
       <c r="Q38" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="R38" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4379,7 +4361,7 @@
         <v>35</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>28</v>
@@ -4431,10 +4413,10 @@
         <v>24</v>
       </c>
       <c r="Q39" s="7" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="R39" s="7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4442,7 +4424,7 @@
         <v>36</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>28</v>
@@ -4494,10 +4476,10 @@
         <v>24</v>
       </c>
       <c r="Q40" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="R40" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4505,7 +4487,7 @@
         <v>37</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>28</v>
@@ -4557,10 +4539,10 @@
         <v>24</v>
       </c>
       <c r="Q41" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="R41" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4568,7 +4550,7 @@
         <v>38</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>28</v>
@@ -4620,10 +4602,10 @@
         <v>24</v>
       </c>
       <c r="Q42" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R42" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4631,7 +4613,7 @@
         <v>39</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>28</v>
@@ -4683,10 +4665,10 @@
         <v>24</v>
       </c>
       <c r="Q43" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="R43" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4694,10 +4676,10 @@
         <v>40</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D44" s="6" t="n">
         <v>3</v>
@@ -4706,7 +4688,7 @@
         <v>79300</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G44" s="9" t="n">
         <v>79000</v>
@@ -4746,7 +4728,7 @@
         <v>43</v>
       </c>
       <c r="Q44" s="7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="R44" s="7"/>
     </row>
@@ -4755,10 +4737,10 @@
         <v>41</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>3</v>
@@ -4767,7 +4749,7 @@
         <v>128700</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G45" s="9" t="n">
         <v>95000</v>
@@ -4807,10 +4789,10 @@
         <v>24</v>
       </c>
       <c r="Q45" s="7" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="R45" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4818,10 +4800,10 @@
         <v>42</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D46" s="6" t="n">
         <v>2</v>
@@ -4830,7 +4812,7 @@
         <v>106600</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G46" s="9" t="n">
         <v>143800</v>
@@ -4870,7 +4852,7 @@
         <v>43</v>
       </c>
       <c r="Q46" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="R46" s="7"/>
     </row>
@@ -4879,7 +4861,7 @@
         <v>43</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>28</v>
@@ -4931,7 +4913,7 @@
         <v>24</v>
       </c>
       <c r="Q47" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="R47" s="7" t="s">
         <v>31</v>
@@ -4942,7 +4924,7 @@
         <v>44</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>28</v>
@@ -4954,7 +4936,7 @@
         <v>1950</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G48" s="9" t="n">
         <v>1750</v>
@@ -4994,7 +4976,7 @@
         <v>43</v>
       </c>
       <c r="Q48" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="R48" s="7"/>
     </row>
@@ -5003,7 +4985,7 @@
         <v>45</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>28</v>
@@ -5015,7 +4997,7 @@
         <v>2210</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G49" s="9" t="n">
         <v>1750</v>
@@ -5055,10 +5037,10 @@
         <v>24</v>
       </c>
       <c r="Q49" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="R49" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5066,7 +5048,7 @@
         <v>47</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>28</v>
@@ -5118,7 +5100,7 @@
         <v>24</v>
       </c>
       <c r="Q50" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="R50" s="7" t="s">
         <v>31</v>
@@ -5129,7 +5111,7 @@
         <v>48</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>28</v>
@@ -5181,7 +5163,7 @@
         <v>24</v>
       </c>
       <c r="Q51" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="R51" s="7" t="s">
         <v>31</v>
@@ -5192,7 +5174,7 @@
         <v>49</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>28</v>
@@ -5244,7 +5226,7 @@
         <v>24</v>
       </c>
       <c r="Q52" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="R52" s="7" t="s">
         <v>31</v>
@@ -5255,7 +5237,7 @@
         <v>50</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>28</v>
@@ -5307,7 +5289,7 @@
         <v>24</v>
       </c>
       <c r="Q53" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="R53" s="7" t="s">
         <v>31</v>
@@ -5318,7 +5300,7 @@
         <v>51</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>28</v>
@@ -5370,7 +5352,7 @@
         <v>24</v>
       </c>
       <c r="Q54" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="R54" s="7" t="s">
         <v>31</v>
@@ -5381,7 +5363,7 @@
         <v>52</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>28</v>
@@ -5433,10 +5415,10 @@
         <v>24</v>
       </c>
       <c r="Q55" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="R55" s="7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5444,7 +5426,7 @@
         <v>53</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>28</v>
@@ -5496,10 +5478,10 @@
         <v>24</v>
       </c>
       <c r="Q56" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="R56" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5507,10 +5489,10 @@
         <v>54</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D57" s="6" t="n">
         <v>2</v>
@@ -5519,7 +5501,7 @@
         <v>400946</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G57" s="9" t="n">
         <v>115000</v>
@@ -5559,7 +5541,7 @@
         <v>43</v>
       </c>
       <c r="Q57" s="7" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="R57" s="7"/>
     </row>
@@ -5568,7 +5550,7 @@
         <v>55</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>28</v>
@@ -5580,7 +5562,7 @@
         <v>15600</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G58" s="9" t="n">
         <v>12000</v>
@@ -5620,10 +5602,10 @@
         <v>24</v>
       </c>
       <c r="Q58" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R58" s="7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5631,7 +5613,7 @@
         <v>56</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>28</v>
@@ -5683,10 +5665,10 @@
         <v>24</v>
       </c>
       <c r="Q59" s="7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="R59" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5694,7 +5676,7 @@
         <v>57</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>28</v>
@@ -5746,7 +5728,7 @@
         <v>43</v>
       </c>
       <c r="Q60" s="7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="R60" s="7"/>
     </row>
@@ -5755,7 +5737,7 @@
         <v>58</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>28</v>
@@ -5807,7 +5789,7 @@
         <v>24</v>
       </c>
       <c r="Q61" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R61" s="7" t="s">
         <v>31</v>
@@ -5818,7 +5800,7 @@
         <v>59</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>28</v>
@@ -5870,7 +5852,7 @@
         <v>24</v>
       </c>
       <c r="Q62" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R62" s="7" t="s">
         <v>31</v>
@@ -5881,7 +5863,7 @@
         <v>60</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>28</v>
@@ -5893,7 +5875,7 @@
         <v>9100</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G63" s="9" t="n">
         <v>8000</v>
@@ -5933,10 +5915,10 @@
         <v>24</v>
       </c>
       <c r="Q63" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="R63" s="7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5944,7 +5926,7 @@
         <v>61</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>28</v>
@@ -5956,7 +5938,7 @@
         <v>5850</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G64" s="9" t="n">
         <v>5000</v>
@@ -5996,10 +5978,10 @@
         <v>24</v>
       </c>
       <c r="Q64" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R64" s="7" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6007,7 +5989,7 @@
         <v>62</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>28</v>
@@ -6059,10 +6041,10 @@
         <v>24</v>
       </c>
       <c r="Q65" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R65" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6070,7 +6052,7 @@
         <v>63</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>28</v>
@@ -6122,10 +6104,10 @@
         <v>24</v>
       </c>
       <c r="Q66" s="7" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R66" s="7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6133,7 +6115,7 @@
         <v>64</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>28</v>
@@ -6145,7 +6127,7 @@
         <v>1560</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G67" s="9" t="n">
         <v>1350</v>
@@ -6185,7 +6167,7 @@
         <v>43</v>
       </c>
       <c r="Q67" s="7" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="R67" s="7"/>
     </row>
@@ -6194,7 +6176,7 @@
         <v>65</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>28</v>
@@ -6206,7 +6188,7 @@
         <v>1560</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G68" s="9" t="n">
         <v>1350</v>
@@ -6246,7 +6228,7 @@
         <v>43</v>
       </c>
       <c r="Q68" s="7" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="R68" s="7"/>
     </row>
@@ -6255,7 +6237,7 @@
         <v>66</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>28</v>
@@ -6267,7 +6249,7 @@
         <v>11700</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G69" s="9" t="n">
         <v>14000</v>
@@ -6307,7 +6289,7 @@
         <v>24</v>
       </c>
       <c r="Q69" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R69" s="7" t="s">
         <v>31</v>
@@ -6318,7 +6300,7 @@
         <v>67</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>28</v>
@@ -6330,7 +6312,7 @@
         <v>9750</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G70" s="9" t="n">
         <v>12000</v>
@@ -6370,7 +6352,7 @@
         <v>24</v>
       </c>
       <c r="Q70" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R70" s="7" t="s">
         <v>31</v>
@@ -6381,7 +6363,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>28</v>
@@ -6393,7 +6375,7 @@
         <v>23400</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G71" s="9" t="n">
         <v>15000</v>
@@ -6433,7 +6415,7 @@
         <v>24</v>
       </c>
       <c r="Q71" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R71" s="7" t="s">
         <v>31</v>
@@ -6444,7 +6426,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>28</v>
@@ -6456,7 +6438,7 @@
         <v>32500</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G72" s="9" t="n">
         <v>25000</v>
@@ -6496,7 +6478,7 @@
         <v>24</v>
       </c>
       <c r="Q72" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R72" s="7" t="s">
         <v>31</v>
@@ -6507,7 +6489,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>28</v>
@@ -6519,7 +6501,7 @@
         <v>1105</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G73" s="9" t="n">
         <v>800</v>
@@ -6559,10 +6541,10 @@
         <v>24</v>
       </c>
       <c r="Q73" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R73" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6570,7 +6552,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>28</v>
@@ -6582,7 +6564,7 @@
         <v>45500</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G74" s="9" t="n">
         <v>35000</v>
@@ -6622,10 +6604,10 @@
         <v>24</v>
       </c>
       <c r="Q74" s="7" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="R74" s="7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6633,7 +6615,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>28</v>
@@ -6645,7 +6627,7 @@
         <v>23400</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G75" s="9" t="n">
         <v>45000</v>
@@ -6685,10 +6667,10 @@
         <v>24</v>
       </c>
       <c r="Q75" s="7" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="R75" s="7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6696,7 +6678,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>28</v>
@@ -6708,7 +6690,7 @@
         <v>1950</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G76" s="9" t="n">
         <v>9790</v>
@@ -6748,7 +6730,7 @@
         <v>24</v>
       </c>
       <c r="Q76" s="7" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="R76" s="7" t="s">
         <v>31</v>
@@ -6759,7 +6741,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>28</v>
@@ -6771,7 +6753,7 @@
         <v>2080</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G77" s="9" t="n">
         <v>11060</v>
@@ -6811,7 +6793,7 @@
         <v>24</v>
       </c>
       <c r="Q77" s="7" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="R77" s="7" t="s">
         <v>31</v>
@@ -6822,7 +6804,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>28</v>
@@ -6834,7 +6816,7 @@
         <v>2210</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G78" s="9" t="n">
         <v>11700</v>
@@ -6874,7 +6856,7 @@
         <v>24</v>
       </c>
       <c r="Q78" s="7" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="R78" s="7" t="s">
         <v>31</v>
@@ -6885,7 +6867,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>28</v>
@@ -6897,7 +6879,7 @@
         <v>2340</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G79" s="9" t="n">
         <v>12330</v>
@@ -6937,7 +6919,7 @@
         <v>24</v>
       </c>
       <c r="Q79" s="7" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="R79" s="7" t="s">
         <v>31</v>
@@ -6948,7 +6930,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>28</v>
@@ -6960,7 +6942,7 @@
         <v>2470</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G80" s="9" t="n">
         <v>12970</v>
@@ -7000,7 +6982,7 @@
         <v>24</v>
       </c>
       <c r="Q80" s="7" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="R80" s="7" t="s">
         <v>31</v>
@@ -7011,7 +6993,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>28</v>
@@ -7023,7 +7005,7 @@
         <v>2600</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G81" s="9" t="n">
         <v>13600</v>
@@ -7063,7 +7045,7 @@
         <v>24</v>
       </c>
       <c r="Q81" s="7" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="R81" s="7" t="s">
         <v>31</v>
@@ -7074,7 +7056,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>28</v>
@@ -7086,7 +7068,7 @@
         <v>2730</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G82" s="9" t="n">
         <v>14240</v>
@@ -7126,7 +7108,7 @@
         <v>24</v>
       </c>
       <c r="Q82" s="7" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="R82" s="7" t="s">
         <v>31</v>
@@ -7137,7 +7119,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>28</v>
@@ -7149,7 +7131,7 @@
         <v>3250</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G83" s="9" t="n">
         <v>16140</v>
@@ -7189,7 +7171,7 @@
         <v>24</v>
       </c>
       <c r="Q83" s="7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="R83" s="7" t="s">
         <v>31</v>
@@ -7200,7 +7182,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>28</v>
@@ -7212,7 +7194,7 @@
         <v>4160</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G84" s="9" t="n">
         <v>19230</v>
@@ -7252,7 +7234,7 @@
         <v>24</v>
       </c>
       <c r="Q84" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="R84" s="7" t="s">
         <v>31</v>
@@ -7263,7 +7245,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>28</v>
@@ -7275,7 +7257,7 @@
         <v>5850</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G85" s="9" t="n">
         <v>26490</v>
@@ -7315,7 +7297,7 @@
         <v>24</v>
       </c>
       <c r="Q85" s="7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="R85" s="7" t="s">
         <v>31</v>
@@ -7326,7 +7308,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>28</v>
@@ -7338,7 +7320,7 @@
         <v>8450</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G86" s="9" t="n">
         <v>38450</v>
@@ -7378,7 +7360,7 @@
         <v>24</v>
       </c>
       <c r="Q86" s="7" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="R86" s="7" t="s">
         <v>31</v>
@@ -7389,7 +7371,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>28</v>
@@ -7401,7 +7383,7 @@
         <v>9750</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G87" s="9" t="n">
         <v>44060</v>
@@ -7441,7 +7423,7 @@
         <v>24</v>
       </c>
       <c r="Q87" s="7" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="R87" s="7" t="s">
         <v>31</v>
@@ -7452,7 +7434,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>28</v>
@@ -7464,7 +7446,7 @@
         <v>11700</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G88" s="9" t="n">
         <v>52470</v>
@@ -7504,7 +7486,7 @@
         <v>24</v>
       </c>
       <c r="Q88" s="7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="R88" s="7" t="s">
         <v>31</v>
@@ -7515,7 +7497,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>28</v>
@@ -7527,7 +7509,7 @@
         <v>4550</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G89" s="9" t="n">
         <v>3500</v>
@@ -7567,7 +7549,7 @@
         <v>24</v>
       </c>
       <c r="Q89" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R89" s="7" t="s">
         <v>31</v>
@@ -7578,7 +7560,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>28</v>
@@ -7590,7 +7572,7 @@
         <v>5850</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G90" s="9" t="n">
         <v>4500</v>
@@ -7630,7 +7612,7 @@
         <v>24</v>
       </c>
       <c r="Q90" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R90" s="7" t="s">
         <v>31</v>
@@ -7641,7 +7623,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>28</v>
@@ -7653,7 +7635,7 @@
         <v>7150</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G91" s="9" t="n">
         <v>5500</v>
@@ -7693,7 +7675,7 @@
         <v>24</v>
       </c>
       <c r="Q91" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R91" s="7" t="s">
         <v>31</v>
@@ -7704,7 +7686,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>28</v>
@@ -7716,7 +7698,7 @@
         <v>2340</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G92" s="9" t="n">
         <v>2500</v>
@@ -7756,7 +7738,7 @@
         <v>24</v>
       </c>
       <c r="Q92" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R92" s="7" t="s">
         <v>31</v>
@@ -7767,7 +7749,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>28</v>
@@ -7779,7 +7761,7 @@
         <v>2860</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G93" s="9" t="n">
         <v>3000</v>
@@ -7819,7 +7801,7 @@
         <v>24</v>
       </c>
       <c r="Q93" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R93" s="7" t="s">
         <v>31</v>
@@ -7830,10 +7812,10 @@
         <v>93</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D94" s="6" t="n">
         <v>2</v>
@@ -7842,7 +7824,7 @@
         <v>25350</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G94" s="9" t="n">
         <v>18100</v>
@@ -7882,7 +7864,7 @@
         <v>43</v>
       </c>
       <c r="Q94" s="7" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="R94" s="7"/>
     </row>
@@ -7891,10 +7873,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D95" s="6" t="n">
         <v>3</v>
@@ -7903,7 +7885,7 @@
         <v>8138</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G95" s="9" t="n">
         <v>15800</v>
@@ -7943,7 +7925,7 @@
         <v>43</v>
       </c>
       <c r="Q95" s="7" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="R95" s="7"/>
     </row>
@@ -7952,10 +7934,10 @@
         <v>95</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D96" s="6" t="n">
         <v>3</v>
@@ -7964,7 +7946,7 @@
         <v>6370</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G96" s="9" t="n">
         <v>7928</v>
@@ -8004,7 +7986,7 @@
         <v>43</v>
       </c>
       <c r="Q96" s="7" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="R96" s="7"/>
     </row>
@@ -8013,7 +7995,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>28</v>
@@ -8025,7 +8007,7 @@
         <v>14950</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G97" s="9" t="n">
         <v>15000</v>
@@ -8065,10 +8047,10 @@
         <v>24</v>
       </c>
       <c r="Q97" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R97" s="7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8076,10 +8058,10 @@
         <v>97</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D98" s="6" t="n">
         <v>2</v>
@@ -8088,7 +8070,7 @@
         <v>286000</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G98" s="9" t="n">
         <v>199500</v>
@@ -8125,13 +8107,13 @@
         <v/>
       </c>
       <c r="P98" s="6" t="s">
-        <v>231</v>
+        <v>51</v>
       </c>
       <c r="Q98" s="7" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="R98" s="7" t="s">
-        <v>233</v>
+        <v>53</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8139,10 +8121,10 @@
         <v>98</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="D99" s="6" t="n">
         <v>1</v>
@@ -8151,7 +8133,7 @@
         <v>15600</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="G99" s="9" t="n">
         <v>12000</v>
@@ -8191,7 +8173,7 @@
         <v>24</v>
       </c>
       <c r="Q99" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R99" s="7" t="s">
         <v>31</v>
@@ -8202,7 +8184,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>28</v>
@@ -8214,7 +8196,7 @@
         <v>11050</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="G100" s="9" t="n">
         <v>8000</v>
@@ -8254,7 +8236,7 @@
         <v>24</v>
       </c>
       <c r="Q100" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R100" s="7" t="s">
         <v>31</v>
@@ -8265,7 +8247,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>28</v>
@@ -8277,7 +8259,7 @@
         <v>9100</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="G101" s="9" t="n">
         <v>6500</v>
@@ -8317,7 +8299,7 @@
         <v>24</v>
       </c>
       <c r="Q101" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R101" s="7" t="s">
         <v>31</v>
@@ -8328,7 +8310,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>28</v>
@@ -8340,7 +8322,7 @@
         <v>7150</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="G102" s="9" t="n">
         <v>5500</v>
@@ -8380,7 +8362,7 @@
         <v>24</v>
       </c>
       <c r="Q102" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R102" s="7" t="s">
         <v>31</v>
@@ -8391,7 +8373,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>28</v>
@@ -8403,7 +8385,7 @@
         <v>5850</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="G103" s="9" t="n">
         <v>4500</v>
@@ -8443,7 +8425,7 @@
         <v>24</v>
       </c>
       <c r="Q103" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R103" s="7" t="s">
         <v>31</v>
@@ -8454,7 +8436,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>22</v>
@@ -8506,7 +8488,7 @@
         <v>24</v>
       </c>
       <c r="Q104" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R104" s="7" t="s">
         <v>31</v>
@@ -8517,7 +8499,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>22</v>
@@ -8569,10 +8551,10 @@
         <v>24</v>
       </c>
       <c r="Q105" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R105" s="7" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8580,7 +8562,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>22</v>
@@ -8592,7 +8574,7 @@
         <v>1170</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="G106" s="9" t="n">
         <v>800</v>
@@ -8632,7 +8614,7 @@
         <v>43</v>
       </c>
       <c r="Q106" s="7" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="R106" s="7"/>
     </row>
@@ -8641,7 +8623,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>28</v>
@@ -8653,7 +8635,7 @@
         <v>3640</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G107" s="9" t="n">
         <v>2000</v>
@@ -8693,10 +8675,10 @@
         <v>24</v>
       </c>
       <c r="Q107" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R107" s="7" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8704,7 +8686,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>28</v>
@@ -8716,7 +8698,7 @@
         <v>6760</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G108" s="9" t="n">
         <v>4500</v>
@@ -8756,10 +8738,10 @@
         <v>24</v>
       </c>
       <c r="Q108" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R108" s="7" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8767,7 +8749,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>28</v>
@@ -8779,7 +8761,7 @@
         <v>4550</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G109" s="9" t="n">
         <v>3500</v>
@@ -8819,10 +8801,10 @@
         <v>24</v>
       </c>
       <c r="Q109" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R109" s="7" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8830,7 +8812,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>28</v>
@@ -8842,7 +8824,7 @@
         <v>2340</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G110" s="9" t="n">
         <v>1800</v>
@@ -8882,10 +8864,10 @@
         <v>24</v>
       </c>
       <c r="Q110" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R110" s="7" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8893,7 +8875,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>28</v>
@@ -8905,7 +8887,7 @@
         <v>1820</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G111" s="9" t="n">
         <v>2000</v>
@@ -8945,10 +8927,10 @@
         <v>24</v>
       </c>
       <c r="Q111" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R111" s="7" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8956,7 +8938,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>28</v>
@@ -8968,7 +8950,7 @@
         <v>2860</v>
       </c>
       <c r="F112" s="7" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G112" s="9" t="n">
         <v>4000</v>
@@ -9008,10 +8990,10 @@
         <v>24</v>
       </c>
       <c r="Q112" s="7" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="R112" s="7" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9019,7 +9001,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>28</v>
@@ -9031,7 +9013,7 @@
         <v>12350</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G113" s="9" t="n">
         <v>8000</v>
@@ -9071,10 +9053,10 @@
         <v>24</v>
       </c>
       <c r="Q113" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R113" s="7" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9082,7 +9064,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>28</v>
@@ -9134,7 +9116,7 @@
         <v>24</v>
       </c>
       <c r="Q114" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R114" s="7" t="s">
         <v>31</v>
@@ -9145,7 +9127,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>28</v>
@@ -9197,7 +9179,7 @@
         <v>24</v>
       </c>
       <c r="Q115" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R115" s="7" t="s">
         <v>31</v>
@@ -9208,7 +9190,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>22</v>
@@ -9220,7 +9202,7 @@
         <v>11050</v>
       </c>
       <c r="F116" s="7" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="G116" s="9" t="n">
         <v>5000</v>
@@ -9260,7 +9242,7 @@
         <v>43</v>
       </c>
       <c r="Q116" s="7" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="R116" s="7"/>
     </row>
@@ -9269,7 +9251,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>28</v>
@@ -9321,10 +9303,10 @@
         <v>24</v>
       </c>
       <c r="Q117" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R117" s="7" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9332,7 +9314,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>22</v>
@@ -9384,7 +9366,7 @@
         <v>24</v>
       </c>
       <c r="Q118" s="7" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="R118" s="7" t="s">
         <v>31</v>
@@ -9395,7 +9377,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>22</v>
@@ -9447,7 +9429,7 @@
         <v>24</v>
       </c>
       <c r="Q119" s="7" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="R119" s="7" t="s">
         <v>31</v>
@@ -9458,7 +9440,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>28</v>
@@ -9510,7 +9492,7 @@
         <v>24</v>
       </c>
       <c r="Q120" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R120" s="7" t="s">
         <v>31</v>
@@ -9521,7 +9503,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>22</v>
@@ -9573,7 +9555,7 @@
         <v>24</v>
       </c>
       <c r="Q121" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R121" s="7" t="s">
         <v>31</v>
@@ -9584,7 +9566,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>22</v>
@@ -9636,7 +9618,7 @@
         <v>43</v>
       </c>
       <c r="Q122" s="7" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="R122" s="7"/>
     </row>
@@ -9645,7 +9627,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>22</v>
@@ -9657,7 +9639,7 @@
         <v>357500</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="G123" s="9" t="n">
         <v>200000</v>
@@ -9697,10 +9679,10 @@
         <v>24</v>
       </c>
       <c r="Q123" s="7" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="R123" s="7" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9708,7 +9690,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C124" s="6" t="s">
         <v>22</v>
@@ -9760,10 +9742,10 @@
         <v>24</v>
       </c>
       <c r="Q124" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R124" s="7" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9771,7 +9753,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>22</v>
@@ -9823,7 +9805,7 @@
         <v>24</v>
       </c>
       <c r="Q125" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R125" s="7" t="s">
         <v>31</v>
@@ -9834,7 +9816,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>22</v>
@@ -9886,7 +9868,7 @@
         <v>24</v>
       </c>
       <c r="Q126" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R126" s="7" t="s">
         <v>31</v>
@@ -9897,7 +9879,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>22</v>
@@ -9949,7 +9931,7 @@
         <v>24</v>
       </c>
       <c r="Q127" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R127" s="7" t="s">
         <v>31</v>
@@ -9960,7 +9942,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>22</v>
@@ -10012,7 +9994,7 @@
         <v>24</v>
       </c>
       <c r="Q128" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R128" s="7" t="s">
         <v>31</v>
@@ -10023,7 +10005,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>22</v>
@@ -10075,7 +10057,7 @@
         <v>24</v>
       </c>
       <c r="Q129" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R129" s="7" t="s">
         <v>31</v>
@@ -10086,7 +10068,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>22</v>
@@ -10138,7 +10120,7 @@
         <v>24</v>
       </c>
       <c r="Q130" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R130" s="7" t="s">
         <v>31</v>
@@ -10149,7 +10131,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>22</v>
@@ -10201,10 +10183,10 @@
         <v>24</v>
       </c>
       <c r="Q131" s="7" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="R131" s="7" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10212,7 +10194,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>22</v>
@@ -10224,7 +10206,7 @@
         <v>7800</v>
       </c>
       <c r="F132" s="7" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="G132" s="9" t="n">
         <v>5000</v>
@@ -10264,7 +10246,7 @@
         <v>43</v>
       </c>
       <c r="Q132" s="7" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="R132" s="7"/>
     </row>
@@ -10273,7 +10255,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="7" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>22</v>
@@ -10325,7 +10307,7 @@
         <v>24</v>
       </c>
       <c r="Q133" s="7" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="R133" s="7" t="s">
         <v>31</v>
@@ -10336,7 +10318,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>28</v>
@@ -10388,7 +10370,7 @@
         <v>24</v>
       </c>
       <c r="Q134" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R134" s="7" t="s">
         <v>31</v>
@@ -10399,7 +10381,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>22</v>
@@ -10451,7 +10433,7 @@
         <v>24</v>
       </c>
       <c r="Q135" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R135" s="7" t="s">
         <v>31</v>
@@ -10462,7 +10444,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="7" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C136" s="6" t="s">
         <v>22</v>
@@ -10514,7 +10496,7 @@
         <v>43</v>
       </c>
       <c r="Q136" s="7" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="R136" s="7"/>
     </row>
@@ -10523,7 +10505,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C137" s="6" t="s">
         <v>22</v>
@@ -10575,7 +10557,7 @@
         <v>43</v>
       </c>
       <c r="Q137" s="7" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="R137" s="7"/>
     </row>
@@ -10584,7 +10566,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C138" s="6" t="s">
         <v>22</v>
@@ -10636,7 +10618,7 @@
         <v>43</v>
       </c>
       <c r="Q138" s="7" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="R138" s="7"/>
     </row>
@@ -10645,7 +10627,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="7" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C139" s="6" t="s">
         <v>28</v>
@@ -10697,7 +10679,7 @@
         <v>24</v>
       </c>
       <c r="Q139" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R139" s="7" t="s">
         <v>31</v>
@@ -10708,7 +10690,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="7" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C140" s="6" t="s">
         <v>22</v>
@@ -10760,10 +10742,10 @@
         <v>24</v>
       </c>
       <c r="Q140" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R140" s="7" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10771,7 +10753,7 @@
         <v>142</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C141" s="6" t="s">
         <v>22</v>
@@ -10783,7 +10765,7 @@
         <v>7150</v>
       </c>
       <c r="F141" s="7" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="G141" s="9" t="n">
         <v>5000</v>
@@ -10823,7 +10805,7 @@
         <v>24</v>
       </c>
       <c r="Q141" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R141" s="7" t="s">
         <v>31</v>
@@ -10834,7 +10816,7 @@
         <v>143</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C142" s="6" t="s">
         <v>22</v>
@@ -10846,7 +10828,7 @@
         <v>7150</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="G142" s="9" t="n">
         <v>5000</v>
@@ -10886,7 +10868,7 @@
         <v>24</v>
       </c>
       <c r="Q142" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R142" s="7" t="s">
         <v>31</v>
@@ -10897,7 +10879,7 @@
         <v>144</v>
       </c>
       <c r="B143" s="7" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C143" s="6" t="s">
         <v>22</v>
@@ -10909,7 +10891,7 @@
         <v>8450</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="G143" s="9" t="n">
         <v>6000</v>
@@ -10949,7 +10931,7 @@
         <v>24</v>
       </c>
       <c r="Q143" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R143" s="7" t="s">
         <v>31</v>
@@ -10960,7 +10942,7 @@
         <v>145</v>
       </c>
       <c r="B144" s="7" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C144" s="6" t="s">
         <v>28</v>
@@ -10972,7 +10954,7 @@
         <v>104</v>
       </c>
       <c r="F144" s="7" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G144" s="9" t="n">
         <v>50</v>
@@ -11012,7 +10994,7 @@
         <v>24</v>
       </c>
       <c r="Q144" s="7" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="R144" s="7" t="s">
         <v>31</v>
@@ -11023,7 +11005,7 @@
         <v>146</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C145" s="6" t="s">
         <v>22</v>
@@ -11035,7 +11017,7 @@
         <v>105788</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="G145" s="9" t="n">
         <v>82000</v>
@@ -11075,7 +11057,7 @@
         <v>43</v>
       </c>
       <c r="Q145" s="7" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="R145" s="7"/>
     </row>
@@ -11084,7 +11066,7 @@
         <v>147</v>
       </c>
       <c r="B146" s="7" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C146" s="6" t="s">
         <v>22</v>
@@ -11096,7 +11078,7 @@
         <v>245700</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="G146" s="9" t="n">
         <v>225000</v>
@@ -11136,7 +11118,7 @@
         <v>43</v>
       </c>
       <c r="Q146" s="7" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="R146" s="7"/>
     </row>
@@ -11145,7 +11127,7 @@
         <v>148</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C147" s="6" t="s">
         <v>28</v>
@@ -11197,10 +11179,10 @@
         <v>24</v>
       </c>
       <c r="Q147" s="7" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="R147" s="7" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11208,7 +11190,7 @@
         <v>149</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C148" s="6" t="s">
         <v>22</v>
@@ -11220,7 +11202,7 @@
         <v>1754</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="G148" s="9" t="n">
         <v>1380</v>
@@ -11260,7 +11242,7 @@
         <v>43</v>
       </c>
       <c r="Q148" s="7" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="R148" s="7"/>
     </row>
@@ -11269,7 +11251,7 @@
         <v>150</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C149" s="6" t="s">
         <v>22</v>
@@ -11321,7 +11303,7 @@
         <v>43</v>
       </c>
       <c r="Q149" s="7" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="R149" s="7"/>
     </row>
@@ -11330,7 +11312,7 @@
         <v>151</v>
       </c>
       <c r="B150" s="7" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C150" s="6" t="s">
         <v>22</v>
@@ -11382,7 +11364,7 @@
         <v>43</v>
       </c>
       <c r="Q150" s="7" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="R150" s="7"/>
     </row>
@@ -11391,7 +11373,7 @@
         <v>152</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C151" s="6" t="s">
         <v>22</v>
@@ -11443,7 +11425,7 @@
         <v>43</v>
       </c>
       <c r="Q151" s="7" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="R151" s="7"/>
     </row>
@@ -11452,7 +11434,7 @@
         <v>153</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C152" s="6" t="s">
         <v>22</v>
@@ -11504,7 +11486,7 @@
         <v>43</v>
       </c>
       <c r="Q152" s="7" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="R152" s="7"/>
     </row>
@@ -11513,7 +11495,7 @@
         <v>154</v>
       </c>
       <c r="B153" s="7" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C153" s="6" t="s">
         <v>22</v>
@@ -11565,7 +11547,7 @@
         <v>24</v>
       </c>
       <c r="Q153" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R153" s="7" t="s">
         <v>31</v>
@@ -11576,7 +11558,7 @@
         <v>155</v>
       </c>
       <c r="B154" s="7" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C154" s="6" t="s">
         <v>22</v>
@@ -11588,7 +11570,7 @@
         <v>748</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G154" s="9" t="n">
         <v>450</v>
@@ -11628,7 +11610,7 @@
         <v>43</v>
       </c>
       <c r="Q154" s="7" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="R154" s="7"/>
     </row>
@@ -11637,7 +11619,7 @@
         <v>156</v>
       </c>
       <c r="B155" s="7" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>22</v>
@@ -11649,7 +11631,7 @@
         <v>748</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G155" s="9" t="n">
         <v>450</v>
@@ -11689,7 +11671,7 @@
         <v>43</v>
       </c>
       <c r="Q155" s="7" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="R155" s="7"/>
     </row>
@@ -11698,7 +11680,7 @@
         <v>157</v>
       </c>
       <c r="B156" s="7" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C156" s="6" t="s">
         <v>22</v>
@@ -11710,7 +11692,7 @@
         <v>748</v>
       </c>
       <c r="F156" s="7" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="G156" s="9" t="n">
         <v>400</v>
@@ -11750,7 +11732,7 @@
         <v>43</v>
       </c>
       <c r="Q156" s="7" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="R156" s="7"/>
     </row>
@@ -11759,7 +11741,7 @@
         <v>158</v>
       </c>
       <c r="B157" s="7" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C157" s="6" t="s">
         <v>28</v>
@@ -11771,7 +11753,7 @@
         <v>311</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G157" s="9" t="n">
         <v>150</v>
@@ -11811,7 +11793,7 @@
         <v>24</v>
       </c>
       <c r="Q157" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R157" s="7" t="s">
         <v>31</v>
@@ -11822,7 +11804,7 @@
         <v>159</v>
       </c>
       <c r="B158" s="7" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C158" s="6" t="s">
         <v>28</v>
@@ -11834,7 +11816,7 @@
         <v>325</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G158" s="9" t="n">
         <v>180</v>
@@ -11874,7 +11856,7 @@
         <v>24</v>
       </c>
       <c r="Q158" s="7" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="R158" s="7" t="s">
         <v>31</v>
@@ -11885,7 +11867,7 @@
         <v>160</v>
       </c>
       <c r="B159" s="7" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C159" s="6" t="s">
         <v>28</v>
@@ -11897,7 +11879,7 @@
         <v>117</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="G159" s="9" t="n">
         <v>60</v>
@@ -11937,7 +11919,7 @@
         <v>24</v>
       </c>
       <c r="Q159" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R159" s="7" t="s">
         <v>31</v>
@@ -11948,7 +11930,7 @@
         <v>161</v>
       </c>
       <c r="B160" s="7" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C160" s="6" t="s">
         <v>28</v>
@@ -11960,7 +11942,7 @@
         <v>169</v>
       </c>
       <c r="F160" s="7" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="G160" s="9" t="n">
         <v>90</v>
@@ -12000,7 +11982,7 @@
         <v>24</v>
       </c>
       <c r="Q160" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R160" s="7" t="s">
         <v>31</v>
@@ -12011,7 +11993,7 @@
         <v>162</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="C161" s="6" t="s">
         <v>28</v>
@@ -12023,7 +12005,7 @@
         <v>234</v>
       </c>
       <c r="F161" s="7" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="G161" s="9" t="n">
         <v>120</v>
@@ -12063,7 +12045,7 @@
         <v>24</v>
       </c>
       <c r="Q161" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R161" s="7" t="s">
         <v>31</v>
@@ -12074,7 +12056,7 @@
         <v>164</v>
       </c>
       <c r="B162" s="7" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C162" s="6" t="s">
         <v>22</v>
@@ -12086,7 +12068,7 @@
         <v>1209</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="G162" s="9" t="n">
         <v>1450</v>
@@ -12123,13 +12105,13 @@
         <v>YES</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>231</v>
+        <v>51</v>
       </c>
       <c r="Q162" s="7" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="R162" s="7" t="s">
-        <v>233</v>
+        <v>53</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12137,7 +12119,7 @@
         <v>165</v>
       </c>
       <c r="B163" s="7" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="C163" s="6" t="s">
         <v>22</v>
@@ -12149,7 +12131,7 @@
         <v>1209</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="G163" s="9" t="n">
         <v>2248</v>
@@ -12186,13 +12168,13 @@
         <v>YES</v>
       </c>
       <c r="P163" s="6" t="s">
-        <v>231</v>
+        <v>51</v>
       </c>
       <c r="Q163" s="7" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="R163" s="7" t="s">
-        <v>233</v>
+        <v>53</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12200,7 +12182,7 @@
         <v>166</v>
       </c>
       <c r="B164" s="7" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="C164" s="6" t="s">
         <v>22</v>
@@ -12212,7 +12194,7 @@
         <v>3022</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="G164" s="9" t="n">
         <v>2325</v>
@@ -12249,13 +12231,13 @@
         <v>YES</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>231</v>
+        <v>51</v>
       </c>
       <c r="Q164" s="7" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="R164" s="7" t="s">
-        <v>233</v>
+        <v>53</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12263,7 +12245,7 @@
         <v>167</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C165" s="6" t="s">
         <v>22</v>
@@ -12315,10 +12297,10 @@
         <v>24</v>
       </c>
       <c r="Q165" s="7" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="R165" s="7" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12326,7 +12308,7 @@
         <v>168</v>
       </c>
       <c r="B166" s="7" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C166" s="6" t="s">
         <v>22</v>
@@ -12378,10 +12360,10 @@
         <v>24</v>
       </c>
       <c r="Q166" s="7" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="R166" s="7" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12389,7 +12371,7 @@
         <v>177</v>
       </c>
       <c r="B167" s="7" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C167" s="6" t="s">
         <v>28</v>
@@ -12401,7 +12383,7 @@
         <v>5850</v>
       </c>
       <c r="F167" s="7" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="G167" s="9" t="n">
         <v>3500</v>
@@ -12441,10 +12423,10 @@
         <v>24</v>
       </c>
       <c r="Q167" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R167" s="7" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12452,7 +12434,7 @@
         <v>179</v>
       </c>
       <c r="B168" s="7" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C168" s="6" t="s">
         <v>28</v>
@@ -12464,7 +12446,7 @@
         <v>23400</v>
       </c>
       <c r="F168" s="7" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="G168" s="9" t="n">
         <v>20000</v>
@@ -12504,7 +12486,7 @@
         <v>24</v>
       </c>
       <c r="Q168" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R168" s="7" t="s">
         <v>31</v>
@@ -12515,7 +12497,7 @@
         <v>180</v>
       </c>
       <c r="B169" s="7" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="C169" s="6" t="s">
         <v>28</v>
@@ -12527,7 +12509,7 @@
         <v>15600</v>
       </c>
       <c r="F169" s="7" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="G169" s="9" t="n">
         <v>14000</v>
@@ -12567,7 +12549,7 @@
         <v>24</v>
       </c>
       <c r="Q169" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R169" s="7" t="s">
         <v>31</v>
@@ -12578,7 +12560,7 @@
         <v>181</v>
       </c>
       <c r="B170" s="7" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C170" s="6" t="s">
         <v>28</v>
@@ -12590,7 +12572,7 @@
         <v>33800</v>
       </c>
       <c r="F170" s="7" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="G170" s="9" t="n">
         <v>28000</v>
@@ -12630,7 +12612,7 @@
         <v>24</v>
       </c>
       <c r="Q170" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R170" s="7" t="s">
         <v>31</v>
@@ -12641,7 +12623,7 @@
         <v>182</v>
       </c>
       <c r="B171" s="7" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C171" s="6" t="s">
         <v>28</v>
@@ -12653,7 +12635,7 @@
         <v>23400</v>
       </c>
       <c r="F171" s="7" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="G171" s="9" t="n">
         <v>20000</v>
@@ -12693,7 +12675,7 @@
         <v>24</v>
       </c>
       <c r="Q171" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R171" s="7" t="s">
         <v>31</v>
@@ -12704,7 +12686,7 @@
         <v>183</v>
       </c>
       <c r="B172" s="7" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C172" s="6" t="s">
         <v>28</v>
@@ -12716,7 +12698,7 @@
         <v>2860</v>
       </c>
       <c r="F172" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G172" s="9" t="n">
         <v>1800</v>
@@ -12756,7 +12738,7 @@
         <v>24</v>
       </c>
       <c r="Q172" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R172" s="7" t="s">
         <v>31</v>
@@ -12767,7 +12749,7 @@
         <v>184</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C173" s="6" t="s">
         <v>28</v>
@@ -12779,7 +12761,7 @@
         <v>3250</v>
       </c>
       <c r="F173" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G173" s="9" t="n">
         <v>2100</v>
@@ -12819,7 +12801,7 @@
         <v>24</v>
       </c>
       <c r="Q173" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R173" s="7" t="s">
         <v>31</v>
@@ -12830,7 +12812,7 @@
         <v>185</v>
       </c>
       <c r="B174" s="7" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C174" s="6" t="s">
         <v>28</v>
@@ -12842,7 +12824,7 @@
         <v>3900</v>
       </c>
       <c r="F174" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G174" s="9" t="n">
         <v>2600</v>
@@ -12882,7 +12864,7 @@
         <v>24</v>
       </c>
       <c r="Q174" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R174" s="7" t="s">
         <v>31</v>
@@ -12893,7 +12875,7 @@
         <v>186</v>
       </c>
       <c r="B175" s="7" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C175" s="6" t="s">
         <v>28</v>
@@ -12905,7 +12887,7 @@
         <v>4550</v>
       </c>
       <c r="F175" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G175" s="9" t="n">
         <v>3300</v>
@@ -12945,7 +12927,7 @@
         <v>24</v>
       </c>
       <c r="Q175" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R175" s="7" t="s">
         <v>31</v>
@@ -12956,7 +12938,7 @@
         <v>187</v>
       </c>
       <c r="B176" s="7" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C176" s="6" t="s">
         <v>28</v>
@@ -12968,7 +12950,7 @@
         <v>7150</v>
       </c>
       <c r="F176" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G176" s="9" t="n">
         <v>5500</v>
@@ -13008,7 +12990,7 @@
         <v>24</v>
       </c>
       <c r="Q176" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R176" s="7" t="s">
         <v>31</v>
@@ -13019,7 +13001,7 @@
         <v>188</v>
       </c>
       <c r="B177" s="7" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="C177" s="6" t="s">
         <v>28</v>
@@ -13031,7 +13013,7 @@
         <v>8450</v>
       </c>
       <c r="F177" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G177" s="9" t="n">
         <v>7000</v>
@@ -13071,7 +13053,7 @@
         <v>24</v>
       </c>
       <c r="Q177" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R177" s="7" t="s">
         <v>31</v>
@@ -13082,7 +13064,7 @@
         <v>189</v>
       </c>
       <c r="B178" s="7" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C178" s="6" t="s">
         <v>28</v>
@@ -13094,7 +13076,7 @@
         <v>9750</v>
       </c>
       <c r="F178" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G178" s="9" t="n">
         <v>8500</v>
@@ -13134,7 +13116,7 @@
         <v>24</v>
       </c>
       <c r="Q178" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R178" s="7" t="s">
         <v>31</v>
@@ -13145,7 +13127,7 @@
         <v>190</v>
       </c>
       <c r="B179" s="7" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C179" s="6" t="s">
         <v>28</v>
@@ -13157,7 +13139,7 @@
         <v>2340</v>
       </c>
       <c r="F179" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G179" s="9" t="n">
         <v>1500</v>
@@ -13197,7 +13179,7 @@
         <v>24</v>
       </c>
       <c r="Q179" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R179" s="7" t="s">
         <v>31</v>
@@ -13208,7 +13190,7 @@
         <v>191</v>
       </c>
       <c r="B180" s="7" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C180" s="6" t="s">
         <v>28</v>
@@ -13220,7 +13202,7 @@
         <v>3640</v>
       </c>
       <c r="F180" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G180" s="9" t="n">
         <v>2300</v>
@@ -13260,7 +13242,7 @@
         <v>24</v>
       </c>
       <c r="Q180" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R180" s="7" t="s">
         <v>31</v>
@@ -13271,7 +13253,7 @@
         <v>192</v>
       </c>
       <c r="B181" s="7" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C181" s="6" t="s">
         <v>28</v>
@@ -13323,7 +13305,7 @@
         <v>24</v>
       </c>
       <c r="Q181" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R181" s="7" t="s">
         <v>31</v>
@@ -13334,7 +13316,7 @@
         <v>193</v>
       </c>
       <c r="B182" s="7" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C182" s="6" t="s">
         <v>28</v>
@@ -13386,7 +13368,7 @@
         <v>24</v>
       </c>
       <c r="Q182" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R182" s="7" t="s">
         <v>31</v>
@@ -13397,7 +13379,7 @@
         <v>194</v>
       </c>
       <c r="B183" s="7" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C183" s="6" t="s">
         <v>28</v>
@@ -13449,7 +13431,7 @@
         <v>24</v>
       </c>
       <c r="Q183" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R183" s="7" t="s">
         <v>31</v>
@@ -13460,7 +13442,7 @@
         <v>195</v>
       </c>
       <c r="B184" s="7" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C184" s="6" t="s">
         <v>28</v>
@@ -13512,7 +13494,7 @@
         <v>24</v>
       </c>
       <c r="Q184" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R184" s="7" t="s">
         <v>31</v>
@@ -13523,7 +13505,7 @@
         <v>196</v>
       </c>
       <c r="B185" s="7" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C185" s="6" t="s">
         <v>28</v>
@@ -13535,7 +13517,7 @@
         <v>4550</v>
       </c>
       <c r="F185" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G185" s="9" t="n">
         <v>3500</v>
@@ -13575,7 +13557,7 @@
         <v>24</v>
       </c>
       <c r="Q185" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R185" s="7" t="s">
         <v>31</v>
@@ -13586,7 +13568,7 @@
         <v>197</v>
       </c>
       <c r="B186" s="7" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C186" s="6" t="s">
         <v>28</v>
@@ -13598,7 +13580,7 @@
         <v>17940</v>
       </c>
       <c r="F186" s="7" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G186" s="9" t="n">
         <v>5500</v>
@@ -13638,7 +13620,7 @@
         <v>43</v>
       </c>
       <c r="Q186" s="7" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="R186" s="7"/>
     </row>
@@ -13647,7 +13629,7 @@
         <v>198</v>
       </c>
       <c r="B187" s="7" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C187" s="6" t="s">
         <v>28</v>
@@ -13659,7 +13641,7 @@
         <v>18850</v>
       </c>
       <c r="F187" s="7" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G187" s="9" t="n">
         <v>5500</v>
@@ -13699,7 +13681,7 @@
         <v>43</v>
       </c>
       <c r="Q187" s="7" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="R187" s="7"/>
     </row>
@@ -13708,7 +13690,7 @@
         <v>199</v>
       </c>
       <c r="B188" s="7" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C188" s="6" t="s">
         <v>28</v>
@@ -13720,7 +13702,7 @@
         <v>19500</v>
       </c>
       <c r="F188" s="7" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G188" s="9" t="n">
         <v>6200</v>
@@ -13760,7 +13742,7 @@
         <v>43</v>
       </c>
       <c r="Q188" s="7" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="R188" s="7"/>
     </row>
@@ -13769,7 +13751,7 @@
         <v>200</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="C189" s="6" t="s">
         <v>28</v>
@@ -13781,7 +13763,7 @@
         <v>20800</v>
       </c>
       <c r="F189" s="7" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G189" s="9" t="n">
         <v>6875</v>
@@ -13821,7 +13803,7 @@
         <v>43</v>
       </c>
       <c r="Q189" s="7" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="R189" s="7"/>
     </row>
@@ -13830,7 +13812,7 @@
         <v>201</v>
       </c>
       <c r="B190" s="7" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C190" s="6" t="s">
         <v>28</v>
@@ -13842,7 +13824,7 @@
         <v>22750</v>
       </c>
       <c r="F190" s="7" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G190" s="9" t="n">
         <v>8750</v>
@@ -13882,7 +13864,7 @@
         <v>43</v>
       </c>
       <c r="Q190" s="7" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="R190" s="7"/>
     </row>
@@ -13891,7 +13873,7 @@
         <v>202</v>
       </c>
       <c r="B191" s="7" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="C191" s="6" t="s">
         <v>28</v>
@@ -13903,7 +13885,7 @@
         <v>2340</v>
       </c>
       <c r="F191" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G191" s="9" t="n">
         <v>1500</v>
@@ -13943,7 +13925,7 @@
         <v>24</v>
       </c>
       <c r="Q191" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R191" s="7" t="s">
         <v>31</v>
@@ -13954,7 +13936,7 @@
         <v>204</v>
       </c>
       <c r="B192" s="7" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="C192" s="6" t="s">
         <v>28</v>
@@ -13966,7 +13948,7 @@
         <v>845</v>
       </c>
       <c r="F192" s="7" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="G192" s="9" t="n">
         <v>5480</v>
@@ -14006,7 +13988,7 @@
         <v>24</v>
       </c>
       <c r="Q192" s="7" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="R192" s="7" t="s">
         <v>31</v>
@@ -14017,7 +13999,7 @@
         <v>205</v>
       </c>
       <c r="B193" s="7" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C193" s="6" t="s">
         <v>28</v>
@@ -14029,7 +14011,7 @@
         <v>910</v>
       </c>
       <c r="F193" s="7" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="G193" s="9" t="n">
         <v>5960</v>
@@ -14069,7 +14051,7 @@
         <v>24</v>
       </c>
       <c r="Q193" s="7" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="R193" s="7" t="s">
         <v>31</v>
@@ -14080,7 +14062,7 @@
         <v>206</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C194" s="6" t="s">
         <v>28</v>
@@ -14092,7 +14074,7 @@
         <v>1170</v>
       </c>
       <c r="F194" s="7" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="G194" s="9" t="n">
         <v>6930</v>
@@ -14132,7 +14114,7 @@
         <v>24</v>
       </c>
       <c r="Q194" s="7" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="R194" s="7" t="s">
         <v>31</v>
@@ -14143,7 +14125,7 @@
         <v>207</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="C195" s="6" t="s">
         <v>28</v>
@@ -14155,7 +14137,7 @@
         <v>1430</v>
       </c>
       <c r="F195" s="7" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="G195" s="9" t="n">
         <v>8960</v>
@@ -14195,7 +14177,7 @@
         <v>24</v>
       </c>
       <c r="Q195" s="7" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="R195" s="7" t="s">
         <v>31</v>
@@ -14206,7 +14188,7 @@
         <v>208</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C196" s="6" t="s">
         <v>28</v>
@@ -14218,7 +14200,7 @@
         <v>1690</v>
       </c>
       <c r="F196" s="7" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="G196" s="9" t="n">
         <v>11050</v>
@@ -14258,7 +14240,7 @@
         <v>24</v>
       </c>
       <c r="Q196" s="7" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="R196" s="7" t="s">
         <v>31</v>
@@ -14269,7 +14251,7 @@
         <v>209</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C197" s="6" t="s">
         <v>28</v>
@@ -14281,7 +14263,7 @@
         <v>2340</v>
       </c>
       <c r="F197" s="7" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="G197" s="9" t="n">
         <v>15380</v>
@@ -14321,7 +14303,7 @@
         <v>24</v>
       </c>
       <c r="Q197" s="7" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="R197" s="7" t="s">
         <v>31</v>
@@ -14332,7 +14314,7 @@
         <v>210</v>
       </c>
       <c r="B198" s="7" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C198" s="6" t="s">
         <v>28</v>
@@ -14344,7 +14326,7 @@
         <v>2860</v>
       </c>
       <c r="F198" s="7" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="G198" s="9" t="n">
         <v>17610</v>
@@ -14384,7 +14366,7 @@
         <v>24</v>
       </c>
       <c r="Q198" s="7" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="R198" s="7" t="s">
         <v>31</v>
@@ -14395,7 +14377,7 @@
         <v>211</v>
       </c>
       <c r="B199" s="7" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C199" s="6" t="s">
         <v>28</v>
@@ -14407,7 +14389,7 @@
         <v>4160</v>
       </c>
       <c r="F199" s="7" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="G199" s="9" t="n">
         <v>22180</v>
@@ -14447,7 +14429,7 @@
         <v>24</v>
       </c>
       <c r="Q199" s="7" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="R199" s="7" t="s">
         <v>31</v>
@@ -14458,7 +14440,7 @@
         <v>212</v>
       </c>
       <c r="B200" s="7" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C200" s="6" t="s">
         <v>28</v>
@@ -14470,7 +14452,7 @@
         <v>5460</v>
       </c>
       <c r="F200" s="7" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="G200" s="9" t="n">
         <v>25690</v>
@@ -14510,7 +14492,7 @@
         <v>24</v>
       </c>
       <c r="Q200" s="7" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="R200" s="7" t="s">
         <v>31</v>
@@ -14521,7 +14503,7 @@
         <v>213</v>
       </c>
       <c r="B201" s="7" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C201" s="6" t="s">
         <v>28</v>
@@ -14533,7 +14515,7 @@
         <v>455</v>
       </c>
       <c r="F201" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G201" s="9" t="n">
         <v>500</v>
@@ -14573,7 +14555,7 @@
         <v>24</v>
       </c>
       <c r="Q201" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R201" s="7" t="s">
         <v>31</v>
@@ -14584,7 +14566,7 @@
         <v>214</v>
       </c>
       <c r="B202" s="7" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C202" s="6" t="s">
         <v>28</v>
@@ -14596,7 +14578,7 @@
         <v>494</v>
       </c>
       <c r="F202" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G202" s="9" t="n">
         <v>550</v>
@@ -14636,7 +14618,7 @@
         <v>24</v>
       </c>
       <c r="Q202" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R202" s="7" t="s">
         <v>31</v>
@@ -14647,7 +14629,7 @@
         <v>215</v>
       </c>
       <c r="B203" s="7" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C203" s="6" t="s">
         <v>28</v>
@@ -14659,7 +14641,7 @@
         <v>585</v>
       </c>
       <c r="F203" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G203" s="9" t="n">
         <v>650</v>
@@ -14699,7 +14681,7 @@
         <v>24</v>
       </c>
       <c r="Q203" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R203" s="7" t="s">
         <v>31</v>
@@ -14710,7 +14692,7 @@
         <v>216</v>
       </c>
       <c r="B204" s="7" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C204" s="6" t="s">
         <v>28</v>
@@ -14722,7 +14704,7 @@
         <v>715</v>
       </c>
       <c r="F204" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G204" s="9" t="n">
         <v>800</v>
@@ -14762,7 +14744,7 @@
         <v>24</v>
       </c>
       <c r="Q204" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R204" s="7" t="s">
         <v>31</v>
@@ -14773,7 +14755,7 @@
         <v>217</v>
       </c>
       <c r="B205" s="7" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C205" s="6" t="s">
         <v>28</v>
@@ -14785,7 +14767,7 @@
         <v>910</v>
       </c>
       <c r="F205" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G205" s="9" t="n">
         <v>1000</v>
@@ -14825,7 +14807,7 @@
         <v>24</v>
       </c>
       <c r="Q205" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R205" s="7" t="s">
         <v>31</v>
@@ -14836,7 +14818,7 @@
         <v>218</v>
       </c>
       <c r="B206" s="7" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="C206" s="6" t="s">
         <v>28</v>
@@ -14848,7 +14830,7 @@
         <v>1170</v>
       </c>
       <c r="F206" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G206" s="9" t="n">
         <v>1400</v>
@@ -14888,7 +14870,7 @@
         <v>24</v>
       </c>
       <c r="Q206" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R206" s="7" t="s">
         <v>31</v>
@@ -14899,7 +14881,7 @@
         <v>219</v>
       </c>
       <c r="B207" s="7" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C207" s="6" t="s">
         <v>28</v>
@@ -14911,7 +14893,7 @@
         <v>1040</v>
       </c>
       <c r="F207" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G207" s="9" t="n">
         <v>1100</v>
@@ -14951,7 +14933,7 @@
         <v>24</v>
       </c>
       <c r="Q207" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R207" s="7" t="s">
         <v>31</v>
@@ -14962,7 +14944,7 @@
         <v>220</v>
       </c>
       <c r="B208" s="7" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="C208" s="6" t="s">
         <v>28</v>
@@ -14974,7 +14956,7 @@
         <v>1430</v>
       </c>
       <c r="F208" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G208" s="9" t="n">
         <v>1400</v>
@@ -15014,7 +14996,7 @@
         <v>24</v>
       </c>
       <c r="Q208" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R208" s="7" t="s">
         <v>31</v>
@@ -15025,7 +15007,7 @@
         <v>221</v>
       </c>
       <c r="B209" s="7" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C209" s="6" t="s">
         <v>28</v>
@@ -15037,7 +15019,7 @@
         <v>1950</v>
       </c>
       <c r="F209" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G209" s="9" t="n">
         <v>2000</v>
@@ -15077,7 +15059,7 @@
         <v>24</v>
       </c>
       <c r="Q209" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R209" s="7" t="s">
         <v>31</v>
@@ -15088,7 +15070,7 @@
         <v>222</v>
       </c>
       <c r="B210" s="7" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C210" s="6" t="s">
         <v>28</v>
@@ -15100,7 +15082,7 @@
         <v>15600</v>
       </c>
       <c r="F210" s="7" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="G210" s="9" t="n">
         <v>18000</v>
@@ -15140,7 +15122,7 @@
         <v>24</v>
       </c>
       <c r="Q210" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R210" s="7" t="s">
         <v>31</v>
@@ -15151,7 +15133,7 @@
         <v>223</v>
       </c>
       <c r="B211" s="7" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C211" s="6" t="s">
         <v>28</v>
@@ -15163,7 +15145,7 @@
         <v>30940</v>
       </c>
       <c r="F211" s="7" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="G211" s="9" t="n">
         <v>45000</v>
@@ -15203,10 +15185,10 @@
         <v>24</v>
       </c>
       <c r="Q211" s="7" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="R211" s="7" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15214,7 +15196,7 @@
         <v>224</v>
       </c>
       <c r="B212" s="7" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="C212" s="6" t="s">
         <v>28</v>
@@ -15226,7 +15208,7 @@
         <v>54600</v>
       </c>
       <c r="F212" s="7" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="G212" s="9" t="n">
         <v>85000</v>
@@ -15266,10 +15248,10 @@
         <v>24</v>
       </c>
       <c r="Q212" s="7" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="R212" s="7" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15277,7 +15259,7 @@
         <v>225</v>
       </c>
       <c r="B213" s="7" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="C213" s="6" t="s">
         <v>28</v>
@@ -15289,7 +15271,7 @@
         <v>1170</v>
       </c>
       <c r="F213" s="7" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="G213" s="9" t="n">
         <v>1800</v>
@@ -15329,7 +15311,7 @@
         <v>24</v>
       </c>
       <c r="Q213" s="7" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="R213" s="7" t="s">
         <v>31</v>
@@ -15340,7 +15322,7 @@
         <v>226</v>
       </c>
       <c r="B214" s="7" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="C214" s="6" t="s">
         <v>28</v>
@@ -15352,7 +15334,7 @@
         <v>1430</v>
       </c>
       <c r="F214" s="7" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="G214" s="9" t="n">
         <v>2600</v>
@@ -15392,7 +15374,7 @@
         <v>24</v>
       </c>
       <c r="Q214" s="7" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="R214" s="7" t="s">
         <v>31</v>
@@ -15403,7 +15385,7 @@
         <v>227</v>
       </c>
       <c r="B215" s="7" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C215" s="6" t="s">
         <v>28</v>
@@ -15415,7 +15397,7 @@
         <v>1820</v>
       </c>
       <c r="F215" s="7" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="G215" s="9" t="n">
         <v>3500</v>
@@ -15455,7 +15437,7 @@
         <v>24</v>
       </c>
       <c r="Q215" s="7" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="R215" s="7" t="s">
         <v>31</v>
@@ -15466,7 +15448,7 @@
         <v>228</v>
       </c>
       <c r="B216" s="7" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C216" s="6" t="s">
         <v>28</v>
@@ -15478,7 +15460,7 @@
         <v>2860</v>
       </c>
       <c r="F216" s="7" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="G216" s="9" t="n">
         <v>6000</v>
@@ -15518,7 +15500,7 @@
         <v>24</v>
       </c>
       <c r="Q216" s="7" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="R216" s="7" t="s">
         <v>31</v>
@@ -15529,7 +15511,7 @@
         <v>229</v>
       </c>
       <c r="B217" s="7" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C217" s="6" t="s">
         <v>28</v>
@@ -15541,7 +15523,7 @@
         <v>2340</v>
       </c>
       <c r="F217" s="7" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="G217" s="9" t="n">
         <v>3200</v>
@@ -15581,7 +15563,7 @@
         <v>24</v>
       </c>
       <c r="Q217" s="7" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="R217" s="7" t="s">
         <v>31</v>
@@ -15592,7 +15574,7 @@
         <v>230</v>
       </c>
       <c r="B218" s="7" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C218" s="6" t="s">
         <v>28</v>
@@ -15604,7 +15586,7 @@
         <v>9750</v>
       </c>
       <c r="F218" s="7" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="G218" s="9" t="n">
         <v>6000</v>
@@ -15644,10 +15626,10 @@
         <v>24</v>
       </c>
       <c r="Q218" s="7" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="R218" s="7" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15655,7 +15637,7 @@
         <v>231</v>
       </c>
       <c r="B219" s="7" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C219" s="6" t="s">
         <v>28</v>
@@ -15667,7 +15649,7 @@
         <v>12350</v>
       </c>
       <c r="F219" s="7" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="G219" s="9" t="n">
         <v>8000</v>
@@ -15707,10 +15689,10 @@
         <v>24</v>
       </c>
       <c r="Q219" s="7" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="R219" s="7" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15718,10 +15700,10 @@
         <v>233</v>
       </c>
       <c r="B220" s="7" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="C220" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D220" s="6" t="n">
         <v>2</v>
@@ -15730,7 +15712,7 @@
         <v>52000</v>
       </c>
       <c r="F220" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G220" s="9" t="n">
         <v>40000</v>
@@ -15770,7 +15752,7 @@
         <v>43</v>
       </c>
       <c r="Q220" s="7" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="R220" s="7"/>
     </row>
@@ -15779,7 +15761,7 @@
         <v>234</v>
       </c>
       <c r="B221" s="7" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="C221" s="6" t="s">
         <v>22</v>
@@ -15828,13 +15810,13 @@
         <v>YES</v>
       </c>
       <c r="P221" s="6" t="s">
-        <v>231</v>
+        <v>51</v>
       </c>
       <c r="Q221" s="7" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="R221" s="7" t="s">
-        <v>233</v>
+        <v>53</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15842,7 +15824,7 @@
         <v>235</v>
       </c>
       <c r="B222" s="7" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C222" s="6" t="s">
         <v>28</v>
@@ -15894,10 +15876,10 @@
         <v>24</v>
       </c>
       <c r="Q222" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R222" s="7" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15905,7 +15887,7 @@
         <v>236</v>
       </c>
       <c r="B223" s="7" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="C223" s="6" t="s">
         <v>22</v>
@@ -15917,7 +15899,7 @@
         <v>2860</v>
       </c>
       <c r="F223" s="7" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="G223" s="9" t="n">
         <v>2400</v>
@@ -15957,10 +15939,10 @@
         <v>24</v>
       </c>
       <c r="Q223" s="7" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="R223" s="7" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15968,7 +15950,7 @@
         <v>237</v>
       </c>
       <c r="B224" s="7" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C224" s="6" t="s">
         <v>28</v>
@@ -16020,7 +16002,7 @@
         <v>24</v>
       </c>
       <c r="Q224" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R224" s="7" t="s">
         <v>31</v>
@@ -16031,7 +16013,7 @@
         <v>238</v>
       </c>
       <c r="B225" s="7" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C225" s="6" t="s">
         <v>28</v>
@@ -16043,7 +16025,7 @@
         <v>8450</v>
       </c>
       <c r="F225" s="7" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="G225" s="9" t="n">
         <v>7800</v>
@@ -16083,7 +16065,7 @@
         <v>43</v>
       </c>
       <c r="Q225" s="7" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="R225" s="7"/>
     </row>
@@ -16092,10 +16074,10 @@
         <v>239</v>
       </c>
       <c r="B226" s="7" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D226" s="6" t="n">
         <v>50</v>
@@ -16104,7 +16086,7 @@
         <v>65000</v>
       </c>
       <c r="F226" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G226" s="9" t="n">
         <v>44000</v>
@@ -16144,7 +16126,7 @@
         <v>43</v>
       </c>
       <c r="Q226" s="7" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="R226" s="7"/>
     </row>
@@ -16153,7 +16135,7 @@
         <v>240</v>
       </c>
       <c r="B227" s="7" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="C227" s="6" t="s">
         <v>28</v>
@@ -16205,15 +16187,15 @@
         <v>24</v>
       </c>
       <c r="Q227" s="7" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="R227" s="7" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B228" s="3" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="L228" s="11" t="n">
         <f aca="false">SUM(L6:L227)</f>
@@ -16221,11 +16203,11 @@
       </c>
       <c r="M228" s="11" t="n">
         <f aca="false">SUM(M6:M227)</f>
-        <v>15308570</v>
+        <v>15544820</v>
       </c>
       <c r="N228" s="11" t="n">
         <f aca="false">SUM(N6:N227)</f>
-        <v>12371727</v>
+        <v>12585567</v>
       </c>
     </row>
   </sheetData>
@@ -16274,12 +16256,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="B3" s="11" t="n">
         <f aca="false">COUNTA('Rate Check'!A6:A227)</f>
@@ -16288,25 +16270,25 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B4" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"LOSS")</f>
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B5" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"THIN / RISK")</f>
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B6" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"OK")</f>
@@ -16315,7 +16297,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="B7" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"OVERPRICED?")</f>
@@ -16324,7 +16306,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="B8" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!O6:O227,"YES")</f>
@@ -16336,7 +16318,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="B10" s="11" t="n">
         <f aca="false">'Rate Check'!L228</f>
@@ -16345,38 +16327,38 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B11" s="11" t="n">
         <f aca="false">'Rate Check'!N228</f>
-        <v>12371727</v>
+        <v>12585567</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="B12" s="11" t="n">
         <f aca="false">B10-B11</f>
-        <v>-162219</v>
+        <v>-376059</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="B13" s="14" t="n">
         <f aca="false">IF(B10=0,0,B12/B10)</f>
-        <v>-0.0132862847544717</v>
+        <v>-0.0308005040006526</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="B14" s="11" t="n">
         <f aca="false">SUMPRODUCT(('Rate Check'!E6:E227&lt;'Rate Check'!H6:H227)*('Rate Check'!H6:H227-'Rate Check'!E6:E227)*'Rate Check'!D6:D227)</f>
-        <v>2550050</v>
+        <v>2755490</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16384,20 +16366,20 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="B16" s="11" t="n">
         <f aca="false">'Rate Check'!M228</f>
-        <v>15308570</v>
+        <v>15544820</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="B17" s="14" t="n">
         <f aca="false">IF(B16=0,0,(B16-B11)/B16)</f>
-        <v>0.19184306568151</v>
+        <v>0.190369074714278</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16405,29 +16387,29 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="B19" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!P6:P227,"V")</f>
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B20" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!P6:P227,"S")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B21" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!P6:P227,"N")</f>
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -16455,247 +16437,247 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
     </row>
   </sheetData>

--- a/quotes/PR-217-228/Quote_PR217_PR228_Rate_Check.xlsx
+++ b/quotes/PR-217-228/Quote_PR217_PR228_Rate_Check.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1382" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1381" uniqueCount="527">
   <si>
     <t xml:space="preserve">Zidane Corporation - Quote PR-217 &amp; PR-228: Brand + Buying Rate Check</t>
   </si>
@@ -228,7 +228,7 @@
     <t xml:space="preserve">PIN PUNCH SET (06PCS SET)</t>
   </si>
   <si>
-    <t xml:space="preserve">toolsmart Licota 6pc pin punch 5,460</t>
+    <t xml:space="preserve">toolsmart.pk Licota 6pc pin punch 5,460; ktools.pk 6,000 (oos)</t>
   </si>
   <si>
     <t xml:space="preserve">HOLLOW PUNCH (3MM-25MM) (15PCS SET)</t>
@@ -249,10 +249,7 @@
     <t xml:space="preserve">SHORT TYPE HEX KEY WRENCH SET (09PCS)</t>
   </si>
   <si>
-    <t xml:space="preserve">toolsmart Licota hex sets (scaled)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Harden 1420</t>
+    <t xml:space="preserve">toolsmart.pk Licota 9pc short type hex key set 1.5-10mm Rs 3,540</t>
   </si>
   <si>
     <t xml:space="preserve">LONG TYPE HEX WRENCH SET 09 PCS</t>
@@ -372,10 +369,7 @@
     <t xml:space="preserve">VICE GRIP PLIER 08"</t>
   </si>
   <si>
-    <t xml:space="preserve">goldentools.ae Licota locking plier 10in AED 42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. 8in (alt 10in Harden toolsmart 1,660 / Ingco 1,790</t>
+    <t xml:space="preserve">toolsmart.pk Licota curved jaw locking plier 10in Rs 4,000 / 7in Rs 3,730 (8in n/a)</t>
   </si>
   <si>
     <t xml:space="preserve">CORDLESS IMPACT WRENCH 185NM (Bosch)</t>
@@ -3177,7 +3171,7 @@
       </c>
       <c r="R19" s="7"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="n">
         <v>15</v>
       </c>
@@ -3362,7 +3356,7 @@
       </c>
       <c r="R22" s="7"/>
     </row>
-    <row r="23" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="n">
         <v>18</v>
       </c>
@@ -3382,14 +3376,14 @@
         <v>28</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>2000</v>
+        <v>3540</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>3000</v>
+        <v>3540</v>
       </c>
       <c r="I23" s="10" t="n">
         <f aca="false">IF(E23=0,0,(E23-H23)/E23)</f>
-        <v>-0.625135427952329</v>
+        <v>-0.917659804983749</v>
       </c>
       <c r="J23" s="6" t="str">
         <f aca="false">IF(E23&lt;G23,"LOSS",IF(E23&lt;H23*1.1,"THIN / RISK",IF(E23&gt;H23*1.8,"OVERPRICED?","OK")))</f>
@@ -3397,7 +3391,7 @@
       </c>
       <c r="K23" s="8" t="n">
         <f aca="false">IF(J23="OVERPRICED?",ROUND(H23*1.35,-1),MAX(E23,ROUND(H23*(1+$E$3),-1)))</f>
-        <v>3450</v>
+        <v>4070</v>
       </c>
       <c r="L23" s="8" t="n">
         <f aca="false">D23*E23</f>
@@ -3405,32 +3399,30 @@
       </c>
       <c r="M23" s="8" t="n">
         <f aca="false">D23*K23</f>
-        <v>13800</v>
+        <v>16280</v>
       </c>
       <c r="N23" s="8" t="n">
         <f aca="false">D23*H23</f>
-        <v>12000</v>
+        <v>14160</v>
       </c>
       <c r="O23" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C23,F23)),"","YES")</f>
         <v/>
       </c>
       <c r="P23" s="6" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="Q23" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="R23" s="7" t="s">
-        <v>75</v>
-      </c>
+      <c r="R23" s="7"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="n">
         <v>19</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>28</v>
@@ -3482,7 +3474,7 @@
         <v>43</v>
       </c>
       <c r="Q24" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="R24" s="7"/>
     </row>
@@ -3491,7 +3483,7 @@
         <v>20</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>28</v>
@@ -3543,7 +3535,7 @@
         <v>24</v>
       </c>
       <c r="Q25" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R25" s="7" t="s">
         <v>31</v>
@@ -3554,7 +3546,7 @@
         <v>21</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>28</v>
@@ -3606,7 +3598,7 @@
         <v>24</v>
       </c>
       <c r="Q26" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="R26" s="7" t="s">
         <v>31</v>
@@ -3617,7 +3609,7 @@
         <v>22</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>28</v>
@@ -3669,7 +3661,7 @@
         <v>24</v>
       </c>
       <c r="Q27" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="R27" s="7" t="s">
         <v>31</v>
@@ -3680,7 +3672,7 @@
         <v>23</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>28</v>
@@ -3732,7 +3724,7 @@
         <v>43</v>
       </c>
       <c r="Q28" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="R28" s="7"/>
     </row>
@@ -3741,7 +3733,7 @@
         <v>24</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>28</v>
@@ -3793,7 +3785,7 @@
         <v>43</v>
       </c>
       <c r="Q29" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="R29" s="7"/>
     </row>
@@ -3802,7 +3794,7 @@
         <v>25</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>28</v>
@@ -3854,7 +3846,7 @@
         <v>43</v>
       </c>
       <c r="Q30" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="R30" s="7"/>
     </row>
@@ -3863,7 +3855,7 @@
         <v>26</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>28</v>
@@ -3915,7 +3907,7 @@
         <v>43</v>
       </c>
       <c r="Q31" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="R31" s="7"/>
     </row>
@@ -3924,7 +3916,7 @@
         <v>27</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>28</v>
@@ -3976,10 +3968,10 @@
         <v>24</v>
       </c>
       <c r="Q32" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="R32" s="7" t="s">
         <v>89</v>
-      </c>
-      <c r="R32" s="7" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3987,7 +3979,7 @@
         <v>28</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>28</v>
@@ -4039,10 +4031,10 @@
         <v>24</v>
       </c>
       <c r="Q33" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="R33" s="7" t="s">
         <v>89</v>
-      </c>
-      <c r="R33" s="7" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4050,7 +4042,7 @@
         <v>30</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>28</v>
@@ -4102,7 +4094,7 @@
         <v>43</v>
       </c>
       <c r="Q34" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R34" s="7"/>
     </row>
@@ -4111,7 +4103,7 @@
         <v>31</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>28</v>
@@ -4163,10 +4155,10 @@
         <v>24</v>
       </c>
       <c r="Q35" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="R35" s="7" t="s">
         <v>95</v>
-      </c>
-      <c r="R35" s="7" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4174,7 +4166,7 @@
         <v>32</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>28</v>
@@ -4226,10 +4218,10 @@
         <v>24</v>
       </c>
       <c r="Q36" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="R36" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4237,7 +4229,7 @@
         <v>33</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>28</v>
@@ -4289,7 +4281,7 @@
         <v>43</v>
       </c>
       <c r="Q37" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="R37" s="7"/>
     </row>
@@ -4298,7 +4290,7 @@
         <v>34</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>28</v>
@@ -4350,10 +4342,10 @@
         <v>24</v>
       </c>
       <c r="Q38" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="R38" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4361,7 +4353,7 @@
         <v>35</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>28</v>
@@ -4413,10 +4405,10 @@
         <v>24</v>
       </c>
       <c r="Q39" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="R39" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4424,7 +4416,7 @@
         <v>36</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>28</v>
@@ -4476,10 +4468,10 @@
         <v>24</v>
       </c>
       <c r="Q40" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="R40" s="7" t="s">
         <v>106</v>
-      </c>
-      <c r="R40" s="7" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4487,7 +4479,7 @@
         <v>37</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>28</v>
@@ -4539,10 +4531,10 @@
         <v>24</v>
       </c>
       <c r="Q41" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="R41" s="7" t="s">
         <v>109</v>
-      </c>
-      <c r="R41" s="7" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4550,7 +4542,7 @@
         <v>38</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>28</v>
@@ -4602,10 +4594,10 @@
         <v>24</v>
       </c>
       <c r="Q42" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="R42" s="7" t="s">
         <v>112</v>
-      </c>
-      <c r="R42" s="7" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4613,7 +4605,7 @@
         <v>39</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>28</v>
@@ -4628,7 +4620,7 @@
         <v>28</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>3500</v>
+        <v>4000</v>
       </c>
       <c r="H43" s="9" t="n">
         <v>4000</v>
@@ -4662,13 +4654,13 @@
         <v/>
       </c>
       <c r="P43" s="6" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="Q43" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="R43" s="7" t="s">
-        <v>116</v>
+        <v>53</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4676,10 +4668,10 @@
         <v>40</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D44" s="6" t="n">
         <v>3</v>
@@ -4688,7 +4680,7 @@
         <v>79300</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G44" s="9" t="n">
         <v>79000</v>
@@ -4728,7 +4720,7 @@
         <v>43</v>
       </c>
       <c r="Q44" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="R44" s="7"/>
     </row>
@@ -4737,10 +4729,10 @@
         <v>41</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>3</v>
@@ -4749,7 +4741,7 @@
         <v>128700</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G45" s="9" t="n">
         <v>95000</v>
@@ -4789,10 +4781,10 @@
         <v>24</v>
       </c>
       <c r="Q45" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="R45" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4800,10 +4792,10 @@
         <v>42</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D46" s="6" t="n">
         <v>2</v>
@@ -4812,7 +4804,7 @@
         <v>106600</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G46" s="9" t="n">
         <v>143800</v>
@@ -4852,7 +4844,7 @@
         <v>43</v>
       </c>
       <c r="Q46" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="R46" s="7"/>
     </row>
@@ -4861,7 +4853,7 @@
         <v>43</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>28</v>
@@ -4913,7 +4905,7 @@
         <v>24</v>
       </c>
       <c r="Q47" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="R47" s="7" t="s">
         <v>31</v>
@@ -4924,7 +4916,7 @@
         <v>44</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>28</v>
@@ -4936,7 +4928,7 @@
         <v>1950</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G48" s="9" t="n">
         <v>1750</v>
@@ -4976,7 +4968,7 @@
         <v>43</v>
       </c>
       <c r="Q48" s="7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="R48" s="7"/>
     </row>
@@ -4985,7 +4977,7 @@
         <v>45</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>28</v>
@@ -4997,7 +4989,7 @@
         <v>2210</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G49" s="9" t="n">
         <v>1750</v>
@@ -5037,10 +5029,10 @@
         <v>24</v>
       </c>
       <c r="Q49" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="R49" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5048,7 +5040,7 @@
         <v>47</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>28</v>
@@ -5100,7 +5092,7 @@
         <v>24</v>
       </c>
       <c r="Q50" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="R50" s="7" t="s">
         <v>31</v>
@@ -5111,7 +5103,7 @@
         <v>48</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>28</v>
@@ -5163,7 +5155,7 @@
         <v>24</v>
       </c>
       <c r="Q51" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="R51" s="7" t="s">
         <v>31</v>
@@ -5174,7 +5166,7 @@
         <v>49</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>28</v>
@@ -5226,7 +5218,7 @@
         <v>24</v>
       </c>
       <c r="Q52" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="R52" s="7" t="s">
         <v>31</v>
@@ -5237,7 +5229,7 @@
         <v>50</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>28</v>
@@ -5289,7 +5281,7 @@
         <v>24</v>
       </c>
       <c r="Q53" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="R53" s="7" t="s">
         <v>31</v>
@@ -5300,7 +5292,7 @@
         <v>51</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>28</v>
@@ -5352,7 +5344,7 @@
         <v>24</v>
       </c>
       <c r="Q54" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="R54" s="7" t="s">
         <v>31</v>
@@ -5363,7 +5355,7 @@
         <v>52</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>28</v>
@@ -5415,10 +5407,10 @@
         <v>24</v>
       </c>
       <c r="Q55" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="R55" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5426,7 +5418,7 @@
         <v>53</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>28</v>
@@ -5478,10 +5470,10 @@
         <v>24</v>
       </c>
       <c r="Q56" s="7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="R56" s="7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5489,10 +5481,10 @@
         <v>54</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D57" s="6" t="n">
         <v>2</v>
@@ -5501,7 +5493,7 @@
         <v>400946</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G57" s="9" t="n">
         <v>115000</v>
@@ -5541,7 +5533,7 @@
         <v>43</v>
       </c>
       <c r="Q57" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="R57" s="7"/>
     </row>
@@ -5550,7 +5542,7 @@
         <v>55</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>28</v>
@@ -5562,7 +5554,7 @@
         <v>15600</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G58" s="9" t="n">
         <v>12000</v>
@@ -5602,10 +5594,10 @@
         <v>24</v>
       </c>
       <c r="Q58" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R58" s="7" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5613,7 +5605,7 @@
         <v>56</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>28</v>
@@ -5665,10 +5657,10 @@
         <v>24</v>
       </c>
       <c r="Q59" s="7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="R59" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5676,7 +5668,7 @@
         <v>57</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>28</v>
@@ -5728,7 +5720,7 @@
         <v>43</v>
       </c>
       <c r="Q60" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="R60" s="7"/>
     </row>
@@ -5737,7 +5729,7 @@
         <v>58</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>28</v>
@@ -5789,7 +5781,7 @@
         <v>24</v>
       </c>
       <c r="Q61" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R61" s="7" t="s">
         <v>31</v>
@@ -5800,7 +5792,7 @@
         <v>59</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>28</v>
@@ -5852,7 +5844,7 @@
         <v>24</v>
       </c>
       <c r="Q62" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R62" s="7" t="s">
         <v>31</v>
@@ -5863,7 +5855,7 @@
         <v>60</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>28</v>
@@ -5875,7 +5867,7 @@
         <v>9100</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G63" s="9" t="n">
         <v>8000</v>
@@ -5915,10 +5907,10 @@
         <v>24</v>
       </c>
       <c r="Q63" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="R63" s="7" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5926,7 +5918,7 @@
         <v>61</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>28</v>
@@ -5938,7 +5930,7 @@
         <v>5850</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G64" s="9" t="n">
         <v>5000</v>
@@ -5978,10 +5970,10 @@
         <v>24</v>
       </c>
       <c r="Q64" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R64" s="7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5989,7 +5981,7 @@
         <v>62</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>28</v>
@@ -6041,10 +6033,10 @@
         <v>24</v>
       </c>
       <c r="Q65" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R65" s="7" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6052,7 +6044,7 @@
         <v>63</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>28</v>
@@ -6104,10 +6096,10 @@
         <v>24</v>
       </c>
       <c r="Q66" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="R66" s="7" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6115,7 +6107,7 @@
         <v>64</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>28</v>
@@ -6127,7 +6119,7 @@
         <v>1560</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G67" s="9" t="n">
         <v>1350</v>
@@ -6167,7 +6159,7 @@
         <v>43</v>
       </c>
       <c r="Q67" s="7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="R67" s="7"/>
     </row>
@@ -6176,7 +6168,7 @@
         <v>65</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>28</v>
@@ -6188,7 +6180,7 @@
         <v>1560</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G68" s="9" t="n">
         <v>1350</v>
@@ -6228,7 +6220,7 @@
         <v>43</v>
       </c>
       <c r="Q68" s="7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="R68" s="7"/>
     </row>
@@ -6237,7 +6229,7 @@
         <v>66</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>28</v>
@@ -6249,7 +6241,7 @@
         <v>11700</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G69" s="9" t="n">
         <v>14000</v>
@@ -6289,7 +6281,7 @@
         <v>24</v>
       </c>
       <c r="Q69" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R69" s="7" t="s">
         <v>31</v>
@@ -6300,7 +6292,7 @@
         <v>67</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>28</v>
@@ -6312,7 +6304,7 @@
         <v>9750</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G70" s="9" t="n">
         <v>12000</v>
@@ -6352,7 +6344,7 @@
         <v>24</v>
       </c>
       <c r="Q70" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R70" s="7" t="s">
         <v>31</v>
@@ -6363,7 +6355,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>28</v>
@@ -6375,7 +6367,7 @@
         <v>23400</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G71" s="9" t="n">
         <v>15000</v>
@@ -6415,7 +6407,7 @@
         <v>24</v>
       </c>
       <c r="Q71" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R71" s="7" t="s">
         <v>31</v>
@@ -6426,7 +6418,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>28</v>
@@ -6438,7 +6430,7 @@
         <v>32500</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G72" s="9" t="n">
         <v>25000</v>
@@ -6478,7 +6470,7 @@
         <v>24</v>
       </c>
       <c r="Q72" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R72" s="7" t="s">
         <v>31</v>
@@ -6489,7 +6481,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>28</v>
@@ -6501,7 +6493,7 @@
         <v>1105</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G73" s="9" t="n">
         <v>800</v>
@@ -6541,10 +6533,10 @@
         <v>24</v>
       </c>
       <c r="Q73" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R73" s="7" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6552,7 +6544,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>28</v>
@@ -6564,7 +6556,7 @@
         <v>45500</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G74" s="9" t="n">
         <v>35000</v>
@@ -6604,10 +6596,10 @@
         <v>24</v>
       </c>
       <c r="Q74" s="7" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="R74" s="7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6615,7 +6607,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>28</v>
@@ -6627,7 +6619,7 @@
         <v>23400</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G75" s="9" t="n">
         <v>45000</v>
@@ -6667,10 +6659,10 @@
         <v>24</v>
       </c>
       <c r="Q75" s="7" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="R75" s="7" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6678,7 +6670,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>28</v>
@@ -6690,7 +6682,7 @@
         <v>1950</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G76" s="9" t="n">
         <v>9790</v>
@@ -6730,7 +6722,7 @@
         <v>24</v>
       </c>
       <c r="Q76" s="7" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="R76" s="7" t="s">
         <v>31</v>
@@ -6741,7 +6733,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>28</v>
@@ -6753,7 +6745,7 @@
         <v>2080</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G77" s="9" t="n">
         <v>11060</v>
@@ -6793,7 +6785,7 @@
         <v>24</v>
       </c>
       <c r="Q77" s="7" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="R77" s="7" t="s">
         <v>31</v>
@@ -6804,7 +6796,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>28</v>
@@ -6816,7 +6808,7 @@
         <v>2210</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G78" s="9" t="n">
         <v>11700</v>
@@ -6856,7 +6848,7 @@
         <v>24</v>
       </c>
       <c r="Q78" s="7" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="R78" s="7" t="s">
         <v>31</v>
@@ -6867,7 +6859,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>28</v>
@@ -6879,7 +6871,7 @@
         <v>2340</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G79" s="9" t="n">
         <v>12330</v>
@@ -6919,7 +6911,7 @@
         <v>24</v>
       </c>
       <c r="Q79" s="7" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="R79" s="7" t="s">
         <v>31</v>
@@ -6930,7 +6922,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>28</v>
@@ -6942,7 +6934,7 @@
         <v>2470</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G80" s="9" t="n">
         <v>12970</v>
@@ -6982,7 +6974,7 @@
         <v>24</v>
       </c>
       <c r="Q80" s="7" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="R80" s="7" t="s">
         <v>31</v>
@@ -6993,7 +6985,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>28</v>
@@ -7005,7 +6997,7 @@
         <v>2600</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G81" s="9" t="n">
         <v>13600</v>
@@ -7045,7 +7037,7 @@
         <v>24</v>
       </c>
       <c r="Q81" s="7" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="R81" s="7" t="s">
         <v>31</v>
@@ -7056,7 +7048,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>28</v>
@@ -7068,7 +7060,7 @@
         <v>2730</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G82" s="9" t="n">
         <v>14240</v>
@@ -7108,7 +7100,7 @@
         <v>24</v>
       </c>
       <c r="Q82" s="7" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="R82" s="7" t="s">
         <v>31</v>
@@ -7119,7 +7111,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>28</v>
@@ -7131,7 +7123,7 @@
         <v>3250</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G83" s="9" t="n">
         <v>16140</v>
@@ -7171,7 +7163,7 @@
         <v>24</v>
       </c>
       <c r="Q83" s="7" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="R83" s="7" t="s">
         <v>31</v>
@@ -7182,7 +7174,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>28</v>
@@ -7194,7 +7186,7 @@
         <v>4160</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G84" s="9" t="n">
         <v>19230</v>
@@ -7234,7 +7226,7 @@
         <v>24</v>
       </c>
       <c r="Q84" s="7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="R84" s="7" t="s">
         <v>31</v>
@@ -7245,7 +7237,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>28</v>
@@ -7257,7 +7249,7 @@
         <v>5850</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G85" s="9" t="n">
         <v>26490</v>
@@ -7297,7 +7289,7 @@
         <v>24</v>
       </c>
       <c r="Q85" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="R85" s="7" t="s">
         <v>31</v>
@@ -7308,7 +7300,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>28</v>
@@ -7320,7 +7312,7 @@
         <v>8450</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G86" s="9" t="n">
         <v>38450</v>
@@ -7360,7 +7352,7 @@
         <v>24</v>
       </c>
       <c r="Q86" s="7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="R86" s="7" t="s">
         <v>31</v>
@@ -7371,7 +7363,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>28</v>
@@ -7383,7 +7375,7 @@
         <v>9750</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G87" s="9" t="n">
         <v>44060</v>
@@ -7423,7 +7415,7 @@
         <v>24</v>
       </c>
       <c r="Q87" s="7" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="R87" s="7" t="s">
         <v>31</v>
@@ -7434,7 +7426,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>28</v>
@@ -7446,7 +7438,7 @@
         <v>11700</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G88" s="9" t="n">
         <v>52470</v>
@@ -7486,7 +7478,7 @@
         <v>24</v>
       </c>
       <c r="Q88" s="7" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="R88" s="7" t="s">
         <v>31</v>
@@ -7497,7 +7489,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>28</v>
@@ -7509,7 +7501,7 @@
         <v>4550</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G89" s="9" t="n">
         <v>3500</v>
@@ -7549,7 +7541,7 @@
         <v>24</v>
       </c>
       <c r="Q89" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R89" s="7" t="s">
         <v>31</v>
@@ -7560,7 +7552,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>28</v>
@@ -7572,7 +7564,7 @@
         <v>5850</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G90" s="9" t="n">
         <v>4500</v>
@@ -7612,7 +7604,7 @@
         <v>24</v>
       </c>
       <c r="Q90" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R90" s="7" t="s">
         <v>31</v>
@@ -7623,7 +7615,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>28</v>
@@ -7635,7 +7627,7 @@
         <v>7150</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G91" s="9" t="n">
         <v>5500</v>
@@ -7675,7 +7667,7 @@
         <v>24</v>
       </c>
       <c r="Q91" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R91" s="7" t="s">
         <v>31</v>
@@ -7686,7 +7678,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>28</v>
@@ -7698,7 +7690,7 @@
         <v>2340</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G92" s="9" t="n">
         <v>2500</v>
@@ -7738,7 +7730,7 @@
         <v>24</v>
       </c>
       <c r="Q92" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R92" s="7" t="s">
         <v>31</v>
@@ -7749,7 +7741,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>28</v>
@@ -7761,7 +7753,7 @@
         <v>2860</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G93" s="9" t="n">
         <v>3000</v>
@@ -7801,7 +7793,7 @@
         <v>24</v>
       </c>
       <c r="Q93" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R93" s="7" t="s">
         <v>31</v>
@@ -7812,10 +7804,10 @@
         <v>93</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D94" s="6" t="n">
         <v>2</v>
@@ -7824,7 +7816,7 @@
         <v>25350</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G94" s="9" t="n">
         <v>18100</v>
@@ -7864,7 +7856,7 @@
         <v>43</v>
       </c>
       <c r="Q94" s="7" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="R94" s="7"/>
     </row>
@@ -7873,10 +7865,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D95" s="6" t="n">
         <v>3</v>
@@ -7885,7 +7877,7 @@
         <v>8138</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G95" s="9" t="n">
         <v>15800</v>
@@ -7925,7 +7917,7 @@
         <v>43</v>
       </c>
       <c r="Q95" s="7" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="R95" s="7"/>
     </row>
@@ -7934,10 +7926,10 @@
         <v>95</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D96" s="6" t="n">
         <v>3</v>
@@ -7946,7 +7938,7 @@
         <v>6370</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G96" s="9" t="n">
         <v>7928</v>
@@ -7986,7 +7978,7 @@
         <v>43</v>
       </c>
       <c r="Q96" s="7" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="R96" s="7"/>
     </row>
@@ -7995,7 +7987,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>28</v>
@@ -8007,7 +7999,7 @@
         <v>14950</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G97" s="9" t="n">
         <v>15000</v>
@@ -8047,10 +8039,10 @@
         <v>24</v>
       </c>
       <c r="Q97" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R97" s="7" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8058,10 +8050,10 @@
         <v>97</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D98" s="6" t="n">
         <v>2</v>
@@ -8070,7 +8062,7 @@
         <v>286000</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G98" s="9" t="n">
         <v>199500</v>
@@ -8110,7 +8102,7 @@
         <v>51</v>
       </c>
       <c r="Q98" s="7" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="R98" s="7" t="s">
         <v>53</v>
@@ -8121,10 +8113,10 @@
         <v>98</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D99" s="6" t="n">
         <v>1</v>
@@ -8133,7 +8125,7 @@
         <v>15600</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G99" s="9" t="n">
         <v>12000</v>
@@ -8173,7 +8165,7 @@
         <v>24</v>
       </c>
       <c r="Q99" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R99" s="7" t="s">
         <v>31</v>
@@ -8184,7 +8176,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>28</v>
@@ -8196,7 +8188,7 @@
         <v>11050</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G100" s="9" t="n">
         <v>8000</v>
@@ -8236,7 +8228,7 @@
         <v>24</v>
       </c>
       <c r="Q100" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R100" s="7" t="s">
         <v>31</v>
@@ -8247,7 +8239,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>28</v>
@@ -8259,7 +8251,7 @@
         <v>9100</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G101" s="9" t="n">
         <v>6500</v>
@@ -8299,7 +8291,7 @@
         <v>24</v>
       </c>
       <c r="Q101" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R101" s="7" t="s">
         <v>31</v>
@@ -8310,7 +8302,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>28</v>
@@ -8322,7 +8314,7 @@
         <v>7150</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G102" s="9" t="n">
         <v>5500</v>
@@ -8362,7 +8354,7 @@
         <v>24</v>
       </c>
       <c r="Q102" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R102" s="7" t="s">
         <v>31</v>
@@ -8373,7 +8365,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>28</v>
@@ -8385,7 +8377,7 @@
         <v>5850</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G103" s="9" t="n">
         <v>4500</v>
@@ -8425,7 +8417,7 @@
         <v>24</v>
       </c>
       <c r="Q103" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R103" s="7" t="s">
         <v>31</v>
@@ -8436,7 +8428,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>22</v>
@@ -8488,7 +8480,7 @@
         <v>24</v>
       </c>
       <c r="Q104" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R104" s="7" t="s">
         <v>31</v>
@@ -8499,7 +8491,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>22</v>
@@ -8551,10 +8543,10 @@
         <v>24</v>
       </c>
       <c r="Q105" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R105" s="7" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8562,7 +8554,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>22</v>
@@ -8574,7 +8566,7 @@
         <v>1170</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="G106" s="9" t="n">
         <v>800</v>
@@ -8614,7 +8606,7 @@
         <v>43</v>
       </c>
       <c r="Q106" s="7" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="R106" s="7"/>
     </row>
@@ -8623,7 +8615,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>28</v>
@@ -8635,7 +8627,7 @@
         <v>3640</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G107" s="9" t="n">
         <v>2000</v>
@@ -8675,10 +8667,10 @@
         <v>24</v>
       </c>
       <c r="Q107" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R107" s="7" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8686,7 +8678,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>28</v>
@@ -8698,7 +8690,7 @@
         <v>6760</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G108" s="9" t="n">
         <v>4500</v>
@@ -8738,10 +8730,10 @@
         <v>24</v>
       </c>
       <c r="Q108" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R108" s="7" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8749,7 +8741,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>28</v>
@@ -8761,7 +8753,7 @@
         <v>4550</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G109" s="9" t="n">
         <v>3500</v>
@@ -8801,10 +8793,10 @@
         <v>24</v>
       </c>
       <c r="Q109" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R109" s="7" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8812,7 +8804,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>28</v>
@@ -8824,7 +8816,7 @@
         <v>2340</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G110" s="9" t="n">
         <v>1800</v>
@@ -8864,10 +8856,10 @@
         <v>24</v>
       </c>
       <c r="Q110" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R110" s="7" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8875,7 +8867,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>28</v>
@@ -8887,7 +8879,7 @@
         <v>1820</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G111" s="9" t="n">
         <v>2000</v>
@@ -8927,10 +8919,10 @@
         <v>24</v>
       </c>
       <c r="Q111" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R111" s="7" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8938,7 +8930,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>28</v>
@@ -8950,7 +8942,7 @@
         <v>2860</v>
       </c>
       <c r="F112" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G112" s="9" t="n">
         <v>4000</v>
@@ -8990,10 +8982,10 @@
         <v>24</v>
       </c>
       <c r="Q112" s="7" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="R112" s="7" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9001,7 +8993,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>28</v>
@@ -9013,7 +9005,7 @@
         <v>12350</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G113" s="9" t="n">
         <v>8000</v>
@@ -9053,10 +9045,10 @@
         <v>24</v>
       </c>
       <c r="Q113" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R113" s="7" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9064,7 +9056,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>28</v>
@@ -9116,7 +9108,7 @@
         <v>24</v>
       </c>
       <c r="Q114" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R114" s="7" t="s">
         <v>31</v>
@@ -9127,7 +9119,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>28</v>
@@ -9179,7 +9171,7 @@
         <v>24</v>
       </c>
       <c r="Q115" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R115" s="7" t="s">
         <v>31</v>
@@ -9190,7 +9182,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>22</v>
@@ -9202,7 +9194,7 @@
         <v>11050</v>
       </c>
       <c r="F116" s="7" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G116" s="9" t="n">
         <v>5000</v>
@@ -9242,7 +9234,7 @@
         <v>43</v>
       </c>
       <c r="Q116" s="7" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="R116" s="7"/>
     </row>
@@ -9251,7 +9243,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>28</v>
@@ -9303,10 +9295,10 @@
         <v>24</v>
       </c>
       <c r="Q117" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R117" s="7" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9314,7 +9306,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>22</v>
@@ -9366,7 +9358,7 @@
         <v>24</v>
       </c>
       <c r="Q118" s="7" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="R118" s="7" t="s">
         <v>31</v>
@@ -9377,7 +9369,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>22</v>
@@ -9429,7 +9421,7 @@
         <v>24</v>
       </c>
       <c r="Q119" s="7" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="R119" s="7" t="s">
         <v>31</v>
@@ -9440,7 +9432,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>28</v>
@@ -9492,7 +9484,7 @@
         <v>24</v>
       </c>
       <c r="Q120" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R120" s="7" t="s">
         <v>31</v>
@@ -9503,7 +9495,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>22</v>
@@ -9555,7 +9547,7 @@
         <v>24</v>
       </c>
       <c r="Q121" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R121" s="7" t="s">
         <v>31</v>
@@ -9566,7 +9558,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>22</v>
@@ -9618,7 +9610,7 @@
         <v>43</v>
       </c>
       <c r="Q122" s="7" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="R122" s="7"/>
     </row>
@@ -9627,7 +9619,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>22</v>
@@ -9639,7 +9631,7 @@
         <v>357500</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G123" s="9" t="n">
         <v>200000</v>
@@ -9679,10 +9671,10 @@
         <v>24</v>
       </c>
       <c r="Q123" s="7" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="R123" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9690,7 +9682,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C124" s="6" t="s">
         <v>22</v>
@@ -9742,10 +9734,10 @@
         <v>24</v>
       </c>
       <c r="Q124" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R124" s="7" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9753,7 +9745,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>22</v>
@@ -9805,7 +9797,7 @@
         <v>24</v>
       </c>
       <c r="Q125" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R125" s="7" t="s">
         <v>31</v>
@@ -9816,7 +9808,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>22</v>
@@ -9868,7 +9860,7 @@
         <v>24</v>
       </c>
       <c r="Q126" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R126" s="7" t="s">
         <v>31</v>
@@ -9879,7 +9871,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>22</v>
@@ -9931,7 +9923,7 @@
         <v>24</v>
       </c>
       <c r="Q127" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R127" s="7" t="s">
         <v>31</v>
@@ -9942,7 +9934,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>22</v>
@@ -9994,7 +9986,7 @@
         <v>24</v>
       </c>
       <c r="Q128" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R128" s="7" t="s">
         <v>31</v>
@@ -10005,7 +9997,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>22</v>
@@ -10057,7 +10049,7 @@
         <v>24</v>
       </c>
       <c r="Q129" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R129" s="7" t="s">
         <v>31</v>
@@ -10068,7 +10060,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>22</v>
@@ -10120,7 +10112,7 @@
         <v>24</v>
       </c>
       <c r="Q130" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R130" s="7" t="s">
         <v>31</v>
@@ -10131,7 +10123,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>22</v>
@@ -10183,10 +10175,10 @@
         <v>24</v>
       </c>
       <c r="Q131" s="7" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="R131" s="7" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10194,7 +10186,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>22</v>
@@ -10206,7 +10198,7 @@
         <v>7800</v>
       </c>
       <c r="F132" s="7" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G132" s="9" t="n">
         <v>5000</v>
@@ -10246,7 +10238,7 @@
         <v>43</v>
       </c>
       <c r="Q132" s="7" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="R132" s="7"/>
     </row>
@@ -10255,7 +10247,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="7" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>22</v>
@@ -10307,7 +10299,7 @@
         <v>24</v>
       </c>
       <c r="Q133" s="7" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="R133" s="7" t="s">
         <v>31</v>
@@ -10318,7 +10310,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>28</v>
@@ -10370,7 +10362,7 @@
         <v>24</v>
       </c>
       <c r="Q134" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R134" s="7" t="s">
         <v>31</v>
@@ -10381,7 +10373,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>22</v>
@@ -10433,7 +10425,7 @@
         <v>24</v>
       </c>
       <c r="Q135" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R135" s="7" t="s">
         <v>31</v>
@@ -10444,7 +10436,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="7" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C136" s="6" t="s">
         <v>22</v>
@@ -10496,7 +10488,7 @@
         <v>43</v>
       </c>
       <c r="Q136" s="7" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="R136" s="7"/>
     </row>
@@ -10505,7 +10497,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C137" s="6" t="s">
         <v>22</v>
@@ -10557,7 +10549,7 @@
         <v>43</v>
       </c>
       <c r="Q137" s="7" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="R137" s="7"/>
     </row>
@@ -10566,7 +10558,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C138" s="6" t="s">
         <v>22</v>
@@ -10618,7 +10610,7 @@
         <v>43</v>
       </c>
       <c r="Q138" s="7" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="R138" s="7"/>
     </row>
@@ -10627,7 +10619,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="7" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C139" s="6" t="s">
         <v>28</v>
@@ -10679,7 +10671,7 @@
         <v>24</v>
       </c>
       <c r="Q139" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R139" s="7" t="s">
         <v>31</v>
@@ -10690,7 +10682,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="7" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C140" s="6" t="s">
         <v>22</v>
@@ -10742,10 +10734,10 @@
         <v>24</v>
       </c>
       <c r="Q140" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R140" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10753,7 +10745,7 @@
         <v>142</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C141" s="6" t="s">
         <v>22</v>
@@ -10765,7 +10757,7 @@
         <v>7150</v>
       </c>
       <c r="F141" s="7" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G141" s="9" t="n">
         <v>5000</v>
@@ -10805,7 +10797,7 @@
         <v>24</v>
       </c>
       <c r="Q141" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R141" s="7" t="s">
         <v>31</v>
@@ -10816,7 +10808,7 @@
         <v>143</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C142" s="6" t="s">
         <v>22</v>
@@ -10828,7 +10820,7 @@
         <v>7150</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G142" s="9" t="n">
         <v>5000</v>
@@ -10868,7 +10860,7 @@
         <v>24</v>
       </c>
       <c r="Q142" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R142" s="7" t="s">
         <v>31</v>
@@ -10879,7 +10871,7 @@
         <v>144</v>
       </c>
       <c r="B143" s="7" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C143" s="6" t="s">
         <v>22</v>
@@ -10891,7 +10883,7 @@
         <v>8450</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G143" s="9" t="n">
         <v>6000</v>
@@ -10931,7 +10923,7 @@
         <v>24</v>
       </c>
       <c r="Q143" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R143" s="7" t="s">
         <v>31</v>
@@ -10942,7 +10934,7 @@
         <v>145</v>
       </c>
       <c r="B144" s="7" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C144" s="6" t="s">
         <v>28</v>
@@ -10954,7 +10946,7 @@
         <v>104</v>
       </c>
       <c r="F144" s="7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G144" s="9" t="n">
         <v>50</v>
@@ -10994,7 +10986,7 @@
         <v>24</v>
       </c>
       <c r="Q144" s="7" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="R144" s="7" t="s">
         <v>31</v>
@@ -11005,7 +10997,7 @@
         <v>146</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C145" s="6" t="s">
         <v>22</v>
@@ -11017,7 +11009,7 @@
         <v>105788</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G145" s="9" t="n">
         <v>82000</v>
@@ -11057,7 +11049,7 @@
         <v>43</v>
       </c>
       <c r="Q145" s="7" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="R145" s="7"/>
     </row>
@@ -11066,7 +11058,7 @@
         <v>147</v>
       </c>
       <c r="B146" s="7" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C146" s="6" t="s">
         <v>22</v>
@@ -11078,7 +11070,7 @@
         <v>245700</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G146" s="9" t="n">
         <v>225000</v>
@@ -11118,7 +11110,7 @@
         <v>43</v>
       </c>
       <c r="Q146" s="7" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="R146" s="7"/>
     </row>
@@ -11127,7 +11119,7 @@
         <v>148</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C147" s="6" t="s">
         <v>28</v>
@@ -11179,10 +11171,10 @@
         <v>24</v>
       </c>
       <c r="Q147" s="7" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="R147" s="7" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11190,7 +11182,7 @@
         <v>149</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C148" s="6" t="s">
         <v>22</v>
@@ -11202,7 +11194,7 @@
         <v>1754</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G148" s="9" t="n">
         <v>1380</v>
@@ -11242,7 +11234,7 @@
         <v>43</v>
       </c>
       <c r="Q148" s="7" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="R148" s="7"/>
     </row>
@@ -11251,7 +11243,7 @@
         <v>150</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C149" s="6" t="s">
         <v>22</v>
@@ -11303,7 +11295,7 @@
         <v>43</v>
       </c>
       <c r="Q149" s="7" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="R149" s="7"/>
     </row>
@@ -11312,7 +11304,7 @@
         <v>151</v>
       </c>
       <c r="B150" s="7" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C150" s="6" t="s">
         <v>22</v>
@@ -11364,7 +11356,7 @@
         <v>43</v>
       </c>
       <c r="Q150" s="7" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="R150" s="7"/>
     </row>
@@ -11373,7 +11365,7 @@
         <v>152</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C151" s="6" t="s">
         <v>22</v>
@@ -11425,7 +11417,7 @@
         <v>43</v>
       </c>
       <c r="Q151" s="7" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="R151" s="7"/>
     </row>
@@ -11434,7 +11426,7 @@
         <v>153</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C152" s="6" t="s">
         <v>22</v>
@@ -11486,7 +11478,7 @@
         <v>43</v>
       </c>
       <c r="Q152" s="7" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="R152" s="7"/>
     </row>
@@ -11495,7 +11487,7 @@
         <v>154</v>
       </c>
       <c r="B153" s="7" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C153" s="6" t="s">
         <v>22</v>
@@ -11547,7 +11539,7 @@
         <v>24</v>
       </c>
       <c r="Q153" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R153" s="7" t="s">
         <v>31</v>
@@ -11558,7 +11550,7 @@
         <v>155</v>
       </c>
       <c r="B154" s="7" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C154" s="6" t="s">
         <v>22</v>
@@ -11570,7 +11562,7 @@
         <v>748</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="G154" s="9" t="n">
         <v>450</v>
@@ -11610,7 +11602,7 @@
         <v>43</v>
       </c>
       <c r="Q154" s="7" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="R154" s="7"/>
     </row>
@@ -11619,7 +11611,7 @@
         <v>156</v>
       </c>
       <c r="B155" s="7" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>22</v>
@@ -11631,7 +11623,7 @@
         <v>748</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="G155" s="9" t="n">
         <v>450</v>
@@ -11671,7 +11663,7 @@
         <v>43</v>
       </c>
       <c r="Q155" s="7" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="R155" s="7"/>
     </row>
@@ -11680,7 +11672,7 @@
         <v>157</v>
       </c>
       <c r="B156" s="7" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C156" s="6" t="s">
         <v>22</v>
@@ -11692,7 +11684,7 @@
         <v>748</v>
       </c>
       <c r="F156" s="7" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G156" s="9" t="n">
         <v>400</v>
@@ -11732,7 +11724,7 @@
         <v>43</v>
       </c>
       <c r="Q156" s="7" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="R156" s="7"/>
     </row>
@@ -11741,7 +11733,7 @@
         <v>158</v>
       </c>
       <c r="B157" s="7" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C157" s="6" t="s">
         <v>28</v>
@@ -11753,7 +11745,7 @@
         <v>311</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G157" s="9" t="n">
         <v>150</v>
@@ -11793,7 +11785,7 @@
         <v>24</v>
       </c>
       <c r="Q157" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R157" s="7" t="s">
         <v>31</v>
@@ -11804,7 +11796,7 @@
         <v>159</v>
       </c>
       <c r="B158" s="7" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C158" s="6" t="s">
         <v>28</v>
@@ -11816,7 +11808,7 @@
         <v>325</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G158" s="9" t="n">
         <v>180</v>
@@ -11856,7 +11848,7 @@
         <v>24</v>
       </c>
       <c r="Q158" s="7" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="R158" s="7" t="s">
         <v>31</v>
@@ -11867,7 +11859,7 @@
         <v>160</v>
       </c>
       <c r="B159" s="7" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C159" s="6" t="s">
         <v>28</v>
@@ -11879,7 +11871,7 @@
         <v>117</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G159" s="9" t="n">
         <v>60</v>
@@ -11919,7 +11911,7 @@
         <v>24</v>
       </c>
       <c r="Q159" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R159" s="7" t="s">
         <v>31</v>
@@ -11930,7 +11922,7 @@
         <v>161</v>
       </c>
       <c r="B160" s="7" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C160" s="6" t="s">
         <v>28</v>
@@ -11942,7 +11934,7 @@
         <v>169</v>
       </c>
       <c r="F160" s="7" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G160" s="9" t="n">
         <v>90</v>
@@ -11982,7 +11974,7 @@
         <v>24</v>
       </c>
       <c r="Q160" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R160" s="7" t="s">
         <v>31</v>
@@ -11993,7 +11985,7 @@
         <v>162</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C161" s="6" t="s">
         <v>28</v>
@@ -12005,7 +11997,7 @@
         <v>234</v>
       </c>
       <c r="F161" s="7" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G161" s="9" t="n">
         <v>120</v>
@@ -12045,7 +12037,7 @@
         <v>24</v>
       </c>
       <c r="Q161" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R161" s="7" t="s">
         <v>31</v>
@@ -12056,7 +12048,7 @@
         <v>164</v>
       </c>
       <c r="B162" s="7" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C162" s="6" t="s">
         <v>22</v>
@@ -12068,7 +12060,7 @@
         <v>1209</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="G162" s="9" t="n">
         <v>1450</v>
@@ -12108,7 +12100,7 @@
         <v>51</v>
       </c>
       <c r="Q162" s="7" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="R162" s="7" t="s">
         <v>53</v>
@@ -12119,7 +12111,7 @@
         <v>165</v>
       </c>
       <c r="B163" s="7" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C163" s="6" t="s">
         <v>22</v>
@@ -12131,7 +12123,7 @@
         <v>1209</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="G163" s="9" t="n">
         <v>2248</v>
@@ -12171,7 +12163,7 @@
         <v>51</v>
       </c>
       <c r="Q163" s="7" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="R163" s="7" t="s">
         <v>53</v>
@@ -12182,7 +12174,7 @@
         <v>166</v>
       </c>
       <c r="B164" s="7" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C164" s="6" t="s">
         <v>22</v>
@@ -12194,7 +12186,7 @@
         <v>3022</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G164" s="9" t="n">
         <v>2325</v>
@@ -12234,7 +12226,7 @@
         <v>51</v>
       </c>
       <c r="Q164" s="7" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="R164" s="7" t="s">
         <v>53</v>
@@ -12245,7 +12237,7 @@
         <v>167</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C165" s="6" t="s">
         <v>22</v>
@@ -12297,10 +12289,10 @@
         <v>24</v>
       </c>
       <c r="Q165" s="7" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="R165" s="7" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12308,7 +12300,7 @@
         <v>168</v>
       </c>
       <c r="B166" s="7" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C166" s="6" t="s">
         <v>22</v>
@@ -12360,10 +12352,10 @@
         <v>24</v>
       </c>
       <c r="Q166" s="7" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="R166" s="7" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12371,7 +12363,7 @@
         <v>177</v>
       </c>
       <c r="B167" s="7" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C167" s="6" t="s">
         <v>28</v>
@@ -12383,7 +12375,7 @@
         <v>5850</v>
       </c>
       <c r="F167" s="7" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G167" s="9" t="n">
         <v>3500</v>
@@ -12423,10 +12415,10 @@
         <v>24</v>
       </c>
       <c r="Q167" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R167" s="7" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12434,7 +12426,7 @@
         <v>179</v>
       </c>
       <c r="B168" s="7" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C168" s="6" t="s">
         <v>28</v>
@@ -12446,7 +12438,7 @@
         <v>23400</v>
       </c>
       <c r="F168" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G168" s="9" t="n">
         <v>20000</v>
@@ -12486,7 +12478,7 @@
         <v>24</v>
       </c>
       <c r="Q168" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R168" s="7" t="s">
         <v>31</v>
@@ -12497,7 +12489,7 @@
         <v>180</v>
       </c>
       <c r="B169" s="7" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C169" s="6" t="s">
         <v>28</v>
@@ -12509,7 +12501,7 @@
         <v>15600</v>
       </c>
       <c r="F169" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G169" s="9" t="n">
         <v>14000</v>
@@ -12549,7 +12541,7 @@
         <v>24</v>
       </c>
       <c r="Q169" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R169" s="7" t="s">
         <v>31</v>
@@ -12560,7 +12552,7 @@
         <v>181</v>
       </c>
       <c r="B170" s="7" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C170" s="6" t="s">
         <v>28</v>
@@ -12572,7 +12564,7 @@
         <v>33800</v>
       </c>
       <c r="F170" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G170" s="9" t="n">
         <v>28000</v>
@@ -12612,7 +12604,7 @@
         <v>24</v>
       </c>
       <c r="Q170" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R170" s="7" t="s">
         <v>31</v>
@@ -12623,7 +12615,7 @@
         <v>182</v>
       </c>
       <c r="B171" s="7" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C171" s="6" t="s">
         <v>28</v>
@@ -12635,7 +12627,7 @@
         <v>23400</v>
       </c>
       <c r="F171" s="7" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G171" s="9" t="n">
         <v>20000</v>
@@ -12675,7 +12667,7 @@
         <v>24</v>
       </c>
       <c r="Q171" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R171" s="7" t="s">
         <v>31</v>
@@ -12686,7 +12678,7 @@
         <v>183</v>
       </c>
       <c r="B172" s="7" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C172" s="6" t="s">
         <v>28</v>
@@ -12698,7 +12690,7 @@
         <v>2860</v>
       </c>
       <c r="F172" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G172" s="9" t="n">
         <v>1800</v>
@@ -12738,7 +12730,7 @@
         <v>24</v>
       </c>
       <c r="Q172" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R172" s="7" t="s">
         <v>31</v>
@@ -12749,7 +12741,7 @@
         <v>184</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C173" s="6" t="s">
         <v>28</v>
@@ -12761,7 +12753,7 @@
         <v>3250</v>
       </c>
       <c r="F173" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G173" s="9" t="n">
         <v>2100</v>
@@ -12801,7 +12793,7 @@
         <v>24</v>
       </c>
       <c r="Q173" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R173" s="7" t="s">
         <v>31</v>
@@ -12812,7 +12804,7 @@
         <v>185</v>
       </c>
       <c r="B174" s="7" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C174" s="6" t="s">
         <v>28</v>
@@ -12824,7 +12816,7 @@
         <v>3900</v>
       </c>
       <c r="F174" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G174" s="9" t="n">
         <v>2600</v>
@@ -12864,7 +12856,7 @@
         <v>24</v>
       </c>
       <c r="Q174" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R174" s="7" t="s">
         <v>31</v>
@@ -12875,7 +12867,7 @@
         <v>186</v>
       </c>
       <c r="B175" s="7" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C175" s="6" t="s">
         <v>28</v>
@@ -12887,7 +12879,7 @@
         <v>4550</v>
       </c>
       <c r="F175" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G175" s="9" t="n">
         <v>3300</v>
@@ -12927,7 +12919,7 @@
         <v>24</v>
       </c>
       <c r="Q175" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R175" s="7" t="s">
         <v>31</v>
@@ -12938,7 +12930,7 @@
         <v>187</v>
       </c>
       <c r="B176" s="7" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C176" s="6" t="s">
         <v>28</v>
@@ -12950,7 +12942,7 @@
         <v>7150</v>
       </c>
       <c r="F176" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G176" s="9" t="n">
         <v>5500</v>
@@ -12990,7 +12982,7 @@
         <v>24</v>
       </c>
       <c r="Q176" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R176" s="7" t="s">
         <v>31</v>
@@ -13001,7 +12993,7 @@
         <v>188</v>
       </c>
       <c r="B177" s="7" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C177" s="6" t="s">
         <v>28</v>
@@ -13013,7 +13005,7 @@
         <v>8450</v>
       </c>
       <c r="F177" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G177" s="9" t="n">
         <v>7000</v>
@@ -13053,7 +13045,7 @@
         <v>24</v>
       </c>
       <c r="Q177" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R177" s="7" t="s">
         <v>31</v>
@@ -13064,7 +13056,7 @@
         <v>189</v>
       </c>
       <c r="B178" s="7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C178" s="6" t="s">
         <v>28</v>
@@ -13076,7 +13068,7 @@
         <v>9750</v>
       </c>
       <c r="F178" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G178" s="9" t="n">
         <v>8500</v>
@@ -13116,7 +13108,7 @@
         <v>24</v>
       </c>
       <c r="Q178" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R178" s="7" t="s">
         <v>31</v>
@@ -13127,7 +13119,7 @@
         <v>190</v>
       </c>
       <c r="B179" s="7" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C179" s="6" t="s">
         <v>28</v>
@@ -13139,7 +13131,7 @@
         <v>2340</v>
       </c>
       <c r="F179" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G179" s="9" t="n">
         <v>1500</v>
@@ -13179,7 +13171,7 @@
         <v>24</v>
       </c>
       <c r="Q179" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R179" s="7" t="s">
         <v>31</v>
@@ -13190,7 +13182,7 @@
         <v>191</v>
       </c>
       <c r="B180" s="7" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C180" s="6" t="s">
         <v>28</v>
@@ -13202,7 +13194,7 @@
         <v>3640</v>
       </c>
       <c r="F180" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G180" s="9" t="n">
         <v>2300</v>
@@ -13242,7 +13234,7 @@
         <v>24</v>
       </c>
       <c r="Q180" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R180" s="7" t="s">
         <v>31</v>
@@ -13253,7 +13245,7 @@
         <v>192</v>
       </c>
       <c r="B181" s="7" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C181" s="6" t="s">
         <v>28</v>
@@ -13305,7 +13297,7 @@
         <v>24</v>
       </c>
       <c r="Q181" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R181" s="7" t="s">
         <v>31</v>
@@ -13316,7 +13308,7 @@
         <v>193</v>
       </c>
       <c r="B182" s="7" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C182" s="6" t="s">
         <v>28</v>
@@ -13368,7 +13360,7 @@
         <v>24</v>
       </c>
       <c r="Q182" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R182" s="7" t="s">
         <v>31</v>
@@ -13379,7 +13371,7 @@
         <v>194</v>
       </c>
       <c r="B183" s="7" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C183" s="6" t="s">
         <v>28</v>
@@ -13431,7 +13423,7 @@
         <v>24</v>
       </c>
       <c r="Q183" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R183" s="7" t="s">
         <v>31</v>
@@ -13442,7 +13434,7 @@
         <v>195</v>
       </c>
       <c r="B184" s="7" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C184" s="6" t="s">
         <v>28</v>
@@ -13494,7 +13486,7 @@
         <v>24</v>
       </c>
       <c r="Q184" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R184" s="7" t="s">
         <v>31</v>
@@ -13505,7 +13497,7 @@
         <v>196</v>
       </c>
       <c r="B185" s="7" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C185" s="6" t="s">
         <v>28</v>
@@ -13517,7 +13509,7 @@
         <v>4550</v>
       </c>
       <c r="F185" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G185" s="9" t="n">
         <v>3500</v>
@@ -13557,7 +13549,7 @@
         <v>24</v>
       </c>
       <c r="Q185" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R185" s="7" t="s">
         <v>31</v>
@@ -13568,7 +13560,7 @@
         <v>197</v>
       </c>
       <c r="B186" s="7" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C186" s="6" t="s">
         <v>28</v>
@@ -13580,7 +13572,7 @@
         <v>17940</v>
       </c>
       <c r="F186" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G186" s="9" t="n">
         <v>5500</v>
@@ -13620,7 +13612,7 @@
         <v>43</v>
       </c>
       <c r="Q186" s="7" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="R186" s="7"/>
     </row>
@@ -13629,7 +13621,7 @@
         <v>198</v>
       </c>
       <c r="B187" s="7" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C187" s="6" t="s">
         <v>28</v>
@@ -13641,7 +13633,7 @@
         <v>18850</v>
       </c>
       <c r="F187" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G187" s="9" t="n">
         <v>5500</v>
@@ -13681,7 +13673,7 @@
         <v>43</v>
       </c>
       <c r="Q187" s="7" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="R187" s="7"/>
     </row>
@@ -13690,7 +13682,7 @@
         <v>199</v>
       </c>
       <c r="B188" s="7" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C188" s="6" t="s">
         <v>28</v>
@@ -13702,7 +13694,7 @@
         <v>19500</v>
       </c>
       <c r="F188" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G188" s="9" t="n">
         <v>6200</v>
@@ -13742,7 +13734,7 @@
         <v>43</v>
       </c>
       <c r="Q188" s="7" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="R188" s="7"/>
     </row>
@@ -13751,7 +13743,7 @@
         <v>200</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C189" s="6" t="s">
         <v>28</v>
@@ -13763,7 +13755,7 @@
         <v>20800</v>
       </c>
       <c r="F189" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G189" s="9" t="n">
         <v>6875</v>
@@ -13803,7 +13795,7 @@
         <v>43</v>
       </c>
       <c r="Q189" s="7" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="R189" s="7"/>
     </row>
@@ -13812,7 +13804,7 @@
         <v>201</v>
       </c>
       <c r="B190" s="7" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C190" s="6" t="s">
         <v>28</v>
@@ -13824,7 +13816,7 @@
         <v>22750</v>
       </c>
       <c r="F190" s="7" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G190" s="9" t="n">
         <v>8750</v>
@@ -13864,7 +13856,7 @@
         <v>43</v>
       </c>
       <c r="Q190" s="7" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="R190" s="7"/>
     </row>
@@ -13873,7 +13865,7 @@
         <v>202</v>
       </c>
       <c r="B191" s="7" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C191" s="6" t="s">
         <v>28</v>
@@ -13885,7 +13877,7 @@
         <v>2340</v>
       </c>
       <c r="F191" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G191" s="9" t="n">
         <v>1500</v>
@@ -13925,7 +13917,7 @@
         <v>24</v>
       </c>
       <c r="Q191" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R191" s="7" t="s">
         <v>31</v>
@@ -13936,7 +13928,7 @@
         <v>204</v>
       </c>
       <c r="B192" s="7" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C192" s="6" t="s">
         <v>28</v>
@@ -13948,7 +13940,7 @@
         <v>845</v>
       </c>
       <c r="F192" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G192" s="9" t="n">
         <v>5480</v>
@@ -13988,7 +13980,7 @@
         <v>24</v>
       </c>
       <c r="Q192" s="7" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="R192" s="7" t="s">
         <v>31</v>
@@ -13999,7 +13991,7 @@
         <v>205</v>
       </c>
       <c r="B193" s="7" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C193" s="6" t="s">
         <v>28</v>
@@ -14011,7 +14003,7 @@
         <v>910</v>
       </c>
       <c r="F193" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G193" s="9" t="n">
         <v>5960</v>
@@ -14051,7 +14043,7 @@
         <v>24</v>
       </c>
       <c r="Q193" s="7" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="R193" s="7" t="s">
         <v>31</v>
@@ -14062,7 +14054,7 @@
         <v>206</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C194" s="6" t="s">
         <v>28</v>
@@ -14074,7 +14066,7 @@
         <v>1170</v>
       </c>
       <c r="F194" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G194" s="9" t="n">
         <v>6930</v>
@@ -14114,7 +14106,7 @@
         <v>24</v>
       </c>
       <c r="Q194" s="7" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="R194" s="7" t="s">
         <v>31</v>
@@ -14125,7 +14117,7 @@
         <v>207</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C195" s="6" t="s">
         <v>28</v>
@@ -14137,7 +14129,7 @@
         <v>1430</v>
       </c>
       <c r="F195" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G195" s="9" t="n">
         <v>8960</v>
@@ -14177,7 +14169,7 @@
         <v>24</v>
       </c>
       <c r="Q195" s="7" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="R195" s="7" t="s">
         <v>31</v>
@@ -14188,7 +14180,7 @@
         <v>208</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C196" s="6" t="s">
         <v>28</v>
@@ -14200,7 +14192,7 @@
         <v>1690</v>
       </c>
       <c r="F196" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G196" s="9" t="n">
         <v>11050</v>
@@ -14240,7 +14232,7 @@
         <v>24</v>
       </c>
       <c r="Q196" s="7" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="R196" s="7" t="s">
         <v>31</v>
@@ -14251,7 +14243,7 @@
         <v>209</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C197" s="6" t="s">
         <v>28</v>
@@ -14263,7 +14255,7 @@
         <v>2340</v>
       </c>
       <c r="F197" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G197" s="9" t="n">
         <v>15380</v>
@@ -14303,7 +14295,7 @@
         <v>24</v>
       </c>
       <c r="Q197" s="7" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="R197" s="7" t="s">
         <v>31</v>
@@ -14314,7 +14306,7 @@
         <v>210</v>
       </c>
       <c r="B198" s="7" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C198" s="6" t="s">
         <v>28</v>
@@ -14326,7 +14318,7 @@
         <v>2860</v>
       </c>
       <c r="F198" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G198" s="9" t="n">
         <v>17610</v>
@@ -14366,7 +14358,7 @@
         <v>24</v>
       </c>
       <c r="Q198" s="7" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="R198" s="7" t="s">
         <v>31</v>
@@ -14377,7 +14369,7 @@
         <v>211</v>
       </c>
       <c r="B199" s="7" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C199" s="6" t="s">
         <v>28</v>
@@ -14389,7 +14381,7 @@
         <v>4160</v>
       </c>
       <c r="F199" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G199" s="9" t="n">
         <v>22180</v>
@@ -14429,7 +14421,7 @@
         <v>24</v>
       </c>
       <c r="Q199" s="7" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="R199" s="7" t="s">
         <v>31</v>
@@ -14440,7 +14432,7 @@
         <v>212</v>
       </c>
       <c r="B200" s="7" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C200" s="6" t="s">
         <v>28</v>
@@ -14452,7 +14444,7 @@
         <v>5460</v>
       </c>
       <c r="F200" s="7" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="G200" s="9" t="n">
         <v>25690</v>
@@ -14492,7 +14484,7 @@
         <v>24</v>
       </c>
       <c r="Q200" s="7" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="R200" s="7" t="s">
         <v>31</v>
@@ -14503,7 +14495,7 @@
         <v>213</v>
       </c>
       <c r="B201" s="7" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C201" s="6" t="s">
         <v>28</v>
@@ -14515,7 +14507,7 @@
         <v>455</v>
       </c>
       <c r="F201" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G201" s="9" t="n">
         <v>500</v>
@@ -14555,7 +14547,7 @@
         <v>24</v>
       </c>
       <c r="Q201" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R201" s="7" t="s">
         <v>31</v>
@@ -14566,7 +14558,7 @@
         <v>214</v>
       </c>
       <c r="B202" s="7" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C202" s="6" t="s">
         <v>28</v>
@@ -14578,7 +14570,7 @@
         <v>494</v>
       </c>
       <c r="F202" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G202" s="9" t="n">
         <v>550</v>
@@ -14618,7 +14610,7 @@
         <v>24</v>
       </c>
       <c r="Q202" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R202" s="7" t="s">
         <v>31</v>
@@ -14629,7 +14621,7 @@
         <v>215</v>
       </c>
       <c r="B203" s="7" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C203" s="6" t="s">
         <v>28</v>
@@ -14641,7 +14633,7 @@
         <v>585</v>
       </c>
       <c r="F203" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G203" s="9" t="n">
         <v>650</v>
@@ -14681,7 +14673,7 @@
         <v>24</v>
       </c>
       <c r="Q203" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R203" s="7" t="s">
         <v>31</v>
@@ -14692,7 +14684,7 @@
         <v>216</v>
       </c>
       <c r="B204" s="7" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C204" s="6" t="s">
         <v>28</v>
@@ -14704,7 +14696,7 @@
         <v>715</v>
       </c>
       <c r="F204" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G204" s="9" t="n">
         <v>800</v>
@@ -14744,7 +14736,7 @@
         <v>24</v>
       </c>
       <c r="Q204" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R204" s="7" t="s">
         <v>31</v>
@@ -14755,7 +14747,7 @@
         <v>217</v>
       </c>
       <c r="B205" s="7" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C205" s="6" t="s">
         <v>28</v>
@@ -14767,7 +14759,7 @@
         <v>910</v>
       </c>
       <c r="F205" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G205" s="9" t="n">
         <v>1000</v>
@@ -14807,7 +14799,7 @@
         <v>24</v>
       </c>
       <c r="Q205" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R205" s="7" t="s">
         <v>31</v>
@@ -14818,7 +14810,7 @@
         <v>218</v>
       </c>
       <c r="B206" s="7" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C206" s="6" t="s">
         <v>28</v>
@@ -14830,7 +14822,7 @@
         <v>1170</v>
       </c>
       <c r="F206" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G206" s="9" t="n">
         <v>1400</v>
@@ -14870,7 +14862,7 @@
         <v>24</v>
       </c>
       <c r="Q206" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R206" s="7" t="s">
         <v>31</v>
@@ -14881,7 +14873,7 @@
         <v>219</v>
       </c>
       <c r="B207" s="7" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C207" s="6" t="s">
         <v>28</v>
@@ -14893,7 +14885,7 @@
         <v>1040</v>
       </c>
       <c r="F207" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G207" s="9" t="n">
         <v>1100</v>
@@ -14933,7 +14925,7 @@
         <v>24</v>
       </c>
       <c r="Q207" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R207" s="7" t="s">
         <v>31</v>
@@ -14944,7 +14936,7 @@
         <v>220</v>
       </c>
       <c r="B208" s="7" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C208" s="6" t="s">
         <v>28</v>
@@ -14956,7 +14948,7 @@
         <v>1430</v>
       </c>
       <c r="F208" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G208" s="9" t="n">
         <v>1400</v>
@@ -14996,7 +14988,7 @@
         <v>24</v>
       </c>
       <c r="Q208" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R208" s="7" t="s">
         <v>31</v>
@@ -15007,7 +14999,7 @@
         <v>221</v>
       </c>
       <c r="B209" s="7" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C209" s="6" t="s">
         <v>28</v>
@@ -15019,7 +15011,7 @@
         <v>1950</v>
       </c>
       <c r="F209" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G209" s="9" t="n">
         <v>2000</v>
@@ -15059,7 +15051,7 @@
         <v>24</v>
       </c>
       <c r="Q209" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R209" s="7" t="s">
         <v>31</v>
@@ -15070,7 +15062,7 @@
         <v>222</v>
       </c>
       <c r="B210" s="7" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C210" s="6" t="s">
         <v>28</v>
@@ -15082,7 +15074,7 @@
         <v>15600</v>
       </c>
       <c r="F210" s="7" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="G210" s="9" t="n">
         <v>18000</v>
@@ -15122,7 +15114,7 @@
         <v>24</v>
       </c>
       <c r="Q210" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R210" s="7" t="s">
         <v>31</v>
@@ -15133,7 +15125,7 @@
         <v>223</v>
       </c>
       <c r="B211" s="7" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C211" s="6" t="s">
         <v>28</v>
@@ -15145,7 +15137,7 @@
         <v>30940</v>
       </c>
       <c r="F211" s="7" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="G211" s="9" t="n">
         <v>45000</v>
@@ -15185,10 +15177,10 @@
         <v>24</v>
       </c>
       <c r="Q211" s="7" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="R211" s="7" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15196,7 +15188,7 @@
         <v>224</v>
       </c>
       <c r="B212" s="7" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C212" s="6" t="s">
         <v>28</v>
@@ -15208,7 +15200,7 @@
         <v>54600</v>
       </c>
       <c r="F212" s="7" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="G212" s="9" t="n">
         <v>85000</v>
@@ -15248,10 +15240,10 @@
         <v>24</v>
       </c>
       <c r="Q212" s="7" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="R212" s="7" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15259,7 +15251,7 @@
         <v>225</v>
       </c>
       <c r="B213" s="7" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C213" s="6" t="s">
         <v>28</v>
@@ -15271,7 +15263,7 @@
         <v>1170</v>
       </c>
       <c r="F213" s="7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G213" s="9" t="n">
         <v>1800</v>
@@ -15311,7 +15303,7 @@
         <v>24</v>
       </c>
       <c r="Q213" s="7" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="R213" s="7" t="s">
         <v>31</v>
@@ -15322,7 +15314,7 @@
         <v>226</v>
       </c>
       <c r="B214" s="7" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C214" s="6" t="s">
         <v>28</v>
@@ -15334,7 +15326,7 @@
         <v>1430</v>
       </c>
       <c r="F214" s="7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G214" s="9" t="n">
         <v>2600</v>
@@ -15374,7 +15366,7 @@
         <v>24</v>
       </c>
       <c r="Q214" s="7" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="R214" s="7" t="s">
         <v>31</v>
@@ -15385,7 +15377,7 @@
         <v>227</v>
       </c>
       <c r="B215" s="7" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C215" s="6" t="s">
         <v>28</v>
@@ -15397,7 +15389,7 @@
         <v>1820</v>
       </c>
       <c r="F215" s="7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G215" s="9" t="n">
         <v>3500</v>
@@ -15437,7 +15429,7 @@
         <v>24</v>
       </c>
       <c r="Q215" s="7" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="R215" s="7" t="s">
         <v>31</v>
@@ -15448,7 +15440,7 @@
         <v>228</v>
       </c>
       <c r="B216" s="7" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C216" s="6" t="s">
         <v>28</v>
@@ -15460,7 +15452,7 @@
         <v>2860</v>
       </c>
       <c r="F216" s="7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G216" s="9" t="n">
         <v>6000</v>
@@ -15500,7 +15492,7 @@
         <v>24</v>
       </c>
       <c r="Q216" s="7" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="R216" s="7" t="s">
         <v>31</v>
@@ -15511,7 +15503,7 @@
         <v>229</v>
       </c>
       <c r="B217" s="7" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C217" s="6" t="s">
         <v>28</v>
@@ -15523,7 +15515,7 @@
         <v>2340</v>
       </c>
       <c r="F217" s="7" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G217" s="9" t="n">
         <v>3200</v>
@@ -15563,7 +15555,7 @@
         <v>24</v>
       </c>
       <c r="Q217" s="7" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="R217" s="7" t="s">
         <v>31</v>
@@ -15574,7 +15566,7 @@
         <v>230</v>
       </c>
       <c r="B218" s="7" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C218" s="6" t="s">
         <v>28</v>
@@ -15586,7 +15578,7 @@
         <v>9750</v>
       </c>
       <c r="F218" s="7" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G218" s="9" t="n">
         <v>6000</v>
@@ -15626,10 +15618,10 @@
         <v>24</v>
       </c>
       <c r="Q218" s="7" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="R218" s="7" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15637,7 +15629,7 @@
         <v>231</v>
       </c>
       <c r="B219" s="7" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C219" s="6" t="s">
         <v>28</v>
@@ -15649,7 +15641,7 @@
         <v>12350</v>
       </c>
       <c r="F219" s="7" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G219" s="9" t="n">
         <v>8000</v>
@@ -15689,10 +15681,10 @@
         <v>24</v>
       </c>
       <c r="Q219" s="7" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="R219" s="7" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15700,10 +15692,10 @@
         <v>233</v>
       </c>
       <c r="B220" s="7" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C220" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D220" s="6" t="n">
         <v>2</v>
@@ -15712,7 +15704,7 @@
         <v>52000</v>
       </c>
       <c r="F220" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G220" s="9" t="n">
         <v>40000</v>
@@ -15752,7 +15744,7 @@
         <v>43</v>
       </c>
       <c r="Q220" s="7" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="R220" s="7"/>
     </row>
@@ -15761,7 +15753,7 @@
         <v>234</v>
       </c>
       <c r="B221" s="7" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C221" s="6" t="s">
         <v>22</v>
@@ -15813,7 +15805,7 @@
         <v>51</v>
       </c>
       <c r="Q221" s="7" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="R221" s="7" t="s">
         <v>53</v>
@@ -15824,7 +15816,7 @@
         <v>235</v>
       </c>
       <c r="B222" s="7" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C222" s="6" t="s">
         <v>28</v>
@@ -15876,10 +15868,10 @@
         <v>24</v>
       </c>
       <c r="Q222" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R222" s="7" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15887,7 +15879,7 @@
         <v>236</v>
       </c>
       <c r="B223" s="7" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C223" s="6" t="s">
         <v>22</v>
@@ -15899,7 +15891,7 @@
         <v>2860</v>
       </c>
       <c r="F223" s="7" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="G223" s="9" t="n">
         <v>2400</v>
@@ -15939,10 +15931,10 @@
         <v>24</v>
       </c>
       <c r="Q223" s="7" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="R223" s="7" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15950,7 +15942,7 @@
         <v>237</v>
       </c>
       <c r="B224" s="7" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C224" s="6" t="s">
         <v>28</v>
@@ -16002,7 +15994,7 @@
         <v>24</v>
       </c>
       <c r="Q224" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="R224" s="7" t="s">
         <v>31</v>
@@ -16013,7 +16005,7 @@
         <v>238</v>
       </c>
       <c r="B225" s="7" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C225" s="6" t="s">
         <v>28</v>
@@ -16025,7 +16017,7 @@
         <v>8450</v>
       </c>
       <c r="F225" s="7" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="G225" s="9" t="n">
         <v>7800</v>
@@ -16065,7 +16057,7 @@
         <v>43</v>
       </c>
       <c r="Q225" s="7" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="R225" s="7"/>
     </row>
@@ -16074,10 +16066,10 @@
         <v>239</v>
       </c>
       <c r="B226" s="7" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D226" s="6" t="n">
         <v>50</v>
@@ -16086,7 +16078,7 @@
         <v>65000</v>
       </c>
       <c r="F226" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G226" s="9" t="n">
         <v>44000</v>
@@ -16126,7 +16118,7 @@
         <v>43</v>
       </c>
       <c r="Q226" s="7" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="R226" s="7"/>
     </row>
@@ -16135,7 +16127,7 @@
         <v>240</v>
       </c>
       <c r="B227" s="7" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C227" s="6" t="s">
         <v>28</v>
@@ -16187,15 +16179,15 @@
         <v>24</v>
       </c>
       <c r="Q227" s="7" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="R227" s="7" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B228" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="L228" s="11" t="n">
         <f aca="false">SUM(L6:L227)</f>
@@ -16203,11 +16195,11 @@
       </c>
       <c r="M228" s="11" t="n">
         <f aca="false">SUM(M6:M227)</f>
-        <v>15544820</v>
+        <v>15547300</v>
       </c>
       <c r="N228" s="11" t="n">
         <f aca="false">SUM(N6:N227)</f>
-        <v>12585567</v>
+        <v>12587727</v>
       </c>
     </row>
   </sheetData>
@@ -16256,12 +16248,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B3" s="11" t="n">
         <f aca="false">COUNTA('Rate Check'!A6:A227)</f>
@@ -16270,7 +16262,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B4" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"LOSS")</f>
@@ -16279,7 +16271,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B5" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"THIN / RISK")</f>
@@ -16288,7 +16280,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B6" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"OK")</f>
@@ -16297,7 +16289,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B7" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"OVERPRICED?")</f>
@@ -16306,7 +16298,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B8" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!O6:O227,"YES")</f>
@@ -16318,7 +16310,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B10" s="11" t="n">
         <f aca="false">'Rate Check'!L228</f>
@@ -16327,38 +16319,38 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B11" s="11" t="n">
         <f aca="false">'Rate Check'!N228</f>
-        <v>12585567</v>
+        <v>12587727</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B12" s="11" t="n">
         <f aca="false">B10-B11</f>
-        <v>-376059</v>
+        <v>-378219</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B13" s="14" t="n">
         <f aca="false">IF(B10=0,0,B12/B10)</f>
-        <v>-0.0308005040006526</v>
+        <v>-0.0309774153061696</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B14" s="11" t="n">
         <f aca="false">SUMPRODUCT(('Rate Check'!E6:E227&lt;'Rate Check'!H6:H227)*('Rate Check'!H6:H227-'Rate Check'!E6:E227)*'Rate Check'!D6:D227)</f>
-        <v>2755490</v>
+        <v>2757650</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16366,20 +16358,20 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B16" s="11" t="n">
         <f aca="false">'Rate Check'!M228</f>
-        <v>15544820</v>
+        <v>15547300</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B17" s="14" t="n">
         <f aca="false">IF(B16=0,0,(B16-B11)/B16)</f>
-        <v>0.190369074714278</v>
+        <v>0.190359290680697</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16387,29 +16379,29 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B19" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!P6:P227,"V")</f>
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B20" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!P6:P227,"S")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B21" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!P6:P227,"N")</f>
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -16437,247 +16429,247 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
   </sheetData>

--- a/quotes/PR-217-228/Quote_PR217_PR228_Rate_Check.xlsx
+++ b/quotes/PR-217-228/Quote_PR217_PR228_Rate_Check.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1381" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1381" uniqueCount="535">
   <si>
     <t xml:space="preserve">Zidane Corporation - Quote PR-217 &amp; PR-228: Brand + Buying Rate Check</t>
   </si>
@@ -192,7 +192,7 @@
     <t xml:space="preserve">DOUBLE OPEN END WRENCH 6 TO 32 (12 PCS SET)</t>
   </si>
   <si>
-    <t xml:space="preserve">toolsmart Licota; Ingco 12pc 9,899</t>
+    <t xml:space="preserve">toolsmart.pk Licota DOE 36x41 7,430 / 41x46 12,310 + offset ring singles 1,230-4,240 -&gt; 12pc 6-32 DOE ~85% of ring set</t>
   </si>
   <si>
     <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Harden 12630</t>
@@ -213,7 +213,7 @@
     <t xml:space="preserve">COMBINATION WRENCH 8 TO 32 (14 PCS SET)</t>
   </si>
   <si>
-    <t xml:space="preserve">toolsmart Licota 14pc combo 25,660</t>
+    <t xml:space="preserve">toolsmart.pk Licota 14pc European combination 5/16-1-1/4in (=8-32mm range) Rs 25,660</t>
   </si>
   <si>
     <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Tolsen 11780</t>
@@ -261,18 +261,21 @@
     <t xml:space="preserve">ALLEN HEX KEY 12MM</t>
   </si>
   <si>
-    <t xml:space="preserve">goldentools.ae Licota 12mm hex AED 250/20pc</t>
+    <t xml:space="preserve">goldentools.ae Licota 12mm hex AED 250/20pc (12.5 ea) x90; Licota PK/UAE ratio ~90 (calibrated: locking plier 10in 4,000/AED42, 143pc 104,750/AED1,200, pin punch 5,460/AED48, hex 9pc 4,400/AED45)</t>
   </si>
   <si>
     <t xml:space="preserve">ALLEN (HEX) KEY 14MM</t>
   </si>
   <si>
-    <t xml:space="preserve">goldentools.ae Licota 12mm hex scaled</t>
+    <t xml:space="preserve">goldentools.ae Licota hex 12mm scaled to 14mm x90</t>
   </si>
   <si>
     <t xml:space="preserve">ALLEN (HEX) KEY 16MM</t>
   </si>
   <si>
+    <t xml:space="preserve">goldentools.ae Licota hex 12mm scaled to 16mm x90</t>
+  </si>
+  <si>
     <t xml:space="preserve">CIRCLIP PLIER INTERNAL STRAIGHT 175MM</t>
   </si>
   <si>
@@ -291,7 +294,7 @@
     <t xml:space="preserve">CIRCLIP PLIER INTERNAL STRAIGHT 230MM</t>
   </si>
   <si>
-    <t xml:space="preserve">toolsmart.pk Licota 175mm snap ring set (2,913/pc) scaled to 230mm</t>
+    <t xml:space="preserve">goldentools.ae Licota snap ring set 4pc 175mm AED 212.5; toolsmart.pk same set 13,750 (3,438/pc) -&gt; 230mm +30%</t>
   </si>
   <si>
     <t xml:space="preserve">Online nahi mila - dealer quote chahiye. 230mm circlip</t>
@@ -309,7 +312,7 @@
     <t xml:space="preserve">PIPE WRENCH SIZE 10"</t>
   </si>
   <si>
-    <t xml:space="preserve">toolsmart.pk Licota 18in 9,620 / 14in 6,730 scaled</t>
+    <t xml:space="preserve">toolsmart.pk Licota ridgid pipe wrench 14in 7,940 / 18in 9,620 scaled to 10in</t>
   </si>
   <si>
     <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Total 1700</t>
@@ -318,6 +321,9 @@
     <t xml:space="preserve">PIPE WRENCH SIZE 12"</t>
   </si>
   <si>
+    <t xml:space="preserve">toolsmart.pk Licota ridgid pipe wrench 14in 7,940 / 18in 9,620 scaled to 12in</t>
+  </si>
+  <si>
     <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Harden 2850</t>
   </si>
   <si>
@@ -330,19 +336,25 @@
     <t xml:space="preserve">PIPE WRENCH SIZE 24"</t>
   </si>
   <si>
+    <t xml:space="preserve">toolsmart.pk Licota 18in 9,620 scaled; goldentools.ae Licota 48in AED 1,000</t>
+  </si>
+  <si>
     <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Harden 6560</t>
   </si>
   <si>
     <t xml:space="preserve">PIPE WRENCH SIZE 36"</t>
   </si>
   <si>
+    <t xml:space="preserve">toolsmart.pk Licota 18in 9,620 scaled; goldentools.ae Licota 48in AED 1,000 (x90=90,000)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Total 7900</t>
   </si>
   <si>
     <t xml:space="preserve">SLEDGE HAMMER 1 LBS WITH FIBREGLASS HANDLE</t>
   </si>
   <si>
-    <t xml:space="preserve">goldentools.ae Licota sledge 1500g AED 96 scaled to 1lb</t>
+    <t xml:space="preserve">goldentools.ae Licota sledge 1500g AED 96 / 2000g AED 110 -&gt; 1lb ~AED 65 x90</t>
   </si>
   <si>
     <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Total 2000</t>
@@ -351,7 +363,7 @@
     <t xml:space="preserve">SLEDGE HAMMER 3 LBS WITH FIBREGLASS HANDLE</t>
   </si>
   <si>
-    <t xml:space="preserve">goldentools.ae Licota sledge 1500g AED 96</t>
+    <t xml:space="preserve">goldentools.ae Licota sledge 1500g AED 96 x90 (3lb=1.36kg)</t>
   </si>
   <si>
     <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Harden 3380</t>
@@ -360,7 +372,7 @@
     <t xml:space="preserve">SOFT FACE DEAD BLOW HAMMER 50MM</t>
   </si>
   <si>
-    <t xml:space="preserve">goldentools.ae Licota dead blow 45mm AED 65</t>
+    <t xml:space="preserve">goldentools.ae Licota dead blow 45mm AED 65 -&gt; 50mm ~AED 72 x90</t>
   </si>
   <si>
     <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Harden 2450</t>
@@ -387,7 +399,7 @@
     <t xml:space="preserve">Bosch Professional GDS 18V-350</t>
   </si>
   <si>
-    <t xml:space="preserve">No PK listing; est from GDX/GDS range</t>
+    <t xml:space="preserve">bosch-pt.com.ph GDS 18V-350 bare PHP 5,915 x~5.6 (calibrated: GDS 18V-1000 PH 12,600 vs PK solo 70,000) + 2x4Ah battery &amp; charger</t>
   </si>
   <si>
     <t xml:space="preserve">Online nahi mila - dealer quote chahiye. GDS 18V-350</t>
@@ -402,7 +414,7 @@
     <t xml:space="preserve">HEX IMPACT ADAPTOR 1/2" FEMALE TO 1/4" FEMALE</t>
   </si>
   <si>
-    <t xml:space="preserve">goldentools.ae Licota AED x~100 (AED76 + PK import)</t>
+    <t xml:space="preserve">toolsmart.pk Licota impact adapter 3/8F x 1/2M 1,130 (similar)</t>
   </si>
   <si>
     <t xml:space="preserve">FLAT FILE 12"</t>
@@ -426,31 +438,37 @@
     <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED WITH HOOK BRAKE 21</t>
   </si>
   <si>
-    <t xml:space="preserve">goldentools.ae/amazon.ae Licota 6in 3-jaw AED 105-120 (~PKR 9k) scaled + import</t>
+    <t xml:space="preserve">goldentools.ae Licota 3-jaw 6in AED 120 / 4in AED 65 scaled x90</t>
   </si>
   <si>
     <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED WITH HOOK BRAK 250</t>
   </si>
   <si>
-    <t xml:space="preserve">goldentools.ae Licota pullers (scaled) + import</t>
+    <t xml:space="preserve">goldentools.ae Licota puller AED 120 (6in) scaled to 250mm x90</t>
   </si>
   <si>
     <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED 160 X 300 MM 5T</t>
   </si>
   <si>
+    <t xml:space="preserve">goldentools.ae Licota puller scaled to 160x300 5T x90</t>
+  </si>
+  <si>
     <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED 250 X 300 MM 7.5T</t>
   </si>
   <si>
+    <t xml:space="preserve">goldentools.ae Licota puller scaled to 250x300 7.5T x90</t>
+  </si>
+  <si>
     <t xml:space="preserve">INTERNAL EXTRACTOR WITH REINFORCED COLLAR</t>
   </si>
   <si>
-    <t xml:space="preserve">Licota catalogue; no PK listing</t>
+    <t xml:space="preserve">Licota internal extractor (ATB-1208 class) est x90</t>
   </si>
   <si>
     <t xml:space="preserve">MECHANICAL PULLER 3 ARMED 200X200</t>
   </si>
   <si>
-    <t xml:space="preserve">goldentools.ae Licota 3-jaw 6in AED 120 scaled to 8in</t>
+    <t xml:space="preserve">goldentools.ae Licota 3-jaw 6in AED 120 scaled to 8in (~AED 190) x90</t>
   </si>
   <si>
     <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Yato 8500</t>
@@ -459,7 +477,7 @@
     <t xml:space="preserve">MECHANICAL PULLER 3 ARMED 250X250</t>
   </si>
   <si>
-    <t xml:space="preserve">goldentools.ae Licota 3-jaw 6in AED 120 scaled to 10in</t>
+    <t xml:space="preserve">goldentools.ae Licota 3-jaw 6in AED 120 scaled to 10in (~AED 290) x90</t>
   </si>
   <si>
     <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Yato 19030</t>
@@ -486,7 +504,7 @@
     <t xml:space="preserve">AIR GREASE GUN 500CC</t>
   </si>
   <si>
-    <t xml:space="preserve">toolsmart Licota grease gun 7,760 (air premium)</t>
+    <t xml:space="preserve">goldentools.ae Licota hand grease gun AGH-10004H AED 120 (=toolsmart 7,760) -&gt; air gun ~1.5x</t>
   </si>
   <si>
     <t xml:space="preserve">Online nahi mila - dealer quote chahiye. air grease gun</t>
@@ -522,13 +540,16 @@
     <t xml:space="preserve">ALIGNING PRY BAR DIA 5/8" X 18" LENGTH</t>
   </si>
   <si>
+    <t xml:space="preserve">Licota pry bar (khmtools PH 4pc set) est x90</t>
+  </si>
+  <si>
     <t xml:space="preserve">Online nahi mila - dealer quote chahiye. pry bar</t>
   </si>
   <si>
     <t xml:space="preserve">ADJUSTABLE WRENCH 15"</t>
   </si>
   <si>
-    <t xml:space="preserve">toolsmart Licota 10" 5,310; Total 15" 3,700-3,890</t>
+    <t xml:space="preserve">toolsmart.pk Licota adjustable angle 10in 5,310-6,270 / goldentools.ae AED 85 -&gt; 15in ~2x</t>
   </si>
   <si>
     <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Total 3890</t>
@@ -765,6 +786,9 @@
     <t xml:space="preserve">SPIRIT LEVEL 1 METER</t>
   </si>
   <si>
+    <t xml:space="preserve">amjadhardware.com Yato YT-3022 600mm 2,800; speedextools.com Yato YT-3024 1000mm AED 41 x90</t>
+  </si>
+  <si>
     <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Total 3350</t>
   </si>
   <si>
@@ -1299,7 +1323,7 @@
     <t xml:space="preserve">Yato YT-17001</t>
   </si>
   <si>
-    <t xml:space="preserve">pakwheels 5T bottle jack 4,000-5,999; purchaser 8,390</t>
+    <t xml:space="preserve">speedextools/UAE Yato YT-17001 3T AED 59 x90</t>
   </si>
   <si>
     <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Ronix 5950</t>
@@ -1311,7 +1335,7 @@
     <t xml:space="preserve">Yato YT-17002</t>
   </si>
   <si>
-    <t xml:space="preserve">pakwheels 5,499-5,999 (generic); Yato premium</t>
+    <t xml:space="preserve">Yato YT-17002 5T EU EUR 26-30 / UAE ref x90</t>
   </si>
   <si>
     <t xml:space="preserve">CORDLESS SMALL ANGLE GRINDER 125MM EQUIVAL</t>
@@ -2882,14 +2906,14 @@
         <v>28</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>16000</v>
+        <v>23000</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>21000</v>
+        <v>27000</v>
       </c>
       <c r="I15" s="10" t="n">
         <f aca="false">IF(E15=0,0,(E15-H15)/E15)</f>
-        <v>-0.346153846153846</v>
+        <v>-0.730769230769231</v>
       </c>
       <c r="J15" s="6" t="str">
         <f aca="false">IF(E15&lt;G15,"LOSS",IF(E15&lt;H15*1.1,"THIN / RISK",IF(E15&gt;H15*1.8,"OVERPRICED?","OK")))</f>
@@ -2897,7 +2921,7 @@
       </c>
       <c r="K15" s="8" t="n">
         <f aca="false">IF(J15="OVERPRICED?",ROUND(H15*1.35,-1),MAX(E15,ROUND(H15*(1+$E$3),-1)))</f>
-        <v>24150</v>
+        <v>31050</v>
       </c>
       <c r="L15" s="8" t="n">
         <f aca="false">D15*E15</f>
@@ -2905,11 +2929,11 @@
       </c>
       <c r="M15" s="8" t="n">
         <f aca="false">D15*K15</f>
-        <v>96600</v>
+        <v>124200</v>
       </c>
       <c r="N15" s="8" t="n">
         <f aca="false">D15*H15</f>
-        <v>84000</v>
+        <v>108000</v>
       </c>
       <c r="O15" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C15,F15)),"","YES")</f>
@@ -3067,14 +3091,14 @@
         <v>28</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>24000</v>
+        <v>25660</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>30000</v>
+        <v>28000</v>
       </c>
       <c r="I18" s="10" t="n">
         <f aca="false">IF(E18=0,0,(E18-H18)/E18)</f>
-        <v>-0.357466063348416</v>
+        <v>-0.266968325791855</v>
       </c>
       <c r="J18" s="6" t="str">
         <f aca="false">IF(E18&lt;G18,"LOSS",IF(E18&lt;H18*1.1,"THIN / RISK",IF(E18&gt;H18*1.8,"OVERPRICED?","OK")))</f>
@@ -3082,7 +3106,7 @@
       </c>
       <c r="K18" s="8" t="n">
         <f aca="false">IF(J18="OVERPRICED?",ROUND(H18*1.35,-1),MAX(E18,ROUND(H18*(1+$E$3),-1)))</f>
-        <v>34500</v>
+        <v>32200</v>
       </c>
       <c r="L18" s="8" t="n">
         <f aca="false">D18*E18</f>
@@ -3090,11 +3114,11 @@
       </c>
       <c r="M18" s="8" t="n">
         <f aca="false">D18*K18</f>
-        <v>138000</v>
+        <v>128800</v>
       </c>
       <c r="N18" s="8" t="n">
         <f aca="false">D18*H18</f>
-        <v>120000</v>
+        <v>112000</v>
       </c>
       <c r="O18" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C18,F18)),"","YES")</f>
@@ -3478,7 +3502,7 @@
       </c>
       <c r="R24" s="7"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="n">
         <v>20</v>
       </c>
@@ -3498,14 +3522,14 @@
         <v>28</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>1100</v>
+        <v>1050</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>1300</v>
+        <v>1250</v>
       </c>
       <c r="I25" s="10" t="n">
         <f aca="false">IF(E25=0,0,(E25-H25)/E25)</f>
-        <v>-0.428571428571429</v>
+        <v>-0.373626373626374</v>
       </c>
       <c r="J25" s="6" t="str">
         <f aca="false">IF(E25&lt;G25,"LOSS",IF(E25&lt;H25*1.1,"THIN / RISK",IF(E25&gt;H25*1.8,"OVERPRICED?","OK")))</f>
@@ -3513,7 +3537,7 @@
       </c>
       <c r="K25" s="8" t="n">
         <f aca="false">IF(J25="OVERPRICED?",ROUND(H25*1.35,-1),MAX(E25,ROUND(H25*(1+$E$3),-1)))</f>
-        <v>1500</v>
+        <v>1440</v>
       </c>
       <c r="L25" s="8" t="n">
         <f aca="false">D25*E25</f>
@@ -3521,11 +3545,11 @@
       </c>
       <c r="M25" s="8" t="n">
         <f aca="false">D25*K25</f>
-        <v>4500</v>
+        <v>4320</v>
       </c>
       <c r="N25" s="8" t="n">
         <f aca="false">D25*H25</f>
-        <v>3900</v>
+        <v>3750</v>
       </c>
       <c r="O25" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C25,F25)),"","YES")</f>
@@ -3561,14 +3585,14 @@
         <v>28</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>1400</v>
+        <v>1350</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="I26" s="10" t="n">
         <f aca="false">IF(E26=0,0,(E26-H26)/E26)</f>
-        <v>-0.452991452991453</v>
+        <v>-0.367521367521368</v>
       </c>
       <c r="J26" s="6" t="str">
         <f aca="false">IF(E26&lt;G26,"LOSS",IF(E26&lt;H26*1.1,"THIN / RISK",IF(E26&gt;H26*1.8,"OVERPRICED?","OK")))</f>
@@ -3576,7 +3600,7 @@
       </c>
       <c r="K26" s="8" t="n">
         <f aca="false">IF(J26="OVERPRICED?",ROUND(H26*1.35,-1),MAX(E26,ROUND(H26*(1+$E$3),-1)))</f>
-        <v>1960</v>
+        <v>1840</v>
       </c>
       <c r="L26" s="8" t="n">
         <f aca="false">D26*E26</f>
@@ -3584,11 +3608,11 @@
       </c>
       <c r="M26" s="8" t="n">
         <f aca="false">D26*K26</f>
-        <v>5880</v>
+        <v>5520</v>
       </c>
       <c r="N26" s="8" t="n">
         <f aca="false">D26*H26</f>
-        <v>5100</v>
+        <v>4800</v>
       </c>
       <c r="O26" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C26,F26)),"","YES")</f>
@@ -3624,14 +3648,14 @@
         <v>28</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="I27" s="10" t="n">
         <f aca="false">IF(E27=0,0,(E27-H27)/E27)</f>
-        <v>-0.468531468531469</v>
+        <v>-0.398601398601399</v>
       </c>
       <c r="J27" s="6" t="str">
         <f aca="false">IF(E27&lt;G27,"LOSS",IF(E27&lt;H27*1.1,"THIN / RISK",IF(E27&gt;H27*1.8,"OVERPRICED?","OK")))</f>
@@ -3639,7 +3663,7 @@
       </c>
       <c r="K27" s="8" t="n">
         <f aca="false">IF(J27="OVERPRICED?",ROUND(H27*1.35,-1),MAX(E27,ROUND(H27*(1+$E$3),-1)))</f>
-        <v>2420</v>
+        <v>2300</v>
       </c>
       <c r="L27" s="8" t="n">
         <f aca="false">D27*E27</f>
@@ -3647,11 +3671,11 @@
       </c>
       <c r="M27" s="8" t="n">
         <f aca="false">D27*K27</f>
-        <v>7260</v>
+        <v>6900</v>
       </c>
       <c r="N27" s="8" t="n">
         <f aca="false">D27*H27</f>
-        <v>6300</v>
+        <v>6000</v>
       </c>
       <c r="O27" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C27,F27)),"","YES")</f>
@@ -3661,7 +3685,7 @@
         <v>24</v>
       </c>
       <c r="Q27" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="R27" s="7" t="s">
         <v>31</v>
@@ -3672,7 +3696,7 @@
         <v>23</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>28</v>
@@ -3724,7 +3748,7 @@
         <v>43</v>
       </c>
       <c r="Q28" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="R28" s="7"/>
     </row>
@@ -3733,7 +3757,7 @@
         <v>24</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>28</v>
@@ -3785,7 +3809,7 @@
         <v>43</v>
       </c>
       <c r="Q29" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="R29" s="7"/>
     </row>
@@ -3794,7 +3818,7 @@
         <v>25</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>28</v>
@@ -3846,7 +3870,7 @@
         <v>43</v>
       </c>
       <c r="Q30" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="R30" s="7"/>
     </row>
@@ -3855,7 +3879,7 @@
         <v>26</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>28</v>
@@ -3907,16 +3931,16 @@
         <v>43</v>
       </c>
       <c r="Q31" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="R31" s="7"/>
     </row>
-    <row r="32" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="n">
         <v>27</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>28</v>
@@ -3931,7 +3955,7 @@
         <v>28</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>4000</v>
+        <v>4300</v>
       </c>
       <c r="H32" s="9" t="n">
         <v>4800</v>
@@ -3968,18 +3992,18 @@
         <v>24</v>
       </c>
       <c r="Q32" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="R32" s="7" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="n">
         <v>28</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>28</v>
@@ -3994,7 +4018,7 @@
         <v>28</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>4000</v>
+        <v>4300</v>
       </c>
       <c r="H33" s="9" t="n">
         <v>4800</v>
@@ -4031,10 +4055,10 @@
         <v>24</v>
       </c>
       <c r="Q33" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="R33" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4042,7 +4066,7 @@
         <v>30</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>28</v>
@@ -4094,7 +4118,7 @@
         <v>43</v>
       </c>
       <c r="Q34" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R34" s="7"/>
     </row>
@@ -4103,7 +4127,7 @@
         <v>31</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>28</v>
@@ -4118,14 +4142,14 @@
         <v>28</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>4000</v>
+        <v>5300</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>4500</v>
+        <v>5800</v>
       </c>
       <c r="I35" s="10" t="n">
         <f aca="false">IF(E35=0,0,(E35-H35)/E35)</f>
-        <v>-1.03619909502262</v>
+        <v>-1.62443438914027</v>
       </c>
       <c r="J35" s="6" t="str">
         <f aca="false">IF(E35&lt;G35,"LOSS",IF(E35&lt;H35*1.1,"THIN / RISK",IF(E35&gt;H35*1.8,"OVERPRICED?","OK")))</f>
@@ -4133,7 +4157,7 @@
       </c>
       <c r="K35" s="8" t="n">
         <f aca="false">IF(J35="OVERPRICED?",ROUND(H35*1.35,-1),MAX(E35,ROUND(H35*(1+$E$3),-1)))</f>
-        <v>5180</v>
+        <v>6670</v>
       </c>
       <c r="L35" s="8" t="n">
         <f aca="false">D35*E35</f>
@@ -4141,11 +4165,11 @@
       </c>
       <c r="M35" s="8" t="n">
         <f aca="false">D35*K35</f>
-        <v>15540</v>
+        <v>20010</v>
       </c>
       <c r="N35" s="8" t="n">
         <f aca="false">D35*H35</f>
-        <v>13500</v>
+        <v>17400</v>
       </c>
       <c r="O35" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C35,F35)),"","YES")</f>
@@ -4155,10 +4179,10 @@
         <v>24</v>
       </c>
       <c r="Q35" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="R35" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4166,7 +4190,7 @@
         <v>32</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>28</v>
@@ -4181,14 +4205,14 @@
         <v>28</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>5200</v>
+        <v>6300</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>5800</v>
+        <v>6800</v>
       </c>
       <c r="I36" s="10" t="n">
         <f aca="false">IF(E36=0,0,(E36-H36)/E36)</f>
-        <v>-1.00970200970201</v>
+        <v>-1.35620235620236</v>
       </c>
       <c r="J36" s="6" t="str">
         <f aca="false">IF(E36&lt;G36,"LOSS",IF(E36&lt;H36*1.1,"THIN / RISK",IF(E36&gt;H36*1.8,"OVERPRICED?","OK")))</f>
@@ -4196,7 +4220,7 @@
       </c>
       <c r="K36" s="8" t="n">
         <f aca="false">IF(J36="OVERPRICED?",ROUND(H36*1.35,-1),MAX(E36,ROUND(H36*(1+$E$3),-1)))</f>
-        <v>6670</v>
+        <v>7820</v>
       </c>
       <c r="L36" s="8" t="n">
         <f aca="false">D36*E36</f>
@@ -4204,11 +4228,11 @@
       </c>
       <c r="M36" s="8" t="n">
         <f aca="false">D36*K36</f>
-        <v>20010</v>
+        <v>23460</v>
       </c>
       <c r="N36" s="8" t="n">
         <f aca="false">D36*H36</f>
-        <v>17400</v>
+        <v>20400</v>
       </c>
       <c r="O36" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C36,F36)),"","YES")</f>
@@ -4218,10 +4242,10 @@
         <v>24</v>
       </c>
       <c r="Q36" s="7" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="R36" s="7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4229,7 +4253,7 @@
         <v>33</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>28</v>
@@ -4281,7 +4305,7 @@
         <v>43</v>
       </c>
       <c r="Q37" s="7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="R37" s="7"/>
     </row>
@@ -4290,7 +4314,7 @@
         <v>34</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>28</v>
@@ -4308,11 +4332,11 @@
         <v>14000</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>15500</v>
+        <v>16000</v>
       </c>
       <c r="I38" s="10" t="n">
         <f aca="false">IF(E38=0,0,(E38-H38)/E38)</f>
-        <v>-1.53267973856209</v>
+        <v>-1.61437908496732</v>
       </c>
       <c r="J38" s="6" t="str">
         <f aca="false">IF(E38&lt;G38,"LOSS",IF(E38&lt;H38*1.1,"THIN / RISK",IF(E38&gt;H38*1.8,"OVERPRICED?","OK")))</f>
@@ -4320,7 +4344,7 @@
       </c>
       <c r="K38" s="8" t="n">
         <f aca="false">IF(J38="OVERPRICED?",ROUND(H38*1.35,-1),MAX(E38,ROUND(H38*(1+$E$3),-1)))</f>
-        <v>17830</v>
+        <v>18400</v>
       </c>
       <c r="L38" s="8" t="n">
         <f aca="false">D38*E38</f>
@@ -4328,11 +4352,11 @@
       </c>
       <c r="M38" s="8" t="n">
         <f aca="false">D38*K38</f>
-        <v>35660</v>
+        <v>36800</v>
       </c>
       <c r="N38" s="8" t="n">
         <f aca="false">D38*H38</f>
-        <v>31000</v>
+        <v>32000</v>
       </c>
       <c r="O38" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C38,F38)),"","YES")</f>
@@ -4342,10 +4366,10 @@
         <v>24</v>
       </c>
       <c r="Q38" s="7" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="R38" s="7" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4353,7 +4377,7 @@
         <v>35</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>28</v>
@@ -4368,14 +4392,14 @@
         <v>28</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>26000</v>
+        <v>30000</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>29000</v>
+        <v>36000</v>
       </c>
       <c r="I39" s="10" t="n">
         <f aca="false">IF(E39=0,0,(E39-H39)/E39)</f>
-        <v>-1.25330225330225</v>
+        <v>-1.7972027972028</v>
       </c>
       <c r="J39" s="6" t="str">
         <f aca="false">IF(E39&lt;G39,"LOSS",IF(E39&lt;H39*1.1,"THIN / RISK",IF(E39&gt;H39*1.8,"OVERPRICED?","OK")))</f>
@@ -4383,7 +4407,7 @@
       </c>
       <c r="K39" s="8" t="n">
         <f aca="false">IF(J39="OVERPRICED?",ROUND(H39*1.35,-1),MAX(E39,ROUND(H39*(1+$E$3),-1)))</f>
-        <v>33350</v>
+        <v>41400</v>
       </c>
       <c r="L39" s="8" t="n">
         <f aca="false">D39*E39</f>
@@ -4391,11 +4415,11 @@
       </c>
       <c r="M39" s="8" t="n">
         <f aca="false">D39*K39</f>
-        <v>66700</v>
+        <v>82800</v>
       </c>
       <c r="N39" s="8" t="n">
         <f aca="false">D39*H39</f>
-        <v>58000</v>
+        <v>72000</v>
       </c>
       <c r="O39" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C39,F39)),"","YES")</f>
@@ -4405,10 +4429,10 @@
         <v>24</v>
       </c>
       <c r="Q39" s="7" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="R39" s="7" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4416,7 +4440,7 @@
         <v>36</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>28</v>
@@ -4431,14 +4455,14 @@
         <v>28</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>5000</v>
+        <v>5400</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>6000</v>
+        <v>6300</v>
       </c>
       <c r="I40" s="10" t="n">
         <f aca="false">IF(E40=0,0,(E40-H40)/E40)</f>
-        <v>-2.07692307692308</v>
+        <v>-2.23076923076923</v>
       </c>
       <c r="J40" s="6" t="str">
         <f aca="false">IF(E40&lt;G40,"LOSS",IF(E40&lt;H40*1.1,"THIN / RISK",IF(E40&gt;H40*1.8,"OVERPRICED?","OK")))</f>
@@ -4446,7 +4470,7 @@
       </c>
       <c r="K40" s="8" t="n">
         <f aca="false">IF(J40="OVERPRICED?",ROUND(H40*1.35,-1),MAX(E40,ROUND(H40*(1+$E$3),-1)))</f>
-        <v>6900</v>
+        <v>7250</v>
       </c>
       <c r="L40" s="8" t="n">
         <f aca="false">D40*E40</f>
@@ -4454,11 +4478,11 @@
       </c>
       <c r="M40" s="8" t="n">
         <f aca="false">D40*K40</f>
-        <v>20700</v>
+        <v>21750</v>
       </c>
       <c r="N40" s="8" t="n">
         <f aca="false">D40*H40</f>
-        <v>18000</v>
+        <v>18900</v>
       </c>
       <c r="O40" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C40,F40)),"","YES")</f>
@@ -4468,10 +4492,10 @@
         <v>24</v>
       </c>
       <c r="Q40" s="7" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="R40" s="7" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4479,7 +4503,7 @@
         <v>37</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>28</v>
@@ -4494,7 +4518,7 @@
         <v>28</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>8500</v>
+        <v>8200</v>
       </c>
       <c r="H41" s="9" t="n">
         <v>9500</v>
@@ -4531,10 +4555,10 @@
         <v>24</v>
       </c>
       <c r="Q41" s="7" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="R41" s="7" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4542,7 +4566,7 @@
         <v>38</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>28</v>
@@ -4557,22 +4581,22 @@
         <v>28</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>6500</v>
+        <v>6000</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>7500</v>
+        <v>7000</v>
       </c>
       <c r="I42" s="10" t="n">
         <f aca="false">IF(E42=0,0,(E42-H42)/E42)</f>
-        <v>-0.201923076923077</v>
+        <v>-0.121794871794872</v>
       </c>
       <c r="J42" s="6" t="str">
         <f aca="false">IF(E42&lt;G42,"LOSS",IF(E42&lt;H42*1.1,"THIN / RISK",IF(E42&gt;H42*1.8,"OVERPRICED?","OK")))</f>
-        <v>LOSS</v>
+        <v>THIN / RISK</v>
       </c>
       <c r="K42" s="8" t="n">
         <f aca="false">IF(J42="OVERPRICED?",ROUND(H42*1.35,-1),MAX(E42,ROUND(H42*(1+$E$3),-1)))</f>
-        <v>8630</v>
+        <v>8050</v>
       </c>
       <c r="L42" s="8" t="n">
         <f aca="false">D42*E42</f>
@@ -4580,11 +4604,11 @@
       </c>
       <c r="M42" s="8" t="n">
         <f aca="false">D42*K42</f>
-        <v>25890</v>
+        <v>24150</v>
       </c>
       <c r="N42" s="8" t="n">
         <f aca="false">D42*H42</f>
-        <v>22500</v>
+        <v>21000</v>
       </c>
       <c r="O42" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C42,F42)),"","YES")</f>
@@ -4594,10 +4618,10 @@
         <v>24</v>
       </c>
       <c r="Q42" s="7" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="R42" s="7" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4605,7 +4629,7 @@
         <v>39</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>28</v>
@@ -4657,7 +4681,7 @@
         <v>51</v>
       </c>
       <c r="Q43" s="7" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="R43" s="7" t="s">
         <v>53</v>
@@ -4668,10 +4692,10 @@
         <v>40</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D44" s="6" t="n">
         <v>3</v>
@@ -4680,7 +4704,7 @@
         <v>79300</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G44" s="9" t="n">
         <v>79000</v>
@@ -4720,19 +4744,19 @@
         <v>43</v>
       </c>
       <c r="Q44" s="7" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="R44" s="7"/>
     </row>
-    <row r="45" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="n">
         <v>41</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>3</v>
@@ -4741,25 +4765,25 @@
         <v>128700</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>95000</v>
+        <v>80000</v>
       </c>
       <c r="H45" s="9" t="n">
-        <v>140000</v>
+        <v>100000</v>
       </c>
       <c r="I45" s="10" t="n">
         <f aca="false">IF(E45=0,0,(E45-H45)/E45)</f>
-        <v>-0.0878010878010878</v>
+        <v>0.222999222999223</v>
       </c>
       <c r="J45" s="6" t="str">
         <f aca="false">IF(E45&lt;G45,"LOSS",IF(E45&lt;H45*1.1,"THIN / RISK",IF(E45&gt;H45*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>OK</v>
       </c>
       <c r="K45" s="8" t="n">
         <f aca="false">IF(J45="OVERPRICED?",ROUND(H45*1.35,-1),MAX(E45,ROUND(H45*(1+$E$3),-1)))</f>
-        <v>161000</v>
+        <v>128700</v>
       </c>
       <c r="L45" s="8" t="n">
         <f aca="false">D45*E45</f>
@@ -4767,11 +4791,11 @@
       </c>
       <c r="M45" s="8" t="n">
         <f aca="false">D45*K45</f>
-        <v>483000</v>
+        <v>386100</v>
       </c>
       <c r="N45" s="8" t="n">
         <f aca="false">D45*H45</f>
-        <v>420000</v>
+        <v>300000</v>
       </c>
       <c r="O45" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C45,F45)),"","YES")</f>
@@ -4781,10 +4805,10 @@
         <v>24</v>
       </c>
       <c r="Q45" s="7" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="R45" s="7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4792,10 +4816,10 @@
         <v>42</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D46" s="6" t="n">
         <v>2</v>
@@ -4804,7 +4828,7 @@
         <v>106600</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G46" s="9" t="n">
         <v>143800</v>
@@ -4844,7 +4868,7 @@
         <v>43</v>
       </c>
       <c r="Q46" s="7" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="R46" s="7"/>
     </row>
@@ -4853,7 +4877,7 @@
         <v>43</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>28</v>
@@ -4868,22 +4892,22 @@
         <v>28</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>1800</v>
+        <v>1300</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>2200</v>
+        <v>1600</v>
       </c>
       <c r="I47" s="10" t="n">
         <f aca="false">IF(E47=0,0,(E47-H47)/E47)</f>
-        <v>-0.41025641025641</v>
+        <v>-0.0256410256410256</v>
       </c>
       <c r="J47" s="6" t="str">
         <f aca="false">IF(E47&lt;G47,"LOSS",IF(E47&lt;H47*1.1,"THIN / RISK",IF(E47&gt;H47*1.8,"OVERPRICED?","OK")))</f>
-        <v>LOSS</v>
+        <v>THIN / RISK</v>
       </c>
       <c r="K47" s="8" t="n">
         <f aca="false">IF(J47="OVERPRICED?",ROUND(H47*1.35,-1),MAX(E47,ROUND(H47*(1+$E$3),-1)))</f>
-        <v>2530</v>
+        <v>1840</v>
       </c>
       <c r="L47" s="8" t="n">
         <f aca="false">D47*E47</f>
@@ -4891,11 +4915,11 @@
       </c>
       <c r="M47" s="8" t="n">
         <f aca="false">D47*K47</f>
-        <v>10120</v>
+        <v>7360</v>
       </c>
       <c r="N47" s="8" t="n">
         <f aca="false">D47*H47</f>
-        <v>8800</v>
+        <v>6400</v>
       </c>
       <c r="O47" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C47,F47)),"","YES")</f>
@@ -4905,7 +4929,7 @@
         <v>24</v>
       </c>
       <c r="Q47" s="7" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="R47" s="7" t="s">
         <v>31</v>
@@ -4916,7 +4940,7 @@
         <v>44</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>28</v>
@@ -4928,7 +4952,7 @@
         <v>1950</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G48" s="9" t="n">
         <v>1750</v>
@@ -4968,7 +4992,7 @@
         <v>43</v>
       </c>
       <c r="Q48" s="7" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="R48" s="7"/>
     </row>
@@ -4977,7 +5001,7 @@
         <v>45</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>28</v>
@@ -4989,7 +5013,7 @@
         <v>2210</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G49" s="9" t="n">
         <v>1750</v>
@@ -5029,10 +5053,10 @@
         <v>24</v>
       </c>
       <c r="Q49" s="7" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="R49" s="7" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5040,7 +5064,7 @@
         <v>47</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>28</v>
@@ -5055,22 +5079,22 @@
         <v>28</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>16000</v>
+        <v>20000</v>
       </c>
       <c r="I50" s="10" t="n">
         <f aca="false">IF(E50=0,0,(E50-H50)/E50)</f>
-        <v>-0.230769230769231</v>
+        <v>-0.538461538461538</v>
       </c>
       <c r="J50" s="6" t="str">
         <f aca="false">IF(E50&lt;G50,"LOSS",IF(E50&lt;H50*1.1,"THIN / RISK",IF(E50&gt;H50*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>LOSS</v>
       </c>
       <c r="K50" s="8" t="n">
         <f aca="false">IF(J50="OVERPRICED?",ROUND(H50*1.35,-1),MAX(E50,ROUND(H50*(1+$E$3),-1)))</f>
-        <v>18400</v>
+        <v>23000</v>
       </c>
       <c r="L50" s="8" t="n">
         <f aca="false">D50*E50</f>
@@ -5078,11 +5102,11 @@
       </c>
       <c r="M50" s="8" t="n">
         <f aca="false">D50*K50</f>
-        <v>55200</v>
+        <v>69000</v>
       </c>
       <c r="N50" s="8" t="n">
         <f aca="false">D50*H50</f>
-        <v>48000</v>
+        <v>60000</v>
       </c>
       <c r="O50" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C50,F50)),"","YES")</f>
@@ -5092,7 +5116,7 @@
         <v>24</v>
       </c>
       <c r="Q50" s="7" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="R50" s="7" t="s">
         <v>31</v>
@@ -5103,7 +5127,7 @@
         <v>48</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>28</v>
@@ -5118,14 +5142,14 @@
         <v>28</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>16000</v>
+        <v>20000</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>24000</v>
+        <v>26000</v>
       </c>
       <c r="I51" s="10" t="n">
         <f aca="false">IF(E51=0,0,(E51-H51)/E51)</f>
-        <v>-0.538461538461538</v>
+        <v>-0.666666666666667</v>
       </c>
       <c r="J51" s="6" t="str">
         <f aca="false">IF(E51&lt;G51,"LOSS",IF(E51&lt;H51*1.1,"THIN / RISK",IF(E51&gt;H51*1.8,"OVERPRICED?","OK")))</f>
@@ -5133,7 +5157,7 @@
       </c>
       <c r="K51" s="8" t="n">
         <f aca="false">IF(J51="OVERPRICED?",ROUND(H51*1.35,-1),MAX(E51,ROUND(H51*(1+$E$3),-1)))</f>
-        <v>27600</v>
+        <v>29900</v>
       </c>
       <c r="L51" s="8" t="n">
         <f aca="false">D51*E51</f>
@@ -5141,11 +5165,11 @@
       </c>
       <c r="M51" s="8" t="n">
         <f aca="false">D51*K51</f>
-        <v>55200</v>
+        <v>59800</v>
       </c>
       <c r="N51" s="8" t="n">
         <f aca="false">D51*H51</f>
-        <v>48000</v>
+        <v>52000</v>
       </c>
       <c r="O51" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C51,F51)),"","YES")</f>
@@ -5155,18 +5179,18 @@
         <v>24</v>
       </c>
       <c r="Q51" s="7" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="R51" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="n">
         <v>49</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>28</v>
@@ -5181,22 +5205,22 @@
         <v>28</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>20000</v>
+        <v>24000</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>28000</v>
+        <v>30000</v>
       </c>
       <c r="I52" s="10" t="n">
         <f aca="false">IF(E52=0,0,(E52-H52)/E52)</f>
-        <v>-0.346153846153846</v>
+        <v>-0.442307692307692</v>
       </c>
       <c r="J52" s="6" t="str">
         <f aca="false">IF(E52&lt;G52,"LOSS",IF(E52&lt;H52*1.1,"THIN / RISK",IF(E52&gt;H52*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>LOSS</v>
       </c>
       <c r="K52" s="8" t="n">
         <f aca="false">IF(J52="OVERPRICED?",ROUND(H52*1.35,-1),MAX(E52,ROUND(H52*(1+$E$3),-1)))</f>
-        <v>32200</v>
+        <v>34500</v>
       </c>
       <c r="L52" s="8" t="n">
         <f aca="false">D52*E52</f>
@@ -5204,11 +5228,11 @@
       </c>
       <c r="M52" s="8" t="n">
         <f aca="false">D52*K52</f>
-        <v>32200</v>
+        <v>34500</v>
       </c>
       <c r="N52" s="8" t="n">
         <f aca="false">D52*H52</f>
-        <v>28000</v>
+        <v>30000</v>
       </c>
       <c r="O52" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C52,F52)),"","YES")</f>
@@ -5218,18 +5242,18 @@
         <v>24</v>
       </c>
       <c r="Q52" s="7" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="R52" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="n">
         <v>50</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>28</v>
@@ -5244,22 +5268,22 @@
         <v>28</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>28000</v>
+        <v>32000</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>38000</v>
+        <v>40000</v>
       </c>
       <c r="I53" s="10" t="n">
         <f aca="false">IF(E53=0,0,(E53-H53)/E53)</f>
-        <v>-0.328671328671329</v>
+        <v>-0.398601398601399</v>
       </c>
       <c r="J53" s="6" t="str">
         <f aca="false">IF(E53&lt;G53,"LOSS",IF(E53&lt;H53*1.1,"THIN / RISK",IF(E53&gt;H53*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>LOSS</v>
       </c>
       <c r="K53" s="8" t="n">
         <f aca="false">IF(J53="OVERPRICED?",ROUND(H53*1.35,-1),MAX(E53,ROUND(H53*(1+$E$3),-1)))</f>
-        <v>43700</v>
+        <v>46000</v>
       </c>
       <c r="L53" s="8" t="n">
         <f aca="false">D53*E53</f>
@@ -5267,11 +5291,11 @@
       </c>
       <c r="M53" s="8" t="n">
         <f aca="false">D53*K53</f>
-        <v>43700</v>
+        <v>46000</v>
       </c>
       <c r="N53" s="8" t="n">
         <f aca="false">D53*H53</f>
-        <v>38000</v>
+        <v>40000</v>
       </c>
       <c r="O53" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C53,F53)),"","YES")</f>
@@ -5281,7 +5305,7 @@
         <v>24</v>
       </c>
       <c r="Q53" s="7" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="R53" s="7" t="s">
         <v>31</v>
@@ -5292,7 +5316,7 @@
         <v>51</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>28</v>
@@ -5307,14 +5331,14 @@
         <v>28</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>30000</v>
+        <v>32000</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>45000</v>
+        <v>42000</v>
       </c>
       <c r="I54" s="10" t="n">
         <f aca="false">IF(E54=0,0,(E54-H54)/E54)</f>
-        <v>-0.384615384615385</v>
+        <v>-0.292307692307692</v>
       </c>
       <c r="J54" s="6" t="str">
         <f aca="false">IF(E54&lt;G54,"LOSS",IF(E54&lt;H54*1.1,"THIN / RISK",IF(E54&gt;H54*1.8,"OVERPRICED?","OK")))</f>
@@ -5322,7 +5346,7 @@
       </c>
       <c r="K54" s="8" t="n">
         <f aca="false">IF(J54="OVERPRICED?",ROUND(H54*1.35,-1),MAX(E54,ROUND(H54*(1+$E$3),-1)))</f>
-        <v>51750</v>
+        <v>48300</v>
       </c>
       <c r="L54" s="8" t="n">
         <f aca="false">D54*E54</f>
@@ -5330,11 +5354,11 @@
       </c>
       <c r="M54" s="8" t="n">
         <f aca="false">D54*K54</f>
-        <v>51750</v>
+        <v>48300</v>
       </c>
       <c r="N54" s="8" t="n">
         <f aca="false">D54*H54</f>
-        <v>45000</v>
+        <v>42000</v>
       </c>
       <c r="O54" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C54,F54)),"","YES")</f>
@@ -5344,7 +5368,7 @@
         <v>24</v>
       </c>
       <c r="Q54" s="7" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="R54" s="7" t="s">
         <v>31</v>
@@ -5355,7 +5379,7 @@
         <v>52</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>28</v>
@@ -5370,14 +5394,14 @@
         <v>28</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>17000</v>
+        <v>16000</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>20000</v>
+        <v>19000</v>
       </c>
       <c r="I55" s="10" t="n">
         <f aca="false">IF(E55=0,0,(E55-H55)/E55)</f>
-        <v>-0.0989010989010989</v>
+        <v>-0.043956043956044</v>
       </c>
       <c r="J55" s="6" t="str">
         <f aca="false">IF(E55&lt;G55,"LOSS",IF(E55&lt;H55*1.1,"THIN / RISK",IF(E55&gt;H55*1.8,"OVERPRICED?","OK")))</f>
@@ -5385,7 +5409,7 @@
       </c>
       <c r="K55" s="8" t="n">
         <f aca="false">IF(J55="OVERPRICED?",ROUND(H55*1.35,-1),MAX(E55,ROUND(H55*(1+$E$3),-1)))</f>
-        <v>23000</v>
+        <v>21850</v>
       </c>
       <c r="L55" s="8" t="n">
         <f aca="false">D55*E55</f>
@@ -5393,11 +5417,11 @@
       </c>
       <c r="M55" s="8" t="n">
         <f aca="false">D55*K55</f>
-        <v>46000</v>
+        <v>43700</v>
       </c>
       <c r="N55" s="8" t="n">
         <f aca="false">D55*H55</f>
-        <v>40000</v>
+        <v>38000</v>
       </c>
       <c r="O55" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C55,F55)),"","YES")</f>
@@ -5407,10 +5431,10 @@
         <v>24</v>
       </c>
       <c r="Q55" s="7" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="R55" s="7" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5418,7 +5442,7 @@
         <v>53</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>28</v>
@@ -5433,14 +5457,14 @@
         <v>28</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>26000</v>
+        <v>24000</v>
       </c>
       <c r="H56" s="9" t="n">
-        <v>30000</v>
+        <v>28000</v>
       </c>
       <c r="I56" s="10" t="n">
         <f aca="false">IF(E56=0,0,(E56-H56)/E56)</f>
-        <v>-0.282051282051282</v>
+        <v>-0.196581196581197</v>
       </c>
       <c r="J56" s="6" t="str">
         <f aca="false">IF(E56&lt;G56,"LOSS",IF(E56&lt;H56*1.1,"THIN / RISK",IF(E56&gt;H56*1.8,"OVERPRICED?","OK")))</f>
@@ -5448,7 +5472,7 @@
       </c>
       <c r="K56" s="8" t="n">
         <f aca="false">IF(J56="OVERPRICED?",ROUND(H56*1.35,-1),MAX(E56,ROUND(H56*(1+$E$3),-1)))</f>
-        <v>34500</v>
+        <v>32200</v>
       </c>
       <c r="L56" s="8" t="n">
         <f aca="false">D56*E56</f>
@@ -5456,11 +5480,11 @@
       </c>
       <c r="M56" s="8" t="n">
         <f aca="false">D56*K56</f>
-        <v>34500</v>
+        <v>32200</v>
       </c>
       <c r="N56" s="8" t="n">
         <f aca="false">D56*H56</f>
-        <v>30000</v>
+        <v>28000</v>
       </c>
       <c r="O56" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C56,F56)),"","YES")</f>
@@ -5470,10 +5494,10 @@
         <v>24</v>
       </c>
       <c r="Q56" s="7" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="R56" s="7" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5481,10 +5505,10 @@
         <v>54</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D57" s="6" t="n">
         <v>2</v>
@@ -5493,7 +5517,7 @@
         <v>400946</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G57" s="9" t="n">
         <v>115000</v>
@@ -5533,7 +5557,7 @@
         <v>43</v>
       </c>
       <c r="Q57" s="7" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="R57" s="7"/>
     </row>
@@ -5542,7 +5566,7 @@
         <v>55</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>28</v>
@@ -5554,7 +5578,7 @@
         <v>15600</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="G58" s="9" t="n">
         <v>12000</v>
@@ -5594,10 +5618,10 @@
         <v>24</v>
       </c>
       <c r="Q58" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R58" s="7" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5605,7 +5629,7 @@
         <v>56</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>28</v>
@@ -5620,7 +5644,7 @@
         <v>28</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>9000</v>
+        <v>10000</v>
       </c>
       <c r="H59" s="9" t="n">
         <v>13000</v>
@@ -5657,10 +5681,10 @@
         <v>24</v>
       </c>
       <c r="Q59" s="7" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="R59" s="7" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5668,7 +5692,7 @@
         <v>57</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>28</v>
@@ -5720,7 +5744,7 @@
         <v>43</v>
       </c>
       <c r="Q60" s="7" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="R60" s="7"/>
     </row>
@@ -5729,7 +5753,7 @@
         <v>58</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>28</v>
@@ -5781,7 +5805,7 @@
         <v>24</v>
       </c>
       <c r="Q61" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R61" s="7" t="s">
         <v>31</v>
@@ -5792,7 +5816,7 @@
         <v>59</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>28</v>
@@ -5844,7 +5868,7 @@
         <v>24</v>
       </c>
       <c r="Q62" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R62" s="7" t="s">
         <v>31</v>
@@ -5855,7 +5879,7 @@
         <v>60</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>28</v>
@@ -5867,7 +5891,7 @@
         <v>9100</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G63" s="9" t="n">
         <v>8000</v>
@@ -5907,10 +5931,10 @@
         <v>24</v>
       </c>
       <c r="Q63" s="7" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="R63" s="7" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5918,7 +5942,7 @@
         <v>61</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>28</v>
@@ -5930,7 +5954,7 @@
         <v>5850</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G64" s="9" t="n">
         <v>5000</v>
@@ -5970,10 +5994,10 @@
         <v>24</v>
       </c>
       <c r="Q64" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R64" s="7" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5981,7 +6005,7 @@
         <v>62</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>28</v>
@@ -5996,7 +6020,7 @@
         <v>28</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>3000</v>
+        <v>3200</v>
       </c>
       <c r="H65" s="9" t="n">
         <v>4000</v>
@@ -6033,10 +6057,10 @@
         <v>24</v>
       </c>
       <c r="Q65" s="7" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="R65" s="7" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6044,7 +6068,7 @@
         <v>63</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>28</v>
@@ -6059,14 +6083,14 @@
         <v>28</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>9000</v>
+        <v>10500</v>
       </c>
       <c r="H66" s="9" t="n">
-        <v>11000</v>
+        <v>12500</v>
       </c>
       <c r="I66" s="10" t="n">
         <f aca="false">IF(E66=0,0,(E66-H66)/E66)</f>
-        <v>-0.981624932444605</v>
+        <v>-1.2518465141416</v>
       </c>
       <c r="J66" s="6" t="str">
         <f aca="false">IF(E66&lt;G66,"LOSS",IF(E66&lt;H66*1.1,"THIN / RISK",IF(E66&gt;H66*1.8,"OVERPRICED?","OK")))</f>
@@ -6074,7 +6098,7 @@
       </c>
       <c r="K66" s="8" t="n">
         <f aca="false">IF(J66="OVERPRICED?",ROUND(H66*1.35,-1),MAX(E66,ROUND(H66*(1+$E$3),-1)))</f>
-        <v>12650</v>
+        <v>14380</v>
       </c>
       <c r="L66" s="8" t="n">
         <f aca="false">D66*E66</f>
@@ -6082,11 +6106,11 @@
       </c>
       <c r="M66" s="8" t="n">
         <f aca="false">D66*K66</f>
-        <v>12650</v>
+        <v>14380</v>
       </c>
       <c r="N66" s="8" t="n">
         <f aca="false">D66*H66</f>
-        <v>11000</v>
+        <v>12500</v>
       </c>
       <c r="O66" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C66,F66)),"","YES")</f>
@@ -6096,10 +6120,10 @@
         <v>24</v>
       </c>
       <c r="Q66" s="7" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="R66" s="7" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6107,7 +6131,7 @@
         <v>64</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>28</v>
@@ -6119,7 +6143,7 @@
         <v>1560</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G67" s="9" t="n">
         <v>1350</v>
@@ -6159,7 +6183,7 @@
         <v>43</v>
       </c>
       <c r="Q67" s="7" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="R67" s="7"/>
     </row>
@@ -6168,7 +6192,7 @@
         <v>65</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>28</v>
@@ -6180,7 +6204,7 @@
         <v>1560</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G68" s="9" t="n">
         <v>1350</v>
@@ -6220,7 +6244,7 @@
         <v>43</v>
       </c>
       <c r="Q68" s="7" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="R68" s="7"/>
     </row>
@@ -6229,7 +6253,7 @@
         <v>66</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>28</v>
@@ -6241,7 +6265,7 @@
         <v>11700</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="G69" s="9" t="n">
         <v>14000</v>
@@ -6281,7 +6305,7 @@
         <v>24</v>
       </c>
       <c r="Q69" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R69" s="7" t="s">
         <v>31</v>
@@ -6292,7 +6316,7 @@
         <v>67</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>28</v>
@@ -6304,7 +6328,7 @@
         <v>9750</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="G70" s="9" t="n">
         <v>12000</v>
@@ -6344,7 +6368,7 @@
         <v>24</v>
       </c>
       <c r="Q70" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R70" s="7" t="s">
         <v>31</v>
@@ -6355,7 +6379,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>28</v>
@@ -6367,7 +6391,7 @@
         <v>23400</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="G71" s="9" t="n">
         <v>15000</v>
@@ -6407,7 +6431,7 @@
         <v>24</v>
       </c>
       <c r="Q71" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R71" s="7" t="s">
         <v>31</v>
@@ -6418,7 +6442,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>28</v>
@@ -6430,7 +6454,7 @@
         <v>32500</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="G72" s="9" t="n">
         <v>25000</v>
@@ -6470,7 +6494,7 @@
         <v>24</v>
       </c>
       <c r="Q72" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R72" s="7" t="s">
         <v>31</v>
@@ -6481,7 +6505,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>28</v>
@@ -6493,7 +6517,7 @@
         <v>1105</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G73" s="9" t="n">
         <v>800</v>
@@ -6533,10 +6557,10 @@
         <v>24</v>
       </c>
       <c r="Q73" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R73" s="7" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6544,7 +6568,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>28</v>
@@ -6556,7 +6580,7 @@
         <v>45500</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="G74" s="9" t="n">
         <v>35000</v>
@@ -6596,10 +6620,10 @@
         <v>24</v>
       </c>
       <c r="Q74" s="7" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="R74" s="7" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6607,7 +6631,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>28</v>
@@ -6619,7 +6643,7 @@
         <v>23400</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="G75" s="9" t="n">
         <v>45000</v>
@@ -6659,10 +6683,10 @@
         <v>24</v>
       </c>
       <c r="Q75" s="7" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="R75" s="7" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6670,7 +6694,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>28</v>
@@ -6682,7 +6706,7 @@
         <v>1950</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="G76" s="9" t="n">
         <v>9790</v>
@@ -6722,7 +6746,7 @@
         <v>24</v>
       </c>
       <c r="Q76" s="7" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="R76" s="7" t="s">
         <v>31</v>
@@ -6733,7 +6757,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>28</v>
@@ -6745,7 +6769,7 @@
         <v>2080</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="G77" s="9" t="n">
         <v>11060</v>
@@ -6785,7 +6809,7 @@
         <v>24</v>
       </c>
       <c r="Q77" s="7" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="R77" s="7" t="s">
         <v>31</v>
@@ -6796,7 +6820,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>28</v>
@@ -6808,7 +6832,7 @@
         <v>2210</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="G78" s="9" t="n">
         <v>11700</v>
@@ -6848,7 +6872,7 @@
         <v>24</v>
       </c>
       <c r="Q78" s="7" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="R78" s="7" t="s">
         <v>31</v>
@@ -6859,7 +6883,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>28</v>
@@ -6871,7 +6895,7 @@
         <v>2340</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="G79" s="9" t="n">
         <v>12330</v>
@@ -6911,7 +6935,7 @@
         <v>24</v>
       </c>
       <c r="Q79" s="7" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="R79" s="7" t="s">
         <v>31</v>
@@ -6922,7 +6946,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>28</v>
@@ -6934,7 +6958,7 @@
         <v>2470</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="G80" s="9" t="n">
         <v>12970</v>
@@ -6974,7 +6998,7 @@
         <v>24</v>
       </c>
       <c r="Q80" s="7" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="R80" s="7" t="s">
         <v>31</v>
@@ -6985,7 +7009,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>28</v>
@@ -6997,7 +7021,7 @@
         <v>2600</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="G81" s="9" t="n">
         <v>13600</v>
@@ -7037,7 +7061,7 @@
         <v>24</v>
       </c>
       <c r="Q81" s="7" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="R81" s="7" t="s">
         <v>31</v>
@@ -7048,7 +7072,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>28</v>
@@ -7060,7 +7084,7 @@
         <v>2730</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="G82" s="9" t="n">
         <v>14240</v>
@@ -7100,7 +7124,7 @@
         <v>24</v>
       </c>
       <c r="Q82" s="7" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="R82" s="7" t="s">
         <v>31</v>
@@ -7111,7 +7135,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>28</v>
@@ -7123,7 +7147,7 @@
         <v>3250</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="G83" s="9" t="n">
         <v>16140</v>
@@ -7163,7 +7187,7 @@
         <v>24</v>
       </c>
       <c r="Q83" s="7" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="R83" s="7" t="s">
         <v>31</v>
@@ -7174,7 +7198,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>28</v>
@@ -7186,7 +7210,7 @@
         <v>4160</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="G84" s="9" t="n">
         <v>19230</v>
@@ -7226,7 +7250,7 @@
         <v>24</v>
       </c>
       <c r="Q84" s="7" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="R84" s="7" t="s">
         <v>31</v>
@@ -7237,7 +7261,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>28</v>
@@ -7249,7 +7273,7 @@
         <v>5850</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="G85" s="9" t="n">
         <v>26490</v>
@@ -7289,7 +7313,7 @@
         <v>24</v>
       </c>
       <c r="Q85" s="7" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="R85" s="7" t="s">
         <v>31</v>
@@ -7300,7 +7324,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>28</v>
@@ -7312,7 +7336,7 @@
         <v>8450</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="G86" s="9" t="n">
         <v>38450</v>
@@ -7352,7 +7376,7 @@
         <v>24</v>
       </c>
       <c r="Q86" s="7" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="R86" s="7" t="s">
         <v>31</v>
@@ -7363,7 +7387,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>28</v>
@@ -7375,7 +7399,7 @@
         <v>9750</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="G87" s="9" t="n">
         <v>44060</v>
@@ -7415,7 +7439,7 @@
         <v>24</v>
       </c>
       <c r="Q87" s="7" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="R87" s="7" t="s">
         <v>31</v>
@@ -7426,7 +7450,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>28</v>
@@ -7438,7 +7462,7 @@
         <v>11700</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="G88" s="9" t="n">
         <v>52470</v>
@@ -7478,7 +7502,7 @@
         <v>24</v>
       </c>
       <c r="Q88" s="7" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="R88" s="7" t="s">
         <v>31</v>
@@ -7489,7 +7513,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>28</v>
@@ -7501,7 +7525,7 @@
         <v>4550</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="G89" s="9" t="n">
         <v>3500</v>
@@ -7541,7 +7565,7 @@
         <v>24</v>
       </c>
       <c r="Q89" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R89" s="7" t="s">
         <v>31</v>
@@ -7552,7 +7576,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>28</v>
@@ -7564,7 +7588,7 @@
         <v>5850</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="G90" s="9" t="n">
         <v>4500</v>
@@ -7604,7 +7628,7 @@
         <v>24</v>
       </c>
       <c r="Q90" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R90" s="7" t="s">
         <v>31</v>
@@ -7615,7 +7639,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>28</v>
@@ -7627,7 +7651,7 @@
         <v>7150</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="G91" s="9" t="n">
         <v>5500</v>
@@ -7667,7 +7691,7 @@
         <v>24</v>
       </c>
       <c r="Q91" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R91" s="7" t="s">
         <v>31</v>
@@ -7678,7 +7702,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>28</v>
@@ -7690,7 +7714,7 @@
         <v>2340</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="G92" s="9" t="n">
         <v>2500</v>
@@ -7730,7 +7754,7 @@
         <v>24</v>
       </c>
       <c r="Q92" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R92" s="7" t="s">
         <v>31</v>
@@ -7741,7 +7765,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>28</v>
@@ -7753,7 +7777,7 @@
         <v>2860</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="G93" s="9" t="n">
         <v>3000</v>
@@ -7793,7 +7817,7 @@
         <v>24</v>
       </c>
       <c r="Q93" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R93" s="7" t="s">
         <v>31</v>
@@ -7804,10 +7828,10 @@
         <v>93</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="D94" s="6" t="n">
         <v>2</v>
@@ -7816,7 +7840,7 @@
         <v>25350</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="G94" s="9" t="n">
         <v>18100</v>
@@ -7856,7 +7880,7 @@
         <v>43</v>
       </c>
       <c r="Q94" s="7" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="R94" s="7"/>
     </row>
@@ -7865,10 +7889,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="D95" s="6" t="n">
         <v>3</v>
@@ -7877,7 +7901,7 @@
         <v>8138</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="G95" s="9" t="n">
         <v>15800</v>
@@ -7917,7 +7941,7 @@
         <v>43</v>
       </c>
       <c r="Q95" s="7" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="R95" s="7"/>
     </row>
@@ -7926,10 +7950,10 @@
         <v>95</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="D96" s="6" t="n">
         <v>3</v>
@@ -7938,7 +7962,7 @@
         <v>6370</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="G96" s="9" t="n">
         <v>7928</v>
@@ -7978,7 +8002,7 @@
         <v>43</v>
       </c>
       <c r="Q96" s="7" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="R96" s="7"/>
     </row>
@@ -7987,7 +8011,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>28</v>
@@ -7999,7 +8023,7 @@
         <v>14950</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="G97" s="9" t="n">
         <v>15000</v>
@@ -8039,10 +8063,10 @@
         <v>24</v>
       </c>
       <c r="Q97" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R97" s="7" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8050,10 +8074,10 @@
         <v>97</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D98" s="6" t="n">
         <v>2</v>
@@ -8062,7 +8086,7 @@
         <v>286000</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G98" s="9" t="n">
         <v>199500</v>
@@ -8102,7 +8126,7 @@
         <v>51</v>
       </c>
       <c r="Q98" s="7" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="R98" s="7" t="s">
         <v>53</v>
@@ -8113,10 +8137,10 @@
         <v>98</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="D99" s="6" t="n">
         <v>1</v>
@@ -8125,7 +8149,7 @@
         <v>15600</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="G99" s="9" t="n">
         <v>12000</v>
@@ -8165,7 +8189,7 @@
         <v>24</v>
       </c>
       <c r="Q99" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R99" s="7" t="s">
         <v>31</v>
@@ -8176,7 +8200,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>28</v>
@@ -8188,7 +8212,7 @@
         <v>11050</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="G100" s="9" t="n">
         <v>8000</v>
@@ -8228,7 +8252,7 @@
         <v>24</v>
       </c>
       <c r="Q100" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R100" s="7" t="s">
         <v>31</v>
@@ -8239,7 +8263,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>28</v>
@@ -8251,7 +8275,7 @@
         <v>9100</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="G101" s="9" t="n">
         <v>6500</v>
@@ -8291,7 +8315,7 @@
         <v>24</v>
       </c>
       <c r="Q101" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R101" s="7" t="s">
         <v>31</v>
@@ -8302,7 +8326,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>28</v>
@@ -8314,7 +8338,7 @@
         <v>7150</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="G102" s="9" t="n">
         <v>5500</v>
@@ -8354,7 +8378,7 @@
         <v>24</v>
       </c>
       <c r="Q102" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R102" s="7" t="s">
         <v>31</v>
@@ -8365,7 +8389,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>28</v>
@@ -8377,7 +8401,7 @@
         <v>5850</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="G103" s="9" t="n">
         <v>4500</v>
@@ -8417,7 +8441,7 @@
         <v>24</v>
       </c>
       <c r="Q103" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R103" s="7" t="s">
         <v>31</v>
@@ -8428,7 +8452,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>22</v>
@@ -8480,7 +8504,7 @@
         <v>24</v>
       </c>
       <c r="Q104" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R104" s="7" t="s">
         <v>31</v>
@@ -8491,7 +8515,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>22</v>
@@ -8543,10 +8567,10 @@
         <v>24</v>
       </c>
       <c r="Q105" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R105" s="7" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8554,7 +8578,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>22</v>
@@ -8566,7 +8590,7 @@
         <v>1170</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="G106" s="9" t="n">
         <v>800</v>
@@ -8606,7 +8630,7 @@
         <v>43</v>
       </c>
       <c r="Q106" s="7" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="R106" s="7"/>
     </row>
@@ -8615,7 +8639,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>28</v>
@@ -8627,7 +8651,7 @@
         <v>3640</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G107" s="9" t="n">
         <v>2000</v>
@@ -8667,10 +8691,10 @@
         <v>24</v>
       </c>
       <c r="Q107" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R107" s="7" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8678,7 +8702,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>28</v>
@@ -8690,7 +8714,7 @@
         <v>6760</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G108" s="9" t="n">
         <v>4500</v>
@@ -8730,18 +8754,18 @@
         <v>24</v>
       </c>
       <c r="Q108" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R108" s="7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="6" t="n">
         <v>108</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>28</v>
@@ -8753,17 +8777,17 @@
         <v>4550</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>3500</v>
+        <v>3800</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>5000</v>
+        <v>4200</v>
       </c>
       <c r="I109" s="10" t="n">
         <f aca="false">IF(E109=0,0,(E109-H109)/E109)</f>
-        <v>-0.0989010989010989</v>
+        <v>0.0769230769230769</v>
       </c>
       <c r="J109" s="6" t="str">
         <f aca="false">IF(E109&lt;G109,"LOSS",IF(E109&lt;H109*1.1,"THIN / RISK",IF(E109&gt;H109*1.8,"OVERPRICED?","OK")))</f>
@@ -8771,7 +8795,7 @@
       </c>
       <c r="K109" s="8" t="n">
         <f aca="false">IF(J109="OVERPRICED?",ROUND(H109*1.35,-1),MAX(E109,ROUND(H109*(1+$E$3),-1)))</f>
-        <v>5750</v>
+        <v>4830</v>
       </c>
       <c r="L109" s="8" t="n">
         <f aca="false">D109*E109</f>
@@ -8779,11 +8803,11 @@
       </c>
       <c r="M109" s="8" t="n">
         <f aca="false">D109*K109</f>
-        <v>17250</v>
+        <v>14490</v>
       </c>
       <c r="N109" s="8" t="n">
         <f aca="false">D109*H109</f>
-        <v>15000</v>
+        <v>12600</v>
       </c>
       <c r="O109" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C109,F109)),"","YES")</f>
@@ -8793,10 +8817,10 @@
         <v>24</v>
       </c>
       <c r="Q109" s="7" t="s">
-        <v>150</v>
+        <v>253</v>
       </c>
       <c r="R109" s="7" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8804,7 +8828,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>28</v>
@@ -8816,7 +8840,7 @@
         <v>2340</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G110" s="9" t="n">
         <v>1800</v>
@@ -8856,10 +8880,10 @@
         <v>24</v>
       </c>
       <c r="Q110" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R110" s="7" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8867,7 +8891,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>28</v>
@@ -8879,7 +8903,7 @@
         <v>1820</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="G111" s="9" t="n">
         <v>2000</v>
@@ -8919,10 +8943,10 @@
         <v>24</v>
       </c>
       <c r="Q111" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R111" s="7" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8930,7 +8954,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>28</v>
@@ -8942,7 +8966,7 @@
         <v>2860</v>
       </c>
       <c r="F112" s="7" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="G112" s="9" t="n">
         <v>4000</v>
@@ -8982,10 +9006,10 @@
         <v>24</v>
       </c>
       <c r="Q112" s="7" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="R112" s="7" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8993,7 +9017,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>28</v>
@@ -9005,7 +9029,7 @@
         <v>12350</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="G113" s="9" t="n">
         <v>8000</v>
@@ -9045,10 +9069,10 @@
         <v>24</v>
       </c>
       <c r="Q113" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R113" s="7" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9056,7 +9080,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>28</v>
@@ -9108,7 +9132,7 @@
         <v>24</v>
       </c>
       <c r="Q114" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R114" s="7" t="s">
         <v>31</v>
@@ -9119,7 +9143,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>28</v>
@@ -9171,7 +9195,7 @@
         <v>24</v>
       </c>
       <c r="Q115" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R115" s="7" t="s">
         <v>31</v>
@@ -9182,7 +9206,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>22</v>
@@ -9194,7 +9218,7 @@
         <v>11050</v>
       </c>
       <c r="F116" s="7" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="G116" s="9" t="n">
         <v>5000</v>
@@ -9234,7 +9258,7 @@
         <v>43</v>
       </c>
       <c r="Q116" s="7" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="R116" s="7"/>
     </row>
@@ -9243,7 +9267,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>28</v>
@@ -9295,10 +9319,10 @@
         <v>24</v>
       </c>
       <c r="Q117" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R117" s="7" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9306,7 +9330,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>22</v>
@@ -9358,7 +9382,7 @@
         <v>24</v>
       </c>
       <c r="Q118" s="7" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="R118" s="7" t="s">
         <v>31</v>
@@ -9369,7 +9393,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>22</v>
@@ -9421,7 +9445,7 @@
         <v>24</v>
       </c>
       <c r="Q119" s="7" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="R119" s="7" t="s">
         <v>31</v>
@@ -9432,7 +9456,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>28</v>
@@ -9484,7 +9508,7 @@
         <v>24</v>
       </c>
       <c r="Q120" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R120" s="7" t="s">
         <v>31</v>
@@ -9495,7 +9519,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>22</v>
@@ -9547,7 +9571,7 @@
         <v>24</v>
       </c>
       <c r="Q121" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R121" s="7" t="s">
         <v>31</v>
@@ -9558,7 +9582,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>22</v>
@@ -9610,7 +9634,7 @@
         <v>43</v>
       </c>
       <c r="Q122" s="7" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="R122" s="7"/>
     </row>
@@ -9619,7 +9643,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>22</v>
@@ -9631,7 +9655,7 @@
         <v>357500</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="G123" s="9" t="n">
         <v>200000</v>
@@ -9671,10 +9695,10 @@
         <v>24</v>
       </c>
       <c r="Q123" s="7" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="R123" s="7" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9682,7 +9706,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="C124" s="6" t="s">
         <v>22</v>
@@ -9734,10 +9758,10 @@
         <v>24</v>
       </c>
       <c r="Q124" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R124" s="7" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9745,7 +9769,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>22</v>
@@ -9797,7 +9821,7 @@
         <v>24</v>
       </c>
       <c r="Q125" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R125" s="7" t="s">
         <v>31</v>
@@ -9808,7 +9832,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>22</v>
@@ -9860,7 +9884,7 @@
         <v>24</v>
       </c>
       <c r="Q126" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R126" s="7" t="s">
         <v>31</v>
@@ -9871,7 +9895,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>22</v>
@@ -9923,7 +9947,7 @@
         <v>24</v>
       </c>
       <c r="Q127" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R127" s="7" t="s">
         <v>31</v>
@@ -9934,7 +9958,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>22</v>
@@ -9986,7 +10010,7 @@
         <v>24</v>
       </c>
       <c r="Q128" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R128" s="7" t="s">
         <v>31</v>
@@ -9997,7 +10021,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>22</v>
@@ -10049,7 +10073,7 @@
         <v>24</v>
       </c>
       <c r="Q129" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R129" s="7" t="s">
         <v>31</v>
@@ -10060,7 +10084,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>22</v>
@@ -10112,7 +10136,7 @@
         <v>24</v>
       </c>
       <c r="Q130" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R130" s="7" t="s">
         <v>31</v>
@@ -10123,7 +10147,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>22</v>
@@ -10175,10 +10199,10 @@
         <v>24</v>
       </c>
       <c r="Q131" s="7" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="R131" s="7" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10186,7 +10210,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>22</v>
@@ -10198,7 +10222,7 @@
         <v>7800</v>
       </c>
       <c r="F132" s="7" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="G132" s="9" t="n">
         <v>5000</v>
@@ -10238,7 +10262,7 @@
         <v>43</v>
       </c>
       <c r="Q132" s="7" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="R132" s="7"/>
     </row>
@@ -10247,7 +10271,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="7" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>22</v>
@@ -10299,7 +10323,7 @@
         <v>24</v>
       </c>
       <c r="Q133" s="7" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="R133" s="7" t="s">
         <v>31</v>
@@ -10310,7 +10334,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>28</v>
@@ -10362,7 +10386,7 @@
         <v>24</v>
       </c>
       <c r="Q134" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R134" s="7" t="s">
         <v>31</v>
@@ -10373,7 +10397,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>22</v>
@@ -10425,7 +10449,7 @@
         <v>24</v>
       </c>
       <c r="Q135" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R135" s="7" t="s">
         <v>31</v>
@@ -10436,7 +10460,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="7" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="C136" s="6" t="s">
         <v>22</v>
@@ -10488,7 +10512,7 @@
         <v>43</v>
       </c>
       <c r="Q136" s="7" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="R136" s="7"/>
     </row>
@@ -10497,7 +10521,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="C137" s="6" t="s">
         <v>22</v>
@@ -10549,7 +10573,7 @@
         <v>43</v>
       </c>
       <c r="Q137" s="7" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="R137" s="7"/>
     </row>
@@ -10558,7 +10582,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="C138" s="6" t="s">
         <v>22</v>
@@ -10610,7 +10634,7 @@
         <v>43</v>
       </c>
       <c r="Q138" s="7" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="R138" s="7"/>
     </row>
@@ -10619,7 +10643,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="7" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="C139" s="6" t="s">
         <v>28</v>
@@ -10671,7 +10695,7 @@
         <v>24</v>
       </c>
       <c r="Q139" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R139" s="7" t="s">
         <v>31</v>
@@ -10682,7 +10706,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="7" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="C140" s="6" t="s">
         <v>22</v>
@@ -10734,10 +10758,10 @@
         <v>24</v>
       </c>
       <c r="Q140" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R140" s="7" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10745,7 +10769,7 @@
         <v>142</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="C141" s="6" t="s">
         <v>22</v>
@@ -10757,7 +10781,7 @@
         <v>7150</v>
       </c>
       <c r="F141" s="7" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="G141" s="9" t="n">
         <v>5000</v>
@@ -10797,7 +10821,7 @@
         <v>24</v>
       </c>
       <c r="Q141" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R141" s="7" t="s">
         <v>31</v>
@@ -10808,7 +10832,7 @@
         <v>143</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="C142" s="6" t="s">
         <v>22</v>
@@ -10820,7 +10844,7 @@
         <v>7150</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="G142" s="9" t="n">
         <v>5000</v>
@@ -10860,7 +10884,7 @@
         <v>24</v>
       </c>
       <c r="Q142" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R142" s="7" t="s">
         <v>31</v>
@@ -10871,7 +10895,7 @@
         <v>144</v>
       </c>
       <c r="B143" s="7" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="C143" s="6" t="s">
         <v>22</v>
@@ -10883,7 +10907,7 @@
         <v>8450</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="G143" s="9" t="n">
         <v>6000</v>
@@ -10923,7 +10947,7 @@
         <v>24</v>
       </c>
       <c r="Q143" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R143" s="7" t="s">
         <v>31</v>
@@ -10934,7 +10958,7 @@
         <v>145</v>
       </c>
       <c r="B144" s="7" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="C144" s="6" t="s">
         <v>28</v>
@@ -10946,7 +10970,7 @@
         <v>104</v>
       </c>
       <c r="F144" s="7" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="G144" s="9" t="n">
         <v>50</v>
@@ -10986,7 +11010,7 @@
         <v>24</v>
       </c>
       <c r="Q144" s="7" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="R144" s="7" t="s">
         <v>31</v>
@@ -10997,7 +11021,7 @@
         <v>146</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="C145" s="6" t="s">
         <v>22</v>
@@ -11009,7 +11033,7 @@
         <v>105788</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="G145" s="9" t="n">
         <v>82000</v>
@@ -11049,7 +11073,7 @@
         <v>43</v>
       </c>
       <c r="Q145" s="7" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="R145" s="7"/>
     </row>
@@ -11058,7 +11082,7 @@
         <v>147</v>
       </c>
       <c r="B146" s="7" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="C146" s="6" t="s">
         <v>22</v>
@@ -11070,7 +11094,7 @@
         <v>245700</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="G146" s="9" t="n">
         <v>225000</v>
@@ -11110,7 +11134,7 @@
         <v>43</v>
       </c>
       <c r="Q146" s="7" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="R146" s="7"/>
     </row>
@@ -11119,7 +11143,7 @@
         <v>148</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="C147" s="6" t="s">
         <v>28</v>
@@ -11171,10 +11195,10 @@
         <v>24</v>
       </c>
       <c r="Q147" s="7" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="R147" s="7" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11182,7 +11206,7 @@
         <v>149</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="C148" s="6" t="s">
         <v>22</v>
@@ -11194,7 +11218,7 @@
         <v>1754</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="G148" s="9" t="n">
         <v>1380</v>
@@ -11234,7 +11258,7 @@
         <v>43</v>
       </c>
       <c r="Q148" s="7" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="R148" s="7"/>
     </row>
@@ -11243,7 +11267,7 @@
         <v>150</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="C149" s="6" t="s">
         <v>22</v>
@@ -11295,7 +11319,7 @@
         <v>43</v>
       </c>
       <c r="Q149" s="7" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="R149" s="7"/>
     </row>
@@ -11304,7 +11328,7 @@
         <v>151</v>
       </c>
       <c r="B150" s="7" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="C150" s="6" t="s">
         <v>22</v>
@@ -11356,7 +11380,7 @@
         <v>43</v>
       </c>
       <c r="Q150" s="7" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="R150" s="7"/>
     </row>
@@ -11365,7 +11389,7 @@
         <v>152</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="C151" s="6" t="s">
         <v>22</v>
@@ -11417,7 +11441,7 @@
         <v>43</v>
       </c>
       <c r="Q151" s="7" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="R151" s="7"/>
     </row>
@@ -11426,7 +11450,7 @@
         <v>153</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="C152" s="6" t="s">
         <v>22</v>
@@ -11478,7 +11502,7 @@
         <v>43</v>
       </c>
       <c r="Q152" s="7" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="R152" s="7"/>
     </row>
@@ -11487,7 +11511,7 @@
         <v>154</v>
       </c>
       <c r="B153" s="7" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="C153" s="6" t="s">
         <v>22</v>
@@ -11539,7 +11563,7 @@
         <v>24</v>
       </c>
       <c r="Q153" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R153" s="7" t="s">
         <v>31</v>
@@ -11550,7 +11574,7 @@
         <v>155</v>
       </c>
       <c r="B154" s="7" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="C154" s="6" t="s">
         <v>22</v>
@@ -11562,7 +11586,7 @@
         <v>748</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="G154" s="9" t="n">
         <v>450</v>
@@ -11602,7 +11626,7 @@
         <v>43</v>
       </c>
       <c r="Q154" s="7" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="R154" s="7"/>
     </row>
@@ -11611,7 +11635,7 @@
         <v>156</v>
       </c>
       <c r="B155" s="7" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>22</v>
@@ -11623,7 +11647,7 @@
         <v>748</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="G155" s="9" t="n">
         <v>450</v>
@@ -11663,7 +11687,7 @@
         <v>43</v>
       </c>
       <c r="Q155" s="7" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="R155" s="7"/>
     </row>
@@ -11672,7 +11696,7 @@
         <v>157</v>
       </c>
       <c r="B156" s="7" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="C156" s="6" t="s">
         <v>22</v>
@@ -11684,7 +11708,7 @@
         <v>748</v>
       </c>
       <c r="F156" s="7" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="G156" s="9" t="n">
         <v>400</v>
@@ -11724,7 +11748,7 @@
         <v>43</v>
       </c>
       <c r="Q156" s="7" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="R156" s="7"/>
     </row>
@@ -11733,7 +11757,7 @@
         <v>158</v>
       </c>
       <c r="B157" s="7" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="C157" s="6" t="s">
         <v>28</v>
@@ -11745,7 +11769,7 @@
         <v>311</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="G157" s="9" t="n">
         <v>150</v>
@@ -11785,7 +11809,7 @@
         <v>24</v>
       </c>
       <c r="Q157" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R157" s="7" t="s">
         <v>31</v>
@@ -11796,7 +11820,7 @@
         <v>159</v>
       </c>
       <c r="B158" s="7" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="C158" s="6" t="s">
         <v>28</v>
@@ -11808,7 +11832,7 @@
         <v>325</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="G158" s="9" t="n">
         <v>180</v>
@@ -11848,7 +11872,7 @@
         <v>24</v>
       </c>
       <c r="Q158" s="7" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="R158" s="7" t="s">
         <v>31</v>
@@ -11859,7 +11883,7 @@
         <v>160</v>
       </c>
       <c r="B159" s="7" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="C159" s="6" t="s">
         <v>28</v>
@@ -11871,7 +11895,7 @@
         <v>117</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="G159" s="9" t="n">
         <v>60</v>
@@ -11911,7 +11935,7 @@
         <v>24</v>
       </c>
       <c r="Q159" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R159" s="7" t="s">
         <v>31</v>
@@ -11922,7 +11946,7 @@
         <v>161</v>
       </c>
       <c r="B160" s="7" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C160" s="6" t="s">
         <v>28</v>
@@ -11934,7 +11958,7 @@
         <v>169</v>
       </c>
       <c r="F160" s="7" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="G160" s="9" t="n">
         <v>90</v>
@@ -11974,7 +11998,7 @@
         <v>24</v>
       </c>
       <c r="Q160" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R160" s="7" t="s">
         <v>31</v>
@@ -11985,7 +12009,7 @@
         <v>162</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="C161" s="6" t="s">
         <v>28</v>
@@ -11997,7 +12021,7 @@
         <v>234</v>
       </c>
       <c r="F161" s="7" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="G161" s="9" t="n">
         <v>120</v>
@@ -12037,7 +12061,7 @@
         <v>24</v>
       </c>
       <c r="Q161" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R161" s="7" t="s">
         <v>31</v>
@@ -12048,7 +12072,7 @@
         <v>164</v>
       </c>
       <c r="B162" s="7" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="C162" s="6" t="s">
         <v>22</v>
@@ -12060,7 +12084,7 @@
         <v>1209</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="G162" s="9" t="n">
         <v>1450</v>
@@ -12100,7 +12124,7 @@
         <v>51</v>
       </c>
       <c r="Q162" s="7" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="R162" s="7" t="s">
         <v>53</v>
@@ -12111,7 +12135,7 @@
         <v>165</v>
       </c>
       <c r="B163" s="7" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="C163" s="6" t="s">
         <v>22</v>
@@ -12123,7 +12147,7 @@
         <v>1209</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="G163" s="9" t="n">
         <v>2248</v>
@@ -12163,7 +12187,7 @@
         <v>51</v>
       </c>
       <c r="Q163" s="7" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="R163" s="7" t="s">
         <v>53</v>
@@ -12174,7 +12198,7 @@
         <v>166</v>
       </c>
       <c r="B164" s="7" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="C164" s="6" t="s">
         <v>22</v>
@@ -12186,7 +12210,7 @@
         <v>3022</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="G164" s="9" t="n">
         <v>2325</v>
@@ -12226,7 +12250,7 @@
         <v>51</v>
       </c>
       <c r="Q164" s="7" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="R164" s="7" t="s">
         <v>53</v>
@@ -12237,7 +12261,7 @@
         <v>167</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="C165" s="6" t="s">
         <v>22</v>
@@ -12289,10 +12313,10 @@
         <v>24</v>
       </c>
       <c r="Q165" s="7" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="R165" s="7" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12300,7 +12324,7 @@
         <v>168</v>
       </c>
       <c r="B166" s="7" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="C166" s="6" t="s">
         <v>22</v>
@@ -12352,10 +12376,10 @@
         <v>24</v>
       </c>
       <c r="Q166" s="7" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="R166" s="7" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12363,7 +12387,7 @@
         <v>177</v>
       </c>
       <c r="B167" s="7" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="C167" s="6" t="s">
         <v>28</v>
@@ -12375,7 +12399,7 @@
         <v>5850</v>
       </c>
       <c r="F167" s="7" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="G167" s="9" t="n">
         <v>3500</v>
@@ -12415,10 +12439,10 @@
         <v>24</v>
       </c>
       <c r="Q167" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R167" s="7" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12426,7 +12450,7 @@
         <v>179</v>
       </c>
       <c r="B168" s="7" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="C168" s="6" t="s">
         <v>28</v>
@@ -12438,7 +12462,7 @@
         <v>23400</v>
       </c>
       <c r="F168" s="7" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="G168" s="9" t="n">
         <v>20000</v>
@@ -12478,7 +12502,7 @@
         <v>24</v>
       </c>
       <c r="Q168" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R168" s="7" t="s">
         <v>31</v>
@@ -12489,7 +12513,7 @@
         <v>180</v>
       </c>
       <c r="B169" s="7" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="C169" s="6" t="s">
         <v>28</v>
@@ -12501,7 +12525,7 @@
         <v>15600</v>
       </c>
       <c r="F169" s="7" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="G169" s="9" t="n">
         <v>14000</v>
@@ -12541,7 +12565,7 @@
         <v>24</v>
       </c>
       <c r="Q169" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R169" s="7" t="s">
         <v>31</v>
@@ -12552,7 +12576,7 @@
         <v>181</v>
       </c>
       <c r="B170" s="7" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="C170" s="6" t="s">
         <v>28</v>
@@ -12564,7 +12588,7 @@
         <v>33800</v>
       </c>
       <c r="F170" s="7" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="G170" s="9" t="n">
         <v>28000</v>
@@ -12604,7 +12628,7 @@
         <v>24</v>
       </c>
       <c r="Q170" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R170" s="7" t="s">
         <v>31</v>
@@ -12615,7 +12639,7 @@
         <v>182</v>
       </c>
       <c r="B171" s="7" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="C171" s="6" t="s">
         <v>28</v>
@@ -12627,7 +12651,7 @@
         <v>23400</v>
       </c>
       <c r="F171" s="7" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="G171" s="9" t="n">
         <v>20000</v>
@@ -12667,7 +12691,7 @@
         <v>24</v>
       </c>
       <c r="Q171" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R171" s="7" t="s">
         <v>31</v>
@@ -12678,7 +12702,7 @@
         <v>183</v>
       </c>
       <c r="B172" s="7" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="C172" s="6" t="s">
         <v>28</v>
@@ -12690,7 +12714,7 @@
         <v>2860</v>
       </c>
       <c r="F172" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G172" s="9" t="n">
         <v>1800</v>
@@ -12730,7 +12754,7 @@
         <v>24</v>
       </c>
       <c r="Q172" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R172" s="7" t="s">
         <v>31</v>
@@ -12741,7 +12765,7 @@
         <v>184</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="C173" s="6" t="s">
         <v>28</v>
@@ -12753,7 +12777,7 @@
         <v>3250</v>
       </c>
       <c r="F173" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G173" s="9" t="n">
         <v>2100</v>
@@ -12793,7 +12817,7 @@
         <v>24</v>
       </c>
       <c r="Q173" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R173" s="7" t="s">
         <v>31</v>
@@ -12804,7 +12828,7 @@
         <v>185</v>
       </c>
       <c r="B174" s="7" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="C174" s="6" t="s">
         <v>28</v>
@@ -12816,7 +12840,7 @@
         <v>3900</v>
       </c>
       <c r="F174" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G174" s="9" t="n">
         <v>2600</v>
@@ -12856,7 +12880,7 @@
         <v>24</v>
       </c>
       <c r="Q174" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R174" s="7" t="s">
         <v>31</v>
@@ -12867,7 +12891,7 @@
         <v>186</v>
       </c>
       <c r="B175" s="7" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="C175" s="6" t="s">
         <v>28</v>
@@ -12879,7 +12903,7 @@
         <v>4550</v>
       </c>
       <c r="F175" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G175" s="9" t="n">
         <v>3300</v>
@@ -12919,7 +12943,7 @@
         <v>24</v>
       </c>
       <c r="Q175" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R175" s="7" t="s">
         <v>31</v>
@@ -12930,7 +12954,7 @@
         <v>187</v>
       </c>
       <c r="B176" s="7" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="C176" s="6" t="s">
         <v>28</v>
@@ -12942,7 +12966,7 @@
         <v>7150</v>
       </c>
       <c r="F176" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G176" s="9" t="n">
         <v>5500</v>
@@ -12982,7 +13006,7 @@
         <v>24</v>
       </c>
       <c r="Q176" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R176" s="7" t="s">
         <v>31</v>
@@ -12993,7 +13017,7 @@
         <v>188</v>
       </c>
       <c r="B177" s="7" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="C177" s="6" t="s">
         <v>28</v>
@@ -13005,7 +13029,7 @@
         <v>8450</v>
       </c>
       <c r="F177" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G177" s="9" t="n">
         <v>7000</v>
@@ -13045,7 +13069,7 @@
         <v>24</v>
       </c>
       <c r="Q177" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R177" s="7" t="s">
         <v>31</v>
@@ -13056,7 +13080,7 @@
         <v>189</v>
       </c>
       <c r="B178" s="7" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="C178" s="6" t="s">
         <v>28</v>
@@ -13068,7 +13092,7 @@
         <v>9750</v>
       </c>
       <c r="F178" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G178" s="9" t="n">
         <v>8500</v>
@@ -13108,7 +13132,7 @@
         <v>24</v>
       </c>
       <c r="Q178" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R178" s="7" t="s">
         <v>31</v>
@@ -13119,7 +13143,7 @@
         <v>190</v>
       </c>
       <c r="B179" s="7" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="C179" s="6" t="s">
         <v>28</v>
@@ -13131,7 +13155,7 @@
         <v>2340</v>
       </c>
       <c r="F179" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G179" s="9" t="n">
         <v>1500</v>
@@ -13171,7 +13195,7 @@
         <v>24</v>
       </c>
       <c r="Q179" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R179" s="7" t="s">
         <v>31</v>
@@ -13182,7 +13206,7 @@
         <v>191</v>
       </c>
       <c r="B180" s="7" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="C180" s="6" t="s">
         <v>28</v>
@@ -13194,7 +13218,7 @@
         <v>3640</v>
       </c>
       <c r="F180" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G180" s="9" t="n">
         <v>2300</v>
@@ -13234,7 +13258,7 @@
         <v>24</v>
       </c>
       <c r="Q180" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R180" s="7" t="s">
         <v>31</v>
@@ -13245,7 +13269,7 @@
         <v>192</v>
       </c>
       <c r="B181" s="7" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="C181" s="6" t="s">
         <v>28</v>
@@ -13297,7 +13321,7 @@
         <v>24</v>
       </c>
       <c r="Q181" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R181" s="7" t="s">
         <v>31</v>
@@ -13308,7 +13332,7 @@
         <v>193</v>
       </c>
       <c r="B182" s="7" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="C182" s="6" t="s">
         <v>28</v>
@@ -13360,7 +13384,7 @@
         <v>24</v>
       </c>
       <c r="Q182" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R182" s="7" t="s">
         <v>31</v>
@@ -13371,7 +13395,7 @@
         <v>194</v>
       </c>
       <c r="B183" s="7" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="C183" s="6" t="s">
         <v>28</v>
@@ -13423,7 +13447,7 @@
         <v>24</v>
       </c>
       <c r="Q183" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R183" s="7" t="s">
         <v>31</v>
@@ -13434,7 +13458,7 @@
         <v>195</v>
       </c>
       <c r="B184" s="7" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="C184" s="6" t="s">
         <v>28</v>
@@ -13486,7 +13510,7 @@
         <v>24</v>
       </c>
       <c r="Q184" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R184" s="7" t="s">
         <v>31</v>
@@ -13497,7 +13521,7 @@
         <v>196</v>
       </c>
       <c r="B185" s="7" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="C185" s="6" t="s">
         <v>28</v>
@@ -13509,7 +13533,7 @@
         <v>4550</v>
       </c>
       <c r="F185" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G185" s="9" t="n">
         <v>3500</v>
@@ -13549,7 +13573,7 @@
         <v>24</v>
       </c>
       <c r="Q185" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R185" s="7" t="s">
         <v>31</v>
@@ -13560,7 +13584,7 @@
         <v>197</v>
       </c>
       <c r="B186" s="7" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="C186" s="6" t="s">
         <v>28</v>
@@ -13572,7 +13596,7 @@
         <v>17940</v>
       </c>
       <c r="F186" s="7" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="G186" s="9" t="n">
         <v>5500</v>
@@ -13612,7 +13636,7 @@
         <v>43</v>
       </c>
       <c r="Q186" s="7" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="R186" s="7"/>
     </row>
@@ -13621,7 +13645,7 @@
         <v>198</v>
       </c>
       <c r="B187" s="7" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="C187" s="6" t="s">
         <v>28</v>
@@ -13633,7 +13657,7 @@
         <v>18850</v>
       </c>
       <c r="F187" s="7" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="G187" s="9" t="n">
         <v>5500</v>
@@ -13673,7 +13697,7 @@
         <v>43</v>
       </c>
       <c r="Q187" s="7" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="R187" s="7"/>
     </row>
@@ -13682,7 +13706,7 @@
         <v>199</v>
       </c>
       <c r="B188" s="7" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="C188" s="6" t="s">
         <v>28</v>
@@ -13694,7 +13718,7 @@
         <v>19500</v>
       </c>
       <c r="F188" s="7" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="G188" s="9" t="n">
         <v>6200</v>
@@ -13734,7 +13758,7 @@
         <v>43</v>
       </c>
       <c r="Q188" s="7" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="R188" s="7"/>
     </row>
@@ -13743,7 +13767,7 @@
         <v>200</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="C189" s="6" t="s">
         <v>28</v>
@@ -13755,7 +13779,7 @@
         <v>20800</v>
       </c>
       <c r="F189" s="7" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="G189" s="9" t="n">
         <v>6875</v>
@@ -13795,7 +13819,7 @@
         <v>43</v>
       </c>
       <c r="Q189" s="7" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="R189" s="7"/>
     </row>
@@ -13804,7 +13828,7 @@
         <v>201</v>
       </c>
       <c r="B190" s="7" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="C190" s="6" t="s">
         <v>28</v>
@@ -13816,7 +13840,7 @@
         <v>22750</v>
       </c>
       <c r="F190" s="7" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="G190" s="9" t="n">
         <v>8750</v>
@@ -13856,7 +13880,7 @@
         <v>43</v>
       </c>
       <c r="Q190" s="7" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="R190" s="7"/>
     </row>
@@ -13865,7 +13889,7 @@
         <v>202</v>
       </c>
       <c r="B191" s="7" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C191" s="6" t="s">
         <v>28</v>
@@ -13877,7 +13901,7 @@
         <v>2340</v>
       </c>
       <c r="F191" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G191" s="9" t="n">
         <v>1500</v>
@@ -13917,7 +13941,7 @@
         <v>24</v>
       </c>
       <c r="Q191" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R191" s="7" t="s">
         <v>31</v>
@@ -13928,7 +13952,7 @@
         <v>204</v>
       </c>
       <c r="B192" s="7" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="C192" s="6" t="s">
         <v>28</v>
@@ -13940,7 +13964,7 @@
         <v>845</v>
       </c>
       <c r="F192" s="7" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="G192" s="9" t="n">
         <v>5480</v>
@@ -13980,7 +14004,7 @@
         <v>24</v>
       </c>
       <c r="Q192" s="7" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="R192" s="7" t="s">
         <v>31</v>
@@ -13991,7 +14015,7 @@
         <v>205</v>
       </c>
       <c r="B193" s="7" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="C193" s="6" t="s">
         <v>28</v>
@@ -14003,7 +14027,7 @@
         <v>910</v>
       </c>
       <c r="F193" s="7" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="G193" s="9" t="n">
         <v>5960</v>
@@ -14043,7 +14067,7 @@
         <v>24</v>
       </c>
       <c r="Q193" s="7" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="R193" s="7" t="s">
         <v>31</v>
@@ -14054,7 +14078,7 @@
         <v>206</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="C194" s="6" t="s">
         <v>28</v>
@@ -14066,7 +14090,7 @@
         <v>1170</v>
       </c>
       <c r="F194" s="7" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="G194" s="9" t="n">
         <v>6930</v>
@@ -14106,7 +14130,7 @@
         <v>24</v>
       </c>
       <c r="Q194" s="7" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="R194" s="7" t="s">
         <v>31</v>
@@ -14117,7 +14141,7 @@
         <v>207</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="C195" s="6" t="s">
         <v>28</v>
@@ -14129,7 +14153,7 @@
         <v>1430</v>
       </c>
       <c r="F195" s="7" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="G195" s="9" t="n">
         <v>8960</v>
@@ -14169,7 +14193,7 @@
         <v>24</v>
       </c>
       <c r="Q195" s="7" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="R195" s="7" t="s">
         <v>31</v>
@@ -14180,7 +14204,7 @@
         <v>208</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="C196" s="6" t="s">
         <v>28</v>
@@ -14192,7 +14216,7 @@
         <v>1690</v>
       </c>
       <c r="F196" s="7" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="G196" s="9" t="n">
         <v>11050</v>
@@ -14232,7 +14256,7 @@
         <v>24</v>
       </c>
       <c r="Q196" s="7" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="R196" s="7" t="s">
         <v>31</v>
@@ -14243,7 +14267,7 @@
         <v>209</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="C197" s="6" t="s">
         <v>28</v>
@@ -14255,7 +14279,7 @@
         <v>2340</v>
       </c>
       <c r="F197" s="7" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="G197" s="9" t="n">
         <v>15380</v>
@@ -14295,7 +14319,7 @@
         <v>24</v>
       </c>
       <c r="Q197" s="7" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="R197" s="7" t="s">
         <v>31</v>
@@ -14306,7 +14330,7 @@
         <v>210</v>
       </c>
       <c r="B198" s="7" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="C198" s="6" t="s">
         <v>28</v>
@@ -14318,7 +14342,7 @@
         <v>2860</v>
       </c>
       <c r="F198" s="7" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="G198" s="9" t="n">
         <v>17610</v>
@@ -14358,7 +14382,7 @@
         <v>24</v>
       </c>
       <c r="Q198" s="7" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="R198" s="7" t="s">
         <v>31</v>
@@ -14369,7 +14393,7 @@
         <v>211</v>
       </c>
       <c r="B199" s="7" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="C199" s="6" t="s">
         <v>28</v>
@@ -14381,7 +14405,7 @@
         <v>4160</v>
       </c>
       <c r="F199" s="7" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="G199" s="9" t="n">
         <v>22180</v>
@@ -14421,7 +14445,7 @@
         <v>24</v>
       </c>
       <c r="Q199" s="7" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="R199" s="7" t="s">
         <v>31</v>
@@ -14432,7 +14456,7 @@
         <v>212</v>
       </c>
       <c r="B200" s="7" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="C200" s="6" t="s">
         <v>28</v>
@@ -14444,7 +14468,7 @@
         <v>5460</v>
       </c>
       <c r="F200" s="7" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="G200" s="9" t="n">
         <v>25690</v>
@@ -14484,7 +14508,7 @@
         <v>24</v>
       </c>
       <c r="Q200" s="7" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="R200" s="7" t="s">
         <v>31</v>
@@ -14495,7 +14519,7 @@
         <v>213</v>
       </c>
       <c r="B201" s="7" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="C201" s="6" t="s">
         <v>28</v>
@@ -14507,7 +14531,7 @@
         <v>455</v>
       </c>
       <c r="F201" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G201" s="9" t="n">
         <v>500</v>
@@ -14547,7 +14571,7 @@
         <v>24</v>
       </c>
       <c r="Q201" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R201" s="7" t="s">
         <v>31</v>
@@ -14558,7 +14582,7 @@
         <v>214</v>
       </c>
       <c r="B202" s="7" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="C202" s="6" t="s">
         <v>28</v>
@@ -14570,7 +14594,7 @@
         <v>494</v>
       </c>
       <c r="F202" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G202" s="9" t="n">
         <v>550</v>
@@ -14610,7 +14634,7 @@
         <v>24</v>
       </c>
       <c r="Q202" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R202" s="7" t="s">
         <v>31</v>
@@ -14621,7 +14645,7 @@
         <v>215</v>
       </c>
       <c r="B203" s="7" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="C203" s="6" t="s">
         <v>28</v>
@@ -14633,7 +14657,7 @@
         <v>585</v>
       </c>
       <c r="F203" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G203" s="9" t="n">
         <v>650</v>
@@ -14673,7 +14697,7 @@
         <v>24</v>
       </c>
       <c r="Q203" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R203" s="7" t="s">
         <v>31</v>
@@ -14684,7 +14708,7 @@
         <v>216</v>
       </c>
       <c r="B204" s="7" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="C204" s="6" t="s">
         <v>28</v>
@@ -14696,7 +14720,7 @@
         <v>715</v>
       </c>
       <c r="F204" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G204" s="9" t="n">
         <v>800</v>
@@ -14736,7 +14760,7 @@
         <v>24</v>
       </c>
       <c r="Q204" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R204" s="7" t="s">
         <v>31</v>
@@ -14747,7 +14771,7 @@
         <v>217</v>
       </c>
       <c r="B205" s="7" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="C205" s="6" t="s">
         <v>28</v>
@@ -14759,7 +14783,7 @@
         <v>910</v>
       </c>
       <c r="F205" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G205" s="9" t="n">
         <v>1000</v>
@@ -14799,7 +14823,7 @@
         <v>24</v>
       </c>
       <c r="Q205" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R205" s="7" t="s">
         <v>31</v>
@@ -14810,7 +14834,7 @@
         <v>218</v>
       </c>
       <c r="B206" s="7" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="C206" s="6" t="s">
         <v>28</v>
@@ -14822,7 +14846,7 @@
         <v>1170</v>
       </c>
       <c r="F206" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G206" s="9" t="n">
         <v>1400</v>
@@ -14862,7 +14886,7 @@
         <v>24</v>
       </c>
       <c r="Q206" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R206" s="7" t="s">
         <v>31</v>
@@ -14873,7 +14897,7 @@
         <v>219</v>
       </c>
       <c r="B207" s="7" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="C207" s="6" t="s">
         <v>28</v>
@@ -14885,7 +14909,7 @@
         <v>1040</v>
       </c>
       <c r="F207" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G207" s="9" t="n">
         <v>1100</v>
@@ -14925,7 +14949,7 @@
         <v>24</v>
       </c>
       <c r="Q207" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R207" s="7" t="s">
         <v>31</v>
@@ -14936,7 +14960,7 @@
         <v>220</v>
       </c>
       <c r="B208" s="7" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="C208" s="6" t="s">
         <v>28</v>
@@ -14948,7 +14972,7 @@
         <v>1430</v>
       </c>
       <c r="F208" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G208" s="9" t="n">
         <v>1400</v>
@@ -14988,7 +15012,7 @@
         <v>24</v>
       </c>
       <c r="Q208" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R208" s="7" t="s">
         <v>31</v>
@@ -14999,7 +15023,7 @@
         <v>221</v>
       </c>
       <c r="B209" s="7" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="C209" s="6" t="s">
         <v>28</v>
@@ -15011,7 +15035,7 @@
         <v>1950</v>
       </c>
       <c r="F209" s="7" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G209" s="9" t="n">
         <v>2000</v>
@@ -15051,7 +15075,7 @@
         <v>24</v>
       </c>
       <c r="Q209" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R209" s="7" t="s">
         <v>31</v>
@@ -15062,7 +15086,7 @@
         <v>222</v>
       </c>
       <c r="B210" s="7" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="C210" s="6" t="s">
         <v>28</v>
@@ -15074,7 +15098,7 @@
         <v>15600</v>
       </c>
       <c r="F210" s="7" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="G210" s="9" t="n">
         <v>18000</v>
@@ -15114,7 +15138,7 @@
         <v>24</v>
       </c>
       <c r="Q210" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R210" s="7" t="s">
         <v>31</v>
@@ -15125,7 +15149,7 @@
         <v>223</v>
       </c>
       <c r="B211" s="7" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="C211" s="6" t="s">
         <v>28</v>
@@ -15137,7 +15161,7 @@
         <v>30940</v>
       </c>
       <c r="F211" s="7" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="G211" s="9" t="n">
         <v>45000</v>
@@ -15177,10 +15201,10 @@
         <v>24</v>
       </c>
       <c r="Q211" s="7" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="R211" s="7" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15188,7 +15212,7 @@
         <v>224</v>
       </c>
       <c r="B212" s="7" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="C212" s="6" t="s">
         <v>28</v>
@@ -15200,7 +15224,7 @@
         <v>54600</v>
       </c>
       <c r="F212" s="7" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="G212" s="9" t="n">
         <v>85000</v>
@@ -15240,10 +15264,10 @@
         <v>24</v>
       </c>
       <c r="Q212" s="7" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="R212" s="7" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15251,7 +15275,7 @@
         <v>225</v>
       </c>
       <c r="B213" s="7" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="C213" s="6" t="s">
         <v>28</v>
@@ -15263,7 +15287,7 @@
         <v>1170</v>
       </c>
       <c r="F213" s="7" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="G213" s="9" t="n">
         <v>1800</v>
@@ -15303,7 +15327,7 @@
         <v>24</v>
       </c>
       <c r="Q213" s="7" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="R213" s="7" t="s">
         <v>31</v>
@@ -15314,7 +15338,7 @@
         <v>226</v>
       </c>
       <c r="B214" s="7" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="C214" s="6" t="s">
         <v>28</v>
@@ -15326,7 +15350,7 @@
         <v>1430</v>
       </c>
       <c r="F214" s="7" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="G214" s="9" t="n">
         <v>2600</v>
@@ -15366,7 +15390,7 @@
         <v>24</v>
       </c>
       <c r="Q214" s="7" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="R214" s="7" t="s">
         <v>31</v>
@@ -15377,7 +15401,7 @@
         <v>227</v>
       </c>
       <c r="B215" s="7" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="C215" s="6" t="s">
         <v>28</v>
@@ -15389,7 +15413,7 @@
         <v>1820</v>
       </c>
       <c r="F215" s="7" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="G215" s="9" t="n">
         <v>3500</v>
@@ -15429,7 +15453,7 @@
         <v>24</v>
       </c>
       <c r="Q215" s="7" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="R215" s="7" t="s">
         <v>31</v>
@@ -15440,7 +15464,7 @@
         <v>228</v>
       </c>
       <c r="B216" s="7" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="C216" s="6" t="s">
         <v>28</v>
@@ -15452,7 +15476,7 @@
         <v>2860</v>
       </c>
       <c r="F216" s="7" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="G216" s="9" t="n">
         <v>6000</v>
@@ -15492,7 +15516,7 @@
         <v>24</v>
       </c>
       <c r="Q216" s="7" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="R216" s="7" t="s">
         <v>31</v>
@@ -15503,7 +15527,7 @@
         <v>229</v>
       </c>
       <c r="B217" s="7" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="C217" s="6" t="s">
         <v>28</v>
@@ -15515,7 +15539,7 @@
         <v>2340</v>
       </c>
       <c r="F217" s="7" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="G217" s="9" t="n">
         <v>3200</v>
@@ -15555,7 +15579,7 @@
         <v>24</v>
       </c>
       <c r="Q217" s="7" t="s">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="R217" s="7" t="s">
         <v>31</v>
@@ -15566,7 +15590,7 @@
         <v>230</v>
       </c>
       <c r="B218" s="7" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="C218" s="6" t="s">
         <v>28</v>
@@ -15578,17 +15602,17 @@
         <v>9750</v>
       </c>
       <c r="F218" s="7" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="G218" s="9" t="n">
+        <v>5300</v>
+      </c>
+      <c r="H218" s="9" t="n">
         <v>6000</v>
-      </c>
-      <c r="H218" s="9" t="n">
-        <v>8500</v>
       </c>
       <c r="I218" s="10" t="n">
         <f aca="false">IF(E218=0,0,(E218-H218)/E218)</f>
-        <v>0.128205128205128</v>
+        <v>0.384615384615385</v>
       </c>
       <c r="J218" s="6" t="str">
         <f aca="false">IF(E218&lt;G218,"LOSS",IF(E218&lt;H218*1.1,"THIN / RISK",IF(E218&gt;H218*1.8,"OVERPRICED?","OK")))</f>
@@ -15596,7 +15620,7 @@
       </c>
       <c r="K218" s="8" t="n">
         <f aca="false">IF(J218="OVERPRICED?",ROUND(H218*1.35,-1),MAX(E218,ROUND(H218*(1+$E$3),-1)))</f>
-        <v>9780</v>
+        <v>9750</v>
       </c>
       <c r="L218" s="8" t="n">
         <f aca="false">D218*E218</f>
@@ -15604,11 +15628,11 @@
       </c>
       <c r="M218" s="8" t="n">
         <f aca="false">D218*K218</f>
-        <v>9780</v>
+        <v>9750</v>
       </c>
       <c r="N218" s="8" t="n">
         <f aca="false">D218*H218</f>
-        <v>8500</v>
+        <v>6000</v>
       </c>
       <c r="O218" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C218,F218)),"","YES")</f>
@@ -15618,10 +15642,10 @@
         <v>24</v>
       </c>
       <c r="Q218" s="7" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="R218" s="7" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15629,7 +15653,7 @@
         <v>231</v>
       </c>
       <c r="B219" s="7" t="s">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="C219" s="6" t="s">
         <v>28</v>
@@ -15641,17 +15665,17 @@
         <v>12350</v>
       </c>
       <c r="F219" s="7" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="G219" s="9" t="n">
-        <v>8000</v>
+        <v>6500</v>
       </c>
       <c r="H219" s="9" t="n">
-        <v>11000</v>
+        <v>7500</v>
       </c>
       <c r="I219" s="10" t="n">
         <f aca="false">IF(E219=0,0,(E219-H219)/E219)</f>
-        <v>0.109311740890688</v>
+        <v>0.392712550607287</v>
       </c>
       <c r="J219" s="6" t="str">
         <f aca="false">IF(E219&lt;G219,"LOSS",IF(E219&lt;H219*1.1,"THIN / RISK",IF(E219&gt;H219*1.8,"OVERPRICED?","OK")))</f>
@@ -15659,7 +15683,7 @@
       </c>
       <c r="K219" s="8" t="n">
         <f aca="false">IF(J219="OVERPRICED?",ROUND(H219*1.35,-1),MAX(E219,ROUND(H219*(1+$E$3),-1)))</f>
-        <v>12650</v>
+        <v>12350</v>
       </c>
       <c r="L219" s="8" t="n">
         <f aca="false">D219*E219</f>
@@ -15667,11 +15691,11 @@
       </c>
       <c r="M219" s="8" t="n">
         <f aca="false">D219*K219</f>
-        <v>12650</v>
+        <v>12350</v>
       </c>
       <c r="N219" s="8" t="n">
         <f aca="false">D219*H219</f>
-        <v>11000</v>
+        <v>7500</v>
       </c>
       <c r="O219" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C219,F219)),"","YES")</f>
@@ -15681,10 +15705,10 @@
         <v>24</v>
       </c>
       <c r="Q219" s="7" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="R219" s="7" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15692,10 +15716,10 @@
         <v>233</v>
       </c>
       <c r="B220" s="7" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="C220" s="6" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D220" s="6" t="n">
         <v>2</v>
@@ -15704,7 +15728,7 @@
         <v>52000</v>
       </c>
       <c r="F220" s="7" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G220" s="9" t="n">
         <v>40000</v>
@@ -15744,7 +15768,7 @@
         <v>43</v>
       </c>
       <c r="Q220" s="7" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="R220" s="7"/>
     </row>
@@ -15753,7 +15777,7 @@
         <v>234</v>
       </c>
       <c r="B221" s="7" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="C221" s="6" t="s">
         <v>22</v>
@@ -15805,7 +15829,7 @@
         <v>51</v>
       </c>
       <c r="Q221" s="7" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="R221" s="7" t="s">
         <v>53</v>
@@ -15816,7 +15840,7 @@
         <v>235</v>
       </c>
       <c r="B222" s="7" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="C222" s="6" t="s">
         <v>28</v>
@@ -15868,10 +15892,10 @@
         <v>24</v>
       </c>
       <c r="Q222" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R222" s="7" t="s">
-        <v>434</v>
+        <v>442</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15879,7 +15903,7 @@
         <v>236</v>
       </c>
       <c r="B223" s="7" t="s">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="C223" s="6" t="s">
         <v>22</v>
@@ -15891,7 +15915,7 @@
         <v>2860</v>
       </c>
       <c r="F223" s="7" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="G223" s="9" t="n">
         <v>2400</v>
@@ -15931,10 +15955,10 @@
         <v>24</v>
       </c>
       <c r="Q223" s="7" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="R223" s="7" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15942,7 +15966,7 @@
         <v>237</v>
       </c>
       <c r="B224" s="7" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="C224" s="6" t="s">
         <v>28</v>
@@ -15994,7 +16018,7 @@
         <v>24</v>
       </c>
       <c r="Q224" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="R224" s="7" t="s">
         <v>31</v>
@@ -16005,7 +16029,7 @@
         <v>238</v>
       </c>
       <c r="B225" s="7" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="C225" s="6" t="s">
         <v>28</v>
@@ -16017,7 +16041,7 @@
         <v>8450</v>
       </c>
       <c r="F225" s="7" t="s">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="G225" s="9" t="n">
         <v>7800</v>
@@ -16057,7 +16081,7 @@
         <v>43</v>
       </c>
       <c r="Q225" s="7" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="R225" s="7"/>
     </row>
@@ -16066,10 +16090,10 @@
         <v>239</v>
       </c>
       <c r="B226" s="7" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="D226" s="6" t="n">
         <v>50</v>
@@ -16078,7 +16102,7 @@
         <v>65000</v>
       </c>
       <c r="F226" s="7" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G226" s="9" t="n">
         <v>44000</v>
@@ -16118,7 +16142,7 @@
         <v>43</v>
       </c>
       <c r="Q226" s="7" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="R226" s="7"/>
     </row>
@@ -16127,7 +16151,7 @@
         <v>240</v>
       </c>
       <c r="B227" s="7" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="C227" s="6" t="s">
         <v>28</v>
@@ -16179,15 +16203,15 @@
         <v>24</v>
       </c>
       <c r="Q227" s="7" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="R227" s="7" t="s">
-        <v>447</v>
+        <v>455</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B228" s="3" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="L228" s="11" t="n">
         <f aca="false">SUM(L6:L227)</f>
@@ -16195,11 +16219,11 @@
       </c>
       <c r="M228" s="11" t="n">
         <f aca="false">SUM(M6:M227)</f>
-        <v>15547300</v>
+        <v>15503200</v>
       </c>
       <c r="N228" s="11" t="n">
         <f aca="false">SUM(N6:N227)</f>
-        <v>12587727</v>
+        <v>12507977</v>
       </c>
     </row>
   </sheetData>
@@ -16248,12 +16272,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="B3" s="11" t="n">
         <f aca="false">COUNTA('Rate Check'!A6:A227)</f>
@@ -16262,34 +16286,34 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="B4" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"LOSS")</f>
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="B5" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"THIN / RISK")</f>
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="B6" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"OK")</f>
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="B7" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"OVERPRICED?")</f>
@@ -16298,7 +16322,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="B8" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!O6:O227,"YES")</f>
@@ -16310,7 +16334,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="B10" s="11" t="n">
         <f aca="false">'Rate Check'!L228</f>
@@ -16319,38 +16343,38 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="B11" s="11" t="n">
         <f aca="false">'Rate Check'!N228</f>
-        <v>12587727</v>
+        <v>12507977</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>458</v>
+        <v>466</v>
       </c>
       <c r="B12" s="11" t="n">
         <f aca="false">B10-B11</f>
-        <v>-378219</v>
+        <v>-298469</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="B13" s="14" t="n">
         <f aca="false">IF(B10=0,0,B12/B10)</f>
-        <v>-0.0309774153061696</v>
+        <v>-0.0244456205770126</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="B14" s="11" t="n">
         <f aca="false">SUMPRODUCT(('Rate Check'!E6:E227&lt;'Rate Check'!H6:H227)*('Rate Check'!H6:H227-'Rate Check'!E6:E227)*'Rate Check'!D6:D227)</f>
-        <v>2757650</v>
+        <v>2771050</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16358,20 +16382,20 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
       <c r="B16" s="11" t="n">
         <f aca="false">'Rate Check'!M228</f>
-        <v>15547300</v>
+        <v>15503200</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="B17" s="14" t="n">
         <f aca="false">IF(B16=0,0,(B16-B11)/B16)</f>
-        <v>0.190359290680697</v>
+        <v>0.193200307033387</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16379,7 +16403,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="B19" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!P6:P227,"V")</f>
@@ -16388,7 +16412,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="B20" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!P6:P227,"S")</f>
@@ -16397,7 +16421,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="B21" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!P6:P227,"N")</f>
@@ -16429,247 +16453,247 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>472</v>
+        <v>480</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>476</v>
+        <v>484</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>478</v>
+        <v>486</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>484</v>
+        <v>492</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>500</v>
+        <v>508</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>502</v>
+        <v>510</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>504</v>
+        <v>512</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>506</v>
+        <v>514</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>508</v>
+        <v>516</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>510</v>
+        <v>518</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>512</v>
+        <v>520</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>514</v>
+        <v>522</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>516</v>
+        <v>524</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>517</v>
+        <v>525</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>520</v>
+        <v>528</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>522</v>
+        <v>530</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>524</v>
+        <v>532</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>525</v>
+        <v>533</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>526</v>
+        <v>534</v>
       </c>
     </row>
   </sheetData>

--- a/quotes/PR-217-228/Quote_PR217_PR228_Rate_Check.xlsx
+++ b/quotes/PR-217-228/Quote_PR217_PR228_Rate_Check.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1381" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="518">
   <si>
     <t xml:space="preserve">Zidane Corporation - Quote PR-217 &amp; PR-228: Brand + Buying Rate Check</t>
   </si>
@@ -96,27 +96,30 @@
     <t xml:space="preserve">Industrial</t>
   </si>
   <si>
-    <t xml:space="preserve">Bosch / Industrial</t>
+    <t xml:space="preserve">Rhodius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nasirnsons.com Rhodius 4in cutting disc Rs 280; toolshub Permanent 4in 120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spec/pack/stock farq - source dekho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STEEL NAIL 1-1/2" Taiwan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Licota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generic (Taiwan)</t>
   </si>
   <si>
     <t xml:space="preserve">N</t>
   </si>
   <si>
-    <t xml:space="preserve">toolshub/ingcomart Permanent 4in 120; nasirnsons Rhodius 280</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. stone 4in (metal 4in Permanent 120 / Rhodius 280</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STEEL NAIL 1-1/2" Taiwan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Licota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generic (Taiwan)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hardware mkt</t>
   </si>
   <si>
@@ -180,22 +183,16 @@
     <t xml:space="preserve">DOUBLE OPEN RING OFFSET WRENCH SET (12PCS)</t>
   </si>
   <si>
-    <t xml:space="preserve">S</t>
-  </si>
-  <si>
     <t xml:space="preserve">toolsmart.pk Licota offset ring singles 8x10 1,230 / 14x15 2,060 / 24x26 3,420 / 30x32 4,240 -&gt; 12pc 6-32 sum ~29,600</t>
   </si>
   <si>
-    <t xml:space="preserve">Spec/pack/stock farq - source dekho</t>
-  </si>
-  <si>
     <t xml:space="preserve">DOUBLE OPEN END WRENCH 6 TO 32 (12 PCS SET)</t>
   </si>
   <si>
-    <t xml:space="preserve">toolsmart.pk Licota DOE 36x41 7,430 / 41x46 12,310 + offset ring singles 1,230-4,240 -&gt; 12pc 6-32 DOE ~85% of ring set</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Harden 12630</t>
+    <t xml:space="preserve">Harden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart.pk Harden double open-end spanner 6-32mm 12pc Rs 12,630 (alt Ingco HKSPA2142 ingcotool 9,899)</t>
   </si>
   <si>
     <t xml:space="preserve">DOUBLE OPEN END WRENCH 36X41</t>
@@ -213,10 +210,10 @@
     <t xml:space="preserve">COMBINATION WRENCH 8 TO 32 (14 PCS SET)</t>
   </si>
   <si>
-    <t xml:space="preserve">toolsmart.pk Licota 14pc European combination 5/16-1-1/4in (=8-32mm range) Rs 25,660</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Tolsen 11780</t>
+    <t xml:space="preserve">Tolsen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">imsons.com.pk Tolsen 15889 combination spanner 6-32mm 14pc Rs 11,780; toolexpert.pk 7,500</t>
   </si>
   <si>
     <t xml:space="preserve">SOCKET SET (113PCS) 1/4" &amp; 1/2"</t>
@@ -234,10 +231,7 @@
     <t xml:space="preserve">HOLLOW PUNCH (3MM-25MM) (15PCS SET)</t>
   </si>
   <si>
-    <t xml:space="preserve">Licota TAP-50042 hollow punch (PH) scaled to 15pc 3-25mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Harden 4699</t>
+    <t xml:space="preserve">Harden 12pc hollow punch 3-16mm 610848: toolsmart 4,140; ingcotool 4,199-4,699; toolshop 4,399</t>
   </si>
   <si>
     <t xml:space="preserve">LONG TYPE HEX KEY WRENCH SET 09 PCS</t>
@@ -312,19 +306,13 @@
     <t xml:space="preserve">PIPE WRENCH SIZE 10"</t>
   </si>
   <si>
-    <t xml:space="preserve">toolsmart.pk Licota ridgid pipe wrench 14in 7,940 / 18in 9,620 scaled to 10in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Total 1700</t>
+    <t xml:space="preserve">toolsmart.pk Total pipe wrench 10in Rs 1,700; totaltool.pk 1,400</t>
   </si>
   <si>
     <t xml:space="preserve">PIPE WRENCH SIZE 12"</t>
   </si>
   <si>
-    <t xml:space="preserve">toolsmart.pk Licota ridgid pipe wrench 14in 7,940 / 18in 9,620 scaled to 12in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Harden 2850</t>
+    <t xml:space="preserve">toolsmart.pk Harden heavy duty pipe wrench 12in Rs 2,850</t>
   </si>
   <si>
     <t xml:space="preserve">PIPE WRENCH SIZE 18"</t>
@@ -336,46 +324,31 @@
     <t xml:space="preserve">PIPE WRENCH SIZE 24"</t>
   </si>
   <si>
-    <t xml:space="preserve">toolsmart.pk Licota 18in 9,620 scaled; goldentools.ae Licota 48in AED 1,000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Harden 6560</t>
+    <t xml:space="preserve">toolsmart.pk Harden pipe wrench 24in Rs 6,560</t>
   </si>
   <si>
     <t xml:space="preserve">PIPE WRENCH SIZE 36"</t>
   </si>
   <si>
-    <t xml:space="preserve">toolsmart.pk Licota 18in 9,620 scaled; goldentools.ae Licota 48in AED 1,000 (x90=90,000)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Total 7900</t>
+    <t xml:space="preserve">totaltool.pk Total pipe wrench 36in THT171366 Rs 7,900 (alt Wiseup toolshub 6,300)</t>
   </si>
   <si>
     <t xml:space="preserve">SLEDGE HAMMER 1 LBS WITH FIBREGLASS HANDLE</t>
   </si>
   <si>
-    <t xml:space="preserve">goldentools.ae Licota sledge 1500g AED 96 / 2000g AED 110 -&gt; 1lb ~AED 65 x90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Total 2000</t>
+    <t xml:space="preserve">toolsmart.pk Total sledge 2lb THT79026 Rs 2,000; purchaser 1,820 (1lb nahi mila)</t>
   </si>
   <si>
     <t xml:space="preserve">SLEDGE HAMMER 3 LBS WITH FIBREGLASS HANDLE</t>
   </si>
   <si>
-    <t xml:space="preserve">goldentools.ae Licota sledge 1500g AED 96 x90 (3lb=1.36kg)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Harden 3380</t>
+    <t xml:space="preserve">toolsmart.pk Harden 3lb sledge fibreglass 590323 Rs 3,380</t>
   </si>
   <si>
     <t xml:space="preserve">SOFT FACE DEAD BLOW HAMMER 50MM</t>
   </si>
   <si>
-    <t xml:space="preserve">goldentools.ae Licota dead blow 45mm AED 65 -&gt; 50mm ~AED 72 x90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Harden 2450</t>
+    <t xml:space="preserve">pakistanpowertools.com Harden dead blow mallet 590445 Rs 1,987-2,450</t>
   </si>
   <si>
     <t xml:space="preserve">VICE GRIP PLIER 08"</t>
@@ -468,19 +441,13 @@
     <t xml:space="preserve">MECHANICAL PULLER 3 ARMED 200X200</t>
   </si>
   <si>
-    <t xml:space="preserve">goldentools.ae Licota 3-jaw 6in AED 120 scaled to 8in (~AED 190) x90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Yato 8500</t>
+    <t xml:space="preserve">zeeshanhardware.pk Yato YT-2522 bearing puller 8in Rs 8,500</t>
   </si>
   <si>
     <t xml:space="preserve">MECHANICAL PULLER 3 ARMED 250X250</t>
   </si>
   <si>
-    <t xml:space="preserve">goldentools.ae Licota 3-jaw 6in AED 120 scaled to 10in (~AED 290) x90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Yato 19030</t>
+    <t xml:space="preserve">imartpk.com Yato 3 arms jaw puller 12in Rs 19,030</t>
   </si>
   <si>
     <t xml:space="preserve">DRILL MACHINE CORDLESS ROTARY HAMMER Bosch</t>
@@ -525,34 +492,28 @@
     <t xml:space="preserve">STEEL MEASURMENT TAPE 100M</t>
   </si>
   <si>
-    <t xml:space="preserve">Market (Licota tapes PK mein nahi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. steel 100m (alt Total fibreglass 100m toolsmart 5,250</t>
+    <t xml:space="preserve">toolsmart.pk Total fibreglass tape 100m TMTF131006 Rs 5,250 (steel 100m nahi mila)</t>
   </si>
   <si>
     <t xml:space="preserve">STEEL MEASURMENT TAPE 50M</t>
   </si>
   <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Ingco 5920</t>
+    <t xml:space="preserve">Ingco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toolsmart.pk Ingco 50m steel tape HSMT8550 Rs 5,920 (alt Total TMT710506 4,750)</t>
   </si>
   <si>
     <t xml:space="preserve">ALIGNING PRY BAR DIA 5/8" X 18" LENGTH</t>
   </si>
   <si>
-    <t xml:space="preserve">Licota pry bar (khmtools PH 4pc set) est x90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. pry bar</t>
+    <t xml:space="preserve">toolshop.pk Ingco crow wrecking bar HWBA01242 (24in) Rs 3,499 (18in nahi)</t>
   </si>
   <si>
     <t xml:space="preserve">ADJUSTABLE WRENCH 15"</t>
   </si>
   <si>
-    <t xml:space="preserve">toolsmart.pk Licota adjustable angle 10in 5,310-6,270 / goldentools.ae AED 85 -&gt; 15in ~2x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Total 3890</t>
+    <t xml:space="preserve">toolsmart.pk Ingco 15in adjustable HADW131152 Rs 4,630 (alt Total 3,890)</t>
   </si>
   <si>
     <t xml:space="preserve">ROUGH FILE SMOOTH 10"</t>
@@ -585,19 +546,13 @@
     <t xml:space="preserve">MEASURING TAPE 5M</t>
   </si>
   <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Total 1000</t>
+    <t xml:space="preserve">toolsmart.pk Total steel tape 5m TMT126251 Rs 1,000; totaltool.pk 700-770</t>
   </si>
   <si>
     <t xml:space="preserve">HSS COBALT DRILL SET 1-13MM 25 PCS</t>
   </si>
   <si>
-    <t xml:space="preserve">Dormer A095 (HSS-Co)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dormer 25pc 1-13mm set - PK listing n/a (UK/US list scaled)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Dormer 25pc cobalt set; alt Ingco AKD1251 M2 22,185</t>
+    <t xml:space="preserve">pakistanpowertools.com Ingco AKD1251 25pc 1-13mm Rs 22,185; almirajtrading 15,968 (M2 HSS)</t>
   </si>
   <si>
     <t xml:space="preserve">HSS DRILL BITS 1/16-1/2" 29 PCS SET</t>
@@ -756,6 +711,9 @@
     <t xml:space="preserve">WIRE BRUSH HEAVY DUTY 4/5 NROW</t>
   </si>
   <si>
+    <t xml:space="preserve">toolsmart.pk Harden steel brush wood handle 4 row Rs 540; pakistanpowertools 325-510</t>
+  </si>
+  <si>
     <t xml:space="preserve">WELDING HELMET (FLIP FRONT)</t>
   </si>
   <si>
@@ -774,7 +732,7 @@
     <t xml:space="preserve">C-CLAMP 6"</t>
   </si>
   <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Total 2420</t>
+    <t xml:space="preserve">toolsmart.pk Total G clamp 6in THT13161 Rs 2,420</t>
   </si>
   <si>
     <t xml:space="preserve">C-CLAMP 12"</t>
@@ -786,10 +744,7 @@
     <t xml:space="preserve">SPIRIT LEVEL 1 METER</t>
   </si>
   <si>
-    <t xml:space="preserve">amjadhardware.com Yato YT-3022 600mm 2,800; speedextools.com Yato YT-3024 1000mm AED 41 x90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Total 3350</t>
+    <t xml:space="preserve">Total spirit level 100cm TMT210026: powerhouseexpress 2,808-3,350; totaltool 2,600 (Yato 600mm amjadhardware 2,800)</t>
   </si>
   <si>
     <t xml:space="preserve">MAGNET SPIRIT LEVEL 12"</t>
@@ -801,30 +756,27 @@
     <t xml:space="preserve">CARBON STEEL RIGHT ANGLE 150MM</t>
   </si>
   <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. 150mm square</t>
+    <t xml:space="preserve">toolshop.pk Ingco stainless try square HSMT08352 Rs 860 (size confirm)</t>
   </si>
   <si>
     <t xml:space="preserve">CARBON STEEL RIGHT ANGLE 300MM</t>
   </si>
   <si>
-    <t xml:space="preserve">Insize square est (industrybuying 2280-300 INR ref)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Harden 3125</t>
+    <t xml:space="preserve">ezmakaan.com Harden aluminium try square 300mm 580713 Rs 3,125</t>
   </si>
   <si>
     <t xml:space="preserve">GAS CUTTING TORCH MEDIUM 6-50MM</t>
   </si>
   <si>
-    <t xml:space="preserve">Harris type / Industrial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. cutting torch</t>
+    <t xml:space="preserve">aliweldinghouse.pk 100B gas cutting torch with connectors Rs 8,500 (388 torch 6,500-7,000)</t>
   </si>
   <si>
     <t xml:space="preserve">CUTTING TIPS/NOZZLES NO. 02 (6MM-12MM)</t>
   </si>
   <si>
+    <t xml:space="preserve">aliweldinghouse.pk GK cutting nozzle Rs 1,600</t>
+  </si>
+  <si>
     <t xml:space="preserve">CUTTING TIPS/NOZZLES NO. 03 (12MM-25)</t>
   </si>
   <si>
@@ -867,13 +819,10 @@
     <t xml:space="preserve">AC/DC SINGLE PHASE WELDING PLANT 300 AMP</t>
   </si>
   <si>
-    <t xml:space="preserve">Industrial (AC/DC TIG 300A)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">houseoftools.com.pk AC/DC TIG WACTA20 126,000 (amp n/a); hyundaipower TIG-200 AC/DC 86,500 - 300A est</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. 300A AC/DC; houseoftools WACTA20 126,000 amps n/a</t>
+    <t xml:space="preserve">WACTA20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">houseoftools.com.pk Inverter AC/DC TIG/MMA WACTA20 Rs 126,000 (TIG 5-200A, MMA 20-180A, 220V)</t>
   </si>
   <si>
     <t xml:space="preserve">TIG WELDING TORCH AIR-COOLED 5METER</t>
@@ -990,10 +939,7 @@
     <t xml:space="preserve">FLATE METAL SCRAPPER 50MM</t>
   </si>
   <si>
-    <t xml:space="preserve">Licota gasket scraper est (UAE ref)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Tolsen 360</t>
+    <t xml:space="preserve">imsons.com.pk Tolsen 50mm wall scraper Rs 360</t>
   </si>
   <si>
     <t xml:space="preserve">WD 40 330ML (MULTI PURPOSE)</t>
@@ -1068,12 +1014,18 @@
     <t xml:space="preserve">ANCHOR BOLT 10X110</t>
   </si>
   <si>
+    <t xml:space="preserve">SMT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">experttoolsworld.com SMT Rawl anchor bolt 10mm heavy duty Rs 65 (length confirm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANCHOR BOLT 12X120</t>
+  </si>
+  <si>
     <t xml:space="preserve">Local / Fischer</t>
   </si>
   <si>
-    <t xml:space="preserve">ANCHOR BOLT 12X120</t>
-  </si>
-  <si>
     <t xml:space="preserve">ANCHOR BOLT 12X160</t>
   </si>
   <si>
@@ -1119,10 +1071,7 @@
     <t xml:space="preserve">BLIND RIVETS 04MMX25MM (1000PCS)</t>
   </si>
   <si>
-    <t xml:space="preserve">Generic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. 4x25 1000pc; alt Ingco 4x10 300pc purchaser 794</t>
+    <t xml:space="preserve">purchaser.com.pk Ingco rivet 4x10mm 300pc bottle Rs 794 (4x25 1000pc nahi mila)</t>
   </si>
   <si>
     <t xml:space="preserve">TAP SET 1" BSPF LEFT HAND</t>
@@ -1209,6 +1158,9 @@
     <t xml:space="preserve">NEEDLE FILE (5PCS SET)</t>
   </si>
   <si>
+    <t xml:space="preserve">Total 6pc needle file THT91462: toolshop.pk 1,352; toolsmart.pk 1,190 (6pc, 5pc nahi)</t>
+  </si>
+  <si>
     <t xml:space="preserve">END MILL CUTTER SIZE 5MM</t>
   </si>
   <si>
@@ -1230,6 +1182,12 @@
     <t xml:space="preserve">END MILL CUTTER SIZE 12MM</t>
   </si>
   <si>
+    <t xml:space="preserve">Generic HSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hallroadlahore.pk 12x12x53x110 4-flute HSS end mill Rs 2,900</t>
+  </si>
+  <si>
     <t xml:space="preserve">END MILL CUTTER SIZE 16MM</t>
   </si>
   <si>
@@ -1278,13 +1236,7 @@
     <t xml:space="preserve">BENCH VISE 08"</t>
   </si>
   <si>
-    <t xml:space="preserve">Yato YT-65049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yato UK GBP250; Total 8" PK 17,999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Ingco 31300</t>
+    <t xml:space="preserve">toolsmart.pk Ingco bench vice 8in HBV088 Rs 31,300; purchaser 24,360</t>
   </si>
   <si>
     <t xml:space="preserve">BENCH VISE 12"</t>
@@ -1320,22 +1272,16 @@
     <t xml:space="preserve">HYDRAULIC JACK 3 TON</t>
   </si>
   <si>
-    <t xml:space="preserve">Yato YT-17001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">speedextools/UAE Yato YT-17001 3T AED 59 x90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Licota/Yato PK listing nahi; sasta alt: Ronix 5950</t>
+    <t xml:space="preserve">Ronix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ingcomart.com.pk Ronix RH-4903 5T bottle jack Rs 5,360-5,950 (3T nahi mila, 5T diya)</t>
   </si>
   <si>
     <t xml:space="preserve">HYDRAULIC JACK 5 TON</t>
   </si>
   <si>
-    <t xml:space="preserve">Yato YT-17002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yato YT-17002 5T EU EUR 26-30 / UAE ref x90</t>
+    <t xml:space="preserve">ingcomart.com.pk Ronix RH-4903 5T bottle jack Rs 5,360-5,950</t>
   </si>
   <si>
     <t xml:space="preserve">CORDLESS SMALL ANGLE GRINDER 125MM EQUIVAL</t>
@@ -1353,7 +1299,7 @@
     <t xml:space="preserve">EARTH CLAMP 1000 AMP</t>
   </si>
   <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. earth clamp</t>
+    <t xml:space="preserve">aliweldinghouse.pk earth clamp 500A Rs 500 (1000A listed nahi)</t>
   </si>
   <si>
     <t xml:space="preserve">WELDING CABLE 1000 AMPERE</t>
@@ -1369,6 +1315,9 @@
   </si>
   <si>
     <t xml:space="preserve">CABLE LUGS 1000 AMPERE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fiaz.com.pk 95mm copper lug 140; enontraders.com 95mm thimble 150</t>
   </si>
   <si>
     <t xml:space="preserve">FULL BODY HARNESS BELT</t>
@@ -2345,7 +2294,7 @@
         <v>23</v>
       </c>
       <c r="G6" s="9" t="n">
-        <v>120</v>
+        <v>280</v>
       </c>
       <c r="H6" s="9" t="n">
         <v>280</v>
@@ -2376,7 +2325,7 @@
       </c>
       <c r="O6" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C6,F6)),"","YES")</f>
-        <v/>
+        <v>YES</v>
       </c>
       <c r="P6" s="6" t="s">
         <v>24</v>
@@ -2442,13 +2391,13 @@
         <v>YES</v>
       </c>
       <c r="P7" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R7" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2456,7 +2405,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>28</v>
@@ -2468,7 +2417,7 @@
         <v>58500</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>45000</v>
@@ -2505,13 +2454,13 @@
         <v>YES</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R8" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2519,7 +2468,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>28</v>
@@ -2531,7 +2480,7 @@
         <v>715</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>1500</v>
@@ -2568,13 +2517,13 @@
         <v>YES</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q9" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R9" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2582,7 +2531,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>28</v>
@@ -2594,7 +2543,7 @@
         <v>41600</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G10" s="9" t="n">
         <v>32000</v>
@@ -2631,13 +2580,13 @@
         <v>YES</v>
       </c>
       <c r="P10" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q10" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R10" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2645,7 +2594,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>22</v>
@@ -2657,7 +2606,7 @@
         <v>1105</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>730</v>
@@ -2694,10 +2643,10 @@
         <v>YES</v>
       </c>
       <c r="P11" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q11" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="R11" s="7"/>
     </row>
@@ -2706,7 +2655,7 @@
         <v>7</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>22</v>
@@ -2718,7 +2667,7 @@
         <v>507</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G12" s="9" t="n">
         <v>350</v>
@@ -2755,10 +2704,10 @@
         <v>YES</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q12" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="R12" s="7"/>
     </row>
@@ -2767,7 +2716,7 @@
         <v>8</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>28</v>
@@ -2816,10 +2765,10 @@
         <v/>
       </c>
       <c r="P13" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R13" s="7"/>
     </row>
@@ -2828,7 +2777,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>28</v>
@@ -2877,13 +2826,13 @@
         <v/>
       </c>
       <c r="P14" s="6" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="Q14" s="7" t="s">
         <v>52</v>
       </c>
       <c r="R14" s="7" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2891,7 +2840,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>28</v>
@@ -2903,25 +2852,25 @@
         <v>15600</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>23000</v>
+        <v>12630</v>
       </c>
       <c r="H15" s="9" t="n">
-        <v>27000</v>
+        <v>12630</v>
       </c>
       <c r="I15" s="10" t="n">
         <f aca="false">IF(E15=0,0,(E15-H15)/E15)</f>
-        <v>-0.730769230769231</v>
+        <v>0.190384615384615</v>
       </c>
       <c r="J15" s="6" t="str">
         <f aca="false">IF(E15&lt;G15,"LOSS",IF(E15&lt;H15*1.1,"THIN / RISK",IF(E15&gt;H15*1.8,"OVERPRICED?","OK")))</f>
-        <v>LOSS</v>
+        <v>OK</v>
       </c>
       <c r="K15" s="8" t="n">
         <f aca="false">IF(J15="OVERPRICED?",ROUND(H15*1.35,-1),MAX(E15,ROUND(H15*(1+$E$3),-1)))</f>
-        <v>31050</v>
+        <v>15600</v>
       </c>
       <c r="L15" s="8" t="n">
         <f aca="false">D15*E15</f>
@@ -2929,32 +2878,30 @@
       </c>
       <c r="M15" s="8" t="n">
         <f aca="false">D15*K15</f>
-        <v>124200</v>
+        <v>62400</v>
       </c>
       <c r="N15" s="8" t="n">
         <f aca="false">D15*H15</f>
-        <v>108000</v>
+        <v>50520</v>
       </c>
       <c r="O15" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C15,F15)),"","YES")</f>
-        <v/>
+        <v>YES</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="Q15" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="R15" s="7" t="s">
-        <v>56</v>
-      </c>
+      <c r="R15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="n">
         <v>11</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>28</v>
@@ -3003,10 +2950,10 @@
         <v/>
       </c>
       <c r="P16" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="R16" s="7"/>
     </row>
@@ -3015,7 +2962,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>28</v>
@@ -3064,19 +3011,19 @@
         <v/>
       </c>
       <c r="P17" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R17" s="7"/>
     </row>
-    <row r="18" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="n">
         <v>13</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>28</v>
@@ -3088,25 +3035,25 @@
         <v>22100</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>25660</v>
+        <v>11780</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>28000</v>
+        <v>11780</v>
       </c>
       <c r="I18" s="10" t="n">
         <f aca="false">IF(E18=0,0,(E18-H18)/E18)</f>
-        <v>-0.266968325791855</v>
+        <v>0.466968325791855</v>
       </c>
       <c r="J18" s="6" t="str">
         <f aca="false">IF(E18&lt;G18,"LOSS",IF(E18&lt;H18*1.1,"THIN / RISK",IF(E18&gt;H18*1.8,"OVERPRICED?","OK")))</f>
-        <v>LOSS</v>
+        <v>OVERPRICED?</v>
       </c>
       <c r="K18" s="8" t="n">
         <f aca="false">IF(J18="OVERPRICED?",ROUND(H18*1.35,-1),MAX(E18,ROUND(H18*(1+$E$3),-1)))</f>
-        <v>32200</v>
+        <v>15900</v>
       </c>
       <c r="L18" s="8" t="n">
         <f aca="false">D18*E18</f>
@@ -3114,32 +3061,30 @@
       </c>
       <c r="M18" s="8" t="n">
         <f aca="false">D18*K18</f>
-        <v>128800</v>
+        <v>63600</v>
       </c>
       <c r="N18" s="8" t="n">
         <f aca="false">D18*H18</f>
-        <v>112000</v>
+        <v>47120</v>
       </c>
       <c r="O18" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C18,F18)),"","YES")</f>
-        <v/>
+        <v>YES</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="Q18" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="R18" s="7" t="s">
-        <v>63</v>
-      </c>
+      <c r="R18" s="7"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="n">
         <v>14</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>28</v>
@@ -3188,10 +3133,10 @@
         <v/>
       </c>
       <c r="P19" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R19" s="7"/>
     </row>
@@ -3200,7 +3145,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>28</v>
@@ -3249,10 +3194,10 @@
         <v/>
       </c>
       <c r="P20" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R20" s="7"/>
     </row>
@@ -3261,7 +3206,7 @@
         <v>16</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>28</v>
@@ -3273,25 +3218,25 @@
         <v>8450</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>12000</v>
+        <v>4699</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>16000</v>
+        <v>4699</v>
       </c>
       <c r="I21" s="10" t="n">
         <f aca="false">IF(E21=0,0,(E21-H21)/E21)</f>
-        <v>-0.893491124260355</v>
+        <v>0.443905325443787</v>
       </c>
       <c r="J21" s="6" t="str">
         <f aca="false">IF(E21&lt;G21,"LOSS",IF(E21&lt;H21*1.1,"THIN / RISK",IF(E21&gt;H21*1.8,"OVERPRICED?","OK")))</f>
-        <v>LOSS</v>
+        <v>OK</v>
       </c>
       <c r="K21" s="8" t="n">
         <f aca="false">IF(J21="OVERPRICED?",ROUND(H21*1.35,-1),MAX(E21,ROUND(H21*(1+$E$3),-1)))</f>
-        <v>18400</v>
+        <v>8450</v>
       </c>
       <c r="L21" s="8" t="n">
         <f aca="false">D21*E21</f>
@@ -3299,24 +3244,24 @@
       </c>
       <c r="M21" s="8" t="n">
         <f aca="false">D21*K21</f>
-        <v>73600</v>
+        <v>33800</v>
       </c>
       <c r="N21" s="8" t="n">
         <f aca="false">D21*H21</f>
-        <v>64000</v>
+        <v>18796</v>
       </c>
       <c r="O21" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C21,F21)),"","YES")</f>
-        <v/>
+        <v>YES</v>
       </c>
       <c r="P21" s="6" t="s">
         <v>24</v>
       </c>
       <c r="Q21" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="R21" s="7" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3324,7 +3269,7 @@
         <v>17</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>28</v>
@@ -3373,10 +3318,10 @@
         <v/>
       </c>
       <c r="P22" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q22" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="R22" s="7"/>
     </row>
@@ -3385,7 +3330,7 @@
         <v>18</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>28</v>
@@ -3434,10 +3379,10 @@
         <v/>
       </c>
       <c r="P23" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q23" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="R23" s="7"/>
     </row>
@@ -3446,7 +3391,7 @@
         <v>19</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>28</v>
@@ -3495,10 +3440,10 @@
         <v/>
       </c>
       <c r="P24" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q24" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="R24" s="7"/>
     </row>
@@ -3507,7 +3452,7 @@
         <v>20</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>28</v>
@@ -3556,13 +3501,13 @@
         <v/>
       </c>
       <c r="P25" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q25" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="R25" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3570,7 +3515,7 @@
         <v>21</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>28</v>
@@ -3619,13 +3564,13 @@
         <v/>
       </c>
       <c r="P26" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q26" s="7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="R26" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3633,7 +3578,7 @@
         <v>22</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>28</v>
@@ -3682,13 +3627,13 @@
         <v/>
       </c>
       <c r="P27" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q27" s="7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="R27" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3696,7 +3641,7 @@
         <v>23</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>28</v>
@@ -3745,10 +3690,10 @@
         <v/>
       </c>
       <c r="P28" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q28" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="R28" s="7"/>
     </row>
@@ -3757,7 +3702,7 @@
         <v>24</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>28</v>
@@ -3806,10 +3751,10 @@
         <v/>
       </c>
       <c r="P29" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q29" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="R29" s="7"/>
     </row>
@@ -3818,7 +3763,7 @@
         <v>25</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>28</v>
@@ -3867,10 +3812,10 @@
         <v/>
       </c>
       <c r="P30" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q30" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="R30" s="7"/>
     </row>
@@ -3879,7 +3824,7 @@
         <v>26</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>28</v>
@@ -3928,10 +3873,10 @@
         <v/>
       </c>
       <c r="P31" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q31" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="R31" s="7"/>
     </row>
@@ -3940,7 +3885,7 @@
         <v>27</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>28</v>
@@ -3989,13 +3934,13 @@
         <v/>
       </c>
       <c r="P32" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q32" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="R32" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4003,7 +3948,7 @@
         <v>28</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>28</v>
@@ -4052,13 +3997,13 @@
         <v/>
       </c>
       <c r="P33" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q33" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="R33" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4066,7 +4011,7 @@
         <v>30</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>28</v>
@@ -4115,10 +4060,10 @@
         <v/>
       </c>
       <c r="P34" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q34" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="R34" s="7"/>
     </row>
@@ -4127,7 +4072,7 @@
         <v>31</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>28</v>
@@ -4139,25 +4084,25 @@
         <v>2210</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>5300</v>
+        <v>1700</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>5800</v>
+        <v>1700</v>
       </c>
       <c r="I35" s="10" t="n">
         <f aca="false">IF(E35=0,0,(E35-H35)/E35)</f>
-        <v>-1.62443438914027</v>
+        <v>0.230769230769231</v>
       </c>
       <c r="J35" s="6" t="str">
         <f aca="false">IF(E35&lt;G35,"LOSS",IF(E35&lt;H35*1.1,"THIN / RISK",IF(E35&gt;H35*1.8,"OVERPRICED?","OK")))</f>
-        <v>LOSS</v>
+        <v>OK</v>
       </c>
       <c r="K35" s="8" t="n">
         <f aca="false">IF(J35="OVERPRICED?",ROUND(H35*1.35,-1),MAX(E35,ROUND(H35*(1+$E$3),-1)))</f>
-        <v>6670</v>
+        <v>2210</v>
       </c>
       <c r="L35" s="8" t="n">
         <f aca="false">D35*E35</f>
@@ -4165,32 +4110,30 @@
       </c>
       <c r="M35" s="8" t="n">
         <f aca="false">D35*K35</f>
-        <v>20010</v>
+        <v>6630</v>
       </c>
       <c r="N35" s="8" t="n">
         <f aca="false">D35*H35</f>
-        <v>17400</v>
+        <v>5100</v>
       </c>
       <c r="O35" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C35,F35)),"","YES")</f>
-        <v/>
+        <v>YES</v>
       </c>
       <c r="P35" s="6" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="Q35" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="R35" s="7" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>93</v>
+      </c>
+      <c r="R35" s="7"/>
+    </row>
+    <row r="36" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="n">
         <v>32</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>28</v>
@@ -4202,25 +4145,25 @@
         <v>2886</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>6300</v>
+        <v>2850</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>6800</v>
+        <v>2850</v>
       </c>
       <c r="I36" s="10" t="n">
         <f aca="false">IF(E36=0,0,(E36-H36)/E36)</f>
-        <v>-1.35620235620236</v>
+        <v>0.0124740124740125</v>
       </c>
       <c r="J36" s="6" t="str">
         <f aca="false">IF(E36&lt;G36,"LOSS",IF(E36&lt;H36*1.1,"THIN / RISK",IF(E36&gt;H36*1.8,"OVERPRICED?","OK")))</f>
-        <v>LOSS</v>
+        <v>THIN / RISK</v>
       </c>
       <c r="K36" s="8" t="n">
         <f aca="false">IF(J36="OVERPRICED?",ROUND(H36*1.35,-1),MAX(E36,ROUND(H36*(1+$E$3),-1)))</f>
-        <v>7820</v>
+        <v>3280</v>
       </c>
       <c r="L36" s="8" t="n">
         <f aca="false">D36*E36</f>
@@ -4228,32 +4171,30 @@
       </c>
       <c r="M36" s="8" t="n">
         <f aca="false">D36*K36</f>
-        <v>23460</v>
+        <v>9840</v>
       </c>
       <c r="N36" s="8" t="n">
         <f aca="false">D36*H36</f>
-        <v>20400</v>
+        <v>8550</v>
       </c>
       <c r="O36" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C36,F36)),"","YES")</f>
-        <v/>
+        <v>YES</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="Q36" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="R36" s="7" t="s">
-        <v>99</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="R36" s="7"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="n">
         <v>33</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>28</v>
@@ -4302,19 +4243,19 @@
         <v/>
       </c>
       <c r="P37" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q37" s="7" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="R37" s="7"/>
     </row>
-    <row r="38" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="n">
         <v>34</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>28</v>
@@ -4326,17 +4267,17 @@
         <v>6120</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>14000</v>
+        <v>6560</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>16000</v>
+        <v>6560</v>
       </c>
       <c r="I38" s="10" t="n">
         <f aca="false">IF(E38=0,0,(E38-H38)/E38)</f>
-        <v>-1.61437908496732</v>
+        <v>-0.0718954248366013</v>
       </c>
       <c r="J38" s="6" t="str">
         <f aca="false">IF(E38&lt;G38,"LOSS",IF(E38&lt;H38*1.1,"THIN / RISK",IF(E38&gt;H38*1.8,"OVERPRICED?","OK")))</f>
@@ -4344,7 +4285,7 @@
       </c>
       <c r="K38" s="8" t="n">
         <f aca="false">IF(J38="OVERPRICED?",ROUND(H38*1.35,-1),MAX(E38,ROUND(H38*(1+$E$3),-1)))</f>
-        <v>18400</v>
+        <v>7540</v>
       </c>
       <c r="L38" s="8" t="n">
         <f aca="false">D38*E38</f>
@@ -4352,32 +4293,30 @@
       </c>
       <c r="M38" s="8" t="n">
         <f aca="false">D38*K38</f>
-        <v>36800</v>
+        <v>15080</v>
       </c>
       <c r="N38" s="8" t="n">
         <f aca="false">D38*H38</f>
-        <v>32000</v>
+        <v>13120</v>
       </c>
       <c r="O38" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C38,F38)),"","YES")</f>
-        <v/>
+        <v>YES</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="Q38" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="R38" s="7" t="s">
-        <v>104</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="R38" s="7"/>
     </row>
     <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="n">
         <v>35</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>28</v>
@@ -4389,25 +4328,25 @@
         <v>12870</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>30000</v>
+        <v>7900</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>36000</v>
+        <v>7900</v>
       </c>
       <c r="I39" s="10" t="n">
         <f aca="false">IF(E39=0,0,(E39-H39)/E39)</f>
-        <v>-1.7972027972028</v>
+        <v>0.386169386169386</v>
       </c>
       <c r="J39" s="6" t="str">
         <f aca="false">IF(E39&lt;G39,"LOSS",IF(E39&lt;H39*1.1,"THIN / RISK",IF(E39&gt;H39*1.8,"OVERPRICED?","OK")))</f>
-        <v>LOSS</v>
+        <v>OK</v>
       </c>
       <c r="K39" s="8" t="n">
         <f aca="false">IF(J39="OVERPRICED?",ROUND(H39*1.35,-1),MAX(E39,ROUND(H39*(1+$E$3),-1)))</f>
-        <v>41400</v>
+        <v>12870</v>
       </c>
       <c r="L39" s="8" t="n">
         <f aca="false">D39*E39</f>
@@ -4415,32 +4354,30 @@
       </c>
       <c r="M39" s="8" t="n">
         <f aca="false">D39*K39</f>
-        <v>82800</v>
+        <v>25740</v>
       </c>
       <c r="N39" s="8" t="n">
         <f aca="false">D39*H39</f>
-        <v>72000</v>
+        <v>15800</v>
       </c>
       <c r="O39" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C39,F39)),"","YES")</f>
-        <v/>
+        <v>YES</v>
       </c>
       <c r="P39" s="6" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="Q39" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="R39" s="7" t="s">
-        <v>107</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="R39" s="7"/>
     </row>
     <row r="40" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="n">
         <v>36</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>28</v>
@@ -4452,17 +4389,17 @@
         <v>1950</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>5400</v>
+        <v>2000</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>6300</v>
+        <v>2000</v>
       </c>
       <c r="I40" s="10" t="n">
         <f aca="false">IF(E40=0,0,(E40-H40)/E40)</f>
-        <v>-2.23076923076923</v>
+        <v>-0.0256410256410256</v>
       </c>
       <c r="J40" s="6" t="str">
         <f aca="false">IF(E40&lt;G40,"LOSS",IF(E40&lt;H40*1.1,"THIN / RISK",IF(E40&gt;H40*1.8,"OVERPRICED?","OK")))</f>
@@ -4470,7 +4407,7 @@
       </c>
       <c r="K40" s="8" t="n">
         <f aca="false">IF(J40="OVERPRICED?",ROUND(H40*1.35,-1),MAX(E40,ROUND(H40*(1+$E$3),-1)))</f>
-        <v>7250</v>
+        <v>2300</v>
       </c>
       <c r="L40" s="8" t="n">
         <f aca="false">D40*E40</f>
@@ -4478,32 +4415,32 @@
       </c>
       <c r="M40" s="8" t="n">
         <f aca="false">D40*K40</f>
-        <v>21750</v>
+        <v>6900</v>
       </c>
       <c r="N40" s="8" t="n">
         <f aca="false">D40*H40</f>
-        <v>18900</v>
+        <v>6000</v>
       </c>
       <c r="O40" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C40,F40)),"","YES")</f>
-        <v/>
+        <v>YES</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>24</v>
       </c>
       <c r="Q40" s="7" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="R40" s="7" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="n">
         <v>37</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>28</v>
@@ -4515,25 +4452,25 @@
         <v>4550</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>8200</v>
+        <v>3380</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>9500</v>
+        <v>3380</v>
       </c>
       <c r="I41" s="10" t="n">
         <f aca="false">IF(E41=0,0,(E41-H41)/E41)</f>
-        <v>-1.08791208791209</v>
+        <v>0.257142857142857</v>
       </c>
       <c r="J41" s="6" t="str">
         <f aca="false">IF(E41&lt;G41,"LOSS",IF(E41&lt;H41*1.1,"THIN / RISK",IF(E41&gt;H41*1.8,"OVERPRICED?","OK")))</f>
-        <v>LOSS</v>
+        <v>OK</v>
       </c>
       <c r="K41" s="8" t="n">
         <f aca="false">IF(J41="OVERPRICED?",ROUND(H41*1.35,-1),MAX(E41,ROUND(H41*(1+$E$3),-1)))</f>
-        <v>10930</v>
+        <v>4550</v>
       </c>
       <c r="L41" s="8" t="n">
         <f aca="false">D41*E41</f>
@@ -4541,32 +4478,30 @@
       </c>
       <c r="M41" s="8" t="n">
         <f aca="false">D41*K41</f>
-        <v>32790</v>
+        <v>13650</v>
       </c>
       <c r="N41" s="8" t="n">
         <f aca="false">D41*H41</f>
-        <v>28500</v>
+        <v>10140</v>
       </c>
       <c r="O41" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C41,F41)),"","YES")</f>
-        <v/>
+        <v>YES</v>
       </c>
       <c r="P41" s="6" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="Q41" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="R41" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>105</v>
+      </c>
+      <c r="R41" s="7"/>
+    </row>
+    <row r="42" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="n">
         <v>38</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>28</v>
@@ -4578,25 +4513,25 @@
         <v>6240</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>6000</v>
+        <v>2450</v>
       </c>
       <c r="H42" s="9" t="n">
-        <v>7000</v>
+        <v>2450</v>
       </c>
       <c r="I42" s="10" t="n">
         <f aca="false">IF(E42=0,0,(E42-H42)/E42)</f>
-        <v>-0.121794871794872</v>
+        <v>0.607371794871795</v>
       </c>
       <c r="J42" s="6" t="str">
         <f aca="false">IF(E42&lt;G42,"LOSS",IF(E42&lt;H42*1.1,"THIN / RISK",IF(E42&gt;H42*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>OVERPRICED?</v>
       </c>
       <c r="K42" s="8" t="n">
         <f aca="false">IF(J42="OVERPRICED?",ROUND(H42*1.35,-1),MAX(E42,ROUND(H42*(1+$E$3),-1)))</f>
-        <v>8050</v>
+        <v>3310</v>
       </c>
       <c r="L42" s="8" t="n">
         <f aca="false">D42*E42</f>
@@ -4604,32 +4539,30 @@
       </c>
       <c r="M42" s="8" t="n">
         <f aca="false">D42*K42</f>
-        <v>24150</v>
+        <v>9930</v>
       </c>
       <c r="N42" s="8" t="n">
         <f aca="false">D42*H42</f>
-        <v>21000</v>
+        <v>7350</v>
       </c>
       <c r="O42" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C42,F42)),"","YES")</f>
-        <v/>
+        <v>YES</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="Q42" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="R42" s="7" t="s">
-        <v>116</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="R42" s="7"/>
     </row>
     <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="n">
         <v>39</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>28</v>
@@ -4678,13 +4611,13 @@
         <v/>
       </c>
       <c r="P43" s="6" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="Q43" s="7" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="R43" s="7" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4692,10 +4625,10 @@
         <v>40</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="D44" s="6" t="n">
         <v>3</v>
@@ -4704,7 +4637,7 @@
         <v>79300</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="G44" s="9" t="n">
         <v>79000</v>
@@ -4741,10 +4674,10 @@
         <v/>
       </c>
       <c r="P44" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q44" s="7" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="R44" s="7"/>
     </row>
@@ -4753,10 +4686,10 @@
         <v>41</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>3</v>
@@ -4765,7 +4698,7 @@
         <v>128700</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="G45" s="9" t="n">
         <v>80000</v>
@@ -4802,13 +4735,13 @@
         <v/>
       </c>
       <c r="P45" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q45" s="7" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="R45" s="7" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4816,10 +4749,10 @@
         <v>42</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="D46" s="6" t="n">
         <v>2</v>
@@ -4828,7 +4761,7 @@
         <v>106600</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="G46" s="9" t="n">
         <v>143800</v>
@@ -4865,10 +4798,10 @@
         <v/>
       </c>
       <c r="P46" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q46" s="7" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="R46" s="7"/>
     </row>
@@ -4877,7 +4810,7 @@
         <v>43</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>28</v>
@@ -4926,13 +4859,13 @@
         <v/>
       </c>
       <c r="P47" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q47" s="7" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="R47" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4940,7 +4873,7 @@
         <v>44</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>28</v>
@@ -4952,7 +4885,7 @@
         <v>1950</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="G48" s="9" t="n">
         <v>1750</v>
@@ -4989,10 +4922,10 @@
         <v>YES</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q48" s="7" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="R48" s="7"/>
     </row>
@@ -5001,7 +4934,7 @@
         <v>45</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>28</v>
@@ -5013,7 +4946,7 @@
         <v>2210</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="G49" s="9" t="n">
         <v>1750</v>
@@ -5050,13 +4983,13 @@
         <v>YES</v>
       </c>
       <c r="P49" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q49" s="7" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="R49" s="7" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5064,7 +4997,7 @@
         <v>47</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>28</v>
@@ -5113,13 +5046,13 @@
         <v/>
       </c>
       <c r="P50" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q50" s="7" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="R50" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5127,7 +5060,7 @@
         <v>48</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>28</v>
@@ -5176,13 +5109,13 @@
         <v/>
       </c>
       <c r="P51" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q51" s="7" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="R51" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5190,7 +5123,7 @@
         <v>49</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>28</v>
@@ -5239,13 +5172,13 @@
         <v/>
       </c>
       <c r="P52" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q52" s="7" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="R52" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5253,7 +5186,7 @@
         <v>50</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>28</v>
@@ -5302,13 +5235,13 @@
         <v/>
       </c>
       <c r="P53" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q53" s="7" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="R53" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5316,7 +5249,7 @@
         <v>51</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>28</v>
@@ -5365,13 +5298,13 @@
         <v/>
       </c>
       <c r="P54" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q54" s="7" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="R54" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5379,7 +5312,7 @@
         <v>52</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>28</v>
@@ -5391,25 +5324,25 @@
         <v>18200</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>28</v>
+        <v>122</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>16000</v>
+        <v>8500</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>19000</v>
+        <v>8500</v>
       </c>
       <c r="I55" s="10" t="n">
         <f aca="false">IF(E55=0,0,(E55-H55)/E55)</f>
-        <v>-0.043956043956044</v>
+        <v>0.532967032967033</v>
       </c>
       <c r="J55" s="6" t="str">
         <f aca="false">IF(E55&lt;G55,"LOSS",IF(E55&lt;H55*1.1,"THIN / RISK",IF(E55&gt;H55*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>OVERPRICED?</v>
       </c>
       <c r="K55" s="8" t="n">
         <f aca="false">IF(J55="OVERPRICED?",ROUND(H55*1.35,-1),MAX(E55,ROUND(H55*(1+$E$3),-1)))</f>
-        <v>21850</v>
+        <v>11480</v>
       </c>
       <c r="L55" s="8" t="n">
         <f aca="false">D55*E55</f>
@@ -5417,32 +5350,30 @@
       </c>
       <c r="M55" s="8" t="n">
         <f aca="false">D55*K55</f>
-        <v>43700</v>
+        <v>22960</v>
       </c>
       <c r="N55" s="8" t="n">
         <f aca="false">D55*H55</f>
-        <v>38000</v>
+        <v>17000</v>
       </c>
       <c r="O55" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C55,F55)),"","YES")</f>
-        <v/>
+        <v>YES</v>
       </c>
       <c r="P55" s="6" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="Q55" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="R55" s="7" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>138</v>
+      </c>
+      <c r="R55" s="7"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="n">
         <v>53</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>28</v>
@@ -5454,25 +5385,25 @@
         <v>23400</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>28</v>
+        <v>122</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>24000</v>
+        <v>19030</v>
       </c>
       <c r="H56" s="9" t="n">
-        <v>28000</v>
+        <v>19030</v>
       </c>
       <c r="I56" s="10" t="n">
         <f aca="false">IF(E56=0,0,(E56-H56)/E56)</f>
-        <v>-0.196581196581197</v>
+        <v>0.186752136752137</v>
       </c>
       <c r="J56" s="6" t="str">
         <f aca="false">IF(E56&lt;G56,"LOSS",IF(E56&lt;H56*1.1,"THIN / RISK",IF(E56&gt;H56*1.8,"OVERPRICED?","OK")))</f>
-        <v>LOSS</v>
+        <v>OK</v>
       </c>
       <c r="K56" s="8" t="n">
         <f aca="false">IF(J56="OVERPRICED?",ROUND(H56*1.35,-1),MAX(E56,ROUND(H56*(1+$E$3),-1)))</f>
-        <v>32200</v>
+        <v>23400</v>
       </c>
       <c r="L56" s="8" t="n">
         <f aca="false">D56*E56</f>
@@ -5480,35 +5411,33 @@
       </c>
       <c r="M56" s="8" t="n">
         <f aca="false">D56*K56</f>
-        <v>32200</v>
+        <v>23400</v>
       </c>
       <c r="N56" s="8" t="n">
         <f aca="false">D56*H56</f>
-        <v>28000</v>
+        <v>19030</v>
       </c>
       <c r="O56" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C56,F56)),"","YES")</f>
-        <v/>
+        <v>YES</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="Q56" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="R56" s="7" t="s">
-        <v>151</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="R56" s="7"/>
     </row>
     <row r="57" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6" t="n">
         <v>54</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="D57" s="6" t="n">
         <v>2</v>
@@ -5517,7 +5446,7 @@
         <v>400946</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="G57" s="9" t="n">
         <v>115000</v>
@@ -5554,10 +5483,10 @@
         <v/>
       </c>
       <c r="P57" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q57" s="7" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="R57" s="7"/>
     </row>
@@ -5566,7 +5495,7 @@
         <v>55</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>28</v>
@@ -5578,7 +5507,7 @@
         <v>15600</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="G58" s="9" t="n">
         <v>12000</v>
@@ -5615,13 +5544,13 @@
         <v>YES</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q58" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R58" s="7" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5629,7 +5558,7 @@
         <v>56</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>28</v>
@@ -5678,13 +5607,13 @@
         <v/>
       </c>
       <c r="P59" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q59" s="7" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="R59" s="7" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5692,7 +5621,7 @@
         <v>57</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>28</v>
@@ -5741,10 +5670,10 @@
         <v/>
       </c>
       <c r="P60" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q60" s="7" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="R60" s="7"/>
     </row>
@@ -5753,7 +5682,7 @@
         <v>58</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>28</v>
@@ -5802,13 +5731,13 @@
         <v/>
       </c>
       <c r="P61" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q61" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R61" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5816,7 +5745,7 @@
         <v>59</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>28</v>
@@ -5865,13 +5794,13 @@
         <v/>
       </c>
       <c r="P62" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q62" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R62" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5879,7 +5808,7 @@
         <v>60</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>28</v>
@@ -5891,25 +5820,25 @@
         <v>9100</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>131</v>
+        <v>43</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>8000</v>
+        <v>5250</v>
       </c>
       <c r="H63" s="9" t="n">
-        <v>12000</v>
+        <v>5250</v>
       </c>
       <c r="I63" s="10" t="n">
         <f aca="false">IF(E63=0,0,(E63-H63)/E63)</f>
-        <v>-0.318681318681319</v>
+        <v>0.423076923076923</v>
       </c>
       <c r="J63" s="6" t="str">
         <f aca="false">IF(E63&lt;G63,"LOSS",IF(E63&lt;H63*1.1,"THIN / RISK",IF(E63&gt;H63*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>OK</v>
       </c>
       <c r="K63" s="8" t="n">
         <f aca="false">IF(J63="OVERPRICED?",ROUND(H63*1.35,-1),MAX(E63,ROUND(H63*(1+$E$3),-1)))</f>
-        <v>13800</v>
+        <v>9100</v>
       </c>
       <c r="L63" s="8" t="n">
         <f aca="false">D63*E63</f>
@@ -5917,11 +5846,11 @@
       </c>
       <c r="M63" s="8" t="n">
         <f aca="false">D63*K63</f>
-        <v>27600</v>
+        <v>18200</v>
       </c>
       <c r="N63" s="8" t="n">
         <f aca="false">D63*H63</f>
-        <v>24000</v>
+        <v>10500</v>
       </c>
       <c r="O63" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C63,F63)),"","YES")</f>
@@ -5931,18 +5860,18 @@
         <v>24</v>
       </c>
       <c r="Q63" s="7" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="R63" s="7" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6" t="n">
         <v>61</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>28</v>
@@ -5954,25 +5883,25 @@
         <v>5850</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>5000</v>
+        <v>5920</v>
       </c>
       <c r="H64" s="9" t="n">
-        <v>7500</v>
+        <v>5920</v>
       </c>
       <c r="I64" s="10" t="n">
         <f aca="false">IF(E64=0,0,(E64-H64)/E64)</f>
-        <v>-0.282051282051282</v>
+        <v>-0.011965811965812</v>
       </c>
       <c r="J64" s="6" t="str">
         <f aca="false">IF(E64&lt;G64,"LOSS",IF(E64&lt;H64*1.1,"THIN / RISK",IF(E64&gt;H64*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>LOSS</v>
       </c>
       <c r="K64" s="8" t="n">
         <f aca="false">IF(J64="OVERPRICED?",ROUND(H64*1.35,-1),MAX(E64,ROUND(H64*(1+$E$3),-1)))</f>
-        <v>8630</v>
+        <v>6810</v>
       </c>
       <c r="L64" s="8" t="n">
         <f aca="false">D64*E64</f>
@@ -5980,32 +5909,30 @@
       </c>
       <c r="M64" s="8" t="n">
         <f aca="false">D64*K64</f>
-        <v>17260</v>
+        <v>13620</v>
       </c>
       <c r="N64" s="8" t="n">
         <f aca="false">D64*H64</f>
-        <v>15000</v>
+        <v>11840</v>
       </c>
       <c r="O64" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C64,F64)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="Q64" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="R64" s="7" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>158</v>
+      </c>
+      <c r="R64" s="7"/>
+    </row>
+    <row r="65" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="n">
         <v>62</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>28</v>
@@ -6017,17 +5944,17 @@
         <v>2600</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>28</v>
+        <v>157</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>3200</v>
+        <v>3499</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>4000</v>
+        <v>3499</v>
       </c>
       <c r="I65" s="10" t="n">
         <f aca="false">IF(E65=0,0,(E65-H65)/E65)</f>
-        <v>-0.538461538461538</v>
+        <v>-0.345769230769231</v>
       </c>
       <c r="J65" s="6" t="str">
         <f aca="false">IF(E65&lt;G65,"LOSS",IF(E65&lt;H65*1.1,"THIN / RISK",IF(E65&gt;H65*1.8,"OVERPRICED?","OK")))</f>
@@ -6035,7 +5962,7 @@
       </c>
       <c r="K65" s="8" t="n">
         <f aca="false">IF(J65="OVERPRICED?",ROUND(H65*1.35,-1),MAX(E65,ROUND(H65*(1+$E$3),-1)))</f>
-        <v>4600</v>
+        <v>4020</v>
       </c>
       <c r="L65" s="8" t="n">
         <f aca="false">D65*E65</f>
@@ -6043,24 +5970,24 @@
       </c>
       <c r="M65" s="8" t="n">
         <f aca="false">D65*K65</f>
-        <v>13800</v>
+        <v>12060</v>
       </c>
       <c r="N65" s="8" t="n">
         <f aca="false">D65*H65</f>
-        <v>12000</v>
+        <v>10497</v>
       </c>
       <c r="O65" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C65,F65)),"","YES")</f>
-        <v/>
+        <v>YES</v>
       </c>
       <c r="P65" s="6" t="s">
         <v>24</v>
       </c>
       <c r="Q65" s="7" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="R65" s="7" t="s">
-        <v>172</v>
+        <v>26</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6068,7 +5995,7 @@
         <v>63</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>28</v>
@@ -6080,25 +6007,25 @@
         <v>5551</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>28</v>
+        <v>157</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>10500</v>
+        <v>4630</v>
       </c>
       <c r="H66" s="9" t="n">
-        <v>12500</v>
+        <v>4630</v>
       </c>
       <c r="I66" s="10" t="n">
         <f aca="false">IF(E66=0,0,(E66-H66)/E66)</f>
-        <v>-1.2518465141416</v>
+        <v>0.165916051161953</v>
       </c>
       <c r="J66" s="6" t="str">
         <f aca="false">IF(E66&lt;G66,"LOSS",IF(E66&lt;H66*1.1,"THIN / RISK",IF(E66&gt;H66*1.8,"OVERPRICED?","OK")))</f>
-        <v>LOSS</v>
+        <v>OK</v>
       </c>
       <c r="K66" s="8" t="n">
         <f aca="false">IF(J66="OVERPRICED?",ROUND(H66*1.35,-1),MAX(E66,ROUND(H66*(1+$E$3),-1)))</f>
-        <v>14380</v>
+        <v>5551</v>
       </c>
       <c r="L66" s="8" t="n">
         <f aca="false">D66*E66</f>
@@ -6106,32 +6033,30 @@
       </c>
       <c r="M66" s="8" t="n">
         <f aca="false">D66*K66</f>
-        <v>14380</v>
+        <v>5551</v>
       </c>
       <c r="N66" s="8" t="n">
         <f aca="false">D66*H66</f>
-        <v>12500</v>
+        <v>4630</v>
       </c>
       <c r="O66" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C66,F66)),"","YES")</f>
-        <v/>
+        <v>YES</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="Q66" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="R66" s="7" t="s">
-        <v>175</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="R66" s="7"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="6" t="n">
         <v>64</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>28</v>
@@ -6143,7 +6068,7 @@
         <v>1560</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="G67" s="9" t="n">
         <v>1350</v>
@@ -6180,10 +6105,10 @@
         <v>YES</v>
       </c>
       <c r="P67" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q67" s="7" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="R67" s="7"/>
     </row>
@@ -6192,7 +6117,7 @@
         <v>65</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>28</v>
@@ -6204,7 +6129,7 @@
         <v>1560</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="G68" s="9" t="n">
         <v>1350</v>
@@ -6241,10 +6166,10 @@
         <v>YES</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q68" s="7" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="R68" s="7"/>
     </row>
@@ -6253,7 +6178,7 @@
         <v>66</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>28</v>
@@ -6265,7 +6190,7 @@
         <v>11700</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="G69" s="9" t="n">
         <v>14000</v>
@@ -6302,13 +6227,13 @@
         <v>YES</v>
       </c>
       <c r="P69" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q69" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R69" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6316,7 +6241,7 @@
         <v>67</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>28</v>
@@ -6328,7 +6253,7 @@
         <v>9750</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="G70" s="9" t="n">
         <v>12000</v>
@@ -6365,13 +6290,13 @@
         <v>YES</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q70" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R70" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6379,7 +6304,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>28</v>
@@ -6391,7 +6316,7 @@
         <v>23400</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="G71" s="9" t="n">
         <v>15000</v>
@@ -6428,13 +6353,13 @@
         <v>YES</v>
       </c>
       <c r="P71" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q71" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R71" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6442,7 +6367,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>28</v>
@@ -6454,7 +6379,7 @@
         <v>32500</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="G72" s="9" t="n">
         <v>25000</v>
@@ -6491,13 +6416,13 @@
         <v>YES</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q72" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R72" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6505,7 +6430,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>28</v>
@@ -6517,25 +6442,25 @@
         <v>1105</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>131</v>
+        <v>43</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="I73" s="10" t="n">
         <f aca="false">IF(E73=0,0,(E73-H73)/E73)</f>
-        <v>-0.085972850678733</v>
+        <v>0.0950226244343891</v>
       </c>
       <c r="J73" s="6" t="str">
         <f aca="false">IF(E73&lt;G73,"LOSS",IF(E73&lt;H73*1.1,"THIN / RISK",IF(E73&gt;H73*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>OK</v>
       </c>
       <c r="K73" s="8" t="n">
         <f aca="false">IF(J73="OVERPRICED?",ROUND(H73*1.35,-1),MAX(E73,ROUND(H73*(1+$E$3),-1)))</f>
-        <v>1380</v>
+        <v>1150</v>
       </c>
       <c r="L73" s="8" t="n">
         <f aca="false">D73*E73</f>
@@ -6543,32 +6468,30 @@
       </c>
       <c r="M73" s="8" t="n">
         <f aca="false">D73*K73</f>
-        <v>1380</v>
+        <v>1150</v>
       </c>
       <c r="N73" s="8" t="n">
         <f aca="false">D73*H73</f>
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="O73" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C73,F73)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P73" s="6" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="Q73" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="R73" s="7" t="s">
-        <v>186</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="R73" s="7"/>
     </row>
     <row r="74" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="6" t="n">
         <v>73</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>28</v>
@@ -6580,25 +6503,25 @@
         <v>45500</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="G74" s="9" t="n">
-        <v>35000</v>
+        <v>22185</v>
       </c>
       <c r="H74" s="9" t="n">
-        <v>55000</v>
+        <v>22185</v>
       </c>
       <c r="I74" s="10" t="n">
         <f aca="false">IF(E74=0,0,(E74-H74)/E74)</f>
-        <v>-0.208791208791209</v>
+        <v>0.512417582417582</v>
       </c>
       <c r="J74" s="6" t="str">
         <f aca="false">IF(E74&lt;G74,"LOSS",IF(E74&lt;H74*1.1,"THIN / RISK",IF(E74&gt;H74*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>OVERPRICED?</v>
       </c>
       <c r="K74" s="8" t="n">
         <f aca="false">IF(J74="OVERPRICED?",ROUND(H74*1.35,-1),MAX(E74,ROUND(H74*(1+$E$3),-1)))</f>
-        <v>63250</v>
+        <v>29950</v>
       </c>
       <c r="L74" s="8" t="n">
         <f aca="false">D74*E74</f>
@@ -6606,11 +6529,11 @@
       </c>
       <c r="M74" s="8" t="n">
         <f aca="false">D74*K74</f>
-        <v>63250</v>
+        <v>29950</v>
       </c>
       <c r="N74" s="8" t="n">
         <f aca="false">D74*H74</f>
-        <v>55000</v>
+        <v>22185</v>
       </c>
       <c r="O74" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C74,F74)),"","YES")</f>
@@ -6620,10 +6543,10 @@
         <v>24</v>
       </c>
       <c r="Q74" s="7" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="R74" s="7" t="s">
-        <v>190</v>
+        <v>26</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6631,7 +6554,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>28</v>
@@ -6643,7 +6566,7 @@
         <v>23400</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="G75" s="9" t="n">
         <v>45000</v>
@@ -6680,13 +6603,13 @@
         <v>YES</v>
       </c>
       <c r="P75" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q75" s="7" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="R75" s="7" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6694,7 +6617,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>28</v>
@@ -6706,7 +6629,7 @@
         <v>1950</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="G76" s="9" t="n">
         <v>9790</v>
@@ -6743,13 +6666,13 @@
         <v>YES</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q76" s="7" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="R76" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6757,7 +6680,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>28</v>
@@ -6769,7 +6692,7 @@
         <v>2080</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="G77" s="9" t="n">
         <v>11060</v>
@@ -6806,13 +6729,13 @@
         <v>YES</v>
       </c>
       <c r="P77" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q77" s="7" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="R77" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6820,7 +6743,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>28</v>
@@ -6832,7 +6755,7 @@
         <v>2210</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="G78" s="9" t="n">
         <v>11700</v>
@@ -6869,13 +6792,13 @@
         <v>YES</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q78" s="7" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="R78" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6883,7 +6806,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>28</v>
@@ -6895,7 +6818,7 @@
         <v>2340</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="G79" s="9" t="n">
         <v>12330</v>
@@ -6932,13 +6855,13 @@
         <v>YES</v>
       </c>
       <c r="P79" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q79" s="7" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="R79" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6946,7 +6869,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>28</v>
@@ -6958,7 +6881,7 @@
         <v>2470</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="G80" s="9" t="n">
         <v>12970</v>
@@ -6995,13 +6918,13 @@
         <v>YES</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q80" s="7" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="R80" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7009,7 +6932,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>28</v>
@@ -7021,7 +6944,7 @@
         <v>2600</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="G81" s="9" t="n">
         <v>13600</v>
@@ -7058,13 +6981,13 @@
         <v>YES</v>
       </c>
       <c r="P81" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q81" s="7" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="R81" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7072,7 +6995,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>28</v>
@@ -7084,7 +7007,7 @@
         <v>2730</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="G82" s="9" t="n">
         <v>14240</v>
@@ -7121,13 +7044,13 @@
         <v>YES</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q82" s="7" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="R82" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7135,7 +7058,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>28</v>
@@ -7147,7 +7070,7 @@
         <v>3250</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="G83" s="9" t="n">
         <v>16140</v>
@@ -7184,13 +7107,13 @@
         <v>YES</v>
       </c>
       <c r="P83" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q83" s="7" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="R83" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7198,7 +7121,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>28</v>
@@ -7210,7 +7133,7 @@
         <v>4160</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="G84" s="9" t="n">
         <v>19230</v>
@@ -7247,13 +7170,13 @@
         <v>YES</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q84" s="7" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="R84" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7261,7 +7184,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>28</v>
@@ -7273,7 +7196,7 @@
         <v>5850</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="G85" s="9" t="n">
         <v>26490</v>
@@ -7310,13 +7233,13 @@
         <v>YES</v>
       </c>
       <c r="P85" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q85" s="7" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="R85" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7324,7 +7247,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>28</v>
@@ -7336,7 +7259,7 @@
         <v>8450</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="G86" s="9" t="n">
         <v>38450</v>
@@ -7373,13 +7296,13 @@
         <v>YES</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q86" s="7" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="R86" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7387,7 +7310,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>28</v>
@@ -7399,7 +7322,7 @@
         <v>9750</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="G87" s="9" t="n">
         <v>44060</v>
@@ -7436,13 +7359,13 @@
         <v>YES</v>
       </c>
       <c r="P87" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q87" s="7" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="R87" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7450,7 +7373,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>28</v>
@@ -7462,7 +7385,7 @@
         <v>11700</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="G88" s="9" t="n">
         <v>52470</v>
@@ -7499,13 +7422,13 @@
         <v>YES</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q88" s="7" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="R88" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7513,7 +7436,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>28</v>
@@ -7525,7 +7448,7 @@
         <v>4550</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="G89" s="9" t="n">
         <v>3500</v>
@@ -7562,13 +7485,13 @@
         <v>YES</v>
       </c>
       <c r="P89" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q89" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R89" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7576,7 +7499,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>28</v>
@@ -7588,7 +7511,7 @@
         <v>5850</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="G90" s="9" t="n">
         <v>4500</v>
@@ -7625,13 +7548,13 @@
         <v>YES</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q90" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R90" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7639,7 +7562,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>28</v>
@@ -7651,7 +7574,7 @@
         <v>7150</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="G91" s="9" t="n">
         <v>5500</v>
@@ -7688,13 +7611,13 @@
         <v>YES</v>
       </c>
       <c r="P91" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q91" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R91" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7702,7 +7625,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>28</v>
@@ -7714,7 +7637,7 @@
         <v>2340</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="G92" s="9" t="n">
         <v>2500</v>
@@ -7751,13 +7674,13 @@
         <v>YES</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q92" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R92" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7765,7 +7688,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>28</v>
@@ -7777,7 +7700,7 @@
         <v>2860</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="G93" s="9" t="n">
         <v>3000</v>
@@ -7814,13 +7737,13 @@
         <v>YES</v>
       </c>
       <c r="P93" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q93" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R93" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7828,10 +7751,10 @@
         <v>93</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="D94" s="6" t="n">
         <v>2</v>
@@ -7840,7 +7763,7 @@
         <v>25350</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="G94" s="9" t="n">
         <v>18100</v>
@@ -7877,10 +7800,10 @@
         <v/>
       </c>
       <c r="P94" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q94" s="7" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="R94" s="7"/>
     </row>
@@ -7889,10 +7812,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="D95" s="6" t="n">
         <v>3</v>
@@ -7901,7 +7824,7 @@
         <v>8138</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="G95" s="9" t="n">
         <v>15800</v>
@@ -7938,10 +7861,10 @@
         <v/>
       </c>
       <c r="P95" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q95" s="7" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="R95" s="7"/>
     </row>
@@ -7950,10 +7873,10 @@
         <v>95</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="D96" s="6" t="n">
         <v>3</v>
@@ -7962,7 +7885,7 @@
         <v>6370</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="G96" s="9" t="n">
         <v>7928</v>
@@ -7999,10 +7922,10 @@
         <v/>
       </c>
       <c r="P96" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q96" s="7" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="R96" s="7"/>
     </row>
@@ -8011,7 +7934,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>28</v>
@@ -8023,7 +7946,7 @@
         <v>14950</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="G97" s="9" t="n">
         <v>15000</v>
@@ -8060,13 +7983,13 @@
         <v>YES</v>
       </c>
       <c r="P97" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q97" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R97" s="7" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8074,10 +7997,10 @@
         <v>97</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="D98" s="6" t="n">
         <v>2</v>
@@ -8086,7 +8009,7 @@
         <v>286000</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="G98" s="9" t="n">
         <v>199500</v>
@@ -8123,13 +8046,13 @@
         <v/>
       </c>
       <c r="P98" s="6" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="Q98" s="7" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="R98" s="7" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8137,10 +8060,10 @@
         <v>98</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="D99" s="6" t="n">
         <v>1</v>
@@ -8149,7 +8072,7 @@
         <v>15600</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="G99" s="9" t="n">
         <v>12000</v>
@@ -8186,13 +8109,13 @@
         <v/>
       </c>
       <c r="P99" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q99" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R99" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8200,7 +8123,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>28</v>
@@ -8212,7 +8135,7 @@
         <v>11050</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="G100" s="9" t="n">
         <v>8000</v>
@@ -8249,13 +8172,13 @@
         <v>YES</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q100" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R100" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8263,7 +8186,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>28</v>
@@ -8275,7 +8198,7 @@
         <v>9100</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="G101" s="9" t="n">
         <v>6500</v>
@@ -8312,13 +8235,13 @@
         <v>YES</v>
       </c>
       <c r="P101" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q101" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R101" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8326,7 +8249,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>28</v>
@@ -8338,7 +8261,7 @@
         <v>7150</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="G102" s="9" t="n">
         <v>5500</v>
@@ -8375,13 +8298,13 @@
         <v>YES</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q102" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R102" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8389,7 +8312,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>28</v>
@@ -8401,7 +8324,7 @@
         <v>5850</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="G103" s="9" t="n">
         <v>4500</v>
@@ -8438,21 +8361,21 @@
         <v>YES</v>
       </c>
       <c r="P103" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q103" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R103" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="6" t="n">
         <v>103</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>22</v>
@@ -8464,17 +8387,17 @@
         <v>715</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="G104" s="9" t="n">
-        <v>350</v>
+        <v>540</v>
       </c>
       <c r="H104" s="9" t="n">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="I104" s="10" t="n">
         <f aca="false">IF(E104=0,0,(E104-H104)/E104)</f>
-        <v>0.230769230769231</v>
+        <v>0.244755244755245</v>
       </c>
       <c r="J104" s="6" t="str">
         <f aca="false">IF(E104&lt;G104,"LOSS",IF(E104&lt;H104*1.1,"THIN / RISK",IF(E104&gt;H104*1.8,"OVERPRICED?","OK")))</f>
@@ -8494,28 +8417,26 @@
       </c>
       <c r="N104" s="8" t="n">
         <f aca="false">D104*H104</f>
-        <v>6600</v>
+        <v>6480</v>
       </c>
       <c r="O104" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C104,F104)),"","YES")</f>
-        <v/>
+        <v>YES</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="Q104" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="R104" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="R104" s="7"/>
     </row>
     <row r="105" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="6" t="n">
         <v>104</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>22</v>
@@ -8564,13 +8485,13 @@
         <v/>
       </c>
       <c r="P105" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q105" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R105" s="7" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8578,7 +8499,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>245</v>
+        <v>231</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>22</v>
@@ -8590,7 +8511,7 @@
         <v>1170</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="G106" s="9" t="n">
         <v>800</v>
@@ -8627,19 +8548,19 @@
         <v>YES</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q106" s="7" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="R106" s="7"/>
     </row>
-    <row r="107" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="6" t="n">
         <v>106</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>28</v>
@@ -8651,17 +8572,17 @@
         <v>3640</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>131</v>
+        <v>43</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>2000</v>
+        <v>2420</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>2800</v>
+        <v>2420</v>
       </c>
       <c r="I107" s="10" t="n">
         <f aca="false">IF(E107=0,0,(E107-H107)/E107)</f>
-        <v>0.230769230769231</v>
+        <v>0.335164835164835</v>
       </c>
       <c r="J107" s="6" t="str">
         <f aca="false">IF(E107&lt;G107,"LOSS",IF(E107&lt;H107*1.1,"THIN / RISK",IF(E107&gt;H107*1.8,"OVERPRICED?","OK")))</f>
@@ -8681,28 +8602,26 @@
       </c>
       <c r="N107" s="8" t="n">
         <f aca="false">D107*H107</f>
-        <v>16800</v>
+        <v>14520</v>
       </c>
       <c r="O107" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C107,F107)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P107" s="6" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="Q107" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="R107" s="7" t="s">
-        <v>249</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="R107" s="7"/>
     </row>
     <row r="108" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="6" t="n">
         <v>107</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>28</v>
@@ -8714,7 +8633,7 @@
         <v>6760</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="G108" s="9" t="n">
         <v>4500</v>
@@ -8751,13 +8670,13 @@
         <v>YES</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q108" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R108" s="7" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8765,7 +8684,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>28</v>
@@ -8777,25 +8696,25 @@
         <v>4550</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>131</v>
+        <v>43</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>3800</v>
+        <v>3350</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>4200</v>
+        <v>3350</v>
       </c>
       <c r="I109" s="10" t="n">
         <f aca="false">IF(E109=0,0,(E109-H109)/E109)</f>
-        <v>0.0769230769230769</v>
+        <v>0.263736263736264</v>
       </c>
       <c r="J109" s="6" t="str">
         <f aca="false">IF(E109&lt;G109,"LOSS",IF(E109&lt;H109*1.1,"THIN / RISK",IF(E109&gt;H109*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>OK</v>
       </c>
       <c r="K109" s="8" t="n">
         <f aca="false">IF(J109="OVERPRICED?",ROUND(H109*1.35,-1),MAX(E109,ROUND(H109*(1+$E$3),-1)))</f>
-        <v>4830</v>
+        <v>4550</v>
       </c>
       <c r="L109" s="8" t="n">
         <f aca="false">D109*E109</f>
@@ -8803,32 +8722,30 @@
       </c>
       <c r="M109" s="8" t="n">
         <f aca="false">D109*K109</f>
-        <v>14490</v>
+        <v>13650</v>
       </c>
       <c r="N109" s="8" t="n">
         <f aca="false">D109*H109</f>
-        <v>12600</v>
+        <v>10050</v>
       </c>
       <c r="O109" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C109,F109)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P109" s="6" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="Q109" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="R109" s="7" t="s">
-        <v>254</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="R109" s="7"/>
     </row>
     <row r="110" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="6" t="n">
         <v>109</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>28</v>
@@ -8840,7 +8757,7 @@
         <v>2340</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="G110" s="9" t="n">
         <v>1800</v>
@@ -8877,13 +8794,13 @@
         <v>YES</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q110" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R110" s="7" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8891,7 +8808,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>28</v>
@@ -8903,25 +8820,25 @@
         <v>1820</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>183</v>
+        <v>157</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>2000</v>
+        <v>860</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>2800</v>
+        <v>860</v>
       </c>
       <c r="I111" s="10" t="n">
         <f aca="false">IF(E111=0,0,(E111-H111)/E111)</f>
-        <v>-0.538461538461538</v>
+        <v>0.527472527472528</v>
       </c>
       <c r="J111" s="6" t="str">
         <f aca="false">IF(E111&lt;G111,"LOSS",IF(E111&lt;H111*1.1,"THIN / RISK",IF(E111&gt;H111*1.8,"OVERPRICED?","OK")))</f>
-        <v>LOSS</v>
+        <v>OVERPRICED?</v>
       </c>
       <c r="K111" s="8" t="n">
         <f aca="false">IF(J111="OVERPRICED?",ROUND(H111*1.35,-1),MAX(E111,ROUND(H111*(1+$E$3),-1)))</f>
-        <v>3220</v>
+        <v>1160</v>
       </c>
       <c r="L111" s="8" t="n">
         <f aca="false">D111*E111</f>
@@ -8929,11 +8846,11 @@
       </c>
       <c r="M111" s="8" t="n">
         <f aca="false">D111*K111</f>
-        <v>9660</v>
+        <v>3480</v>
       </c>
       <c r="N111" s="8" t="n">
         <f aca="false">D111*H111</f>
-        <v>8400</v>
+        <v>2580</v>
       </c>
       <c r="O111" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C111,F111)),"","YES")</f>
@@ -8943,18 +8860,18 @@
         <v>24</v>
       </c>
       <c r="Q111" s="7" t="s">
-        <v>156</v>
+        <v>243</v>
       </c>
       <c r="R111" s="7" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="6" t="n">
         <v>111</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>28</v>
@@ -8966,17 +8883,17 @@
         <v>2860</v>
       </c>
       <c r="F112" s="7" t="s">
-        <v>183</v>
+        <v>54</v>
       </c>
       <c r="G112" s="9" t="n">
-        <v>4000</v>
+        <v>3125</v>
       </c>
       <c r="H112" s="9" t="n">
-        <v>5500</v>
+        <v>3125</v>
       </c>
       <c r="I112" s="10" t="n">
         <f aca="false">IF(E112=0,0,(E112-H112)/E112)</f>
-        <v>-0.923076923076923</v>
+        <v>-0.0926573426573427</v>
       </c>
       <c r="J112" s="6" t="str">
         <f aca="false">IF(E112&lt;G112,"LOSS",IF(E112&lt;H112*1.1,"THIN / RISK",IF(E112&gt;H112*1.8,"OVERPRICED?","OK")))</f>
@@ -8984,7 +8901,7 @@
       </c>
       <c r="K112" s="8" t="n">
         <f aca="false">IF(J112="OVERPRICED?",ROUND(H112*1.35,-1),MAX(E112,ROUND(H112*(1+$E$3),-1)))</f>
-        <v>6330</v>
+        <v>3590</v>
       </c>
       <c r="L112" s="8" t="n">
         <f aca="false">D112*E112</f>
@@ -8992,11 +8909,11 @@
       </c>
       <c r="M112" s="8" t="n">
         <f aca="false">D112*K112</f>
-        <v>18990</v>
+        <v>10770</v>
       </c>
       <c r="N112" s="8" t="n">
         <f aca="false">D112*H112</f>
-        <v>16500</v>
+        <v>9375</v>
       </c>
       <c r="O112" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C112,F112)),"","YES")</f>
@@ -9006,10 +8923,10 @@
         <v>24</v>
       </c>
       <c r="Q112" s="7" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="R112" s="7" t="s">
-        <v>261</v>
+        <v>26</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9017,7 +8934,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>28</v>
@@ -9029,25 +8946,25 @@
         <v>12350</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>263</v>
+        <v>22</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>8000</v>
+        <v>8500</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>12000</v>
+        <v>8500</v>
       </c>
       <c r="I113" s="10" t="n">
         <f aca="false">IF(E113=0,0,(E113-H113)/E113)</f>
-        <v>0.0283400809716599</v>
+        <v>0.311740890688259</v>
       </c>
       <c r="J113" s="6" t="str">
         <f aca="false">IF(E113&lt;G113,"LOSS",IF(E113&lt;H113*1.1,"THIN / RISK",IF(E113&gt;H113*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>OK</v>
       </c>
       <c r="K113" s="8" t="n">
         <f aca="false">IF(J113="OVERPRICED?",ROUND(H113*1.35,-1),MAX(E113,ROUND(H113*(1+$E$3),-1)))</f>
-        <v>13800</v>
+        <v>12350</v>
       </c>
       <c r="L113" s="8" t="n">
         <f aca="false">D113*E113</f>
@@ -9055,32 +8972,30 @@
       </c>
       <c r="M113" s="8" t="n">
         <f aca="false">D113*K113</f>
-        <v>27600</v>
+        <v>24700</v>
       </c>
       <c r="N113" s="8" t="n">
         <f aca="false">D113*H113</f>
-        <v>24000</v>
+        <v>17000</v>
       </c>
       <c r="O113" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C113,F113)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P113" s="6" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="Q113" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="R113" s="7" t="s">
-        <v>264</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="R113" s="7"/>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="6" t="n">
         <v>113</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>28</v>
@@ -9095,22 +9010,22 @@
         <v>22</v>
       </c>
       <c r="G114" s="9" t="n">
-        <v>800</v>
+        <v>1600</v>
       </c>
       <c r="H114" s="9" t="n">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="I114" s="10" t="n">
         <f aca="false">IF(E114=0,0,(E114-H114)/E114)</f>
-        <v>0.230769230769231</v>
+        <v>-0.0256410256410256</v>
       </c>
       <c r="J114" s="6" t="str">
         <f aca="false">IF(E114&lt;G114,"LOSS",IF(E114&lt;H114*1.1,"THIN / RISK",IF(E114&gt;H114*1.8,"OVERPRICED?","OK")))</f>
-        <v>OK</v>
+        <v>LOSS</v>
       </c>
       <c r="K114" s="8" t="n">
         <f aca="false">IF(J114="OVERPRICED?",ROUND(H114*1.35,-1),MAX(E114,ROUND(H114*(1+$E$3),-1)))</f>
-        <v>1560</v>
+        <v>1840</v>
       </c>
       <c r="L114" s="8" t="n">
         <f aca="false">D114*E114</f>
@@ -9118,32 +9033,30 @@
       </c>
       <c r="M114" s="8" t="n">
         <f aca="false">D114*K114</f>
-        <v>4680</v>
+        <v>5520</v>
       </c>
       <c r="N114" s="8" t="n">
         <f aca="false">D114*H114</f>
-        <v>3600</v>
+        <v>4800</v>
       </c>
       <c r="O114" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C114,F114)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="Q114" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="R114" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="R114" s="7"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="6" t="n">
         <v>114</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>28</v>
@@ -9158,14 +9071,14 @@
         <v>22</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>900</v>
+        <v>1600</v>
       </c>
       <c r="H115" s="9" t="n">
-        <v>1400</v>
+        <v>1600</v>
       </c>
       <c r="I115" s="10" t="n">
         <f aca="false">IF(E115=0,0,(E115-H115)/E115)</f>
-        <v>0.282051282051282</v>
+        <v>0.17948717948718</v>
       </c>
       <c r="J115" s="6" t="str">
         <f aca="false">IF(E115&lt;G115,"LOSS",IF(E115&lt;H115*1.1,"THIN / RISK",IF(E115&gt;H115*1.8,"OVERPRICED?","OK")))</f>
@@ -9185,28 +9098,26 @@
       </c>
       <c r="N115" s="8" t="n">
         <f aca="false">D115*H115</f>
-        <v>4200</v>
+        <v>4800</v>
       </c>
       <c r="O115" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C115,F115)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P115" s="6" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="Q115" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="R115" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="R115" s="7"/>
     </row>
     <row r="116" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="6" t="n">
         <v>115</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>22</v>
@@ -9218,7 +9129,7 @@
         <v>11050</v>
       </c>
       <c r="F116" s="7" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="G116" s="9" t="n">
         <v>5000</v>
@@ -9255,10 +9166,10 @@
         <v>YES</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q116" s="7" t="s">
-        <v>269</v>
+        <v>253</v>
       </c>
       <c r="R116" s="7"/>
     </row>
@@ -9267,7 +9178,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>270</v>
+        <v>254</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>28</v>
@@ -9316,13 +9227,13 @@
         <v>YES</v>
       </c>
       <c r="P117" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q117" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R117" s="7" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9330,7 +9241,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>272</v>
+        <v>256</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>22</v>
@@ -9379,13 +9290,13 @@
         <v/>
       </c>
       <c r="P118" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q118" s="7" t="s">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="R118" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9393,7 +9304,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>22</v>
@@ -9442,13 +9353,13 @@
         <v/>
       </c>
       <c r="P119" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q119" s="7" t="s">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="R119" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9456,7 +9367,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>275</v>
+        <v>259</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>28</v>
@@ -9505,13 +9416,13 @@
         <v>YES</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q120" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R120" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9519,7 +9430,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>276</v>
+        <v>260</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>22</v>
@@ -9568,13 +9479,13 @@
         <v/>
       </c>
       <c r="P121" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q121" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R121" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9582,7 +9493,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>277</v>
+        <v>261</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>22</v>
@@ -9594,7 +9505,7 @@
         <v>637</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G122" s="9" t="n">
         <v>600</v>
@@ -9631,10 +9542,10 @@
         <v>YES</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q122" s="7" t="s">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="R122" s="7"/>
     </row>
@@ -9643,7 +9554,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>22</v>
@@ -9655,25 +9566,25 @@
         <v>357500</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>280</v>
+        <v>264</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>200000</v>
+        <v>126000</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>330000</v>
+        <v>126000</v>
       </c>
       <c r="I123" s="10" t="n">
         <f aca="false">IF(E123=0,0,(E123-H123)/E123)</f>
-        <v>0.0769230769230769</v>
+        <v>0.647552447552448</v>
       </c>
       <c r="J123" s="6" t="str">
         <f aca="false">IF(E123&lt;G123,"LOSS",IF(E123&lt;H123*1.1,"THIN / RISK",IF(E123&gt;H123*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>OVERPRICED?</v>
       </c>
       <c r="K123" s="8" t="n">
         <f aca="false">IF(J123="OVERPRICED?",ROUND(H123*1.35,-1),MAX(E123,ROUND(H123*(1+$E$3),-1)))</f>
-        <v>379500</v>
+        <v>170100</v>
       </c>
       <c r="L123" s="8" t="n">
         <f aca="false">D123*E123</f>
@@ -9681,24 +9592,24 @@
       </c>
       <c r="M123" s="8" t="n">
         <f aca="false">D123*K123</f>
-        <v>379500</v>
+        <v>170100</v>
       </c>
       <c r="N123" s="8" t="n">
         <f aca="false">D123*H123</f>
-        <v>330000</v>
+        <v>126000</v>
       </c>
       <c r="O123" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C123,F123)),"","YES")</f>
-        <v/>
+        <v>YES</v>
       </c>
       <c r="P123" s="6" t="s">
         <v>24</v>
       </c>
       <c r="Q123" s="7" t="s">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="R123" s="7" t="s">
-        <v>282</v>
+        <v>26</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9706,7 +9617,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="C124" s="6" t="s">
         <v>22</v>
@@ -9755,13 +9666,13 @@
         <v/>
       </c>
       <c r="P124" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q124" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R124" s="7" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9769,7 +9680,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>22</v>
@@ -9818,13 +9729,13 @@
         <v/>
       </c>
       <c r="P125" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q125" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R125" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9832,7 +9743,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>22</v>
@@ -9881,13 +9792,13 @@
         <v/>
       </c>
       <c r="P126" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q126" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R126" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9895,7 +9806,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>22</v>
@@ -9944,13 +9855,13 @@
         <v/>
       </c>
       <c r="P127" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q127" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R127" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9958,7 +9869,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>22</v>
@@ -10007,13 +9918,13 @@
         <v/>
       </c>
       <c r="P128" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q128" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R128" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10021,7 +9932,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>22</v>
@@ -10070,13 +9981,13 @@
         <v/>
       </c>
       <c r="P129" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q129" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R129" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10084,7 +9995,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>22</v>
@@ -10133,13 +10044,13 @@
         <v/>
       </c>
       <c r="P130" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q130" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R130" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10147,7 +10058,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>22</v>
@@ -10196,13 +10107,13 @@
         <v/>
       </c>
       <c r="P131" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q131" s="7" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="R131" s="7" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10210,7 +10121,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>22</v>
@@ -10222,7 +10133,7 @@
         <v>7800</v>
       </c>
       <c r="F132" s="7" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="G132" s="9" t="n">
         <v>5000</v>
@@ -10259,10 +10170,10 @@
         <v>YES</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q132" s="7" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="R132" s="7"/>
     </row>
@@ -10271,7 +10182,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="7" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>22</v>
@@ -10320,13 +10231,13 @@
         <v/>
       </c>
       <c r="P133" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q133" s="7" t="s">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="R133" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10334,7 +10245,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>28</v>
@@ -10383,13 +10294,13 @@
         <v>YES</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q134" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R134" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10397,7 +10308,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>22</v>
@@ -10446,13 +10357,13 @@
         <v/>
       </c>
       <c r="P135" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q135" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R135" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10460,7 +10371,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="7" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="C136" s="6" t="s">
         <v>22</v>
@@ -10472,7 +10383,7 @@
         <v>2860</v>
       </c>
       <c r="F136" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G136" s="9" t="n">
         <v>990</v>
@@ -10509,10 +10420,10 @@
         <v>YES</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q136" s="7" t="s">
-        <v>301</v>
+        <v>284</v>
       </c>
       <c r="R136" s="7"/>
     </row>
@@ -10521,7 +10432,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="C137" s="6" t="s">
         <v>22</v>
@@ -10533,7 +10444,7 @@
         <v>130</v>
       </c>
       <c r="F137" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G137" s="9" t="n">
         <v>270</v>
@@ -10570,10 +10481,10 @@
         <v>YES</v>
       </c>
       <c r="P137" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q137" s="7" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="R137" s="7"/>
     </row>
@@ -10582,7 +10493,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>304</v>
+        <v>287</v>
       </c>
       <c r="C138" s="6" t="s">
         <v>22</v>
@@ -10594,7 +10505,7 @@
         <v>1170</v>
       </c>
       <c r="F138" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G138" s="9" t="n">
         <v>590</v>
@@ -10631,10 +10542,10 @@
         <v>YES</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q138" s="7" t="s">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="R138" s="7"/>
     </row>
@@ -10643,7 +10554,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="7" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="C139" s="6" t="s">
         <v>28</v>
@@ -10692,13 +10603,13 @@
         <v>YES</v>
       </c>
       <c r="P139" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q139" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R139" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10706,7 +10617,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="7" t="s">
-        <v>307</v>
+        <v>290</v>
       </c>
       <c r="C140" s="6" t="s">
         <v>22</v>
@@ -10755,13 +10666,13 @@
         <v/>
       </c>
       <c r="P140" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q140" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R140" s="7" t="s">
-        <v>308</v>
+        <v>291</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10769,7 +10680,7 @@
         <v>142</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
       <c r="C141" s="6" t="s">
         <v>22</v>
@@ -10781,7 +10692,7 @@
         <v>7150</v>
       </c>
       <c r="F141" s="7" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="G141" s="9" t="n">
         <v>5000</v>
@@ -10818,13 +10729,13 @@
         <v/>
       </c>
       <c r="P141" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q141" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R141" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10832,7 +10743,7 @@
         <v>143</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>311</v>
+        <v>294</v>
       </c>
       <c r="C142" s="6" t="s">
         <v>22</v>
@@ -10844,7 +10755,7 @@
         <v>7150</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="G142" s="9" t="n">
         <v>5000</v>
@@ -10881,13 +10792,13 @@
         <v/>
       </c>
       <c r="P142" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q142" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R142" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10895,7 +10806,7 @@
         <v>144</v>
       </c>
       <c r="B143" s="7" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="C143" s="6" t="s">
         <v>22</v>
@@ -10907,7 +10818,7 @@
         <v>8450</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="G143" s="9" t="n">
         <v>6000</v>
@@ -10944,13 +10855,13 @@
         <v/>
       </c>
       <c r="P143" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q143" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R143" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10958,7 +10869,7 @@
         <v>145</v>
       </c>
       <c r="B144" s="7" t="s">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="C144" s="6" t="s">
         <v>28</v>
@@ -10970,7 +10881,7 @@
         <v>104</v>
       </c>
       <c r="F144" s="7" t="s">
-        <v>314</v>
+        <v>297</v>
       </c>
       <c r="G144" s="9" t="n">
         <v>50</v>
@@ -11007,13 +10918,13 @@
         <v>YES</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q144" s="7" t="s">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="R144" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11021,7 +10932,7 @@
         <v>146</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>315</v>
+        <v>298</v>
       </c>
       <c r="C145" s="6" t="s">
         <v>22</v>
@@ -11033,7 +10944,7 @@
         <v>105788</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>316</v>
+        <v>299</v>
       </c>
       <c r="G145" s="9" t="n">
         <v>82000</v>
@@ -11070,10 +10981,10 @@
         <v/>
       </c>
       <c r="P145" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q145" s="7" t="s">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="R145" s="7"/>
     </row>
@@ -11082,7 +10993,7 @@
         <v>147</v>
       </c>
       <c r="B146" s="7" t="s">
-        <v>318</v>
+        <v>301</v>
       </c>
       <c r="C146" s="6" t="s">
         <v>22</v>
@@ -11094,7 +11005,7 @@
         <v>245700</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>316</v>
+        <v>299</v>
       </c>
       <c r="G146" s="9" t="n">
         <v>225000</v>
@@ -11131,19 +11042,19 @@
         <v/>
       </c>
       <c r="P146" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q146" s="7" t="s">
-        <v>319</v>
+        <v>302</v>
       </c>
       <c r="R146" s="7"/>
     </row>
-    <row r="147" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="6" t="n">
         <v>148</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="C147" s="6" t="s">
         <v>28</v>
@@ -11155,25 +11066,25 @@
         <v>650</v>
       </c>
       <c r="F147" s="7" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="G147" s="9" t="n">
-        <v>800</v>
+        <v>360</v>
       </c>
       <c r="H147" s="9" t="n">
-        <v>1200</v>
+        <v>360</v>
       </c>
       <c r="I147" s="10" t="n">
         <f aca="false">IF(E147=0,0,(E147-H147)/E147)</f>
-        <v>-0.846153846153846</v>
+        <v>0.446153846153846</v>
       </c>
       <c r="J147" s="6" t="str">
         <f aca="false">IF(E147&lt;G147,"LOSS",IF(E147&lt;H147*1.1,"THIN / RISK",IF(E147&gt;H147*1.8,"OVERPRICED?","OK")))</f>
-        <v>LOSS</v>
+        <v>OVERPRICED?</v>
       </c>
       <c r="K147" s="8" t="n">
         <f aca="false">IF(J147="OVERPRICED?",ROUND(H147*1.35,-1),MAX(E147,ROUND(H147*(1+$E$3),-1)))</f>
-        <v>1380</v>
+        <v>490</v>
       </c>
       <c r="L147" s="8" t="n">
         <f aca="false">D147*E147</f>
@@ -11181,32 +11092,30 @@
       </c>
       <c r="M147" s="8" t="n">
         <f aca="false">D147*K147</f>
-        <v>16560</v>
+        <v>5880</v>
       </c>
       <c r="N147" s="8" t="n">
         <f aca="false">D147*H147</f>
-        <v>14400</v>
+        <v>4320</v>
       </c>
       <c r="O147" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C147,F147)),"","YES")</f>
-        <v/>
+        <v>YES</v>
       </c>
       <c r="P147" s="6" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="Q147" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="R147" s="7" t="s">
-        <v>322</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="R147" s="7"/>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="6" t="n">
         <v>149</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="C148" s="6" t="s">
         <v>22</v>
@@ -11218,7 +11127,7 @@
         <v>1754</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
       <c r="G148" s="9" t="n">
         <v>1380</v>
@@ -11255,10 +11164,10 @@
         <v>YES</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q148" s="7" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="R148" s="7"/>
     </row>
@@ -11267,7 +11176,7 @@
         <v>150</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>326</v>
+        <v>308</v>
       </c>
       <c r="C149" s="6" t="s">
         <v>22</v>
@@ -11279,7 +11188,7 @@
         <v>1235</v>
       </c>
       <c r="F149" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G149" s="9" t="n">
         <v>900</v>
@@ -11316,10 +11225,10 @@
         <v>YES</v>
       </c>
       <c r="P149" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q149" s="7" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
       <c r="R149" s="7"/>
     </row>
@@ -11328,7 +11237,7 @@
         <v>151</v>
       </c>
       <c r="B150" s="7" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
       <c r="C150" s="6" t="s">
         <v>22</v>
@@ -11340,7 +11249,7 @@
         <v>650</v>
       </c>
       <c r="F150" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G150" s="9" t="n">
         <v>590</v>
@@ -11377,10 +11286,10 @@
         <v>YES</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q150" s="7" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
       <c r="R150" s="7"/>
     </row>
@@ -11389,7 +11298,7 @@
         <v>152</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>330</v>
+        <v>312</v>
       </c>
       <c r="C151" s="6" t="s">
         <v>22</v>
@@ -11401,7 +11310,7 @@
         <v>546</v>
       </c>
       <c r="F151" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G151" s="9" t="n">
         <v>550</v>
@@ -11438,10 +11347,10 @@
         <v>YES</v>
       </c>
       <c r="P151" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q151" s="7" t="s">
-        <v>331</v>
+        <v>313</v>
       </c>
       <c r="R151" s="7"/>
     </row>
@@ -11450,7 +11359,7 @@
         <v>153</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="C152" s="6" t="s">
         <v>22</v>
@@ -11462,7 +11371,7 @@
         <v>1105</v>
       </c>
       <c r="F152" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G152" s="9" t="n">
         <v>730</v>
@@ -11499,10 +11408,10 @@
         <v>YES</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q152" s="7" t="s">
-        <v>333</v>
+        <v>315</v>
       </c>
       <c r="R152" s="7"/>
     </row>
@@ -11511,7 +11420,7 @@
         <v>154</v>
       </c>
       <c r="B153" s="7" t="s">
-        <v>334</v>
+        <v>316</v>
       </c>
       <c r="C153" s="6" t="s">
         <v>22</v>
@@ -11560,13 +11469,13 @@
         <v/>
       </c>
       <c r="P153" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q153" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R153" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11574,7 +11483,7 @@
         <v>155</v>
       </c>
       <c r="B154" s="7" t="s">
-        <v>335</v>
+        <v>317</v>
       </c>
       <c r="C154" s="6" t="s">
         <v>22</v>
@@ -11586,7 +11495,7 @@
         <v>748</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>336</v>
+        <v>318</v>
       </c>
       <c r="G154" s="9" t="n">
         <v>450</v>
@@ -11623,10 +11532,10 @@
         <v>YES</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q154" s="7" t="s">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="R154" s="7"/>
     </row>
@@ -11635,7 +11544,7 @@
         <v>156</v>
       </c>
       <c r="B155" s="7" t="s">
-        <v>338</v>
+        <v>320</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>22</v>
@@ -11647,7 +11556,7 @@
         <v>748</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>336</v>
+        <v>318</v>
       </c>
       <c r="G155" s="9" t="n">
         <v>450</v>
@@ -11684,10 +11593,10 @@
         <v>YES</v>
       </c>
       <c r="P155" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q155" s="7" t="s">
-        <v>339</v>
+        <v>321</v>
       </c>
       <c r="R155" s="7"/>
     </row>
@@ -11696,7 +11605,7 @@
         <v>157</v>
       </c>
       <c r="B156" s="7" t="s">
-        <v>340</v>
+        <v>322</v>
       </c>
       <c r="C156" s="6" t="s">
         <v>22</v>
@@ -11708,7 +11617,7 @@
         <v>748</v>
       </c>
       <c r="F156" s="7" t="s">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="G156" s="9" t="n">
         <v>400</v>
@@ -11745,10 +11654,10 @@
         <v>YES</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q156" s="7" t="s">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="R156" s="7"/>
     </row>
@@ -11757,7 +11666,7 @@
         <v>158</v>
       </c>
       <c r="B157" s="7" t="s">
-        <v>343</v>
+        <v>325</v>
       </c>
       <c r="C157" s="6" t="s">
         <v>28</v>
@@ -11769,7 +11678,7 @@
         <v>311</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>314</v>
+        <v>297</v>
       </c>
       <c r="G157" s="9" t="n">
         <v>150</v>
@@ -11806,13 +11715,13 @@
         <v>YES</v>
       </c>
       <c r="P157" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q157" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R157" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11820,7 +11729,7 @@
         <v>159</v>
       </c>
       <c r="B158" s="7" t="s">
-        <v>344</v>
+        <v>326</v>
       </c>
       <c r="C158" s="6" t="s">
         <v>28</v>
@@ -11832,7 +11741,7 @@
         <v>325</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>314</v>
+        <v>297</v>
       </c>
       <c r="G158" s="9" t="n">
         <v>180</v>
@@ -11869,21 +11778,21 @@
         <v>YES</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q158" s="7" t="s">
-        <v>345</v>
+        <v>327</v>
       </c>
       <c r="R158" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="6" t="n">
         <v>160</v>
       </c>
       <c r="B159" s="7" t="s">
-        <v>346</v>
+        <v>328</v>
       </c>
       <c r="C159" s="6" t="s">
         <v>28</v>
@@ -11895,17 +11804,17 @@
         <v>117</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>347</v>
+        <v>329</v>
       </c>
       <c r="G159" s="9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H159" s="9" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="I159" s="10" t="n">
         <f aca="false">IF(E159=0,0,(E159-H159)/E159)</f>
-        <v>0.145299145299145</v>
+        <v>0.444444444444444</v>
       </c>
       <c r="J159" s="6" t="str">
         <f aca="false">IF(E159&lt;G159,"LOSS",IF(E159&lt;H159*1.1,"THIN / RISK",IF(E159&gt;H159*1.8,"OVERPRICED?","OK")))</f>
@@ -11913,7 +11822,7 @@
       </c>
       <c r="K159" s="8" t="n">
         <f aca="false">IF(J159="OVERPRICED?",ROUND(H159*1.35,-1),MAX(E159,ROUND(H159*(1+$E$3),-1)))</f>
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="L159" s="8" t="n">
         <f aca="false">D159*E159</f>
@@ -11921,11 +11830,11 @@
       </c>
       <c r="M159" s="8" t="n">
         <f aca="false">D159*K159</f>
-        <v>18000</v>
+        <v>17550</v>
       </c>
       <c r="N159" s="8" t="n">
         <f aca="false">D159*H159</f>
-        <v>15000</v>
+        <v>9750</v>
       </c>
       <c r="O159" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C159,F159)),"","YES")</f>
@@ -11935,10 +11844,10 @@
         <v>24</v>
       </c>
       <c r="Q159" s="7" t="s">
-        <v>156</v>
+        <v>330</v>
       </c>
       <c r="R159" s="7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11946,7 +11855,7 @@
         <v>161</v>
       </c>
       <c r="B160" s="7" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="C160" s="6" t="s">
         <v>28</v>
@@ -11958,7 +11867,7 @@
         <v>169</v>
       </c>
       <c r="F160" s="7" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="G160" s="9" t="n">
         <v>90</v>
@@ -11995,13 +11904,13 @@
         <v>YES</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q160" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R160" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12009,7 +11918,7 @@
         <v>162</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>349</v>
+        <v>333</v>
       </c>
       <c r="C161" s="6" t="s">
         <v>28</v>
@@ -12021,7 +11930,7 @@
         <v>234</v>
       </c>
       <c r="F161" s="7" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="G161" s="9" t="n">
         <v>120</v>
@@ -12058,13 +11967,13 @@
         <v>YES</v>
       </c>
       <c r="P161" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q161" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R161" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12072,7 +11981,7 @@
         <v>164</v>
       </c>
       <c r="B162" s="7" t="s">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="C162" s="6" t="s">
         <v>22</v>
@@ -12084,7 +11993,7 @@
         <v>1209</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>351</v>
+        <v>335</v>
       </c>
       <c r="G162" s="9" t="n">
         <v>1450</v>
@@ -12121,13 +12030,13 @@
         <v>YES</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="Q162" s="7" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="R162" s="7" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12135,7 +12044,7 @@
         <v>165</v>
       </c>
       <c r="B163" s="7" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="C163" s="6" t="s">
         <v>22</v>
@@ -12147,7 +12056,7 @@
         <v>1209</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>351</v>
+        <v>335</v>
       </c>
       <c r="G163" s="9" t="n">
         <v>2248</v>
@@ -12184,13 +12093,13 @@
         <v>YES</v>
       </c>
       <c r="P163" s="6" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="Q163" s="7" t="s">
-        <v>354</v>
+        <v>338</v>
       </c>
       <c r="R163" s="7" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12198,7 +12107,7 @@
         <v>166</v>
       </c>
       <c r="B164" s="7" t="s">
-        <v>355</v>
+        <v>339</v>
       </c>
       <c r="C164" s="6" t="s">
         <v>22</v>
@@ -12210,7 +12119,7 @@
         <v>3022</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="G164" s="9" t="n">
         <v>2325</v>
@@ -12247,13 +12156,13 @@
         <v>YES</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="Q164" s="7" t="s">
-        <v>357</v>
+        <v>341</v>
       </c>
       <c r="R164" s="7" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12261,7 +12170,7 @@
         <v>167</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="C165" s="6" t="s">
         <v>22</v>
@@ -12310,13 +12219,13 @@
         <v/>
       </c>
       <c r="P165" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q165" s="7" t="s">
-        <v>359</v>
+        <v>343</v>
       </c>
       <c r="R165" s="7" t="s">
-        <v>360</v>
+        <v>344</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12324,7 +12233,7 @@
         <v>168</v>
       </c>
       <c r="B166" s="7" t="s">
-        <v>361</v>
+        <v>345</v>
       </c>
       <c r="C166" s="6" t="s">
         <v>22</v>
@@ -12373,13 +12282,13 @@
         <v/>
       </c>
       <c r="P166" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q166" s="7" t="s">
-        <v>359</v>
+        <v>343</v>
       </c>
       <c r="R166" s="7" t="s">
-        <v>362</v>
+        <v>346</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12387,7 +12296,7 @@
         <v>177</v>
       </c>
       <c r="B167" s="7" t="s">
-        <v>363</v>
+        <v>347</v>
       </c>
       <c r="C167" s="6" t="s">
         <v>28</v>
@@ -12399,25 +12308,25 @@
         <v>5850</v>
       </c>
       <c r="F167" s="7" t="s">
-        <v>364</v>
+        <v>157</v>
       </c>
       <c r="G167" s="9" t="n">
-        <v>3500</v>
+        <v>794</v>
       </c>
       <c r="H167" s="9" t="n">
-        <v>5000</v>
+        <v>794</v>
       </c>
       <c r="I167" s="10" t="n">
         <f aca="false">IF(E167=0,0,(E167-H167)/E167)</f>
-        <v>0.145299145299145</v>
+        <v>0.864273504273504</v>
       </c>
       <c r="J167" s="6" t="str">
         <f aca="false">IF(E167&lt;G167,"LOSS",IF(E167&lt;H167*1.1,"THIN / RISK",IF(E167&gt;H167*1.8,"OVERPRICED?","OK")))</f>
-        <v>OK</v>
+        <v>OVERPRICED?</v>
       </c>
       <c r="K167" s="8" t="n">
         <f aca="false">IF(J167="OVERPRICED?",ROUND(H167*1.35,-1),MAX(E167,ROUND(H167*(1+$E$3),-1)))</f>
-        <v>5850</v>
+        <v>1070</v>
       </c>
       <c r="L167" s="8" t="n">
         <f aca="false">D167*E167</f>
@@ -12425,11 +12334,11 @@
       </c>
       <c r="M167" s="8" t="n">
         <f aca="false">D167*K167</f>
-        <v>17550</v>
+        <v>3210</v>
       </c>
       <c r="N167" s="8" t="n">
         <f aca="false">D167*H167</f>
-        <v>15000</v>
+        <v>2382</v>
       </c>
       <c r="O167" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C167,F167)),"","YES")</f>
@@ -12439,10 +12348,10 @@
         <v>24</v>
       </c>
       <c r="Q167" s="7" t="s">
-        <v>156</v>
+        <v>348</v>
       </c>
       <c r="R167" s="7" t="s">
-        <v>365</v>
+        <v>26</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12450,7 +12359,7 @@
         <v>179</v>
       </c>
       <c r="B168" s="7" t="s">
-        <v>366</v>
+        <v>349</v>
       </c>
       <c r="C168" s="6" t="s">
         <v>28</v>
@@ -12462,7 +12371,7 @@
         <v>23400</v>
       </c>
       <c r="F168" s="7" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="G168" s="9" t="n">
         <v>20000</v>
@@ -12499,13 +12408,13 @@
         <v>YES</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q168" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R168" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12513,7 +12422,7 @@
         <v>180</v>
       </c>
       <c r="B169" s="7" t="s">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="C169" s="6" t="s">
         <v>28</v>
@@ -12525,7 +12434,7 @@
         <v>15600</v>
       </c>
       <c r="F169" s="7" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="G169" s="9" t="n">
         <v>14000</v>
@@ -12562,13 +12471,13 @@
         <v>YES</v>
       </c>
       <c r="P169" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q169" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R169" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12576,7 +12485,7 @@
         <v>181</v>
       </c>
       <c r="B170" s="7" t="s">
-        <v>368</v>
+        <v>351</v>
       </c>
       <c r="C170" s="6" t="s">
         <v>28</v>
@@ -12588,7 +12497,7 @@
         <v>33800</v>
       </c>
       <c r="F170" s="7" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="G170" s="9" t="n">
         <v>28000</v>
@@ -12625,13 +12534,13 @@
         <v>YES</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q170" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R170" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12639,7 +12548,7 @@
         <v>182</v>
       </c>
       <c r="B171" s="7" t="s">
-        <v>369</v>
+        <v>352</v>
       </c>
       <c r="C171" s="6" t="s">
         <v>28</v>
@@ -12651,7 +12560,7 @@
         <v>23400</v>
       </c>
       <c r="F171" s="7" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="G171" s="9" t="n">
         <v>20000</v>
@@ -12688,13 +12597,13 @@
         <v>YES</v>
       </c>
       <c r="P171" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q171" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R171" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12702,7 +12611,7 @@
         <v>183</v>
       </c>
       <c r="B172" s="7" t="s">
-        <v>370</v>
+        <v>353</v>
       </c>
       <c r="C172" s="6" t="s">
         <v>28</v>
@@ -12714,7 +12623,7 @@
         <v>2860</v>
       </c>
       <c r="F172" s="7" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="G172" s="9" t="n">
         <v>1800</v>
@@ -12751,13 +12660,13 @@
         <v>YES</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q172" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R172" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12765,7 +12674,7 @@
         <v>184</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
       <c r="C173" s="6" t="s">
         <v>28</v>
@@ -12777,7 +12686,7 @@
         <v>3250</v>
       </c>
       <c r="F173" s="7" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="G173" s="9" t="n">
         <v>2100</v>
@@ -12814,13 +12723,13 @@
         <v>YES</v>
       </c>
       <c r="P173" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q173" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R173" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12828,7 +12737,7 @@
         <v>185</v>
       </c>
       <c r="B174" s="7" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
       <c r="C174" s="6" t="s">
         <v>28</v>
@@ -12840,7 +12749,7 @@
         <v>3900</v>
       </c>
       <c r="F174" s="7" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="G174" s="9" t="n">
         <v>2600</v>
@@ -12877,13 +12786,13 @@
         <v>YES</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q174" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R174" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12891,7 +12800,7 @@
         <v>186</v>
       </c>
       <c r="B175" s="7" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="C175" s="6" t="s">
         <v>28</v>
@@ -12903,7 +12812,7 @@
         <v>4550</v>
       </c>
       <c r="F175" s="7" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="G175" s="9" t="n">
         <v>3300</v>
@@ -12940,13 +12849,13 @@
         <v>YES</v>
       </c>
       <c r="P175" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q175" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R175" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12954,7 +12863,7 @@
         <v>187</v>
       </c>
       <c r="B176" s="7" t="s">
-        <v>374</v>
+        <v>357</v>
       </c>
       <c r="C176" s="6" t="s">
         <v>28</v>
@@ -12966,7 +12875,7 @@
         <v>7150</v>
       </c>
       <c r="F176" s="7" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="G176" s="9" t="n">
         <v>5500</v>
@@ -13003,13 +12912,13 @@
         <v>YES</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q176" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R176" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13017,7 +12926,7 @@
         <v>188</v>
       </c>
       <c r="B177" s="7" t="s">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="C177" s="6" t="s">
         <v>28</v>
@@ -13029,7 +12938,7 @@
         <v>8450</v>
       </c>
       <c r="F177" s="7" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="G177" s="9" t="n">
         <v>7000</v>
@@ -13066,13 +12975,13 @@
         <v>YES</v>
       </c>
       <c r="P177" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q177" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R177" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13080,7 +12989,7 @@
         <v>189</v>
       </c>
       <c r="B178" s="7" t="s">
-        <v>376</v>
+        <v>359</v>
       </c>
       <c r="C178" s="6" t="s">
         <v>28</v>
@@ -13092,7 +13001,7 @@
         <v>9750</v>
       </c>
       <c r="F178" s="7" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="G178" s="9" t="n">
         <v>8500</v>
@@ -13129,13 +13038,13 @@
         <v>YES</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q178" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R178" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13143,7 +13052,7 @@
         <v>190</v>
       </c>
       <c r="B179" s="7" t="s">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="C179" s="6" t="s">
         <v>28</v>
@@ -13155,7 +13064,7 @@
         <v>2340</v>
       </c>
       <c r="F179" s="7" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="G179" s="9" t="n">
         <v>1500</v>
@@ -13192,13 +13101,13 @@
         <v>YES</v>
       </c>
       <c r="P179" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q179" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R179" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13206,7 +13115,7 @@
         <v>191</v>
       </c>
       <c r="B180" s="7" t="s">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="C180" s="6" t="s">
         <v>28</v>
@@ -13218,7 +13127,7 @@
         <v>3640</v>
       </c>
       <c r="F180" s="7" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="G180" s="9" t="n">
         <v>2300</v>
@@ -13255,13 +13164,13 @@
         <v>YES</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q180" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R180" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13269,7 +13178,7 @@
         <v>192</v>
       </c>
       <c r="B181" s="7" t="s">
-        <v>378</v>
+        <v>361</v>
       </c>
       <c r="C181" s="6" t="s">
         <v>28</v>
@@ -13318,13 +13227,13 @@
         <v>YES</v>
       </c>
       <c r="P181" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q181" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R181" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13332,7 +13241,7 @@
         <v>193</v>
       </c>
       <c r="B182" s="7" t="s">
-        <v>379</v>
+        <v>362</v>
       </c>
       <c r="C182" s="6" t="s">
         <v>28</v>
@@ -13381,13 +13290,13 @@
         <v>YES</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q182" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R182" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13395,7 +13304,7 @@
         <v>194</v>
       </c>
       <c r="B183" s="7" t="s">
-        <v>380</v>
+        <v>363</v>
       </c>
       <c r="C183" s="6" t="s">
         <v>28</v>
@@ -13444,13 +13353,13 @@
         <v>YES</v>
       </c>
       <c r="P183" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q183" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R183" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13458,7 +13367,7 @@
         <v>195</v>
       </c>
       <c r="B184" s="7" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="C184" s="6" t="s">
         <v>28</v>
@@ -13507,13 +13416,13 @@
         <v>YES</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q184" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R184" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13521,7 +13430,7 @@
         <v>196</v>
       </c>
       <c r="B185" s="7" t="s">
-        <v>382</v>
+        <v>365</v>
       </c>
       <c r="C185" s="6" t="s">
         <v>28</v>
@@ -13533,7 +13442,7 @@
         <v>4550</v>
       </c>
       <c r="F185" s="7" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="G185" s="9" t="n">
         <v>3500</v>
@@ -13570,13 +13479,13 @@
         <v>YES</v>
       </c>
       <c r="P185" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q185" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R185" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13584,7 +13493,7 @@
         <v>197</v>
       </c>
       <c r="B186" s="7" t="s">
-        <v>383</v>
+        <v>366</v>
       </c>
       <c r="C186" s="6" t="s">
         <v>28</v>
@@ -13596,7 +13505,7 @@
         <v>17940</v>
       </c>
       <c r="F186" s="7" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="G186" s="9" t="n">
         <v>5500</v>
@@ -13633,10 +13542,10 @@
         <v>YES</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q186" s="7" t="s">
-        <v>384</v>
+        <v>367</v>
       </c>
       <c r="R186" s="7"/>
     </row>
@@ -13645,7 +13554,7 @@
         <v>198</v>
       </c>
       <c r="B187" s="7" t="s">
-        <v>385</v>
+        <v>368</v>
       </c>
       <c r="C187" s="6" t="s">
         <v>28</v>
@@ -13657,7 +13566,7 @@
         <v>18850</v>
       </c>
       <c r="F187" s="7" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="G187" s="9" t="n">
         <v>5500</v>
@@ -13694,10 +13603,10 @@
         <v>YES</v>
       </c>
       <c r="P187" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q187" s="7" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="R187" s="7"/>
     </row>
@@ -13706,7 +13615,7 @@
         <v>199</v>
       </c>
       <c r="B188" s="7" t="s">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="C188" s="6" t="s">
         <v>28</v>
@@ -13718,7 +13627,7 @@
         <v>19500</v>
       </c>
       <c r="F188" s="7" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="G188" s="9" t="n">
         <v>6200</v>
@@ -13755,10 +13664,10 @@
         <v>YES</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q188" s="7" t="s">
-        <v>388</v>
+        <v>371</v>
       </c>
       <c r="R188" s="7"/>
     </row>
@@ -13767,7 +13676,7 @@
         <v>200</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="C189" s="6" t="s">
         <v>28</v>
@@ -13779,7 +13688,7 @@
         <v>20800</v>
       </c>
       <c r="F189" s="7" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="G189" s="9" t="n">
         <v>6875</v>
@@ -13816,10 +13725,10 @@
         <v>YES</v>
       </c>
       <c r="P189" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q189" s="7" t="s">
-        <v>390</v>
+        <v>373</v>
       </c>
       <c r="R189" s="7"/>
     </row>
@@ -13828,7 +13737,7 @@
         <v>201</v>
       </c>
       <c r="B190" s="7" t="s">
-        <v>391</v>
+        <v>374</v>
       </c>
       <c r="C190" s="6" t="s">
         <v>28</v>
@@ -13840,7 +13749,7 @@
         <v>22750</v>
       </c>
       <c r="F190" s="7" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="G190" s="9" t="n">
         <v>8750</v>
@@ -13877,19 +13786,19 @@
         <v>YES</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q190" s="7" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="R190" s="7"/>
     </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="6" t="n">
         <v>202</v>
       </c>
       <c r="B191" s="7" t="s">
-        <v>393</v>
+        <v>376</v>
       </c>
       <c r="C191" s="6" t="s">
         <v>28</v>
@@ -13901,17 +13810,17 @@
         <v>2340</v>
       </c>
       <c r="F191" s="7" t="s">
-        <v>131</v>
+        <v>43</v>
       </c>
       <c r="G191" s="9" t="n">
-        <v>1500</v>
+        <v>1352</v>
       </c>
       <c r="H191" s="9" t="n">
-        <v>2000</v>
+        <v>1352</v>
       </c>
       <c r="I191" s="10" t="n">
         <f aca="false">IF(E191=0,0,(E191-H191)/E191)</f>
-        <v>0.145299145299145</v>
+        <v>0.422222222222222</v>
       </c>
       <c r="J191" s="6" t="str">
         <f aca="false">IF(E191&lt;G191,"LOSS",IF(E191&lt;H191*1.1,"THIN / RISK",IF(E191&gt;H191*1.8,"OVERPRICED?","OK")))</f>
@@ -13931,7 +13840,7 @@
       </c>
       <c r="N191" s="8" t="n">
         <f aca="false">D191*H191</f>
-        <v>4000</v>
+        <v>2704</v>
       </c>
       <c r="O191" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C191,F191)),"","YES")</f>
@@ -13941,10 +13850,10 @@
         <v>24</v>
       </c>
       <c r="Q191" s="7" t="s">
-        <v>156</v>
+        <v>377</v>
       </c>
       <c r="R191" s="7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13952,7 +13861,7 @@
         <v>204</v>
       </c>
       <c r="B192" s="7" t="s">
-        <v>394</v>
+        <v>378</v>
       </c>
       <c r="C192" s="6" t="s">
         <v>28</v>
@@ -13964,7 +13873,7 @@
         <v>845</v>
       </c>
       <c r="F192" s="7" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="G192" s="9" t="n">
         <v>5480</v>
@@ -14001,13 +13910,13 @@
         <v>YES</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q192" s="7" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="R192" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14015,7 +13924,7 @@
         <v>205</v>
       </c>
       <c r="B193" s="7" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="C193" s="6" t="s">
         <v>28</v>
@@ -14027,7 +13936,7 @@
         <v>910</v>
       </c>
       <c r="F193" s="7" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="G193" s="9" t="n">
         <v>5960</v>
@@ -14064,13 +13973,13 @@
         <v>YES</v>
       </c>
       <c r="P193" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q193" s="7" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="R193" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14078,7 +13987,7 @@
         <v>206</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="C194" s="6" t="s">
         <v>28</v>
@@ -14090,7 +13999,7 @@
         <v>1170</v>
       </c>
       <c r="F194" s="7" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="G194" s="9" t="n">
         <v>6930</v>
@@ -14127,13 +14036,13 @@
         <v>YES</v>
       </c>
       <c r="P194" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q194" s="7" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="R194" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14141,7 +14050,7 @@
         <v>207</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>399</v>
+        <v>383</v>
       </c>
       <c r="C195" s="6" t="s">
         <v>28</v>
@@ -14153,7 +14062,7 @@
         <v>1430</v>
       </c>
       <c r="F195" s="7" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="G195" s="9" t="n">
         <v>8960</v>
@@ -14190,13 +14099,13 @@
         <v>YES</v>
       </c>
       <c r="P195" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q195" s="7" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="R195" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14204,7 +14113,7 @@
         <v>208</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>400</v>
+        <v>384</v>
       </c>
       <c r="C196" s="6" t="s">
         <v>28</v>
@@ -14216,17 +14125,17 @@
         <v>1690</v>
       </c>
       <c r="F196" s="7" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="G196" s="9" t="n">
-        <v>11050</v>
+        <v>2900</v>
       </c>
       <c r="H196" s="9" t="n">
-        <v>14360</v>
+        <v>2900</v>
       </c>
       <c r="I196" s="10" t="n">
         <f aca="false">IF(E196=0,0,(E196-H196)/E196)</f>
-        <v>-7.49704142011834</v>
+        <v>-0.715976331360947</v>
       </c>
       <c r="J196" s="6" t="str">
         <f aca="false">IF(E196&lt;G196,"LOSS",IF(E196&lt;H196*1.1,"THIN / RISK",IF(E196&gt;H196*1.8,"OVERPRICED?","OK")))</f>
@@ -14234,7 +14143,7 @@
       </c>
       <c r="K196" s="8" t="n">
         <f aca="false">IF(J196="OVERPRICED?",ROUND(H196*1.35,-1),MAX(E196,ROUND(H196*(1+$E$3),-1)))</f>
-        <v>16510</v>
+        <v>3340</v>
       </c>
       <c r="L196" s="8" t="n">
         <f aca="false">D196*E196</f>
@@ -14242,32 +14151,30 @@
       </c>
       <c r="M196" s="8" t="n">
         <f aca="false">D196*K196</f>
-        <v>49530</v>
+        <v>10020</v>
       </c>
       <c r="N196" s="8" t="n">
         <f aca="false">D196*H196</f>
-        <v>43080</v>
+        <v>8700</v>
       </c>
       <c r="O196" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C196,F196)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="Q196" s="7" t="s">
-        <v>396</v>
-      </c>
-      <c r="R196" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="R196" s="7"/>
     </row>
     <row r="197" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="6" t="n">
         <v>209</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>401</v>
+        <v>387</v>
       </c>
       <c r="C197" s="6" t="s">
         <v>28</v>
@@ -14279,7 +14186,7 @@
         <v>2340</v>
       </c>
       <c r="F197" s="7" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="G197" s="9" t="n">
         <v>15380</v>
@@ -14316,13 +14223,13 @@
         <v>YES</v>
       </c>
       <c r="P197" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q197" s="7" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="R197" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14330,7 +14237,7 @@
         <v>210</v>
       </c>
       <c r="B198" s="7" t="s">
-        <v>402</v>
+        <v>388</v>
       </c>
       <c r="C198" s="6" t="s">
         <v>28</v>
@@ -14342,7 +14249,7 @@
         <v>2860</v>
       </c>
       <c r="F198" s="7" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="G198" s="9" t="n">
         <v>17610</v>
@@ -14379,13 +14286,13 @@
         <v>YES</v>
       </c>
       <c r="P198" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q198" s="7" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="R198" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14393,7 +14300,7 @@
         <v>211</v>
       </c>
       <c r="B199" s="7" t="s">
-        <v>403</v>
+        <v>389</v>
       </c>
       <c r="C199" s="6" t="s">
         <v>28</v>
@@ -14405,7 +14312,7 @@
         <v>4160</v>
       </c>
       <c r="F199" s="7" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="G199" s="9" t="n">
         <v>22180</v>
@@ -14442,13 +14349,13 @@
         <v>YES</v>
       </c>
       <c r="P199" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q199" s="7" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="R199" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14456,7 +14363,7 @@
         <v>212</v>
       </c>
       <c r="B200" s="7" t="s">
-        <v>404</v>
+        <v>390</v>
       </c>
       <c r="C200" s="6" t="s">
         <v>28</v>
@@ -14468,7 +14375,7 @@
         <v>5460</v>
       </c>
       <c r="F200" s="7" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="G200" s="9" t="n">
         <v>25690</v>
@@ -14505,13 +14412,13 @@
         <v>YES</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q200" s="7" t="s">
-        <v>396</v>
+        <v>380</v>
       </c>
       <c r="R200" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14519,7 +14426,7 @@
         <v>213</v>
       </c>
       <c r="B201" s="7" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="C201" s="6" t="s">
         <v>28</v>
@@ -14531,7 +14438,7 @@
         <v>455</v>
       </c>
       <c r="F201" s="7" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="G201" s="9" t="n">
         <v>500</v>
@@ -14568,13 +14475,13 @@
         <v>YES</v>
       </c>
       <c r="P201" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q201" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R201" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14582,7 +14489,7 @@
         <v>214</v>
       </c>
       <c r="B202" s="7" t="s">
-        <v>406</v>
+        <v>392</v>
       </c>
       <c r="C202" s="6" t="s">
         <v>28</v>
@@ -14594,7 +14501,7 @@
         <v>494</v>
       </c>
       <c r="F202" s="7" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="G202" s="9" t="n">
         <v>550</v>
@@ -14631,13 +14538,13 @@
         <v>YES</v>
       </c>
       <c r="P202" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q202" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R202" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14645,7 +14552,7 @@
         <v>215</v>
       </c>
       <c r="B203" s="7" t="s">
-        <v>407</v>
+        <v>393</v>
       </c>
       <c r="C203" s="6" t="s">
         <v>28</v>
@@ -14657,7 +14564,7 @@
         <v>585</v>
       </c>
       <c r="F203" s="7" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="G203" s="9" t="n">
         <v>650</v>
@@ -14694,13 +14601,13 @@
         <v>YES</v>
       </c>
       <c r="P203" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q203" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R203" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14708,7 +14615,7 @@
         <v>216</v>
       </c>
       <c r="B204" s="7" t="s">
-        <v>408</v>
+        <v>394</v>
       </c>
       <c r="C204" s="6" t="s">
         <v>28</v>
@@ -14720,7 +14627,7 @@
         <v>715</v>
       </c>
       <c r="F204" s="7" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="G204" s="9" t="n">
         <v>800</v>
@@ -14757,13 +14664,13 @@
         <v>YES</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q204" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R204" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14771,7 +14678,7 @@
         <v>217</v>
       </c>
       <c r="B205" s="7" t="s">
-        <v>409</v>
+        <v>395</v>
       </c>
       <c r="C205" s="6" t="s">
         <v>28</v>
@@ -14783,7 +14690,7 @@
         <v>910</v>
       </c>
       <c r="F205" s="7" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="G205" s="9" t="n">
         <v>1000</v>
@@ -14820,13 +14727,13 @@
         <v>YES</v>
       </c>
       <c r="P205" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q205" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R205" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14834,7 +14741,7 @@
         <v>218</v>
       </c>
       <c r="B206" s="7" t="s">
-        <v>410</v>
+        <v>396</v>
       </c>
       <c r="C206" s="6" t="s">
         <v>28</v>
@@ -14846,7 +14753,7 @@
         <v>1170</v>
       </c>
       <c r="F206" s="7" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="G206" s="9" t="n">
         <v>1400</v>
@@ -14883,13 +14790,13 @@
         <v>YES</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q206" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R206" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14897,7 +14804,7 @@
         <v>219</v>
       </c>
       <c r="B207" s="7" t="s">
-        <v>411</v>
+        <v>397</v>
       </c>
       <c r="C207" s="6" t="s">
         <v>28</v>
@@ -14909,7 +14816,7 @@
         <v>1040</v>
       </c>
       <c r="F207" s="7" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="G207" s="9" t="n">
         <v>1100</v>
@@ -14946,13 +14853,13 @@
         <v>YES</v>
       </c>
       <c r="P207" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q207" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R207" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14960,7 +14867,7 @@
         <v>220</v>
       </c>
       <c r="B208" s="7" t="s">
-        <v>412</v>
+        <v>398</v>
       </c>
       <c r="C208" s="6" t="s">
         <v>28</v>
@@ -14972,7 +14879,7 @@
         <v>1430</v>
       </c>
       <c r="F208" s="7" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="G208" s="9" t="n">
         <v>1400</v>
@@ -15009,13 +14916,13 @@
         <v>YES</v>
       </c>
       <c r="P208" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q208" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R208" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15023,7 +14930,7 @@
         <v>221</v>
       </c>
       <c r="B209" s="7" t="s">
-        <v>413</v>
+        <v>399</v>
       </c>
       <c r="C209" s="6" t="s">
         <v>28</v>
@@ -15035,7 +14942,7 @@
         <v>1950</v>
       </c>
       <c r="F209" s="7" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="G209" s="9" t="n">
         <v>2000</v>
@@ -15072,13 +14979,13 @@
         <v>YES</v>
       </c>
       <c r="P209" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q209" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R209" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15086,7 +14993,7 @@
         <v>222</v>
       </c>
       <c r="B210" s="7" t="s">
-        <v>414</v>
+        <v>400</v>
       </c>
       <c r="C210" s="6" t="s">
         <v>28</v>
@@ -15098,7 +15005,7 @@
         <v>15600</v>
       </c>
       <c r="F210" s="7" t="s">
-        <v>415</v>
+        <v>401</v>
       </c>
       <c r="G210" s="9" t="n">
         <v>18000</v>
@@ -15135,21 +15042,21 @@
         <v>YES</v>
       </c>
       <c r="P210" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q210" s="7" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="R210" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="211" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="6" t="n">
         <v>223</v>
       </c>
       <c r="B211" s="7" t="s">
-        <v>416</v>
+        <v>402</v>
       </c>
       <c r="C211" s="6" t="s">
         <v>28</v>
@@ -15161,17 +15068,17 @@
         <v>30940</v>
       </c>
       <c r="F211" s="7" t="s">
-        <v>417</v>
+        <v>157</v>
       </c>
       <c r="G211" s="9" t="n">
-        <v>45000</v>
+        <v>31300</v>
       </c>
       <c r="H211" s="9" t="n">
-        <v>60000</v>
+        <v>31300</v>
       </c>
       <c r="I211" s="10" t="n">
         <f aca="false">IF(E211=0,0,(E211-H211)/E211)</f>
-        <v>-0.93923723335488</v>
+        <v>-0.0116354234001293</v>
       </c>
       <c r="J211" s="6" t="str">
         <f aca="false">IF(E211&lt;G211,"LOSS",IF(E211&lt;H211*1.1,"THIN / RISK",IF(E211&gt;H211*1.8,"OVERPRICED?","OK")))</f>
@@ -15179,7 +15086,7 @@
       </c>
       <c r="K211" s="8" t="n">
         <f aca="false">IF(J211="OVERPRICED?",ROUND(H211*1.35,-1),MAX(E211,ROUND(H211*(1+$E$3),-1)))</f>
-        <v>69000</v>
+        <v>36000</v>
       </c>
       <c r="L211" s="8" t="n">
         <f aca="false">D211*E211</f>
@@ -15187,32 +15094,30 @@
       </c>
       <c r="M211" s="8" t="n">
         <f aca="false">D211*K211</f>
-        <v>138000</v>
+        <v>72000</v>
       </c>
       <c r="N211" s="8" t="n">
         <f aca="false">D211*H211</f>
-        <v>120000</v>
+        <v>62600</v>
       </c>
       <c r="O211" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C211,F211)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P211" s="6" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="Q211" s="7" t="s">
-        <v>418</v>
-      </c>
-      <c r="R211" s="7" t="s">
-        <v>419</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="R211" s="7"/>
     </row>
     <row r="212" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="6" t="n">
         <v>224</v>
       </c>
       <c r="B212" s="7" t="s">
-        <v>420</v>
+        <v>404</v>
       </c>
       <c r="C212" s="6" t="s">
         <v>28</v>
@@ -15224,7 +15129,7 @@
         <v>54600</v>
       </c>
       <c r="F212" s="7" t="s">
-        <v>421</v>
+        <v>405</v>
       </c>
       <c r="G212" s="9" t="n">
         <v>85000</v>
@@ -15261,13 +15166,13 @@
         <v>YES</v>
       </c>
       <c r="P212" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q212" s="7" t="s">
-        <v>422</v>
+        <v>406</v>
       </c>
       <c r="R212" s="7" t="s">
-        <v>423</v>
+        <v>407</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15275,7 +15180,7 @@
         <v>225</v>
       </c>
       <c r="B213" s="7" t="s">
-        <v>424</v>
+        <v>408</v>
       </c>
       <c r="C213" s="6" t="s">
         <v>28</v>
@@ -15287,7 +15192,7 @@
         <v>1170</v>
       </c>
       <c r="F213" s="7" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="G213" s="9" t="n">
         <v>1800</v>
@@ -15324,13 +15229,13 @@
         <v>YES</v>
       </c>
       <c r="P213" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q213" s="7" t="s">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="R213" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15338,7 +15243,7 @@
         <v>226</v>
       </c>
       <c r="B214" s="7" t="s">
-        <v>426</v>
+        <v>410</v>
       </c>
       <c r="C214" s="6" t="s">
         <v>28</v>
@@ -15350,7 +15255,7 @@
         <v>1430</v>
       </c>
       <c r="F214" s="7" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="G214" s="9" t="n">
         <v>2600</v>
@@ -15387,13 +15292,13 @@
         <v>YES</v>
       </c>
       <c r="P214" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q214" s="7" t="s">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="R214" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15401,7 +15306,7 @@
         <v>227</v>
       </c>
       <c r="B215" s="7" t="s">
-        <v>427</v>
+        <v>411</v>
       </c>
       <c r="C215" s="6" t="s">
         <v>28</v>
@@ -15413,7 +15318,7 @@
         <v>1820</v>
       </c>
       <c r="F215" s="7" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="G215" s="9" t="n">
         <v>3500</v>
@@ -15450,13 +15355,13 @@
         <v>YES</v>
       </c>
       <c r="P215" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q215" s="7" t="s">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="R215" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15464,7 +15369,7 @@
         <v>228</v>
       </c>
       <c r="B216" s="7" t="s">
-        <v>428</v>
+        <v>412</v>
       </c>
       <c r="C216" s="6" t="s">
         <v>28</v>
@@ -15476,7 +15381,7 @@
         <v>2860</v>
       </c>
       <c r="F216" s="7" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="G216" s="9" t="n">
         <v>6000</v>
@@ -15513,13 +15418,13 @@
         <v>YES</v>
       </c>
       <c r="P216" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q216" s="7" t="s">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="R216" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15527,7 +15432,7 @@
         <v>229</v>
       </c>
       <c r="B217" s="7" t="s">
-        <v>429</v>
+        <v>413</v>
       </c>
       <c r="C217" s="6" t="s">
         <v>28</v>
@@ -15539,7 +15444,7 @@
         <v>2340</v>
       </c>
       <c r="F217" s="7" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="G217" s="9" t="n">
         <v>3200</v>
@@ -15576,21 +15481,21 @@
         <v>YES</v>
       </c>
       <c r="P217" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q217" s="7" t="s">
-        <v>425</v>
+        <v>409</v>
       </c>
       <c r="R217" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="218" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="6" t="n">
         <v>230</v>
       </c>
       <c r="B218" s="7" t="s">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="C218" s="6" t="s">
         <v>28</v>
@@ -15602,17 +15507,17 @@
         <v>9750</v>
       </c>
       <c r="F218" s="7" t="s">
-        <v>431</v>
+        <v>415</v>
       </c>
       <c r="G218" s="9" t="n">
-        <v>5300</v>
+        <v>5950</v>
       </c>
       <c r="H218" s="9" t="n">
-        <v>6000</v>
+        <v>5950</v>
       </c>
       <c r="I218" s="10" t="n">
         <f aca="false">IF(E218=0,0,(E218-H218)/E218)</f>
-        <v>0.384615384615385</v>
+        <v>0.38974358974359</v>
       </c>
       <c r="J218" s="6" t="str">
         <f aca="false">IF(E218&lt;G218,"LOSS",IF(E218&lt;H218*1.1,"THIN / RISK",IF(E218&gt;H218*1.8,"OVERPRICED?","OK")))</f>
@@ -15632,7 +15537,7 @@
       </c>
       <c r="N218" s="8" t="n">
         <f aca="false">D218*H218</f>
-        <v>6000</v>
+        <v>5950</v>
       </c>
       <c r="O218" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C218,F218)),"","YES")</f>
@@ -15642,18 +15547,18 @@
         <v>24</v>
       </c>
       <c r="Q218" s="7" t="s">
-        <v>432</v>
+        <v>416</v>
       </c>
       <c r="R218" s="7" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="219" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="6" t="n">
         <v>231</v>
       </c>
       <c r="B219" s="7" t="s">
-        <v>434</v>
+        <v>417</v>
       </c>
       <c r="C219" s="6" t="s">
         <v>28</v>
@@ -15665,25 +15570,25 @@
         <v>12350</v>
       </c>
       <c r="F219" s="7" t="s">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="G219" s="9" t="n">
-        <v>6500</v>
+        <v>5950</v>
       </c>
       <c r="H219" s="9" t="n">
-        <v>7500</v>
+        <v>5950</v>
       </c>
       <c r="I219" s="10" t="n">
         <f aca="false">IF(E219=0,0,(E219-H219)/E219)</f>
-        <v>0.392712550607287</v>
+        <v>0.518218623481781</v>
       </c>
       <c r="J219" s="6" t="str">
         <f aca="false">IF(E219&lt;G219,"LOSS",IF(E219&lt;H219*1.1,"THIN / RISK",IF(E219&gt;H219*1.8,"OVERPRICED?","OK")))</f>
-        <v>OK</v>
+        <v>OVERPRICED?</v>
       </c>
       <c r="K219" s="8" t="n">
         <f aca="false">IF(J219="OVERPRICED?",ROUND(H219*1.35,-1),MAX(E219,ROUND(H219*(1+$E$3),-1)))</f>
-        <v>12350</v>
+        <v>8030</v>
       </c>
       <c r="L219" s="8" t="n">
         <f aca="false">D219*E219</f>
@@ -15691,35 +15596,33 @@
       </c>
       <c r="M219" s="8" t="n">
         <f aca="false">D219*K219</f>
-        <v>12350</v>
+        <v>8030</v>
       </c>
       <c r="N219" s="8" t="n">
         <f aca="false">D219*H219</f>
-        <v>7500</v>
+        <v>5950</v>
       </c>
       <c r="O219" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C219,F219)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P219" s="6" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="Q219" s="7" t="s">
-        <v>436</v>
-      </c>
-      <c r="R219" s="7" t="s">
-        <v>433</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="R219" s="7"/>
     </row>
     <row r="220" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="6" t="n">
         <v>233</v>
       </c>
       <c r="B220" s="7" t="s">
-        <v>437</v>
+        <v>419</v>
       </c>
       <c r="C220" s="6" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="D220" s="6" t="n">
         <v>2</v>
@@ -15728,7 +15631,7 @@
         <v>52000</v>
       </c>
       <c r="F220" s="7" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="G220" s="9" t="n">
         <v>40000</v>
@@ -15765,10 +15668,10 @@
         <v/>
       </c>
       <c r="P220" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q220" s="7" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="R220" s="7"/>
     </row>
@@ -15777,7 +15680,7 @@
         <v>234</v>
       </c>
       <c r="B221" s="7" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="C221" s="6" t="s">
         <v>22</v>
@@ -15789,7 +15692,7 @@
         <v>3094</v>
       </c>
       <c r="F221" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G221" s="9" t="n">
         <v>1740</v>
@@ -15826,13 +15729,13 @@
         <v>YES</v>
       </c>
       <c r="P221" s="6" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="Q221" s="7" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="R221" s="7" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15840,7 +15743,7 @@
         <v>235</v>
       </c>
       <c r="B222" s="7" t="s">
-        <v>441</v>
+        <v>423</v>
       </c>
       <c r="C222" s="6" t="s">
         <v>28</v>
@@ -15855,22 +15758,22 @@
         <v>22</v>
       </c>
       <c r="G222" s="9" t="n">
-        <v>1500</v>
+        <v>500</v>
       </c>
       <c r="H222" s="9" t="n">
-        <v>2300</v>
+        <v>500</v>
       </c>
       <c r="I222" s="10" t="n">
         <f aca="false">IF(E222=0,0,(E222-H222)/E222)</f>
-        <v>0.195804195804196</v>
+        <v>0.825174825174825</v>
       </c>
       <c r="J222" s="6" t="str">
         <f aca="false">IF(E222&lt;G222,"LOSS",IF(E222&lt;H222*1.1,"THIN / RISK",IF(E222&gt;H222*1.8,"OVERPRICED?","OK")))</f>
-        <v>OK</v>
+        <v>OVERPRICED?</v>
       </c>
       <c r="K222" s="8" t="n">
         <f aca="false">IF(J222="OVERPRICED?",ROUND(H222*1.35,-1),MAX(E222,ROUND(H222*(1+$E$3),-1)))</f>
-        <v>2860</v>
+        <v>680</v>
       </c>
       <c r="L222" s="8" t="n">
         <f aca="false">D222*E222</f>
@@ -15878,11 +15781,11 @@
       </c>
       <c r="M222" s="8" t="n">
         <f aca="false">D222*K222</f>
-        <v>8580</v>
+        <v>2040</v>
       </c>
       <c r="N222" s="8" t="n">
         <f aca="false">D222*H222</f>
-        <v>6900</v>
+        <v>1500</v>
       </c>
       <c r="O222" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C222,F222)),"","YES")</f>
@@ -15892,10 +15795,10 @@
         <v>24</v>
       </c>
       <c r="Q222" s="7" t="s">
-        <v>156</v>
+        <v>424</v>
       </c>
       <c r="R222" s="7" t="s">
-        <v>442</v>
+        <v>26</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15903,7 +15806,7 @@
         <v>236</v>
       </c>
       <c r="B223" s="7" t="s">
-        <v>443</v>
+        <v>425</v>
       </c>
       <c r="C223" s="6" t="s">
         <v>22</v>
@@ -15915,7 +15818,7 @@
         <v>2860</v>
       </c>
       <c r="F223" s="7" t="s">
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="G223" s="9" t="n">
         <v>2400</v>
@@ -15952,21 +15855,21 @@
         <v/>
       </c>
       <c r="P223" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q223" s="7" t="s">
-        <v>445</v>
+        <v>427</v>
       </c>
       <c r="R223" s="7" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="6" t="n">
         <v>237</v>
       </c>
       <c r="B224" s="7" t="s">
-        <v>447</v>
+        <v>429</v>
       </c>
       <c r="C224" s="6" t="s">
         <v>28</v>
@@ -15981,22 +15884,22 @@
         <v>22</v>
       </c>
       <c r="G224" s="9" t="n">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="H224" s="9" t="n">
-        <v>700</v>
+        <v>150</v>
       </c>
       <c r="I224" s="10" t="n">
         <f aca="false">IF(E224=0,0,(E224-H224)/E224)</f>
-        <v>0.171597633136095</v>
+        <v>0.822485207100592</v>
       </c>
       <c r="J224" s="6" t="str">
         <f aca="false">IF(E224&lt;G224,"LOSS",IF(E224&lt;H224*1.1,"THIN / RISK",IF(E224&gt;H224*1.8,"OVERPRICED?","OK")))</f>
-        <v>OK</v>
+        <v>OVERPRICED?</v>
       </c>
       <c r="K224" s="8" t="n">
         <f aca="false">IF(J224="OVERPRICED?",ROUND(H224*1.35,-1),MAX(E224,ROUND(H224*(1+$E$3),-1)))</f>
-        <v>845</v>
+        <v>200</v>
       </c>
       <c r="L224" s="8" t="n">
         <f aca="false">D224*E224</f>
@@ -16004,11 +15907,11 @@
       </c>
       <c r="M224" s="8" t="n">
         <f aca="false">D224*K224</f>
-        <v>20280</v>
+        <v>4800</v>
       </c>
       <c r="N224" s="8" t="n">
         <f aca="false">D224*H224</f>
-        <v>16800</v>
+        <v>3600</v>
       </c>
       <c r="O224" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C224,F224)),"","YES")</f>
@@ -16018,10 +15921,10 @@
         <v>24</v>
       </c>
       <c r="Q224" s="7" t="s">
-        <v>156</v>
+        <v>430</v>
       </c>
       <c r="R224" s="7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16029,7 +15932,7 @@
         <v>238</v>
       </c>
       <c r="B225" s="7" t="s">
-        <v>448</v>
+        <v>431</v>
       </c>
       <c r="C225" s="6" t="s">
         <v>28</v>
@@ -16041,7 +15944,7 @@
         <v>8450</v>
       </c>
       <c r="F225" s="7" t="s">
-        <v>449</v>
+        <v>432</v>
       </c>
       <c r="G225" s="9" t="n">
         <v>7800</v>
@@ -16078,10 +15981,10 @@
         <v>YES</v>
       </c>
       <c r="P225" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q225" s="7" t="s">
-        <v>450</v>
+        <v>433</v>
       </c>
       <c r="R225" s="7"/>
     </row>
@@ -16090,10 +15993,10 @@
         <v>239</v>
       </c>
       <c r="B226" s="7" t="s">
-        <v>451</v>
+        <v>434</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="D226" s="6" t="n">
         <v>50</v>
@@ -16102,7 +16005,7 @@
         <v>65000</v>
       </c>
       <c r="F226" s="7" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="G226" s="9" t="n">
         <v>44000</v>
@@ -16139,10 +16042,10 @@
         <v/>
       </c>
       <c r="P226" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q226" s="7" t="s">
-        <v>452</v>
+        <v>435</v>
       </c>
       <c r="R226" s="7"/>
     </row>
@@ -16151,7 +16054,7 @@
         <v>240</v>
       </c>
       <c r="B227" s="7" t="s">
-        <v>453</v>
+        <v>436</v>
       </c>
       <c r="C227" s="6" t="s">
         <v>28</v>
@@ -16163,7 +16066,7 @@
         <v>325</v>
       </c>
       <c r="F227" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G227" s="9" t="n">
         <v>900</v>
@@ -16200,18 +16103,18 @@
         <v>YES</v>
       </c>
       <c r="P227" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Q227" s="7" t="s">
-        <v>454</v>
+        <v>437</v>
       </c>
       <c r="R227" s="7" t="s">
-        <v>455</v>
+        <v>438</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B228" s="3" t="s">
-        <v>456</v>
+        <v>439</v>
       </c>
       <c r="L228" s="11" t="n">
         <f aca="false">SUM(L6:L227)</f>
@@ -16219,11 +16122,11 @@
       </c>
       <c r="M228" s="11" t="n">
         <f aca="false">SUM(M6:M227)</f>
-        <v>15503200</v>
+        <v>14711711</v>
       </c>
       <c r="N228" s="11" t="n">
         <f aca="false">SUM(N6:N227)</f>
-        <v>12507977</v>
+        <v>11738936</v>
       </c>
     </row>
   </sheetData>
@@ -16272,12 +16175,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>457</v>
+        <v>440</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>458</v>
+        <v>441</v>
       </c>
       <c r="B3" s="11" t="n">
         <f aca="false">COUNTA('Rate Check'!A6:A227)</f>
@@ -16286,47 +16189,47 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>459</v>
+        <v>442</v>
       </c>
       <c r="B4" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"LOSS")</f>
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="B5" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"THIN / RISK")</f>
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>461</v>
+        <v>444</v>
       </c>
       <c r="B6" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"OK")</f>
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>462</v>
+        <v>445</v>
       </c>
       <c r="B7" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"OVERPRICED?")</f>
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>463</v>
+        <v>446</v>
       </c>
       <c r="B8" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!O6:O227,"YES")</f>
-        <v>138</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16334,7 +16237,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>464</v>
+        <v>447</v>
       </c>
       <c r="B10" s="11" t="n">
         <f aca="false">'Rate Check'!L228</f>
@@ -16343,38 +16246,38 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>465</v>
+        <v>448</v>
       </c>
       <c r="B11" s="11" t="n">
         <f aca="false">'Rate Check'!N228</f>
-        <v>12507977</v>
+        <v>11738936</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>466</v>
+        <v>449</v>
       </c>
       <c r="B12" s="11" t="n">
         <f aca="false">B10-B11</f>
-        <v>-298469</v>
+        <v>470572</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="B13" s="14" t="n">
         <f aca="false">IF(B10=0,0,B12/B10)</f>
-        <v>-0.0244456205770126</v>
+        <v>0.0385414383609888</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>468</v>
+        <v>451</v>
       </c>
       <c r="B14" s="11" t="n">
         <f aca="false">SUMPRODUCT(('Rate Check'!E6:E227&lt;'Rate Check'!H6:H227)*('Rate Check'!H6:H227-'Rate Check'!E6:E227)*'Rate Check'!D6:D227)</f>
-        <v>2771050</v>
+        <v>2412436</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16382,20 +16285,20 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>469</v>
+        <v>452</v>
       </c>
       <c r="B16" s="11" t="n">
         <f aca="false">'Rate Check'!M228</f>
-        <v>15503200</v>
+        <v>14711711</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>470</v>
+        <v>453</v>
       </c>
       <c r="B17" s="14" t="n">
         <f aca="false">IF(B16=0,0,(B16-B11)/B16)</f>
-        <v>0.193200307033387</v>
+        <v>0.202068610510361</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16403,29 +16306,29 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>471</v>
+        <v>454</v>
       </c>
       <c r="B19" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!P6:P227,"V")</f>
-        <v>51</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>472</v>
+        <v>455</v>
       </c>
       <c r="B20" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!P6:P227,"S")</f>
-        <v>7</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>473</v>
+        <v>456</v>
       </c>
       <c r="B21" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!P6:P227,"N")</f>
-        <v>164</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -16453,247 +16356,247 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>474</v>
+        <v>457</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>475</v>
+        <v>458</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>476</v>
+        <v>459</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>477</v>
+        <v>460</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>478</v>
+        <v>461</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>479</v>
+        <v>462</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>480</v>
+        <v>463</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>481</v>
+        <v>464</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>482</v>
+        <v>465</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>483</v>
+        <v>466</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>484</v>
+        <v>467</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>485</v>
+        <v>468</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>486</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>487</v>
+        <v>470</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>488</v>
+        <v>471</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>489</v>
+        <v>472</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>490</v>
+        <v>473</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>491</v>
+        <v>474</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>492</v>
+        <v>475</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>493</v>
+        <v>476</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>494</v>
+        <v>477</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>495</v>
+        <v>478</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>496</v>
+        <v>479</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>497</v>
+        <v>480</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>498</v>
+        <v>481</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>499</v>
+        <v>482</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>500</v>
+        <v>483</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>501</v>
+        <v>484</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>502</v>
+        <v>485</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>506</v>
+        <v>489</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>507</v>
+        <v>490</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>508</v>
+        <v>491</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>509</v>
+        <v>492</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>510</v>
+        <v>493</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>511</v>
+        <v>494</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>512</v>
+        <v>495</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>513</v>
+        <v>496</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>514</v>
+        <v>497</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>515</v>
+        <v>498</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>516</v>
+        <v>499</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>517</v>
+        <v>500</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>518</v>
+        <v>501</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>519</v>
+        <v>502</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>520</v>
+        <v>503</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>521</v>
+        <v>504</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>522</v>
+        <v>505</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>523</v>
+        <v>506</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>524</v>
+        <v>507</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>525</v>
+        <v>508</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>526</v>
+        <v>509</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>527</v>
+        <v>510</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>528</v>
+        <v>511</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>529</v>
+        <v>512</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>530</v>
+        <v>513</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>531</v>
+        <v>514</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>532</v>
+        <v>515</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>533</v>
+        <v>516</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>534</v>
+        <v>517</v>
       </c>
     </row>
   </sheetData>

--- a/quotes/PR-217-228/Quote_PR217_PR228_Rate_Check.xlsx
+++ b/quotes/PR-217-228/Quote_PR217_PR228_Rate_Check.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1357" uniqueCount="520">
   <si>
     <t xml:space="preserve">Zidane Corporation - Quote PR-217 &amp; PR-228: Brand + Buying Rate Check</t>
   </si>
@@ -1005,10 +1005,16 @@
     <t xml:space="preserve">TOILET CLEANING BRUSH</t>
   </si>
   <si>
+    <t xml:space="preserve">Local</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alclean.pk round toilet brush Rs 203; mjstraders 8142 toilet brush Rs 203</t>
+  </si>
+  <si>
     <t xml:space="preserve">CUT PIECES OF CLOTHS FOR CLEANING</t>
   </si>
   <si>
-    <t xml:space="preserve">Market (per kg)</t>
+    <t xml:space="preserve">nasirnsons.com cotton waste per kg Rs 160 (cleaning cloth/rags)</t>
   </si>
   <si>
     <t xml:space="preserve">ANCHOR BOLT 10X110</t>
@@ -1056,16 +1062,16 @@
     <t xml:space="preserve">SS WELDING RODS 309L-16 2.6MM NO.12</t>
   </si>
   <si>
-    <t xml:space="preserve">Market (pack)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. SS 309L</t>
+    <t xml:space="preserve">Stainarc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">priceinfo.pk Stainarc stainless rod 4.0mm 1kg packet Rs 4,200-4,400 (309L 2.6mm exact nahi)</t>
   </si>
   <si>
     <t xml:space="preserve">SS WELDING RODS 316L-16 2.6MM NO.12</t>
   </si>
   <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. SS 316L</t>
+    <t xml:space="preserve">priceinfo.pk Stainarc stainless rod 4.0mm 1kg packet Rs 4,200-4,400 (316L 2.6mm exact nahi)</t>
   </si>
   <si>
     <t xml:space="preserve">BLIND RIVETS 04MMX25MM (1000PCS)</t>
@@ -11661,7 +11667,7 @@
       </c>
       <c r="R156" s="7"/>
     </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="6" t="n">
         <v>158</v>
       </c>
@@ -11678,17 +11684,17 @@
         <v>311</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>297</v>
+        <v>326</v>
       </c>
       <c r="G157" s="9" t="n">
-        <v>150</v>
+        <v>203</v>
       </c>
       <c r="H157" s="9" t="n">
-        <v>250</v>
+        <v>203</v>
       </c>
       <c r="I157" s="10" t="n">
         <f aca="false">IF(E157=0,0,(E157-H157)/E157)</f>
-        <v>0.196141479099678</v>
+        <v>0.347266881028939</v>
       </c>
       <c r="J157" s="6" t="str">
         <f aca="false">IF(E157&lt;G157,"LOSS",IF(E157&lt;H157*1.1,"THIN / RISK",IF(E157&gt;H157*1.8,"OVERPRICED?","OK")))</f>
@@ -11708,28 +11714,26 @@
       </c>
       <c r="N157" s="8" t="n">
         <f aca="false">D157*H157</f>
-        <v>3000</v>
+        <v>2436</v>
       </c>
       <c r="O157" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C157,F157)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P157" s="6" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="Q157" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="R157" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>327</v>
+      </c>
+      <c r="R157" s="7"/>
+    </row>
+    <row r="158" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="6" t="n">
         <v>159</v>
       </c>
       <c r="B158" s="7" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C158" s="6" t="s">
         <v>28</v>
@@ -11741,25 +11745,25 @@
         <v>325</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>297</v>
+        <v>326</v>
       </c>
       <c r="G158" s="9" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="H158" s="9" t="n">
-        <v>280</v>
+        <v>160</v>
       </c>
       <c r="I158" s="10" t="n">
         <f aca="false">IF(E158=0,0,(E158-H158)/E158)</f>
-        <v>0.138461538461538</v>
+        <v>0.507692307692308</v>
       </c>
       <c r="J158" s="6" t="str">
         <f aca="false">IF(E158&lt;G158,"LOSS",IF(E158&lt;H158*1.1,"THIN / RISK",IF(E158&gt;H158*1.8,"OVERPRICED?","OK")))</f>
-        <v>OK</v>
+        <v>OVERPRICED?</v>
       </c>
       <c r="K158" s="8" t="n">
         <f aca="false">IF(J158="OVERPRICED?",ROUND(H158*1.35,-1),MAX(E158,ROUND(H158*(1+$E$3),-1)))</f>
-        <v>325</v>
+        <v>220</v>
       </c>
       <c r="L158" s="8" t="n">
         <f aca="false">D158*E158</f>
@@ -11767,24 +11771,24 @@
       </c>
       <c r="M158" s="8" t="n">
         <f aca="false">D158*K158</f>
-        <v>32500</v>
+        <v>22000</v>
       </c>
       <c r="N158" s="8" t="n">
         <f aca="false">D158*H158</f>
-        <v>28000</v>
+        <v>16000</v>
       </c>
       <c r="O158" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C158,F158)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="Q158" s="7" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="R158" s="7" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11792,7 +11796,7 @@
         <v>160</v>
       </c>
       <c r="B159" s="7" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C159" s="6" t="s">
         <v>28</v>
@@ -11804,7 +11808,7 @@
         <v>117</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="G159" s="9" t="n">
         <v>65</v>
@@ -11844,7 +11848,7 @@
         <v>24</v>
       </c>
       <c r="Q159" s="7" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="R159" s="7" t="s">
         <v>26</v>
@@ -11855,7 +11859,7 @@
         <v>161</v>
       </c>
       <c r="B160" s="7" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C160" s="6" t="s">
         <v>28</v>
@@ -11867,7 +11871,7 @@
         <v>169</v>
       </c>
       <c r="F160" s="7" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G160" s="9" t="n">
         <v>90</v>
@@ -11918,7 +11922,7 @@
         <v>162</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C161" s="6" t="s">
         <v>28</v>
@@ -11930,7 +11934,7 @@
         <v>234</v>
       </c>
       <c r="F161" s="7" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G161" s="9" t="n">
         <v>120</v>
@@ -11981,7 +11985,7 @@
         <v>164</v>
       </c>
       <c r="B162" s="7" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C162" s="6" t="s">
         <v>22</v>
@@ -11993,7 +11997,7 @@
         <v>1209</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G162" s="9" t="n">
         <v>1450</v>
@@ -12033,7 +12037,7 @@
         <v>24</v>
       </c>
       <c r="Q162" s="7" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="R162" s="7" t="s">
         <v>26</v>
@@ -12044,7 +12048,7 @@
         <v>165</v>
       </c>
       <c r="B163" s="7" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C163" s="6" t="s">
         <v>22</v>
@@ -12056,7 +12060,7 @@
         <v>1209</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="G163" s="9" t="n">
         <v>2248</v>
@@ -12096,7 +12100,7 @@
         <v>24</v>
       </c>
       <c r="Q163" s="7" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="R163" s="7" t="s">
         <v>26</v>
@@ -12107,7 +12111,7 @@
         <v>166</v>
       </c>
       <c r="B164" s="7" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C164" s="6" t="s">
         <v>22</v>
@@ -12119,7 +12123,7 @@
         <v>3022</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="G164" s="9" t="n">
         <v>2325</v>
@@ -12159,7 +12163,7 @@
         <v>24</v>
       </c>
       <c r="Q164" s="7" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="R164" s="7" t="s">
         <v>26</v>
@@ -12170,7 +12174,7 @@
         <v>167</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C165" s="6" t="s">
         <v>22</v>
@@ -12182,25 +12186,25 @@
         <v>6240</v>
       </c>
       <c r="F165" s="7" t="s">
-        <v>22</v>
+        <v>345</v>
       </c>
       <c r="G165" s="9" t="n">
-        <v>4500</v>
+        <v>4400</v>
       </c>
       <c r="H165" s="9" t="n">
-        <v>6000</v>
+        <v>4400</v>
       </c>
       <c r="I165" s="10" t="n">
         <f aca="false">IF(E165=0,0,(E165-H165)/E165)</f>
-        <v>0.0384615384615385</v>
+        <v>0.294871794871795</v>
       </c>
       <c r="J165" s="6" t="str">
         <f aca="false">IF(E165&lt;G165,"LOSS",IF(E165&lt;H165*1.1,"THIN / RISK",IF(E165&gt;H165*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>OK</v>
       </c>
       <c r="K165" s="8" t="n">
         <f aca="false">IF(J165="OVERPRICED?",ROUND(H165*1.35,-1),MAX(E165,ROUND(H165*(1+$E$3),-1)))</f>
-        <v>6900</v>
+        <v>6240</v>
       </c>
       <c r="L165" s="8" t="n">
         <f aca="false">D165*E165</f>
@@ -12208,24 +12212,24 @@
       </c>
       <c r="M165" s="8" t="n">
         <f aca="false">D165*K165</f>
-        <v>276000</v>
+        <v>249600</v>
       </c>
       <c r="N165" s="8" t="n">
         <f aca="false">D165*H165</f>
-        <v>240000</v>
+        <v>176000</v>
       </c>
       <c r="O165" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C165,F165)),"","YES")</f>
-        <v/>
+        <v>YES</v>
       </c>
       <c r="P165" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="Q165" s="7" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="R165" s="7" t="s">
-        <v>344</v>
+        <v>26</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12233,7 +12237,7 @@
         <v>168</v>
       </c>
       <c r="B166" s="7" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C166" s="6" t="s">
         <v>22</v>
@@ -12245,25 +12249,25 @@
         <v>7150</v>
       </c>
       <c r="F166" s="7" t="s">
-        <v>22</v>
+        <v>345</v>
       </c>
       <c r="G166" s="9" t="n">
-        <v>5200</v>
+        <v>4400</v>
       </c>
       <c r="H166" s="9" t="n">
-        <v>6800</v>
+        <v>4400</v>
       </c>
       <c r="I166" s="10" t="n">
         <f aca="false">IF(E166=0,0,(E166-H166)/E166)</f>
-        <v>0.048951048951049</v>
+        <v>0.384615384615385</v>
       </c>
       <c r="J166" s="6" t="str">
         <f aca="false">IF(E166&lt;G166,"LOSS",IF(E166&lt;H166*1.1,"THIN / RISK",IF(E166&gt;H166*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>OK</v>
       </c>
       <c r="K166" s="8" t="n">
         <f aca="false">IF(J166="OVERPRICED?",ROUND(H166*1.35,-1),MAX(E166,ROUND(H166*(1+$E$3),-1)))</f>
-        <v>7820</v>
+        <v>7150</v>
       </c>
       <c r="L166" s="8" t="n">
         <f aca="false">D166*E166</f>
@@ -12271,24 +12275,24 @@
       </c>
       <c r="M166" s="8" t="n">
         <f aca="false">D166*K166</f>
-        <v>156400</v>
+        <v>143000</v>
       </c>
       <c r="N166" s="8" t="n">
         <f aca="false">D166*H166</f>
-        <v>136000</v>
+        <v>88000</v>
       </c>
       <c r="O166" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C166,F166)),"","YES")</f>
-        <v/>
+        <v>YES</v>
       </c>
       <c r="P166" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="Q166" s="7" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="R166" s="7" t="s">
-        <v>346</v>
+        <v>26</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12296,7 +12300,7 @@
         <v>177</v>
       </c>
       <c r="B167" s="7" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C167" s="6" t="s">
         <v>28</v>
@@ -12348,7 +12352,7 @@
         <v>24</v>
       </c>
       <c r="Q167" s="7" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="R167" s="7" t="s">
         <v>26</v>
@@ -12359,7 +12363,7 @@
         <v>179</v>
       </c>
       <c r="B168" s="7" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C168" s="6" t="s">
         <v>28</v>
@@ -12422,7 +12426,7 @@
         <v>180</v>
       </c>
       <c r="B169" s="7" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C169" s="6" t="s">
         <v>28</v>
@@ -12485,7 +12489,7 @@
         <v>181</v>
       </c>
       <c r="B170" s="7" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C170" s="6" t="s">
         <v>28</v>
@@ -12548,7 +12552,7 @@
         <v>182</v>
       </c>
       <c r="B171" s="7" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C171" s="6" t="s">
         <v>28</v>
@@ -12611,7 +12615,7 @@
         <v>183</v>
       </c>
       <c r="B172" s="7" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C172" s="6" t="s">
         <v>28</v>
@@ -12674,7 +12678,7 @@
         <v>184</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C173" s="6" t="s">
         <v>28</v>
@@ -12737,7 +12741,7 @@
         <v>185</v>
       </c>
       <c r="B174" s="7" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C174" s="6" t="s">
         <v>28</v>
@@ -12800,7 +12804,7 @@
         <v>186</v>
       </c>
       <c r="B175" s="7" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C175" s="6" t="s">
         <v>28</v>
@@ -12863,7 +12867,7 @@
         <v>187</v>
       </c>
       <c r="B176" s="7" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C176" s="6" t="s">
         <v>28</v>
@@ -12926,7 +12930,7 @@
         <v>188</v>
       </c>
       <c r="B177" s="7" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C177" s="6" t="s">
         <v>28</v>
@@ -12989,7 +12993,7 @@
         <v>189</v>
       </c>
       <c r="B178" s="7" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C178" s="6" t="s">
         <v>28</v>
@@ -13052,7 +13056,7 @@
         <v>190</v>
       </c>
       <c r="B179" s="7" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C179" s="6" t="s">
         <v>28</v>
@@ -13115,7 +13119,7 @@
         <v>191</v>
       </c>
       <c r="B180" s="7" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C180" s="6" t="s">
         <v>28</v>
@@ -13178,7 +13182,7 @@
         <v>192</v>
       </c>
       <c r="B181" s="7" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C181" s="6" t="s">
         <v>28</v>
@@ -13241,7 +13245,7 @@
         <v>193</v>
       </c>
       <c r="B182" s="7" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C182" s="6" t="s">
         <v>28</v>
@@ -13304,7 +13308,7 @@
         <v>194</v>
       </c>
       <c r="B183" s="7" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C183" s="6" t="s">
         <v>28</v>
@@ -13367,7 +13371,7 @@
         <v>195</v>
       </c>
       <c r="B184" s="7" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C184" s="6" t="s">
         <v>28</v>
@@ -13430,7 +13434,7 @@
         <v>196</v>
       </c>
       <c r="B185" s="7" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C185" s="6" t="s">
         <v>28</v>
@@ -13493,7 +13497,7 @@
         <v>197</v>
       </c>
       <c r="B186" s="7" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C186" s="6" t="s">
         <v>28</v>
@@ -13545,7 +13549,7 @@
         <v>44</v>
       </c>
       <c r="Q186" s="7" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="R186" s="7"/>
     </row>
@@ -13554,7 +13558,7 @@
         <v>198</v>
       </c>
       <c r="B187" s="7" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C187" s="6" t="s">
         <v>28</v>
@@ -13606,7 +13610,7 @@
         <v>44</v>
       </c>
       <c r="Q187" s="7" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="R187" s="7"/>
     </row>
@@ -13615,7 +13619,7 @@
         <v>199</v>
       </c>
       <c r="B188" s="7" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C188" s="6" t="s">
         <v>28</v>
@@ -13667,7 +13671,7 @@
         <v>44</v>
       </c>
       <c r="Q188" s="7" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="R188" s="7"/>
     </row>
@@ -13676,7 +13680,7 @@
         <v>200</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C189" s="6" t="s">
         <v>28</v>
@@ -13728,7 +13732,7 @@
         <v>44</v>
       </c>
       <c r="Q189" s="7" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="R189" s="7"/>
     </row>
@@ -13737,7 +13741,7 @@
         <v>201</v>
       </c>
       <c r="B190" s="7" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C190" s="6" t="s">
         <v>28</v>
@@ -13789,7 +13793,7 @@
         <v>44</v>
       </c>
       <c r="Q190" s="7" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="R190" s="7"/>
     </row>
@@ -13798,7 +13802,7 @@
         <v>202</v>
       </c>
       <c r="B191" s="7" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C191" s="6" t="s">
         <v>28</v>
@@ -13850,7 +13854,7 @@
         <v>24</v>
       </c>
       <c r="Q191" s="7" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="R191" s="7" t="s">
         <v>26</v>
@@ -13861,7 +13865,7 @@
         <v>204</v>
       </c>
       <c r="B192" s="7" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C192" s="6" t="s">
         <v>28</v>
@@ -13873,7 +13877,7 @@
         <v>845</v>
       </c>
       <c r="F192" s="7" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="G192" s="9" t="n">
         <v>5480</v>
@@ -13913,7 +13917,7 @@
         <v>30</v>
       </c>
       <c r="Q192" s="7" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="R192" s="7" t="s">
         <v>32</v>
@@ -13924,7 +13928,7 @@
         <v>205</v>
       </c>
       <c r="B193" s="7" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C193" s="6" t="s">
         <v>28</v>
@@ -13936,7 +13940,7 @@
         <v>910</v>
       </c>
       <c r="F193" s="7" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="G193" s="9" t="n">
         <v>5960</v>
@@ -13976,7 +13980,7 @@
         <v>30</v>
       </c>
       <c r="Q193" s="7" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="R193" s="7" t="s">
         <v>32</v>
@@ -13987,7 +13991,7 @@
         <v>206</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C194" s="6" t="s">
         <v>28</v>
@@ -13999,7 +14003,7 @@
         <v>1170</v>
       </c>
       <c r="F194" s="7" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="G194" s="9" t="n">
         <v>6930</v>
@@ -14039,7 +14043,7 @@
         <v>30</v>
       </c>
       <c r="Q194" s="7" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="R194" s="7" t="s">
         <v>32</v>
@@ -14050,7 +14054,7 @@
         <v>207</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C195" s="6" t="s">
         <v>28</v>
@@ -14062,7 +14066,7 @@
         <v>1430</v>
       </c>
       <c r="F195" s="7" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="G195" s="9" t="n">
         <v>8960</v>
@@ -14102,7 +14106,7 @@
         <v>30</v>
       </c>
       <c r="Q195" s="7" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="R195" s="7" t="s">
         <v>32</v>
@@ -14113,7 +14117,7 @@
         <v>208</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C196" s="6" t="s">
         <v>28</v>
@@ -14125,7 +14129,7 @@
         <v>1690</v>
       </c>
       <c r="F196" s="7" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G196" s="9" t="n">
         <v>2900</v>
@@ -14165,7 +14169,7 @@
         <v>44</v>
       </c>
       <c r="Q196" s="7" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="R196" s="7"/>
     </row>
@@ -14174,7 +14178,7 @@
         <v>209</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C197" s="6" t="s">
         <v>28</v>
@@ -14186,7 +14190,7 @@
         <v>2340</v>
       </c>
       <c r="F197" s="7" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="G197" s="9" t="n">
         <v>15380</v>
@@ -14226,7 +14230,7 @@
         <v>30</v>
       </c>
       <c r="Q197" s="7" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="R197" s="7" t="s">
         <v>32</v>
@@ -14237,7 +14241,7 @@
         <v>210</v>
       </c>
       <c r="B198" s="7" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C198" s="6" t="s">
         <v>28</v>
@@ -14249,7 +14253,7 @@
         <v>2860</v>
       </c>
       <c r="F198" s="7" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="G198" s="9" t="n">
         <v>17610</v>
@@ -14289,7 +14293,7 @@
         <v>30</v>
       </c>
       <c r="Q198" s="7" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="R198" s="7" t="s">
         <v>32</v>
@@ -14300,7 +14304,7 @@
         <v>211</v>
       </c>
       <c r="B199" s="7" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C199" s="6" t="s">
         <v>28</v>
@@ -14312,7 +14316,7 @@
         <v>4160</v>
       </c>
       <c r="F199" s="7" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="G199" s="9" t="n">
         <v>22180</v>
@@ -14352,7 +14356,7 @@
         <v>30</v>
       </c>
       <c r="Q199" s="7" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="R199" s="7" t="s">
         <v>32</v>
@@ -14363,7 +14367,7 @@
         <v>212</v>
       </c>
       <c r="B200" s="7" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C200" s="6" t="s">
         <v>28</v>
@@ -14375,7 +14379,7 @@
         <v>5460</v>
       </c>
       <c r="F200" s="7" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="G200" s="9" t="n">
         <v>25690</v>
@@ -14415,7 +14419,7 @@
         <v>30</v>
       </c>
       <c r="Q200" s="7" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="R200" s="7" t="s">
         <v>32</v>
@@ -14426,7 +14430,7 @@
         <v>213</v>
       </c>
       <c r="B201" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C201" s="6" t="s">
         <v>28</v>
@@ -14489,7 +14493,7 @@
         <v>214</v>
       </c>
       <c r="B202" s="7" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C202" s="6" t="s">
         <v>28</v>
@@ -14552,7 +14556,7 @@
         <v>215</v>
       </c>
       <c r="B203" s="7" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C203" s="6" t="s">
         <v>28</v>
@@ -14615,7 +14619,7 @@
         <v>216</v>
       </c>
       <c r="B204" s="7" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C204" s="6" t="s">
         <v>28</v>
@@ -14678,7 +14682,7 @@
         <v>217</v>
       </c>
       <c r="B205" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C205" s="6" t="s">
         <v>28</v>
@@ -14741,7 +14745,7 @@
         <v>218</v>
       </c>
       <c r="B206" s="7" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C206" s="6" t="s">
         <v>28</v>
@@ -14804,7 +14808,7 @@
         <v>219</v>
       </c>
       <c r="B207" s="7" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C207" s="6" t="s">
         <v>28</v>
@@ -14867,7 +14871,7 @@
         <v>220</v>
       </c>
       <c r="B208" s="7" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C208" s="6" t="s">
         <v>28</v>
@@ -14930,7 +14934,7 @@
         <v>221</v>
       </c>
       <c r="B209" s="7" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C209" s="6" t="s">
         <v>28</v>
@@ -14993,7 +14997,7 @@
         <v>222</v>
       </c>
       <c r="B210" s="7" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C210" s="6" t="s">
         <v>28</v>
@@ -15005,7 +15009,7 @@
         <v>15600</v>
       </c>
       <c r="F210" s="7" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="G210" s="9" t="n">
         <v>18000</v>
@@ -15056,7 +15060,7 @@
         <v>223</v>
       </c>
       <c r="B211" s="7" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C211" s="6" t="s">
         <v>28</v>
@@ -15108,7 +15112,7 @@
         <v>44</v>
       </c>
       <c r="Q211" s="7" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="R211" s="7"/>
     </row>
@@ -15117,7 +15121,7 @@
         <v>224</v>
       </c>
       <c r="B212" s="7" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C212" s="6" t="s">
         <v>28</v>
@@ -15129,7 +15133,7 @@
         <v>54600</v>
       </c>
       <c r="F212" s="7" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="G212" s="9" t="n">
         <v>85000</v>
@@ -15169,10 +15173,10 @@
         <v>30</v>
       </c>
       <c r="Q212" s="7" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="R212" s="7" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15180,7 +15184,7 @@
         <v>225</v>
       </c>
       <c r="B213" s="7" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C213" s="6" t="s">
         <v>28</v>
@@ -15232,7 +15236,7 @@
         <v>30</v>
       </c>
       <c r="Q213" s="7" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="R213" s="7" t="s">
         <v>32</v>
@@ -15243,7 +15247,7 @@
         <v>226</v>
       </c>
       <c r="B214" s="7" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C214" s="6" t="s">
         <v>28</v>
@@ -15295,7 +15299,7 @@
         <v>30</v>
       </c>
       <c r="Q214" s="7" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="R214" s="7" t="s">
         <v>32</v>
@@ -15306,7 +15310,7 @@
         <v>227</v>
       </c>
       <c r="B215" s="7" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C215" s="6" t="s">
         <v>28</v>
@@ -15358,7 +15362,7 @@
         <v>30</v>
       </c>
       <c r="Q215" s="7" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="R215" s="7" t="s">
         <v>32</v>
@@ -15369,7 +15373,7 @@
         <v>228</v>
       </c>
       <c r="B216" s="7" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C216" s="6" t="s">
         <v>28</v>
@@ -15421,7 +15425,7 @@
         <v>30</v>
       </c>
       <c r="Q216" s="7" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="R216" s="7" t="s">
         <v>32</v>
@@ -15432,7 +15436,7 @@
         <v>229</v>
       </c>
       <c r="B217" s="7" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C217" s="6" t="s">
         <v>28</v>
@@ -15484,7 +15488,7 @@
         <v>30</v>
       </c>
       <c r="Q217" s="7" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="R217" s="7" t="s">
         <v>32</v>
@@ -15495,7 +15499,7 @@
         <v>230</v>
       </c>
       <c r="B218" s="7" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C218" s="6" t="s">
         <v>28</v>
@@ -15507,7 +15511,7 @@
         <v>9750</v>
       </c>
       <c r="F218" s="7" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="G218" s="9" t="n">
         <v>5950</v>
@@ -15547,7 +15551,7 @@
         <v>24</v>
       </c>
       <c r="Q218" s="7" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="R218" s="7" t="s">
         <v>26</v>
@@ -15558,7 +15562,7 @@
         <v>231</v>
       </c>
       <c r="B219" s="7" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C219" s="6" t="s">
         <v>28</v>
@@ -15570,7 +15574,7 @@
         <v>12350</v>
       </c>
       <c r="F219" s="7" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="G219" s="9" t="n">
         <v>5950</v>
@@ -15610,7 +15614,7 @@
         <v>44</v>
       </c>
       <c r="Q219" s="7" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="R219" s="7"/>
     </row>
@@ -15619,7 +15623,7 @@
         <v>233</v>
       </c>
       <c r="B220" s="7" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C220" s="6" t="s">
         <v>111</v>
@@ -15671,7 +15675,7 @@
         <v>44</v>
       </c>
       <c r="Q220" s="7" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="R220" s="7"/>
     </row>
@@ -15680,7 +15684,7 @@
         <v>234</v>
       </c>
       <c r="B221" s="7" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C221" s="6" t="s">
         <v>22</v>
@@ -15732,7 +15736,7 @@
         <v>24</v>
       </c>
       <c r="Q221" s="7" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="R221" s="7" t="s">
         <v>26</v>
@@ -15743,7 +15747,7 @@
         <v>235</v>
       </c>
       <c r="B222" s="7" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C222" s="6" t="s">
         <v>28</v>
@@ -15795,7 +15799,7 @@
         <v>24</v>
       </c>
       <c r="Q222" s="7" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="R222" s="7" t="s">
         <v>26</v>
@@ -15806,7 +15810,7 @@
         <v>236</v>
       </c>
       <c r="B223" s="7" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C223" s="6" t="s">
         <v>22</v>
@@ -15818,7 +15822,7 @@
         <v>2860</v>
       </c>
       <c r="F223" s="7" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="G223" s="9" t="n">
         <v>2400</v>
@@ -15858,10 +15862,10 @@
         <v>30</v>
       </c>
       <c r="Q223" s="7" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="R223" s="7" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15869,7 +15873,7 @@
         <v>237</v>
       </c>
       <c r="B224" s="7" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C224" s="6" t="s">
         <v>28</v>
@@ -15921,7 +15925,7 @@
         <v>24</v>
       </c>
       <c r="Q224" s="7" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="R224" s="7" t="s">
         <v>26</v>
@@ -15932,7 +15936,7 @@
         <v>238</v>
       </c>
       <c r="B225" s="7" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C225" s="6" t="s">
         <v>28</v>
@@ -15944,7 +15948,7 @@
         <v>8450</v>
       </c>
       <c r="F225" s="7" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G225" s="9" t="n">
         <v>7800</v>
@@ -15984,7 +15988,7 @@
         <v>44</v>
       </c>
       <c r="Q225" s="7" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="R225" s="7"/>
     </row>
@@ -15993,7 +15997,7 @@
         <v>239</v>
       </c>
       <c r="B226" s="7" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C226" s="6" t="s">
         <v>111</v>
@@ -16045,7 +16049,7 @@
         <v>44</v>
       </c>
       <c r="Q226" s="7" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="R226" s="7"/>
     </row>
@@ -16054,7 +16058,7 @@
         <v>240</v>
       </c>
       <c r="B227" s="7" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C227" s="6" t="s">
         <v>28</v>
@@ -16106,15 +16110,15 @@
         <v>30</v>
       </c>
       <c r="Q227" s="7" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="R227" s="7" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B228" s="3" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="L228" s="11" t="n">
         <f aca="false">SUM(L6:L227)</f>
@@ -16122,11 +16126,11 @@
       </c>
       <c r="M228" s="11" t="n">
         <f aca="false">SUM(M6:M227)</f>
-        <v>14711711</v>
+        <v>14661411</v>
       </c>
       <c r="N228" s="11" t="n">
         <f aca="false">SUM(N6:N227)</f>
-        <v>11738936</v>
+        <v>11614372</v>
       </c>
     </row>
   </sheetData>
@@ -16175,12 +16179,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B3" s="11" t="n">
         <f aca="false">COUNTA('Rate Check'!A6:A227)</f>
@@ -16189,7 +16193,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B4" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"LOSS")</f>
@@ -16198,38 +16202,38 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B5" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"THIN / RISK")</f>
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B6" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"OK")</f>
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B7" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"OVERPRICED?")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B8" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!O6:O227,"YES")</f>
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16237,7 +16241,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B10" s="11" t="n">
         <f aca="false">'Rate Check'!L228</f>
@@ -16246,34 +16250,34 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B11" s="11" t="n">
         <f aca="false">'Rate Check'!N228</f>
-        <v>11738936</v>
+        <v>11614372</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B12" s="11" t="n">
         <f aca="false">B10-B11</f>
-        <v>470572</v>
+        <v>595136</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B13" s="14" t="n">
         <f aca="false">IF(B10=0,0,B12/B10)</f>
-        <v>0.0385414383609888</v>
+        <v>0.04874365125933</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B14" s="11" t="n">
         <f aca="false">SUMPRODUCT(('Rate Check'!E6:E227&lt;'Rate Check'!H6:H227)*('Rate Check'!H6:H227-'Rate Check'!E6:E227)*'Rate Check'!D6:D227)</f>
@@ -16285,20 +16289,20 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B16" s="11" t="n">
         <f aca="false">'Rate Check'!M228</f>
-        <v>14711711</v>
+        <v>14661411</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B17" s="14" t="n">
         <f aca="false">IF(B16=0,0,(B16-B11)/B16)</f>
-        <v>0.202068610510361</v>
+        <v>0.207827132054343</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16306,29 +16310,29 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B19" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!P6:P227,"V")</f>
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B20" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!P6:P227,"S")</f>
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B21" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!P6:P227,"N")</f>
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -16356,247 +16360,247 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>

--- a/quotes/PR-217-228/Quote_PR217_PR228_Rate_Check.xlsx
+++ b/quotes/PR-217-228/Quote_PR217_PR228_Rate_Check.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1307" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="572">
   <si>
     <t xml:space="preserve">Zidane Corporation - Quote PR-217 &amp; PR-228: Brand + Buying Rate Check</t>
   </si>
@@ -255,19 +255,16 @@
     <t xml:space="preserve">ALLEN (HEX) KEY 14MM</t>
   </si>
   <si>
-    <t xml:space="preserve">N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">goldentools.ae Licota hex 12mm scaled to 14mm x90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye.</t>
+    <t xml:space="preserve">Yato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inserv.lv Yato long hex key 14mm YT-05444 EUR 4.80 -&gt; PKR 1,845 (fx x shelf basis)</t>
   </si>
   <si>
     <t xml:space="preserve">ALLEN (HEX) KEY 16MM</t>
   </si>
   <si>
-    <t xml:space="preserve">goldentools.ae Licota hex 12mm scaled to 16mm x90</t>
+    <t xml:space="preserve">inserv.lv Yato long hex key 14mm YT-05444 EUR 4.80 (16mm listed nahi - 14mm rate) -&gt; PKR 1,845 (fx x shelf basis)</t>
   </si>
   <si>
     <t xml:space="preserve">CIRCLIP PLIER INTERNAL STRAIGHT 175MM</t>
@@ -288,15 +285,15 @@
     <t xml:space="preserve">CIRCLIP PLIER INTERNAL STRAIGHT 230MM</t>
   </si>
   <si>
-    <t xml:space="preserve">goldentools.ae Licota snap ring set 4pc 175mm AED 212.5; toolsmart.pk same set 13,750 (3,438/pc) -&gt; 230mm +30%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. 230mm circlip</t>
+    <t xml:space="preserve">mecatechnic.com circlip plier straight internal 300mm EUR 16.57 (230mm listed nahi) -&gt; PKR 6,368 (fx x shelf basis)</t>
   </si>
   <si>
     <t xml:space="preserve">CIRCLIP PLIER EXTERNAL STRAIGHT 230MM</t>
   </si>
   <si>
+    <t xml:space="preserve">inserv.lv Yato circlip plier external 300mm YT-19973 EUR 13.00 (230mm listed nahi) -&gt; PKR 4,996 (fx x shelf basis)</t>
+  </si>
+  <si>
     <t xml:space="preserve">CHISEL SET (05 PCS SET)</t>
   </si>
   <si>
@@ -381,25 +378,22 @@
     <t xml:space="preserve">HEX IMPACT ADAPTOR 1/2" FEMALE TO 1/4" FEMALE</t>
   </si>
   <si>
-    <t xml:space="preserve">toolsmart.pk Licota impact adapter 3/8F x 1/2M 1,130 (similar)</t>
+    <t xml:space="preserve">DeWalt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uk.rubix.com DeWalt DT7508 1/2in sq female to 1/4in hex female impact adaptor GBP 14.23 incl VAT -&gt; PKR 5,955 (fx x shelf basis)</t>
   </si>
   <si>
     <t xml:space="preserve">FLAT FILE 12"</t>
   </si>
   <si>
-    <t xml:space="preserve">Yato</t>
-  </si>
-  <si>
     <t xml:space="preserve">zeeshanhardware Yato YT-6190 12in 1,750</t>
   </si>
   <si>
     <t xml:space="preserve">ROUNDE FILE 12"</t>
   </si>
   <si>
-    <t xml:space="preserve">zeeshanhardware Yato 12in file 1,750 (flat; round similar)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. Yato round file</t>
+    <t xml:space="preserve">inserv.lv Yato round file 300mm YT-6194 EUR 5.10 -&gt; PKR 1,960 (fx x shelf basis)</t>
   </si>
   <si>
     <t xml:space="preserve">UNIVERSAL PULLER 2-ARMED WITH HOOK BRAKE 21</t>
@@ -453,22 +447,13 @@
     <t xml:space="preserve">MANUAL GREASE GUN 5KG</t>
   </si>
   <si>
-    <t xml:space="preserve">Yato / Industrial (bucket type)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. 5kg bucket grease pump</t>
+    <t xml:space="preserve">aajjo.com ATS ELGI 5kg manual grease bucket pump INR 20,000 (Groz 12L INR 25,000) -&gt; PKR 67,000 (fx x shelf basis)</t>
   </si>
   <si>
     <t xml:space="preserve">AIR GREASE GUN 500CC</t>
   </si>
   <si>
-    <t xml:space="preserve">goldentools.ae Licota hand grease gun AGH-10004H AED 120 (=toolsmart 7,760) -&gt; air gun ~1.5x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. air grease gun</t>
+    <t xml:space="preserve">diy.com Yato pneumatic air grease gun 400cc YT-07055 GBP 49.99 (500cc air listed nahi) -&gt; PKR 20,921 (fx x shelf basis)</t>
   </si>
   <si>
     <t xml:space="preserve">HAND GREASE GUN WITH HOSE 500CC</t>
@@ -480,9 +465,15 @@
     <t xml:space="preserve">GREASE PIPE 1/4"X12"</t>
   </si>
   <si>
+    <t xml:space="preserve">tooled-up.com Sealey grease gun flexible hose 300mm GBP 10.95 (1/8 BSP; 1/4 listed nahi) -&gt; PKR 4,583 (fx x shelf basis)</t>
+  </si>
+  <si>
     <t xml:space="preserve">DOUBLE HANDLE GREASE NOZZLE</t>
   </si>
   <si>
+    <t xml:space="preserve">amazon COMVIEE double handle quick lock grease coupler USD 12.99 -&gt; PKR 4,294 (fx x shelf basis)</t>
+  </si>
+  <si>
     <t xml:space="preserve">STEEL MEASURMENT TAPE 100M</t>
   </si>
   <si>
@@ -561,13 +552,7 @@
     <t xml:space="preserve">HSS DRILL BITS 1/16-1/2" 29 PCS SET</t>
   </si>
   <si>
-    <t xml:space="preserve">Dormer A095 (A002 x29)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mrosupply Dormer A09518 29pc set (USD) scaled - PK listing n/a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. 29pc inch set</t>
+    <t xml:space="preserve">rapidonline.com Dormer A09518 29pc HSS-TiN 1/16-1/2 set GBP 140.75 ex VAT (168.90 incl) -&gt; PKR 70,685 (fx x shelf basis)</t>
   </si>
   <si>
     <t xml:space="preserve">HSS DRILL BIT 14MM TAPER SHANK</t>
@@ -708,10 +693,13 @@
     <t xml:space="preserve">TAP SET 1/2" BSPF LEFT HAND (Dormer)</t>
   </si>
   <si>
+    <t xml:space="preserve">cromwell.co.uk Dormer E547 1/2in BSPF tap set (2pc) GBP 95.99 incl VAT - RH rate, LH listed nahi -&gt; PKR 40,172 (fx x shelf basis)</t>
+  </si>
+  <si>
     <t xml:space="preserve">TAP SET 1/2" BSPF RIGHT HAND</t>
   </si>
   <si>
-    <t xml:space="preserve">Dormer / Totem</t>
+    <t xml:space="preserve">cromwell.co.uk Dormer E547 1/2in BSPF tap set (2pc) GBP 95.99 incl VAT -&gt; PKR 40,172 (fx x shelf basis)</t>
   </si>
   <si>
     <t xml:space="preserve">TAP SET 3/8" BSPF</t>
@@ -762,7 +750,7 @@
     <t xml:space="preserve">C-CLAMP 12"</t>
   </si>
   <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. 12in (Total G clamp range totaltool 1,430-3,699 size unclear</t>
+    <t xml:space="preserve">inserv.lv Yato G-clamp 12in (300mm) YT-64258 EUR 13.60 -&gt; PKR 5,226 (fx x shelf basis)</t>
   </si>
   <si>
     <t xml:space="preserve">SPIRIT LEVEL 1 METER</t>
@@ -774,7 +762,7 @@
     <t xml:space="preserve">MAGNET SPIRIT LEVEL 12"</t>
   </si>
   <si>
-    <t xml:space="preserve">Online nahi mila - dealer quote chahiye. 12in magnetic level</t>
+    <t xml:space="preserve">inserv.lv Yato magnetic spirit level 300mm YT-30310 EUR 9.50 -&gt; PKR 3,651 (fx x shelf basis)</t>
   </si>
   <si>
     <t xml:space="preserve">CARBON STEEL RIGHT ANGLE 150MM</t>
@@ -831,6 +819,12 @@
     <t xml:space="preserve">CYLINDER KEY/SPANNER</t>
   </si>
   <si>
+    <t xml:space="preserve">Draper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">airconspares.com Draper 35109 gas cylinder key spanner GBP 5.36 incl VAT -&gt; PKR 2,243 (fx x shelf basis)</t>
+  </si>
+  <si>
     <t xml:space="preserve">TIP CLEANER FOR GAS WELDING TORCH</t>
   </si>
   <si>
@@ -861,6 +855,9 @@
     <t xml:space="preserve">TORCH HEAD ARGON WELDING</t>
   </si>
   <si>
+    <t xml:space="preserve">ebay WP-26 TIG torch head body USD 21.00 (Weldcraft OEM USD 87.30) -&gt; PKR 6,941 (fx x shelf basis)</t>
+  </si>
+  <si>
     <t xml:space="preserve">COLLECT OF ARGON 2.4MM</t>
   </si>
   <si>
@@ -945,6 +942,9 @@
     <t xml:space="preserve">BUFFING DISC 125MM</t>
   </si>
   <si>
+    <t xml:space="preserve">toya24.pl polishing felt disc 125mm PLN 8.97 incl VAT -&gt; PKR 812 (fx x shelf basis)</t>
+  </si>
+  <si>
     <t xml:space="preserve">BRASS PLATED CUP WIRE BRUSH 125MM</t>
   </si>
   <si>
@@ -972,10 +972,7 @@
     <t xml:space="preserve">COTTON ROPE 2MM</t>
   </si>
   <si>
-    <t xml:space="preserve">Local / Generic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Market (per metre)</t>
+    <t xml:space="preserve">walmart.com cotton rope 2mm x 91.5m USD 3.97 (=USD 0.043/m) -&gt; PKR 14 (fx x shelf basis)</t>
   </si>
   <si>
     <t xml:space="preserve">HYDRAULIC HAND TROLLY 3T</t>
@@ -1146,15 +1143,27 @@
     <t xml:space="preserve">TAP SET 1" BSPF LEFT HAND</t>
   </si>
   <si>
+    <t xml:space="preserve">cromwell.co.uk Dormer E119 1in BSPF hand tap set of 3 GBP 224.40 incl VAT - RH rate, LH listed nahi -&gt; PKR 93,911 (fx x shelf basis)</t>
+  </si>
+  <si>
     <t xml:space="preserve">TAP SET 1" BSPF RIGHT HAND</t>
   </si>
   <si>
+    <t xml:space="preserve">cromwell.co.uk Dormer E119 1in BSPF hand tap set of 3 GBP 224.40 incl VAT -&gt; PKR 93,911 (fx x shelf basis)</t>
+  </si>
+  <si>
     <t xml:space="preserve">TAP SET 1-1/4" BSPF LEFT HAND</t>
   </si>
   <si>
+    <t xml:space="preserve">cromwell.co.uk Dormer E547 1-1/4in BSPF second tap GBP 214.80 x2 (set listed nahi; LH listed nahi) -&gt; PKR 179,788 (fx x shelf basis)</t>
+  </si>
+  <si>
     <t xml:space="preserve">TAP SET 1-1/4" BSPF RIGHT HAND</t>
   </si>
   <si>
+    <t xml:space="preserve">cromwell.co.uk Dormer E547 1-1/4in BSPF second tap GBP 214.80 x2 (set listed nahi) -&gt; PKR 179,788 (fx x shelf basis)</t>
+  </si>
+  <si>
     <t xml:space="preserve">TAP SET M6</t>
   </si>
   <si>
@@ -1164,6 +1173,9 @@
     <t xml:space="preserve">TAP SET M8</t>
   </si>
   <si>
+    <t xml:space="preserve">inserv.lv Yato hand tap set M8 3pc YT-2935 EUR 7.60 -&gt; PKR 2,921 (fx x shelf basis)</t>
+  </si>
+  <si>
     <t xml:space="preserve">TAP SET M10</t>
   </si>
   <si>
@@ -1329,18 +1341,33 @@
     <t xml:space="preserve">DIE NUT SIZE 5MM</t>
   </si>
   <si>
+    <t xml:space="preserve">lcsc.com Yato round die M5 YT-2962 USD 2.46 -&gt; PKR 813 (fx x shelf basis)</t>
+  </si>
+  <si>
     <t xml:space="preserve">DIE NUT SIZE 6MM</t>
   </si>
   <si>
+    <t xml:space="preserve">lcsc.com Yato round die M5 YT-2962 USD 2.46 (M6 YT-2963 same size 20mm, price listed nahi) -&gt; PKR 813 (fx x shelf basis)</t>
+  </si>
+  <si>
     <t xml:space="preserve">DIE NUT SIZE 8MM</t>
   </si>
   <si>
+    <t xml:space="preserve">inserv.lv Yato round die M8 YT-2965 EUR 4.70 -&gt; PKR 1,806 (fx x shelf basis)</t>
+  </si>
+  <si>
     <t xml:space="preserve">DIE NUT SIZE 10MM</t>
   </si>
   <si>
+    <t xml:space="preserve">inserv.lv Yato round die M10 YT-2967 EUR 4.70 -&gt; PKR 1,806 (fx x shelf basis)</t>
+  </si>
+  <si>
     <t xml:space="preserve">DIE NUT SIZE 12MM</t>
   </si>
   <si>
+    <t xml:space="preserve">800benaa.com Yato die M16 AED 57.14 (M12 price listed nahi - upper rate) -&gt; PKR 5,143 (fx x shelf basis)</t>
+  </si>
+  <si>
     <t xml:space="preserve">DIE NUT SIZE 16MM</t>
   </si>
   <si>
@@ -1350,12 +1377,21 @@
     <t xml:space="preserve">DIE NUT HANDLE SMALL</t>
   </si>
   <si>
+    <t xml:space="preserve">inserv.lv Yato die handle M10-M11 YT-2983 EUR 5.30 -&gt; PKR 2,037 (fx x shelf basis)</t>
+  </si>
+  <si>
     <t xml:space="preserve">DIE NUT HANDLE MEDIUM</t>
   </si>
   <si>
+    <t xml:space="preserve">inserv.lv Yato die handle M16-M20 YT-2985 EUR 9.70 (M12-14 38mm price listed nahi) -&gt; PKR 3,728 (fx x shelf basis)</t>
+  </si>
+  <si>
     <t xml:space="preserve">DIE NUT HANDLE LARGE</t>
   </si>
   <si>
+    <t xml:space="preserve">inserv.lv Yato die handle M16-M20 YT-2985 EUR 9.70 -&gt; PKR 3,728 (fx x shelf basis)</t>
+  </si>
+  <si>
     <t xml:space="preserve">3 JAW CHUCK 4"</t>
   </si>
   <si>
@@ -1395,7 +1431,7 @@
     <t xml:space="preserve">HSS TOOL 16MMX16MMX200MM</t>
   </si>
   <si>
-    <t xml:space="preserve">Dormer HSS toolbit - PK listing n/a, est ~1.8x generic</t>
+    <t xml:space="preserve">ebay.co.uk HSS tool bit 16x16x200mm GBP 4.99 (variant price unclear) -&gt; PKR 2,088 (fx x shelf basis)</t>
   </si>
   <si>
     <t xml:space="preserve">HSS PARTING OFF TOOL 1/8" X 3/4" X 8"</t>
@@ -3628,7 +3664,7 @@
       </c>
       <c r="R25" s="7"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="n">
         <v>21</v>
       </c>
@@ -3645,17 +3681,17 @@
         <v>1170</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>1350</v>
+        <v>1845</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>1600</v>
+        <v>1845</v>
       </c>
       <c r="I26" s="10" t="n">
         <f aca="false">IF(E26=0,0,(E26-H26)/E26)</f>
-        <v>-0.367521367521368</v>
+        <v>-0.576923076923077</v>
       </c>
       <c r="J26" s="6" t="str">
         <f aca="false">IF(E26&lt;G26,"LOSS",IF(E26&lt;H26*1.1,"THIN / RISK",IF(E26&gt;H26*1.8,"OVERPRICED?","OK")))</f>
@@ -3663,7 +3699,7 @@
       </c>
       <c r="K26" s="8" t="n">
         <f aca="false">IF(J26="OVERPRICED?",ROUND(H26*1.35,-1),MAX(E26,ROUND(H26*(1+$E$3),-1)))</f>
-        <v>1840</v>
+        <v>2120</v>
       </c>
       <c r="L26" s="8" t="n">
         <f aca="false">D26*E26</f>
@@ -3671,32 +3707,30 @@
       </c>
       <c r="M26" s="8" t="n">
         <f aca="false">D26*K26</f>
-        <v>5520</v>
+        <v>6360</v>
       </c>
       <c r="N26" s="8" t="n">
         <f aca="false">D26*H26</f>
-        <v>4800</v>
+        <v>5535</v>
       </c>
       <c r="O26" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C26,F26)),"","YES")</f>
-        <v/>
+        <v>YES</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="Q26" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="R26" s="7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R26" s="7"/>
+    </row>
+    <row r="27" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="n">
         <v>22</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>28</v>
@@ -3708,17 +3742,17 @@
         <v>1430</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>1700</v>
+        <v>1845</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>2000</v>
+        <v>1845</v>
       </c>
       <c r="I27" s="10" t="n">
         <f aca="false">IF(E27=0,0,(E27-H27)/E27)</f>
-        <v>-0.398601398601399</v>
+        <v>-0.29020979020979</v>
       </c>
       <c r="J27" s="6" t="str">
         <f aca="false">IF(E27&lt;G27,"LOSS",IF(E27&lt;H27*1.1,"THIN / RISK",IF(E27&gt;H27*1.8,"OVERPRICED?","OK")))</f>
@@ -3726,7 +3760,7 @@
       </c>
       <c r="K27" s="8" t="n">
         <f aca="false">IF(J27="OVERPRICED?",ROUND(H27*1.35,-1),MAX(E27,ROUND(H27*(1+$E$3),-1)))</f>
-        <v>2300</v>
+        <v>2120</v>
       </c>
       <c r="L27" s="8" t="n">
         <f aca="false">D27*E27</f>
@@ -3734,24 +3768,24 @@
       </c>
       <c r="M27" s="8" t="n">
         <f aca="false">D27*K27</f>
-        <v>6900</v>
+        <v>6360</v>
       </c>
       <c r="N27" s="8" t="n">
         <f aca="false">D27*H27</f>
-        <v>6000</v>
+        <v>5535</v>
       </c>
       <c r="O27" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C27,F27)),"","YES")</f>
-        <v/>
+        <v>YES</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="Q27" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R27" s="7" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3759,7 +3793,7 @@
         <v>23</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>28</v>
@@ -3811,7 +3845,7 @@
         <v>33</v>
       </c>
       <c r="Q28" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="R28" s="7"/>
     </row>
@@ -3820,7 +3854,7 @@
         <v>24</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>28</v>
@@ -3872,7 +3906,7 @@
         <v>33</v>
       </c>
       <c r="Q29" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="R29" s="7"/>
     </row>
@@ -3881,7 +3915,7 @@
         <v>25</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>28</v>
@@ -3933,7 +3967,7 @@
         <v>33</v>
       </c>
       <c r="Q30" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="R30" s="7"/>
     </row>
@@ -3942,7 +3976,7 @@
         <v>26</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>28</v>
@@ -3994,7 +4028,7 @@
         <v>33</v>
       </c>
       <c r="Q31" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="R31" s="7"/>
     </row>
@@ -4003,7 +4037,7 @@
         <v>27</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>28</v>
@@ -4015,25 +4049,25 @@
         <v>6760</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>4300</v>
+        <v>6368</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>4800</v>
+        <v>6368</v>
       </c>
       <c r="I32" s="10" t="n">
         <f aca="false">IF(E32=0,0,(E32-H32)/E32)</f>
-        <v>0.289940828402367</v>
+        <v>0.0579881656804734</v>
       </c>
       <c r="J32" s="6" t="str">
         <f aca="false">IF(E32&lt;G32,"LOSS",IF(E32&lt;H32*1.1,"THIN / RISK",IF(E32&gt;H32*1.8,"OVERPRICED?","OK")))</f>
-        <v>OK</v>
+        <v>THIN / RISK</v>
       </c>
       <c r="K32" s="8" t="n">
         <f aca="false">IF(J32="OVERPRICED?",ROUND(H32*1.35,-1),MAX(E32,ROUND(H32*(1+$E$3),-1)))</f>
-        <v>6760</v>
+        <v>7320</v>
       </c>
       <c r="L32" s="8" t="n">
         <f aca="false">D32*E32</f>
@@ -4041,24 +4075,24 @@
       </c>
       <c r="M32" s="8" t="n">
         <f aca="false">D32*K32</f>
-        <v>27040</v>
+        <v>29280</v>
       </c>
       <c r="N32" s="8" t="n">
         <f aca="false">D32*H32</f>
-        <v>19200</v>
+        <v>25472</v>
       </c>
       <c r="O32" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C32,F32)),"","YES")</f>
-        <v/>
+        <v>YES</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="Q32" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="R32" s="7" t="s">
-        <v>88</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4066,7 +4100,7 @@
         <v>28</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>28</v>
@@ -4078,17 +4112,17 @@
         <v>6760</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>4300</v>
+        <v>4996</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>4800</v>
+        <v>4996</v>
       </c>
       <c r="I33" s="10" t="n">
         <f aca="false">IF(E33=0,0,(E33-H33)/E33)</f>
-        <v>0.289940828402367</v>
+        <v>0.26094674556213</v>
       </c>
       <c r="J33" s="6" t="str">
         <f aca="false">IF(E33&lt;G33,"LOSS",IF(E33&lt;H33*1.1,"THIN / RISK",IF(E33&gt;H33*1.8,"OVERPRICED?","OK")))</f>
@@ -4108,20 +4142,20 @@
       </c>
       <c r="N33" s="8" t="n">
         <f aca="false">D33*H33</f>
-        <v>14400</v>
+        <v>14988</v>
       </c>
       <c r="O33" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C33,F33)),"","YES")</f>
-        <v/>
+        <v>YES</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="Q33" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="R33" s="7" t="s">
-        <v>88</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4129,7 +4163,7 @@
         <v>30</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>28</v>
@@ -4181,7 +4215,7 @@
         <v>33</v>
       </c>
       <c r="Q34" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="R34" s="7"/>
     </row>
@@ -4190,7 +4224,7 @@
         <v>31</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>28</v>
@@ -4242,7 +4276,7 @@
         <v>33</v>
       </c>
       <c r="Q35" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R35" s="7"/>
     </row>
@@ -4251,7 +4285,7 @@
         <v>32</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>28</v>
@@ -4303,7 +4337,7 @@
         <v>33</v>
       </c>
       <c r="Q36" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="R36" s="7"/>
     </row>
@@ -4312,7 +4346,7 @@
         <v>33</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>28</v>
@@ -4364,7 +4398,7 @@
         <v>33</v>
       </c>
       <c r="Q37" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R37" s="7"/>
     </row>
@@ -4373,7 +4407,7 @@
         <v>34</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>28</v>
@@ -4425,7 +4459,7 @@
         <v>33</v>
       </c>
       <c r="Q38" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="R38" s="7"/>
     </row>
@@ -4434,7 +4468,7 @@
         <v>35</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>28</v>
@@ -4486,7 +4520,7 @@
         <v>33</v>
       </c>
       <c r="Q39" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="R39" s="7"/>
     </row>
@@ -4495,7 +4529,7 @@
         <v>36</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>28</v>
@@ -4547,7 +4581,7 @@
         <v>24</v>
       </c>
       <c r="Q40" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="R40" s="7" t="s">
         <v>26</v>
@@ -4558,7 +4592,7 @@
         <v>37</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>28</v>
@@ -4610,7 +4644,7 @@
         <v>33</v>
       </c>
       <c r="Q41" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="R41" s="7"/>
     </row>
@@ -4619,7 +4653,7 @@
         <v>38</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>28</v>
@@ -4671,7 +4705,7 @@
         <v>33</v>
       </c>
       <c r="Q42" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="R42" s="7"/>
     </row>
@@ -4680,7 +4714,7 @@
         <v>39</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>28</v>
@@ -4732,7 +4766,7 @@
         <v>24</v>
       </c>
       <c r="Q43" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R43" s="7" t="s">
         <v>26</v>
@@ -4743,10 +4777,10 @@
         <v>40</v>
       </c>
       <c r="B44" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C44" s="6" t="s">
         <v>110</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>111</v>
       </c>
       <c r="D44" s="6" t="n">
         <v>3</v>
@@ -4755,7 +4789,7 @@
         <v>79300</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G44" s="9" t="n">
         <v>79000</v>
@@ -4795,7 +4829,7 @@
         <v>33</v>
       </c>
       <c r="Q44" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="R44" s="7"/>
     </row>
@@ -4804,10 +4838,10 @@
         <v>41</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>3</v>
@@ -4816,7 +4850,7 @@
         <v>128700</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G45" s="9" t="n">
         <v>114345</v>
@@ -4856,7 +4890,7 @@
         <v>33</v>
       </c>
       <c r="Q45" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R45" s="7"/>
     </row>
@@ -4865,10 +4899,10 @@
         <v>42</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D46" s="6" t="n">
         <v>2</v>
@@ -4877,7 +4911,7 @@
         <v>106600</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G46" s="9" t="n">
         <v>143800</v>
@@ -4917,16 +4951,16 @@
         <v>33</v>
       </c>
       <c r="Q46" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="R46" s="7"/>
     </row>
-    <row r="47" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="n">
         <v>43</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>28</v>
@@ -4938,25 +4972,25 @@
         <v>1560</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>28</v>
+        <v>117</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>1300</v>
+        <v>5955</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>1600</v>
+        <v>5955</v>
       </c>
       <c r="I47" s="10" t="n">
         <f aca="false">IF(E47=0,0,(E47-H47)/E47)</f>
-        <v>-0.0256410256410256</v>
+        <v>-2.81730769230769</v>
       </c>
       <c r="J47" s="6" t="str">
         <f aca="false">IF(E47&lt;G47,"LOSS",IF(E47&lt;H47*1.1,"THIN / RISK",IF(E47&gt;H47*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>LOSS</v>
       </c>
       <c r="K47" s="8" t="n">
         <f aca="false">IF(J47="OVERPRICED?",ROUND(H47*1.35,-1),MAX(E47,ROUND(H47*(1+$E$3),-1)))</f>
-        <v>1840</v>
+        <v>6850</v>
       </c>
       <c r="L47" s="8" t="n">
         <f aca="false">D47*E47</f>
@@ -4964,25 +4998,23 @@
       </c>
       <c r="M47" s="8" t="n">
         <f aca="false">D47*K47</f>
-        <v>7360</v>
+        <v>27400</v>
       </c>
       <c r="N47" s="8" t="n">
         <f aca="false">D47*H47</f>
-        <v>6400</v>
+        <v>23820</v>
       </c>
       <c r="O47" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C47,F47)),"","YES")</f>
-        <v/>
+        <v>YES</v>
       </c>
       <c r="P47" s="6" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="Q47" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="R47" s="7" t="s">
-        <v>78</v>
-      </c>
+      <c r="R47" s="7"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="n">
@@ -5001,7 +5033,7 @@
         <v>1950</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="G48" s="9" t="n">
         <v>1750</v>
@@ -5041,7 +5073,7 @@
         <v>33</v>
       </c>
       <c r="Q48" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="R48" s="7"/>
     </row>
@@ -5050,7 +5082,7 @@
         <v>45</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>28</v>
@@ -5062,17 +5094,17 @@
         <v>2210</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>1750</v>
+        <v>1960</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>2000</v>
+        <v>1960</v>
       </c>
       <c r="I49" s="10" t="n">
         <f aca="false">IF(E49=0,0,(E49-H49)/E49)</f>
-        <v>0.0950226244343891</v>
+        <v>0.113122171945701</v>
       </c>
       <c r="J49" s="6" t="str">
         <f aca="false">IF(E49&lt;G49,"LOSS",IF(E49&lt;H49*1.1,"THIN / RISK",IF(E49&gt;H49*1.8,"OVERPRICED?","OK")))</f>
@@ -5080,7 +5112,7 @@
       </c>
       <c r="K49" s="8" t="n">
         <f aca="false">IF(J49="OVERPRICED?",ROUND(H49*1.35,-1),MAX(E49,ROUND(H49*(1+$E$3),-1)))</f>
-        <v>2300</v>
+        <v>2250</v>
       </c>
       <c r="L49" s="8" t="n">
         <f aca="false">D49*E49</f>
@@ -5088,32 +5120,30 @@
       </c>
       <c r="M49" s="8" t="n">
         <f aca="false">D49*K49</f>
-        <v>9200</v>
+        <v>9000</v>
       </c>
       <c r="N49" s="8" t="n">
         <f aca="false">D49*H49</f>
-        <v>8000</v>
+        <v>7840</v>
       </c>
       <c r="O49" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C49,F49)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P49" s="6" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="Q49" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="R49" s="7" t="s">
-        <v>124</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="R49" s="7"/>
     </row>
     <row r="50" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="n">
         <v>47</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>28</v>
@@ -5125,7 +5155,7 @@
         <v>13000</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="G50" s="9" t="n">
         <v>6255</v>
@@ -5165,7 +5195,7 @@
         <v>24</v>
       </c>
       <c r="Q50" s="7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="R50" s="7" t="s">
         <v>26</v>
@@ -5176,7 +5206,7 @@
         <v>48</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>28</v>
@@ -5228,7 +5258,7 @@
         <v>33</v>
       </c>
       <c r="Q51" s="7" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="R51" s="7"/>
     </row>
@@ -5237,7 +5267,7 @@
         <v>49</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>28</v>
@@ -5289,7 +5319,7 @@
         <v>24</v>
       </c>
       <c r="Q52" s="7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="R52" s="7" t="s">
         <v>26</v>
@@ -5300,7 +5330,7 @@
         <v>50</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>28</v>
@@ -5352,7 +5382,7 @@
         <v>24</v>
       </c>
       <c r="Q53" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="R53" s="7" t="s">
         <v>26</v>
@@ -5363,7 +5393,7 @@
         <v>51</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>28</v>
@@ -5415,7 +5445,7 @@
         <v>24</v>
       </c>
       <c r="Q54" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="R54" s="7" t="s">
         <v>26</v>
@@ -5426,7 +5456,7 @@
         <v>52</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>28</v>
@@ -5438,7 +5468,7 @@
         <v>18200</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="G55" s="9" t="n">
         <v>8500</v>
@@ -5478,7 +5508,7 @@
         <v>33</v>
       </c>
       <c r="Q55" s="7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="R55" s="7"/>
     </row>
@@ -5487,7 +5517,7 @@
         <v>53</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>28</v>
@@ -5499,7 +5529,7 @@
         <v>23400</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="G56" s="9" t="n">
         <v>19030</v>
@@ -5539,7 +5569,7 @@
         <v>33</v>
       </c>
       <c r="Q56" s="7" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="R56" s="7"/>
     </row>
@@ -5548,10 +5578,10 @@
         <v>54</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D57" s="6" t="n">
         <v>2</v>
@@ -5560,7 +5590,7 @@
         <v>400946</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G57" s="9" t="n">
         <v>115000</v>
@@ -5600,16 +5630,16 @@
         <v>33</v>
       </c>
       <c r="Q57" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="R57" s="7"/>
     </row>
-    <row r="58" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="n">
         <v>55</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>28</v>
@@ -5621,25 +5651,25 @@
         <v>15600</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>142</v>
+        <v>39</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>12000</v>
+        <v>67000</v>
       </c>
       <c r="H58" s="9" t="n">
-        <v>18000</v>
+        <v>67000</v>
       </c>
       <c r="I58" s="10" t="n">
         <f aca="false">IF(E58=0,0,(E58-H58)/E58)</f>
-        <v>-0.153846153846154</v>
+        <v>-3.29487179487179</v>
       </c>
       <c r="J58" s="6" t="str">
         <f aca="false">IF(E58&lt;G58,"LOSS",IF(E58&lt;H58*1.1,"THIN / RISK",IF(E58&gt;H58*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>LOSS</v>
       </c>
       <c r="K58" s="8" t="n">
         <f aca="false">IF(J58="OVERPRICED?",ROUND(H58*1.35,-1),MAX(E58,ROUND(H58*(1+$E$3),-1)))</f>
-        <v>20700</v>
+        <v>77050</v>
       </c>
       <c r="L58" s="8" t="n">
         <f aca="false">D58*E58</f>
@@ -5647,32 +5677,32 @@
       </c>
       <c r="M58" s="8" t="n">
         <f aca="false">D58*K58</f>
-        <v>41400</v>
+        <v>154100</v>
       </c>
       <c r="N58" s="8" t="n">
         <f aca="false">D58*H58</f>
-        <v>36000</v>
+        <v>134000</v>
       </c>
       <c r="O58" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C58,F58)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="Q58" s="7" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="R58" s="7" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="n">
         <v>56</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>28</v>
@@ -5684,25 +5714,25 @@
         <v>10400</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>10000</v>
+        <v>20921</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>13000</v>
+        <v>20921</v>
       </c>
       <c r="I59" s="10" t="n">
         <f aca="false">IF(E59=0,0,(E59-H59)/E59)</f>
-        <v>-0.25</v>
+        <v>-1.01163461538462</v>
       </c>
       <c r="J59" s="6" t="str">
         <f aca="false">IF(E59&lt;G59,"LOSS",IF(E59&lt;H59*1.1,"THIN / RISK",IF(E59&gt;H59*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>LOSS</v>
       </c>
       <c r="K59" s="8" t="n">
         <f aca="false">IF(J59="OVERPRICED?",ROUND(H59*1.35,-1),MAX(E59,ROUND(H59*(1+$E$3),-1)))</f>
-        <v>14950</v>
+        <v>24060</v>
       </c>
       <c r="L59" s="8" t="n">
         <f aca="false">D59*E59</f>
@@ -5710,24 +5740,24 @@
       </c>
       <c r="M59" s="8" t="n">
         <f aca="false">D59*K59</f>
-        <v>14950</v>
+        <v>24060</v>
       </c>
       <c r="N59" s="8" t="n">
         <f aca="false">D59*H59</f>
-        <v>13000</v>
+        <v>20921</v>
       </c>
       <c r="O59" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C59,F59)),"","YES")</f>
-        <v/>
+        <v>YES</v>
       </c>
       <c r="P59" s="6" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="Q59" s="7" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="R59" s="7" t="s">
-        <v>147</v>
+        <v>26</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5735,7 +5765,7 @@
         <v>57</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>28</v>
@@ -5787,16 +5817,16 @@
         <v>33</v>
       </c>
       <c r="Q60" s="7" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="R60" s="7"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="6" t="n">
         <v>58</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>28</v>
@@ -5808,17 +5838,17 @@
         <v>715</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>800</v>
+        <v>4583</v>
       </c>
       <c r="H61" s="9" t="n">
-        <v>1200</v>
+        <v>4583</v>
       </c>
       <c r="I61" s="10" t="n">
         <f aca="false">IF(E61=0,0,(E61-H61)/E61)</f>
-        <v>-0.678321678321678</v>
+        <v>-5.40979020979021</v>
       </c>
       <c r="J61" s="6" t="str">
         <f aca="false">IF(E61&lt;G61,"LOSS",IF(E61&lt;H61*1.1,"THIN / RISK",IF(E61&gt;H61*1.8,"OVERPRICED?","OK")))</f>
@@ -5826,7 +5856,7 @@
       </c>
       <c r="K61" s="8" t="n">
         <f aca="false">IF(J61="OVERPRICED?",ROUND(H61*1.35,-1),MAX(E61,ROUND(H61*(1+$E$3),-1)))</f>
-        <v>1380</v>
+        <v>5270</v>
       </c>
       <c r="L61" s="8" t="n">
         <f aca="false">D61*E61</f>
@@ -5834,32 +5864,32 @@
       </c>
       <c r="M61" s="8" t="n">
         <f aca="false">D61*K61</f>
-        <v>16560</v>
+        <v>63240</v>
       </c>
       <c r="N61" s="8" t="n">
         <f aca="false">D61*H61</f>
-        <v>14400</v>
+        <v>54996</v>
       </c>
       <c r="O61" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C61,F61)),"","YES")</f>
-        <v/>
+        <v>YES</v>
       </c>
       <c r="P61" s="6" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="Q61" s="7" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="R61" s="7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="6" t="n">
         <v>59</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>28</v>
@@ -5871,25 +5901,25 @@
         <v>1950</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>1200</v>
+        <v>4294</v>
       </c>
       <c r="H62" s="9" t="n">
-        <v>1800</v>
+        <v>4294</v>
       </c>
       <c r="I62" s="10" t="n">
         <f aca="false">IF(E62=0,0,(E62-H62)/E62)</f>
-        <v>0.0769230769230769</v>
+        <v>-1.20205128205128</v>
       </c>
       <c r="J62" s="6" t="str">
         <f aca="false">IF(E62&lt;G62,"LOSS",IF(E62&lt;H62*1.1,"THIN / RISK",IF(E62&gt;H62*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>LOSS</v>
       </c>
       <c r="K62" s="8" t="n">
         <f aca="false">IF(J62="OVERPRICED?",ROUND(H62*1.35,-1),MAX(E62,ROUND(H62*(1+$E$3),-1)))</f>
-        <v>2070</v>
+        <v>4940</v>
       </c>
       <c r="L62" s="8" t="n">
         <f aca="false">D62*E62</f>
@@ -5897,32 +5927,30 @@
       </c>
       <c r="M62" s="8" t="n">
         <f aca="false">D62*K62</f>
-        <v>24840</v>
+        <v>59280</v>
       </c>
       <c r="N62" s="8" t="n">
         <f aca="false">D62*H62</f>
-        <v>21600</v>
+        <v>51528</v>
       </c>
       <c r="O62" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C62,F62)),"","YES")</f>
-        <v/>
+        <v>YES</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="Q62" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="R62" s="7" t="s">
-        <v>78</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="R62" s="7"/>
     </row>
     <row r="63" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="n">
         <v>60</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>28</v>
@@ -5974,7 +6002,7 @@
         <v>24</v>
       </c>
       <c r="Q63" s="7" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="R63" s="7" t="s">
         <v>26</v>
@@ -5985,7 +6013,7 @@
         <v>61</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>28</v>
@@ -5997,7 +6025,7 @@
         <v>5850</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G64" s="9" t="n">
         <v>5920</v>
@@ -6037,7 +6065,7 @@
         <v>33</v>
       </c>
       <c r="Q64" s="7" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="R64" s="7"/>
     </row>
@@ -6046,7 +6074,7 @@
         <v>62</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>28</v>
@@ -6058,7 +6086,7 @@
         <v>2600</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G65" s="9" t="n">
         <v>3499</v>
@@ -6098,7 +6126,7 @@
         <v>24</v>
       </c>
       <c r="Q65" s="7" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="R65" s="7" t="s">
         <v>26</v>
@@ -6109,7 +6137,7 @@
         <v>63</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>28</v>
@@ -6121,7 +6149,7 @@
         <v>5551</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G66" s="9" t="n">
         <v>4630</v>
@@ -6161,7 +6189,7 @@
         <v>33</v>
       </c>
       <c r="Q66" s="7" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="R66" s="7"/>
     </row>
@@ -6170,7 +6198,7 @@
         <v>64</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>28</v>
@@ -6182,7 +6210,7 @@
         <v>1560</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="G67" s="9" t="n">
         <v>1350</v>
@@ -6222,7 +6250,7 @@
         <v>33</v>
       </c>
       <c r="Q67" s="7" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="R67" s="7"/>
     </row>
@@ -6231,7 +6259,7 @@
         <v>65</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>28</v>
@@ -6243,7 +6271,7 @@
         <v>1560</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="G68" s="9" t="n">
         <v>1350</v>
@@ -6283,7 +6311,7 @@
         <v>33</v>
       </c>
       <c r="Q68" s="7" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="R68" s="7"/>
     </row>
@@ -6292,7 +6320,7 @@
         <v>66</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>28</v>
@@ -6344,7 +6372,7 @@
         <v>24</v>
       </c>
       <c r="Q69" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="R69" s="7" t="s">
         <v>26</v>
@@ -6355,7 +6383,7 @@
         <v>67</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>28</v>
@@ -6407,7 +6435,7 @@
         <v>33</v>
       </c>
       <c r="Q70" s="7" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="R70" s="7"/>
     </row>
@@ -6416,7 +6444,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>28</v>
@@ -6428,7 +6456,7 @@
         <v>23400</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G71" s="9" t="n">
         <v>16156</v>
@@ -6468,7 +6496,7 @@
         <v>33</v>
       </c>
       <c r="Q71" s="7" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="R71" s="7"/>
     </row>
@@ -6477,7 +6505,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>28</v>
@@ -6489,7 +6517,7 @@
         <v>32500</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G72" s="9" t="n">
         <v>11453</v>
@@ -6529,7 +6557,7 @@
         <v>33</v>
       </c>
       <c r="Q72" s="7" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="R72" s="7"/>
     </row>
@@ -6538,7 +6566,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>28</v>
@@ -6590,7 +6618,7 @@
         <v>33</v>
       </c>
       <c r="Q73" s="7" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="R73" s="7"/>
     </row>
@@ -6599,7 +6627,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>28</v>
@@ -6611,7 +6639,7 @@
         <v>45500</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G74" s="9" t="n">
         <v>22185</v>
@@ -6651,18 +6679,18 @@
         <v>24</v>
       </c>
       <c r="Q74" s="7" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="R74" s="7" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="6" t="n">
         <v>74</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>28</v>
@@ -6674,17 +6702,17 @@
         <v>23400</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>178</v>
+        <v>36</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>45000</v>
+        <v>70685</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>70000</v>
+        <v>70685</v>
       </c>
       <c r="I75" s="10" t="n">
         <f aca="false">IF(E75=0,0,(E75-H75)/E75)</f>
-        <v>-1.99145299145299</v>
+        <v>-2.0207264957265</v>
       </c>
       <c r="J75" s="6" t="str">
         <f aca="false">IF(E75&lt;G75,"LOSS",IF(E75&lt;H75*1.1,"THIN / RISK",IF(E75&gt;H75*1.8,"OVERPRICED?","OK")))</f>
@@ -6692,7 +6720,7 @@
       </c>
       <c r="K75" s="8" t="n">
         <f aca="false">IF(J75="OVERPRICED?",ROUND(H75*1.35,-1),MAX(E75,ROUND(H75*(1+$E$3),-1)))</f>
-        <v>80500</v>
+        <v>81290</v>
       </c>
       <c r="L75" s="8" t="n">
         <f aca="false">D75*E75</f>
@@ -6700,32 +6728,30 @@
       </c>
       <c r="M75" s="8" t="n">
         <f aca="false">D75*K75</f>
-        <v>161000</v>
+        <v>162580</v>
       </c>
       <c r="N75" s="8" t="n">
         <f aca="false">D75*H75</f>
-        <v>140000</v>
+        <v>141370</v>
       </c>
       <c r="O75" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C75,F75)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P75" s="6" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="Q75" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="R75" s="7" t="s">
-        <v>180</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="R75" s="7"/>
     </row>
     <row r="76" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="6" t="n">
         <v>75</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>28</v>
@@ -6737,7 +6763,7 @@
         <v>1950</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="G76" s="9" t="n">
         <v>7020</v>
@@ -6777,7 +6803,7 @@
         <v>33</v>
       </c>
       <c r="Q76" s="7" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="R76" s="7"/>
     </row>
@@ -6786,7 +6812,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>28</v>
@@ -6798,7 +6824,7 @@
         <v>2080</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="G77" s="9" t="n">
         <v>9630</v>
@@ -6838,7 +6864,7 @@
         <v>33</v>
       </c>
       <c r="Q77" s="7" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="R77" s="7"/>
     </row>
@@ -6847,7 +6873,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>28</v>
@@ -6859,7 +6885,7 @@
         <v>2210</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="G78" s="9" t="n">
         <v>9630</v>
@@ -6899,7 +6925,7 @@
         <v>24</v>
       </c>
       <c r="Q78" s="7" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="R78" s="7" t="s">
         <v>26</v>
@@ -6910,7 +6936,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>28</v>
@@ -6922,7 +6948,7 @@
         <v>2340</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="G79" s="9" t="n">
         <v>7920</v>
@@ -6962,7 +6988,7 @@
         <v>33</v>
       </c>
       <c r="Q79" s="7" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="R79" s="7"/>
     </row>
@@ -6971,7 +6997,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>28</v>
@@ -6983,7 +7009,7 @@
         <v>2470</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="G80" s="9" t="n">
         <v>11250</v>
@@ -7023,7 +7049,7 @@
         <v>24</v>
       </c>
       <c r="Q80" s="7" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="R80" s="7" t="s">
         <v>26</v>
@@ -7034,7 +7060,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>28</v>
@@ -7046,7 +7072,7 @@
         <v>2600</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="G81" s="9" t="n">
         <v>12600</v>
@@ -7086,7 +7112,7 @@
         <v>33</v>
       </c>
       <c r="Q81" s="7" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="R81" s="7"/>
     </row>
@@ -7095,7 +7121,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>28</v>
@@ -7107,7 +7133,7 @@
         <v>2730</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="G82" s="9" t="n">
         <v>11250</v>
@@ -7147,7 +7173,7 @@
         <v>33</v>
       </c>
       <c r="Q82" s="7" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="R82" s="7"/>
     </row>
@@ -7156,7 +7182,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>28</v>
@@ -7168,7 +7194,7 @@
         <v>3250</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="G83" s="9" t="n">
         <v>12240</v>
@@ -7208,7 +7234,7 @@
         <v>33</v>
       </c>
       <c r="Q83" s="7" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="R83" s="7"/>
     </row>
@@ -7217,7 +7243,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>28</v>
@@ -7229,7 +7255,7 @@
         <v>4160</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="G84" s="9" t="n">
         <v>13500</v>
@@ -7269,7 +7295,7 @@
         <v>24</v>
       </c>
       <c r="Q84" s="7" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="R84" s="7" t="s">
         <v>26</v>
@@ -7280,7 +7306,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>28</v>
@@ -7292,7 +7318,7 @@
         <v>5850</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="G85" s="9" t="n">
         <v>20250</v>
@@ -7332,7 +7358,7 @@
         <v>33</v>
       </c>
       <c r="Q85" s="7" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="R85" s="7"/>
     </row>
@@ -7341,7 +7367,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>28</v>
@@ -7353,7 +7379,7 @@
         <v>8450</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="G86" s="9" t="n">
         <v>39640</v>
@@ -7393,7 +7419,7 @@
         <v>24</v>
       </c>
       <c r="Q86" s="7" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="R86" s="7" t="s">
         <v>26</v>
@@ -7404,7 +7430,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>28</v>
@@ -7416,7 +7442,7 @@
         <v>9750</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="G87" s="9" t="n">
         <v>39640</v>
@@ -7456,7 +7482,7 @@
         <v>33</v>
       </c>
       <c r="Q87" s="7" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="R87" s="7"/>
     </row>
@@ -7465,7 +7491,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>28</v>
@@ -7477,7 +7503,7 @@
         <v>11700</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="G88" s="9" t="n">
         <v>40500</v>
@@ -7517,7 +7543,7 @@
         <v>24</v>
       </c>
       <c r="Q88" s="7" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="R88" s="7" t="s">
         <v>26</v>
@@ -7528,7 +7554,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>28</v>
@@ -7580,7 +7606,7 @@
         <v>24</v>
       </c>
       <c r="Q89" s="7" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="R89" s="7" t="s">
         <v>26</v>
@@ -7591,7 +7617,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>28</v>
@@ -7643,7 +7669,7 @@
         <v>24</v>
       </c>
       <c r="Q90" s="7" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="R90" s="7" t="s">
         <v>26</v>
@@ -7654,7 +7680,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>28</v>
@@ -7706,7 +7732,7 @@
         <v>24</v>
       </c>
       <c r="Q91" s="7" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="R91" s="7" t="s">
         <v>26</v>
@@ -7717,7 +7743,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>28</v>
@@ -7769,7 +7795,7 @@
         <v>24</v>
       </c>
       <c r="Q92" s="7" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="R92" s="7" t="s">
         <v>26</v>
@@ -7780,7 +7806,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>28</v>
@@ -7832,7 +7858,7 @@
         <v>33</v>
       </c>
       <c r="Q93" s="7" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="R93" s="7"/>
     </row>
@@ -7841,10 +7867,10 @@
         <v>93</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D94" s="6" t="n">
         <v>2</v>
@@ -7853,7 +7879,7 @@
         <v>25350</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G94" s="9" t="n">
         <v>18100</v>
@@ -7893,7 +7919,7 @@
         <v>33</v>
       </c>
       <c r="Q94" s="7" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="R94" s="7"/>
     </row>
@@ -7902,10 +7928,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D95" s="6" t="n">
         <v>3</v>
@@ -7914,7 +7940,7 @@
         <v>8138</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G95" s="9" t="n">
         <v>15800</v>
@@ -7954,7 +7980,7 @@
         <v>33</v>
       </c>
       <c r="Q95" s="7" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="R95" s="7"/>
     </row>
@@ -7963,10 +7989,10 @@
         <v>95</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D96" s="6" t="n">
         <v>3</v>
@@ -7975,7 +8001,7 @@
         <v>6370</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G96" s="9" t="n">
         <v>7928</v>
@@ -8015,7 +8041,7 @@
         <v>33</v>
       </c>
       <c r="Q96" s="7" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="R96" s="7"/>
     </row>
@@ -8024,7 +8050,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>28</v>
@@ -8036,7 +8062,7 @@
         <v>14950</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G97" s="9" t="n">
         <v>27919</v>
@@ -8076,7 +8102,7 @@
         <v>24</v>
       </c>
       <c r="Q97" s="7" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="R97" s="7" t="s">
         <v>26</v>
@@ -8087,10 +8113,10 @@
         <v>97</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D98" s="6" t="n">
         <v>2</v>
@@ -8099,7 +8125,7 @@
         <v>286000</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G98" s="9" t="n">
         <v>199500</v>
@@ -8139,18 +8165,18 @@
         <v>24</v>
       </c>
       <c r="Q98" s="7" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="R98" s="7" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="6" t="n">
         <v>98</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>36</v>
@@ -8165,22 +8191,22 @@
         <v>36</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>12000</v>
+        <v>40172</v>
       </c>
       <c r="H99" s="9" t="n">
-        <v>16000</v>
+        <v>40172</v>
       </c>
       <c r="I99" s="10" t="n">
         <f aca="false">IF(E99=0,0,(E99-H99)/E99)</f>
-        <v>-0.0256410256410256</v>
+        <v>-1.57512820512821</v>
       </c>
       <c r="J99" s="6" t="str">
         <f aca="false">IF(E99&lt;G99,"LOSS",IF(E99&lt;H99*1.1,"THIN / RISK",IF(E99&gt;H99*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>LOSS</v>
       </c>
       <c r="K99" s="8" t="n">
         <f aca="false">IF(J99="OVERPRICED?",ROUND(H99*1.35,-1),MAX(E99,ROUND(H99*(1+$E$3),-1)))</f>
-        <v>18400</v>
+        <v>46200</v>
       </c>
       <c r="L99" s="8" t="n">
         <f aca="false">D99*E99</f>
@@ -8188,32 +8214,32 @@
       </c>
       <c r="M99" s="8" t="n">
         <f aca="false">D99*K99</f>
-        <v>18400</v>
+        <v>46200</v>
       </c>
       <c r="N99" s="8" t="n">
         <f aca="false">D99*H99</f>
-        <v>16000</v>
+        <v>40172</v>
       </c>
       <c r="O99" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C99,F99)),"","YES")</f>
         <v/>
       </c>
       <c r="P99" s="6" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="Q99" s="7" t="s">
-        <v>143</v>
+        <v>222</v>
       </c>
       <c r="R99" s="7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="6" t="n">
         <v>99</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>28</v>
@@ -8225,25 +8251,25 @@
         <v>11050</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>228</v>
+        <v>36</v>
       </c>
       <c r="G100" s="9" t="n">
-        <v>8000</v>
+        <v>40172</v>
       </c>
       <c r="H100" s="9" t="n">
-        <v>11000</v>
+        <v>40172</v>
       </c>
       <c r="I100" s="10" t="n">
         <f aca="false">IF(E100=0,0,(E100-H100)/E100)</f>
-        <v>0.00452488687782806</v>
+        <v>-2.63547511312217</v>
       </c>
       <c r="J100" s="6" t="str">
         <f aca="false">IF(E100&lt;G100,"LOSS",IF(E100&lt;H100*1.1,"THIN / RISK",IF(E100&gt;H100*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>LOSS</v>
       </c>
       <c r="K100" s="8" t="n">
         <f aca="false">IF(J100="OVERPRICED?",ROUND(H100*1.35,-1),MAX(E100,ROUND(H100*(1+$E$3),-1)))</f>
-        <v>12650</v>
+        <v>46200</v>
       </c>
       <c r="L100" s="8" t="n">
         <f aca="false">D100*E100</f>
@@ -8251,32 +8277,30 @@
       </c>
       <c r="M100" s="8" t="n">
         <f aca="false">D100*K100</f>
-        <v>12650</v>
+        <v>46200</v>
       </c>
       <c r="N100" s="8" t="n">
         <f aca="false">D100*H100</f>
-        <v>11000</v>
+        <v>40172</v>
       </c>
       <c r="O100" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C100,F100)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="Q100" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="R100" s="7" t="s">
-        <v>78</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="R100" s="7"/>
     </row>
     <row r="101" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="6" t="n">
         <v>100</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>28</v>
@@ -8328,7 +8352,7 @@
         <v>24</v>
       </c>
       <c r="Q101" s="7" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="R101" s="7" t="s">
         <v>26</v>
@@ -8339,7 +8363,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>28</v>
@@ -8391,7 +8415,7 @@
         <v>33</v>
       </c>
       <c r="Q102" s="7" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="R102" s="7"/>
     </row>
@@ -8400,7 +8424,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>28</v>
@@ -8452,7 +8476,7 @@
         <v>33</v>
       </c>
       <c r="Q103" s="7" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="R103" s="7"/>
     </row>
@@ -8461,7 +8485,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>22</v>
@@ -8513,7 +8537,7 @@
         <v>33</v>
       </c>
       <c r="Q104" s="7" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="R104" s="7"/>
     </row>
@@ -8522,7 +8546,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>22</v>
@@ -8574,7 +8598,7 @@
         <v>24</v>
       </c>
       <c r="Q105" s="7" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="R105" s="7" t="s">
         <v>26</v>
@@ -8585,7 +8609,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>22</v>
@@ -8597,7 +8621,7 @@
         <v>1170</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G106" s="9" t="n">
         <v>800</v>
@@ -8637,7 +8661,7 @@
         <v>33</v>
       </c>
       <c r="Q106" s="7" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="R106" s="7"/>
     </row>
@@ -8646,7 +8670,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>28</v>
@@ -8698,16 +8722,16 @@
         <v>33</v>
       </c>
       <c r="Q107" s="7" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="R107" s="7"/>
     </row>
-    <row r="108" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="6" t="n">
         <v>107</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>28</v>
@@ -8719,17 +8743,17 @@
         <v>6760</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="G108" s="9" t="n">
-        <v>4500</v>
+        <v>5226</v>
       </c>
       <c r="H108" s="9" t="n">
-        <v>6000</v>
+        <v>5226</v>
       </c>
       <c r="I108" s="10" t="n">
         <f aca="false">IF(E108=0,0,(E108-H108)/E108)</f>
-        <v>0.112426035502959</v>
+        <v>0.226923076923077</v>
       </c>
       <c r="J108" s="6" t="str">
         <f aca="false">IF(E108&lt;G108,"LOSS",IF(E108&lt;H108*1.1,"THIN / RISK",IF(E108&gt;H108*1.8,"OVERPRICED?","OK")))</f>
@@ -8737,7 +8761,7 @@
       </c>
       <c r="K108" s="8" t="n">
         <f aca="false">IF(J108="OVERPRICED?",ROUND(H108*1.35,-1),MAX(E108,ROUND(H108*(1+$E$3),-1)))</f>
-        <v>6900</v>
+        <v>6760</v>
       </c>
       <c r="L108" s="8" t="n">
         <f aca="false">D108*E108</f>
@@ -8745,32 +8769,30 @@
       </c>
       <c r="M108" s="8" t="n">
         <f aca="false">D108*K108</f>
-        <v>41400</v>
+        <v>40560</v>
       </c>
       <c r="N108" s="8" t="n">
         <f aca="false">D108*H108</f>
-        <v>36000</v>
+        <v>31356</v>
       </c>
       <c r="O108" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C108,F108)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="Q108" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="R108" s="7" t="s">
-        <v>245</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="R108" s="7"/>
     </row>
     <row r="109" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="6" t="n">
         <v>108</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>28</v>
@@ -8822,7 +8844,7 @@
         <v>33</v>
       </c>
       <c r="Q109" s="7" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="R109" s="7"/>
     </row>
@@ -8831,7 +8853,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>28</v>
@@ -8843,25 +8865,25 @@
         <v>2340</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="G110" s="9" t="n">
-        <v>1800</v>
+        <v>3651</v>
       </c>
       <c r="H110" s="9" t="n">
-        <v>2500</v>
+        <v>3651</v>
       </c>
       <c r="I110" s="10" t="n">
         <f aca="false">IF(E110=0,0,(E110-H110)/E110)</f>
-        <v>-0.0683760683760684</v>
+        <v>-0.56025641025641</v>
       </c>
       <c r="J110" s="6" t="str">
         <f aca="false">IF(E110&lt;G110,"LOSS",IF(E110&lt;H110*1.1,"THIN / RISK",IF(E110&gt;H110*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>LOSS</v>
       </c>
       <c r="K110" s="8" t="n">
         <f aca="false">IF(J110="OVERPRICED?",ROUND(H110*1.35,-1),MAX(E110,ROUND(H110*(1+$E$3),-1)))</f>
-        <v>2880</v>
+        <v>4200</v>
       </c>
       <c r="L110" s="8" t="n">
         <f aca="false">D110*E110</f>
@@ -8869,32 +8891,30 @@
       </c>
       <c r="M110" s="8" t="n">
         <f aca="false">D110*K110</f>
-        <v>17280</v>
+        <v>25200</v>
       </c>
       <c r="N110" s="8" t="n">
         <f aca="false">D110*H110</f>
-        <v>15000</v>
+        <v>21906</v>
       </c>
       <c r="O110" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C110,F110)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="Q110" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="R110" s="7" t="s">
-        <v>249</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="R110" s="7"/>
     </row>
     <row r="111" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="6" t="n">
         <v>110</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>28</v>
@@ -8906,7 +8926,7 @@
         <v>1820</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G111" s="9" t="n">
         <v>15399</v>
@@ -8946,7 +8966,7 @@
         <v>33</v>
       </c>
       <c r="Q111" s="7" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="R111" s="7"/>
     </row>
@@ -8955,7 +8975,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>28</v>
@@ -9007,7 +9027,7 @@
         <v>24</v>
       </c>
       <c r="Q112" s="7" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="R112" s="7" t="s">
         <v>26</v>
@@ -9018,7 +9038,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>28</v>
@@ -9070,7 +9090,7 @@
         <v>33</v>
       </c>
       <c r="Q113" s="7" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="R113" s="7"/>
     </row>
@@ -9079,7 +9099,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>28</v>
@@ -9131,7 +9151,7 @@
         <v>33</v>
       </c>
       <c r="Q114" s="7" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="R114" s="7"/>
     </row>
@@ -9140,7 +9160,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>28</v>
@@ -9192,7 +9212,7 @@
         <v>33</v>
       </c>
       <c r="Q115" s="7" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="R115" s="7"/>
     </row>
@@ -9201,7 +9221,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>22</v>
@@ -9213,7 +9233,7 @@
         <v>11050</v>
       </c>
       <c r="F116" s="7" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="G116" s="9" t="n">
         <v>5000</v>
@@ -9253,7 +9273,7 @@
         <v>33</v>
       </c>
       <c r="Q116" s="7" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="R116" s="7"/>
     </row>
@@ -9262,7 +9282,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>28</v>
@@ -9314,7 +9334,7 @@
         <v>33</v>
       </c>
       <c r="Q117" s="7" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="R117" s="7"/>
     </row>
@@ -9323,7 +9343,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>22</v>
@@ -9375,7 +9395,7 @@
         <v>24</v>
       </c>
       <c r="Q118" s="7" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="R118" s="7" t="s">
         <v>26</v>
@@ -9386,7 +9406,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>22</v>
@@ -9438,18 +9458,18 @@
         <v>24</v>
       </c>
       <c r="Q119" s="7" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="R119" s="7" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="6" t="n">
         <v>119</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>28</v>
@@ -9461,25 +9481,25 @@
         <v>910</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>22</v>
+        <v>264</v>
       </c>
       <c r="G120" s="9" t="n">
-        <v>400</v>
+        <v>2243</v>
       </c>
       <c r="H120" s="9" t="n">
-        <v>700</v>
+        <v>2243</v>
       </c>
       <c r="I120" s="10" t="n">
         <f aca="false">IF(E120=0,0,(E120-H120)/E120)</f>
-        <v>0.230769230769231</v>
+        <v>-1.46483516483516</v>
       </c>
       <c r="J120" s="6" t="str">
         <f aca="false">IF(E120&lt;G120,"LOSS",IF(E120&lt;H120*1.1,"THIN / RISK",IF(E120&gt;H120*1.8,"OVERPRICED?","OK")))</f>
-        <v>OK</v>
+        <v>LOSS</v>
       </c>
       <c r="K120" s="8" t="n">
         <f aca="false">IF(J120="OVERPRICED?",ROUND(H120*1.35,-1),MAX(E120,ROUND(H120*(1+$E$3),-1)))</f>
-        <v>910</v>
+        <v>2580</v>
       </c>
       <c r="L120" s="8" t="n">
         <f aca="false">D120*E120</f>
@@ -9487,32 +9507,30 @@
       </c>
       <c r="M120" s="8" t="n">
         <f aca="false">D120*K120</f>
-        <v>1820</v>
+        <v>5160</v>
       </c>
       <c r="N120" s="8" t="n">
         <f aca="false">D120*H120</f>
-        <v>1400</v>
+        <v>4486</v>
       </c>
       <c r="O120" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C120,F120)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="Q120" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="R120" s="7" t="s">
-        <v>78</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="R120" s="7"/>
     </row>
     <row r="121" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="6" t="n">
         <v>120</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>22</v>
@@ -9564,7 +9582,7 @@
         <v>33</v>
       </c>
       <c r="Q121" s="7" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="R121" s="7"/>
     </row>
@@ -9573,7 +9591,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>22</v>
@@ -9625,7 +9643,7 @@
         <v>33</v>
       </c>
       <c r="Q122" s="7" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="R122" s="7"/>
     </row>
@@ -9634,7 +9652,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>22</v>
@@ -9646,7 +9664,7 @@
         <v>357500</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G123" s="9" t="n">
         <v>126000</v>
@@ -9686,7 +9704,7 @@
         <v>24</v>
       </c>
       <c r="Q123" s="7" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="R123" s="7" t="s">
         <v>26</v>
@@ -9697,7 +9715,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C124" s="6" t="s">
         <v>22</v>
@@ -9749,18 +9767,18 @@
         <v>24</v>
       </c>
       <c r="Q124" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="R124" s="7" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="6" t="n">
         <v>124</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>22</v>
@@ -9772,25 +9790,25 @@
         <v>4550</v>
       </c>
       <c r="F125" s="7" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>2500</v>
+        <v>6941</v>
       </c>
       <c r="H125" s="9" t="n">
-        <v>3500</v>
+        <v>6941</v>
       </c>
       <c r="I125" s="10" t="n">
         <f aca="false">IF(E125=0,0,(E125-H125)/E125)</f>
-        <v>0.230769230769231</v>
+        <v>-0.525494505494506</v>
       </c>
       <c r="J125" s="6" t="str">
         <f aca="false">IF(E125&lt;G125,"LOSS",IF(E125&lt;H125*1.1,"THIN / RISK",IF(E125&gt;H125*1.8,"OVERPRICED?","OK")))</f>
-        <v>OK</v>
+        <v>LOSS</v>
       </c>
       <c r="K125" s="8" t="n">
         <f aca="false">IF(J125="OVERPRICED?",ROUND(H125*1.35,-1),MAX(E125,ROUND(H125*(1+$E$3),-1)))</f>
-        <v>4550</v>
+        <v>7980</v>
       </c>
       <c r="L125" s="8" t="n">
         <f aca="false">D125*E125</f>
@@ -9798,32 +9816,30 @@
       </c>
       <c r="M125" s="8" t="n">
         <f aca="false">D125*K125</f>
-        <v>9100</v>
+        <v>15960</v>
       </c>
       <c r="N125" s="8" t="n">
         <f aca="false">D125*H125</f>
-        <v>7000</v>
+        <v>13882</v>
       </c>
       <c r="O125" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C125,F125)),"","YES")</f>
-        <v/>
+        <v>YES</v>
       </c>
       <c r="P125" s="6" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="Q125" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="R125" s="7" t="s">
-        <v>78</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="R125" s="7"/>
     </row>
     <row r="126" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="6" t="n">
         <v>125</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>22</v>
@@ -9875,7 +9891,7 @@
         <v>33</v>
       </c>
       <c r="Q126" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="R126" s="7"/>
     </row>
@@ -9884,7 +9900,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>22</v>
@@ -9936,7 +9952,7 @@
         <v>33</v>
       </c>
       <c r="Q127" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="R127" s="7"/>
     </row>
@@ -9945,7 +9961,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>22</v>
@@ -9997,7 +10013,7 @@
         <v>33</v>
       </c>
       <c r="Q128" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="R128" s="7"/>
     </row>
@@ -10006,7 +10022,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>22</v>
@@ -10058,7 +10074,7 @@
         <v>24</v>
       </c>
       <c r="Q129" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="R129" s="7" t="s">
         <v>26</v>
@@ -10069,7 +10085,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>22</v>
@@ -10121,7 +10137,7 @@
         <v>24</v>
       </c>
       <c r="Q130" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="R130" s="7" t="s">
         <v>26</v>
@@ -10132,7 +10148,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>22</v>
@@ -10184,7 +10200,7 @@
         <v>33</v>
       </c>
       <c r="Q131" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="R131" s="7"/>
     </row>
@@ -10193,7 +10209,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>22</v>
@@ -10205,7 +10221,7 @@
         <v>7800</v>
       </c>
       <c r="F132" s="7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G132" s="9" t="n">
         <v>5000</v>
@@ -10245,7 +10261,7 @@
         <v>33</v>
       </c>
       <c r="Q132" s="7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="R132" s="7"/>
     </row>
@@ -10254,7 +10270,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="7" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>22</v>
@@ -10306,7 +10322,7 @@
         <v>24</v>
       </c>
       <c r="Q133" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="R133" s="7" t="s">
         <v>26</v>
@@ -10317,7 +10333,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>28</v>
@@ -10369,7 +10385,7 @@
         <v>33</v>
       </c>
       <c r="Q134" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="R134" s="7"/>
     </row>
@@ -10378,7 +10394,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>22</v>
@@ -10430,7 +10446,7 @@
         <v>33</v>
       </c>
       <c r="Q135" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="R135" s="7"/>
     </row>
@@ -10439,7 +10455,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C136" s="6" t="s">
         <v>22</v>
@@ -10491,7 +10507,7 @@
         <v>33</v>
       </c>
       <c r="Q136" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="R136" s="7"/>
     </row>
@@ -10500,7 +10516,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C137" s="6" t="s">
         <v>22</v>
@@ -10552,7 +10568,7 @@
         <v>33</v>
       </c>
       <c r="Q137" s="7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="R137" s="7"/>
     </row>
@@ -10561,7 +10577,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C138" s="6" t="s">
         <v>22</v>
@@ -10613,16 +10629,16 @@
         <v>33</v>
       </c>
       <c r="Q138" s="7" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="R138" s="7"/>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="6" t="n">
         <v>139</v>
       </c>
       <c r="B139" s="7" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C139" s="6" t="s">
         <v>28</v>
@@ -10634,25 +10650,25 @@
         <v>715</v>
       </c>
       <c r="F139" s="7" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v>350</v>
+        <v>812</v>
       </c>
       <c r="H139" s="9" t="n">
-        <v>600</v>
+        <v>812</v>
       </c>
       <c r="I139" s="10" t="n">
         <f aca="false">IF(E139=0,0,(E139-H139)/E139)</f>
-        <v>0.160839160839161</v>
+        <v>-0.135664335664336</v>
       </c>
       <c r="J139" s="6" t="str">
         <f aca="false">IF(E139&lt;G139,"LOSS",IF(E139&lt;H139*1.1,"THIN / RISK",IF(E139&gt;H139*1.8,"OVERPRICED?","OK")))</f>
-        <v>OK</v>
+        <v>LOSS</v>
       </c>
       <c r="K139" s="8" t="n">
         <f aca="false">IF(J139="OVERPRICED?",ROUND(H139*1.35,-1),MAX(E139,ROUND(H139*(1+$E$3),-1)))</f>
-        <v>715</v>
+        <v>930</v>
       </c>
       <c r="L139" s="8" t="n">
         <f aca="false">D139*E139</f>
@@ -10660,25 +10676,23 @@
       </c>
       <c r="M139" s="8" t="n">
         <f aca="false">D139*K139</f>
-        <v>17160</v>
+        <v>22320</v>
       </c>
       <c r="N139" s="8" t="n">
         <f aca="false">D139*H139</f>
-        <v>14400</v>
+        <v>19488</v>
       </c>
       <c r="O139" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C139,F139)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P139" s="6" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="Q139" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="R139" s="7" t="s">
-        <v>78</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="R139" s="7"/>
     </row>
     <row r="140" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="6" t="n">
@@ -10930,7 +10944,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="6" t="n">
         <v>145</v>
       </c>
@@ -10947,25 +10961,25 @@
         <v>104</v>
       </c>
       <c r="F144" s="7" t="s">
-        <v>315</v>
+        <v>39</v>
       </c>
       <c r="G144" s="9" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="H144" s="9" t="n">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="I144" s="10" t="n">
         <f aca="false">IF(E144=0,0,(E144-H144)/E144)</f>
-        <v>0.230769230769231</v>
+        <v>0.865384615384615</v>
       </c>
       <c r="J144" s="6" t="str">
         <f aca="false">IF(E144&lt;G144,"LOSS",IF(E144&lt;H144*1.1,"THIN / RISK",IF(E144&gt;H144*1.8,"OVERPRICED?","OK")))</f>
-        <v>OK</v>
+        <v>OVERPRICED?</v>
       </c>
       <c r="K144" s="8" t="n">
         <f aca="false">IF(J144="OVERPRICED?",ROUND(H144*1.35,-1),MAX(E144,ROUND(H144*(1+$E$3),-1)))</f>
-        <v>104</v>
+        <v>20</v>
       </c>
       <c r="L144" s="8" t="n">
         <f aca="false">D144*E144</f>
@@ -10973,32 +10987,30 @@
       </c>
       <c r="M144" s="8" t="n">
         <f aca="false">D144*K144</f>
-        <v>52000</v>
+        <v>10000</v>
       </c>
       <c r="N144" s="8" t="n">
         <f aca="false">D144*H144</f>
-        <v>40000</v>
+        <v>7000</v>
       </c>
       <c r="O144" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C144,F144)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="Q144" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="R144" s="7" t="s">
-        <v>78</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="R144" s="7"/>
     </row>
     <row r="145" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="6" t="n">
         <v>146</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C145" s="6" t="s">
         <v>22</v>
@@ -11010,7 +11022,7 @@
         <v>105788</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G145" s="9" t="n">
         <v>82000</v>
@@ -11050,7 +11062,7 @@
         <v>33</v>
       </c>
       <c r="Q145" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="R145" s="7"/>
     </row>
@@ -11059,7 +11071,7 @@
         <v>147</v>
       </c>
       <c r="B146" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C146" s="6" t="s">
         <v>22</v>
@@ -11071,7 +11083,7 @@
         <v>245700</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G146" s="9" t="n">
         <v>225000</v>
@@ -11111,7 +11123,7 @@
         <v>33</v>
       </c>
       <c r="Q146" s="7" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="R146" s="7"/>
     </row>
@@ -11120,7 +11132,7 @@
         <v>148</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C147" s="6" t="s">
         <v>28</v>
@@ -11172,7 +11184,7 @@
         <v>33</v>
       </c>
       <c r="Q147" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="R147" s="7"/>
     </row>
@@ -11181,7 +11193,7 @@
         <v>149</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C148" s="6" t="s">
         <v>22</v>
@@ -11193,7 +11205,7 @@
         <v>1754</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G148" s="9" t="n">
         <v>1380</v>
@@ -11233,7 +11245,7 @@
         <v>33</v>
       </c>
       <c r="Q148" s="7" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="R148" s="7"/>
     </row>
@@ -11242,7 +11254,7 @@
         <v>150</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C149" s="6" t="s">
         <v>22</v>
@@ -11294,7 +11306,7 @@
         <v>33</v>
       </c>
       <c r="Q149" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="R149" s="7"/>
     </row>
@@ -11303,7 +11315,7 @@
         <v>151</v>
       </c>
       <c r="B150" s="7" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C150" s="6" t="s">
         <v>22</v>
@@ -11355,7 +11367,7 @@
         <v>33</v>
       </c>
       <c r="Q150" s="7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="R150" s="7"/>
     </row>
@@ -11364,7 +11376,7 @@
         <v>152</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C151" s="6" t="s">
         <v>22</v>
@@ -11416,7 +11428,7 @@
         <v>33</v>
       </c>
       <c r="Q151" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="R151" s="7"/>
     </row>
@@ -11425,7 +11437,7 @@
         <v>153</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C152" s="6" t="s">
         <v>22</v>
@@ -11477,7 +11489,7 @@
         <v>33</v>
       </c>
       <c r="Q152" s="7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="R152" s="7"/>
     </row>
@@ -11486,7 +11498,7 @@
         <v>154</v>
       </c>
       <c r="B153" s="7" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C153" s="6" t="s">
         <v>22</v>
@@ -11538,7 +11550,7 @@
         <v>24</v>
       </c>
       <c r="Q153" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="R153" s="7" t="s">
         <v>26</v>
@@ -11549,7 +11561,7 @@
         <v>155</v>
       </c>
       <c r="B154" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C154" s="6" t="s">
         <v>22</v>
@@ -11561,7 +11573,7 @@
         <v>748</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G154" s="9" t="n">
         <v>450</v>
@@ -11601,7 +11613,7 @@
         <v>33</v>
       </c>
       <c r="Q154" s="7" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="R154" s="7"/>
     </row>
@@ -11610,7 +11622,7 @@
         <v>156</v>
       </c>
       <c r="B155" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>22</v>
@@ -11622,7 +11634,7 @@
         <v>748</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="G155" s="9" t="n">
         <v>450</v>
@@ -11662,7 +11674,7 @@
         <v>33</v>
       </c>
       <c r="Q155" s="7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="R155" s="7"/>
     </row>
@@ -11671,7 +11683,7 @@
         <v>157</v>
       </c>
       <c r="B156" s="7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C156" s="6" t="s">
         <v>22</v>
@@ -11683,7 +11695,7 @@
         <v>748</v>
       </c>
       <c r="F156" s="7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G156" s="9" t="n">
         <v>400</v>
@@ -11723,7 +11735,7 @@
         <v>33</v>
       </c>
       <c r="Q156" s="7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="R156" s="7"/>
     </row>
@@ -11732,7 +11744,7 @@
         <v>158</v>
       </c>
       <c r="B157" s="7" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C157" s="6" t="s">
         <v>28</v>
@@ -11744,7 +11756,7 @@
         <v>311</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G157" s="9" t="n">
         <v>203</v>
@@ -11784,7 +11796,7 @@
         <v>33</v>
       </c>
       <c r="Q157" s="7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="R157" s="7"/>
     </row>
@@ -11793,7 +11805,7 @@
         <v>159</v>
       </c>
       <c r="B158" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C158" s="6" t="s">
         <v>28</v>
@@ -11805,7 +11817,7 @@
         <v>325</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G158" s="9" t="n">
         <v>160</v>
@@ -11845,7 +11857,7 @@
         <v>24</v>
       </c>
       <c r="Q158" s="7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="R158" s="7" t="s">
         <v>26</v>
@@ -11856,7 +11868,7 @@
         <v>160</v>
       </c>
       <c r="B159" s="7" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C159" s="6" t="s">
         <v>28</v>
@@ -11868,7 +11880,7 @@
         <v>117</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G159" s="9" t="n">
         <v>65</v>
@@ -11908,7 +11920,7 @@
         <v>24</v>
       </c>
       <c r="Q159" s="7" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="R159" s="7" t="s">
         <v>26</v>
@@ -11919,7 +11931,7 @@
         <v>161</v>
       </c>
       <c r="B160" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C160" s="6" t="s">
         <v>28</v>
@@ -11971,7 +11983,7 @@
         <v>24</v>
       </c>
       <c r="Q160" s="7" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="R160" s="7" t="s">
         <v>26</v>
@@ -11982,7 +11994,7 @@
         <v>162</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C161" s="6" t="s">
         <v>28</v>
@@ -12034,7 +12046,7 @@
         <v>24</v>
       </c>
       <c r="Q161" s="7" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="R161" s="7" t="s">
         <v>26</v>
@@ -12045,7 +12057,7 @@
         <v>164</v>
       </c>
       <c r="B162" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C162" s="6" t="s">
         <v>22</v>
@@ -12057,7 +12069,7 @@
         <v>1209</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G162" s="9" t="n">
         <v>1450</v>
@@ -12097,7 +12109,7 @@
         <v>24</v>
       </c>
       <c r="Q162" s="7" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="R162" s="7" t="s">
         <v>26</v>
@@ -12108,7 +12120,7 @@
         <v>165</v>
       </c>
       <c r="B163" s="7" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C163" s="6" t="s">
         <v>22</v>
@@ -12120,7 +12132,7 @@
         <v>1209</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G163" s="9" t="n">
         <v>2248</v>
@@ -12160,7 +12172,7 @@
         <v>24</v>
       </c>
       <c r="Q163" s="7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="R163" s="7" t="s">
         <v>26</v>
@@ -12171,7 +12183,7 @@
         <v>166</v>
       </c>
       <c r="B164" s="7" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C164" s="6" t="s">
         <v>22</v>
@@ -12183,7 +12195,7 @@
         <v>3022</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G164" s="9" t="n">
         <v>2325</v>
@@ -12223,7 +12235,7 @@
         <v>24</v>
       </c>
       <c r="Q164" s="7" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="R164" s="7" t="s">
         <v>26</v>
@@ -12234,7 +12246,7 @@
         <v>167</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C165" s="6" t="s">
         <v>22</v>
@@ -12246,7 +12258,7 @@
         <v>6240</v>
       </c>
       <c r="F165" s="7" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G165" s="9" t="n">
         <v>4400</v>
@@ -12286,7 +12298,7 @@
         <v>24</v>
       </c>
       <c r="Q165" s="7" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="R165" s="7" t="s">
         <v>26</v>
@@ -12297,7 +12309,7 @@
         <v>168</v>
       </c>
       <c r="B166" s="7" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C166" s="6" t="s">
         <v>22</v>
@@ -12309,7 +12321,7 @@
         <v>7150</v>
       </c>
       <c r="F166" s="7" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G166" s="9" t="n">
         <v>4400</v>
@@ -12349,7 +12361,7 @@
         <v>24</v>
       </c>
       <c r="Q166" s="7" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="R166" s="7" t="s">
         <v>26</v>
@@ -12360,7 +12372,7 @@
         <v>177</v>
       </c>
       <c r="B167" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C167" s="6" t="s">
         <v>28</v>
@@ -12412,18 +12424,18 @@
         <v>24</v>
       </c>
       <c r="Q167" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="R167" s="7" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="6" t="n">
         <v>179</v>
       </c>
       <c r="B168" s="7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C168" s="6" t="s">
         <v>28</v>
@@ -12435,25 +12447,25 @@
         <v>23400</v>
       </c>
       <c r="F168" s="7" t="s">
-        <v>228</v>
+        <v>36</v>
       </c>
       <c r="G168" s="9" t="n">
-        <v>20000</v>
+        <v>93911</v>
       </c>
       <c r="H168" s="9" t="n">
-        <v>26000</v>
+        <v>93911</v>
       </c>
       <c r="I168" s="10" t="n">
         <f aca="false">IF(E168=0,0,(E168-H168)/E168)</f>
-        <v>-0.111111111111111</v>
+        <v>-3.0132905982906</v>
       </c>
       <c r="J168" s="6" t="str">
         <f aca="false">IF(E168&lt;G168,"LOSS",IF(E168&lt;H168*1.1,"THIN / RISK",IF(E168&gt;H168*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>LOSS</v>
       </c>
       <c r="K168" s="8" t="n">
         <f aca="false">IF(J168="OVERPRICED?",ROUND(H168*1.35,-1),MAX(E168,ROUND(H168*(1+$E$3),-1)))</f>
-        <v>29900</v>
+        <v>108000</v>
       </c>
       <c r="L168" s="8" t="n">
         <f aca="false">D168*E168</f>
@@ -12461,27 +12473,27 @@
       </c>
       <c r="M168" s="8" t="n">
         <f aca="false">D168*K168</f>
-        <v>29900</v>
+        <v>108000</v>
       </c>
       <c r="N168" s="8" t="n">
         <f aca="false">D168*H168</f>
-        <v>26000</v>
+        <v>93911</v>
       </c>
       <c r="O168" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C168,F168)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="Q168" s="7" t="s">
-        <v>143</v>
+        <v>372</v>
       </c>
       <c r="R168" s="7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="6" t="n">
         <v>180</v>
       </c>
@@ -12498,25 +12510,25 @@
         <v>15600</v>
       </c>
       <c r="F169" s="7" t="s">
-        <v>228</v>
+        <v>36</v>
       </c>
       <c r="G169" s="9" t="n">
-        <v>14000</v>
+        <v>93911</v>
       </c>
       <c r="H169" s="9" t="n">
-        <v>18000</v>
+        <v>93911</v>
       </c>
       <c r="I169" s="10" t="n">
         <f aca="false">IF(E169=0,0,(E169-H169)/E169)</f>
-        <v>-0.153846153846154</v>
+        <v>-5.0199358974359</v>
       </c>
       <c r="J169" s="6" t="str">
         <f aca="false">IF(E169&lt;G169,"LOSS",IF(E169&lt;H169*1.1,"THIN / RISK",IF(E169&gt;H169*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>LOSS</v>
       </c>
       <c r="K169" s="8" t="n">
         <f aca="false">IF(J169="OVERPRICED?",ROUND(H169*1.35,-1),MAX(E169,ROUND(H169*(1+$E$3),-1)))</f>
-        <v>20700</v>
+        <v>108000</v>
       </c>
       <c r="L169" s="8" t="n">
         <f aca="false">D169*E169</f>
@@ -12524,32 +12536,30 @@
       </c>
       <c r="M169" s="8" t="n">
         <f aca="false">D169*K169</f>
-        <v>20700</v>
+        <v>108000</v>
       </c>
       <c r="N169" s="8" t="n">
         <f aca="false">D169*H169</f>
-        <v>18000</v>
+        <v>93911</v>
       </c>
       <c r="O169" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C169,F169)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P169" s="6" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="Q169" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="R169" s="7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>374</v>
+      </c>
+      <c r="R169" s="7"/>
+    </row>
+    <row r="170" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="6" t="n">
         <v>181</v>
       </c>
       <c r="B170" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C170" s="6" t="s">
         <v>28</v>
@@ -12561,25 +12571,25 @@
         <v>33800</v>
       </c>
       <c r="F170" s="7" t="s">
-        <v>228</v>
+        <v>36</v>
       </c>
       <c r="G170" s="9" t="n">
-        <v>28000</v>
+        <v>179788</v>
       </c>
       <c r="H170" s="9" t="n">
-        <v>36000</v>
+        <v>179788</v>
       </c>
       <c r="I170" s="10" t="n">
         <f aca="false">IF(E170=0,0,(E170-H170)/E170)</f>
-        <v>-0.0650887573964497</v>
+        <v>-4.31917159763314</v>
       </c>
       <c r="J170" s="6" t="str">
         <f aca="false">IF(E170&lt;G170,"LOSS",IF(E170&lt;H170*1.1,"THIN / RISK",IF(E170&gt;H170*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>LOSS</v>
       </c>
       <c r="K170" s="8" t="n">
         <f aca="false">IF(J170="OVERPRICED?",ROUND(H170*1.35,-1),MAX(E170,ROUND(H170*(1+$E$3),-1)))</f>
-        <v>41400</v>
+        <v>206760</v>
       </c>
       <c r="L170" s="8" t="n">
         <f aca="false">D170*E170</f>
@@ -12587,32 +12597,32 @@
       </c>
       <c r="M170" s="8" t="n">
         <f aca="false">D170*K170</f>
-        <v>41400</v>
+        <v>206760</v>
       </c>
       <c r="N170" s="8" t="n">
         <f aca="false">D170*H170</f>
-        <v>36000</v>
+        <v>179788</v>
       </c>
       <c r="O170" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C170,F170)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="Q170" s="7" t="s">
-        <v>143</v>
+        <v>376</v>
       </c>
       <c r="R170" s="7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="6" t="n">
         <v>182</v>
       </c>
       <c r="B171" s="7" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C171" s="6" t="s">
         <v>28</v>
@@ -12624,25 +12634,25 @@
         <v>23400</v>
       </c>
       <c r="F171" s="7" t="s">
-        <v>228</v>
+        <v>36</v>
       </c>
       <c r="G171" s="9" t="n">
-        <v>20000</v>
+        <v>179788</v>
       </c>
       <c r="H171" s="9" t="n">
-        <v>26000</v>
+        <v>179788</v>
       </c>
       <c r="I171" s="10" t="n">
         <f aca="false">IF(E171=0,0,(E171-H171)/E171)</f>
-        <v>-0.111111111111111</v>
+        <v>-6.68324786324786</v>
       </c>
       <c r="J171" s="6" t="str">
         <f aca="false">IF(E171&lt;G171,"LOSS",IF(E171&lt;H171*1.1,"THIN / RISK",IF(E171&gt;H171*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>LOSS</v>
       </c>
       <c r="K171" s="8" t="n">
         <f aca="false">IF(J171="OVERPRICED?",ROUND(H171*1.35,-1),MAX(E171,ROUND(H171*(1+$E$3),-1)))</f>
-        <v>29900</v>
+        <v>206760</v>
       </c>
       <c r="L171" s="8" t="n">
         <f aca="false">D171*E171</f>
@@ -12650,24 +12660,24 @@
       </c>
       <c r="M171" s="8" t="n">
         <f aca="false">D171*K171</f>
-        <v>29900</v>
+        <v>206760</v>
       </c>
       <c r="N171" s="8" t="n">
         <f aca="false">D171*H171</f>
-        <v>26000</v>
+        <v>179788</v>
       </c>
       <c r="O171" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C171,F171)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P171" s="6" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="Q171" s="7" t="s">
-        <v>143</v>
+        <v>378</v>
       </c>
       <c r="R171" s="7" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12675,7 +12685,7 @@
         <v>183</v>
       </c>
       <c r="B172" s="7" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C172" s="6" t="s">
         <v>28</v>
@@ -12727,16 +12737,16 @@
         <v>33</v>
       </c>
       <c r="Q172" s="7" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="R172" s="7"/>
     </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="6" t="n">
         <v>184</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C173" s="6" t="s">
         <v>28</v>
@@ -12748,17 +12758,17 @@
         <v>3250</v>
       </c>
       <c r="F173" s="7" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="G173" s="9" t="n">
-        <v>2100</v>
+        <v>2921</v>
       </c>
       <c r="H173" s="9" t="n">
-        <v>2900</v>
+        <v>2921</v>
       </c>
       <c r="I173" s="10" t="n">
         <f aca="false">IF(E173=0,0,(E173-H173)/E173)</f>
-        <v>0.107692307692308</v>
+        <v>0.101230769230769</v>
       </c>
       <c r="J173" s="6" t="str">
         <f aca="false">IF(E173&lt;G173,"LOSS",IF(E173&lt;H173*1.1,"THIN / RISK",IF(E173&gt;H173*1.8,"OVERPRICED?","OK")))</f>
@@ -12766,7 +12776,7 @@
       </c>
       <c r="K173" s="8" t="n">
         <f aca="false">IF(J173="OVERPRICED?",ROUND(H173*1.35,-1),MAX(E173,ROUND(H173*(1+$E$3),-1)))</f>
-        <v>3340</v>
+        <v>3360</v>
       </c>
       <c r="L173" s="8" t="n">
         <f aca="false">D173*E173</f>
@@ -12774,32 +12784,30 @@
       </c>
       <c r="M173" s="8" t="n">
         <f aca="false">D173*K173</f>
-        <v>10020</v>
+        <v>10080</v>
       </c>
       <c r="N173" s="8" t="n">
         <f aca="false">D173*H173</f>
-        <v>8700</v>
+        <v>8763</v>
       </c>
       <c r="O173" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C173,F173)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P173" s="6" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="Q173" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="R173" s="7" t="s">
-        <v>78</v>
-      </c>
+        <v>382</v>
+      </c>
+      <c r="R173" s="7"/>
     </row>
     <row r="174" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="6" t="n">
         <v>185</v>
       </c>
       <c r="B174" s="7" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C174" s="6" t="s">
         <v>28</v>
@@ -12851,7 +12859,7 @@
         <v>33</v>
       </c>
       <c r="Q174" s="7" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="R174" s="7"/>
     </row>
@@ -12860,7 +12868,7 @@
         <v>186</v>
       </c>
       <c r="B175" s="7" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C175" s="6" t="s">
         <v>28</v>
@@ -12872,7 +12880,7 @@
         <v>4550</v>
       </c>
       <c r="F175" s="7" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="G175" s="9" t="n">
         <v>7245</v>
@@ -12912,7 +12920,7 @@
         <v>33</v>
       </c>
       <c r="Q175" s="7" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="R175" s="7"/>
     </row>
@@ -12921,7 +12929,7 @@
         <v>187</v>
       </c>
       <c r="B176" s="7" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="C176" s="6" t="s">
         <v>28</v>
@@ -12933,7 +12941,7 @@
         <v>7150</v>
       </c>
       <c r="F176" s="7" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="G176" s="9" t="n">
         <v>9900</v>
@@ -12973,7 +12981,7 @@
         <v>33</v>
       </c>
       <c r="Q176" s="7" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="R176" s="7"/>
     </row>
@@ -12982,7 +12990,7 @@
         <v>188</v>
       </c>
       <c r="B177" s="7" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C177" s="6" t="s">
         <v>28</v>
@@ -13034,7 +13042,7 @@
         <v>24</v>
       </c>
       <c r="Q177" s="7" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="R177" s="7" t="s">
         <v>26</v>
@@ -13045,7 +13053,7 @@
         <v>189</v>
       </c>
       <c r="B178" s="7" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="C178" s="6" t="s">
         <v>28</v>
@@ -13057,7 +13065,7 @@
         <v>9750</v>
       </c>
       <c r="F178" s="7" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="G178" s="9" t="n">
         <v>10458</v>
@@ -13097,7 +13105,7 @@
         <v>33</v>
       </c>
       <c r="Q178" s="7" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="R178" s="7"/>
     </row>
@@ -13106,7 +13114,7 @@
         <v>190</v>
       </c>
       <c r="B179" s="7" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C179" s="6" t="s">
         <v>28</v>
@@ -13118,7 +13126,7 @@
         <v>2340</v>
       </c>
       <c r="F179" s="7" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="G179" s="9" t="n">
         <v>891</v>
@@ -13158,7 +13166,7 @@
         <v>33</v>
       </c>
       <c r="Q179" s="7" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="R179" s="7"/>
     </row>
@@ -13167,7 +13175,7 @@
         <v>191</v>
       </c>
       <c r="B180" s="7" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C180" s="6" t="s">
         <v>28</v>
@@ -13179,7 +13187,7 @@
         <v>3640</v>
       </c>
       <c r="F180" s="7" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="G180" s="9" t="n">
         <v>1440</v>
@@ -13219,7 +13227,7 @@
         <v>33</v>
       </c>
       <c r="Q180" s="7" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="R180" s="7"/>
     </row>
@@ -13228,7 +13236,7 @@
         <v>192</v>
       </c>
       <c r="B181" s="7" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="C181" s="6" t="s">
         <v>28</v>
@@ -13240,7 +13248,7 @@
         <v>1950</v>
       </c>
       <c r="F181" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G181" s="9" t="n">
         <v>7685</v>
@@ -13280,7 +13288,7 @@
         <v>33</v>
       </c>
       <c r="Q181" s="7" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="R181" s="7"/>
     </row>
@@ -13289,7 +13297,7 @@
         <v>193</v>
       </c>
       <c r="B182" s="7" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="C182" s="6" t="s">
         <v>28</v>
@@ -13301,7 +13309,7 @@
         <v>5850</v>
       </c>
       <c r="F182" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G182" s="9" t="n">
         <v>11948</v>
@@ -13341,7 +13349,7 @@
         <v>24</v>
       </c>
       <c r="Q182" s="7" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="R182" s="7" t="s">
         <v>26</v>
@@ -13352,7 +13360,7 @@
         <v>194</v>
       </c>
       <c r="B183" s="7" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="C183" s="6" t="s">
         <v>28</v>
@@ -13364,7 +13372,7 @@
         <v>1950</v>
       </c>
       <c r="F183" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G183" s="9" t="n">
         <v>7387</v>
@@ -13404,7 +13412,7 @@
         <v>33</v>
       </c>
       <c r="Q183" s="7" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="R183" s="7"/>
     </row>
@@ -13413,7 +13421,7 @@
         <v>195</v>
       </c>
       <c r="B184" s="7" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C184" s="6" t="s">
         <v>28</v>
@@ -13425,7 +13433,7 @@
         <v>5850</v>
       </c>
       <c r="F184" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G184" s="9" t="n">
         <v>12788</v>
@@ -13465,7 +13473,7 @@
         <v>24</v>
       </c>
       <c r="Q184" s="7" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="R184" s="7" t="s">
         <v>26</v>
@@ -13476,7 +13484,7 @@
         <v>196</v>
       </c>
       <c r="B185" s="7" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C185" s="6" t="s">
         <v>28</v>
@@ -13488,7 +13496,7 @@
         <v>4550</v>
       </c>
       <c r="F185" s="7" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="G185" s="9" t="n">
         <v>3006</v>
@@ -13528,7 +13536,7 @@
         <v>33</v>
       </c>
       <c r="Q185" s="7" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="R185" s="7"/>
     </row>
@@ -13537,7 +13545,7 @@
         <v>197</v>
       </c>
       <c r="B186" s="7" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="C186" s="6" t="s">
         <v>28</v>
@@ -13549,7 +13557,7 @@
         <v>17940</v>
       </c>
       <c r="F186" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G186" s="9" t="n">
         <v>5500</v>
@@ -13589,7 +13597,7 @@
         <v>33</v>
       </c>
       <c r="Q186" s="7" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="R186" s="7"/>
     </row>
@@ -13598,7 +13606,7 @@
         <v>198</v>
       </c>
       <c r="B187" s="7" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C187" s="6" t="s">
         <v>28</v>
@@ -13610,7 +13618,7 @@
         <v>18850</v>
       </c>
       <c r="F187" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G187" s="9" t="n">
         <v>5500</v>
@@ -13650,7 +13658,7 @@
         <v>33</v>
       </c>
       <c r="Q187" s="7" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="R187" s="7"/>
     </row>
@@ -13659,7 +13667,7 @@
         <v>199</v>
       </c>
       <c r="B188" s="7" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C188" s="6" t="s">
         <v>28</v>
@@ -13671,7 +13679,7 @@
         <v>19500</v>
       </c>
       <c r="F188" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G188" s="9" t="n">
         <v>6200</v>
@@ -13711,7 +13719,7 @@
         <v>33</v>
       </c>
       <c r="Q188" s="7" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="R188" s="7"/>
     </row>
@@ -13720,7 +13728,7 @@
         <v>200</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="C189" s="6" t="s">
         <v>28</v>
@@ -13732,7 +13740,7 @@
         <v>20800</v>
       </c>
       <c r="F189" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G189" s="9" t="n">
         <v>6875</v>
@@ -13772,7 +13780,7 @@
         <v>33</v>
       </c>
       <c r="Q189" s="7" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="R189" s="7"/>
     </row>
@@ -13781,7 +13789,7 @@
         <v>201</v>
       </c>
       <c r="B190" s="7" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="C190" s="6" t="s">
         <v>28</v>
@@ -13793,7 +13801,7 @@
         <v>22750</v>
       </c>
       <c r="F190" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G190" s="9" t="n">
         <v>8750</v>
@@ -13833,7 +13841,7 @@
         <v>33</v>
       </c>
       <c r="Q190" s="7" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="R190" s="7"/>
     </row>
@@ -13842,7 +13850,7 @@
         <v>202</v>
       </c>
       <c r="B191" s="7" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C191" s="6" t="s">
         <v>28</v>
@@ -13894,7 +13902,7 @@
         <v>24</v>
       </c>
       <c r="Q191" s="7" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="R191" s="7" t="s">
         <v>26</v>
@@ -13905,7 +13913,7 @@
         <v>204</v>
       </c>
       <c r="B192" s="7" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C192" s="6" t="s">
         <v>28</v>
@@ -13957,7 +13965,7 @@
         <v>33</v>
       </c>
       <c r="Q192" s="7" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="R192" s="7"/>
     </row>
@@ -13966,7 +13974,7 @@
         <v>205</v>
       </c>
       <c r="B193" s="7" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="C193" s="6" t="s">
         <v>28</v>
@@ -14018,7 +14026,7 @@
         <v>33</v>
       </c>
       <c r="Q193" s="7" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="R193" s="7"/>
     </row>
@@ -14027,7 +14035,7 @@
         <v>206</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="C194" s="6" t="s">
         <v>28</v>
@@ -14079,7 +14087,7 @@
         <v>33</v>
       </c>
       <c r="Q194" s="7" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="R194" s="7"/>
     </row>
@@ -14088,7 +14096,7 @@
         <v>207</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C195" s="6" t="s">
         <v>28</v>
@@ -14140,7 +14148,7 @@
         <v>33</v>
       </c>
       <c r="Q195" s="7" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="R195" s="7"/>
     </row>
@@ -14149,7 +14157,7 @@
         <v>208</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="C196" s="6" t="s">
         <v>28</v>
@@ -14161,7 +14169,7 @@
         <v>1690</v>
       </c>
       <c r="F196" s="7" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="G196" s="9" t="n">
         <v>2900</v>
@@ -14201,7 +14209,7 @@
         <v>33</v>
       </c>
       <c r="Q196" s="7" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="R196" s="7"/>
     </row>
@@ -14210,7 +14218,7 @@
         <v>209</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="C197" s="6" t="s">
         <v>28</v>
@@ -14262,7 +14270,7 @@
         <v>33</v>
       </c>
       <c r="Q197" s="7" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="R197" s="7"/>
     </row>
@@ -14271,7 +14279,7 @@
         <v>210</v>
       </c>
       <c r="B198" s="7" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C198" s="6" t="s">
         <v>28</v>
@@ -14323,7 +14331,7 @@
         <v>24</v>
       </c>
       <c r="Q198" s="7" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="R198" s="7" t="s">
         <v>26</v>
@@ -14334,7 +14342,7 @@
         <v>211</v>
       </c>
       <c r="B199" s="7" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C199" s="6" t="s">
         <v>28</v>
@@ -14386,7 +14394,7 @@
         <v>24</v>
       </c>
       <c r="Q199" s="7" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="R199" s="7" t="s">
         <v>26</v>
@@ -14397,7 +14405,7 @@
         <v>212</v>
       </c>
       <c r="B200" s="7" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C200" s="6" t="s">
         <v>28</v>
@@ -14449,16 +14457,16 @@
         <v>33</v>
       </c>
       <c r="Q200" s="7" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="R200" s="7"/>
     </row>
-    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="6" t="n">
         <v>213</v>
       </c>
       <c r="B201" s="7" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C201" s="6" t="s">
         <v>28</v>
@@ -14470,17 +14478,17 @@
         <v>455</v>
       </c>
       <c r="F201" s="7" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="G201" s="9" t="n">
-        <v>500</v>
+        <v>813</v>
       </c>
       <c r="H201" s="9" t="n">
-        <v>700</v>
+        <v>813</v>
       </c>
       <c r="I201" s="10" t="n">
         <f aca="false">IF(E201=0,0,(E201-H201)/E201)</f>
-        <v>-0.538461538461538</v>
+        <v>-0.786813186813187</v>
       </c>
       <c r="J201" s="6" t="str">
         <f aca="false">IF(E201&lt;G201,"LOSS",IF(E201&lt;H201*1.1,"THIN / RISK",IF(E201&gt;H201*1.8,"OVERPRICED?","OK")))</f>
@@ -14488,7 +14496,7 @@
       </c>
       <c r="K201" s="8" t="n">
         <f aca="false">IF(J201="OVERPRICED?",ROUND(H201*1.35,-1),MAX(E201,ROUND(H201*(1+$E$3),-1)))</f>
-        <v>810</v>
+        <v>930</v>
       </c>
       <c r="L201" s="8" t="n">
         <f aca="false">D201*E201</f>
@@ -14496,32 +14504,30 @@
       </c>
       <c r="M201" s="8" t="n">
         <f aca="false">D201*K201</f>
-        <v>1620</v>
+        <v>1860</v>
       </c>
       <c r="N201" s="8" t="n">
         <f aca="false">D201*H201</f>
-        <v>1400</v>
+        <v>1626</v>
       </c>
       <c r="O201" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C201,F201)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P201" s="6" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="Q201" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="R201" s="7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>438</v>
+      </c>
+      <c r="R201" s="7"/>
+    </row>
+    <row r="202" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="6" t="n">
         <v>214</v>
       </c>
       <c r="B202" s="7" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C202" s="6" t="s">
         <v>28</v>
@@ -14533,17 +14539,17 @@
         <v>494</v>
       </c>
       <c r="F202" s="7" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="G202" s="9" t="n">
-        <v>550</v>
+        <v>813</v>
       </c>
       <c r="H202" s="9" t="n">
-        <v>750</v>
+        <v>813</v>
       </c>
       <c r="I202" s="10" t="n">
         <f aca="false">IF(E202=0,0,(E202-H202)/E202)</f>
-        <v>-0.518218623481781</v>
+        <v>-0.645748987854251</v>
       </c>
       <c r="J202" s="6" t="str">
         <f aca="false">IF(E202&lt;G202,"LOSS",IF(E202&lt;H202*1.1,"THIN / RISK",IF(E202&gt;H202*1.8,"OVERPRICED?","OK")))</f>
@@ -14551,7 +14557,7 @@
       </c>
       <c r="K202" s="8" t="n">
         <f aca="false">IF(J202="OVERPRICED?",ROUND(H202*1.35,-1),MAX(E202,ROUND(H202*(1+$E$3),-1)))</f>
-        <v>860</v>
+        <v>930</v>
       </c>
       <c r="L202" s="8" t="n">
         <f aca="false">D202*E202</f>
@@ -14559,32 +14565,32 @@
       </c>
       <c r="M202" s="8" t="n">
         <f aca="false">D202*K202</f>
-        <v>1720</v>
+        <v>1860</v>
       </c>
       <c r="N202" s="8" t="n">
         <f aca="false">D202*H202</f>
-        <v>1500</v>
+        <v>1626</v>
       </c>
       <c r="O202" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C202,F202)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P202" s="6" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="Q202" s="7" t="s">
-        <v>143</v>
+        <v>440</v>
       </c>
       <c r="R202" s="7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="6" t="n">
         <v>215</v>
       </c>
       <c r="B203" s="7" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="C203" s="6" t="s">
         <v>28</v>
@@ -14596,17 +14602,17 @@
         <v>585</v>
       </c>
       <c r="F203" s="7" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="G203" s="9" t="n">
-        <v>650</v>
+        <v>1806</v>
       </c>
       <c r="H203" s="9" t="n">
-        <v>850</v>
+        <v>1806</v>
       </c>
       <c r="I203" s="10" t="n">
         <f aca="false">IF(E203=0,0,(E203-H203)/E203)</f>
-        <v>-0.452991452991453</v>
+        <v>-2.08717948717949</v>
       </c>
       <c r="J203" s="6" t="str">
         <f aca="false">IF(E203&lt;G203,"LOSS",IF(E203&lt;H203*1.1,"THIN / RISK",IF(E203&gt;H203*1.8,"OVERPRICED?","OK")))</f>
@@ -14614,7 +14620,7 @@
       </c>
       <c r="K203" s="8" t="n">
         <f aca="false">IF(J203="OVERPRICED?",ROUND(H203*1.35,-1),MAX(E203,ROUND(H203*(1+$E$3),-1)))</f>
-        <v>980</v>
+        <v>2080</v>
       </c>
       <c r="L203" s="8" t="n">
         <f aca="false">D203*E203</f>
@@ -14622,32 +14628,30 @@
       </c>
       <c r="M203" s="8" t="n">
         <f aca="false">D203*K203</f>
-        <v>1960</v>
+        <v>4160</v>
       </c>
       <c r="N203" s="8" t="n">
         <f aca="false">D203*H203</f>
-        <v>1700</v>
+        <v>3612</v>
       </c>
       <c r="O203" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C203,F203)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P203" s="6" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="Q203" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="R203" s="7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>442</v>
+      </c>
+      <c r="R203" s="7"/>
+    </row>
+    <row r="204" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="6" t="n">
         <v>216</v>
       </c>
       <c r="B204" s="7" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="C204" s="6" t="s">
         <v>28</v>
@@ -14659,17 +14663,17 @@
         <v>715</v>
       </c>
       <c r="F204" s="7" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="G204" s="9" t="n">
-        <v>800</v>
+        <v>1806</v>
       </c>
       <c r="H204" s="9" t="n">
-        <v>1050</v>
+        <v>1806</v>
       </c>
       <c r="I204" s="10" t="n">
         <f aca="false">IF(E204=0,0,(E204-H204)/E204)</f>
-        <v>-0.468531468531469</v>
+        <v>-1.52587412587413</v>
       </c>
       <c r="J204" s="6" t="str">
         <f aca="false">IF(E204&lt;G204,"LOSS",IF(E204&lt;H204*1.1,"THIN / RISK",IF(E204&gt;H204*1.8,"OVERPRICED?","OK")))</f>
@@ -14677,7 +14681,7 @@
       </c>
       <c r="K204" s="8" t="n">
         <f aca="false">IF(J204="OVERPRICED?",ROUND(H204*1.35,-1),MAX(E204,ROUND(H204*(1+$E$3),-1)))</f>
-        <v>1210</v>
+        <v>2080</v>
       </c>
       <c r="L204" s="8" t="n">
         <f aca="false">D204*E204</f>
@@ -14685,32 +14689,30 @@
       </c>
       <c r="M204" s="8" t="n">
         <f aca="false">D204*K204</f>
-        <v>2420</v>
+        <v>4160</v>
       </c>
       <c r="N204" s="8" t="n">
         <f aca="false">D204*H204</f>
-        <v>2100</v>
+        <v>3612</v>
       </c>
       <c r="O204" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C204,F204)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="Q204" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="R204" s="7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>444</v>
+      </c>
+      <c r="R204" s="7"/>
+    </row>
+    <row r="205" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="6" t="n">
         <v>217</v>
       </c>
       <c r="B205" s="7" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="C205" s="6" t="s">
         <v>28</v>
@@ -14722,17 +14724,17 @@
         <v>910</v>
       </c>
       <c r="F205" s="7" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="G205" s="9" t="n">
-        <v>1000</v>
+        <v>5143</v>
       </c>
       <c r="H205" s="9" t="n">
-        <v>1300</v>
+        <v>5143</v>
       </c>
       <c r="I205" s="10" t="n">
         <f aca="false">IF(E205=0,0,(E205-H205)/E205)</f>
-        <v>-0.428571428571429</v>
+        <v>-4.65164835164835</v>
       </c>
       <c r="J205" s="6" t="str">
         <f aca="false">IF(E205&lt;G205,"LOSS",IF(E205&lt;H205*1.1,"THIN / RISK",IF(E205&gt;H205*1.8,"OVERPRICED?","OK")))</f>
@@ -14740,7 +14742,7 @@
       </c>
       <c r="K205" s="8" t="n">
         <f aca="false">IF(J205="OVERPRICED?",ROUND(H205*1.35,-1),MAX(E205,ROUND(H205*(1+$E$3),-1)))</f>
-        <v>1500</v>
+        <v>5910</v>
       </c>
       <c r="L205" s="8" t="n">
         <f aca="false">D205*E205</f>
@@ -14748,24 +14750,24 @@
       </c>
       <c r="M205" s="8" t="n">
         <f aca="false">D205*K205</f>
-        <v>3000</v>
+        <v>11820</v>
       </c>
       <c r="N205" s="8" t="n">
         <f aca="false">D205*H205</f>
-        <v>2600</v>
+        <v>10286</v>
       </c>
       <c r="O205" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C205,F205)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P205" s="6" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="Q205" s="7" t="s">
-        <v>143</v>
+        <v>446</v>
       </c>
       <c r="R205" s="7" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14773,7 +14775,7 @@
         <v>218</v>
       </c>
       <c r="B206" s="7" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="C206" s="6" t="s">
         <v>28</v>
@@ -14785,7 +14787,7 @@
         <v>1170</v>
       </c>
       <c r="F206" s="7" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="G206" s="9" t="n">
         <v>5143</v>
@@ -14825,16 +14827,16 @@
         <v>33</v>
       </c>
       <c r="Q206" s="7" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="R206" s="7"/>
     </row>
-    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="207" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="6" t="n">
         <v>219</v>
       </c>
       <c r="B207" s="7" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="C207" s="6" t="s">
         <v>28</v>
@@ -14846,17 +14848,17 @@
         <v>1040</v>
       </c>
       <c r="F207" s="7" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="G207" s="9" t="n">
-        <v>1100</v>
+        <v>2037</v>
       </c>
       <c r="H207" s="9" t="n">
-        <v>1500</v>
+        <v>2037</v>
       </c>
       <c r="I207" s="10" t="n">
         <f aca="false">IF(E207=0,0,(E207-H207)/E207)</f>
-        <v>-0.442307692307692</v>
+        <v>-0.958653846153846</v>
       </c>
       <c r="J207" s="6" t="str">
         <f aca="false">IF(E207&lt;G207,"LOSS",IF(E207&lt;H207*1.1,"THIN / RISK",IF(E207&gt;H207*1.8,"OVERPRICED?","OK")))</f>
@@ -14864,7 +14866,7 @@
       </c>
       <c r="K207" s="8" t="n">
         <f aca="false">IF(J207="OVERPRICED?",ROUND(H207*1.35,-1),MAX(E207,ROUND(H207*(1+$E$3),-1)))</f>
-        <v>1730</v>
+        <v>2340</v>
       </c>
       <c r="L207" s="8" t="n">
         <f aca="false">D207*E207</f>
@@ -14872,32 +14874,32 @@
       </c>
       <c r="M207" s="8" t="n">
         <f aca="false">D207*K207</f>
-        <v>1730</v>
+        <v>2340</v>
       </c>
       <c r="N207" s="8" t="n">
         <f aca="false">D207*H207</f>
-        <v>1500</v>
+        <v>2037</v>
       </c>
       <c r="O207" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C207,F207)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P207" s="6" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="Q207" s="7" t="s">
-        <v>143</v>
+        <v>450</v>
       </c>
       <c r="R207" s="7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="6" t="n">
         <v>220</v>
       </c>
       <c r="B208" s="7" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="C208" s="6" t="s">
         <v>28</v>
@@ -14909,25 +14911,25 @@
         <v>1430</v>
       </c>
       <c r="F208" s="7" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="G208" s="9" t="n">
-        <v>1400</v>
+        <v>3728</v>
       </c>
       <c r="H208" s="9" t="n">
-        <v>1900</v>
+        <v>3728</v>
       </c>
       <c r="I208" s="10" t="n">
         <f aca="false">IF(E208=0,0,(E208-H208)/E208)</f>
-        <v>-0.328671328671329</v>
+        <v>-1.60699300699301</v>
       </c>
       <c r="J208" s="6" t="str">
         <f aca="false">IF(E208&lt;G208,"LOSS",IF(E208&lt;H208*1.1,"THIN / RISK",IF(E208&gt;H208*1.8,"OVERPRICED?","OK")))</f>
-        <v>THIN / RISK</v>
+        <v>LOSS</v>
       </c>
       <c r="K208" s="8" t="n">
         <f aca="false">IF(J208="OVERPRICED?",ROUND(H208*1.35,-1),MAX(E208,ROUND(H208*(1+$E$3),-1)))</f>
-        <v>2190</v>
+        <v>4290</v>
       </c>
       <c r="L208" s="8" t="n">
         <f aca="false">D208*E208</f>
@@ -14935,32 +14937,32 @@
       </c>
       <c r="M208" s="8" t="n">
         <f aca="false">D208*K208</f>
-        <v>2190</v>
+        <v>4290</v>
       </c>
       <c r="N208" s="8" t="n">
         <f aca="false">D208*H208</f>
-        <v>1900</v>
+        <v>3728</v>
       </c>
       <c r="O208" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C208,F208)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P208" s="6" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="Q208" s="7" t="s">
-        <v>143</v>
+        <v>452</v>
       </c>
       <c r="R208" s="7" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="6" t="n">
         <v>221</v>
       </c>
       <c r="B209" s="7" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="C209" s="6" t="s">
         <v>28</v>
@@ -14972,17 +14974,17 @@
         <v>1950</v>
       </c>
       <c r="F209" s="7" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="G209" s="9" t="n">
-        <v>2000</v>
+        <v>3728</v>
       </c>
       <c r="H209" s="9" t="n">
-        <v>2600</v>
+        <v>3728</v>
       </c>
       <c r="I209" s="10" t="n">
         <f aca="false">IF(E209=0,0,(E209-H209)/E209)</f>
-        <v>-0.333333333333333</v>
+        <v>-0.911794871794872</v>
       </c>
       <c r="J209" s="6" t="str">
         <f aca="false">IF(E209&lt;G209,"LOSS",IF(E209&lt;H209*1.1,"THIN / RISK",IF(E209&gt;H209*1.8,"OVERPRICED?","OK")))</f>
@@ -14990,7 +14992,7 @@
       </c>
       <c r="K209" s="8" t="n">
         <f aca="false">IF(J209="OVERPRICED?",ROUND(H209*1.35,-1),MAX(E209,ROUND(H209*(1+$E$3),-1)))</f>
-        <v>2990</v>
+        <v>4290</v>
       </c>
       <c r="L209" s="8" t="n">
         <f aca="false">D209*E209</f>
@@ -14998,32 +15000,30 @@
       </c>
       <c r="M209" s="8" t="n">
         <f aca="false">D209*K209</f>
-        <v>2990</v>
+        <v>4290</v>
       </c>
       <c r="N209" s="8" t="n">
         <f aca="false">D209*H209</f>
-        <v>2600</v>
+        <v>3728</v>
       </c>
       <c r="O209" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C209,F209)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P209" s="6" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="Q209" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="R209" s="7" t="s">
-        <v>78</v>
-      </c>
+        <v>454</v>
+      </c>
+      <c r="R209" s="7"/>
     </row>
     <row r="210" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="6" t="n">
         <v>222</v>
       </c>
       <c r="B210" s="7" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="C210" s="6" t="s">
         <v>28</v>
@@ -15075,7 +15075,7 @@
         <v>33</v>
       </c>
       <c r="Q210" s="7" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="R210" s="7"/>
     </row>
@@ -15084,7 +15084,7 @@
         <v>223</v>
       </c>
       <c r="B211" s="7" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="C211" s="6" t="s">
         <v>28</v>
@@ -15096,7 +15096,7 @@
         <v>30940</v>
       </c>
       <c r="F211" s="7" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G211" s="9" t="n">
         <v>31300</v>
@@ -15136,7 +15136,7 @@
         <v>33</v>
       </c>
       <c r="Q211" s="7" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="R211" s="7"/>
     </row>
@@ -15145,7 +15145,7 @@
         <v>224</v>
       </c>
       <c r="B212" s="7" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="C212" s="6" t="s">
         <v>28</v>
@@ -15197,7 +15197,7 @@
         <v>24</v>
       </c>
       <c r="Q212" s="7" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="R212" s="7" t="s">
         <v>26</v>
@@ -15208,7 +15208,7 @@
         <v>225</v>
       </c>
       <c r="B213" s="7" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="C213" s="6" t="s">
         <v>28</v>
@@ -15260,7 +15260,7 @@
         <v>33</v>
       </c>
       <c r="Q213" s="7" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="R213" s="7"/>
     </row>
@@ -15269,7 +15269,7 @@
         <v>226</v>
       </c>
       <c r="B214" s="7" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="C214" s="6" t="s">
         <v>28</v>
@@ -15321,7 +15321,7 @@
         <v>24</v>
       </c>
       <c r="Q214" s="7" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="R214" s="7" t="s">
         <v>26</v>
@@ -15332,7 +15332,7 @@
         <v>227</v>
       </c>
       <c r="B215" s="7" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="C215" s="6" t="s">
         <v>28</v>
@@ -15384,18 +15384,18 @@
         <v>24</v>
       </c>
       <c r="Q215" s="7" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="R215" s="7" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="216" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="6" t="n">
         <v>228</v>
       </c>
       <c r="B216" s="7" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="C216" s="6" t="s">
         <v>28</v>
@@ -15407,25 +15407,25 @@
         <v>2860</v>
       </c>
       <c r="F216" s="7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G216" s="9" t="n">
-        <v>6000</v>
+        <v>2088</v>
       </c>
       <c r="H216" s="9" t="n">
-        <v>8000</v>
+        <v>2088</v>
       </c>
       <c r="I216" s="10" t="n">
         <f aca="false">IF(E216=0,0,(E216-H216)/E216)</f>
-        <v>-1.7972027972028</v>
+        <v>0.26993006993007</v>
       </c>
       <c r="J216" s="6" t="str">
         <f aca="false">IF(E216&lt;G216,"LOSS",IF(E216&lt;H216*1.1,"THIN / RISK",IF(E216&gt;H216*1.8,"OVERPRICED?","OK")))</f>
-        <v>LOSS</v>
+        <v>OK</v>
       </c>
       <c r="K216" s="8" t="n">
         <f aca="false">IF(J216="OVERPRICED?",ROUND(H216*1.35,-1),MAX(E216,ROUND(H216*(1+$E$3),-1)))</f>
-        <v>9200</v>
+        <v>2860</v>
       </c>
       <c r="L216" s="8" t="n">
         <f aca="false">D216*E216</f>
@@ -15433,24 +15433,24 @@
       </c>
       <c r="M216" s="8" t="n">
         <f aca="false">D216*K216</f>
-        <v>220800</v>
+        <v>68640</v>
       </c>
       <c r="N216" s="8" t="n">
         <f aca="false">D216*H216</f>
-        <v>192000</v>
+        <v>50112</v>
       </c>
       <c r="O216" s="6" t="str">
         <f aca="false">IF(ISNUMBER(SEARCH(C216,F216)),"","YES")</f>
         <v>YES</v>
       </c>
       <c r="P216" s="6" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="Q216" s="7" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="R216" s="7" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15458,7 +15458,7 @@
         <v>229</v>
       </c>
       <c r="B217" s="7" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="C217" s="6" t="s">
         <v>28</v>
@@ -15510,7 +15510,7 @@
         <v>24</v>
       </c>
       <c r="Q217" s="7" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="R217" s="7" t="s">
         <v>26</v>
@@ -15521,7 +15521,7 @@
         <v>230</v>
       </c>
       <c r="B218" s="7" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="C218" s="6" t="s">
         <v>28</v>
@@ -15533,7 +15533,7 @@
         <v>9750</v>
       </c>
       <c r="F218" s="7" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="G218" s="9" t="n">
         <v>5950</v>
@@ -15573,7 +15573,7 @@
         <v>24</v>
       </c>
       <c r="Q218" s="7" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="R218" s="7" t="s">
         <v>26</v>
@@ -15584,7 +15584,7 @@
         <v>231</v>
       </c>
       <c r="B219" s="7" t="s">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="C219" s="6" t="s">
         <v>28</v>
@@ -15596,7 +15596,7 @@
         <v>12350</v>
       </c>
       <c r="F219" s="7" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="G219" s="9" t="n">
         <v>5950</v>
@@ -15636,7 +15636,7 @@
         <v>33</v>
       </c>
       <c r="Q219" s="7" t="s">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="R219" s="7"/>
     </row>
@@ -15645,10 +15645,10 @@
         <v>233</v>
       </c>
       <c r="B220" s="7" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="C220" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D220" s="6" t="n">
         <v>2</v>
@@ -15657,7 +15657,7 @@
         <v>52000</v>
       </c>
       <c r="F220" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G220" s="9" t="n">
         <v>40000</v>
@@ -15697,7 +15697,7 @@
         <v>33</v>
       </c>
       <c r="Q220" s="7" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="R220" s="7"/>
     </row>
@@ -15706,7 +15706,7 @@
         <v>234</v>
       </c>
       <c r="B221" s="7" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="C221" s="6" t="s">
         <v>22</v>
@@ -15758,7 +15758,7 @@
         <v>24</v>
       </c>
       <c r="Q221" s="7" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="R221" s="7" t="s">
         <v>26</v>
@@ -15769,7 +15769,7 @@
         <v>235</v>
       </c>
       <c r="B222" s="7" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="C222" s="6" t="s">
         <v>28</v>
@@ -15821,7 +15821,7 @@
         <v>24</v>
       </c>
       <c r="Q222" s="7" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="R222" s="7" t="s">
         <v>26</v>
@@ -15832,7 +15832,7 @@
         <v>236</v>
       </c>
       <c r="B223" s="7" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="C223" s="6" t="s">
         <v>22</v>
@@ -15884,7 +15884,7 @@
         <v>24</v>
       </c>
       <c r="Q223" s="7" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="R223" s="7" t="s">
         <v>26</v>
@@ -15895,7 +15895,7 @@
         <v>237</v>
       </c>
       <c r="B224" s="7" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="C224" s="6" t="s">
         <v>28</v>
@@ -15947,7 +15947,7 @@
         <v>24</v>
       </c>
       <c r="Q224" s="7" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="R224" s="7" t="s">
         <v>26</v>
@@ -15958,7 +15958,7 @@
         <v>238</v>
       </c>
       <c r="B225" s="7" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="C225" s="6" t="s">
         <v>28</v>
@@ -15970,7 +15970,7 @@
         <v>8450</v>
       </c>
       <c r="F225" s="7" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="G225" s="9" t="n">
         <v>7800</v>
@@ -16010,7 +16010,7 @@
         <v>33</v>
       </c>
       <c r="Q225" s="7" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="R225" s="7"/>
     </row>
@@ -16019,10 +16019,10 @@
         <v>239</v>
       </c>
       <c r="B226" s="7" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D226" s="6" t="n">
         <v>50</v>
@@ -16031,7 +16031,7 @@
         <v>65000</v>
       </c>
       <c r="F226" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G226" s="9" t="n">
         <v>44000</v>
@@ -16071,7 +16071,7 @@
         <v>33</v>
       </c>
       <c r="Q226" s="7" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="R226" s="7"/>
     </row>
@@ -16080,7 +16080,7 @@
         <v>240</v>
       </c>
       <c r="B227" s="7" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="C227" s="6" t="s">
         <v>28</v>
@@ -16132,13 +16132,13 @@
         <v>33</v>
       </c>
       <c r="Q227" s="7" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="R227" s="7"/>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B228" s="3" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="L228" s="11" t="n">
         <f aca="false">SUM(L6:L227)</f>
@@ -16146,11 +16146,11 @@
       </c>
       <c r="M228" s="11" t="n">
         <f aca="false">SUM(M6:M227)</f>
-        <v>15128395</v>
+        <v>15769745</v>
       </c>
       <c r="N228" s="11" t="n">
         <f aca="false">SUM(N6:N227)</f>
-        <v>12024011</v>
+        <v>12578406</v>
       </c>
     </row>
   </sheetData>
@@ -16199,12 +16199,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="B3" s="11" t="n">
         <f aca="false">COUNTA('Rate Check'!A6:A227)</f>
@@ -16213,47 +16213,47 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="B4" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"LOSS")</f>
-        <v>104</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="B5" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"THIN / RISK")</f>
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="B6" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"OK")</f>
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="B7" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"OVERPRICED?")</f>
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="B8" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!O6:O227,"YES")</f>
-        <v>172</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16261,7 +16261,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="B10" s="11" t="n">
         <f aca="false">'Rate Check'!L228</f>
@@ -16270,38 +16270,38 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="B11" s="11" t="n">
         <f aca="false">'Rate Check'!N228</f>
-        <v>12024011</v>
+        <v>12578406</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="B12" s="11" t="n">
         <f aca="false">B10-B11</f>
-        <v>185497</v>
+        <v>-368898</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="B13" s="14" t="n">
         <f aca="false">IF(B10=0,0,B12/B10)</f>
-        <v>0.0151928316849459</v>
+        <v>-0.0302139938808345</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="B14" s="11" t="n">
         <f aca="false">SUMPRODUCT(('Rate Check'!E6:E227&lt;'Rate Check'!H6:H227)*('Rate Check'!H6:H227-'Rate Check'!E6:E227)*'Rate Check'!D6:D227)</f>
-        <v>2862418</v>
+        <v>3459092</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16309,20 +16309,20 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="B16" s="11" t="n">
         <f aca="false">'Rate Check'!M228</f>
-        <v>15128395</v>
+        <v>15769745</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="B17" s="14" t="n">
         <f aca="false">IF(B16=0,0,(B16-B11)/B16)</f>
-        <v>0.205202468602915</v>
+        <v>0.202370995853135</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16330,29 +16330,29 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="B19" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!P6:P227,"V")</f>
-        <v>125</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="B20" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!P6:P227,"S")</f>
-        <v>64</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="B21" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!P6:P227,"N")</f>
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -16380,247 +16380,247 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>525</v>
+        <v>537</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
     </row>
   </sheetData>

--- a/quotes/PR-217-228/Quote_PR217_PR228_Rate_Check.xlsx
+++ b/quotes/PR-217-228/Quote_PR217_PR228_Rate_Check.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="572">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="573">
   <si>
     <t xml:space="preserve">Zidane Corporation - Quote PR-217 &amp; PR-228: Brand + Buying Rate Check</t>
   </si>
@@ -172,6 +172,9 @@
   </si>
   <si>
     <t xml:space="preserve">toolsmart.pk LICOTA MADE IN TAIWAN 7 Drawer Cabinet Trolley without tools Rs 272,440 in stock (screenshot Hassan)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selling rate fixed by Hassan at 270,000. </t>
   </si>
   <si>
     <t xml:space="preserve">DOUBLE OPEN RING OFFSET WRENCH SET (12PCS)</t>
@@ -2900,9 +2903,8 @@
         <f aca="false">IF(E13&lt;G13,"LOSS",IF(E13&lt;H13*1.1,"THIN / RISK",IF(E13&gt;H13*1.8,"OVERPRICED?","OK")))</f>
         <v>LOSS</v>
       </c>
-      <c r="K13" s="8" t="n">
-        <f aca="false">IF(J13="OVERPRICED?",ROUND(H13*1.35,-1),MAX(E13,ROUND(H13*(1+$E$3),-1)))</f>
-        <v>313310</v>
+      <c r="K13" s="9" t="n">
+        <v>270000</v>
       </c>
       <c r="L13" s="8" t="n">
         <f aca="false">D13*E13</f>
@@ -2910,7 +2912,7 @@
       </c>
       <c r="M13" s="8" t="n">
         <f aca="false">D13*K13</f>
-        <v>939930</v>
+        <v>810000</v>
       </c>
       <c r="N13" s="8" t="n">
         <f aca="false">D13*H13</f>
@@ -2926,14 +2928,16 @@
       <c r="Q13" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="R13" s="7"/>
+      <c r="R13" s="7" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="n">
         <v>9</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>28</v>
@@ -2985,7 +2989,7 @@
         <v>24</v>
       </c>
       <c r="Q14" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R14" s="7" t="s">
         <v>26</v>
@@ -2996,7 +3000,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>28</v>
@@ -3008,7 +3012,7 @@
         <v>15600</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G15" s="9" t="n">
         <v>12630</v>
@@ -3048,7 +3052,7 @@
         <v>33</v>
       </c>
       <c r="Q15" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R15" s="7"/>
     </row>
@@ -3057,7 +3061,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>28</v>
@@ -3109,7 +3113,7 @@
         <v>33</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="R16" s="7"/>
     </row>
@@ -3118,7 +3122,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>28</v>
@@ -3170,7 +3174,7 @@
         <v>33</v>
       </c>
       <c r="Q17" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R17" s="7"/>
     </row>
@@ -3179,7 +3183,7 @@
         <v>13</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>28</v>
@@ -3191,7 +3195,7 @@
         <v>22100</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G18" s="9" t="n">
         <v>11780</v>
@@ -3231,7 +3235,7 @@
         <v>33</v>
       </c>
       <c r="Q18" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="R18" s="7"/>
     </row>
@@ -3240,7 +3244,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>28</v>
@@ -3292,7 +3296,7 @@
         <v>33</v>
       </c>
       <c r="Q19" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="R19" s="7"/>
     </row>
@@ -3301,7 +3305,7 @@
         <v>15</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>28</v>
@@ -3353,7 +3357,7 @@
         <v>33</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="R20" s="7"/>
     </row>
@@ -3362,7 +3366,7 @@
         <v>16</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>28</v>
@@ -3374,7 +3378,7 @@
         <v>8450</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G21" s="9" t="n">
         <v>4699</v>
@@ -3414,7 +3418,7 @@
         <v>24</v>
       </c>
       <c r="Q21" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R21" s="7" t="s">
         <v>26</v>
@@ -3425,7 +3429,7 @@
         <v>17</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>28</v>
@@ -3477,7 +3481,7 @@
         <v>33</v>
       </c>
       <c r="Q22" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="R22" s="7"/>
     </row>
@@ -3486,7 +3490,7 @@
         <v>18</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>28</v>
@@ -3538,7 +3542,7 @@
         <v>33</v>
       </c>
       <c r="Q23" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="R23" s="7"/>
     </row>
@@ -3547,7 +3551,7 @@
         <v>19</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>28</v>
@@ -3599,7 +3603,7 @@
         <v>33</v>
       </c>
       <c r="Q24" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="R24" s="7"/>
     </row>
@@ -3608,7 +3612,7 @@
         <v>20</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>28</v>
@@ -3660,7 +3664,7 @@
         <v>33</v>
       </c>
       <c r="Q25" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="R25" s="7"/>
     </row>
@@ -3669,7 +3673,7 @@
         <v>21</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>28</v>
@@ -3681,7 +3685,7 @@
         <v>1170</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G26" s="9" t="n">
         <v>1845</v>
@@ -3721,7 +3725,7 @@
         <v>33</v>
       </c>
       <c r="Q26" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R26" s="7"/>
     </row>
@@ -3730,7 +3734,7 @@
         <v>22</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>28</v>
@@ -3742,7 +3746,7 @@
         <v>1430</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G27" s="9" t="n">
         <v>1845</v>
@@ -3782,7 +3786,7 @@
         <v>24</v>
       </c>
       <c r="Q27" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R27" s="7" t="s">
         <v>26</v>
@@ -3793,7 +3797,7 @@
         <v>23</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>28</v>
@@ -3845,7 +3849,7 @@
         <v>33</v>
       </c>
       <c r="Q28" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R28" s="7"/>
     </row>
@@ -3854,7 +3858,7 @@
         <v>24</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>28</v>
@@ -3906,7 +3910,7 @@
         <v>33</v>
       </c>
       <c r="Q29" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R29" s="7"/>
     </row>
@@ -3915,7 +3919,7 @@
         <v>25</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>28</v>
@@ -3967,7 +3971,7 @@
         <v>33</v>
       </c>
       <c r="Q30" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R30" s="7"/>
     </row>
@@ -3976,7 +3980,7 @@
         <v>26</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>28</v>
@@ -4028,7 +4032,7 @@
         <v>33</v>
       </c>
       <c r="Q31" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R31" s="7"/>
     </row>
@@ -4037,7 +4041,7 @@
         <v>27</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>28</v>
@@ -4089,7 +4093,7 @@
         <v>24</v>
       </c>
       <c r="Q32" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="R32" s="7" t="s">
         <v>26</v>
@@ -4100,7 +4104,7 @@
         <v>28</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>28</v>
@@ -4112,7 +4116,7 @@
         <v>6760</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G33" s="9" t="n">
         <v>4996</v>
@@ -4152,7 +4156,7 @@
         <v>24</v>
       </c>
       <c r="Q33" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="R33" s="7" t="s">
         <v>26</v>
@@ -4163,7 +4167,7 @@
         <v>30</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>28</v>
@@ -4215,7 +4219,7 @@
         <v>33</v>
       </c>
       <c r="Q34" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="R34" s="7"/>
     </row>
@@ -4224,7 +4228,7 @@
         <v>31</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>28</v>
@@ -4276,7 +4280,7 @@
         <v>33</v>
       </c>
       <c r="Q35" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R35" s="7"/>
     </row>
@@ -4285,7 +4289,7 @@
         <v>32</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>28</v>
@@ -4297,7 +4301,7 @@
         <v>2886</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G36" s="9" t="n">
         <v>2850</v>
@@ -4337,7 +4341,7 @@
         <v>33</v>
       </c>
       <c r="Q36" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="R36" s="7"/>
     </row>
@@ -4346,7 +4350,7 @@
         <v>33</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>28</v>
@@ -4398,7 +4402,7 @@
         <v>33</v>
       </c>
       <c r="Q37" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="R37" s="7"/>
     </row>
@@ -4407,7 +4411,7 @@
         <v>34</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>28</v>
@@ -4419,7 +4423,7 @@
         <v>6120</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G38" s="9" t="n">
         <v>6560</v>
@@ -4459,7 +4463,7 @@
         <v>33</v>
       </c>
       <c r="Q38" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="R38" s="7"/>
     </row>
@@ -4468,7 +4472,7 @@
         <v>35</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>28</v>
@@ -4520,7 +4524,7 @@
         <v>33</v>
       </c>
       <c r="Q39" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="R39" s="7"/>
     </row>
@@ -4529,7 +4533,7 @@
         <v>36</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>28</v>
@@ -4581,7 +4585,7 @@
         <v>24</v>
       </c>
       <c r="Q40" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="R40" s="7" t="s">
         <v>26</v>
@@ -4592,7 +4596,7 @@
         <v>37</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>28</v>
@@ -4604,7 +4608,7 @@
         <v>4550</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G41" s="9" t="n">
         <v>3380</v>
@@ -4644,7 +4648,7 @@
         <v>33</v>
       </c>
       <c r="Q41" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="R41" s="7"/>
     </row>
@@ -4653,7 +4657,7 @@
         <v>38</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>28</v>
@@ -4665,7 +4669,7 @@
         <v>6240</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G42" s="9" t="n">
         <v>2450</v>
@@ -4705,7 +4709,7 @@
         <v>33</v>
       </c>
       <c r="Q42" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="R42" s="7"/>
     </row>
@@ -4714,7 +4718,7 @@
         <v>39</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>28</v>
@@ -4766,7 +4770,7 @@
         <v>24</v>
       </c>
       <c r="Q43" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="R43" s="7" t="s">
         <v>26</v>
@@ -4777,10 +4781,10 @@
         <v>40</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D44" s="6" t="n">
         <v>3</v>
@@ -4789,7 +4793,7 @@
         <v>79300</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G44" s="9" t="n">
         <v>79000</v>
@@ -4829,7 +4833,7 @@
         <v>33</v>
       </c>
       <c r="Q44" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R44" s="7"/>
     </row>
@@ -4838,10 +4842,10 @@
         <v>41</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D45" s="6" t="n">
         <v>3</v>
@@ -4850,7 +4854,7 @@
         <v>128700</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G45" s="9" t="n">
         <v>114345</v>
@@ -4890,7 +4894,7 @@
         <v>33</v>
       </c>
       <c r="Q45" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="R45" s="7"/>
     </row>
@@ -4899,10 +4903,10 @@
         <v>42</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D46" s="6" t="n">
         <v>2</v>
@@ -4911,7 +4915,7 @@
         <v>106600</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G46" s="9" t="n">
         <v>143800</v>
@@ -4951,7 +4955,7 @@
         <v>33</v>
       </c>
       <c r="Q46" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="R46" s="7"/>
     </row>
@@ -4960,7 +4964,7 @@
         <v>43</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>28</v>
@@ -4972,7 +4976,7 @@
         <v>1560</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G47" s="9" t="n">
         <v>5955</v>
@@ -5012,7 +5016,7 @@
         <v>33</v>
       </c>
       <c r="Q47" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="R47" s="7"/>
     </row>
@@ -5021,7 +5025,7 @@
         <v>44</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>28</v>
@@ -5033,7 +5037,7 @@
         <v>1950</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G48" s="9" t="n">
         <v>1750</v>
@@ -5073,7 +5077,7 @@
         <v>33</v>
       </c>
       <c r="Q48" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="R48" s="7"/>
     </row>
@@ -5082,7 +5086,7 @@
         <v>45</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>28</v>
@@ -5094,7 +5098,7 @@
         <v>2210</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G49" s="9" t="n">
         <v>1960</v>
@@ -5134,7 +5138,7 @@
         <v>33</v>
       </c>
       <c r="Q49" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="R49" s="7"/>
     </row>
@@ -5143,7 +5147,7 @@
         <v>47</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>28</v>
@@ -5155,7 +5159,7 @@
         <v>13000</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G50" s="9" t="n">
         <v>6255</v>
@@ -5195,7 +5199,7 @@
         <v>24</v>
       </c>
       <c r="Q50" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="R50" s="7" t="s">
         <v>26</v>
@@ -5206,7 +5210,7 @@
         <v>48</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>28</v>
@@ -5258,7 +5262,7 @@
         <v>33</v>
       </c>
       <c r="Q51" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="R51" s="7"/>
     </row>
@@ -5267,7 +5271,7 @@
         <v>49</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>28</v>
@@ -5319,7 +5323,7 @@
         <v>24</v>
       </c>
       <c r="Q52" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="R52" s="7" t="s">
         <v>26</v>
@@ -5330,7 +5334,7 @@
         <v>50</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>28</v>
@@ -5382,7 +5386,7 @@
         <v>24</v>
       </c>
       <c r="Q53" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R53" s="7" t="s">
         <v>26</v>
@@ -5393,7 +5397,7 @@
         <v>51</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>28</v>
@@ -5445,7 +5449,7 @@
         <v>24</v>
       </c>
       <c r="Q54" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="R54" s="7" t="s">
         <v>26</v>
@@ -5456,7 +5460,7 @@
         <v>52</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>28</v>
@@ -5468,7 +5472,7 @@
         <v>18200</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G55" s="9" t="n">
         <v>8500</v>
@@ -5508,7 +5512,7 @@
         <v>33</v>
       </c>
       <c r="Q55" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="R55" s="7"/>
     </row>
@@ -5517,7 +5521,7 @@
         <v>53</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>28</v>
@@ -5529,7 +5533,7 @@
         <v>23400</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G56" s="9" t="n">
         <v>19030</v>
@@ -5569,7 +5573,7 @@
         <v>33</v>
       </c>
       <c r="Q56" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="R56" s="7"/>
     </row>
@@ -5578,10 +5582,10 @@
         <v>54</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D57" s="6" t="n">
         <v>2</v>
@@ -5590,7 +5594,7 @@
         <v>400946</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G57" s="9" t="n">
         <v>115000</v>
@@ -5630,7 +5634,7 @@
         <v>33</v>
       </c>
       <c r="Q57" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="R57" s="7"/>
     </row>
@@ -5639,7 +5643,7 @@
         <v>55</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>28</v>
@@ -5691,7 +5695,7 @@
         <v>24</v>
       </c>
       <c r="Q58" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="R58" s="7" t="s">
         <v>26</v>
@@ -5702,7 +5706,7 @@
         <v>56</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>28</v>
@@ -5714,7 +5718,7 @@
         <v>10400</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G59" s="9" t="n">
         <v>20921</v>
@@ -5754,7 +5758,7 @@
         <v>24</v>
       </c>
       <c r="Q59" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="R59" s="7" t="s">
         <v>26</v>
@@ -5765,7 +5769,7 @@
         <v>57</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>28</v>
@@ -5817,7 +5821,7 @@
         <v>33</v>
       </c>
       <c r="Q60" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="R60" s="7"/>
     </row>
@@ -5826,7 +5830,7 @@
         <v>58</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>28</v>
@@ -5878,7 +5882,7 @@
         <v>24</v>
       </c>
       <c r="Q61" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="R61" s="7" t="s">
         <v>26</v>
@@ -5889,7 +5893,7 @@
         <v>59</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>28</v>
@@ -5941,7 +5945,7 @@
         <v>33</v>
       </c>
       <c r="Q62" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="R62" s="7"/>
     </row>
@@ -5950,7 +5954,7 @@
         <v>60</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>28</v>
@@ -6002,7 +6006,7 @@
         <v>24</v>
       </c>
       <c r="Q63" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="R63" s="7" t="s">
         <v>26</v>
@@ -6013,7 +6017,7 @@
         <v>61</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>28</v>
@@ -6025,7 +6029,7 @@
         <v>5850</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G64" s="9" t="n">
         <v>5920</v>
@@ -6065,7 +6069,7 @@
         <v>33</v>
       </c>
       <c r="Q64" s="7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="R64" s="7"/>
     </row>
@@ -6074,7 +6078,7 @@
         <v>62</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>28</v>
@@ -6086,7 +6090,7 @@
         <v>2600</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G65" s="9" t="n">
         <v>3499</v>
@@ -6126,7 +6130,7 @@
         <v>24</v>
       </c>
       <c r="Q65" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="R65" s="7" t="s">
         <v>26</v>
@@ -6137,7 +6141,7 @@
         <v>63</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>28</v>
@@ -6149,7 +6153,7 @@
         <v>5551</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G66" s="9" t="n">
         <v>4630</v>
@@ -6189,7 +6193,7 @@
         <v>33</v>
       </c>
       <c r="Q66" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="R66" s="7"/>
     </row>
@@ -6198,7 +6202,7 @@
         <v>64</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>28</v>
@@ -6210,7 +6214,7 @@
         <v>1560</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G67" s="9" t="n">
         <v>1350</v>
@@ -6250,7 +6254,7 @@
         <v>33</v>
       </c>
       <c r="Q67" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="R67" s="7"/>
     </row>
@@ -6259,7 +6263,7 @@
         <v>65</v>
       </c>
       <c r="B68" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>28</v>
@@ -6271,7 +6275,7 @@
         <v>1560</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G68" s="9" t="n">
         <v>1350</v>
@@ -6311,7 +6315,7 @@
         <v>33</v>
       </c>
       <c r="Q68" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="R68" s="7"/>
     </row>
@@ -6320,7 +6324,7 @@
         <v>66</v>
       </c>
       <c r="B69" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>28</v>
@@ -6372,7 +6376,7 @@
         <v>24</v>
       </c>
       <c r="Q69" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="R69" s="7" t="s">
         <v>26</v>
@@ -6383,7 +6387,7 @@
         <v>67</v>
       </c>
       <c r="B70" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>28</v>
@@ -6435,7 +6439,7 @@
         <v>33</v>
       </c>
       <c r="Q70" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="R70" s="7"/>
     </row>
@@ -6444,7 +6448,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>28</v>
@@ -6456,7 +6460,7 @@
         <v>23400</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G71" s="9" t="n">
         <v>16156</v>
@@ -6496,7 +6500,7 @@
         <v>33</v>
       </c>
       <c r="Q71" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="R71" s="7"/>
     </row>
@@ -6505,7 +6509,7 @@
         <v>70</v>
       </c>
       <c r="B72" s="7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>28</v>
@@ -6517,7 +6521,7 @@
         <v>32500</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G72" s="9" t="n">
         <v>11453</v>
@@ -6557,7 +6561,7 @@
         <v>33</v>
       </c>
       <c r="Q72" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="R72" s="7"/>
     </row>
@@ -6566,7 +6570,7 @@
         <v>71</v>
       </c>
       <c r="B73" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>28</v>
@@ -6618,7 +6622,7 @@
         <v>33</v>
       </c>
       <c r="Q73" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="R73" s="7"/>
     </row>
@@ -6627,7 +6631,7 @@
         <v>73</v>
       </c>
       <c r="B74" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>28</v>
@@ -6639,7 +6643,7 @@
         <v>45500</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G74" s="9" t="n">
         <v>22185</v>
@@ -6679,7 +6683,7 @@
         <v>24</v>
       </c>
       <c r="Q74" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="R74" s="7" t="s">
         <v>26</v>
@@ -6690,7 +6694,7 @@
         <v>74</v>
       </c>
       <c r="B75" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>28</v>
@@ -6742,7 +6746,7 @@
         <v>33</v>
       </c>
       <c r="Q75" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="R75" s="7"/>
     </row>
@@ -6751,7 +6755,7 @@
         <v>75</v>
       </c>
       <c r="B76" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>28</v>
@@ -6763,7 +6767,7 @@
         <v>1950</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G76" s="9" t="n">
         <v>7020</v>
@@ -6803,7 +6807,7 @@
         <v>33</v>
       </c>
       <c r="Q76" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="R76" s="7"/>
     </row>
@@ -6812,7 +6816,7 @@
         <v>76</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>28</v>
@@ -6824,7 +6828,7 @@
         <v>2080</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G77" s="9" t="n">
         <v>9630</v>
@@ -6864,7 +6868,7 @@
         <v>33</v>
       </c>
       <c r="Q77" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="R77" s="7"/>
     </row>
@@ -6873,7 +6877,7 @@
         <v>77</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>28</v>
@@ -6885,7 +6889,7 @@
         <v>2210</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G78" s="9" t="n">
         <v>9630</v>
@@ -6925,7 +6929,7 @@
         <v>24</v>
       </c>
       <c r="Q78" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="R78" s="7" t="s">
         <v>26</v>
@@ -6936,7 +6940,7 @@
         <v>78</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>28</v>
@@ -6948,7 +6952,7 @@
         <v>2340</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G79" s="9" t="n">
         <v>7920</v>
@@ -6988,7 +6992,7 @@
         <v>33</v>
       </c>
       <c r="Q79" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="R79" s="7"/>
     </row>
@@ -6997,7 +7001,7 @@
         <v>79</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>28</v>
@@ -7009,7 +7013,7 @@
         <v>2470</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G80" s="9" t="n">
         <v>11250</v>
@@ -7049,7 +7053,7 @@
         <v>24</v>
       </c>
       <c r="Q80" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="R80" s="7" t="s">
         <v>26</v>
@@ -7060,7 +7064,7 @@
         <v>80</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>28</v>
@@ -7072,7 +7076,7 @@
         <v>2600</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G81" s="9" t="n">
         <v>12600</v>
@@ -7112,7 +7116,7 @@
         <v>33</v>
       </c>
       <c r="Q81" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="R81" s="7"/>
     </row>
@@ -7121,7 +7125,7 @@
         <v>81</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>28</v>
@@ -7133,7 +7137,7 @@
         <v>2730</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G82" s="9" t="n">
         <v>11250</v>
@@ -7173,7 +7177,7 @@
         <v>33</v>
       </c>
       <c r="Q82" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="R82" s="7"/>
     </row>
@@ -7182,7 +7186,7 @@
         <v>82</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>28</v>
@@ -7194,7 +7198,7 @@
         <v>3250</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G83" s="9" t="n">
         <v>12240</v>
@@ -7234,7 +7238,7 @@
         <v>33</v>
       </c>
       <c r="Q83" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="R83" s="7"/>
     </row>
@@ -7243,7 +7247,7 @@
         <v>83</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>28</v>
@@ -7255,7 +7259,7 @@
         <v>4160</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G84" s="9" t="n">
         <v>13500</v>
@@ -7295,7 +7299,7 @@
         <v>24</v>
       </c>
       <c r="Q84" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="R84" s="7" t="s">
         <v>26</v>
@@ -7306,7 +7310,7 @@
         <v>84</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>28</v>
@@ -7318,7 +7322,7 @@
         <v>5850</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G85" s="9" t="n">
         <v>20250</v>
@@ -7358,7 +7362,7 @@
         <v>33</v>
       </c>
       <c r="Q85" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="R85" s="7"/>
     </row>
@@ -7367,7 +7371,7 @@
         <v>85</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>28</v>
@@ -7379,7 +7383,7 @@
         <v>8450</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G86" s="9" t="n">
         <v>39640</v>
@@ -7419,7 +7423,7 @@
         <v>24</v>
       </c>
       <c r="Q86" s="7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="R86" s="7" t="s">
         <v>26</v>
@@ -7430,7 +7434,7 @@
         <v>86</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>28</v>
@@ -7442,7 +7446,7 @@
         <v>9750</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G87" s="9" t="n">
         <v>39640</v>
@@ -7482,7 +7486,7 @@
         <v>33</v>
       </c>
       <c r="Q87" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="R87" s="7"/>
     </row>
@@ -7491,7 +7495,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>28</v>
@@ -7503,7 +7507,7 @@
         <v>11700</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G88" s="9" t="n">
         <v>40500</v>
@@ -7543,7 +7547,7 @@
         <v>24</v>
       </c>
       <c r="Q88" s="7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="R88" s="7" t="s">
         <v>26</v>
@@ -7554,7 +7558,7 @@
         <v>88</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>28</v>
@@ -7606,7 +7610,7 @@
         <v>24</v>
       </c>
       <c r="Q89" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="R89" s="7" t="s">
         <v>26</v>
@@ -7617,7 +7621,7 @@
         <v>89</v>
       </c>
       <c r="B90" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>28</v>
@@ -7669,7 +7673,7 @@
         <v>24</v>
       </c>
       <c r="Q90" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="R90" s="7" t="s">
         <v>26</v>
@@ -7680,7 +7684,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>28</v>
@@ -7732,7 +7736,7 @@
         <v>24</v>
       </c>
       <c r="Q91" s="7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="R91" s="7" t="s">
         <v>26</v>
@@ -7743,7 +7747,7 @@
         <v>91</v>
       </c>
       <c r="B92" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>28</v>
@@ -7795,7 +7799,7 @@
         <v>24</v>
       </c>
       <c r="Q92" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="R92" s="7" t="s">
         <v>26</v>
@@ -7806,7 +7810,7 @@
         <v>92</v>
       </c>
       <c r="B93" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>28</v>
@@ -7858,7 +7862,7 @@
         <v>33</v>
       </c>
       <c r="Q93" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="R93" s="7"/>
     </row>
@@ -7867,10 +7871,10 @@
         <v>93</v>
       </c>
       <c r="B94" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D94" s="6" t="n">
         <v>2</v>
@@ -7879,7 +7883,7 @@
         <v>25350</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G94" s="9" t="n">
         <v>18100</v>
@@ -7919,7 +7923,7 @@
         <v>33</v>
       </c>
       <c r="Q94" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="R94" s="7"/>
     </row>
@@ -7928,10 +7932,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="7" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D95" s="6" t="n">
         <v>3</v>
@@ -7940,7 +7944,7 @@
         <v>8138</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G95" s="9" t="n">
         <v>15800</v>
@@ -7980,7 +7984,7 @@
         <v>33</v>
       </c>
       <c r="Q95" s="7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="R95" s="7"/>
     </row>
@@ -7989,10 +7993,10 @@
         <v>95</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D96" s="6" t="n">
         <v>3</v>
@@ -8001,7 +8005,7 @@
         <v>6370</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G96" s="9" t="n">
         <v>7928</v>
@@ -8041,7 +8045,7 @@
         <v>33</v>
       </c>
       <c r="Q96" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="R96" s="7"/>
     </row>
@@ -8050,7 +8054,7 @@
         <v>96</v>
       </c>
       <c r="B97" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>28</v>
@@ -8062,7 +8066,7 @@
         <v>14950</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G97" s="9" t="n">
         <v>27919</v>
@@ -8102,7 +8106,7 @@
         <v>24</v>
       </c>
       <c r="Q97" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="R97" s="7" t="s">
         <v>26</v>
@@ -8113,10 +8117,10 @@
         <v>97</v>
       </c>
       <c r="B98" s="7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D98" s="6" t="n">
         <v>2</v>
@@ -8125,7 +8129,7 @@
         <v>286000</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G98" s="9" t="n">
         <v>199500</v>
@@ -8165,7 +8169,7 @@
         <v>24</v>
       </c>
       <c r="Q98" s="7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="R98" s="7" t="s">
         <v>26</v>
@@ -8176,7 +8180,7 @@
         <v>98</v>
       </c>
       <c r="B99" s="7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>36</v>
@@ -8228,7 +8232,7 @@
         <v>24</v>
       </c>
       <c r="Q99" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="R99" s="7" t="s">
         <v>26</v>
@@ -8239,7 +8243,7 @@
         <v>99</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>28</v>
@@ -8291,7 +8295,7 @@
         <v>33</v>
       </c>
       <c r="Q100" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="R100" s="7"/>
     </row>
@@ -8300,7 +8304,7 @@
         <v>100</v>
       </c>
       <c r="B101" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>28</v>
@@ -8352,7 +8356,7 @@
         <v>24</v>
       </c>
       <c r="Q101" s="7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="R101" s="7" t="s">
         <v>26</v>
@@ -8363,7 +8367,7 @@
         <v>101</v>
       </c>
       <c r="B102" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>28</v>
@@ -8415,7 +8419,7 @@
         <v>33</v>
       </c>
       <c r="Q102" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="R102" s="7"/>
     </row>
@@ -8424,7 +8428,7 @@
         <v>102</v>
       </c>
       <c r="B103" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>28</v>
@@ -8476,7 +8480,7 @@
         <v>33</v>
       </c>
       <c r="Q103" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="R103" s="7"/>
     </row>
@@ -8485,7 +8489,7 @@
         <v>103</v>
       </c>
       <c r="B104" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>22</v>
@@ -8497,7 +8501,7 @@
         <v>715</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G104" s="9" t="n">
         <v>540</v>
@@ -8537,7 +8541,7 @@
         <v>33</v>
       </c>
       <c r="Q104" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="R104" s="7"/>
     </row>
@@ -8546,7 +8550,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>22</v>
@@ -8598,7 +8602,7 @@
         <v>24</v>
       </c>
       <c r="Q105" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="R105" s="7" t="s">
         <v>26</v>
@@ -8609,7 +8613,7 @@
         <v>105</v>
       </c>
       <c r="B106" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>22</v>
@@ -8621,7 +8625,7 @@
         <v>1170</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G106" s="9" t="n">
         <v>800</v>
@@ -8661,7 +8665,7 @@
         <v>33</v>
       </c>
       <c r="Q106" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="R106" s="7"/>
     </row>
@@ -8670,7 +8674,7 @@
         <v>106</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>28</v>
@@ -8722,7 +8726,7 @@
         <v>33</v>
       </c>
       <c r="Q107" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="R107" s="7"/>
     </row>
@@ -8731,7 +8735,7 @@
         <v>107</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>28</v>
@@ -8743,7 +8747,7 @@
         <v>6760</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G108" s="9" t="n">
         <v>5226</v>
@@ -8783,7 +8787,7 @@
         <v>33</v>
       </c>
       <c r="Q108" s="7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="R108" s="7"/>
     </row>
@@ -8792,7 +8796,7 @@
         <v>108</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>28</v>
@@ -8844,7 +8848,7 @@
         <v>33</v>
       </c>
       <c r="Q109" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="R109" s="7"/>
     </row>
@@ -8853,7 +8857,7 @@
         <v>109</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>28</v>
@@ -8865,7 +8869,7 @@
         <v>2340</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G110" s="9" t="n">
         <v>3651</v>
@@ -8905,7 +8909,7 @@
         <v>33</v>
       </c>
       <c r="Q110" s="7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="R110" s="7"/>
     </row>
@@ -8914,7 +8918,7 @@
         <v>110</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>28</v>
@@ -8926,7 +8930,7 @@
         <v>1820</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G111" s="9" t="n">
         <v>15399</v>
@@ -8966,7 +8970,7 @@
         <v>33</v>
       </c>
       <c r="Q111" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="R111" s="7"/>
     </row>
@@ -8975,7 +8979,7 @@
         <v>111</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>28</v>
@@ -8987,7 +8991,7 @@
         <v>2860</v>
       </c>
       <c r="F112" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G112" s="9" t="n">
         <v>3125</v>
@@ -9027,7 +9031,7 @@
         <v>24</v>
       </c>
       <c r="Q112" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="R112" s="7" t="s">
         <v>26</v>
@@ -9038,7 +9042,7 @@
         <v>112</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>28</v>
@@ -9090,7 +9094,7 @@
         <v>33</v>
       </c>
       <c r="Q113" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="R113" s="7"/>
     </row>
@@ -9099,7 +9103,7 @@
         <v>113</v>
       </c>
       <c r="B114" s="7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>28</v>
@@ -9151,7 +9155,7 @@
         <v>33</v>
       </c>
       <c r="Q114" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="R114" s="7"/>
     </row>
@@ -9160,7 +9164,7 @@
         <v>114</v>
       </c>
       <c r="B115" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>28</v>
@@ -9212,7 +9216,7 @@
         <v>33</v>
       </c>
       <c r="Q115" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="R115" s="7"/>
     </row>
@@ -9221,7 +9225,7 @@
         <v>115</v>
       </c>
       <c r="B116" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>22</v>
@@ -9233,7 +9237,7 @@
         <v>11050</v>
       </c>
       <c r="F116" s="7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G116" s="9" t="n">
         <v>5000</v>
@@ -9273,7 +9277,7 @@
         <v>33</v>
       </c>
       <c r="Q116" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="R116" s="7"/>
     </row>
@@ -9282,7 +9286,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>28</v>
@@ -9334,7 +9338,7 @@
         <v>33</v>
       </c>
       <c r="Q117" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="R117" s="7"/>
     </row>
@@ -9343,7 +9347,7 @@
         <v>117</v>
       </c>
       <c r="B118" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>22</v>
@@ -9395,7 +9399,7 @@
         <v>24</v>
       </c>
       <c r="Q118" s="7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="R118" s="7" t="s">
         <v>26</v>
@@ -9406,7 +9410,7 @@
         <v>118</v>
       </c>
       <c r="B119" s="7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>22</v>
@@ -9458,7 +9462,7 @@
         <v>24</v>
       </c>
       <c r="Q119" s="7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="R119" s="7" t="s">
         <v>26</v>
@@ -9469,7 +9473,7 @@
         <v>119</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>28</v>
@@ -9481,7 +9485,7 @@
         <v>910</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G120" s="9" t="n">
         <v>2243</v>
@@ -9521,7 +9525,7 @@
         <v>33</v>
       </c>
       <c r="Q120" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="R120" s="7"/>
     </row>
@@ -9530,7 +9534,7 @@
         <v>120</v>
       </c>
       <c r="B121" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>22</v>
@@ -9582,7 +9586,7 @@
         <v>33</v>
       </c>
       <c r="Q121" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="R121" s="7"/>
     </row>
@@ -9591,7 +9595,7 @@
         <v>121</v>
       </c>
       <c r="B122" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>22</v>
@@ -9643,7 +9647,7 @@
         <v>33</v>
       </c>
       <c r="Q122" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="R122" s="7"/>
     </row>
@@ -9652,7 +9656,7 @@
         <v>122</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>22</v>
@@ -9664,7 +9668,7 @@
         <v>357500</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G123" s="9" t="n">
         <v>126000</v>
@@ -9704,7 +9708,7 @@
         <v>24</v>
       </c>
       <c r="Q123" s="7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="R123" s="7" t="s">
         <v>26</v>
@@ -9715,7 +9719,7 @@
         <v>123</v>
       </c>
       <c r="B124" s="7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C124" s="6" t="s">
         <v>22</v>
@@ -9767,7 +9771,7 @@
         <v>24</v>
       </c>
       <c r="Q124" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="R124" s="7" t="s">
         <v>26</v>
@@ -9778,7 +9782,7 @@
         <v>124</v>
       </c>
       <c r="B125" s="7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>22</v>
@@ -9830,7 +9834,7 @@
         <v>33</v>
       </c>
       <c r="Q125" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="R125" s="7"/>
     </row>
@@ -9839,7 +9843,7 @@
         <v>125</v>
       </c>
       <c r="B126" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>22</v>
@@ -9891,7 +9895,7 @@
         <v>33</v>
       </c>
       <c r="Q126" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="R126" s="7"/>
     </row>
@@ -9900,7 +9904,7 @@
         <v>126</v>
       </c>
       <c r="B127" s="7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>22</v>
@@ -9952,7 +9956,7 @@
         <v>33</v>
       </c>
       <c r="Q127" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="R127" s="7"/>
     </row>
@@ -9961,7 +9965,7 @@
         <v>127</v>
       </c>
       <c r="B128" s="7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>22</v>
@@ -10013,7 +10017,7 @@
         <v>33</v>
       </c>
       <c r="Q128" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="R128" s="7"/>
     </row>
@@ -10022,7 +10026,7 @@
         <v>128</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>22</v>
@@ -10074,7 +10078,7 @@
         <v>24</v>
       </c>
       <c r="Q129" s="7" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="R129" s="7" t="s">
         <v>26</v>
@@ -10085,7 +10089,7 @@
         <v>129</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>22</v>
@@ -10137,7 +10141,7 @@
         <v>24</v>
       </c>
       <c r="Q130" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="R130" s="7" t="s">
         <v>26</v>
@@ -10148,7 +10152,7 @@
         <v>130</v>
       </c>
       <c r="B131" s="7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>22</v>
@@ -10200,7 +10204,7 @@
         <v>33</v>
       </c>
       <c r="Q131" s="7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="R131" s="7"/>
     </row>
@@ -10209,7 +10213,7 @@
         <v>131</v>
       </c>
       <c r="B132" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>22</v>
@@ -10221,7 +10225,7 @@
         <v>7800</v>
       </c>
       <c r="F132" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G132" s="9" t="n">
         <v>5000</v>
@@ -10261,7 +10265,7 @@
         <v>33</v>
       </c>
       <c r="Q132" s="7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="R132" s="7"/>
     </row>
@@ -10270,7 +10274,7 @@
         <v>132</v>
       </c>
       <c r="B133" s="7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>22</v>
@@ -10322,7 +10326,7 @@
         <v>24</v>
       </c>
       <c r="Q133" s="7" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="R133" s="7" t="s">
         <v>26</v>
@@ -10333,7 +10337,7 @@
         <v>133</v>
       </c>
       <c r="B134" s="7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>28</v>
@@ -10385,7 +10389,7 @@
         <v>33</v>
       </c>
       <c r="Q134" s="7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="R134" s="7"/>
     </row>
@@ -10394,7 +10398,7 @@
         <v>134</v>
       </c>
       <c r="B135" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>22</v>
@@ -10446,7 +10450,7 @@
         <v>33</v>
       </c>
       <c r="Q135" s="7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="R135" s="7"/>
     </row>
@@ -10455,7 +10459,7 @@
         <v>135</v>
       </c>
       <c r="B136" s="7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C136" s="6" t="s">
         <v>22</v>
@@ -10507,7 +10511,7 @@
         <v>33</v>
       </c>
       <c r="Q136" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="R136" s="7"/>
     </row>
@@ -10516,7 +10520,7 @@
         <v>136</v>
       </c>
       <c r="B137" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C137" s="6" t="s">
         <v>22</v>
@@ -10568,7 +10572,7 @@
         <v>33</v>
       </c>
       <c r="Q137" s="7" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="R137" s="7"/>
     </row>
@@ -10577,7 +10581,7 @@
         <v>138</v>
       </c>
       <c r="B138" s="7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C138" s="6" t="s">
         <v>22</v>
@@ -10629,7 +10633,7 @@
         <v>33</v>
       </c>
       <c r="Q138" s="7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="R138" s="7"/>
     </row>
@@ -10638,7 +10642,7 @@
         <v>139</v>
       </c>
       <c r="B139" s="7" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C139" s="6" t="s">
         <v>28</v>
@@ -10690,7 +10694,7 @@
         <v>33</v>
       </c>
       <c r="Q139" s="7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="R139" s="7"/>
     </row>
@@ -10699,7 +10703,7 @@
         <v>140</v>
       </c>
       <c r="B140" s="7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C140" s="6" t="s">
         <v>22</v>
@@ -10751,7 +10755,7 @@
         <v>33</v>
       </c>
       <c r="Q140" s="7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="R140" s="7"/>
     </row>
@@ -10760,7 +10764,7 @@
         <v>142</v>
       </c>
       <c r="B141" s="7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C141" s="6" t="s">
         <v>22</v>
@@ -10812,7 +10816,7 @@
         <v>24</v>
       </c>
       <c r="Q141" s="7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="R141" s="7" t="s">
         <v>26</v>
@@ -10823,7 +10827,7 @@
         <v>143</v>
       </c>
       <c r="B142" s="7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C142" s="6" t="s">
         <v>22</v>
@@ -10875,7 +10879,7 @@
         <v>24</v>
       </c>
       <c r="Q142" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="R142" s="7" t="s">
         <v>26</v>
@@ -10886,7 +10890,7 @@
         <v>144</v>
       </c>
       <c r="B143" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C143" s="6" t="s">
         <v>22</v>
@@ -10938,7 +10942,7 @@
         <v>24</v>
       </c>
       <c r="Q143" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="R143" s="7" t="s">
         <v>26</v>
@@ -10949,7 +10953,7 @@
         <v>145</v>
       </c>
       <c r="B144" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C144" s="6" t="s">
         <v>28</v>
@@ -11001,7 +11005,7 @@
         <v>33</v>
       </c>
       <c r="Q144" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="R144" s="7"/>
     </row>
@@ -11010,7 +11014,7 @@
         <v>146</v>
       </c>
       <c r="B145" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C145" s="6" t="s">
         <v>22</v>
@@ -11022,7 +11026,7 @@
         <v>105788</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G145" s="9" t="n">
         <v>82000</v>
@@ -11062,7 +11066,7 @@
         <v>33</v>
       </c>
       <c r="Q145" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="R145" s="7"/>
     </row>
@@ -11071,7 +11075,7 @@
         <v>147</v>
       </c>
       <c r="B146" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C146" s="6" t="s">
         <v>22</v>
@@ -11083,7 +11087,7 @@
         <v>245700</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G146" s="9" t="n">
         <v>225000</v>
@@ -11123,7 +11127,7 @@
         <v>33</v>
       </c>
       <c r="Q146" s="7" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="R146" s="7"/>
     </row>
@@ -11132,7 +11136,7 @@
         <v>148</v>
       </c>
       <c r="B147" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C147" s="6" t="s">
         <v>28</v>
@@ -11144,7 +11148,7 @@
         <v>650</v>
       </c>
       <c r="F147" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G147" s="9" t="n">
         <v>360</v>
@@ -11184,7 +11188,7 @@
         <v>33</v>
       </c>
       <c r="Q147" s="7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="R147" s="7"/>
     </row>
@@ -11193,7 +11197,7 @@
         <v>149</v>
       </c>
       <c r="B148" s="7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C148" s="6" t="s">
         <v>22</v>
@@ -11205,7 +11209,7 @@
         <v>1754</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G148" s="9" t="n">
         <v>1380</v>
@@ -11245,7 +11249,7 @@
         <v>33</v>
       </c>
       <c r="Q148" s="7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="R148" s="7"/>
     </row>
@@ -11254,7 +11258,7 @@
         <v>150</v>
       </c>
       <c r="B149" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C149" s="6" t="s">
         <v>22</v>
@@ -11306,7 +11310,7 @@
         <v>33</v>
       </c>
       <c r="Q149" s="7" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="R149" s="7"/>
     </row>
@@ -11315,7 +11319,7 @@
         <v>151</v>
       </c>
       <c r="B150" s="7" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C150" s="6" t="s">
         <v>22</v>
@@ -11367,7 +11371,7 @@
         <v>33</v>
       </c>
       <c r="Q150" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="R150" s="7"/>
     </row>
@@ -11376,7 +11380,7 @@
         <v>152</v>
       </c>
       <c r="B151" s="7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C151" s="6" t="s">
         <v>22</v>
@@ -11428,7 +11432,7 @@
         <v>33</v>
       </c>
       <c r="Q151" s="7" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="R151" s="7"/>
     </row>
@@ -11437,7 +11441,7 @@
         <v>153</v>
       </c>
       <c r="B152" s="7" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C152" s="6" t="s">
         <v>22</v>
@@ -11489,7 +11493,7 @@
         <v>33</v>
       </c>
       <c r="Q152" s="7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="R152" s="7"/>
     </row>
@@ -11498,7 +11502,7 @@
         <v>154</v>
       </c>
       <c r="B153" s="7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C153" s="6" t="s">
         <v>22</v>
@@ -11550,7 +11554,7 @@
         <v>24</v>
       </c>
       <c r="Q153" s="7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="R153" s="7" t="s">
         <v>26</v>
@@ -11561,7 +11565,7 @@
         <v>155</v>
       </c>
       <c r="B154" s="7" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C154" s="6" t="s">
         <v>22</v>
@@ -11573,7 +11577,7 @@
         <v>748</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G154" s="9" t="n">
         <v>450</v>
@@ -11613,7 +11617,7 @@
         <v>33</v>
       </c>
       <c r="Q154" s="7" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="R154" s="7"/>
     </row>
@@ -11622,7 +11626,7 @@
         <v>156</v>
       </c>
       <c r="B155" s="7" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>22</v>
@@ -11634,7 +11638,7 @@
         <v>748</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G155" s="9" t="n">
         <v>450</v>
@@ -11674,7 +11678,7 @@
         <v>33</v>
       </c>
       <c r="Q155" s="7" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="R155" s="7"/>
     </row>
@@ -11683,7 +11687,7 @@
         <v>157</v>
       </c>
       <c r="B156" s="7" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C156" s="6" t="s">
         <v>22</v>
@@ -11695,7 +11699,7 @@
         <v>748</v>
       </c>
       <c r="F156" s="7" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G156" s="9" t="n">
         <v>400</v>
@@ -11735,7 +11739,7 @@
         <v>33</v>
       </c>
       <c r="Q156" s="7" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="R156" s="7"/>
     </row>
@@ -11744,7 +11748,7 @@
         <v>158</v>
       </c>
       <c r="B157" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C157" s="6" t="s">
         <v>28</v>
@@ -11756,7 +11760,7 @@
         <v>311</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G157" s="9" t="n">
         <v>203</v>
@@ -11796,7 +11800,7 @@
         <v>33</v>
       </c>
       <c r="Q157" s="7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="R157" s="7"/>
     </row>
@@ -11805,7 +11809,7 @@
         <v>159</v>
       </c>
       <c r="B158" s="7" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C158" s="6" t="s">
         <v>28</v>
@@ -11817,7 +11821,7 @@
         <v>325</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G158" s="9" t="n">
         <v>160</v>
@@ -11857,7 +11861,7 @@
         <v>24</v>
       </c>
       <c r="Q158" s="7" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="R158" s="7" t="s">
         <v>26</v>
@@ -11868,7 +11872,7 @@
         <v>160</v>
       </c>
       <c r="B159" s="7" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C159" s="6" t="s">
         <v>28</v>
@@ -11880,7 +11884,7 @@
         <v>117</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G159" s="9" t="n">
         <v>65</v>
@@ -11920,7 +11924,7 @@
         <v>24</v>
       </c>
       <c r="Q159" s="7" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="R159" s="7" t="s">
         <v>26</v>
@@ -11931,7 +11935,7 @@
         <v>161</v>
       </c>
       <c r="B160" s="7" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C160" s="6" t="s">
         <v>28</v>
@@ -11983,7 +11987,7 @@
         <v>24</v>
       </c>
       <c r="Q160" s="7" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="R160" s="7" t="s">
         <v>26</v>
@@ -11994,7 +11998,7 @@
         <v>162</v>
       </c>
       <c r="B161" s="7" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C161" s="6" t="s">
         <v>28</v>
@@ -12046,7 +12050,7 @@
         <v>24</v>
       </c>
       <c r="Q161" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="R161" s="7" t="s">
         <v>26</v>
@@ -12057,7 +12061,7 @@
         <v>164</v>
       </c>
       <c r="B162" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C162" s="6" t="s">
         <v>22</v>
@@ -12069,7 +12073,7 @@
         <v>1209</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G162" s="9" t="n">
         <v>1450</v>
@@ -12109,7 +12113,7 @@
         <v>24</v>
       </c>
       <c r="Q162" s="7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="R162" s="7" t="s">
         <v>26</v>
@@ -12120,7 +12124,7 @@
         <v>165</v>
       </c>
       <c r="B163" s="7" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C163" s="6" t="s">
         <v>22</v>
@@ -12132,7 +12136,7 @@
         <v>1209</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="G163" s="9" t="n">
         <v>2248</v>
@@ -12172,7 +12176,7 @@
         <v>24</v>
       </c>
       <c r="Q163" s="7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="R163" s="7" t="s">
         <v>26</v>
@@ -12183,7 +12187,7 @@
         <v>166</v>
       </c>
       <c r="B164" s="7" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C164" s="6" t="s">
         <v>22</v>
@@ -12195,7 +12199,7 @@
         <v>3022</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G164" s="9" t="n">
         <v>2325</v>
@@ -12235,7 +12239,7 @@
         <v>24</v>
       </c>
       <c r="Q164" s="7" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="R164" s="7" t="s">
         <v>26</v>
@@ -12246,7 +12250,7 @@
         <v>167</v>
       </c>
       <c r="B165" s="7" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C165" s="6" t="s">
         <v>22</v>
@@ -12258,7 +12262,7 @@
         <v>6240</v>
       </c>
       <c r="F165" s="7" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G165" s="9" t="n">
         <v>4400</v>
@@ -12298,7 +12302,7 @@
         <v>24</v>
       </c>
       <c r="Q165" s="7" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="R165" s="7" t="s">
         <v>26</v>
@@ -12309,7 +12313,7 @@
         <v>168</v>
       </c>
       <c r="B166" s="7" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C166" s="6" t="s">
         <v>22</v>
@@ -12321,7 +12325,7 @@
         <v>7150</v>
       </c>
       <c r="F166" s="7" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G166" s="9" t="n">
         <v>4400</v>
@@ -12361,7 +12365,7 @@
         <v>24</v>
       </c>
       <c r="Q166" s="7" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="R166" s="7" t="s">
         <v>26</v>
@@ -12372,7 +12376,7 @@
         <v>177</v>
       </c>
       <c r="B167" s="7" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C167" s="6" t="s">
         <v>28</v>
@@ -12424,7 +12428,7 @@
         <v>24</v>
       </c>
       <c r="Q167" s="7" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="R167" s="7" t="s">
         <v>26</v>
@@ -12435,7 +12439,7 @@
         <v>179</v>
       </c>
       <c r="B168" s="7" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C168" s="6" t="s">
         <v>28</v>
@@ -12487,7 +12491,7 @@
         <v>24</v>
       </c>
       <c r="Q168" s="7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="R168" s="7" t="s">
         <v>26</v>
@@ -12498,7 +12502,7 @@
         <v>180</v>
       </c>
       <c r="B169" s="7" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C169" s="6" t="s">
         <v>28</v>
@@ -12550,7 +12554,7 @@
         <v>33</v>
       </c>
       <c r="Q169" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="R169" s="7"/>
     </row>
@@ -12559,7 +12563,7 @@
         <v>181</v>
       </c>
       <c r="B170" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C170" s="6" t="s">
         <v>28</v>
@@ -12611,7 +12615,7 @@
         <v>24</v>
       </c>
       <c r="Q170" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="R170" s="7" t="s">
         <v>26</v>
@@ -12622,7 +12626,7 @@
         <v>182</v>
       </c>
       <c r="B171" s="7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C171" s="6" t="s">
         <v>28</v>
@@ -12674,7 +12678,7 @@
         <v>24</v>
       </c>
       <c r="Q171" s="7" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="R171" s="7" t="s">
         <v>26</v>
@@ -12685,7 +12689,7 @@
         <v>183</v>
       </c>
       <c r="B172" s="7" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C172" s="6" t="s">
         <v>28</v>
@@ -12737,7 +12741,7 @@
         <v>33</v>
       </c>
       <c r="Q172" s="7" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="R172" s="7"/>
     </row>
@@ -12746,7 +12750,7 @@
         <v>184</v>
       </c>
       <c r="B173" s="7" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C173" s="6" t="s">
         <v>28</v>
@@ -12758,7 +12762,7 @@
         <v>3250</v>
       </c>
       <c r="F173" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G173" s="9" t="n">
         <v>2921</v>
@@ -12798,7 +12802,7 @@
         <v>33</v>
       </c>
       <c r="Q173" s="7" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="R173" s="7"/>
     </row>
@@ -12807,7 +12811,7 @@
         <v>185</v>
       </c>
       <c r="B174" s="7" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C174" s="6" t="s">
         <v>28</v>
@@ -12859,7 +12863,7 @@
         <v>33</v>
       </c>
       <c r="Q174" s="7" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="R174" s="7"/>
     </row>
@@ -12868,7 +12872,7 @@
         <v>186</v>
       </c>
       <c r="B175" s="7" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C175" s="6" t="s">
         <v>28</v>
@@ -12880,7 +12884,7 @@
         <v>4550</v>
       </c>
       <c r="F175" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G175" s="9" t="n">
         <v>7245</v>
@@ -12920,7 +12924,7 @@
         <v>33</v>
       </c>
       <c r="Q175" s="7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="R175" s="7"/>
     </row>
@@ -12929,7 +12933,7 @@
         <v>187</v>
       </c>
       <c r="B176" s="7" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C176" s="6" t="s">
         <v>28</v>
@@ -12941,7 +12945,7 @@
         <v>7150</v>
       </c>
       <c r="F176" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G176" s="9" t="n">
         <v>9900</v>
@@ -12981,7 +12985,7 @@
         <v>33</v>
       </c>
       <c r="Q176" s="7" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="R176" s="7"/>
     </row>
@@ -12990,7 +12994,7 @@
         <v>188</v>
       </c>
       <c r="B177" s="7" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C177" s="6" t="s">
         <v>28</v>
@@ -13042,7 +13046,7 @@
         <v>24</v>
       </c>
       <c r="Q177" s="7" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="R177" s="7" t="s">
         <v>26</v>
@@ -13053,7 +13057,7 @@
         <v>189</v>
       </c>
       <c r="B178" s="7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C178" s="6" t="s">
         <v>28</v>
@@ -13065,7 +13069,7 @@
         <v>9750</v>
       </c>
       <c r="F178" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G178" s="9" t="n">
         <v>10458</v>
@@ -13105,7 +13109,7 @@
         <v>33</v>
       </c>
       <c r="Q178" s="7" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="R178" s="7"/>
     </row>
@@ -13114,7 +13118,7 @@
         <v>190</v>
       </c>
       <c r="B179" s="7" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C179" s="6" t="s">
         <v>28</v>
@@ -13126,7 +13130,7 @@
         <v>2340</v>
       </c>
       <c r="F179" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G179" s="9" t="n">
         <v>891</v>
@@ -13166,7 +13170,7 @@
         <v>33</v>
       </c>
       <c r="Q179" s="7" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="R179" s="7"/>
     </row>
@@ -13175,7 +13179,7 @@
         <v>191</v>
       </c>
       <c r="B180" s="7" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C180" s="6" t="s">
         <v>28</v>
@@ -13187,7 +13191,7 @@
         <v>3640</v>
       </c>
       <c r="F180" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G180" s="9" t="n">
         <v>1440</v>
@@ -13227,7 +13231,7 @@
         <v>33</v>
       </c>
       <c r="Q180" s="7" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="R180" s="7"/>
     </row>
@@ -13236,7 +13240,7 @@
         <v>192</v>
       </c>
       <c r="B181" s="7" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C181" s="6" t="s">
         <v>28</v>
@@ -13248,7 +13252,7 @@
         <v>1950</v>
       </c>
       <c r="F181" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G181" s="9" t="n">
         <v>7685</v>
@@ -13288,7 +13292,7 @@
         <v>33</v>
       </c>
       <c r="Q181" s="7" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="R181" s="7"/>
     </row>
@@ -13297,7 +13301,7 @@
         <v>193</v>
       </c>
       <c r="B182" s="7" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C182" s="6" t="s">
         <v>28</v>
@@ -13309,7 +13313,7 @@
         <v>5850</v>
       </c>
       <c r="F182" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G182" s="9" t="n">
         <v>11948</v>
@@ -13349,7 +13353,7 @@
         <v>24</v>
       </c>
       <c r="Q182" s="7" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="R182" s="7" t="s">
         <v>26</v>
@@ -13360,7 +13364,7 @@
         <v>194</v>
       </c>
       <c r="B183" s="7" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C183" s="6" t="s">
         <v>28</v>
@@ -13372,7 +13376,7 @@
         <v>1950</v>
       </c>
       <c r="F183" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G183" s="9" t="n">
         <v>7387</v>
@@ -13412,7 +13416,7 @@
         <v>33</v>
       </c>
       <c r="Q183" s="7" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="R183" s="7"/>
     </row>
@@ -13421,7 +13425,7 @@
         <v>195</v>
       </c>
       <c r="B184" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C184" s="6" t="s">
         <v>28</v>
@@ -13433,7 +13437,7 @@
         <v>5850</v>
       </c>
       <c r="F184" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G184" s="9" t="n">
         <v>12788</v>
@@ -13473,7 +13477,7 @@
         <v>24</v>
       </c>
       <c r="Q184" s="7" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="R184" s="7" t="s">
         <v>26</v>
@@ -13484,7 +13488,7 @@
         <v>196</v>
       </c>
       <c r="B185" s="7" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C185" s="6" t="s">
         <v>28</v>
@@ -13496,7 +13500,7 @@
         <v>4550</v>
       </c>
       <c r="F185" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G185" s="9" t="n">
         <v>3006</v>
@@ -13536,7 +13540,7 @@
         <v>33</v>
       </c>
       <c r="Q185" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="R185" s="7"/>
     </row>
@@ -13545,7 +13549,7 @@
         <v>197</v>
       </c>
       <c r="B186" s="7" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C186" s="6" t="s">
         <v>28</v>
@@ -13557,7 +13561,7 @@
         <v>17940</v>
       </c>
       <c r="F186" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G186" s="9" t="n">
         <v>5500</v>
@@ -13597,7 +13601,7 @@
         <v>33</v>
       </c>
       <c r="Q186" s="7" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="R186" s="7"/>
     </row>
@@ -13606,7 +13610,7 @@
         <v>198</v>
       </c>
       <c r="B187" s="7" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C187" s="6" t="s">
         <v>28</v>
@@ -13618,7 +13622,7 @@
         <v>18850</v>
       </c>
       <c r="F187" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G187" s="9" t="n">
         <v>5500</v>
@@ -13658,7 +13662,7 @@
         <v>33</v>
       </c>
       <c r="Q187" s="7" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="R187" s="7"/>
     </row>
@@ -13667,7 +13671,7 @@
         <v>199</v>
       </c>
       <c r="B188" s="7" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C188" s="6" t="s">
         <v>28</v>
@@ -13679,7 +13683,7 @@
         <v>19500</v>
       </c>
       <c r="F188" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G188" s="9" t="n">
         <v>6200</v>
@@ -13719,7 +13723,7 @@
         <v>33</v>
       </c>
       <c r="Q188" s="7" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="R188" s="7"/>
     </row>
@@ -13728,7 +13732,7 @@
         <v>200</v>
       </c>
       <c r="B189" s="7" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C189" s="6" t="s">
         <v>28</v>
@@ -13740,7 +13744,7 @@
         <v>20800</v>
       </c>
       <c r="F189" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G189" s="9" t="n">
         <v>6875</v>
@@ -13780,7 +13784,7 @@
         <v>33</v>
       </c>
       <c r="Q189" s="7" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="R189" s="7"/>
     </row>
@@ -13789,7 +13793,7 @@
         <v>201</v>
       </c>
       <c r="B190" s="7" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C190" s="6" t="s">
         <v>28</v>
@@ -13801,7 +13805,7 @@
         <v>22750</v>
       </c>
       <c r="F190" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G190" s="9" t="n">
         <v>8750</v>
@@ -13841,7 +13845,7 @@
         <v>33</v>
       </c>
       <c r="Q190" s="7" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="R190" s="7"/>
     </row>
@@ -13850,7 +13854,7 @@
         <v>202</v>
       </c>
       <c r="B191" s="7" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C191" s="6" t="s">
         <v>28</v>
@@ -13902,7 +13906,7 @@
         <v>24</v>
       </c>
       <c r="Q191" s="7" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="R191" s="7" t="s">
         <v>26</v>
@@ -13913,7 +13917,7 @@
         <v>204</v>
       </c>
       <c r="B192" s="7" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C192" s="6" t="s">
         <v>28</v>
@@ -13965,7 +13969,7 @@
         <v>33</v>
       </c>
       <c r="Q192" s="7" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="R192" s="7"/>
     </row>
@@ -13974,7 +13978,7 @@
         <v>205</v>
       </c>
       <c r="B193" s="7" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C193" s="6" t="s">
         <v>28</v>
@@ -14026,7 +14030,7 @@
         <v>33</v>
       </c>
       <c r="Q193" s="7" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="R193" s="7"/>
     </row>
@@ -14035,7 +14039,7 @@
         <v>206</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C194" s="6" t="s">
         <v>28</v>
@@ -14087,7 +14091,7 @@
         <v>33</v>
       </c>
       <c r="Q194" s="7" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="R194" s="7"/>
     </row>
@@ -14096,7 +14100,7 @@
         <v>207</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C195" s="6" t="s">
         <v>28</v>
@@ -14148,7 +14152,7 @@
         <v>33</v>
       </c>
       <c r="Q195" s="7" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="R195" s="7"/>
     </row>
@@ -14157,7 +14161,7 @@
         <v>208</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C196" s="6" t="s">
         <v>28</v>
@@ -14169,7 +14173,7 @@
         <v>1690</v>
       </c>
       <c r="F196" s="7" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G196" s="9" t="n">
         <v>2900</v>
@@ -14209,7 +14213,7 @@
         <v>33</v>
       </c>
       <c r="Q196" s="7" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="R196" s="7"/>
     </row>
@@ -14218,7 +14222,7 @@
         <v>209</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C197" s="6" t="s">
         <v>28</v>
@@ -14270,7 +14274,7 @@
         <v>33</v>
       </c>
       <c r="Q197" s="7" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="R197" s="7"/>
     </row>
@@ -14279,7 +14283,7 @@
         <v>210</v>
       </c>
       <c r="B198" s="7" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C198" s="6" t="s">
         <v>28</v>
@@ -14331,7 +14335,7 @@
         <v>24</v>
       </c>
       <c r="Q198" s="7" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="R198" s="7" t="s">
         <v>26</v>
@@ -14342,7 +14346,7 @@
         <v>211</v>
       </c>
       <c r="B199" s="7" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C199" s="6" t="s">
         <v>28</v>
@@ -14394,7 +14398,7 @@
         <v>24</v>
       </c>
       <c r="Q199" s="7" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="R199" s="7" t="s">
         <v>26</v>
@@ -14405,7 +14409,7 @@
         <v>212</v>
       </c>
       <c r="B200" s="7" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C200" s="6" t="s">
         <v>28</v>
@@ -14457,7 +14461,7 @@
         <v>33</v>
       </c>
       <c r="Q200" s="7" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="R200" s="7"/>
     </row>
@@ -14466,7 +14470,7 @@
         <v>213</v>
       </c>
       <c r="B201" s="7" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C201" s="6" t="s">
         <v>28</v>
@@ -14478,7 +14482,7 @@
         <v>455</v>
       </c>
       <c r="F201" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G201" s="9" t="n">
         <v>813</v>
@@ -14518,7 +14522,7 @@
         <v>33</v>
       </c>
       <c r="Q201" s="7" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="R201" s="7"/>
     </row>
@@ -14527,7 +14531,7 @@
         <v>214</v>
       </c>
       <c r="B202" s="7" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C202" s="6" t="s">
         <v>28</v>
@@ -14539,7 +14543,7 @@
         <v>494</v>
       </c>
       <c r="F202" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G202" s="9" t="n">
         <v>813</v>
@@ -14579,7 +14583,7 @@
         <v>24</v>
       </c>
       <c r="Q202" s="7" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="R202" s="7" t="s">
         <v>26</v>
@@ -14590,7 +14594,7 @@
         <v>215</v>
       </c>
       <c r="B203" s="7" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C203" s="6" t="s">
         <v>28</v>
@@ -14602,7 +14606,7 @@
         <v>585</v>
       </c>
       <c r="F203" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G203" s="9" t="n">
         <v>1806</v>
@@ -14642,7 +14646,7 @@
         <v>33</v>
       </c>
       <c r="Q203" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="R203" s="7"/>
     </row>
@@ -14651,7 +14655,7 @@
         <v>216</v>
       </c>
       <c r="B204" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C204" s="6" t="s">
         <v>28</v>
@@ -14663,7 +14667,7 @@
         <v>715</v>
       </c>
       <c r="F204" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G204" s="9" t="n">
         <v>1806</v>
@@ -14703,7 +14707,7 @@
         <v>33</v>
       </c>
       <c r="Q204" s="7" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="R204" s="7"/>
     </row>
@@ -14712,7 +14716,7 @@
         <v>217</v>
       </c>
       <c r="B205" s="7" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C205" s="6" t="s">
         <v>28</v>
@@ -14724,7 +14728,7 @@
         <v>910</v>
       </c>
       <c r="F205" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G205" s="9" t="n">
         <v>5143</v>
@@ -14764,7 +14768,7 @@
         <v>24</v>
       </c>
       <c r="Q205" s="7" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="R205" s="7" t="s">
         <v>26</v>
@@ -14775,7 +14779,7 @@
         <v>218</v>
       </c>
       <c r="B206" s="7" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C206" s="6" t="s">
         <v>28</v>
@@ -14787,7 +14791,7 @@
         <v>1170</v>
       </c>
       <c r="F206" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G206" s="9" t="n">
         <v>5143</v>
@@ -14827,7 +14831,7 @@
         <v>33</v>
       </c>
       <c r="Q206" s="7" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="R206" s="7"/>
     </row>
@@ -14836,7 +14840,7 @@
         <v>219</v>
       </c>
       <c r="B207" s="7" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C207" s="6" t="s">
         <v>28</v>
@@ -14848,7 +14852,7 @@
         <v>1040</v>
       </c>
       <c r="F207" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G207" s="9" t="n">
         <v>2037</v>
@@ -14888,7 +14892,7 @@
         <v>24</v>
       </c>
       <c r="Q207" s="7" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="R207" s="7" t="s">
         <v>26</v>
@@ -14899,7 +14903,7 @@
         <v>220</v>
       </c>
       <c r="B208" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C208" s="6" t="s">
         <v>28</v>
@@ -14911,7 +14915,7 @@
         <v>1430</v>
       </c>
       <c r="F208" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G208" s="9" t="n">
         <v>3728</v>
@@ -14951,7 +14955,7 @@
         <v>24</v>
       </c>
       <c r="Q208" s="7" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="R208" s="7" t="s">
         <v>26</v>
@@ -14962,7 +14966,7 @@
         <v>221</v>
       </c>
       <c r="B209" s="7" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C209" s="6" t="s">
         <v>28</v>
@@ -14974,7 +14978,7 @@
         <v>1950</v>
       </c>
       <c r="F209" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G209" s="9" t="n">
         <v>3728</v>
@@ -15014,7 +15018,7 @@
         <v>33</v>
       </c>
       <c r="Q209" s="7" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="R209" s="7"/>
     </row>
@@ -15023,7 +15027,7 @@
         <v>222</v>
       </c>
       <c r="B210" s="7" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C210" s="6" t="s">
         <v>28</v>
@@ -15075,7 +15079,7 @@
         <v>33</v>
       </c>
       <c r="Q210" s="7" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="R210" s="7"/>
     </row>
@@ -15084,7 +15088,7 @@
         <v>223</v>
       </c>
       <c r="B211" s="7" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C211" s="6" t="s">
         <v>28</v>
@@ -15096,7 +15100,7 @@
         <v>30940</v>
       </c>
       <c r="F211" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G211" s="9" t="n">
         <v>31300</v>
@@ -15136,7 +15140,7 @@
         <v>33</v>
       </c>
       <c r="Q211" s="7" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="R211" s="7"/>
     </row>
@@ -15145,7 +15149,7 @@
         <v>224</v>
       </c>
       <c r="B212" s="7" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C212" s="6" t="s">
         <v>28</v>
@@ -15197,7 +15201,7 @@
         <v>24</v>
       </c>
       <c r="Q212" s="7" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="R212" s="7" t="s">
         <v>26</v>
@@ -15208,7 +15212,7 @@
         <v>225</v>
       </c>
       <c r="B213" s="7" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C213" s="6" t="s">
         <v>28</v>
@@ -15260,7 +15264,7 @@
         <v>33</v>
       </c>
       <c r="Q213" s="7" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="R213" s="7"/>
     </row>
@@ -15269,7 +15273,7 @@
         <v>226</v>
       </c>
       <c r="B214" s="7" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C214" s="6" t="s">
         <v>28</v>
@@ -15321,7 +15325,7 @@
         <v>24</v>
       </c>
       <c r="Q214" s="7" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="R214" s="7" t="s">
         <v>26</v>
@@ -15332,7 +15336,7 @@
         <v>227</v>
       </c>
       <c r="B215" s="7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C215" s="6" t="s">
         <v>28</v>
@@ -15384,7 +15388,7 @@
         <v>24</v>
       </c>
       <c r="Q215" s="7" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="R215" s="7" t="s">
         <v>26</v>
@@ -15395,7 +15399,7 @@
         <v>228</v>
       </c>
       <c r="B216" s="7" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C216" s="6" t="s">
         <v>28</v>
@@ -15447,7 +15451,7 @@
         <v>24</v>
       </c>
       <c r="Q216" s="7" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="R216" s="7" t="s">
         <v>26</v>
@@ -15458,7 +15462,7 @@
         <v>229</v>
       </c>
       <c r="B217" s="7" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C217" s="6" t="s">
         <v>28</v>
@@ -15510,7 +15514,7 @@
         <v>24</v>
       </c>
       <c r="Q217" s="7" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="R217" s="7" t="s">
         <v>26</v>
@@ -15521,7 +15525,7 @@
         <v>230</v>
       </c>
       <c r="B218" s="7" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C218" s="6" t="s">
         <v>28</v>
@@ -15533,7 +15537,7 @@
         <v>9750</v>
       </c>
       <c r="F218" s="7" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G218" s="9" t="n">
         <v>5950</v>
@@ -15573,7 +15577,7 @@
         <v>24</v>
       </c>
       <c r="Q218" s="7" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="R218" s="7" t="s">
         <v>26</v>
@@ -15584,7 +15588,7 @@
         <v>231</v>
       </c>
       <c r="B219" s="7" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C219" s="6" t="s">
         <v>28</v>
@@ -15596,7 +15600,7 @@
         <v>12350</v>
       </c>
       <c r="F219" s="7" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G219" s="9" t="n">
         <v>5950</v>
@@ -15636,7 +15640,7 @@
         <v>33</v>
       </c>
       <c r="Q219" s="7" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="R219" s="7"/>
     </row>
@@ -15645,10 +15649,10 @@
         <v>233</v>
       </c>
       <c r="B220" s="7" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C220" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D220" s="6" t="n">
         <v>2</v>
@@ -15657,7 +15661,7 @@
         <v>52000</v>
       </c>
       <c r="F220" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G220" s="9" t="n">
         <v>40000</v>
@@ -15697,7 +15701,7 @@
         <v>33</v>
       </c>
       <c r="Q220" s="7" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="R220" s="7"/>
     </row>
@@ -15706,7 +15710,7 @@
         <v>234</v>
       </c>
       <c r="B221" s="7" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C221" s="6" t="s">
         <v>22</v>
@@ -15758,7 +15762,7 @@
         <v>24</v>
       </c>
       <c r="Q221" s="7" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="R221" s="7" t="s">
         <v>26</v>
@@ -15769,7 +15773,7 @@
         <v>235</v>
       </c>
       <c r="B222" s="7" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C222" s="6" t="s">
         <v>28</v>
@@ -15821,7 +15825,7 @@
         <v>24</v>
       </c>
       <c r="Q222" s="7" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="R222" s="7" t="s">
         <v>26</v>
@@ -15832,7 +15836,7 @@
         <v>236</v>
       </c>
       <c r="B223" s="7" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C223" s="6" t="s">
         <v>22</v>
@@ -15884,7 +15888,7 @@
         <v>24</v>
       </c>
       <c r="Q223" s="7" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="R223" s="7" t="s">
         <v>26</v>
@@ -15895,7 +15899,7 @@
         <v>237</v>
       </c>
       <c r="B224" s="7" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C224" s="6" t="s">
         <v>28</v>
@@ -15947,7 +15951,7 @@
         <v>24</v>
       </c>
       <c r="Q224" s="7" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="R224" s="7" t="s">
         <v>26</v>
@@ -15958,7 +15962,7 @@
         <v>238</v>
       </c>
       <c r="B225" s="7" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C225" s="6" t="s">
         <v>28</v>
@@ -15970,7 +15974,7 @@
         <v>8450</v>
       </c>
       <c r="F225" s="7" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="G225" s="9" t="n">
         <v>7800</v>
@@ -16010,7 +16014,7 @@
         <v>33</v>
       </c>
       <c r="Q225" s="7" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="R225" s="7"/>
     </row>
@@ -16019,10 +16023,10 @@
         <v>239</v>
       </c>
       <c r="B226" s="7" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D226" s="6" t="n">
         <v>50</v>
@@ -16031,7 +16035,7 @@
         <v>65000</v>
       </c>
       <c r="F226" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G226" s="9" t="n">
         <v>44000</v>
@@ -16071,7 +16075,7 @@
         <v>33</v>
       </c>
       <c r="Q226" s="7" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="R226" s="7"/>
     </row>
@@ -16080,7 +16084,7 @@
         <v>240</v>
       </c>
       <c r="B227" s="7" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C227" s="6" t="s">
         <v>28</v>
@@ -16132,13 +16136,13 @@
         <v>33</v>
       </c>
       <c r="Q227" s="7" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="R227" s="7"/>
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B228" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L228" s="11" t="n">
         <f aca="false">SUM(L6:L227)</f>
@@ -16146,7 +16150,7 @@
       </c>
       <c r="M228" s="11" t="n">
         <f aca="false">SUM(M6:M227)</f>
-        <v>15769745</v>
+        <v>15639815</v>
       </c>
       <c r="N228" s="11" t="n">
         <f aca="false">SUM(N6:N227)</f>
@@ -16199,12 +16203,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="12" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B3" s="11" t="n">
         <f aca="false">COUNTA('Rate Check'!A6:A227)</f>
@@ -16213,7 +16217,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B4" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"LOSS")</f>
@@ -16222,7 +16226,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B5" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"THIN / RISK")</f>
@@ -16231,7 +16235,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B6" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"OK")</f>
@@ -16240,7 +16244,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B7" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!J6:J227,"OVERPRICED?")</f>
@@ -16249,7 +16253,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B8" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!O6:O227,"YES")</f>
@@ -16261,7 +16265,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B10" s="11" t="n">
         <f aca="false">'Rate Check'!L228</f>
@@ -16270,7 +16274,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B11" s="11" t="n">
         <f aca="false">'Rate Check'!N228</f>
@@ -16279,7 +16283,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B12" s="11" t="n">
         <f aca="false">B10-B11</f>
@@ -16288,7 +16292,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B13" s="14" t="n">
         <f aca="false">IF(B10=0,0,B12/B10)</f>
@@ -16297,7 +16301,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B14" s="11" t="n">
         <f aca="false">SUMPRODUCT(('Rate Check'!E6:E227&lt;'Rate Check'!H6:H227)*('Rate Check'!H6:H227-'Rate Check'!E6:E227)*'Rate Check'!D6:D227)</f>
@@ -16309,20 +16313,20 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B16" s="11" t="n">
         <f aca="false">'Rate Check'!M228</f>
-        <v>15769745</v>
+        <v>15639815</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B17" s="14" t="n">
         <f aca="false">IF(B16=0,0,(B16-B11)/B16)</f>
-        <v>0.202370995853135</v>
+        <v>0.195744578820146</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16330,7 +16334,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B19" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!P6:P227,"V")</f>
@@ -16339,7 +16343,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B20" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!P6:P227,"S")</f>
@@ -16348,7 +16352,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B21" s="11" t="n">
         <f aca="false">COUNTIF('Rate Check'!P6:P227,"N")</f>
@@ -16380,247 +16384,247 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
   </sheetData>
